--- a/company_radar_output.xlsx
+++ b/company_radar_output.xlsx
@@ -851,13 +851,13 @@
         <v>48.40296980201639</v>
       </c>
       <c r="AP2" t="n">
-        <v>24804700</v>
+        <v>24901800</v>
       </c>
       <c r="AQ2" t="n">
-        <v>18033748</v>
+        <v>18035690</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.375460054116316</v>
+        <v>1.380695720540772</v>
       </c>
       <c r="AS2" t="n">
         <v>-0.1432771718372023</v>
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>0.1275023967027664</v>
+        <v>0.1275022327899933</v>
       </c>
       <c r="AA3" t="n">
-        <v>33688585106.47998</v>
+        <v>33688541797.57324</v>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
@@ -1045,13 +1045,13 @@
         <v>44.6258487866469</v>
       </c>
       <c r="AP3" t="n">
-        <v>85631007</v>
+        <v>85627007</v>
       </c>
       <c r="AQ3" t="n">
-        <v>178253930.26</v>
+        <v>178253850.26</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.4803877641020267</v>
+        <v>0.480365539791174</v>
       </c>
       <c r="AS3" t="n">
         <v>-0.1851568579035451</v>
@@ -1066,13 +1066,13 @@
         <v>1.387044466912197</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.907304171734348</v>
+        <v>1.907303793290557</v>
       </c>
       <c r="AX3" t="n">
         <v>1.230366367712243</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.526157300528979</v>
+        <v>2.526158692287994</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
@@ -1241,13 +1241,13 @@
         <v>50.88631042013413</v>
       </c>
       <c r="AP4" t="n">
-        <v>48246400</v>
+        <v>48298100</v>
       </c>
       <c r="AQ4" t="n">
-        <v>51911590</v>
+        <v>51912624</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9293955357560807</v>
+        <v>0.9303729281725386</v>
       </c>
       <c r="AS4" t="n">
         <v>-0.02939767209789301</v>
@@ -1410,40 +1410,40 @@
         <v>370.8261206054688</v>
       </c>
       <c r="AG5" t="n">
-        <v>315.8090982055664</v>
+        <v>315.8090985870361</v>
       </c>
       <c r="AH5" t="n">
         <v>-0.02943729240414894</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.1396441891862052</v>
+        <v>0.1396441878096149</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.1742097447873103</v>
+        <v>0.1742097433689678</v>
       </c>
       <c r="AK5" t="n">
         <v>402.3796691894531</v>
       </c>
       <c r="AL5" t="n">
-        <v>173.864013671875</v>
+        <v>173.8639984130859</v>
       </c>
       <c r="AM5" t="n">
         <v>-0.1055462509149478</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.070066116967424</v>
+        <v>1.070066298642196</v>
       </c>
       <c r="AO5" t="n">
         <v>51.25972223020631</v>
       </c>
       <c r="AP5" t="n">
-        <v>25974800</v>
+        <v>25999300</v>
       </c>
       <c r="AQ5" t="n">
-        <v>33539852</v>
+        <v>33540342</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.7744458741201362</v>
+        <v>0.7751650236601643</v>
       </c>
       <c r="AS5" t="n">
         <v>0.003161607306750192</v>
@@ -1455,16 +1455,16 @@
         <v>0.1513689622359589</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.020469849018952</v>
+        <v>1.020470022092596</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.963887586939176</v>
+        <v>1.963887400722065</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1435141099292949</v>
+        <v>0.1435142208057276</v>
       </c>
       <c r="AY5" t="n">
-        <v>143.6036867727892</v>
+        <v>143.603700624549</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -1629,13 +1629,13 @@
         <v>50.98039124022075</v>
       </c>
       <c r="AP6" t="n">
-        <v>13258500</v>
+        <v>13301400</v>
       </c>
       <c r="AQ6" t="n">
-        <v>26932690</v>
+        <v>26933548</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.4922827983391188</v>
+        <v>0.4938599251758439</v>
       </c>
       <c r="AS6" t="n">
         <v>0.09788862731487957</v>
@@ -1825,13 +1825,13 @@
         <v>40.0199692887312</v>
       </c>
       <c r="AP7" t="n">
-        <v>32579500</v>
+        <v>32788100</v>
       </c>
       <c r="AQ7" t="n">
-        <v>30245858</v>
+        <v>30250030</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.077155754682178</v>
+        <v>1.083903057286224</v>
       </c>
       <c r="AS7" t="n">
         <v>-0.2630938202317127</v>
@@ -2015,13 +2015,13 @@
         <v>45.73855602962526</v>
       </c>
       <c r="AP8" t="n">
-        <v>3159300</v>
+        <v>3160300</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2604018</v>
+        <v>2604038</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.213240461471464</v>
+        <v>1.213615162297939</v>
       </c>
       <c r="AS8" t="n">
         <v>-0.1460656518981024</v>
@@ -2184,25 +2184,25 @@
         <v>604.8063073730468</v>
       </c>
       <c r="AG9" t="n">
-        <v>645.4064831542969</v>
+        <v>645.4064825439453</v>
       </c>
       <c r="AH9" t="n">
         <v>-0.03622032821405818</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.09684820399501781</v>
+        <v>-0.09684820314092024</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.0629063649668109</v>
+        <v>-0.06290636408061501</v>
       </c>
       <c r="AK9" t="n">
-        <v>787.4192504882812</v>
+        <v>787.419189453125</v>
       </c>
       <c r="AL9" t="n">
         <v>525.233154296875</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.2597335865835078</v>
+        <v>-0.2597335292033006</v>
       </c>
       <c r="AN9" t="n">
         <v>0.1097928979643061</v>
@@ -2211,13 +2211,13 @@
         <v>53.53899664596091</v>
       </c>
       <c r="AP9" t="n">
-        <v>21705900</v>
+        <v>21750500</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17883844</v>
+        <v>17884736</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.21371557479477</v>
+        <v>1.216148787435274</v>
       </c>
       <c r="AS9" t="n">
         <v>-0.06346869164290336</v>
@@ -2226,16 +2226,16 @@
         <v>0.01563248744740897</v>
       </c>
       <c r="AU9" t="n">
-        <v>-0.1153633354598057</v>
+        <v>-0.1153634174035524</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.1804441780738748</v>
+        <v>-0.1804441077434721</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.7225263774552615</v>
+        <v>0.7225262221136828</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.1021973346349117</v>
+        <v>-0.1021974190359378</v>
       </c>
       <c r="AY9" t="n">
         <v>14.38108358286718</v>
@@ -2407,13 +2407,13 @@
         <v>50.06410542348838</v>
       </c>
       <c r="AP10" t="n">
-        <v>42128900</v>
+        <v>42194400</v>
       </c>
       <c r="AQ10" t="n">
-        <v>41452210</v>
+        <v>41453520</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.016324581970419</v>
+        <v>1.01787254737354</v>
       </c>
       <c r="AS10" t="n">
         <v>-0.08623111906047509</v>
@@ -2428,13 +2428,13 @@
         <v>-0.1984991719137187</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.5353138690615604</v>
+        <v>0.5353143296092888</v>
       </c>
       <c r="AX10" t="n">
         <v>-0.1706581093930165</v>
       </c>
       <c r="AY10" t="n">
-        <v>6603.448714115002</v>
+        <v>6603.444968995992</v>
       </c>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
@@ -2576,16 +2576,16 @@
         <v>186.372600402832</v>
       </c>
       <c r="AG11" t="n">
-        <v>199.0704570770264</v>
+        <v>199.0704573059082</v>
       </c>
       <c r="AH11" t="n">
         <v>-0.2473678857875212</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.2953750831134816</v>
+        <v>-0.2953750839236261</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0.0637857412929993</v>
+        <v>-0.06378574236941437</v>
       </c>
       <c r="AK11" t="n">
         <v>325.7593383789062</v>
@@ -2603,13 +2603,13 @@
         <v>14.89667012187238</v>
       </c>
       <c r="AP11" t="n">
-        <v>44166700</v>
+        <v>44273600</v>
       </c>
       <c r="AQ11" t="n">
-        <v>27420740</v>
+        <v>27422878</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.610704160427472</v>
+        <v>1.614476788322509</v>
       </c>
       <c r="AS11" t="n">
         <v>-0.3910041976409659</v>
@@ -2624,13 +2624,13 @@
         <v>-0.3839580958804084</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.9128475459422813</v>
+        <v>0.9128473469272249</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.27887188244104</v>
+        <v>-0.278871825871825</v>
       </c>
       <c r="AY11" t="n">
-        <v>2781.449937106862</v>
+        <v>2781.451170783875</v>
       </c>
       <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="n">
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>0.1275023967027664</v>
+        <v>0.1275022327899933</v>
       </c>
       <c r="AA12" t="n">
-        <v>495159440424.6602</v>
+        <v>495158803864.4141</v>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
@@ -2795,13 +2795,13 @@
         <v>37.68939820859566</v>
       </c>
       <c r="AP12" t="n">
-        <v>24957596</v>
+        <v>24957296</v>
       </c>
       <c r="AQ12" t="n">
-        <v>32118896.24</v>
+        <v>32118890.24</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.7770377852810051</v>
+        <v>0.7770285901384867</v>
       </c>
       <c r="AS12" t="n">
         <v>-0.0754716598415428</v>
@@ -2816,13 +2816,13 @@
         <v>-0.1438196160460328</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.1617097237685621</v>
+        <v>-0.1617096242990003</v>
       </c>
       <c r="AX12" t="n">
         <v>-0.299801143307051</v>
       </c>
       <c r="AY12" t="n">
-        <v>612.11764617143</v>
+        <v>612.1175422467029</v>
       </c>
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="n">
@@ -2987,13 +2987,13 @@
         <v>14.28570487774199</v>
       </c>
       <c r="AP13" t="n">
-        <v>11744600</v>
+        <v>11764200</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12128350</v>
+        <v>12128742</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.9683592574422737</v>
+        <v>0.9699439562652087</v>
       </c>
       <c r="AS13" t="n">
         <v>-0.2373009403500753</v>
@@ -3014,7 +3014,7 @@
         <v>-0.3770197493635609</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.08810534153544447</v>
+        <v>0.08810543549217154</v>
       </c>
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="n">
@@ -3183,13 +3183,13 @@
         <v>75.83420310261931</v>
       </c>
       <c r="AP14" t="n">
-        <v>10423900</v>
+        <v>10432200</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13094270</v>
+        <v>13094436</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.796065760061462</v>
+        <v>0.7966895252304108</v>
       </c>
       <c r="AS14" t="n">
         <v>0.03786733472437631</v>
@@ -3379,13 +3379,13 @@
         <v>68.26571628261831</v>
       </c>
       <c r="AP15" t="n">
-        <v>3036700</v>
+        <v>3037600</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6069508</v>
+        <v>6069526</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.5003206190683001</v>
+        <v>0.5004674170602449</v>
       </c>
       <c r="AS15" t="n">
         <v>0.04006704528879035</v>
@@ -3575,13 +3575,13 @@
         <v>84.31645102657885</v>
       </c>
       <c r="AP16" t="n">
-        <v>7697700</v>
+        <v>7699600</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8309046</v>
+        <v>8309084</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.9264240443487736</v>
+        <v>0.9266484729243319</v>
       </c>
       <c r="AS16" t="n">
         <v>0.2411653769181632</v>
@@ -3771,13 +3771,13 @@
         <v>41.6450519969167</v>
       </c>
       <c r="AP17" t="n">
-        <v>26749500</v>
+        <v>26788900</v>
       </c>
       <c r="AQ17" t="n">
-        <v>27280644</v>
+        <v>27281432</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.9805303716437193</v>
+        <v>0.9819462556071104</v>
       </c>
       <c r="AS17" t="n">
         <v>-0.2466655334868972</v>
@@ -3798,7 +3798,7 @@
         <v>0.04072788759895696</v>
       </c>
       <c r="AY17" t="n">
-        <v>316.4115837281723</v>
+        <v>316.4116836894942</v>
       </c>
       <c r="AZ17" t="inlineStr"/>
       <c r="BA17" t="n">
@@ -3967,13 +3967,13 @@
         <v>63.28670403112168</v>
       </c>
       <c r="AP18" t="n">
-        <v>8093200</v>
+        <v>8095800</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8931916</v>
+        <v>8931968</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.9060989825699212</v>
+        <v>0.9063847967211706</v>
       </c>
       <c r="AS18" t="n">
         <v>0.07820787140523922</v>
@@ -4328,16 +4328,16 @@
         <v>254.9357025146484</v>
       </c>
       <c r="AG20" t="n">
-        <v>271.4952764892578</v>
+        <v>271.4952757263184</v>
       </c>
       <c r="AH20" t="n">
         <v>0.1356588589118319</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.06639051978175847</v>
+        <v>0.06639052277846402</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0.06099396714647676</v>
+        <v>-0.0609939645077392</v>
       </c>
       <c r="AK20" t="n">
         <v>329.2300109863281</v>
@@ -4355,13 +4355,13 @@
         <v>58.76238147144925</v>
       </c>
       <c r="AP20" t="n">
-        <v>5944100</v>
+        <v>5950200</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9762754</v>
+        <v>9762876</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.6088548374772118</v>
+        <v>0.6094720449179115</v>
       </c>
       <c r="AS20" t="n">
         <v>-0.05271084517803704</v>
@@ -4373,16 +4373,16 @@
         <v>-0.009777814054530043</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.03224397235102461</v>
+        <v>0.03224386003643476</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.507965381744046</v>
+        <v>1.507965878995356</v>
       </c>
       <c r="AX20" t="n">
         <v>0.006221993973904993</v>
       </c>
       <c r="AY20" t="n">
-        <v>199.3960688314256</v>
+        <v>199.3961019018683</v>
       </c>
       <c r="AZ20" t="inlineStr"/>
       <c r="BA20" t="n">
@@ -4551,13 +4551,13 @@
         <v>50.1459359200975</v>
       </c>
       <c r="AP21" t="n">
-        <v>1612000</v>
+        <v>1612800</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2181182</v>
+        <v>2181198</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.7390488276539968</v>
+        <v>0.7394101773429097</v>
       </c>
       <c r="AS21" t="n">
         <v>-0.03649001459096823</v>
@@ -4933,13 +4933,13 @@
         <v>75.37064233238407</v>
       </c>
       <c r="AP23" t="n">
-        <v>2594500</v>
+        <v>2596200</v>
       </c>
       <c r="AQ23" t="n">
-        <v>4982518</v>
+        <v>4982552</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.5207206476725222</v>
+        <v>0.5210582849913057</v>
       </c>
       <c r="AS23" t="n">
         <v>0.09645015393923639</v>
@@ -5102,40 +5102,40 @@
         <v>293.4565985107422</v>
       </c>
       <c r="AG24" t="n">
-        <v>270.321223449707</v>
+        <v>270.3212226867676</v>
       </c>
       <c r="AH24" t="n">
         <v>0.05170579380076501</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.1417157740862061</v>
+        <v>0.1417157773085205</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.08558475270936139</v>
+        <v>0.08558475577325475</v>
       </c>
       <c r="AK24" t="n">
         <v>315.2000122070312</v>
       </c>
       <c r="AL24" t="n">
-        <v>201.5802917480469</v>
+        <v>201.5803070068359</v>
       </c>
       <c r="AM24" t="n">
         <v>-0.02084393105893478</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.5310524764423199</v>
+        <v>0.5310523605480288</v>
       </c>
       <c r="AO24" t="n">
         <v>58.29293135375314</v>
       </c>
       <c r="AP24" t="n">
-        <v>75352800</v>
+        <v>75400600</v>
       </c>
       <c r="AQ24" t="n">
-        <v>56523224</v>
+        <v>56524180</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.333129900728946</v>
+        <v>1.333953009136975</v>
       </c>
       <c r="AS24" t="n">
         <v>-0.005253673794582303</v>
@@ -5147,16 +5147,16 @@
         <v>0.1373626991556705</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.4585501750032972</v>
+        <v>0.4585500698253624</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.378664997029958</v>
+        <v>1.378665836238499</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.1409297936775185</v>
+        <v>0.1409299223927112</v>
       </c>
       <c r="AY24" t="n">
-        <v>3141.646152184104</v>
+        <v>3141.647344285259</v>
       </c>
       <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="n">
@@ -5271,10 +5271,10 @@
         </is>
       </c>
       <c r="Z25" t="n">
-        <v>0.1474947929382324</v>
+        <v>0.1477061361074448</v>
       </c>
       <c r="AA25" t="n">
-        <v>125382437317.5625</v>
+        <v>125562096010.1738</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
@@ -5517,13 +5517,13 @@
         <v>54.57120633420597</v>
       </c>
       <c r="AP26" t="n">
-        <v>28142500</v>
+        <v>28228900</v>
       </c>
       <c r="AQ26" t="n">
-        <v>37623120</v>
+        <v>37624848</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.748010797615934</v>
+        <v>0.7502727984442622</v>
       </c>
       <c r="AS26" t="n">
         <v>-0.0455282963168302</v>
@@ -5713,13 +5713,13 @@
         <v>45.42335820442248</v>
       </c>
       <c r="AP27" t="n">
-        <v>7553900</v>
+        <v>7576000</v>
       </c>
       <c r="AQ27" t="n">
-        <v>12236322</v>
+        <v>12236764</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.6173341956839645</v>
+        <v>0.6191179301978856</v>
       </c>
       <c r="AS27" t="n">
         <v>-0.2344413737245593</v>
@@ -5907,13 +5907,13 @@
         <v>51.85753391213613</v>
       </c>
       <c r="AP28" t="n">
-        <v>124577600</v>
+        <v>125021700</v>
       </c>
       <c r="AQ28" t="n">
-        <v>141743218</v>
+        <v>141752100</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.8788963716062944</v>
+        <v>0.8819742353023341</v>
       </c>
       <c r="AS28" t="n">
         <v>0.06778457503067226</v>
@@ -5928,13 +5928,13 @@
         <v>4.500457179629271</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.352237829814573</v>
+        <v>1.352237303679072</v>
       </c>
       <c r="AX28" t="n">
         <v>2.056119736156248</v>
       </c>
       <c r="AY28" t="n">
-        <v>662.0861976164024</v>
+        <v>662.08663313256</v>
       </c>
       <c r="AZ28" t="inlineStr"/>
       <c r="BA28" t="n">
@@ -6099,13 +6099,13 @@
         <v>62.40265095833276</v>
       </c>
       <c r="AP29" t="n">
-        <v>2832000</v>
+        <v>2832500</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4156362</v>
+        <v>4156372</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.681365097650301</v>
+        <v>0.6814837555444989</v>
       </c>
       <c r="AS29" t="n">
         <v>-0.0863829347231122</v>
@@ -6268,16 +6268,16 @@
         <v>209.6465234375</v>
       </c>
       <c r="AG30" t="n">
-        <v>190.8195568847656</v>
+        <v>190.8195567321777</v>
       </c>
       <c r="AH30" t="n">
         <v>-0.07067382450948412</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.02101694926747433</v>
+        <v>0.02101695008392546</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.09866371592144429</v>
+        <v>0.09866371679998509</v>
       </c>
       <c r="AK30" t="n">
         <v>235.465576171875</v>
@@ -6295,13 +6295,13 @@
         <v>40.41985540843898</v>
       </c>
       <c r="AP30" t="n">
-        <v>142068700</v>
+        <v>142385500</v>
       </c>
       <c r="AQ30" t="n">
-        <v>163779186</v>
+        <v>163785522</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.8674405061458786</v>
+        <v>0.8693411863351389</v>
       </c>
       <c r="AS30" t="n">
         <v>-0.09170162316524622</v>
@@ -6316,13 +6316,13 @@
         <v>0.2406326416810851</v>
       </c>
       <c r="AW30" t="n">
-        <v>9.272916737275118</v>
+        <v>9.27291880356794</v>
       </c>
       <c r="AX30" t="n">
         <v>0.03292362505629431</v>
       </c>
       <c r="AY30" t="n">
-        <v>5186.295215214715</v>
+        <v>5186.296244216904</v>
       </c>
       <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="n">
@@ -6464,16 +6464,16 @@
         <v>202.0392489624024</v>
       </c>
       <c r="AG31" t="n">
-        <v>166.9712874603271</v>
+        <v>166.9712875366211</v>
       </c>
       <c r="AH31" t="n">
         <v>-0.1276447477153387</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.05557070728030111</v>
+        <v>0.05557070679798071</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.2100239031241071</v>
+        <v>0.2100239025712127</v>
       </c>
       <c r="AK31" t="n">
         <v>250.0962829589844</v>
@@ -6491,13 +6491,13 @@
         <v>37.11777030562479</v>
       </c>
       <c r="AP31" t="n">
-        <v>18661200</v>
+        <v>18682500</v>
       </c>
       <c r="AQ31" t="n">
-        <v>26187758</v>
+        <v>26188184</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.7125925021912911</v>
+        <v>0.7133942544469674</v>
       </c>
       <c r="AS31" t="n">
         <v>-0.2924244145039175</v>
@@ -6506,19 +6506,19 @@
         <v>0.3951180314046254</v>
       </c>
       <c r="AU31" t="n">
-        <v>0.04084620658184712</v>
+        <v>0.04084630037348291</v>
       </c>
       <c r="AV31" t="n">
         <v>0.1087038965105265</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.426369205929251</v>
+        <v>0.426369029790546</v>
       </c>
       <c r="AX31" t="n">
         <v>0.02923321291609837</v>
       </c>
       <c r="AY31" t="n">
-        <v>521.4037341906666</v>
+        <v>521.4038264825695</v>
       </c>
       <c r="AZ31" t="inlineStr"/>
       <c r="BA31" t="n">
@@ -6651,7 +6651,7 @@
         <v>36801</v>
       </c>
       <c r="AD32" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="AE32" t="n">
         <v>41.86999893188477</v>
@@ -6687,13 +6687,13 @@
         <v>59.79899623455247</v>
       </c>
       <c r="AP32" t="n">
-        <v>18385800</v>
+        <v>18423100</v>
       </c>
       <c r="AQ32" t="n">
-        <v>10855152</v>
+        <v>10855898</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.693739525710925</v>
+        <v>1.69705905490269</v>
       </c>
       <c r="AS32" t="n">
         <v>0.04911047586986528</v>
@@ -6708,7 +6708,7 @@
         <v>3.065048364712458</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.399913353698032</v>
+        <v>5.399912887237076</v>
       </c>
       <c r="AX32" t="n">
         <v>1.483392492060633</v>
@@ -6829,10 +6829,10 @@
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>0.03134599700570107</v>
+        <v>0.03132537752389908</v>
       </c>
       <c r="AA33" t="n">
-        <v>13758411310.29993</v>
+        <v>13749360990.04419</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
@@ -6879,13 +6879,13 @@
         <v>70.49237362621658</v>
       </c>
       <c r="AP33" t="n">
-        <v>3309164</v>
+        <v>3221991</v>
       </c>
       <c r="AQ33" t="n">
-        <v>26336243.48</v>
+        <v>26334500.02</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.1256505698131554</v>
+        <v>0.1223486680040641</v>
       </c>
       <c r="AS33" t="n">
         <v>0.2058179494682617</v>
@@ -6900,13 +6900,13 @@
         <v>9.244454277651485</v>
       </c>
       <c r="AW33" t="n">
-        <v>7.577853447149552</v>
+        <v>7.57785412106025</v>
       </c>
       <c r="AX33" t="n">
         <v>4.348884750205366</v>
       </c>
       <c r="AY33" t="n">
-        <v>35.452156679906</v>
+        <v>35.45216580742827</v>
       </c>
       <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="n">
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>0.006215117871761322</v>
+        <v>0.00619820598512888</v>
       </c>
       <c r="AA34" t="n">
-        <v>9299549686.189453</v>
+        <v>9274244787.188232</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
@@ -7092,13 +7092,13 @@
         <v>0.4519825970641753</v>
       </c>
       <c r="AW34" t="n">
-        <v>2.075711346780389</v>
+        <v>2.075710912078704</v>
       </c>
       <c r="AX34" t="n">
         <v>0.1476909744709201</v>
       </c>
       <c r="AY34" t="n">
-        <v>3.554786507672973</v>
+        <v>3.554787460987867</v>
       </c>
       <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
@@ -7240,16 +7240,16 @@
         <v>75.22947402954101</v>
       </c>
       <c r="AG35" t="n">
-        <v>50.30421326637268</v>
+        <v>50.30421349525452</v>
       </c>
       <c r="AH35" t="n">
         <v>-0.07416604430161455</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.3845759033555642</v>
+        <v>0.384575897055808</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.4954905194756392</v>
+        <v>0.4954905126712266</v>
       </c>
       <c r="AK35" t="n">
         <v>93.55000305175781</v>
@@ -7267,13 +7267,13 @@
         <v>44.78163251855959</v>
       </c>
       <c r="AP35" t="n">
-        <v>6962100</v>
+        <v>6995500</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5805134</v>
+        <v>5805802</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.199300481263654</v>
+        <v>1.204915358808309</v>
       </c>
       <c r="AS35" t="n">
         <v>-0.07380313361160329</v>
@@ -7285,16 +7285,16 @@
         <v>0.7695539298593599</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.150252038900717</v>
+        <v>2.150252310669514</v>
       </c>
       <c r="AW35" t="n">
-        <v>2.155732261231075</v>
+        <v>2.15573253394624</v>
       </c>
       <c r="AX35" t="n">
         <v>0.627725753939528</v>
       </c>
       <c r="AY35" t="n">
-        <v>4.631298635017683</v>
+        <v>4.631299937636747</v>
       </c>
       <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="n">
@@ -7409,10 +7409,10 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>0.03134599700570107</v>
+        <v>0.03132537752389908</v>
       </c>
       <c r="AA36" t="n">
-        <v>47813530465.06445</v>
+        <v>47782078595.11328</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
@@ -7459,13 +7459,13 @@
         <v>56.12431444241317</v>
       </c>
       <c r="AP36" t="n">
-        <v>18997866</v>
+        <v>17574418</v>
       </c>
       <c r="AQ36" t="n">
-        <v>25718815.14</v>
+        <v>25690346.18</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.7386757864460469</v>
+        <v>0.6840864609945089</v>
       </c>
       <c r="AS36" t="n">
         <v>-0.002059732234809486</v>
@@ -7601,10 +7601,10 @@
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>0.006215117871761322</v>
+        <v>0.00619820598512888</v>
       </c>
       <c r="AA37" t="n">
-        <v>40516272799.21484</v>
+        <v>40406024429.59619</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
@@ -7624,16 +7624,16 @@
         <v>19194.6</v>
       </c>
       <c r="AG37" t="n">
-        <v>9944.236696777343</v>
+        <v>9944.236700439453</v>
       </c>
       <c r="AH37" t="n">
         <v>0.2162274806455984</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.347590942557258</v>
+        <v>1.347590941692724</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.9302235641897429</v>
+        <v>0.93022356347891</v>
       </c>
       <c r="AK37" t="n">
         <v>26425</v>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="X38" t="n">
-        <v>7521360384</v>
+        <v>7867125248</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
@@ -7793,10 +7793,10 @@
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>1.145869135856628</v>
+        <v>1.144033789634705</v>
       </c>
       <c r="AA38" t="n">
-        <v>8618494723.680359</v>
+        <v>9000257111.000305</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
@@ -7810,22 +7810,22 @@
         <v>18.7</v>
       </c>
       <c r="AE38" t="n">
-        <v>193.6000061035156</v>
+        <v>202.5</v>
       </c>
       <c r="AF38" t="n">
-        <v>146.0380001831055</v>
+        <v>146.2160000610351</v>
       </c>
       <c r="AG38" t="n">
-        <v>66.63825007438659</v>
+        <v>66.68275004386902</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.3256823967787557</v>
+        <v>0.3849373523791524</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.905238446198765</v>
+        <v>2.036767377871788</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.191504128936264</v>
+        <v>1.19271100794198</v>
       </c>
       <c r="AK38" t="n">
         <v>239</v>
@@ -7834,43 +7834,43 @@
         <v>17.63999938964844</v>
       </c>
       <c r="AM38" t="n">
-        <v>-0.1899581334580936</v>
+        <v>-0.1527196652719666</v>
       </c>
       <c r="AN38" t="n">
-        <v>9.975057415088383</v>
+        <v>10.47959223393351</v>
       </c>
       <c r="AO38" t="n">
-        <v>44.47439536017632</v>
+        <v>47.61602015828788</v>
       </c>
       <c r="AP38" t="n">
-        <v>15909</v>
+        <v>85427</v>
       </c>
       <c r="AQ38" t="n">
-        <v>194014.18</v>
+        <v>195404.54</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.08199916109224593</v>
+        <v>0.4371802210941465</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.4534535325758544</v>
+        <v>0.5202703051013271</v>
       </c>
       <c r="AT38" t="n">
-        <v>2.30940181373531</v>
+        <v>2.461538461538462</v>
       </c>
       <c r="AU38" t="n">
-        <v>4.66910680682709</v>
+        <v>4.929721550569925</v>
       </c>
       <c r="AV38" t="n">
-        <v>9.579235747258577</v>
+        <v>10.06557423182312</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.334065687594783</v>
+        <v>4.5792782421732</v>
       </c>
       <c r="AX38" t="n">
-        <v>4.902439347765838</v>
+        <v>5.173780631409171</v>
       </c>
       <c r="AY38" t="n">
-        <v>15.87161250370981</v>
+        <v>16.64721956733127</v>
       </c>
       <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="n">
@@ -8035,13 +8035,13 @@
         <v>29.57746531061807</v>
       </c>
       <c r="AP39" t="n">
-        <v>24591700</v>
+        <v>24641100</v>
       </c>
       <c r="AQ39" t="n">
-        <v>22744018</v>
+        <v>22745006</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.081238152379232</v>
+        <v>1.083363090781335</v>
       </c>
       <c r="AS39" t="n">
         <v>-0.2605680597123423</v>
@@ -8202,16 +8202,16 @@
         <v>1073.05529296875</v>
       </c>
       <c r="AG40" t="n">
-        <v>900.0563131713867</v>
+        <v>900.0563137817383</v>
       </c>
       <c r="AH40" t="n">
         <v>-0.06619908023655663</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.1132859187450059</v>
+        <v>0.1132859179900578</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.1922090621061188</v>
+        <v>0.1922090612976508</v>
       </c>
       <c r="AK40" t="n">
         <v>1115.93994140625</v>
@@ -8250,7 +8250,7 @@
         <v>0.2888253521148874</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.4112062721592988</v>
+        <v>0.4112061508526457</v>
       </c>
       <c r="AX40" t="n">
         <v>0.3250242896831437</v>
@@ -8413,13 +8413,13 @@
         <v>133.0599975585938</v>
       </c>
       <c r="AL41" t="n">
-        <v>77.69110870361328</v>
+        <v>77.69111633300781</v>
       </c>
       <c r="AM41" t="n">
         <v>-0.1194949209996995</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.5080233197477906</v>
+        <v>0.5080231716574373</v>
       </c>
       <c r="AO41" t="n">
         <v>39.49274924214231</v>
@@ -8446,13 +8446,13 @@
         <v>0.2162630355228989</v>
       </c>
       <c r="AW41" t="n">
-        <v>2.298557036650715</v>
+        <v>2.298556328120133</v>
       </c>
       <c r="AX41" t="n">
-        <v>0.4286725968013296</v>
+        <v>0.4286727297169941</v>
       </c>
       <c r="AY41" t="n">
-        <v>100.6865596436493</v>
+        <v>100.686580685693</v>
       </c>
       <c r="AZ41" t="inlineStr"/>
       <c r="BA41" t="n">
@@ -8559,7 +8559,7 @@
         </is>
       </c>
       <c r="X42" t="n">
-        <v>5528353280</v>
+        <v>5503891456</v>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
@@ -8567,10 +8567,10 @@
         </is>
       </c>
       <c r="Z42" t="n">
-        <v>0.7751156687736511</v>
+        <v>0.7744133472442627</v>
       </c>
       <c r="AA42" t="n">
-        <v>4285113249.844208</v>
+        <v>4262287005.310059</v>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
@@ -8584,22 +8584,22 @@
         <v>11.6</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.259999990463257</v>
+        <v>2.25</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.288999967575073</v>
+        <v>2.288799967765808</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.268190586566925</v>
+        <v>2.268140586614609</v>
       </c>
       <c r="AH42" t="n">
-        <v>-0.0126692780789065</v>
+        <v>-0.01695210080052656</v>
       </c>
       <c r="AI42" t="n">
-        <v>-0.003611070494770496</v>
+        <v>-0.007997999207661532</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.009174441130030964</v>
+        <v>0.009108509972053813</v>
       </c>
       <c r="AK42" t="n">
         <v>2.390000104904175</v>
@@ -8608,51 +8608,51 @@
         <v>2.093223333358765</v>
       </c>
       <c r="AM42" t="n">
-        <v>-0.05439335093507458</v>
+        <v>-0.05857744717956315</v>
       </c>
       <c r="AN42" t="n">
-        <v>0.0796745643174559</v>
+        <v>0.07489724777225426</v>
       </c>
       <c r="AO42" t="n">
-        <v>50</v>
+        <v>47.36842105263158</v>
       </c>
       <c r="AP42" t="n">
-        <v>7301400</v>
+        <v>10133200</v>
       </c>
       <c r="AQ42" t="n">
-        <v>9458647.16</v>
+        <v>9515283.16</v>
       </c>
       <c r="AR42" t="n">
-        <v>0.7719285725000022</v>
+        <v>1.064939406385464</v>
       </c>
       <c r="AS42" t="n">
-        <v>-0.01310042440590042</v>
+        <v>-0.01746723254120064</v>
       </c>
       <c r="AT42" t="n">
-        <v>0.01345290185344239</v>
+        <v>0.00896860123562826</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.03280594000915005</v>
+        <v>0.028236006560447</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.04162442003483169</v>
+        <v>0.03701546680005374</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.1271953795002783</v>
+        <v>0.1222077940609883</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.03280594000915005</v>
+        <v>0.028236006560447</v>
       </c>
       <c r="AY42" t="n">
-        <v>3.047814299238745</v>
+        <v>3.029904063720521</v>
       </c>
       <c r="AZ42" t="inlineStr"/>
       <c r="BA42" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>Positive momentum</t>
+          <t>Strong momentum</t>
         </is>
       </c>
     </row>
@@ -8759,10 +8759,10 @@
         </is>
       </c>
       <c r="Z43" t="n">
-        <v>0.006215117871761322</v>
+        <v>0.00619820598512888</v>
       </c>
       <c r="AA43" t="n">
-        <v>63945047002.79688</v>
+        <v>63771046861.86133</v>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
@@ -8782,16 +8782,16 @@
         <v>2664.9</v>
       </c>
       <c r="AG43" t="n">
-        <v>2593.725720214844</v>
+        <v>2593.725723876953</v>
       </c>
       <c r="AH43" t="n">
         <v>0.01410934744268078</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.04193746429601131</v>
+        <v>0.04193746282488853</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.02744094305363198</v>
+        <v>0.02744094160297705</v>
       </c>
       <c r="AK43" t="n">
         <v>2780</v>
@@ -8830,13 +8830,13 @@
         <v>0.1543973501121187</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.8713530964641725</v>
+        <v>0.8713527801011207</v>
       </c>
       <c r="AX43" t="n">
         <v>0.00339885699202247</v>
       </c>
       <c r="AY43" t="n">
-        <v>3.130111049454799</v>
+        <v>3.130110278963514</v>
       </c>
       <c r="AZ43" t="inlineStr"/>
       <c r="BA43" t="n">
@@ -8978,16 +8978,16 @@
         <v>189.9223980712891</v>
       </c>
       <c r="AG44" t="n">
-        <v>173.0878996276855</v>
+        <v>173.0878987121582</v>
       </c>
       <c r="AH44" t="n">
         <v>-0.08752203630712307</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.001225408734686351</v>
+        <v>0.001225414030546101</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.09725982278261358</v>
+        <v>0.09725982858643567</v>
       </c>
       <c r="AK44" t="n">
         <v>202.5594635009766</v>
@@ -9023,16 +9023,16 @@
         <v>0.1353065752561424</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.03568225842309936</v>
+        <v>0.03568216397906454</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.3504699728999674</v>
+        <v>0.3504698123200198</v>
       </c>
       <c r="AX44" t="n">
         <v>0.1329632533256775</v>
       </c>
       <c r="AY44" t="n">
-        <v>32.99627986665141</v>
+        <v>32.99628940681208</v>
       </c>
       <c r="AZ44" t="inlineStr"/>
       <c r="BA44" t="n">
@@ -9147,10 +9147,10 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>0.6947821974754333</v>
+        <v>0.6942998170852661</v>
       </c>
       <c r="AA45" t="n">
-        <v>6732516597.686096</v>
+        <v>6727842278.172729</v>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
@@ -9339,10 +9339,10 @@
         </is>
       </c>
       <c r="Z46" t="n">
-        <v>0.006215117871761322</v>
+        <v>0.00619820598512888</v>
       </c>
       <c r="AA46" t="n">
-        <v>73934992230.14062</v>
+        <v>73733808562.74023</v>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
@@ -9362,16 +9362,16 @@
         <v>148.8519998168945</v>
       </c>
       <c r="AG46" t="n">
-        <v>152.0525869750977</v>
+        <v>152.0525868988037</v>
       </c>
       <c r="AH46" t="n">
         <v>-0.0184881205275319</v>
       </c>
       <c r="AI46" t="n">
-        <v>-0.03914817228697931</v>
+        <v>-0.03914817180486219</v>
       </c>
       <c r="AJ46" t="n">
-        <v>-0.0210492121303224</v>
+        <v>-0.02104921163912388</v>
       </c>
       <c r="AK46" t="n">
         <v>160.0310211181641</v>
@@ -9407,16 +9407,16 @@
         <v>-0.05184251697780218</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.00527541208185478</v>
+        <v>0.005275517627422843</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.5331723430396678</v>
+        <v>0.5331724657897601</v>
       </c>
       <c r="AX46" t="n">
         <v>-0.0684873374028192</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.5884234397888475</v>
+        <v>0.5884235715454689</v>
       </c>
       <c r="AZ46" t="inlineStr"/>
       <c r="BA46" t="n">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="AO48" t="inlineStr"/>
       <c r="AP48" t="n">
-        <v>60938000</v>
+        <v>61257100</v>
       </c>
       <c r="AQ48" t="inlineStr"/>
       <c r="AR48" t="inlineStr"/>
@@ -9910,16 +9910,16 @@
         <v>65.47655090332032</v>
       </c>
       <c r="AG49" t="n">
-        <v>61.19086208343506</v>
+        <v>61.19086206436157</v>
       </c>
       <c r="AH49" t="n">
         <v>0.0652668632926261</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.1398760799430212</v>
+        <v>0.1398760802983259</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.07003805264324647</v>
+        <v>0.07003805297678234</v>
       </c>
       <c r="AK49" t="n">
         <v>69.75</v>
@@ -9937,13 +9937,13 @@
         <v>68.65849392254501</v>
       </c>
       <c r="AP49" t="n">
-        <v>4301400</v>
+        <v>4304400</v>
       </c>
       <c r="AQ49" t="n">
-        <v>7573788</v>
+        <v>7573848</v>
       </c>
       <c r="AR49" t="n">
-        <v>0.567932453350952</v>
+        <v>0.5683240540343562</v>
       </c>
       <c r="AS49" t="n">
         <v>0.06553622021887473</v>
@@ -9958,13 +9958,13 @@
         <v>0.2683822198137273</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.1606245401184305</v>
+        <v>0.1606241717611732</v>
       </c>
       <c r="AX49" t="n">
         <v>0.2018768282491283</v>
       </c>
       <c r="AY49" t="n">
-        <v>187.7446846088052</v>
+        <v>187.7447607159686</v>
       </c>
       <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
@@ -10106,40 +10106,40 @@
         <v>112.1158570861816</v>
       </c>
       <c r="AG50" t="n">
-        <v>101.2313226318359</v>
+        <v>101.2313223648071</v>
       </c>
       <c r="AH50" t="n">
         <v>0.02670579882262669</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.1370986530423042</v>
+        <v>0.1370986560417522</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.1075214090991503</v>
+        <v>0.1075214120205792</v>
       </c>
       <c r="AK50" t="n">
         <v>117.3600006103516</v>
       </c>
       <c r="AL50" t="n">
-        <v>78.91034698486328</v>
+        <v>78.91035461425781</v>
       </c>
       <c r="AM50" t="n">
         <v>-0.019171779041398</v>
       </c>
       <c r="AN50" t="n">
-        <v>0.4587440685368189</v>
+        <v>0.4587439274991303</v>
       </c>
       <c r="AO50" t="n">
         <v>67.08115719150381</v>
       </c>
       <c r="AP50" t="n">
-        <v>2726400</v>
+        <v>2726900</v>
       </c>
       <c r="AQ50" t="n">
-        <v>3770050</v>
+        <v>3770060</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.723173432713094</v>
+        <v>0.7233041383956754</v>
       </c>
       <c r="AS50" t="n">
         <v>0.05935943982018621</v>
@@ -10148,7 +10148,7 @@
         <v>0.007295158076668695</v>
       </c>
       <c r="AU50" t="n">
-        <v>0.2604061399247568</v>
+        <v>0.26040603463212</v>
       </c>
       <c r="AV50" t="n">
         <v>0.4517479007784346</v>
@@ -10160,7 +10160,7 @@
         <v>0.2412032442714338</v>
       </c>
       <c r="AY50" t="n">
-        <v>213.1717399262585</v>
+        <v>213.1717161747428</v>
       </c>
       <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
@@ -10302,40 +10302,40 @@
         <v>1041.696948242188</v>
       </c>
       <c r="AG51" t="n">
-        <v>793.7075695800781</v>
+        <v>793.7075711059571</v>
       </c>
       <c r="AH51" t="n">
         <v>0.06855452272360107</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.4024182558073228</v>
+        <v>0.4024182531112159</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.3124442655792128</v>
+        <v>0.3124442630560782</v>
       </c>
       <c r="AK51" t="n">
         <v>1174.859985351562</v>
       </c>
       <c r="AL51" t="n">
-        <v>503.7064514160156</v>
+        <v>503.7064819335938</v>
       </c>
       <c r="AM51" t="n">
         <v>-0.05255945454770261</v>
       </c>
       <c r="AN51" t="n">
-        <v>1.209838651505051</v>
+        <v>1.209838517619691</v>
       </c>
       <c r="AO51" t="n">
         <v>67.34457920145803</v>
       </c>
       <c r="AP51" t="n">
-        <v>2360300</v>
+        <v>2363000</v>
       </c>
       <c r="AQ51" t="n">
-        <v>2911538</v>
+        <v>2911592</v>
       </c>
       <c r="AR51" t="n">
-        <v>0.810671198521194</v>
+        <v>0.8115834910935323</v>
       </c>
       <c r="AS51" t="n">
         <v>0.1608559243346663</v>
@@ -10344,17 +10344,17 @@
         <v>0.2393900990658835</v>
       </c>
       <c r="AU51" t="n">
-        <v>0.7062789499231121</v>
+        <v>0.7062787902830061</v>
       </c>
       <c r="AV51" t="n">
-        <v>1.209838651505051</v>
+        <v>1.209838517619691</v>
       </c>
       <c r="AW51" t="inlineStr"/>
       <c r="AX51" t="n">
-        <v>0.6410458849977139</v>
+        <v>0.6410457373307343</v>
       </c>
       <c r="AY51" t="n">
-        <v>7.516676621441324</v>
+        <v>7.516675627130299</v>
       </c>
       <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="n">
@@ -10496,40 +10496,40 @@
         <v>93.50025115966797</v>
       </c>
       <c r="AG52" t="n">
-        <v>91.52396598815918</v>
+        <v>91.52396572113037</v>
       </c>
       <c r="AH52" t="n">
         <v>0.04791165950576604</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.0705393095575606</v>
+        <v>0.0705393126809486</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.02159308930913761</v>
+        <v>0.02159309228972073</v>
       </c>
       <c r="AK52" t="n">
         <v>98.29612731933594</v>
       </c>
       <c r="AL52" t="n">
-        <v>82.73965454101562</v>
+        <v>82.73964691162109</v>
       </c>
       <c r="AM52" t="n">
         <v>-0.00321603679639737</v>
       </c>
       <c r="AN52" t="n">
-        <v>0.1841964279457202</v>
+        <v>0.1841965371400676</v>
       </c>
       <c r="AO52" t="n">
         <v>68.52873416946491</v>
       </c>
       <c r="AP52" t="n">
-        <v>5279800</v>
+        <v>5282700</v>
       </c>
       <c r="AQ52" t="n">
-        <v>6146960</v>
+        <v>6147018</v>
       </c>
       <c r="AR52" t="n">
-        <v>0.8589286411494462</v>
+        <v>0.8593923102226153</v>
       </c>
       <c r="AS52" t="n">
         <v>0.08277163962850431</v>
@@ -10538,19 +10538,19 @@
         <v>0.01376357279798657</v>
       </c>
       <c r="AU52" t="n">
-        <v>0.1418261504540166</v>
+        <v>0.1418262519742559</v>
       </c>
       <c r="AV52" t="n">
-        <v>0.1100636367675336</v>
+        <v>0.1100637327182925</v>
       </c>
       <c r="AW52" t="n">
-        <v>0.9152711376984386</v>
+        <v>0.9152707092443282</v>
       </c>
       <c r="AX52" t="n">
         <v>0.1420881327438168</v>
       </c>
       <c r="AY52" t="n">
-        <v>360.2949883319881</v>
+        <v>360.2950677404207</v>
       </c>
       <c r="AZ52" t="inlineStr"/>
       <c r="BA52" t="n">
@@ -10692,16 +10692,16 @@
         <v>14.54532102584839</v>
       </c>
       <c r="AG53" t="n">
-        <v>14.17657375812531</v>
+        <v>14.17657376766205</v>
       </c>
       <c r="AH53" t="n">
         <v>0.002384196113378367</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.02845724026579588</v>
+        <v>0.02845723957394086</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.02601102875874606</v>
+        <v>0.02601102806853661</v>
       </c>
       <c r="AK53" t="n">
         <v>17.06953239440918</v>
@@ -10737,16 +10737,16 @@
         <v>0.04146013598854292</v>
       </c>
       <c r="AV53" t="n">
-        <v>0.3773202277335794</v>
+        <v>0.3773201036505531</v>
       </c>
       <c r="AW53" t="n">
-        <v>-0.3234067867509463</v>
+        <v>-0.3234069065236225</v>
       </c>
       <c r="AX53" t="n">
         <v>0.007728700033076352</v>
       </c>
       <c r="AY53" t="n">
-        <v>6.306200819186889</v>
+        <v>6.306201255638213</v>
       </c>
       <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="X54" t="n">
-        <v>142908538880</v>
+        <v>143044657152</v>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
@@ -10861,10 +10861,10 @@
         </is>
       </c>
       <c r="Z54" t="n">
-        <v>1.145869135856628</v>
+        <v>1.144033789634705</v>
       </c>
       <c r="AA54" t="n">
-        <v>163754483952.959</v>
+        <v>163647921208.5996</v>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
@@ -10878,22 +10878,22 @@
         <v>5.8</v>
       </c>
       <c r="AE54" t="n">
-        <v>167.9600067138672</v>
+        <v>168.1199951171875</v>
       </c>
       <c r="AF54" t="n">
-        <v>167.9911996459961</v>
+        <v>167.9943994140625</v>
       </c>
       <c r="AG54" t="n">
-        <v>139.2212530517578</v>
+        <v>139.2220529937744</v>
       </c>
       <c r="AH54" t="n">
-        <v>-0.000185681941641147</v>
+        <v>0.000747618394202787</v>
       </c>
       <c r="AI54" t="n">
-        <v>0.2064250466947406</v>
+        <v>0.2075672747384736</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.2066490996424417</v>
+        <v>0.2066651496769316</v>
       </c>
       <c r="AK54" t="n">
         <v>187.6199951171875</v>
@@ -10902,43 +10902,43 @@
         <v>84.04161071777344</v>
       </c>
       <c r="AM54" t="n">
-        <v>-0.1047862110381181</v>
+        <v>-0.1039334852760245</v>
       </c>
       <c r="AN54" t="n">
-        <v>0.9985338843386349</v>
+        <v>1.000437565169522</v>
       </c>
       <c r="AO54" t="n">
-        <v>63.56092001657687</v>
+        <v>63.67054448734005</v>
       </c>
       <c r="AP54" t="n">
-        <v>228286</v>
+        <v>1393958</v>
       </c>
       <c r="AQ54" t="n">
-        <v>2591057.58</v>
+        <v>2614371.02</v>
       </c>
       <c r="AR54" t="n">
-        <v>0.08810533650896327</v>
+        <v>0.5331905798129601</v>
       </c>
       <c r="AS54" t="n">
-        <v>0.05317288195075998</v>
+        <v>0.0541760698590017</v>
       </c>
       <c r="AT54" t="n">
-        <v>0.1219773556303965</v>
+        <v>0.1230460824612702</v>
       </c>
       <c r="AU54" t="n">
-        <v>0.3224324292016403</v>
+        <v>0.3236920972439701</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.8223450537013841</v>
+        <v>0.8240809078558617</v>
       </c>
       <c r="AW54" t="n">
-        <v>6.459145828115101</v>
+        <v>6.466251585481487</v>
       </c>
       <c r="AX54" t="n">
-        <v>0.3735851246264577</v>
+        <v>0.3748935175898367</v>
       </c>
       <c r="AY54" t="n">
-        <v>6.706653723556665</v>
+        <v>6.713995284434406</v>
       </c>
       <c r="AZ54" t="inlineStr"/>
       <c r="BA54" t="n">
@@ -11080,16 +11080,16 @@
         <v>124.7349671936035</v>
       </c>
       <c r="AG55" t="n">
-        <v>122.6580275344849</v>
+        <v>122.6580275726318</v>
       </c>
       <c r="AH55" t="n">
         <v>0.03900300789241395</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.05659620253618591</v>
+        <v>0.05659620220758166</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.01693276584392112</v>
+        <v>0.0169327655276521</v>
       </c>
       <c r="AK55" t="n">
         <v>132.3166198730469</v>
@@ -11122,19 +11122,19 @@
         <v>-0.0113453335045216</v>
       </c>
       <c r="AU55" t="n">
-        <v>0.1247611933785884</v>
+        <v>0.1247611189044187</v>
       </c>
       <c r="AV55" t="n">
-        <v>0.1458119888150171</v>
+        <v>0.1458119115270744</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.5765101918121374</v>
+        <v>0.5765103381237029</v>
       </c>
       <c r="AX55" t="n">
         <v>0.1225583250916018</v>
       </c>
       <c r="AY55" t="n">
-        <v>174.0547423435545</v>
+        <v>174.0547564371849</v>
       </c>
       <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="n">
@@ -11276,40 +11276,40 @@
         <v>45.48177169799805</v>
       </c>
       <c r="AG56" t="n">
-        <v>45.33060747146607</v>
+        <v>45.33060731887817</v>
       </c>
       <c r="AH56" t="n">
         <v>0.05272946238861542</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.05624000512796834</v>
+        <v>0.0562400086833903</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.003334705510556812</v>
+        <v>0.003334708887893667</v>
       </c>
       <c r="AK56" t="n">
         <v>49.82146072387695</v>
       </c>
       <c r="AL56" t="n">
-        <v>41.35775375366211</v>
+        <v>41.35774993896484</v>
       </c>
       <c r="AM56" t="n">
         <v>-0.03896834070204758</v>
       </c>
       <c r="AN56" t="n">
-        <v>0.1577031323630722</v>
+        <v>0.1577032391456459</v>
       </c>
       <c r="AO56" t="n">
         <v>66.76096387102345</v>
       </c>
       <c r="AP56" t="n">
-        <v>12709500</v>
+        <v>12710100</v>
       </c>
       <c r="AQ56" t="n">
-        <v>8699846</v>
+        <v>8699858</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.460887928361031</v>
+        <v>1.460954879953213</v>
       </c>
       <c r="AS56" t="n">
         <v>0.07210024948425575</v>
@@ -11324,13 +11324,13 @@
         <v>0.1558150972839467</v>
       </c>
       <c r="AW56" t="n">
-        <v>0.7941666183036384</v>
+        <v>0.7941663618366874</v>
       </c>
       <c r="AX56" t="n">
         <v>0.1098387516070902</v>
       </c>
       <c r="AY56" t="n">
-        <v>194.2716223453859</v>
+        <v>194.2717528834614</v>
       </c>
       <c r="AZ56" t="inlineStr"/>
       <c r="BA56" t="n">
@@ -11472,16 +11472,16 @@
         <v>89.31747680664063</v>
       </c>
       <c r="AG57" t="n">
-        <v>85.53363929748535</v>
+        <v>85.53363903045654</v>
       </c>
       <c r="AH57" t="n">
         <v>-0.01094388806869351</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.03280998053461492</v>
+        <v>0.0328099837589606</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.04423800437153291</v>
+        <v>0.04423800763155583</v>
       </c>
       <c r="AK57" t="n">
         <v>97.16828918457031</v>
@@ -11499,13 +11499,13 @@
         <v>66.79462867100609</v>
       </c>
       <c r="AP57" t="n">
-        <v>14281800</v>
+        <v>14283600</v>
       </c>
       <c r="AQ57" t="n">
-        <v>12075616</v>
+        <v>12075652</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.18269742926572</v>
+        <v>1.182842963675999</v>
       </c>
       <c r="AS57" t="n">
         <v>0.05210495044233032</v>
@@ -11526,7 +11526,7 @@
         <v>0.1070531241894106</v>
       </c>
       <c r="AY57" t="n">
-        <v>253.2130287806661</v>
+        <v>253.2130941854791</v>
       </c>
       <c r="AZ57" t="inlineStr"/>
       <c r="BA57" t="n">
@@ -11691,13 +11691,13 @@
         <v>45.73833492870085</v>
       </c>
       <c r="AP58" t="n">
-        <v>3809400</v>
+        <v>3810900</v>
       </c>
       <c r="AQ58" t="n">
-        <v>3234014</v>
+        <v>3234044</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.177916978714378</v>
+        <v>1.178369867571375</v>
       </c>
       <c r="AS58" t="n">
         <v>-0.1572974600828685</v>
@@ -11718,7 +11718,7 @@
         <v>-0.02049509631801205</v>
       </c>
       <c r="AY58" t="n">
-        <v>15.13440308925134</v>
+        <v>15.13440437503716</v>
       </c>
       <c r="AZ58" t="inlineStr"/>
       <c r="BA58" t="n">
@@ -12046,40 +12046,40 @@
         <v>202.3799096679687</v>
       </c>
       <c r="AG60" t="n">
-        <v>197.7321705627441</v>
+        <v>197.732170715332</v>
       </c>
       <c r="AH60" t="n">
         <v>-0.05593397154859303</v>
       </c>
       <c r="AI60" t="n">
-        <v>-0.0337434873908552</v>
+        <v>-0.03374348813650541</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.02350522472897154</v>
+        <v>0.02350522393914289</v>
       </c>
       <c r="AK60" t="n">
         <v>238.1012115478516</v>
       </c>
       <c r="AL60" t="n">
-        <v>135.6905670166016</v>
+        <v>135.6905517578125</v>
       </c>
       <c r="AM60" t="n">
         <v>-0.1975681420663576</v>
       </c>
       <c r="AN60" t="n">
-        <v>0.4080565934639937</v>
+        <v>0.4080567518039686</v>
       </c>
       <c r="AO60" t="n">
         <v>46.19108169811867</v>
       </c>
       <c r="AP60" t="n">
-        <v>586700</v>
+        <v>587500</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1036794</v>
+        <v>1036810</v>
       </c>
       <c r="AR60" t="n">
-        <v>0.5658790463679381</v>
+        <v>0.566641911246998</v>
       </c>
       <c r="AS60" t="n">
         <v>0.03432219735812803</v>
@@ -12091,16 +12091,16 @@
         <v>0.1084229842021078</v>
       </c>
       <c r="AV60" t="n">
-        <v>0.3648456201479875</v>
+        <v>0.3648454713773188</v>
       </c>
       <c r="AW60" t="n">
-        <v>2.412546981495748</v>
+        <v>2.412546748982577</v>
       </c>
       <c r="AX60" t="n">
         <v>0.05350470796736562</v>
       </c>
       <c r="AY60" t="n">
-        <v>12.48362323482563</v>
+        <v>12.48362414231921</v>
       </c>
       <c r="AZ60" t="inlineStr"/>
       <c r="BA60" t="n">
@@ -12265,13 +12265,13 @@
         <v>47.90209965097517</v>
       </c>
       <c r="AP61" t="n">
-        <v>4445200</v>
+        <v>4446000</v>
       </c>
       <c r="AQ61" t="n">
-        <v>6176886</v>
+        <v>6176902</v>
       </c>
       <c r="AR61" t="n">
-        <v>0.7196506459727442</v>
+        <v>0.7197782966283098</v>
       </c>
       <c r="AS61" t="n">
         <v>-0.1507936521285439</v>
@@ -12457,13 +12457,13 @@
         <v>39.08729696189509</v>
       </c>
       <c r="AP62" t="n">
-        <v>9657200</v>
+        <v>9675600</v>
       </c>
       <c r="AQ62" t="n">
-        <v>14043754</v>
+        <v>14044122</v>
       </c>
       <c r="AR62" t="n">
-        <v>0.6876508944830563</v>
+        <v>0.6889430325370287</v>
       </c>
       <c r="AS62" t="n">
         <v>-0.1970556456759841</v>
@@ -12622,16 +12622,16 @@
         <v>154.2383877563477</v>
       </c>
       <c r="AG63" t="n">
-        <v>168.128985824585</v>
+        <v>168.1289860534668</v>
       </c>
       <c r="AH63" t="n">
         <v>-0.02067179741029568</v>
       </c>
       <c r="AI63" t="n">
-        <v>-0.1015826193744264</v>
+        <v>-0.101582620597484</v>
       </c>
       <c r="AJ63" t="n">
-        <v>-0.08261869897157326</v>
+        <v>-0.08261870022044726</v>
       </c>
       <c r="AK63" t="n">
         <v>217.0162200927734</v>
@@ -12649,13 +12649,13 @@
         <v>55.07202843033653</v>
       </c>
       <c r="AP63" t="n">
-        <v>4254100</v>
+        <v>4255900</v>
       </c>
       <c r="AQ63" t="n">
-        <v>4945728</v>
+        <v>4945764</v>
       </c>
       <c r="AR63" t="n">
-        <v>0.8601564825239075</v>
+        <v>0.8605141692972006</v>
       </c>
       <c r="AS63" t="n">
         <v>-0.0165049549737063</v>
@@ -12670,13 +12670,13 @@
         <v>-0.1880956335346442</v>
       </c>
       <c r="AW63" t="n">
-        <v>8.01061744475893</v>
+        <v>8.010621545653805</v>
       </c>
       <c r="AX63" t="n">
         <v>-0.08329068135345574</v>
       </c>
       <c r="AY63" t="n">
-        <v>12.32288682132202</v>
+        <v>12.32288457999127</v>
       </c>
       <c r="AZ63" t="inlineStr"/>
       <c r="BA63" t="n">
@@ -12818,25 +12818,25 @@
         <v>278.6736727905273</v>
       </c>
       <c r="AG64" t="n">
-        <v>316.0922011566162</v>
+        <v>316.0922017669678</v>
       </c>
       <c r="AH64" t="n">
         <v>-0.1414689532590372</v>
       </c>
       <c r="AI64" t="n">
-        <v>-0.2431005917749383</v>
+        <v>-0.2431005932364572</v>
       </c>
       <c r="AJ64" t="n">
-        <v>-0.1183785244595418</v>
+        <v>-0.11837852616189</v>
       </c>
       <c r="AK64" t="n">
-        <v>402.3219299316406</v>
+        <v>402.3219604492188</v>
       </c>
       <c r="AL64" t="n">
         <v>236.5</v>
       </c>
       <c r="AM64" t="n">
-        <v>-0.405326972753756</v>
+        <v>-0.4053270178618593</v>
       </c>
       <c r="AN64" t="n">
         <v>0.01162790697674421</v>
@@ -12845,13 +12845,13 @@
         <v>44.93893479525159</v>
       </c>
       <c r="AP64" t="n">
-        <v>4267000</v>
+        <v>4271000</v>
       </c>
       <c r="AQ64" t="n">
-        <v>3882464</v>
+        <v>3882544</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.099044318247381</v>
+        <v>1.100051924717402</v>
       </c>
       <c r="AS64" t="n">
         <v>-0.1047372820580752</v>
@@ -12870,7 +12870,7 @@
         <v>-0.3448660178010061</v>
       </c>
       <c r="AY64" t="n">
-        <v>4.90855329642942</v>
+        <v>4.90855385306439</v>
       </c>
       <c r="AZ64" t="inlineStr"/>
       <c r="BA64" t="n">
@@ -13012,16 +13012,16 @@
         <v>139.1372401428223</v>
       </c>
       <c r="AG65" t="n">
-        <v>155.3622073745728</v>
+        <v>155.3622074508667</v>
       </c>
       <c r="AH65" t="n">
         <v>-0.01751682865118132</v>
       </c>
       <c r="AI65" t="n">
-        <v>-0.1201206570226996</v>
+        <v>-0.1201206574547831</v>
       </c>
       <c r="AJ65" t="n">
-        <v>-0.1044331662502238</v>
+        <v>-0.104433166690011</v>
       </c>
       <c r="AK65" t="n">
         <v>183.4681396484375</v>
@@ -13060,13 +13060,13 @@
         <v>-0.1110736815617641</v>
       </c>
       <c r="AW65" t="n">
-        <v>3.067549194698657</v>
+        <v>3.067549656395868</v>
       </c>
       <c r="AX65" t="n">
         <v>-0.1722033776148241</v>
       </c>
       <c r="AY65" t="n">
-        <v>18.08119051493735</v>
+        <v>18.08119178496317</v>
       </c>
       <c r="AZ65" t="inlineStr"/>
       <c r="BA65" t="n">
@@ -13231,13 +13231,13 @@
         <v>51.73245606641598</v>
       </c>
       <c r="AP66" t="n">
-        <v>642900</v>
+        <v>649800</v>
       </c>
       <c r="AQ66" t="n">
-        <v>919884</v>
+        <v>920022</v>
       </c>
       <c r="AR66" t="n">
-        <v>0.6988924690504454</v>
+        <v>0.7062874583433875</v>
       </c>
       <c r="AS66" t="n">
         <v>-0.1075576236201723</v>
@@ -13258,7 +13258,7 @@
         <v>-0.4050275050172019</v>
       </c>
       <c r="AY66" t="n">
-        <v>-0.9254627484067164</v>
+        <v>-0.9254627567728223</v>
       </c>
       <c r="AZ66" t="inlineStr"/>
       <c r="BA66" t="n">
@@ -13423,13 +13423,13 @@
         <v>51.6509471626282</v>
       </c>
       <c r="AP67" t="n">
-        <v>6300100</v>
+        <v>6315400</v>
       </c>
       <c r="AQ67" t="n">
-        <v>10760382</v>
+        <v>10760688</v>
       </c>
       <c r="AR67" t="n">
-        <v>0.5854903664200769</v>
+        <v>0.5868955590943628</v>
       </c>
       <c r="AS67" t="n">
         <v>-0.2356280808282631</v>
@@ -13565,10 +13565,10 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>0.000653701601549983</v>
+        <v>0.0006535307038575411</v>
       </c>
       <c r="AA68" t="n">
-        <v>1125280757744.75</v>
+        <v>1124986574765.25</v>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
@@ -13588,16 +13588,16 @@
         <v>2046908.1275</v>
       </c>
       <c r="AG68" t="n">
-        <v>1027839.74234375</v>
+        <v>1027839.74203125</v>
       </c>
       <c r="AH68" t="n">
         <v>0.1847136505153186</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.359317216583152</v>
+        <v>1.359317217300468</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.9914662210205076</v>
+        <v>0.9914662216259844</v>
       </c>
       <c r="AK68" t="n">
         <v>2919000</v>
@@ -13615,13 +13615,13 @@
         <v>52.89151540734487</v>
       </c>
       <c r="AP68" t="n">
-        <v>7951599</v>
+        <v>7984914</v>
       </c>
       <c r="AQ68" t="n">
-        <v>5523422.08</v>
+        <v>5524088.38</v>
       </c>
       <c r="AR68" t="n">
-        <v>1.439614587628979</v>
+        <v>1.445471804707078</v>
       </c>
       <c r="AS68" t="n">
         <v>0.1714975845410629</v>
@@ -13636,13 +13636,13 @@
         <v>8.383944071693334</v>
       </c>
       <c r="AW68" t="n">
-        <v>18.74907225806337</v>
+        <v>18.74907477111688</v>
       </c>
       <c r="AX68" t="n">
         <v>2.589189177188556</v>
       </c>
       <c r="AY68" t="n">
-        <v>-11.59536170291493</v>
+        <v>-11.59535736290294</v>
       </c>
       <c r="AZ68" t="inlineStr"/>
       <c r="BA68" t="n">
@@ -13761,10 +13761,10 @@
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>0.000653701601549983</v>
+        <v>0.0006535307038575411</v>
       </c>
       <c r="AA69" t="n">
-        <v>1328551373254.562</v>
+        <v>1328204049087.938</v>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
@@ -13784,16 +13784,16 @@
         <v>296350</v>
       </c>
       <c r="AG69" t="n">
-        <v>175546.9338671875</v>
+        <v>175546.9340625</v>
       </c>
       <c r="AH69" t="n">
         <v>0.04437320735616668</v>
       </c>
       <c r="AI69" t="n">
-        <v>0.7630612690402019</v>
+        <v>0.7630612670786303</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.6881525269145843</v>
+        <v>0.6881525250363558</v>
       </c>
       <c r="AK69" t="n">
         <v>362500</v>
@@ -13811,13 +13811,13 @@
         <v>44.37627811860941</v>
       </c>
       <c r="AP69" t="n">
-        <v>31498600</v>
+        <v>31520538</v>
       </c>
       <c r="AQ69" t="n">
-        <v>31334251.9</v>
+        <v>31334690.66</v>
       </c>
       <c r="AR69" t="n">
-        <v>1.005244998365511</v>
+        <v>1.005931041158713</v>
       </c>
       <c r="AS69" t="n">
         <v>-0.05927051671732519</v>
@@ -13826,7 +13826,7 @@
         <v>0.7348654708520179</v>
       </c>
       <c r="AU69" t="n">
-        <v>1.663660366628483</v>
+        <v>1.663660187532005</v>
       </c>
       <c r="AV69" t="n">
         <v>4.430324350712925</v>
@@ -13949,10 +13949,10 @@
         </is>
       </c>
       <c r="Z70" t="n">
-        <v>0.006215117871761322</v>
+        <v>0.00619820598512888</v>
       </c>
       <c r="AA70" t="n">
-        <v>283318000886.8125</v>
+        <v>282547067493.3047</v>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
@@ -14166,16 +14166,16 @@
         <v>320.9159280395508</v>
       </c>
       <c r="AG71" t="n">
-        <v>222.4916584014892</v>
+        <v>222.4916584777832</v>
       </c>
       <c r="AH71" t="n">
         <v>0.09502200719311249</v>
       </c>
       <c r="AI71" t="n">
-        <v>0.5794300163289052</v>
+        <v>0.5794300157873076</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.4423728527406345</v>
+        <v>0.4423728522460346</v>
       </c>
       <c r="AK71" t="n">
         <v>433.3299865722656</v>
@@ -14193,13 +14193,13 @@
         <v>48.27151631497328</v>
       </c>
       <c r="AP71" t="n">
-        <v>18954700</v>
+        <v>18973400</v>
       </c>
       <c r="AQ71" t="n">
-        <v>11510688</v>
+        <v>11511062</v>
       </c>
       <c r="AR71" t="n">
-        <v>1.646704349905062</v>
+        <v>1.64827537198566</v>
       </c>
       <c r="AS71" t="n">
         <v>0.02312283663775716</v>
@@ -14214,13 +14214,13 @@
         <v>2.575380862185094</v>
       </c>
       <c r="AW71" t="n">
-        <v>4.871855144966326</v>
+        <v>4.871854770686348</v>
       </c>
       <c r="AX71" t="n">
         <v>0.9025119429474571</v>
       </c>
       <c r="AY71" t="n">
-        <v>1862.928416350627</v>
+        <v>1862.928710992533</v>
       </c>
       <c r="AZ71" t="inlineStr"/>
       <c r="BA71" t="n">
@@ -14389,13 +14389,13 @@
         <v>48.97250957724861</v>
       </c>
       <c r="AP72" t="n">
-        <v>61316900</v>
+        <v>61844400</v>
       </c>
       <c r="AQ72" t="n">
-        <v>54270470</v>
+        <v>54281020</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.129839118769379</v>
+        <v>1.139337470077018</v>
       </c>
       <c r="AS72" t="n">
         <v>-0.09634387200940042</v>
@@ -14410,13 +14410,13 @@
         <v>7.032652616102846</v>
       </c>
       <c r="AW72" t="n">
-        <v>11.19407550453576</v>
+        <v>11.1940720159052</v>
       </c>
       <c r="AX72" t="n">
         <v>2.094191142429402</v>
       </c>
       <c r="AY72" t="n">
-        <v>721.1265113552224</v>
+        <v>721.1264476342116</v>
       </c>
       <c r="AZ72" t="inlineStr"/>
       <c r="BA72" t="n">
@@ -14585,13 +14585,13 @@
         <v>33.19841922233957</v>
       </c>
       <c r="AP73" t="n">
-        <v>3529100</v>
+        <v>3530800</v>
       </c>
       <c r="AQ73" t="n">
-        <v>3199688</v>
+        <v>3199722</v>
       </c>
       <c r="AR73" t="n">
-        <v>1.102951287750556</v>
+        <v>1.103470864031313</v>
       </c>
       <c r="AS73" t="n">
         <v>-0.3383335535810945</v>
@@ -14781,13 +14781,13 @@
         <v>47.27723873943231</v>
       </c>
       <c r="AP74" t="n">
-        <v>17259300</v>
+        <v>17346200</v>
       </c>
       <c r="AQ74" t="n">
-        <v>13081826</v>
+        <v>13083564</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.319334166346502</v>
+        <v>1.325800829193024</v>
       </c>
       <c r="AS74" t="n">
         <v>-0.04722904722904719</v>
@@ -14948,40 +14948,40 @@
         <v>839.6896154785156</v>
       </c>
       <c r="AG75" t="n">
-        <v>455.8909462738037</v>
+        <v>455.8909461212158</v>
       </c>
       <c r="AH75" t="n">
         <v>-0.02325816822547577</v>
       </c>
       <c r="AI75" t="n">
-        <v>0.7990266747959305</v>
+        <v>0.7990266753980693</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.8418650827389016</v>
+        <v>0.8418650833553787</v>
       </c>
       <c r="AK75" t="n">
         <v>1093.260498046875</v>
       </c>
       <c r="AL75" t="n">
-        <v>140.8470458984375</v>
+        <v>140.8470611572266</v>
       </c>
       <c r="AM75" t="n">
         <v>-0.2498037067928839</v>
       </c>
       <c r="AN75" t="n">
-        <v>4.823054135873997</v>
+        <v>4.823053505028355</v>
       </c>
       <c r="AO75" t="n">
         <v>46.62238839814433</v>
       </c>
       <c r="AP75" t="n">
-        <v>6294100</v>
+        <v>6302800</v>
       </c>
       <c r="AQ75" t="n">
-        <v>4500926</v>
+        <v>4501100</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.398401129012119</v>
+        <v>1.400279931572282</v>
       </c>
       <c r="AS75" t="n">
         <v>-0.1275077454581059</v>
@@ -14993,7 +14993,7 @@
         <v>1.985498642667444</v>
       </c>
       <c r="AV75" t="n">
-        <v>4.442489997210408</v>
+        <v>4.442489446127762</v>
       </c>
       <c r="AW75" t="n">
         <v>10.00629785435567</v>
@@ -15002,7 +15002,7 @@
         <v>1.859346343367094</v>
       </c>
       <c r="AY75" t="n">
-        <v>154.5867890181787</v>
+        <v>154.5868171661456</v>
       </c>
       <c r="AZ75" t="inlineStr"/>
       <c r="BA75" t="n">
@@ -15142,40 +15142,40 @@
         <v>529.5487768554688</v>
       </c>
       <c r="AG76" t="n">
-        <v>290.413363609314</v>
+        <v>290.4133644485474</v>
       </c>
       <c r="AH76" t="n">
         <v>0.01784769138860809</v>
       </c>
       <c r="AI76" t="n">
-        <v>0.8559751979082599</v>
+        <v>0.8559751925448829</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.8234311612734799</v>
+        <v>0.8234311560041483</v>
       </c>
       <c r="AK76" t="n">
         <v>746.22998046875</v>
       </c>
       <c r="AL76" t="n">
-        <v>63.84696960449219</v>
+        <v>63.84696578979492</v>
       </c>
       <c r="AM76" t="n">
         <v>-0.2777025660890453</v>
       </c>
       <c r="AN76" t="n">
-        <v>7.442060811012661</v>
+        <v>7.442061315404779</v>
       </c>
       <c r="AO76" t="n">
         <v>50.78540989629602</v>
       </c>
       <c r="AP76" t="n">
-        <v>8925700</v>
+        <v>8956300</v>
       </c>
       <c r="AQ76" t="n">
-        <v>8810084</v>
+        <v>8810696</v>
       </c>
       <c r="AR76" t="n">
-        <v>1.013123143888299</v>
+        <v>1.016525822704585</v>
       </c>
       <c r="AS76" t="n">
         <v>-0.09252405701525201</v>
@@ -15184,19 +15184,19 @@
         <v>0.8277808122439088</v>
       </c>
       <c r="AU76" t="n">
-        <v>2.131123186684376</v>
+        <v>2.131122909140548</v>
       </c>
       <c r="AV76" t="n">
-        <v>7.21618553873915</v>
+        <v>7.216186494263669</v>
       </c>
       <c r="AW76" t="n">
-        <v>9.125255083010678</v>
+        <v>9.125254357434144</v>
       </c>
       <c r="AX76" t="n">
-        <v>1.873726999098114</v>
+        <v>1.87372723288619</v>
       </c>
       <c r="AY76" t="n">
-        <v>792.1837188797826</v>
+        <v>792.1836493070787</v>
       </c>
       <c r="AZ76" t="inlineStr"/>
       <c r="BA76" t="n">
@@ -15311,10 +15311,10 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>0.03134599700570107</v>
+        <v>0.03132537752389908</v>
       </c>
       <c r="AA77" t="n">
-        <v>26025014796.37939</v>
+        <v>26007895471.09863</v>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
@@ -15361,13 +15361,13 @@
         <v>54.90196078431373</v>
       </c>
       <c r="AP77" t="n">
-        <v>141735235</v>
+        <v>139567309</v>
       </c>
       <c r="AQ77" t="n">
-        <v>238547451.72</v>
+        <v>238504093.2</v>
       </c>
       <c r="AR77" t="n">
-        <v>0.5941595015081723</v>
+        <v>0.5851778354301217</v>
       </c>
       <c r="AS77" t="n">
         <v>0.02785515320334264</v>
@@ -15388,7 +15388,7 @@
         <v>1.04257665453312</v>
       </c>
       <c r="AY77" t="n">
-        <v>3.84687919862932</v>
+        <v>3.846878712907007</v>
       </c>
       <c r="AZ77" t="inlineStr"/>
       <c r="BA77" t="n">
@@ -15503,10 +15503,10 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>0.03134599700570107</v>
+        <v>0.03132537752389908</v>
       </c>
       <c r="AA78" t="n">
-        <v>39774562867.03906</v>
+        <v>39748399051.76562</v>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
@@ -15553,13 +15553,13 @@
         <v>55.79119086460032</v>
       </c>
       <c r="AP78" t="n">
-        <v>61646202</v>
+        <v>60517156</v>
       </c>
       <c r="AQ78" t="n">
-        <v>133116378.08</v>
+        <v>133093797.16</v>
       </c>
       <c r="AR78" t="n">
-        <v>0.4631000549230088</v>
+        <v>0.4546955402230257</v>
       </c>
       <c r="AS78" t="n">
         <v>0.03670886075949364</v>
@@ -15580,7 +15580,7 @@
         <v>0.9782608695652173</v>
       </c>
       <c r="AY78" t="n">
-        <v>-0.5236898227160816</v>
+        <v>-0.5236897212718811</v>
       </c>
       <c r="AZ78" t="inlineStr"/>
       <c r="BA78" t="n">
@@ -15722,16 +15722,16 @@
         <v>139.9099995422363</v>
       </c>
       <c r="AG79" t="n">
-        <v>115.683702507019</v>
+        <v>115.6837024688721</v>
       </c>
       <c r="AH79" t="n">
         <v>0.1019226550880241</v>
       </c>
       <c r="AI79" t="n">
-        <v>0.3326855453955679</v>
+        <v>0.3326855458350242</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0.209418409941948</v>
+        <v>0.2094184103407568</v>
       </c>
       <c r="AK79" t="n">
         <v>181.0800018310547</v>
@@ -15749,13 +15749,13 @@
         <v>38.44462542995721</v>
       </c>
       <c r="AP79" t="n">
-        <v>1930200</v>
+        <v>1931100</v>
       </c>
       <c r="AQ79" t="n">
-        <v>3254274</v>
+        <v>3254292</v>
       </c>
       <c r="AR79" t="n">
-        <v>0.5931276837783174</v>
+        <v>0.5934009609463441</v>
       </c>
       <c r="AS79" t="n">
         <v>-0.1486083686216</v>
@@ -15767,10 +15767,10 @@
         <v>0.454064820011054</v>
       </c>
       <c r="AV79" t="n">
-        <v>0.460389494147311</v>
+        <v>0.460389388604763</v>
       </c>
       <c r="AW79" t="n">
-        <v>1.101840290938381</v>
+        <v>1.101840946798197</v>
       </c>
       <c r="AX79" t="n">
         <v>0.4554303765741006</v>
@@ -16059,13 +16059,13 @@
         <v>52.45790251046104</v>
       </c>
       <c r="AP81" t="n">
-        <v>9764500</v>
+        <v>9766500</v>
       </c>
       <c r="AQ81" t="n">
-        <v>10197862</v>
+        <v>10197902</v>
       </c>
       <c r="AR81" t="n">
-        <v>0.9575046220472487</v>
+        <v>0.9576969851249796</v>
       </c>
       <c r="AS81" t="n">
         <v>-0.08246825730745244</v>
@@ -16228,16 +16228,16 @@
         <v>145.9177880859375</v>
       </c>
       <c r="AG82" t="n">
-        <v>138.3811526107788</v>
+        <v>138.3811506652832</v>
       </c>
       <c r="AH82" t="n">
         <v>0.1279638932092106</v>
       </c>
       <c r="AI82" t="n">
-        <v>0.1893960502036631</v>
+        <v>0.1893960669253392</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.05446287542030248</v>
+        <v>0.05446289024495798</v>
       </c>
       <c r="AK82" t="n">
         <v>176.3200073242188</v>
@@ -16255,13 +16255,13 @@
         <v>61.72649480589948</v>
       </c>
       <c r="AP82" t="n">
-        <v>8303100</v>
+        <v>8304600</v>
       </c>
       <c r="AQ82" t="n">
-        <v>10561806</v>
+        <v>10561836</v>
       </c>
       <c r="AR82" t="n">
-        <v>0.7861439606067372</v>
+        <v>0.7862837483937452</v>
       </c>
       <c r="AS82" t="n">
         <v>0.1166393767357281</v>
@@ -16279,10 +16279,10 @@
         <v>4.069713096474089</v>
       </c>
       <c r="AX82" t="n">
-        <v>0.1821924708424008</v>
+        <v>0.1821923412758299</v>
       </c>
       <c r="AY82" t="n">
-        <v>1314.309893861354</v>
+        <v>1314.309110715601</v>
       </c>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="n">
@@ -16389,7 +16389,7 @@
         </is>
       </c>
       <c r="X83" t="n">
-        <v>42580045824</v>
+        <v>42755395584</v>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
@@ -16397,10 +16397,10 @@
         </is>
       </c>
       <c r="Z83" t="n">
-        <v>1.145869135856628</v>
+        <v>1.144033789634705</v>
       </c>
       <c r="AA83" t="n">
-        <v>48791160313.08252</v>
+        <v>48913617237.29443</v>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
@@ -16414,22 +16414,22 @@
         <v>19.2</v>
       </c>
       <c r="AE83" t="n">
-        <v>145.6999969482422</v>
+        <v>146.3000030517578</v>
       </c>
       <c r="AF83" t="n">
-        <v>144.2400001525879</v>
+        <v>144.2520002746582</v>
       </c>
       <c r="AG83" t="n">
-        <v>105.3565885543823</v>
+        <v>105.3595885848999</v>
       </c>
       <c r="AH83" t="n">
-        <v>0.01012199663137681</v>
+        <v>0.01419739603749126</v>
       </c>
       <c r="AI83" t="n">
-        <v>0.3829225010739186</v>
+        <v>0.3885779644428631</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.3690648314617264</v>
+        <v>0.3691397452488947</v>
       </c>
       <c r="AK83" t="n">
         <v>156.8999938964844</v>
@@ -16438,43 +16438,43 @@
         <v>58.9009895324707</v>
       </c>
       <c r="AM83" t="n">
-        <v>-0.0713830298529613</v>
+        <v>-0.06755889902532419</v>
       </c>
       <c r="AN83" t="n">
-        <v>1.473642600994356</v>
+        <v>1.483829290696485</v>
       </c>
       <c r="AO83" t="n">
-        <v>54.867251379231</v>
+        <v>55.95027211031852</v>
       </c>
       <c r="AP83" t="n">
-        <v>125734</v>
+        <v>539484</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1124330.84</v>
+        <v>1132605.84</v>
       </c>
       <c r="AR83" t="n">
-        <v>0.1118300730770669</v>
+        <v>0.4763210473998615</v>
       </c>
       <c r="AS83" t="n">
-        <v>-0.05481671931765741</v>
+        <v>-0.05092436688643676</v>
       </c>
       <c r="AT83" t="n">
-        <v>0.4026368752701943</v>
+        <v>0.408413064040309</v>
       </c>
       <c r="AU83" t="n">
-        <v>0.6331326365529708</v>
+        <v>0.6398580282503394</v>
       </c>
       <c r="AV83" t="n">
-        <v>1.440737584403156</v>
+        <v>1.450788768194478</v>
       </c>
       <c r="AW83" t="n">
-        <v>4.154716199891519</v>
+        <v>4.175944148660687</v>
       </c>
       <c r="AX83" t="n">
-        <v>0.6331326365529708</v>
+        <v>0.6398580282503394</v>
       </c>
       <c r="AY83" t="n">
-        <v>12.9158406791638</v>
+        <v>12.97314867475823</v>
       </c>
       <c r="AZ83" t="inlineStr"/>
       <c r="BA83" t="n">
@@ -16589,10 +16589,10 @@
         </is>
       </c>
       <c r="Z84" t="n">
-        <v>0.1474947929382324</v>
+        <v>0.1477061361074448</v>
       </c>
       <c r="AA84" t="n">
-        <v>183572300895.0625</v>
+        <v>183835339006.9707</v>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
@@ -16612,16 +16612,16 @@
         <v>1099.623658447266</v>
       </c>
       <c r="AG84" t="n">
-        <v>679.0193696594238</v>
+        <v>679.0193692016602</v>
       </c>
       <c r="AH84" t="n">
         <v>0.01489267844223985</v>
       </c>
       <c r="AI84" t="n">
-        <v>0.6435466348474757</v>
+        <v>0.6435466359554789</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0.6194289994979152</v>
+        <v>0.6194290005896594</v>
       </c>
       <c r="AK84" t="n">
         <v>1382.329956054688</v>
@@ -16657,16 +16657,16 @@
         <v>0.7992280986117701</v>
       </c>
       <c r="AV84" t="n">
-        <v>7.636816357503678</v>
+        <v>7.636817377417076</v>
       </c>
       <c r="AW84" t="n">
-        <v>33.57516829755242</v>
+        <v>33.57517647004597</v>
       </c>
       <c r="AX84" t="n">
         <v>0.7919851721657041</v>
       </c>
       <c r="AY84" t="n">
-        <v>240.1334643461855</v>
+        <v>240.133514034121</v>
       </c>
       <c r="AZ84" t="inlineStr"/>
       <c r="BA84" t="n">
@@ -16835,13 +16835,13 @@
         <v>55.57368157652713</v>
       </c>
       <c r="AP85" t="n">
-        <v>7247100</v>
+        <v>7258800</v>
       </c>
       <c r="AQ85" t="n">
-        <v>6320728</v>
+        <v>6320962</v>
       </c>
       <c r="AR85" t="n">
-        <v>1.146560965762172</v>
+        <v>1.148369504515294</v>
       </c>
       <c r="AS85" t="n">
         <v>0.117951267742004</v>
@@ -17029,13 +17029,13 @@
         <v>45.02764286885688</v>
       </c>
       <c r="AP86" t="n">
-        <v>6965900</v>
+        <v>6975900</v>
       </c>
       <c r="AQ86" t="n">
-        <v>6299064</v>
+        <v>6299264</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.105862712301383</v>
+        <v>1.107415088492878</v>
       </c>
       <c r="AS86" t="n">
         <v>-0.2013990580440062</v>
@@ -17225,13 +17225,13 @@
         <v>45.1306306405907</v>
       </c>
       <c r="AP87" t="n">
-        <v>9047500</v>
+        <v>9061700</v>
       </c>
       <c r="AQ87" t="n">
-        <v>8677948</v>
+        <v>8678232</v>
       </c>
       <c r="AR87" t="n">
-        <v>1.042585182580029</v>
+        <v>1.044187341384743</v>
       </c>
       <c r="AS87" t="n">
         <v>0.127260003643338</v>
@@ -17392,40 +17392,40 @@
         <v>188.4265856933594</v>
       </c>
       <c r="AG88" t="n">
-        <v>126.8898726272583</v>
+        <v>126.8898728179932</v>
       </c>
       <c r="AH88" t="n">
         <v>0.04438549667499592</v>
       </c>
       <c r="AI88" t="n">
-        <v>0.5508723368665331</v>
+        <v>0.550872334535335</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.4849615796121609</v>
+        <v>0.4849615773800369</v>
       </c>
       <c r="AK88" t="n">
         <v>255.6900024414062</v>
       </c>
       <c r="AL88" t="n">
-        <v>51.04203414916992</v>
+        <v>51.04203796386719</v>
       </c>
       <c r="AM88" t="n">
         <v>-0.2303571066247337</v>
       </c>
       <c r="AN88" t="n">
-        <v>2.855449661567478</v>
+        <v>2.855449373425118</v>
       </c>
       <c r="AO88" t="n">
         <v>54.85511178212172</v>
       </c>
       <c r="AP88" t="n">
-        <v>21142600</v>
+        <v>21192200</v>
       </c>
       <c r="AQ88" t="n">
-        <v>15729750</v>
+        <v>15730742</v>
       </c>
       <c r="AR88" t="n">
-        <v>1.344115450023045</v>
+        <v>1.347183750137152</v>
       </c>
       <c r="AS88" t="n">
         <v>-0.01977486217040092</v>
@@ -17446,7 +17446,7 @@
         <v>1.177781571539224</v>
       </c>
       <c r="AY88" t="n">
-        <v>255.704059578942</v>
+        <v>255.7039997014336</v>
       </c>
       <c r="AZ88" t="inlineStr"/>
       <c r="BA88" t="n">
@@ -17784,16 +17784,16 @@
         <v>93.46663955688477</v>
       </c>
       <c r="AG90" t="n">
-        <v>73.11352228164672</v>
+        <v>73.11352226257324</v>
       </c>
       <c r="AH90" t="n">
         <v>-0.09443626313177067</v>
       </c>
       <c r="AI90" t="n">
-        <v>0.1576517824377222</v>
+        <v>0.1576517827397244</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0.2783769218070784</v>
+        <v>0.2783769221405747</v>
       </c>
       <c r="AK90" t="n">
         <v>102.7099990844727</v>
@@ -17811,13 +17811,13 @@
         <v>41.7132535171701</v>
       </c>
       <c r="AP90" t="n">
-        <v>14794000</v>
+        <v>14795800</v>
       </c>
       <c r="AQ90" t="n">
-        <v>12563634</v>
+        <v>12563670</v>
       </c>
       <c r="AR90" t="n">
-        <v>1.17752554714663</v>
+        <v>1.177665443298017</v>
       </c>
       <c r="AS90" t="n">
         <v>-0.1233558082408838</v>
@@ -17832,13 +17832,13 @@
         <v>0.18829792715007</v>
       </c>
       <c r="AW90" t="n">
-        <v>0.2653072117807713</v>
+        <v>0.2653073560940982</v>
       </c>
       <c r="AX90" t="n">
         <v>0.3157878881324572</v>
       </c>
       <c r="AY90" t="n">
-        <v>480.7969615741064</v>
+        <v>480.7968798401546</v>
       </c>
       <c r="AZ90" t="inlineStr"/>
       <c r="BA90" t="n">
@@ -18003,13 +18003,13 @@
         <v>39.16539110922148</v>
       </c>
       <c r="AP91" t="n">
-        <v>4137100</v>
+        <v>4138300</v>
       </c>
       <c r="AQ91" t="n">
-        <v>3853744</v>
+        <v>3853768</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.073527457973337</v>
+        <v>1.073832155957494</v>
       </c>
       <c r="AS91" t="n">
         <v>-0.172660524327456</v>
@@ -18145,10 +18145,10 @@
         </is>
       </c>
       <c r="Z92" t="n">
-        <v>0.1474947929382324</v>
+        <v>0.1477061361074448</v>
       </c>
       <c r="AA92" t="n">
-        <v>26527634836.39844</v>
+        <v>26565645903.13745</v>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>4.054186089094295</v>
       </c>
       <c r="AW92" t="n">
-        <v>8.716713904211197</v>
+        <v>8.716714732819474</v>
       </c>
       <c r="AX92" t="n">
         <v>2.068332573948467</v>
@@ -18337,10 +18337,10 @@
         </is>
       </c>
       <c r="Z93" t="n">
-        <v>0.1474947929382324</v>
+        <v>0.1477061361074448</v>
       </c>
       <c r="AA93" t="n">
-        <v>108169579266.4062</v>
+        <v>108324573902.0752</v>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>0.7292197037105557</v>
       </c>
       <c r="AY93" t="n">
-        <v>284.2523557003436</v>
+        <v>284.2523741412754</v>
       </c>
       <c r="AZ93" t="inlineStr"/>
       <c r="BA93" t="n">
@@ -18583,13 +18583,13 @@
         <v>41.6450519969167</v>
       </c>
       <c r="AP94" t="n">
-        <v>26749500</v>
+        <v>26788900</v>
       </c>
       <c r="AQ94" t="n">
-        <v>27280644</v>
+        <v>27281432</v>
       </c>
       <c r="AR94" t="n">
-        <v>0.9805303716437193</v>
+        <v>0.9819462556071104</v>
       </c>
       <c r="AS94" t="n">
         <v>-0.2466655334868972</v>
@@ -18610,7 +18610,7 @@
         <v>0.04072788759895696</v>
       </c>
       <c r="AY94" t="n">
-        <v>316.4115837281723</v>
+        <v>316.4116836894942</v>
       </c>
       <c r="AZ94" t="inlineStr"/>
       <c r="BA94" t="n">
@@ -18779,13 +18779,13 @@
         <v>42.26502405412126</v>
       </c>
       <c r="AP95" t="n">
-        <v>38435900</v>
+        <v>38579900</v>
       </c>
       <c r="AQ95" t="n">
-        <v>46063942</v>
+        <v>46066822</v>
       </c>
       <c r="AR95" t="n">
-        <v>0.8344031867702508</v>
+        <v>0.837476915598823</v>
       </c>
       <c r="AS95" t="n">
         <v>-0.1868390576851539</v>
@@ -18800,13 +18800,13 @@
         <v>2.312499864772374</v>
       </c>
       <c r="AW95" t="n">
-        <v>3.442105612207184</v>
+        <v>3.442106225952319</v>
       </c>
       <c r="AX95" t="n">
         <v>1.747391867747758</v>
       </c>
       <c r="AY95" t="n">
-        <v>19.21793582350067</v>
+        <v>19.21793423424472</v>
       </c>
       <c r="AZ95" t="inlineStr"/>
       <c r="BA95" t="n">
@@ -18913,7 +18913,7 @@
         </is>
       </c>
       <c r="X96" t="n">
-        <v>6137413120</v>
+        <v>6211779072</v>
       </c>
       <c r="Y96" t="inlineStr">
         <is>
@@ -18921,10 +18921,10 @@
         </is>
       </c>
       <c r="Z96" t="n">
-        <v>1.145869135856628</v>
+        <v>1.144033789634705</v>
       </c>
       <c r="AA96" t="n">
-        <v>7032672268.209534</v>
+        <v>7106485152.113708</v>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
@@ -18938,22 +18938,22 @@
         <v>25.1</v>
       </c>
       <c r="AE96" t="n">
-        <v>140.3000030517578</v>
+        <v>142</v>
       </c>
       <c r="AF96" t="n">
-        <v>153.1125091552734</v>
+        <v>153.1465090942383</v>
       </c>
       <c r="AG96" t="n">
-        <v>130.880330657959</v>
+        <v>130.8888306427002</v>
       </c>
       <c r="AH96" t="n">
-        <v>-0.08368033529201913</v>
+        <v>-0.07278330508584618</v>
       </c>
       <c r="AI96" t="n">
-        <v>0.07197164269408884</v>
+        <v>0.08489012624485159</v>
       </c>
       <c r="AJ96" t="n">
-        <v>0.1698664603424311</v>
+        <v>0.1700502506000454</v>
       </c>
       <c r="AK96" t="n">
         <v>164.8832092285156</v>
@@ -18962,43 +18962,43 @@
         <v>107.2379150390625</v>
       </c>
       <c r="AM96" t="n">
-        <v>-0.1490946609529377</v>
+        <v>-0.1387843512725497</v>
       </c>
       <c r="AN96" t="n">
-        <v>0.3083059569057465</v>
+        <v>0.324158530574518</v>
       </c>
       <c r="AO96" t="n">
-        <v>40.43061921498253</v>
+        <v>42.75861464177788</v>
       </c>
       <c r="AP96" t="n">
-        <v>24790</v>
+        <v>123663</v>
       </c>
       <c r="AQ96" t="n">
-        <v>135853.5</v>
+        <v>137830.96</v>
       </c>
       <c r="AR96" t="n">
-        <v>0.1824759759593974</v>
+        <v>0.897207710081973</v>
       </c>
       <c r="AS96" t="n">
-        <v>-0.09366924879938077</v>
+        <v>-0.08268735658537485</v>
       </c>
       <c r="AT96" t="n">
-        <v>0.2148554635029101</v>
+        <v>0.2295757096582036</v>
       </c>
       <c r="AU96" t="n">
-        <v>0.1267113595743281</v>
+        <v>0.1403635750494736</v>
       </c>
       <c r="AV96" t="n">
-        <v>0.3083059569057465</v>
+        <v>0.324158530574518</v>
       </c>
       <c r="AW96" t="n">
-        <v>0.945016128082049</v>
+        <v>0.9685836363507518</v>
       </c>
       <c r="AX96" t="n">
-        <v>0.1135386113752244</v>
+        <v>0.1270312143681791</v>
       </c>
       <c r="AY96" t="n">
-        <v>7.687326389545014</v>
+        <v>7.792589597167055</v>
       </c>
       <c r="AZ96" t="inlineStr"/>
       <c r="BA96" t="n">
@@ -19105,7 +19105,7 @@
         </is>
       </c>
       <c r="X97" t="n">
-        <v>52327993344</v>
+        <v>52461617152</v>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
@@ -19113,10 +19113,10 @@
         </is>
       </c>
       <c r="Z97" t="n">
-        <v>0.1532780826091766</v>
+        <v>0.1530245244503021</v>
       </c>
       <c r="AA97" t="n">
-        <v>8020734486.554077</v>
+        <v>8027914016.578613</v>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
@@ -19130,22 +19130,22 @@
         <v>25.2</v>
       </c>
       <c r="AE97" t="n">
-        <v>979</v>
+        <v>981.5</v>
       </c>
       <c r="AF97" t="n">
-        <v>994.01</v>
+        <v>994.0599999999999</v>
       </c>
       <c r="AG97" t="n">
-        <v>827.585</v>
+        <v>827.5975</v>
       </c>
       <c r="AH97" t="n">
-        <v>-0.01510045170571728</v>
+        <v>-0.01263505221012806</v>
       </c>
       <c r="AI97" t="n">
-        <v>0.1829600584834186</v>
+        <v>0.1859629832134584</v>
       </c>
       <c r="AJ97" t="n">
-        <v>0.2010971682667038</v>
+        <v>0.2011394427846869</v>
       </c>
       <c r="AK97" t="n">
         <v>1112</v>
@@ -19154,43 +19154,43 @@
         <v>497.7999877929688</v>
       </c>
       <c r="AM97" t="n">
-        <v>-0.1196043165467626</v>
+        <v>-0.1173561151079137</v>
       </c>
       <c r="AN97" t="n">
-        <v>0.9666533226335849</v>
+        <v>0.971675419984539</v>
       </c>
       <c r="AO97" t="n">
-        <v>47.85992217898833</v>
+        <v>48.36223506743738</v>
       </c>
       <c r="AP97" t="n">
-        <v>19441</v>
+        <v>90824</v>
       </c>
       <c r="AQ97" t="n">
-        <v>143261.5</v>
+        <v>144689.16</v>
       </c>
       <c r="AR97" t="n">
-        <v>0.1357028929614726</v>
+        <v>0.6277180681676499</v>
       </c>
       <c r="AS97" t="n">
-        <v>-0.04019607843137252</v>
+        <v>-0.03774509803921566</v>
       </c>
       <c r="AT97" t="n">
-        <v>0.2056650246305418</v>
+        <v>0.208743842364532</v>
       </c>
       <c r="AU97" t="n">
-        <v>0.2408111533586819</v>
+        <v>0.2439797211660331</v>
       </c>
       <c r="AV97" t="n">
-        <v>0.9102439024390243</v>
+        <v>0.9151219512195121</v>
       </c>
       <c r="AW97" t="n">
-        <v>3.051129550474996</v>
+        <v>3.061474620828609</v>
       </c>
       <c r="AX97" t="n">
-        <v>0.1881067961165048</v>
+        <v>0.1911407766990292</v>
       </c>
       <c r="AY97" t="n">
-        <v>27.9857091435572</v>
+        <v>28.05972780837731</v>
       </c>
       <c r="AZ97" t="inlineStr"/>
       <c r="BA97" t="n">
@@ -19355,13 +19355,13 @@
         <v>34.36531931855089</v>
       </c>
       <c r="AP98" t="n">
-        <v>77939100</v>
+        <v>78276600</v>
       </c>
       <c r="AQ98" t="n">
-        <v>119837476</v>
+        <v>119844226</v>
       </c>
       <c r="AR98" t="n">
-        <v>0.6503733439779723</v>
+        <v>0.6531528686246428</v>
       </c>
       <c r="AS98" t="n">
         <v>-0.2785415406406639</v>
@@ -19376,13 +19376,13 @@
         <v>1.347048653512317</v>
       </c>
       <c r="AW98" t="n">
-        <v>1.465491230101939</v>
+        <v>1.465491710387839</v>
       </c>
       <c r="AX98" t="n">
         <v>0.8540705484579336</v>
       </c>
       <c r="AY98" t="n">
-        <v>19.19928789130941</v>
+        <v>19.19928990617002</v>
       </c>
       <c r="AZ98" t="inlineStr"/>
       <c r="BA98" t="n">
@@ -19551,13 +19551,13 @@
         <v>44.55866688068173</v>
       </c>
       <c r="AP99" t="n">
-        <v>2153800</v>
+        <v>2155600</v>
       </c>
       <c r="AQ99" t="n">
-        <v>2944024</v>
+        <v>2944060</v>
       </c>
       <c r="AR99" t="n">
-        <v>0.7315837099154083</v>
+        <v>0.7321861646841437</v>
       </c>
       <c r="AS99" t="n">
         <v>-0.3190193033509371</v>
@@ -19747,13 +19747,13 @@
         <v>34.91929555406399</v>
       </c>
       <c r="AP100" t="n">
-        <v>5217800</v>
+        <v>5229100</v>
       </c>
       <c r="AQ100" t="n">
-        <v>5957254</v>
+        <v>5957480</v>
       </c>
       <c r="AR100" t="n">
-        <v>0.8758733470152523</v>
+        <v>0.8777368954658681</v>
       </c>
       <c r="AS100" t="n">
         <v>-0.2235394378206623</v>
@@ -19916,28 +19916,28 @@
         <v>207.8093933105469</v>
       </c>
       <c r="AG101" t="n">
-        <v>220.1607160949707</v>
+        <v>220.1607162475586</v>
       </c>
       <c r="AH101" t="n">
         <v>-0.04989856668146264</v>
       </c>
       <c r="AI101" t="n">
-        <v>-0.1032005802695674</v>
+        <v>-0.1032005808911166</v>
       </c>
       <c r="AJ101" t="n">
-        <v>-0.05610139267123304</v>
+        <v>-0.05610139332542563</v>
       </c>
       <c r="AK101" t="n">
-        <v>247.2834167480469</v>
+        <v>247.2834320068359</v>
       </c>
       <c r="AL101" t="n">
-        <v>169.3577117919922</v>
+        <v>169.3577423095703</v>
       </c>
       <c r="AM101" t="n">
-        <v>-0.2015639178806126</v>
+        <v>-0.2015639671486434</v>
       </c>
       <c r="AN101" t="n">
-        <v>0.1658164269714815</v>
+        <v>0.1658162168960906</v>
       </c>
       <c r="AO101" t="n">
         <v>39.79793589192133</v>
@@ -19961,16 +19961,16 @@
         <v>-0.1261457603330571</v>
       </c>
       <c r="AV101" t="n">
-        <v>0.1505554076049385</v>
+        <v>0.1505553052992084</v>
       </c>
       <c r="AW101" t="n">
-        <v>0.5939330305424741</v>
+        <v>0.5939328341951402</v>
       </c>
       <c r="AX101" t="n">
         <v>-0.1475406250424107</v>
       </c>
       <c r="AY101" t="n">
-        <v>6.388353208016032</v>
+        <v>6.388353735355485</v>
       </c>
       <c r="AZ101" t="inlineStr"/>
       <c r="BA101" t="n">
@@ -20135,13 +20135,13 @@
         <v>37.61368387887931</v>
       </c>
       <c r="AP102" t="n">
-        <v>16845300</v>
+        <v>16848000</v>
       </c>
       <c r="AQ102" t="n">
-        <v>13072744</v>
+        <v>13072798</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.288581800423844</v>
+        <v>1.288783013399274</v>
       </c>
       <c r="AS102" t="n">
         <v>-0.1415497841985546</v>
@@ -20156,13 +20156,13 @@
         <v>1.179000769200366</v>
       </c>
       <c r="AW102" t="n">
-        <v>0.9515702383921736</v>
+        <v>0.9515704509563081</v>
       </c>
       <c r="AX102" t="n">
         <v>1.507202654753022</v>
       </c>
       <c r="AY102" t="n">
-        <v>30.21470654782139</v>
+        <v>30.21471334533662</v>
       </c>
       <c r="AZ102" t="inlineStr"/>
       <c r="BA102" t="n">
@@ -20327,13 +20327,13 @@
         <v>51.51515566336486</v>
       </c>
       <c r="AP103" t="n">
-        <v>28030600</v>
+        <v>28189000</v>
       </c>
       <c r="AQ103" t="n">
-        <v>35085020</v>
+        <v>35088188</v>
       </c>
       <c r="AR103" t="n">
-        <v>0.7989335619589215</v>
+        <v>0.8033757685064843</v>
       </c>
       <c r="AS103" t="n">
         <v>-0.2045639882021086</v>
@@ -20467,10 +20467,10 @@
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>0.006215117871761322</v>
+        <v>0.00619820598512888</v>
       </c>
       <c r="AA104" t="n">
-        <v>44449570158.73047</v>
+        <v>44328618938.35205</v>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
@@ -20538,13 +20538,13 @@
         <v>0.6029249715744189</v>
       </c>
       <c r="AW104" t="n">
-        <v>0.3122078204986392</v>
+        <v>0.3122075587306301</v>
       </c>
       <c r="AX104" t="n">
         <v>0.2804182101509511</v>
       </c>
       <c r="AY104" t="n">
-        <v>22.96189836969774</v>
+        <v>22.96190109744374</v>
       </c>
       <c r="AZ104" t="inlineStr"/>
       <c r="BA104" t="n">
@@ -20659,10 +20659,10 @@
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>0.1532806605100632</v>
+        <v>0.1530245244503021</v>
       </c>
       <c r="AA105" t="n">
-        <v>83181348.22944927</v>
+        <v>83042349.98459435</v>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
@@ -20876,40 +20876,40 @@
         <v>406.694769897461</v>
       </c>
       <c r="AG106" t="n">
-        <v>369.7095411682129</v>
+        <v>369.7095402526855</v>
       </c>
       <c r="AH106" t="n">
         <v>-0.02010053113259891</v>
       </c>
       <c r="AI106" t="n">
-        <v>0.07792725000935441</v>
+        <v>0.07792725267867096</v>
       </c>
       <c r="AJ106" t="n">
-        <v>0.1000386103436273</v>
+        <v>0.1000386130676993</v>
       </c>
       <c r="AK106" t="n">
         <v>435.7799987792969</v>
       </c>
       <c r="AL106" t="n">
-        <v>313.9706115722656</v>
+        <v>313.9706420898438</v>
       </c>
       <c r="AM106" t="n">
         <v>-0.08550188138509662</v>
       </c>
       <c r="AN106" t="n">
-        <v>0.2692907371744435</v>
+        <v>0.2692906138008726</v>
       </c>
       <c r="AO106" t="n">
         <v>51.51232629106249</v>
       </c>
       <c r="AP106" t="n">
-        <v>2601600</v>
+        <v>2602200</v>
       </c>
       <c r="AQ106" t="n">
-        <v>2734486</v>
+        <v>2734498</v>
       </c>
       <c r="AR106" t="n">
-        <v>0.9514036641621131</v>
+        <v>0.9516189077483326</v>
       </c>
       <c r="AS106" t="n">
         <v>-0.05386862349352917</v>
@@ -20921,16 +20921,16 @@
         <v>0.2585708173976435</v>
       </c>
       <c r="AV106" t="n">
-        <v>0.1255054611828823</v>
+        <v>0.125505558188125</v>
       </c>
       <c r="AW106" t="n">
-        <v>1.942022654472657</v>
+        <v>1.942022985879928</v>
       </c>
       <c r="AX106" t="n">
         <v>0.224733195479329</v>
       </c>
       <c r="AY106" t="n">
-        <v>1152.82371512424</v>
+        <v>1152.823615565617</v>
       </c>
       <c r="AZ106" t="inlineStr"/>
       <c r="BA106" t="n">
@@ -21037,7 +21037,7 @@
         </is>
       </c>
       <c r="X107" t="n">
-        <v>37653970944</v>
+        <v>37470994432</v>
       </c>
       <c r="Y107" t="inlineStr">
         <is>
@@ -21045,10 +21045,10 @@
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>1.145869135856628</v>
+        <v>1.144033789634705</v>
       </c>
       <c r="AA107" t="n">
-        <v>43146523147.17188</v>
+        <v>42868083761.42188</v>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
@@ -21062,22 +21062,22 @@
         <v>20.2</v>
       </c>
       <c r="AE107" t="n">
-        <v>144.0500030517578</v>
+        <v>143.3500061035156</v>
       </c>
       <c r="AF107" t="n">
-        <v>146.9828268432617</v>
+        <v>146.9688269042969</v>
       </c>
       <c r="AG107" t="n">
-        <v>138.2835628128052</v>
+        <v>138.280062828064</v>
       </c>
       <c r="AH107" t="n">
-        <v>-0.01995351330826811</v>
+        <v>-0.0246230501869471</v>
       </c>
       <c r="AI107" t="n">
-        <v>0.04170011331541024</v>
+        <v>0.03666431133861714</v>
       </c>
       <c r="AJ107" t="n">
-        <v>0.06290887979385329</v>
+        <v>0.06283453954628593</v>
       </c>
       <c r="AK107" t="n">
         <v>157.5401306152344</v>
@@ -21086,43 +21086,43 @@
         <v>109.7664031982422</v>
       </c>
       <c r="AM107" t="n">
-        <v>-0.08562978531751986</v>
+        <v>-0.09007307824554101</v>
       </c>
       <c r="AN107" t="n">
-        <v>0.3123323608554265</v>
+        <v>0.3059552096703051</v>
       </c>
       <c r="AO107" t="n">
-        <v>59.21909381942587</v>
+        <v>58.59031577305801</v>
       </c>
       <c r="AP107" t="n">
-        <v>43435</v>
+        <v>329172</v>
       </c>
       <c r="AQ107" t="n">
-        <v>584928.28</v>
+        <v>590643.02</v>
       </c>
       <c r="AR107" t="n">
-        <v>0.07425696702508554</v>
+        <v>0.5573112503725177</v>
       </c>
       <c r="AS107" t="n">
-        <v>0.0003472434149847103</v>
+        <v>-0.004513846503363728</v>
       </c>
       <c r="AT107" t="n">
-        <v>0.07917943842884623</v>
+        <v>0.07393527114316778</v>
       </c>
       <c r="AU107" t="n">
-        <v>0.1636778411674571</v>
+        <v>0.1580230621303362</v>
       </c>
       <c r="AV107" t="n">
-        <v>0.2869510557834003</v>
+        <v>0.2806972425761785</v>
       </c>
       <c r="AW107" t="n">
-        <v>0.6689323438320669</v>
+        <v>0.6608223297900306</v>
       </c>
       <c r="AX107" t="n">
-        <v>0.1454669570154181</v>
+        <v>0.1399006719946885</v>
       </c>
       <c r="AY107" t="n">
-        <v>9.638426254669403</v>
+        <v>9.58672985928861</v>
       </c>
       <c r="AZ107" t="inlineStr"/>
       <c r="BA107" t="n">
@@ -21229,7 +21229,7 @@
         </is>
       </c>
       <c r="X108" t="n">
-        <v>156609036288</v>
+        <v>157508780032</v>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
@@ -21237,10 +21237,10 @@
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>1.145869135856628</v>
+        <v>1.144033789634705</v>
       </c>
       <c r="AA108" t="n">
-        <v>179453461078.6699</v>
+        <v>180195366520.748</v>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
@@ -21254,22 +21254,22 @@
         <v>26.5</v>
       </c>
       <c r="AE108" t="n">
-        <v>278.5</v>
+        <v>280.1000061035156</v>
       </c>
       <c r="AF108" t="n">
-        <v>272.6139846801758</v>
+        <v>272.6459848022461</v>
       </c>
       <c r="AG108" t="n">
-        <v>248.600802230835</v>
+        <v>248.6088022613525</v>
       </c>
       <c r="AH108" t="n">
-        <v>0.02159102485783904</v>
+        <v>0.02733956015041272</v>
       </c>
       <c r="AI108" t="n">
-        <v>0.1202699166730867</v>
+        <v>0.1266697058017183</v>
       </c>
       <c r="AJ108" t="n">
-        <v>0.09659334255504004</v>
+        <v>0.09668677183692087</v>
       </c>
       <c r="AK108" t="n">
         <v>292.75</v>
@@ -21278,43 +21278,43 @@
         <v>206.813720703125</v>
       </c>
       <c r="AM108" t="n">
-        <v>-0.04867634500426987</v>
+        <v>-0.04321090997945132</v>
       </c>
       <c r="AN108" t="n">
-        <v>0.3466224535449394</v>
+        <v>0.3543589136699055</v>
       </c>
       <c r="AO108" t="n">
-        <v>56.30188849596086</v>
+        <v>57.33235581183011</v>
       </c>
       <c r="AP108" t="n">
-        <v>74459</v>
+        <v>621910</v>
       </c>
       <c r="AQ108" t="n">
-        <v>975967.4</v>
+        <v>986916.42</v>
       </c>
       <c r="AR108" t="n">
-        <v>0.07629250731120732</v>
+        <v>0.6301546791571265</v>
       </c>
       <c r="AS108" t="n">
-        <v>0.03512362994159646</v>
+        <v>0.04107050292471959</v>
       </c>
       <c r="AT108" t="n">
-        <v>0.2126819169778416</v>
+        <v>0.2196488773684613</v>
       </c>
       <c r="AU108" t="n">
-        <v>0.1753919164217312</v>
+        <v>0.1821446425987427</v>
       </c>
       <c r="AV108" t="n">
-        <v>0.2422400561043114</v>
+        <v>0.2493768305093329</v>
       </c>
       <c r="AW108" t="n">
-        <v>1.120147831363704</v>
+        <v>1.132328012648557</v>
       </c>
       <c r="AX108" t="n">
-        <v>0.1932421601975371</v>
+        <v>0.2000974375378899</v>
       </c>
       <c r="AY108" t="n">
-        <v>13.9657362061881</v>
+        <v>14.05171254362061</v>
       </c>
       <c r="AZ108" t="inlineStr"/>
       <c r="BA108" t="n">
@@ -21456,16 +21456,16 @@
         <v>470.6744177246094</v>
       </c>
       <c r="AG109" t="n">
-        <v>432.5672790527344</v>
+        <v>432.5672796630859</v>
       </c>
       <c r="AH109" t="n">
         <v>0.01584022176995692</v>
       </c>
       <c r="AI109" t="n">
-        <v>0.1053309578335526</v>
+        <v>0.1053309562739329</v>
       </c>
       <c r="AJ109" t="n">
-        <v>0.08809528717781112</v>
+        <v>0.08809528564251101</v>
       </c>
       <c r="AK109" t="n">
         <v>503.4599914550781</v>
@@ -21498,19 +21498,19 @@
         <v>0.1220993649725488</v>
       </c>
       <c r="AU109" t="n">
-        <v>0.2342520907037224</v>
+        <v>0.23425199347115</v>
       </c>
       <c r="AV109" t="n">
-        <v>0.112676806536226</v>
+        <v>0.1126767275153016</v>
       </c>
       <c r="AW109" t="n">
-        <v>1.823918522642057</v>
+        <v>1.823918013653156</v>
       </c>
       <c r="AX109" t="n">
         <v>0.2069620222934965</v>
       </c>
       <c r="AY109" t="n">
-        <v>535.316584214782</v>
+        <v>535.3164049287656</v>
       </c>
       <c r="AZ109" t="inlineStr"/>
       <c r="BA109" t="n">
@@ -21625,10 +21625,10 @@
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>0.03134599700570107</v>
+        <v>0.03132537752389908</v>
       </c>
       <c r="AA110" t="n">
-        <v>168951864924.748</v>
+        <v>168840727930.0117</v>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
@@ -21675,13 +21675,13 @@
         <v>41.29871023170327</v>
       </c>
       <c r="AP110" t="n">
-        <v>15169564</v>
+        <v>14301078</v>
       </c>
       <c r="AQ110" t="n">
-        <v>11730352.86</v>
+        <v>11712983.14</v>
       </c>
       <c r="AR110" t="n">
-        <v>1.293189060981069</v>
+        <v>1.22095949674525</v>
       </c>
       <c r="AS110" t="n">
         <v>-0.1398555489245108</v>
@@ -21696,13 +21696,13 @@
         <v>4.214625425425027</v>
       </c>
       <c r="AW110" t="n">
-        <v>6.592861903997761</v>
+        <v>6.592861056101114</v>
       </c>
       <c r="AX110" t="n">
         <v>1.096331813966337</v>
       </c>
       <c r="AY110" t="n">
-        <v>83.00149765294866</v>
+        <v>83.00147170841333</v>
       </c>
       <c r="AZ110" t="inlineStr"/>
       <c r="BA110" t="n">
@@ -21844,40 +21844,40 @@
         <v>408.1078063964844</v>
       </c>
       <c r="AG111" t="n">
-        <v>316.0571625518799</v>
+        <v>316.0571635437012</v>
       </c>
       <c r="AH111" t="n">
         <v>-0.07583242037842475</v>
       </c>
       <c r="AI111" t="n">
-        <v>0.1933284492491123</v>
+        <v>0.1933284455043194</v>
       </c>
       <c r="AJ111" t="n">
-        <v>0.2912468209907904</v>
+        <v>0.2912468169387192</v>
       </c>
       <c r="AK111" t="n">
         <v>445.4800109863281</v>
       </c>
       <c r="AL111" t="n">
-        <v>217.7568817138672</v>
+        <v>217.7568664550781</v>
       </c>
       <c r="AM111" t="n">
         <v>-0.1533626776495601</v>
       </c>
       <c r="AN111" t="n">
-        <v>0.7320233495890067</v>
+        <v>0.7320234709563802</v>
       </c>
       <c r="AO111" t="n">
         <v>39.70198126167281</v>
       </c>
       <c r="AP111" t="n">
-        <v>6144100</v>
+        <v>6144800</v>
       </c>
       <c r="AQ111" t="n">
-        <v>4941630</v>
+        <v>4941644</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.243334689161269</v>
+        <v>1.24347281997651</v>
       </c>
       <c r="AS111" t="n">
         <v>-0.1382548676152703</v>
@@ -21889,16 +21889,16 @@
         <v>0.3988836575230703</v>
       </c>
       <c r="AV111" t="n">
-        <v>0.5591388313125183</v>
+        <v>0.5591390280078554</v>
       </c>
       <c r="AW111" t="n">
-        <v>1.448391049057945</v>
+        <v>1.448391291582685</v>
       </c>
       <c r="AX111" t="n">
         <v>0.3859036311571151</v>
       </c>
       <c r="AY111" t="n">
-        <v>849.198250049613</v>
+        <v>849.1983071665513</v>
       </c>
       <c r="AZ111" t="inlineStr"/>
       <c r="BA111" t="n">
@@ -22063,13 +22063,13 @@
         <v>34.63694613138524</v>
       </c>
       <c r="AP112" t="n">
-        <v>1787600</v>
+        <v>1788100</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1435666</v>
+        <v>1435676</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.245136403592479</v>
+        <v>1.245475998762952</v>
       </c>
       <c r="AS112" t="n">
         <v>-0.2352746344594717</v>
@@ -22090,7 +22090,7 @@
         <v>0.6402954706720456</v>
       </c>
       <c r="AY112" t="n">
-        <v>260.6639916397898</v>
+        <v>260.6639739707714</v>
       </c>
       <c r="AZ112" t="inlineStr"/>
       <c r="BA112" t="n">
@@ -22280,13 +22280,13 @@
         <v>0.6969826739866007</v>
       </c>
       <c r="AW113" t="n">
-        <v>2.659031957042135</v>
+        <v>2.659032274227168</v>
       </c>
       <c r="AX113" t="n">
         <v>0.3806377349946872</v>
       </c>
       <c r="AY113" t="n">
-        <v>152.4500923040569</v>
+        <v>152.4501620348754</v>
       </c>
       <c r="AZ113" t="inlineStr"/>
       <c r="BA113" t="n">
@@ -22631,25 +22631,25 @@
         <v>184.3399963378906</v>
       </c>
       <c r="AL115" t="n">
-        <v>72.85917663574219</v>
+        <v>72.85916900634766</v>
       </c>
       <c r="AM115" t="n">
         <v>-0.1746229959905325</v>
       </c>
       <c r="AN115" t="n">
-        <v>1.088274956182319</v>
+        <v>1.088275174854502</v>
       </c>
       <c r="AO115" t="n">
         <v>42.01213411573622</v>
       </c>
       <c r="AP115" t="n">
-        <v>2947700</v>
+        <v>2948300</v>
       </c>
       <c r="AQ115" t="n">
-        <v>2216288</v>
+        <v>2216300</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.330016676533014</v>
+        <v>1.33028019672427</v>
       </c>
       <c r="AS115" t="n">
         <v>-0.1374227880097527</v>
@@ -22661,16 +22661,16 @@
         <v>0.4971214579007963</v>
       </c>
       <c r="AV115" t="n">
-        <v>1.088274956182319</v>
+        <v>1.088275174854502</v>
       </c>
       <c r="AW115" t="n">
-        <v>4.175859300413301</v>
+        <v>4.175858628747855</v>
       </c>
       <c r="AX115" t="n">
         <v>0.4291469644159489</v>
       </c>
       <c r="AY115" t="n">
-        <v>6.956316985516128</v>
+        <v>6.956313811258909</v>
       </c>
       <c r="AZ115" t="inlineStr"/>
       <c r="BA115" t="n">
@@ -22839,13 +22839,13 @@
         <v>37.63000201187118</v>
       </c>
       <c r="AP116" t="n">
-        <v>16098300</v>
+        <v>16104500</v>
       </c>
       <c r="AQ116" t="n">
-        <v>13843036</v>
+        <v>13843160</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.162916863034958</v>
+        <v>1.16335432083426</v>
       </c>
       <c r="AS116" t="n">
         <v>-0.3188978853935339</v>
@@ -23035,13 +23035,13 @@
         <v>45.22904060383183</v>
       </c>
       <c r="AP117" t="n">
-        <v>1342200</v>
+        <v>1343300</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1321634</v>
+        <v>1321656</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.015561040348538</v>
+        <v>1.016376424727766</v>
       </c>
       <c r="AS117" t="n">
         <v>-0.1411930850879041</v>
@@ -23056,13 +23056,13 @@
         <v>0.2556006581605916</v>
       </c>
       <c r="AW117" t="n">
-        <v>-0.04107725120863348</v>
+        <v>-0.04107715509300514</v>
       </c>
       <c r="AX117" t="n">
         <v>0.9704226876518129</v>
       </c>
       <c r="AY117" t="n">
-        <v>40.83596701167809</v>
+        <v>40.8359698702321</v>
       </c>
       <c r="AZ117" t="inlineStr"/>
       <c r="BA117" t="n">
@@ -23204,16 +23204,16 @@
         <v>295.5794573974609</v>
       </c>
       <c r="AG118" t="n">
-        <v>213.9372723388672</v>
+        <v>213.9372719573975</v>
       </c>
       <c r="AH118" t="n">
         <v>-0.008456172317260591</v>
       </c>
       <c r="AI118" t="n">
-        <v>0.3699342025266166</v>
+        <v>0.3699342049693346</v>
       </c>
       <c r="AJ118" t="n">
-        <v>0.381617397314836</v>
+        <v>0.3816173997783863</v>
       </c>
       <c r="AK118" t="n">
         <v>332.2799987792969</v>
@@ -23231,13 +23231,13 @@
         <v>48.57101572785252</v>
       </c>
       <c r="AP118" t="n">
-        <v>9766000</v>
+        <v>9767600</v>
       </c>
       <c r="AQ118" t="n">
-        <v>9599424</v>
+        <v>9599456</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.017352707829136</v>
+        <v>1.017515992572912</v>
       </c>
       <c r="AS118" t="n">
         <v>-0.05026089617189766</v>
@@ -23249,16 +23249,16 @@
         <v>0.7089853707651266</v>
       </c>
       <c r="AV118" t="n">
-        <v>0.3975622086606656</v>
+        <v>0.3975623103501944</v>
       </c>
       <c r="AW118" t="n">
-        <v>0.7953501814718584</v>
+        <v>0.7953506849187024</v>
       </c>
       <c r="AX118" t="n">
         <v>0.6701885283684721</v>
       </c>
       <c r="AY118" t="n">
-        <v>425.2507490928749</v>
+        <v>425.2506751912186</v>
       </c>
       <c r="AZ118" t="inlineStr"/>
       <c r="BA118" t="n">
@@ -23387,7 +23387,7 @@
         <v>32966</v>
       </c>
       <c r="AD119" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="AE119" t="n">
         <v>282.9500122070312</v>
@@ -23423,13 +23423,13 @@
         <v>47.2850137831924</v>
       </c>
       <c r="AP119" t="n">
-        <v>1152900</v>
+        <v>1156100</v>
       </c>
       <c r="AQ119" t="n">
-        <v>925184</v>
+        <v>925248</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.246130499446596</v>
+        <v>1.249502835996403</v>
       </c>
       <c r="AS119" t="n">
         <v>-0.1438211002155383</v>
@@ -23450,7 +23450,7 @@
         <v>1.421273410313223</v>
       </c>
       <c r="AY119" t="n">
-        <v>133.1547618913046</v>
+        <v>133.1547770563116</v>
       </c>
       <c r="AZ119" t="inlineStr"/>
       <c r="BA119" t="n">
@@ -23565,10 +23565,10 @@
         </is>
       </c>
       <c r="Z120" t="n">
-        <v>0.03134599700570107</v>
+        <v>0.03132537752389908</v>
       </c>
       <c r="AA120" t="n">
-        <v>15581470518.7207</v>
+        <v>15571220985.17578</v>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
@@ -23615,13 +23615,13 @@
         <v>51.0989010989011</v>
       </c>
       <c r="AP120" t="n">
-        <v>16944709</v>
+        <v>16656824</v>
       </c>
       <c r="AQ120" t="n">
-        <v>37824367.3</v>
+        <v>37818609.6</v>
       </c>
       <c r="AR120" t="n">
-        <v>0.4479839375925265</v>
+        <v>0.4404398833319351</v>
       </c>
       <c r="AS120" t="n">
         <v>-0.1187122736418511</v>
@@ -23636,13 +23636,13 @@
         <v>1.115064724598368</v>
       </c>
       <c r="AW120" t="n">
-        <v>3.574250704429147</v>
+        <v>3.574250339964125</v>
       </c>
       <c r="AX120" t="n">
         <v>0.3349349892334681</v>
       </c>
       <c r="AY120" t="n">
-        <v>56.38528354454199</v>
+        <v>56.38529071467305</v>
       </c>
       <c r="AZ120" t="inlineStr"/>
       <c r="BA120" t="n">
@@ -23832,7 +23832,7 @@
         <v>-0.05525478052623667</v>
       </c>
       <c r="AW121" t="n">
-        <v>0.5925125571721426</v>
+        <v>0.5925124191039448</v>
       </c>
       <c r="AX121" t="n">
         <v>0.3195294114266503</v>
@@ -23945,7 +23945,7 @@
         </is>
       </c>
       <c r="X122" t="n">
-        <v>100503298048</v>
+        <v>100555276288</v>
       </c>
       <c r="Y122" t="inlineStr">
         <is>
@@ -23953,10 +23953,10 @@
         </is>
       </c>
       <c r="Z122" t="n">
-        <v>1.145869135856628</v>
+        <v>1.144033789634705</v>
       </c>
       <c r="AA122" t="n">
-        <v>115163627285.0029</v>
+        <v>115038633799.5254</v>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
@@ -23970,22 +23970,22 @@
         <v>26.3</v>
       </c>
       <c r="AE122" t="n">
-        <v>77.33999633789062</v>
+        <v>77.37999725341797</v>
       </c>
       <c r="AF122" t="n">
-        <v>71.46880020141602</v>
+        <v>71.46960021972656</v>
       </c>
       <c r="AG122" t="n">
-        <v>46.40517364501953</v>
+        <v>46.40537364959717</v>
       </c>
       <c r="AH122" t="n">
-        <v>0.08215047852948687</v>
+        <v>0.08269805645365924</v>
       </c>
       <c r="AI122" t="n">
-        <v>0.666624435661199</v>
+        <v>0.6674792414712016</v>
       </c>
       <c r="AJ122" t="n">
-        <v>0.5401041433035658</v>
+        <v>0.5401147453177972</v>
       </c>
       <c r="AK122" t="n">
         <v>88</v>
@@ -23994,43 +23994,43 @@
         <v>31.03618240356445</v>
       </c>
       <c r="AM122" t="n">
-        <v>-0.1211364052512429</v>
+        <v>-0.1206818493929777</v>
       </c>
       <c r="AN122" t="n">
-        <v>1.491930074782917</v>
+        <v>1.493218922586658</v>
       </c>
       <c r="AO122" t="n">
-        <v>50.38146944107555</v>
+        <v>50.43644225732518</v>
       </c>
       <c r="AP122" t="n">
-        <v>459205</v>
+        <v>2824473</v>
       </c>
       <c r="AQ122" t="n">
-        <v>6083234.72</v>
+        <v>6130540.08</v>
       </c>
       <c r="AR122" t="n">
-        <v>0.07548697709957837</v>
+        <v>0.4607217248631054</v>
       </c>
       <c r="AS122" t="n">
-        <v>-0.1211364052512429</v>
+        <v>-0.1206818493929777</v>
       </c>
       <c r="AT122" t="n">
-        <v>0.9262762988449875</v>
+        <v>0.9272725856197606</v>
       </c>
       <c r="AU122" t="n">
-        <v>1.036720655496802</v>
+        <v>1.037774065048793</v>
       </c>
       <c r="AV122" t="n">
-        <v>1.111204541092814</v>
+        <v>1.112296474355136</v>
       </c>
       <c r="AW122" t="n">
-        <v>1.558498787742077</v>
+        <v>1.559822065460351</v>
       </c>
       <c r="AX122" t="n">
-        <v>1.036720655496802</v>
+        <v>1.037774065048793</v>
       </c>
       <c r="AY122" t="n">
-        <v>0.5308006355390074</v>
+        <v>0.5315922632350845</v>
       </c>
       <c r="AZ122" t="inlineStr"/>
       <c r="BA122" t="n">
@@ -24137,7 +24137,7 @@
         </is>
       </c>
       <c r="X123" t="n">
-        <v>31670939648</v>
+        <v>32081657856</v>
       </c>
       <c r="Y123" t="inlineStr">
         <is>
@@ -24145,10 +24145,10 @@
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>0.1037822365760803</v>
+        <v>0.1036892607808113</v>
       </c>
       <c r="AA123" t="n">
-        <v>3286880951.135498</v>
+        <v>3326523387.711548</v>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
@@ -24162,22 +24162,22 @@
         <v>9.1</v>
       </c>
       <c r="AE123" t="n">
-        <v>173.5</v>
+        <v>175.75</v>
       </c>
       <c r="AF123" t="n">
-        <v>193.9346072387695</v>
+        <v>193.9796072387695</v>
       </c>
       <c r="AG123" t="n">
-        <v>169.6803088378906</v>
+        <v>169.6915588378906</v>
       </c>
       <c r="AH123" t="n">
-        <v>-0.1053685442207369</v>
+        <v>-0.0939769262257073</v>
       </c>
       <c r="AI123" t="n">
-        <v>0.02251110448978855</v>
+        <v>0.03570266667122257</v>
       </c>
       <c r="AJ123" t="n">
-        <v>0.1429411495475943</v>
+        <v>0.1431305632832431</v>
       </c>
       <c r="AK123" t="n">
         <v>210.6000061035156</v>
@@ -24186,43 +24186,43 @@
         <v>110.4240570068359</v>
       </c>
       <c r="AM123" t="n">
-        <v>-0.1761633667060768</v>
+        <v>-0.165479606331948</v>
       </c>
       <c r="AN123" t="n">
-        <v>0.571215591085005</v>
+        <v>0.5915915857820726</v>
       </c>
       <c r="AO123" t="n">
-        <v>30.63750029036679</v>
+        <v>33.48541060585136</v>
       </c>
       <c r="AP123" t="n">
-        <v>48791</v>
+        <v>202797</v>
       </c>
       <c r="AQ123" t="n">
-        <v>430870.88</v>
+        <v>433951</v>
       </c>
       <c r="AR123" t="n">
-        <v>0.1132381004722343</v>
+        <v>0.4673269562692562</v>
       </c>
       <c r="AS123" t="n">
-        <v>-0.1585838866741116</v>
+        <v>-0.1476721503341505</v>
       </c>
       <c r="AT123" t="n">
-        <v>0.07928405108919878</v>
+        <v>0.09328053013790605</v>
       </c>
       <c r="AU123" t="n">
-        <v>0.01335918103473621</v>
+        <v>0.02650072661011471</v>
       </c>
       <c r="AV123" t="n">
-        <v>0.286064621645435</v>
+        <v>0.3027426931076955</v>
       </c>
       <c r="AW123" t="n">
-        <v>1.366933405163957</v>
+        <v>1.39762900606123</v>
       </c>
       <c r="AX123" t="n">
-        <v>-0.09882859167715341</v>
+        <v>-0.08714193076230381</v>
       </c>
       <c r="AY123" t="n">
-        <v>1.78100611654023</v>
+        <v>1.817071037359915</v>
       </c>
       <c r="AZ123" t="inlineStr"/>
       <c r="BA123" t="n">
@@ -24556,16 +24556,16 @@
         <v>711.5302380371094</v>
       </c>
       <c r="AG125" t="n">
-        <v>537.9320043945313</v>
+        <v>537.9320042419433</v>
       </c>
       <c r="AH125" t="n">
         <v>-0.06074266161582509</v>
       </c>
       <c r="AI125" t="n">
-        <v>0.2423689092654178</v>
+        <v>0.2423689096178239</v>
       </c>
       <c r="AJ125" t="n">
-        <v>0.3227140832380317</v>
+        <v>0.3227140836132285</v>
       </c>
       <c r="AK125" t="n">
         <v>785.1200561523438</v>
@@ -24604,7 +24604,7 @@
         <v>0.7912726264996539</v>
       </c>
       <c r="AW125" t="n">
-        <v>6.302163821995272</v>
+        <v>6.302162604561954</v>
       </c>
       <c r="AX125" t="n">
         <v>0.5205226849628715</v>
@@ -24750,40 +24750,40 @@
         <v>324.550894165039</v>
       </c>
       <c r="AG126" t="n">
-        <v>232.3926040649414</v>
+        <v>232.3926043701172</v>
       </c>
       <c r="AH126" t="n">
         <v>-0.07401272286597727</v>
       </c>
       <c r="AI126" t="n">
-        <v>0.2931994974130705</v>
+        <v>0.2931994957148529</v>
       </c>
       <c r="AJ126" t="n">
-        <v>0.3965629219178779</v>
+        <v>0.3965629200839245</v>
       </c>
       <c r="AK126" t="n">
         <v>376.1517333984375</v>
       </c>
       <c r="AL126" t="n">
-        <v>120.5871658325195</v>
+        <v>120.5871734619141</v>
       </c>
       <c r="AM126" t="n">
         <v>-0.2010405054787786</v>
       </c>
       <c r="AN126" t="n">
-        <v>1.492222092661962</v>
+        <v>1.492221934982293</v>
       </c>
       <c r="AO126" t="n">
         <v>50.61010598879461</v>
       </c>
       <c r="AP126" t="n">
-        <v>5898700</v>
+        <v>5906900</v>
       </c>
       <c r="AQ126" t="n">
-        <v>6492416</v>
+        <v>6492580</v>
       </c>
       <c r="AR126" t="n">
-        <v>0.9085523786522613</v>
+        <v>0.909792409180942</v>
       </c>
       <c r="AS126" t="n">
         <v>-0.09307108518251406</v>
@@ -24795,10 +24795,10 @@
         <v>0.8558366387907679</v>
       </c>
       <c r="AV126" t="n">
-        <v>1.419858742809654</v>
+        <v>1.419858891465606</v>
       </c>
       <c r="AW126" t="n">
-        <v>10.12216794230013</v>
+        <v>10.12216872739327</v>
       </c>
       <c r="AX126" t="n">
         <v>0.7121124652229793</v>
@@ -24911,7 +24911,7 @@
         </is>
       </c>
       <c r="X127" t="n">
-        <v>215360585728</v>
+        <v>216695390208</v>
       </c>
       <c r="Y127" t="inlineStr">
         <is>
@@ -24919,10 +24919,10 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>1.145869135856628</v>
+        <v>1.144033789634705</v>
       </c>
       <c r="AA127" t="n">
-        <v>246775048265.7207</v>
+        <v>247906848456.0293</v>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
@@ -24933,28 +24933,28 @@
         <v>35377</v>
       </c>
       <c r="AD127" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="AE127" t="n">
-        <v>282.3500061035156</v>
+        <v>284.1000061035156</v>
       </c>
       <c r="AF127" t="n">
-        <v>265.9219982910156</v>
+        <v>265.9569982910156</v>
       </c>
       <c r="AG127" t="n">
-        <v>241.4672766113281</v>
+        <v>241.4760266113281</v>
       </c>
       <c r="AH127" t="n">
-        <v>0.0617775434829646</v>
+        <v>0.06821782441929791</v>
       </c>
       <c r="AI127" t="n">
-        <v>0.169309606112771</v>
+        <v>0.1765143318379743</v>
       </c>
       <c r="AJ127" t="n">
-        <v>0.1012755103833403</v>
+        <v>0.1013805470598175</v>
       </c>
       <c r="AK127" t="n">
-        <v>282.3500061035156</v>
+        <v>284.1000061035156</v>
       </c>
       <c r="AL127" t="n">
         <v>203.75</v>
@@ -24963,40 +24963,40 @@
         <v>0</v>
       </c>
       <c r="AN127" t="n">
-        <v>0.385766901121549</v>
+        <v>0.3943558581767639</v>
       </c>
       <c r="AO127" t="n">
-        <v>72.31058397932226</v>
+        <v>73.18841901754374</v>
       </c>
       <c r="AP127" t="n">
-        <v>123470</v>
+        <v>707250</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1094291.26</v>
+        <v>1105966.86</v>
       </c>
       <c r="AR127" t="n">
-        <v>0.1128310208746436</v>
+        <v>0.6394857075554686</v>
       </c>
       <c r="AS127" t="n">
-        <v>0.02672729492187509</v>
+        <v>0.03309093128551144</v>
       </c>
       <c r="AT127" t="n">
-        <v>0.3111214214119598</v>
+        <v>0.319247727195108</v>
       </c>
       <c r="AU127" t="n">
-        <v>0.1959877984501486</v>
+        <v>0.2034005082147816</v>
       </c>
       <c r="AV127" t="n">
-        <v>0.3029944503297044</v>
+        <v>0.3110703852997252</v>
       </c>
       <c r="AW127" t="n">
-        <v>1.397526765708848</v>
+        <v>1.41238643499413</v>
       </c>
       <c r="AX127" t="n">
-        <v>0.1959877984501486</v>
+        <v>0.2034005082147816</v>
       </c>
       <c r="AY127" t="n">
-        <v>28.70152949131322</v>
+        <v>28.88561900959268</v>
       </c>
       <c r="AZ127" t="inlineStr"/>
       <c r="BA127" t="n">
@@ -25103,7 +25103,7 @@
         </is>
       </c>
       <c r="X128" t="n">
-        <v>21390092288</v>
+        <v>21626284032</v>
       </c>
       <c r="Y128" t="inlineStr">
         <is>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>1.145869135856628</v>
+        <v>1.144033789634705</v>
       </c>
       <c r="AA128" t="n">
-        <v>24510246565.94409</v>
+        <v>24741199676.84546</v>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
@@ -25128,22 +25128,22 @@
         <v>28</v>
       </c>
       <c r="AE128" t="n">
-        <v>270.1000061035156</v>
+        <v>273.1000061035156</v>
       </c>
       <c r="AF128" t="n">
-        <v>276.4623986816407</v>
+        <v>276.5223986816407</v>
       </c>
       <c r="AG128" t="n">
-        <v>188.1223388290405</v>
+        <v>188.1373388290405</v>
       </c>
       <c r="AH128" t="n">
-        <v>-0.02301359102888934</v>
+        <v>-0.01237654741330818</v>
       </c>
       <c r="AI128" t="n">
-        <v>0.435767850775945</v>
+        <v>0.4515991764488616</v>
       </c>
       <c r="AJ128" t="n">
-        <v>0.4695883561860279</v>
+        <v>0.4697901033505911</v>
       </c>
       <c r="AK128" t="n">
         <v>320.2999877929688</v>
@@ -25152,43 +25152,43 @@
         <v>105.1371765136719</v>
       </c>
       <c r="AM128" t="n">
-        <v>-0.1567280162430126</v>
+        <v>-0.1473617967165257</v>
       </c>
       <c r="AN128" t="n">
-        <v>1.569024726171834</v>
+        <v>1.597558876502662</v>
       </c>
       <c r="AO128" t="n">
-        <v>33.70207238202065</v>
+        <v>35.13709239713805</v>
       </c>
       <c r="AP128" t="n">
-        <v>51496</v>
+        <v>225799</v>
       </c>
       <c r="AQ128" t="n">
-        <v>424023.84</v>
+        <v>427509.9</v>
       </c>
       <c r="AR128" t="n">
-        <v>0.1214460017153752</v>
+        <v>0.5281725639569984</v>
       </c>
       <c r="AS128" t="n">
-        <v>-0.00478993302212305</v>
+        <v>0.006263862362795969</v>
       </c>
       <c r="AT128" t="n">
-        <v>0.4204483784020401</v>
+        <v>0.4362252945031562</v>
       </c>
       <c r="AU128" t="n">
-        <v>0.689265471484436</v>
+        <v>0.7080281382742732</v>
       </c>
       <c r="AV128" t="n">
-        <v>1.228805412912832</v>
+        <v>1.253560748298407</v>
       </c>
       <c r="AW128" t="n">
-        <v>3.154038496717079</v>
+        <v>3.200177390491762</v>
       </c>
       <c r="AX128" t="n">
-        <v>0.8229564969870347</v>
+        <v>0.8432040696170966</v>
       </c>
       <c r="AY128" t="n">
-        <v>127.2606329333478</v>
+        <v>128.6852234187422</v>
       </c>
       <c r="AZ128" t="inlineStr"/>
       <c r="BA128" t="n">
@@ -25517,7 +25517,7 @@
         <v>33660</v>
       </c>
       <c r="AD130" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="AE130" t="n">
         <v>437.1600036621094</v>
@@ -25699,10 +25699,10 @@
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>0.006215117871761322</v>
+        <v>0.00619820598512888</v>
       </c>
       <c r="AA131" t="n">
-        <v>206934758461.9062</v>
+        <v>206371670641.5898</v>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
@@ -25722,16 +25722,16 @@
         <v>58845.8</v>
       </c>
       <c r="AG131" t="n">
-        <v>41055.65071289062</v>
+        <v>41055.65072265625</v>
       </c>
       <c r="AH131" t="n">
         <v>0.2439290484622521</v>
       </c>
       <c r="AI131" t="n">
-        <v>0.7829457998827118</v>
+        <v>0.7829457994586146</v>
       </c>
       <c r="AJ131" t="n">
-        <v>0.4333179228242909</v>
+        <v>0.4333179224833572</v>
       </c>
       <c r="AK131" t="n">
         <v>78800</v>
@@ -25770,13 +25770,13 @@
         <v>2.148141412687131</v>
       </c>
       <c r="AW131" t="n">
-        <v>4.342258764376019</v>
+        <v>4.342259145125073</v>
       </c>
       <c r="AX131" t="n">
         <v>1.000663428670688</v>
       </c>
       <c r="AY131" t="n">
-        <v>26.01421198862695</v>
+        <v>26.01420712070624</v>
       </c>
       <c r="AZ131" t="inlineStr"/>
       <c r="BA131" t="n">
@@ -25918,40 +25918,40 @@
         <v>418.8306805419922</v>
       </c>
       <c r="AG132" t="n">
-        <v>342.5128793334961</v>
+        <v>342.5128746032715</v>
       </c>
       <c r="AH132" t="n">
         <v>0.03660028701880225</v>
       </c>
       <c r="AI132" t="n">
-        <v>0.2675727829766623</v>
+        <v>0.2675728004822933</v>
       </c>
       <c r="AJ132" t="n">
-        <v>0.2228173181604287</v>
+        <v>0.2228173350479707</v>
       </c>
       <c r="AK132" t="n">
         <v>477.5700073242188</v>
       </c>
       <c r="AL132" t="n">
-        <v>224.8433532714844</v>
+        <v>224.8433685302734</v>
       </c>
       <c r="AM132" t="n">
         <v>-0.09089767572576779</v>
       </c>
       <c r="AN132" t="n">
-        <v>0.9309443545697709</v>
+        <v>0.9309442235280025</v>
       </c>
       <c r="AO132" t="n">
         <v>53.1082295150535</v>
       </c>
       <c r="AP132" t="n">
-        <v>18375000</v>
+        <v>18424800</v>
       </c>
       <c r="AQ132" t="n">
-        <v>14077596</v>
+        <v>14078592</v>
       </c>
       <c r="AR132" t="n">
-        <v>1.305265472883296</v>
+        <v>1.308710416496195</v>
       </c>
       <c r="AS132" t="n">
         <v>-0.003465320110792702</v>
@@ -25966,13 +25966,13 @@
         <v>0.8791163504878894</v>
       </c>
       <c r="AW132" t="n">
-        <v>3.041808614645729</v>
+        <v>3.041808040500598</v>
       </c>
       <c r="AX132" t="n">
         <v>0.3654235008760789</v>
       </c>
       <c r="AY132" t="n">
-        <v>138.0244236495557</v>
+        <v>138.024466104924</v>
       </c>
       <c r="AZ132" t="inlineStr"/>
       <c r="BA132" t="n">
@@ -25987,12 +25987,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AMAT</t>
+          <t>ASM.AS</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Applied Materials</t>
+          <t>ASM International</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -26007,26 +26007,22 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Semiconductor equipment, deposition/process tools</t>
+          <t>Atomic layer deposition equipment</t>
         </is>
       </c>
       <c r="F133" t="n">
         <v>8</v>
       </c>
       <c r="G133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>S&amp;P 500, Nasdaq-100, SOXX, STOXX Global AI Infrastructure</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" s="1" t="n">
         <v>46195</v>
       </c>
@@ -26046,10 +26042,10 @@
         </is>
       </c>
       <c r="O133" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P133" t="n">
-        <v>4.07</v>
+        <v>0</v>
       </c>
       <c r="Q133" s="1" t="n">
         <v>46192</v>
@@ -26064,7 +26060,7 @@
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>Applied Materials, Inc.</t>
+          <t>ASM International NV</t>
         </is>
       </c>
       <c r="U133" t="inlineStr">
@@ -26079,100 +26075,100 @@
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="X133" t="n">
-        <v>478789271552</v>
+        <v>47693250560</v>
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>1</v>
+        <v>1.144033789634705</v>
       </c>
       <c r="AA133" t="n">
-        <v>478789271552</v>
+        <v>54562690178.1543</v>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>Mega cap</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC133" s="2" t="n">
-        <v>29297</v>
+        <v>36166</v>
       </c>
       <c r="AD133" t="n">
-        <v>46.3</v>
+        <v>27.5</v>
       </c>
       <c r="AE133" t="n">
-        <v>603.0399780273438</v>
+        <v>975.5999755859375</v>
       </c>
       <c r="AF133" t="n">
-        <v>489.9698193359375</v>
+        <v>914.1653564453125</v>
       </c>
       <c r="AG133" t="n">
-        <v>338.7531447601318</v>
+        <v>685.8842190551758</v>
       </c>
       <c r="AH133" t="n">
-        <v>0.2307696397395491</v>
+        <v>0.06720296137616777</v>
       </c>
       <c r="AI133" t="n">
-        <v>0.780175290931546</v>
+        <v>0.4223974666305241</v>
       </c>
       <c r="AJ133" t="n">
-        <v>0.44639194326264</v>
+        <v>0.3328275108947691</v>
       </c>
       <c r="AK133" t="n">
-        <v>723</v>
+        <v>1079</v>
       </c>
       <c r="AL133" t="n">
-        <v>155.5566864013672</v>
+        <v>400.14208984375</v>
       </c>
       <c r="AM133" t="n">
-        <v>-0.1659198090908108</v>
+        <v>-0.09582949435965016</v>
       </c>
       <c r="AN133" t="n">
-        <v>2.876657390807237</v>
+        <v>1.438133853819017</v>
       </c>
       <c r="AO133" t="n">
-        <v>54.8805012934833</v>
+        <v>44.6904525366329</v>
       </c>
       <c r="AP133" t="n">
-        <v>15071700</v>
+        <v>96434</v>
       </c>
       <c r="AQ133" t="n">
-        <v>9722654</v>
+        <v>162086.04</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.550163155039766</v>
+        <v>0.5949556173992528</v>
       </c>
       <c r="AS133" t="n">
-        <v>0.2042254752827843</v>
+        <v>0.1252594874116926</v>
       </c>
       <c r="AT133" t="n">
-        <v>0.7326876693357622</v>
+        <v>0.4565710419909976</v>
       </c>
       <c r="AU133" t="n">
-        <v>1.352397752602464</v>
+        <v>0.5660350461921766</v>
       </c>
       <c r="AV133" t="n">
-        <v>2.197009564375317</v>
+        <v>0.9010061486864169</v>
       </c>
       <c r="AW133" t="n">
-        <v>3.618435257368365</v>
+        <v>2.292347112698032</v>
       </c>
       <c r="AX133" t="n">
-        <v>1.248457034376891</v>
+        <v>0.7685056729336115</v>
       </c>
       <c r="AY133" t="n">
-        <v>8739.120578088561</v>
+        <v>330.9221549503248</v>
       </c>
       <c r="AZ133" t="inlineStr"/>
       <c r="BA133" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
@@ -26183,12 +26179,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>AMAT</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>Applied Materials</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -26198,19 +26194,19 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>EUV/DUV lithography equipment</t>
+          <t>Semiconductor process equipment</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Litografía EUV/DUV, cuello de botella semis</t>
+          <t>Semiconductor equipment, deposition/process tools</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H134" t="n">
         <v>1</v>
@@ -26220,7 +26216,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Nasdaq-100, SOXX, STOXX Global AI Infrastructure</t>
+          <t>S&amp;P 500, Nasdaq-100, SOXX, STOXX Global AI Infrastructure</t>
         </is>
       </c>
       <c r="K134" s="1" t="n">
@@ -26245,7 +26241,7 @@
         <v>1</v>
       </c>
       <c r="P134" t="n">
-        <v>3.82</v>
+        <v>4.07</v>
       </c>
       <c r="Q134" s="1" t="n">
         <v>46192</v>
@@ -26260,7 +26256,7 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>ASML Holding N.V.</t>
+          <t>Applied Materials, Inc.</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
@@ -26279,7 +26275,7 @@
         </is>
       </c>
       <c r="X134" t="n">
-        <v>681927180288</v>
+        <v>478789271552</v>
       </c>
       <c r="Y134" t="inlineStr">
         <is>
@@ -26290,7 +26286,7 @@
         <v>1</v>
       </c>
       <c r="AA134" t="n">
-        <v>681927180288</v>
+        <v>478789271552</v>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
@@ -26298,73 +26294,73 @@
         </is>
       </c>
       <c r="AC134" s="2" t="n">
-        <v>34773</v>
+        <v>29297</v>
       </c>
       <c r="AD134" t="n">
-        <v>31.3</v>
+        <v>46.3</v>
       </c>
       <c r="AE134" t="n">
-        <v>1769.319946289062</v>
+        <v>603.0399780273438</v>
       </c>
       <c r="AF134" t="n">
-        <v>1646.9611328125</v>
+        <v>489.9698193359375</v>
       </c>
       <c r="AG134" t="n">
-        <v>1311.797275085449</v>
+        <v>338.7531456756592</v>
       </c>
       <c r="AH134" t="n">
-        <v>0.07429368613429976</v>
+        <v>0.2307696397395491</v>
       </c>
       <c r="AI134" t="n">
-        <v>0.3487754395387128</v>
+        <v>0.7801752861203752</v>
       </c>
       <c r="AJ134" t="n">
-        <v>0.2554997361960663</v>
+        <v>0.4463919393535651</v>
       </c>
       <c r="AK134" t="n">
-        <v>1989.43994140625</v>
+        <v>723</v>
       </c>
       <c r="AL134" t="n">
-        <v>686.00341796875</v>
+        <v>155.5567016601562</v>
       </c>
       <c r="AM134" t="n">
-        <v>-0.110644202187674</v>
+        <v>-0.1659198090908108</v>
       </c>
       <c r="AN134" t="n">
-        <v>1.579170744554018</v>
+        <v>2.876657010540127</v>
       </c>
       <c r="AO134" t="n">
-        <v>43.40240321663092</v>
+        <v>54.8805012934833</v>
       </c>
       <c r="AP134" t="n">
-        <v>2699100</v>
+        <v>15096100</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1937930</v>
+        <v>9723142</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.392774764826387</v>
+        <v>1.552594829942831</v>
       </c>
       <c r="AS134" t="n">
-        <v>0.02488470614589189</v>
+        <v>0.2042254752827843</v>
       </c>
       <c r="AT134" t="n">
-        <v>0.3461465019322518</v>
+        <v>0.7326876693357622</v>
       </c>
       <c r="AU134" t="n">
-        <v>0.6595847657205354</v>
+        <v>1.352397752602464</v>
       </c>
       <c r="AV134" t="n">
-        <v>1.230124274730702</v>
+        <v>2.197009564375317</v>
       </c>
       <c r="AW134" t="n">
-        <v>1.698999122664664</v>
+        <v>3.61843579708243</v>
       </c>
       <c r="AX134" t="n">
-        <v>0.525651982021345</v>
+        <v>1.248457290219689</v>
       </c>
       <c r="AY134" t="n">
-        <v>1003.134998063732</v>
+        <v>8739.124353280527</v>
       </c>
       <c r="AZ134" t="inlineStr"/>
       <c r="BA134" t="n">
@@ -26379,12 +26375,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>KLAC</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -26394,19 +26390,19 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Inspection / metrology</t>
+          <t>EUV/DUV lithography equipment</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Inspection/metrology semis</t>
+          <t>Litografía EUV/DUV, cuello de botella semis</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G135" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H135" t="n">
         <v>1</v>
@@ -26416,7 +26412,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>S&amp;P 500, Nasdaq-100, SOXX, STOXX Global AI Infrastructure</t>
+          <t>Nasdaq-100, SOXX, STOXX Global AI Infrastructure</t>
         </is>
       </c>
       <c r="K135" s="1" t="n">
@@ -26441,7 +26437,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="n">
-        <v>3.92</v>
+        <v>3.82</v>
       </c>
       <c r="Q135" s="1" t="n">
         <v>46192</v>
@@ -26456,7 +26452,7 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>KLA Corporation</t>
+          <t>ASML Holding N.V.</t>
         </is>
       </c>
       <c r="U135" t="inlineStr">
@@ -26475,7 +26471,7 @@
         </is>
       </c>
       <c r="X135" t="n">
-        <v>307693125632</v>
+        <v>681927180288</v>
       </c>
       <c r="Y135" t="inlineStr">
         <is>
@@ -26486,7 +26482,7 @@
         <v>1</v>
       </c>
       <c r="AA135" t="n">
-        <v>307693125632</v>
+        <v>681927180288</v>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
@@ -26494,73 +26490,73 @@
         </is>
       </c>
       <c r="AC135" s="2" t="n">
-        <v>29502</v>
+        <v>34773</v>
       </c>
       <c r="AD135" t="n">
-        <v>45.7</v>
+        <v>31.3</v>
       </c>
       <c r="AE135" t="n">
-        <v>235.5500030517578</v>
+        <v>1769.319946289062</v>
       </c>
       <c r="AF135" t="n">
-        <v>208.7226901245117</v>
+        <v>1646.9611328125</v>
       </c>
       <c r="AG135" t="n">
-        <v>151.703902015686</v>
+        <v>1311.797275085449</v>
       </c>
       <c r="AH135" t="n">
-        <v>0.1285308890530421</v>
+        <v>0.07429368613429976</v>
       </c>
       <c r="AI135" t="n">
-        <v>0.5526957442887803</v>
+        <v>0.3487754395387128</v>
       </c>
       <c r="AJ135" t="n">
-        <v>0.3758557779412293</v>
+        <v>0.2554997361960663</v>
       </c>
       <c r="AK135" t="n">
-        <v>301.7099914550781</v>
+        <v>1989.43994140625</v>
       </c>
       <c r="AL135" t="n">
-        <v>84.03205871582031</v>
+        <v>686.0034790039062</v>
       </c>
       <c r="AM135" t="n">
-        <v>-0.2192833856255335</v>
+        <v>-0.110644202187674</v>
       </c>
       <c r="AN135" t="n">
-        <v>1.803096897201353</v>
+        <v>1.579170515079833</v>
       </c>
       <c r="AO135" t="n">
-        <v>48.84278947876633</v>
+        <v>43.40240321663092</v>
       </c>
       <c r="AP135" t="n">
-        <v>23622500</v>
+        <v>2701000</v>
       </c>
       <c r="AQ135" t="n">
-        <v>12816126</v>
+        <v>1937968</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.843185686532732</v>
+        <v>1.393727863411573</v>
       </c>
       <c r="AS135" t="n">
-        <v>0.108413217634858</v>
+        <v>0.02488470614589189</v>
       </c>
       <c r="AT135" t="n">
-        <v>0.5548814973593614</v>
+        <v>0.3461465019322518</v>
       </c>
       <c r="AU135" t="n">
-        <v>0.9435519032185244</v>
+        <v>0.6595847657205354</v>
       </c>
       <c r="AV135" t="n">
-        <v>1.573750421816833</v>
+        <v>1.230124274730702</v>
       </c>
       <c r="AW135" t="n">
-        <v>6.835291436506853</v>
+        <v>1.698998871372392</v>
       </c>
       <c r="AX135" t="n">
-        <v>0.8529828939737503</v>
+        <v>0.525651982021345</v>
       </c>
       <c r="AY135" t="n">
-        <v>3881.275961480781</v>
+        <v>1003.135133931984</v>
       </c>
       <c r="AZ135" t="inlineStr"/>
       <c r="BA135" t="n">
@@ -26575,12 +26571,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ONTO</t>
+          <t>KLAC</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Onto Innovation</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -26595,24 +26591,24 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Metrology/inspection, packaging</t>
+          <t>Inspection/metrology semis</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I136" t="n">
         <v>1</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>S&amp;P 500, Nasdaq-100, SOXX, STOXX Global AI Infrastructure</t>
         </is>
       </c>
       <c r="K136" s="1" t="n">
@@ -26634,10 +26630,10 @@
         </is>
       </c>
       <c r="O136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Q136" s="1" t="n">
         <v>46192</v>
@@ -26652,7 +26648,7 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>Onto Innovation Inc.</t>
+          <t>KLA Corporation</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
@@ -26671,7 +26667,7 @@
         </is>
       </c>
       <c r="X136" t="n">
-        <v>15300125696</v>
+        <v>307693125632</v>
       </c>
       <c r="Y136" t="inlineStr">
         <is>
@@ -26682,81 +26678,81 @@
         <v>1</v>
       </c>
       <c r="AA136" t="n">
-        <v>15300125696</v>
+        <v>307693125632</v>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Mega cap</t>
         </is>
       </c>
       <c r="AC136" s="2" t="n">
-        <v>43766</v>
+        <v>29502</v>
       </c>
       <c r="AD136" t="n">
-        <v>6.7</v>
+        <v>45.7</v>
       </c>
       <c r="AE136" t="n">
-        <v>307.5799865722656</v>
+        <v>235.5500030517578</v>
       </c>
       <c r="AF136" t="n">
-        <v>293.5242001342774</v>
+        <v>208.7226901245117</v>
       </c>
       <c r="AG136" t="n">
-        <v>205.8853503036499</v>
+        <v>151.70390209198</v>
       </c>
       <c r="AH136" t="n">
-        <v>0.04788629500245034</v>
+        <v>0.1285308890530421</v>
       </c>
       <c r="AI136" t="n">
-        <v>0.4939381851046294</v>
+        <v>0.5526957435079085</v>
       </c>
       <c r="AJ136" t="n">
-        <v>0.4256682163222072</v>
+        <v>0.3758557772492928</v>
       </c>
       <c r="AK136" t="n">
-        <v>378.4500122070312</v>
+        <v>301.7099914550781</v>
       </c>
       <c r="AL136" t="n">
-        <v>90</v>
+        <v>84.03205871582031</v>
       </c>
       <c r="AM136" t="n">
-        <v>-0.1872639010406377</v>
+        <v>-0.2192833856255335</v>
       </c>
       <c r="AN136" t="n">
-        <v>2.417555406358507</v>
+        <v>1.803096897201353</v>
       </c>
       <c r="AO136" t="n">
-        <v>50.69820160606887</v>
+        <v>48.84278947876633</v>
       </c>
       <c r="AP136" t="n">
-        <v>1966900</v>
+        <v>23648900</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1310678</v>
+        <v>12816654</v>
       </c>
       <c r="AR136" t="n">
-        <v>1.500673697124694</v>
+        <v>1.845169573899709</v>
       </c>
       <c r="AS136" t="n">
-        <v>0.09857837882321263</v>
+        <v>0.108413217634858</v>
       </c>
       <c r="AT136" t="n">
-        <v>0.4270866622480154</v>
+        <v>0.5548814973593614</v>
       </c>
       <c r="AU136" t="n">
-        <v>0.9484352298431213</v>
+        <v>0.9435517808698641</v>
       </c>
       <c r="AV136" t="n">
-        <v>1.974949109082411</v>
+        <v>1.573750421816833</v>
       </c>
       <c r="AW136" t="n">
-        <v>3.264836035198885</v>
+        <v>6.83529044227604</v>
       </c>
       <c r="AX136" t="n">
-        <v>0.8543437368220799</v>
+        <v>0.8529828939737503</v>
       </c>
       <c r="AY136" t="n">
-        <v>7.705914821150849</v>
+        <v>3881.275961480781</v>
       </c>
       <c r="AZ136" t="inlineStr"/>
       <c r="BA136" t="n">
@@ -26771,12 +26767,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>ONTO</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Teradyne</t>
+          <t>Onto Innovation</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -26786,29 +26782,29 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Semiconductor test equipment</t>
+          <t>Inspection / metrology</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Semiconductor testing</t>
+          <t>Metrology/inspection, packaging</t>
         </is>
       </c>
       <c r="F137" t="n">
         <v>7</v>
       </c>
       <c r="G137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I137" t="n">
         <v>1</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="K137" s="1" t="n">
@@ -26848,7 +26844,7 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>Teradyne, Inc.</t>
+          <t>Onto Innovation Inc.</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
@@ -26867,7 +26863,7 @@
         </is>
       </c>
       <c r="X137" t="n">
-        <v>57778143232</v>
+        <v>15300125696</v>
       </c>
       <c r="Y137" t="inlineStr">
         <is>
@@ -26878,7 +26874,7 @@
         <v>1</v>
       </c>
       <c r="AA137" t="n">
-        <v>57778143232</v>
+        <v>15300125696</v>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
@@ -26886,73 +26882,73 @@
         </is>
       </c>
       <c r="AC137" s="2" t="n">
-        <v>26716</v>
+        <v>43766</v>
       </c>
       <c r="AD137" t="n">
-        <v>53.4</v>
+        <v>6.7</v>
       </c>
       <c r="AE137" t="n">
-        <v>369.0899963378906</v>
+        <v>307.5799865722656</v>
       </c>
       <c r="AF137" t="n">
-        <v>384.6154473876953</v>
+        <v>293.5242001342774</v>
       </c>
       <c r="AG137" t="n">
-        <v>267.7719185256958</v>
+        <v>205.8853503036499</v>
       </c>
       <c r="AH137" t="n">
-        <v>-0.04036616614141064</v>
+        <v>0.04788629500245034</v>
       </c>
       <c r="AI137" t="n">
-        <v>0.3783745449113334</v>
+        <v>0.4939381851046294</v>
       </c>
       <c r="AJ137" t="n">
-        <v>0.4363546764175983</v>
+        <v>0.4256682163222072</v>
       </c>
       <c r="AK137" t="n">
-        <v>483.8399963378906</v>
+        <v>378.4500122070312</v>
       </c>
       <c r="AL137" t="n">
-        <v>89.91980743408203</v>
+        <v>90</v>
       </c>
       <c r="AM137" t="n">
-        <v>-0.2371651803664948</v>
+        <v>-0.1872639010406377</v>
       </c>
       <c r="AN137" t="n">
-        <v>3.104657326011973</v>
+        <v>2.417555406358507</v>
       </c>
       <c r="AO137" t="n">
-        <v>48.49455833973641</v>
+        <v>50.69820160606887</v>
       </c>
       <c r="AP137" t="n">
-        <v>5932300</v>
+        <v>1968000</v>
       </c>
       <c r="AQ137" t="n">
-        <v>4702730</v>
+        <v>1310700</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.261458769693348</v>
+        <v>1.501487754634928</v>
       </c>
       <c r="AS137" t="n">
-        <v>-0.09905537569203138</v>
+        <v>0.09857837882321263</v>
       </c>
       <c r="AT137" t="n">
-        <v>0.1925629124771853</v>
+        <v>0.4270866622480154</v>
       </c>
       <c r="AU137" t="n">
-        <v>0.9083683949715737</v>
+        <v>0.9484352298431213</v>
       </c>
       <c r="AV137" t="n">
-        <v>2.929017194325826</v>
+        <v>1.974949109082411</v>
       </c>
       <c r="AW137" t="n">
-        <v>1.905111707871798</v>
+        <v>3.264836035198885</v>
       </c>
       <c r="AX137" t="n">
-        <v>0.7796481328421168</v>
+        <v>0.8543437368220799</v>
       </c>
       <c r="AY137" t="n">
-        <v>330.3905011811632</v>
+        <v>7.705914821150849</v>
       </c>
       <c r="AZ137" t="inlineStr"/>
       <c r="BA137" t="n">
@@ -26967,12 +26963,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>UMC</t>
+          <t>Teradyne</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -26982,27 +26978,31 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Foundry</t>
+          <t>Semiconductor test equipment</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Mature-node foundry</t>
+          <t>Semiconductor testing</t>
         </is>
       </c>
       <c r="F138" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I138" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
+        </is>
+      </c>
       <c r="K138" s="1" t="n">
         <v>46195</v>
       </c>
@@ -27040,7 +27040,7 @@
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>United Microelectronics Corporation</t>
+          <t>Teradyne, Inc.</t>
         </is>
       </c>
       <c r="U138" t="inlineStr">
@@ -27050,7 +27050,7 @@
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
@@ -27059,7 +27059,7 @@
         </is>
       </c>
       <c r="X138" t="n">
-        <v>61577895936</v>
+        <v>57778143232</v>
       </c>
       <c r="Y138" t="inlineStr">
         <is>
@@ -27070,7 +27070,7 @@
         <v>1</v>
       </c>
       <c r="AA138" t="n">
-        <v>61577895936</v>
+        <v>57778143232</v>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
@@ -27078,73 +27078,73 @@
         </is>
       </c>
       <c r="AC138" s="2" t="n">
-        <v>36788</v>
+        <v>26716</v>
       </c>
       <c r="AD138" t="n">
-        <v>25.8</v>
+        <v>53.4</v>
       </c>
       <c r="AE138" t="n">
-        <v>24.54000091552734</v>
+        <v>369.0899963378906</v>
       </c>
       <c r="AF138" t="n">
-        <v>19.38199995040894</v>
+        <v>384.6154473876953</v>
       </c>
       <c r="AG138" t="n">
-        <v>11.35295000076294</v>
+        <v>267.7719180297852</v>
       </c>
       <c r="AH138" t="n">
-        <v>0.26612325757485</v>
+        <v>-0.04036616614141064</v>
       </c>
       <c r="AI138" t="n">
-        <v>1.161552804678802</v>
+        <v>0.3783745474640678</v>
       </c>
       <c r="AJ138" t="n">
-        <v>0.7072214665885457</v>
+        <v>0.4363546790777113</v>
       </c>
       <c r="AK138" t="n">
-        <v>28.01000022888184</v>
+        <v>483.8399963378906</v>
       </c>
       <c r="AL138" t="n">
-        <v>6.579999923706055</v>
+        <v>89.91980743408203</v>
       </c>
       <c r="AM138" t="n">
-        <v>-0.1238843014994511</v>
+        <v>-0.2371651803664948</v>
       </c>
       <c r="AN138" t="n">
-        <v>2.729483465055373</v>
+        <v>3.104657326011973</v>
       </c>
       <c r="AO138" t="n">
-        <v>59.85700141326977</v>
+        <v>48.49455833973641</v>
       </c>
       <c r="AP138" t="n">
-        <v>21004300</v>
+        <v>5938000</v>
       </c>
       <c r="AQ138" t="n">
-        <v>17731600</v>
+        <v>4702844</v>
       </c>
       <c r="AR138" t="n">
-        <v>1.184568792438359</v>
+        <v>1.262640223660406</v>
       </c>
       <c r="AS138" t="n">
-        <v>0.1456583019664124</v>
+        <v>-0.09905537569203138</v>
       </c>
       <c r="AT138" t="n">
-        <v>1.830449907679487</v>
+        <v>0.1925629124771853</v>
       </c>
       <c r="AU138" t="n">
-        <v>2.122137468025066</v>
+        <v>0.9083683949715737</v>
       </c>
       <c r="AV138" t="n">
-        <v>2.122137468025066</v>
+        <v>2.929017194325826</v>
       </c>
       <c r="AW138" t="n">
-        <v>2.461463058190307</v>
+        <v>1.905111010051884</v>
       </c>
       <c r="AX138" t="n">
-        <v>2.130102096672406</v>
+        <v>0.7796481328421168</v>
       </c>
       <c r="AY138" t="n">
-        <v>2.989008392835551</v>
+        <v>330.3906075904007</v>
       </c>
       <c r="AZ138" t="inlineStr"/>
       <c r="BA138" t="n">
@@ -27159,12 +27159,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>0981.HK</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SMIC</t>
+          <t>UMC</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -27179,11 +27179,11 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>China foundry</t>
+          <t>Mature-node foundry</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -27232,7 +27232,7 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturing International Corporation</t>
+          <t>United Microelectronics Corporation</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
@@ -27247,22 +27247,22 @@
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X139" t="n">
-        <v>664308613120</v>
+        <v>61577895936</v>
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>HKD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z139" t="n">
-        <v>0.1275023967027664</v>
+        <v>1</v>
       </c>
       <c r="AA139" t="n">
-        <v>84700940323.09082</v>
+        <v>61577895936</v>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
@@ -27270,77 +27270,77 @@
         </is>
       </c>
       <c r="AC139" s="2" t="n">
-        <v>38064</v>
+        <v>36788</v>
       </c>
       <c r="AD139" t="n">
-        <v>22.3</v>
+        <v>25.8</v>
       </c>
       <c r="AE139" t="n">
-        <v>77.59999847412109</v>
+        <v>24.54000091552734</v>
       </c>
       <c r="AF139" t="n">
-        <v>75.31800018310547</v>
+        <v>19.38199995040894</v>
       </c>
       <c r="AG139" t="n">
-        <v>70.83299987792969</v>
+        <v>11.35295000076294</v>
       </c>
       <c r="AH139" t="n">
-        <v>0.03029817952505187</v>
+        <v>0.26612325757485</v>
       </c>
       <c r="AI139" t="n">
-        <v>0.09553454756756508</v>
+        <v>1.161552804678802</v>
       </c>
       <c r="AJ139" t="n">
-        <v>0.06331794944312708</v>
+        <v>0.7072214665885457</v>
       </c>
       <c r="AK139" t="n">
-        <v>91.05000305175781</v>
+        <v>28.01000022888184</v>
       </c>
       <c r="AL139" t="n">
-        <v>41.70000076293945</v>
+        <v>6.579999923706055</v>
       </c>
       <c r="AM139" t="n">
-        <v>-0.1477210777246323</v>
+        <v>-0.1238843014994511</v>
       </c>
       <c r="AN139" t="n">
-        <v>0.8609112003443291</v>
+        <v>2.729483465055373</v>
       </c>
       <c r="AO139" t="n">
-        <v>54.2490061811649</v>
+        <v>59.85700141326977</v>
       </c>
       <c r="AP139" t="n">
-        <v>124054283</v>
+        <v>21014000</v>
       </c>
       <c r="AQ139" t="n">
-        <v>139152933.62</v>
+        <v>17731794</v>
       </c>
       <c r="AR139" t="n">
-        <v>0.8914959948941391</v>
+        <v>1.185102872275642</v>
       </c>
       <c r="AS139" t="n">
-        <v>-0.06449666872753834</v>
+        <v>0.1456583019664124</v>
       </c>
       <c r="AT139" t="n">
-        <v>0.5097275519544682</v>
+        <v>1.830449907679487</v>
       </c>
       <c r="AU139" t="n">
-        <v>0.1262699093696604</v>
+        <v>2.122137468025066</v>
       </c>
       <c r="AV139" t="n">
-        <v>0.8609112003443291</v>
+        <v>2.122137468025066</v>
       </c>
       <c r="AW139" t="n">
-        <v>2.267368356805099</v>
+        <v>2.461462825373199</v>
       </c>
       <c r="AX139" t="n">
-        <v>0.03328894874560451</v>
+        <v>2.130102096672406</v>
       </c>
       <c r="AY139" t="n">
-        <v>2.135353473701862</v>
+        <v>2.989006846886231</v>
       </c>
       <c r="AZ139" t="inlineStr"/>
       <c r="BA139" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
@@ -27351,12 +27351,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>6146.T</t>
+          <t>0981.HK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Disco Corp</t>
+          <t>SMIC</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -27366,16 +27366,16 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Wafer processing</t>
+          <t>Foundry</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Wafer cutting/grinding</t>
+          <t>China foundry</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -27424,7 +27424,7 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>Disco Corporation</t>
+          <t>Semiconductor Manufacturing International Corporation</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
@@ -27434,27 +27434,27 @@
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>HKD</t>
         </is>
       </c>
       <c r="X140" t="n">
-        <v>8307543113728</v>
+        <v>664308613120</v>
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>HKD</t>
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>0.006215117871761322</v>
+        <v>0.1275022327899933</v>
       </c>
       <c r="AA140" t="n">
-        <v>51632359676.55859</v>
+        <v>84700831434.42383</v>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
@@ -27462,73 +27462,73 @@
         </is>
       </c>
       <c r="AC140" s="2" t="n">
-        <v>36892</v>
+        <v>38064</v>
       </c>
       <c r="AD140" t="n">
-        <v>25.5</v>
+        <v>22.3</v>
       </c>
       <c r="AE140" t="n">
-        <v>76590</v>
+        <v>77.59999847412109</v>
       </c>
       <c r="AF140" t="n">
-        <v>73718.2</v>
+        <v>75.31800018310547</v>
       </c>
       <c r="AG140" t="n">
-        <v>61171.60685546875</v>
+        <v>70.83299987792969</v>
       </c>
       <c r="AH140" t="n">
-        <v>0.03895645851363705</v>
+        <v>0.03029817952505187</v>
       </c>
       <c r="AI140" t="n">
-        <v>0.2520514653303216</v>
+        <v>0.09553454756756508</v>
       </c>
       <c r="AJ140" t="n">
-        <v>0.2051048483028295</v>
+        <v>0.06331794944312708</v>
       </c>
       <c r="AK140" t="n">
-        <v>88480</v>
+        <v>91.05000305175781</v>
       </c>
       <c r="AL140" t="n">
-        <v>35806.73828125</v>
+        <v>41.70000076293945</v>
       </c>
       <c r="AM140" t="n">
-        <v>-0.1343806509945751</v>
+        <v>-0.1477210777246323</v>
       </c>
       <c r="AN140" t="n">
-        <v>1.138982875189889</v>
+        <v>0.8609112003443291</v>
       </c>
       <c r="AO140" t="n">
-        <v>40.82238236540907</v>
+        <v>54.2490061811649</v>
       </c>
       <c r="AP140" t="n">
-        <v>1572400</v>
+        <v>124053283</v>
       </c>
       <c r="AQ140" t="n">
-        <v>1978612</v>
+        <v>139152913.62</v>
       </c>
       <c r="AR140" t="n">
-        <v>0.7946985058212525</v>
+        <v>0.8914889366870592</v>
       </c>
       <c r="AS140" t="n">
-        <v>0.05524937999448887</v>
+        <v>-0.06449666872753834</v>
       </c>
       <c r="AT140" t="n">
-        <v>0.2048135913166589</v>
+        <v>0.5097275519544682</v>
       </c>
       <c r="AU140" t="n">
-        <v>0.6141097618742239</v>
+        <v>0.1262699093696604</v>
       </c>
       <c r="AV140" t="n">
-        <v>1.138982875189889</v>
+        <v>0.8609112003443291</v>
       </c>
       <c r="AW140" t="n">
-        <v>6.635624103513569</v>
+        <v>2.267368356805099</v>
       </c>
       <c r="AX140" t="n">
-        <v>0.5073447446536921</v>
+        <v>0.03328894874560451</v>
       </c>
       <c r="AY140" t="n">
-        <v>51.40804862976935</v>
+        <v>2.135353473701862</v>
       </c>
       <c r="AZ140" t="inlineStr"/>
       <c r="BA140" t="n">
@@ -27543,12 +27543,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>6857.T</t>
+          <t>6146.T</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Advantest</t>
+          <t>Disco Corp</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -27558,16 +27558,16 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Semiconductor test equipment</t>
+          <t>Wafer processing</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AI chip testing equipment</t>
+          <t>Wafer cutting/grinding</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -27616,7 +27616,7 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>Advantest Corporation</t>
+          <t>Disco Corporation</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
@@ -27635,7 +27635,7 @@
         </is>
       </c>
       <c r="X141" t="n">
-        <v>21269657419776</v>
+        <v>8307543113728</v>
       </c>
       <c r="Y141" t="inlineStr">
         <is>
@@ -27643,10 +27643,10 @@
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>0.006215117871761322</v>
+        <v>0.00619820598512888</v>
       </c>
       <c r="AA141" t="n">
-        <v>132193427955.8906</v>
+        <v>51491863449.2251</v>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
@@ -27654,73 +27654,73 @@
         </is>
       </c>
       <c r="AC141" s="2" t="n">
-        <v>36529</v>
+        <v>36892</v>
       </c>
       <c r="AD141" t="n">
-        <v>26.5</v>
+        <v>25.5</v>
       </c>
       <c r="AE141" t="n">
-        <v>29345</v>
+        <v>76590</v>
       </c>
       <c r="AF141" t="n">
-        <v>28551.6</v>
+        <v>73718.2</v>
       </c>
       <c r="AG141" t="n">
-        <v>22980.15449707031</v>
+        <v>61171.60685546875</v>
       </c>
       <c r="AH141" t="n">
-        <v>0.02778828506983855</v>
+        <v>0.03895645851363705</v>
       </c>
       <c r="AI141" t="n">
-        <v>0.2769713973742487</v>
+        <v>0.2520514653303216</v>
       </c>
       <c r="AJ141" t="n">
-        <v>0.2424459549930345</v>
+        <v>0.2051048483028295</v>
       </c>
       <c r="AK141" t="n">
-        <v>35900</v>
+        <v>88480</v>
       </c>
       <c r="AL141" t="n">
-        <v>9677.3681640625</v>
+        <v>35806.73828125</v>
       </c>
       <c r="AM141" t="n">
-        <v>-0.1825905292479109</v>
+        <v>-0.1343806509945751</v>
       </c>
       <c r="AN141" t="n">
-        <v>2.032332706838049</v>
+        <v>1.138982875189889</v>
       </c>
       <c r="AO141" t="n">
-        <v>49.78417266187051</v>
+        <v>40.82238236540907</v>
       </c>
       <c r="AP141" t="n">
-        <v>7931300</v>
+        <v>1572400</v>
       </c>
       <c r="AQ141" t="n">
-        <v>9330252</v>
+        <v>1978612</v>
       </c>
       <c r="AR141" t="n">
-        <v>0.8500627850137381</v>
+        <v>0.7946985058212525</v>
       </c>
       <c r="AS141" t="n">
-        <v>0.09639454511488887</v>
+        <v>0.05524937999448887</v>
       </c>
       <c r="AT141" t="n">
-        <v>0.389112426035503</v>
+        <v>0.2048135913166589</v>
       </c>
       <c r="AU141" t="n">
-        <v>0.4844628101786497</v>
+        <v>0.6141097618742239</v>
       </c>
       <c r="AV141" t="n">
-        <v>2.032332706838049</v>
+        <v>1.138982875189889</v>
       </c>
       <c r="AW141" t="n">
-        <v>12.10179301570498</v>
+        <v>6.635624846904223</v>
       </c>
       <c r="AX141" t="n">
-        <v>0.3877186771459102</v>
+        <v>0.5073447446536921</v>
       </c>
       <c r="AY141" t="n">
-        <v>11.37390513537603</v>
+        <v>51.40803111946027</v>
       </c>
       <c r="AZ141" t="inlineStr"/>
       <c r="BA141" t="n">
@@ -27735,12 +27735,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>6920.T</t>
+          <t>6857.T</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Lasertec</t>
+          <t>Advantest</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -27750,16 +27750,16 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Inspection / metrology</t>
+          <t>Semiconductor test equipment</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>EUV mask inspection</t>
+          <t>AI chip testing equipment</t>
         </is>
       </c>
       <c r="F142" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -27808,7 +27808,7 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>Lasertec Corporation</t>
+          <t>Advantest Corporation</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
@@ -27827,7 +27827,7 @@
         </is>
       </c>
       <c r="X142" t="n">
-        <v>4270901428224</v>
+        <v>21269657419776</v>
       </c>
       <c r="Y142" t="inlineStr">
         <is>
@@ -27835,10 +27835,10 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>0.006215117871761322</v>
+        <v>0.00619820598512888</v>
       </c>
       <c r="AA142" t="n">
-        <v>26544155795.08594</v>
+        <v>131833717920.8965</v>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
@@ -27846,73 +27846,73 @@
         </is>
       </c>
       <c r="AC142" s="2" t="n">
-        <v>40231</v>
+        <v>36529</v>
       </c>
       <c r="AD142" t="n">
-        <v>16.4</v>
+        <v>26.5</v>
       </c>
       <c r="AE142" t="n">
-        <v>47650</v>
+        <v>29345</v>
       </c>
       <c r="AF142" t="n">
-        <v>44245.3728125</v>
+        <v>28551.6</v>
       </c>
       <c r="AG142" t="n">
-        <v>33154.52732910156</v>
+        <v>22980.15449707031</v>
       </c>
       <c r="AH142" t="n">
-        <v>0.07694877387355059</v>
+        <v>0.02778828506983855</v>
       </c>
       <c r="AI142" t="n">
-        <v>0.4372094503719546</v>
+        <v>0.2769713973742487</v>
       </c>
       <c r="AJ142" t="n">
-        <v>0.3345197889056735</v>
+        <v>0.2424459549930345</v>
       </c>
       <c r="AK142" t="n">
-        <v>57263.48828125</v>
+        <v>35900</v>
       </c>
       <c r="AL142" t="n">
-        <v>14136.361328125</v>
+        <v>9677.3681640625</v>
       </c>
       <c r="AM142" t="n">
-        <v>-0.1678816392398816</v>
+        <v>-0.1825905292479109</v>
       </c>
       <c r="AN142" t="n">
-        <v>2.370740100226353</v>
+        <v>2.032332706838049</v>
       </c>
       <c r="AO142" t="n">
-        <v>49.30773932179242</v>
+        <v>49.78417266187051</v>
       </c>
       <c r="AP142" t="n">
-        <v>2970300</v>
+        <v>7931300</v>
       </c>
       <c r="AQ142" t="n">
-        <v>3644294</v>
+        <v>9330252</v>
       </c>
       <c r="AR142" t="n">
-        <v>0.8150549873308794</v>
+        <v>0.8500627850137381</v>
       </c>
       <c r="AS142" t="n">
-        <v>0.1341508224229828</v>
+        <v>0.09639454511488887</v>
       </c>
       <c r="AT142" t="n">
-        <v>0.3660331398313825</v>
+        <v>0.389112426035503</v>
       </c>
       <c r="AU142" t="n">
-        <v>0.6365770901075996</v>
+        <v>0.4844628101786497</v>
       </c>
       <c r="AV142" t="n">
-        <v>1.999475023021531</v>
+        <v>2.032332706838049</v>
       </c>
       <c r="AW142" t="n">
-        <v>1.873559630708577</v>
+        <v>12.10179158757624</v>
       </c>
       <c r="AX142" t="n">
-        <v>0.5086245278127912</v>
+        <v>0.3877186771459102</v>
       </c>
       <c r="AY142" t="n">
-        <v>366.2273835721099</v>
+        <v>11.37390640922971</v>
       </c>
       <c r="AZ142" t="inlineStr"/>
       <c r="BA142" t="n">
@@ -27927,12 +27927,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ASM.AS</t>
+          <t>6920.T</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ASM International</t>
+          <t>Lasertec</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -27942,16 +27942,16 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Semiconductor process equipment</t>
+          <t>Inspection / metrology</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Atomic layer deposition equipment</t>
+          <t>EUV mask inspection</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -28000,7 +28000,7 @@
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>ASM International NV</t>
+          <t>Lasertec Corporation</t>
         </is>
       </c>
       <c r="U143" t="inlineStr">
@@ -28015,22 +28015,22 @@
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="X143" t="n">
-        <v>46881742848</v>
+        <v>4270901428224</v>
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="Z143" t="n">
-        <v>1.145869135856628</v>
+        <v>0.00619820598512888</v>
       </c>
       <c r="AA143" t="n">
-        <v>53720342164.69043</v>
+        <v>26471926794.31348</v>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
@@ -28038,73 +28038,73 @@
         </is>
       </c>
       <c r="AC143" s="2" t="n">
-        <v>36166</v>
+        <v>40231</v>
       </c>
       <c r="AD143" t="n">
-        <v>27.5</v>
+        <v>16.4</v>
       </c>
       <c r="AE143" t="n">
-        <v>959</v>
+        <v>47650</v>
       </c>
       <c r="AF143" t="n">
-        <v>913.8333569335938</v>
+        <v>44245.3728125</v>
       </c>
       <c r="AG143" t="n">
-        <v>685.8012191772461</v>
+        <v>33154.52732910156</v>
       </c>
       <c r="AH143" t="n">
-        <v>0.04942546988869467</v>
+        <v>0.07694877387355059</v>
       </c>
       <c r="AI143" t="n">
-        <v>0.3983643848730827</v>
+        <v>0.4372094503719546</v>
       </c>
       <c r="AJ143" t="n">
-        <v>0.3325047132898322</v>
+        <v>0.3345197889056735</v>
       </c>
       <c r="AK143" t="n">
-        <v>1079</v>
+        <v>57263.48828125</v>
       </c>
       <c r="AL143" t="n">
-        <v>400.14208984375</v>
+        <v>14136.361328125</v>
       </c>
       <c r="AM143" t="n">
-        <v>-0.1112140871177015</v>
+        <v>-0.1678816392398816</v>
       </c>
       <c r="AN143" t="n">
-        <v>1.396648651418991</v>
+        <v>2.370740100226353</v>
       </c>
       <c r="AO143" t="n">
-        <v>42.64378025056798</v>
+        <v>49.30773932179242</v>
       </c>
       <c r="AP143" t="n">
-        <v>15461</v>
+        <v>2970300</v>
       </c>
       <c r="AQ143" t="n">
-        <v>160466.58</v>
+        <v>3644294</v>
       </c>
       <c r="AR143" t="n">
-        <v>0.09635028053816565</v>
+        <v>0.8150549873308794</v>
       </c>
       <c r="AS143" t="n">
-        <v>0.1061130334486735</v>
+        <v>0.1341508224229828</v>
       </c>
       <c r="AT143" t="n">
-        <v>0.4317872737034754</v>
+        <v>0.3660331398313825</v>
       </c>
       <c r="AU143" t="n">
-        <v>0.5393887319403752</v>
+        <v>0.6365770901075996</v>
       </c>
       <c r="AV143" t="n">
-        <v>0.8686602523696823</v>
+        <v>1.999475023021531</v>
       </c>
       <c r="AW143" t="n">
-        <v>2.236327680665842</v>
+        <v>1.873559969168782</v>
       </c>
       <c r="AX143" t="n">
-        <v>0.7384142914976308</v>
+        <v>0.5086245278127912</v>
       </c>
       <c r="AY143" t="n">
-        <v>325.2744776375947</v>
+        <v>366.2273403876761</v>
       </c>
       <c r="AZ143" t="inlineStr"/>
       <c r="BA143" t="n">
@@ -28273,13 +28273,13 @@
         <v>38.6930032830109</v>
       </c>
       <c r="AP144" t="n">
-        <v>3792500</v>
+        <v>3796900</v>
       </c>
       <c r="AQ144" t="n">
-        <v>4974246</v>
+        <v>4974334</v>
       </c>
       <c r="AR144" t="n">
-        <v>0.7624271095559005</v>
+        <v>0.7632981621258242</v>
       </c>
       <c r="AS144" t="n">
         <v>-0.1866421221712389</v>
@@ -28463,13 +28463,13 @@
         <v>33.3573114875642</v>
       </c>
       <c r="AP145" t="n">
-        <v>671100</v>
+        <v>671900</v>
       </c>
       <c r="AQ145" t="n">
-        <v>510442</v>
+        <v>510458</v>
       </c>
       <c r="AR145" t="n">
-        <v>1.314742909086635</v>
+        <v>1.316268919284251</v>
       </c>
       <c r="AS145" t="n">
         <v>-0.2232215733412939</v>
@@ -28490,7 +28490,7 @@
         <v>0.2337662337662338</v>
       </c>
       <c r="AY145" t="n">
-        <v>24.62711860918476</v>
+        <v>24.62712080681601</v>
       </c>
       <c r="AZ145" t="inlineStr"/>
       <c r="BA145" t="n">
@@ -28680,13 +28680,13 @@
         <v>0.3475263935133022</v>
       </c>
       <c r="AW146" t="n">
-        <v>1.302541642530659</v>
+        <v>1.302541498850832</v>
       </c>
       <c r="AX146" t="n">
         <v>0.1575880559526486</v>
       </c>
       <c r="AY146" t="n">
-        <v>44.5810689046025</v>
+        <v>44.58108650003868</v>
       </c>
       <c r="AZ146" t="inlineStr"/>
       <c r="BA146" t="n">
@@ -28801,10 +28801,10 @@
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>0.03134599700570107</v>
+        <v>0.03132537752389908</v>
       </c>
       <c r="AA147" t="n">
-        <v>45550543756.21924</v>
+        <v>45520580485.05957</v>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
@@ -28851,13 +28851,13 @@
         <v>53.78787878787878</v>
       </c>
       <c r="AP147" t="n">
-        <v>13098566</v>
+        <v>12753585</v>
       </c>
       <c r="AQ147" t="n">
-        <v>34039310.68</v>
+        <v>34032411.06</v>
       </c>
       <c r="AR147" t="n">
-        <v>0.3848070286480901</v>
+        <v>0.3747482062765141</v>
       </c>
       <c r="AS147" t="n">
         <v>-0.06683168316831678</v>
@@ -28872,13 +28872,13 @@
         <v>0.4131853059356814</v>
       </c>
       <c r="AW147" t="n">
-        <v>4.159402778994461</v>
+        <v>4.159402240293756</v>
       </c>
       <c r="AX147" t="n">
         <v>0.3610108303249098</v>
       </c>
       <c r="AY147" t="n">
-        <v>18.00702452791016</v>
+        <v>18.00702635566122</v>
       </c>
       <c r="AZ147" t="inlineStr"/>
       <c r="BA147" t="n">
@@ -28993,10 +28993,10 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>0.03134599700570107</v>
+        <v>0.03132537752389908</v>
       </c>
       <c r="AA148" t="n">
-        <v>92011639787.58203</v>
+        <v>91951114281.50781</v>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
@@ -29043,13 +29043,13 @@
         <v>63.77673640249019</v>
       </c>
       <c r="AP148" t="n">
-        <v>1551729</v>
+        <v>1352064</v>
       </c>
       <c r="AQ148" t="n">
-        <v>2064805.34</v>
+        <v>2060812.04</v>
       </c>
       <c r="AR148" t="n">
-        <v>0.751513457438075</v>
+        <v>0.6560831234274038</v>
       </c>
       <c r="AS148" t="n">
         <v>-0.02738185557774409</v>
@@ -29064,13 +29064,13 @@
         <v>1.200944759097657</v>
       </c>
       <c r="AW148" t="n">
-        <v>6.34015263223684</v>
+        <v>6.340153256822348</v>
       </c>
       <c r="AX148" t="n">
         <v>0.209259605048675</v>
       </c>
       <c r="AY148" t="n">
-        <v>61.77580222678169</v>
+        <v>61.77581364783913</v>
       </c>
       <c r="AZ148" t="inlineStr"/>
       <c r="BA148" t="n">
@@ -29177,7 +29177,7 @@
         </is>
       </c>
       <c r="X149" t="n">
-        <v>123175534592</v>
+        <v>124667363328</v>
       </c>
       <c r="Y149" t="inlineStr">
         <is>
@@ -29185,10 +29185,10 @@
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>1.33650529384613</v>
+        <v>1.334988713264465</v>
       </c>
       <c r="AA149" t="n">
-        <v>164624754054.5352</v>
+        <v>166429522955.3203</v>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
@@ -29202,25 +29202,25 @@
         <v>38</v>
       </c>
       <c r="AE149" t="n">
-        <v>1486.199951171875</v>
+        <v>1504.199951171875</v>
       </c>
       <c r="AF149" t="n">
-        <v>1282.147985839844</v>
+        <v>1282.507985839844</v>
       </c>
       <c r="AG149" t="n">
-        <v>1212.776298217774</v>
+        <v>1212.866298217773</v>
       </c>
       <c r="AH149" t="n">
-        <v>0.1591485285517733</v>
+        <v>0.172858155878739</v>
       </c>
       <c r="AI149" t="n">
-        <v>0.2254526686874647</v>
+        <v>0.2402026120951641</v>
       </c>
       <c r="AJ149" t="n">
-        <v>0.05720072838166024</v>
+        <v>0.057419096997257</v>
       </c>
       <c r="AK149" t="n">
-        <v>1486.199951171875</v>
+        <v>1504.199951171875</v>
       </c>
       <c r="AL149" t="n">
         <v>962.5178833007812</v>
@@ -29229,40 +29229,40 @@
         <v>0</v>
       </c>
       <c r="AN149" t="n">
-        <v>0.5440751563755062</v>
+        <v>0.5627761076121442</v>
       </c>
       <c r="AO149" t="n">
-        <v>77.85522605596816</v>
+        <v>79.46640430294917</v>
       </c>
       <c r="AP149" t="n">
-        <v>782986</v>
+        <v>10723720</v>
       </c>
       <c r="AQ149" t="n">
-        <v>31514831.82</v>
+        <v>31713646.5</v>
       </c>
       <c r="AR149" t="n">
-        <v>0.02484500010890428</v>
+        <v>0.3381421307070444</v>
       </c>
       <c r="AS149" t="n">
-        <v>0.1795237707713293</v>
+        <v>0.1938094850570435</v>
       </c>
       <c r="AT149" t="n">
-        <v>0.2505387353267807</v>
+        <v>0.2656845420657279</v>
       </c>
       <c r="AU149" t="n">
-        <v>0.2068739061885874</v>
+        <v>0.221490869602067</v>
       </c>
       <c r="AV149" t="n">
-        <v>0.5440751563755062</v>
+        <v>0.5627761076121442</v>
       </c>
       <c r="AW149" t="n">
-        <v>13.33966703126966</v>
+        <v>13.5133408403418</v>
       </c>
       <c r="AX149" t="n">
-        <v>0.2416585444356998</v>
+        <v>0.2566967994041647</v>
       </c>
       <c r="AY149" t="n">
-        <v>10.93585322614632</v>
+        <v>11.08041490377719</v>
       </c>
       <c r="AZ149" t="inlineStr"/>
       <c r="BA149" t="n">
@@ -29381,10 +29381,10 @@
         </is>
       </c>
       <c r="Z150" t="n">
-        <v>0.03134599700570107</v>
+        <v>0.03132537752389908</v>
       </c>
       <c r="AA150" t="n">
-        <v>105556444865.5459</v>
+        <v>105487009549.9746</v>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
@@ -29431,13 +29431,13 @@
         <v>37.39576693260896</v>
       </c>
       <c r="AP150" t="n">
-        <v>50441014</v>
+        <v>49052306</v>
       </c>
       <c r="AQ150" t="n">
-        <v>88734249.08</v>
+        <v>88706474.92</v>
       </c>
       <c r="AR150" t="n">
-        <v>0.5684503393331697</v>
+        <v>0.5529732304686649</v>
       </c>
       <c r="AS150" t="n">
         <v>-0.1547371730221786</v>
@@ -29452,7 +29452,7 @@
         <v>0.6505246649713299</v>
       </c>
       <c r="AW150" t="n">
-        <v>1.571705881541916</v>
+        <v>1.571705671736086</v>
       </c>
       <c r="AX150" t="n">
         <v>0.06750867696625695</v>
@@ -29573,10 +29573,10 @@
         </is>
       </c>
       <c r="Z151" t="n">
-        <v>0.03134599700570107</v>
+        <v>0.03132537752389908</v>
       </c>
       <c r="AA151" t="n">
-        <v>7601821094.39386</v>
+        <v>7596820595.871216</v>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
@@ -29623,13 +29623,13 @@
         <v>55.5555589194845</v>
       </c>
       <c r="AP151" t="n">
-        <v>23231651</v>
+        <v>23041933</v>
       </c>
       <c r="AQ151" t="n">
-        <v>67295444.84</v>
+        <v>67291650.48</v>
       </c>
       <c r="AR151" t="n">
-        <v>0.3452187745431359</v>
+        <v>0.3424189009429688</v>
       </c>
       <c r="AS151" t="n">
         <v>-0.1311054521534014</v>
@@ -29644,13 +29644,13 @@
         <v>0.742671356683702</v>
       </c>
       <c r="AW151" t="n">
-        <v>2.119157048232528</v>
+        <v>2.119156773722735</v>
       </c>
       <c r="AX151" t="n">
         <v>0.5173961757980359</v>
       </c>
       <c r="AY151" t="n">
-        <v>7.615744321328933</v>
+        <v>7.615742226884246</v>
       </c>
       <c r="AZ151" t="inlineStr"/>
       <c r="BA151" t="n">
@@ -29765,10 +29765,10 @@
         </is>
       </c>
       <c r="Z152" t="n">
-        <v>0.03134599700570107</v>
+        <v>0.03132537752389908</v>
       </c>
       <c r="AA152" t="n">
-        <v>15851216422.60364</v>
+        <v>15840789449.47192</v>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
@@ -29815,13 +29815,13 @@
         <v>53.94736842105263</v>
       </c>
       <c r="AP152" t="n">
-        <v>24709723</v>
+        <v>24456191</v>
       </c>
       <c r="AQ152" t="n">
-        <v>54997917.76</v>
+        <v>54992847.12</v>
       </c>
       <c r="AR152" t="n">
-        <v>0.4492847003377169</v>
+        <v>0.4447158545298464</v>
       </c>
       <c r="AS152" t="n">
         <v>-0.09659090909090906</v>
@@ -29842,7 +29842,7 @@
         <v>0.02580645161290329</v>
       </c>
       <c r="AY152" t="n">
-        <v>30.9573400149931</v>
+        <v>30.95734307776219</v>
       </c>
       <c r="AZ152" t="inlineStr"/>
       <c r="BA152" t="n">
@@ -29957,10 +29957,10 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>0.03134599700570107</v>
+        <v>0.03132537752389908</v>
       </c>
       <c r="AA153" t="n">
-        <v>7028364662.084656</v>
+        <v>7023741384.75769</v>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
@@ -30007,13 +30007,13 @@
         <v>38.69815846596519</v>
       </c>
       <c r="AP153" t="n">
-        <v>8973220</v>
+        <v>8948782</v>
       </c>
       <c r="AQ153" t="n">
-        <v>21893513.36</v>
+        <v>21893024.6</v>
       </c>
       <c r="AR153" t="n">
-        <v>0.4098574702219471</v>
+        <v>0.4087503743087193</v>
       </c>
       <c r="AS153" t="n">
         <v>-0.09935737185348714</v>
@@ -30028,13 +30028,13 @@
         <v>0.1525373901367431</v>
       </c>
       <c r="AW153" t="n">
-        <v>0.5801791802063203</v>
+        <v>0.5801790662688826</v>
       </c>
       <c r="AX153" t="n">
         <v>0.2679583829508632</v>
       </c>
       <c r="AY153" t="n">
-        <v>-0.1263678881278293</v>
+        <v>-0.1263679577810091</v>
       </c>
       <c r="AZ153" t="inlineStr"/>
       <c r="BA153" t="n">
@@ -30199,13 +30199,13 @@
         <v>35.3996370484801</v>
       </c>
       <c r="AP154" t="n">
-        <v>2132800</v>
+        <v>2135000</v>
       </c>
       <c r="AQ154" t="n">
-        <v>2238324</v>
+        <v>2238368</v>
       </c>
       <c r="AR154" t="n">
-        <v>0.9528557974627444</v>
+        <v>0.9538199259460464</v>
       </c>
       <c r="AS154" t="n">
         <v>-0.2661413962867328</v>
@@ -30368,40 +30368,40 @@
         <v>111.019400177002</v>
       </c>
       <c r="AG155" t="n">
-        <v>84.46414356231689</v>
+        <v>84.46414367675781</v>
       </c>
       <c r="AH155" t="n">
         <v>0.0150478408434993</v>
       </c>
       <c r="AI155" t="n">
-        <v>0.3341756358218984</v>
+        <v>0.3341756340142168</v>
       </c>
       <c r="AJ155" t="n">
-        <v>0.3143968019410843</v>
+        <v>0.3143968001602011</v>
       </c>
       <c r="AK155" t="n">
         <v>130</v>
       </c>
       <c r="AL155" t="n">
-        <v>65.09966278076172</v>
+        <v>65.09967041015625</v>
       </c>
       <c r="AM155" t="n">
         <v>-0.1331538273737981</v>
       </c>
       <c r="AN155" t="n">
-        <v>0.7310381901810472</v>
+        <v>0.7310379873109987</v>
       </c>
       <c r="AO155" t="n">
         <v>32.0078708937928</v>
       </c>
       <c r="AP155" t="n">
-        <v>24251000</v>
+        <v>24254900</v>
       </c>
       <c r="AQ155" t="n">
-        <v>26043142</v>
+        <v>26043220</v>
       </c>
       <c r="AR155" t="n">
-        <v>0.9311856457258498</v>
+        <v>0.9313326078726056</v>
       </c>
       <c r="AS155" t="n">
         <v>-0.1091699411746542</v>
@@ -30422,7 +30422,7 @@
         <v>0.4900135176031475</v>
       </c>
       <c r="AY155" t="n">
-        <v>2265.500366086732</v>
+        <v>2265.500196267729</v>
       </c>
       <c r="AZ155" t="inlineStr"/>
       <c r="BA155" t="n">
@@ -30564,16 +30564,16 @@
         <v>323.0927981567383</v>
       </c>
       <c r="AG156" t="n">
-        <v>186.1366176605225</v>
+        <v>186.1366176223755</v>
       </c>
       <c r="AH156" t="n">
         <v>0.2204543387343683</v>
       </c>
       <c r="AI156" t="n">
-        <v>1.118444034711015</v>
+        <v>1.11844403514517</v>
       </c>
       <c r="AJ156" t="n">
-        <v>0.7357831157435002</v>
+        <v>0.7357831160992327</v>
       </c>
       <c r="AK156" t="n">
         <v>465.9599914550781</v>
@@ -30591,13 +30591,13 @@
         <v>50.81575651172232</v>
       </c>
       <c r="AP156" t="n">
-        <v>6611600</v>
+        <v>6618400</v>
       </c>
       <c r="AQ156" t="n">
-        <v>9038770</v>
+        <v>9038906</v>
       </c>
       <c r="AR156" t="n">
-        <v>0.7314712068124314</v>
+        <v>0.7322125044778649</v>
       </c>
       <c r="AS156" t="n">
         <v>-0.06355082193737638</v>
@@ -30612,13 +30612,13 @@
         <v>2.241947806485914</v>
       </c>
       <c r="AW156" t="n">
-        <v>7.593164166203001</v>
+        <v>7.593164880563643</v>
       </c>
       <c r="AX156" t="n">
         <v>2.108532938768634</v>
       </c>
       <c r="AY156" t="n">
-        <v>34.91083939360699</v>
+        <v>34.91083315579463</v>
       </c>
       <c r="AZ156" t="inlineStr"/>
       <c r="BA156" t="n">
@@ -30787,13 +30787,13 @@
         <v>41.80833574290553</v>
       </c>
       <c r="AP157" t="n">
-        <v>6566100</v>
+        <v>6570400</v>
       </c>
       <c r="AQ157" t="n">
-        <v>7755850</v>
+        <v>7755936</v>
       </c>
       <c r="AR157" t="n">
-        <v>0.846599663479825</v>
+        <v>0.8471446902088929</v>
       </c>
       <c r="AS157" t="n">
         <v>-0.1548721838517276</v>
@@ -30956,40 +30956,40 @@
         <v>39.29432300567627</v>
       </c>
       <c r="AG158" t="n">
-        <v>27.05629073143005</v>
+        <v>27.05629078865051</v>
       </c>
       <c r="AH158" t="n">
         <v>0.04926097177651956</v>
       </c>
       <c r="AI158" t="n">
-        <v>0.523860012870919</v>
+        <v>0.5238600096481576</v>
       </c>
       <c r="AJ158" t="n">
-        <v>0.4523174442396811</v>
+        <v>0.4523174411682227</v>
       </c>
       <c r="AK158" t="n">
         <v>55.98620223999023</v>
       </c>
       <c r="AL158" t="n">
-        <v>19.40578269958496</v>
+        <v>19.40578460693359</v>
       </c>
       <c r="AM158" t="n">
         <v>-0.2635685598837375</v>
       </c>
       <c r="AN158" t="n">
-        <v>1.124624406060062</v>
+        <v>1.124624197235759</v>
       </c>
       <c r="AO158" t="n">
         <v>32.6744442052229</v>
       </c>
       <c r="AP158" t="n">
-        <v>18968400</v>
+        <v>18976700</v>
       </c>
       <c r="AQ158" t="n">
-        <v>27574146</v>
+        <v>27574312</v>
       </c>
       <c r="AR158" t="n">
-        <v>0.6879052573377975</v>
+        <v>0.688202120872499</v>
       </c>
       <c r="AS158" t="n">
         <v>-0.2502153302363888</v>
@@ -31001,16 +31001,16 @@
         <v>0.7326086048707248</v>
       </c>
       <c r="AV158" t="n">
-        <v>0.980649799991552</v>
+        <v>0.9806496185101601</v>
       </c>
       <c r="AW158" t="n">
-        <v>2.22172376368455</v>
+        <v>2.221723283516467</v>
       </c>
       <c r="AX158" t="n">
         <v>0.7218560211767862</v>
       </c>
       <c r="AY158" t="n">
-        <v>4.722387719115726</v>
+        <v>4.722385825546522</v>
       </c>
       <c r="AZ158" t="inlineStr"/>
       <c r="BA158" t="n">
@@ -31152,16 +31152,16 @@
         <v>359.1488330078125</v>
       </c>
       <c r="AG159" t="n">
-        <v>267.7773109436035</v>
+        <v>267.7773107910156</v>
       </c>
       <c r="AH159" t="n">
         <v>-0.04969762832128011</v>
       </c>
       <c r="AI159" t="n">
-        <v>0.2745664917997843</v>
+        <v>0.2745664925260722</v>
       </c>
       <c r="AJ159" t="n">
-        <v>0.3412220465663451</v>
+        <v>0.3412220473306156</v>
       </c>
       <c r="AK159" t="n">
         <v>385.6300048828125</v>
@@ -31206,7 +31206,7 @@
         <v>0.4205431288416457</v>
       </c>
       <c r="AY159" t="n">
-        <v>460.8583239923539</v>
+        <v>460.8585102574845</v>
       </c>
       <c r="AZ159" t="inlineStr"/>
       <c r="BA159" t="n">
@@ -31371,13 +31371,13 @@
         <v>38.21423982321316</v>
       </c>
       <c r="AP160" t="n">
-        <v>679600</v>
+        <v>680200</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1024486</v>
+        <v>1024498</v>
       </c>
       <c r="AR160" t="n">
-        <v>0.6633570395300667</v>
+        <v>0.6639349222741284</v>
       </c>
       <c r="AS160" t="n">
         <v>-0.310882778825431</v>
@@ -31567,13 +31567,13 @@
         <v>39.78494623655914</v>
       </c>
       <c r="AP161" t="n">
-        <v>42742400</v>
+        <v>42867500</v>
       </c>
       <c r="AQ161" t="n">
-        <v>55708418</v>
+        <v>55710920</v>
       </c>
       <c r="AR161" t="n">
-        <v>0.7672520874672837</v>
+        <v>0.7694631501328645</v>
       </c>
       <c r="AS161" t="n">
         <v>-0.4259805912185698</v>
@@ -32059,13 +32059,13 @@
         <v>55.57368157652713</v>
       </c>
       <c r="AP2" t="n">
-        <v>7247100</v>
+        <v>7258800</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6320728</v>
+        <v>6320962</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.146560965762172</v>
+        <v>1.148369504515294</v>
       </c>
       <c r="AS2" t="n">
         <v>0.117951267742004</v>
@@ -32259,13 +32259,13 @@
         <v>52.45790251046104</v>
       </c>
       <c r="AP3" t="n">
-        <v>9764500</v>
+        <v>9766500</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10197862</v>
+        <v>10197902</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9575046220472487</v>
+        <v>0.9576969851249796</v>
       </c>
       <c r="AS3" t="n">
         <v>-0.08246825730745244</v>
@@ -32461,13 +32461,13 @@
         <v>45.42335820442248</v>
       </c>
       <c r="AP4" t="n">
-        <v>7553900</v>
+        <v>7576000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12236322</v>
+        <v>12236764</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.6173341956839645</v>
+        <v>0.6191179301978856</v>
       </c>
       <c r="AS4" t="n">
         <v>-0.2344413737245593</v>
@@ -32661,13 +32661,13 @@
         <v>41.6450519969167</v>
       </c>
       <c r="AP5" t="n">
-        <v>26749500</v>
+        <v>26788900</v>
       </c>
       <c r="AQ5" t="n">
-        <v>27280644</v>
+        <v>27281432</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9805303716437193</v>
+        <v>0.9819462556071104</v>
       </c>
       <c r="AS5" t="n">
         <v>-0.2466655334868972</v>
@@ -32688,7 +32688,7 @@
         <v>0.04072788759895696</v>
       </c>
       <c r="AY5" t="n">
-        <v>316.4115837281723</v>
+        <v>316.4116836894942</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -32863,13 +32863,13 @@
         <v>45.1306306405907</v>
       </c>
       <c r="AP6" t="n">
-        <v>9047500</v>
+        <v>9061700</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8677948</v>
+        <v>8678232</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.042585182580029</v>
+        <v>1.044187341384743</v>
       </c>
       <c r="AS6" t="n">
         <v>0.127260003643338</v>
@@ -33036,16 +33036,16 @@
         <v>320.9159280395508</v>
       </c>
       <c r="AG7" t="n">
-        <v>222.4916584014892</v>
+        <v>222.4916584777832</v>
       </c>
       <c r="AH7" t="n">
         <v>0.09502200719311249</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.5794300163289052</v>
+        <v>0.5794300157873076</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.4423728527406345</v>
+        <v>0.4423728522460346</v>
       </c>
       <c r="AK7" t="n">
         <v>433.3299865722656</v>
@@ -33063,13 +33063,13 @@
         <v>48.27151631497328</v>
       </c>
       <c r="AP7" t="n">
-        <v>18954700</v>
+        <v>18973400</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11510688</v>
+        <v>11511062</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.646704349905062</v>
+        <v>1.64827537198566</v>
       </c>
       <c r="AS7" t="n">
         <v>0.02312283663775716</v>
@@ -33084,13 +33084,13 @@
         <v>2.575380862185094</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.871855144966326</v>
+        <v>4.871854770686348</v>
       </c>
       <c r="AX7" t="n">
         <v>0.9025119429474571</v>
       </c>
       <c r="AY7" t="n">
-        <v>1862.928416350627</v>
+        <v>1862.928710992533</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
@@ -33265,13 +33265,13 @@
         <v>42.26502405412126</v>
       </c>
       <c r="AP8" t="n">
-        <v>38435900</v>
+        <v>38579900</v>
       </c>
       <c r="AQ8" t="n">
-        <v>46063942</v>
+        <v>46066822</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.8344031867702508</v>
+        <v>0.837476915598823</v>
       </c>
       <c r="AS8" t="n">
         <v>-0.1868390576851539</v>
@@ -33286,13 +33286,13 @@
         <v>2.312499864772374</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.442105612207184</v>
+        <v>3.442106225952319</v>
       </c>
       <c r="AX8" t="n">
         <v>1.747391867747758</v>
       </c>
       <c r="AY8" t="n">
-        <v>19.21793582350067</v>
+        <v>19.21793423424472</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
@@ -33463,13 +33463,13 @@
         <v>48.40296980201639</v>
       </c>
       <c r="AP9" t="n">
-        <v>24804700</v>
+        <v>24901800</v>
       </c>
       <c r="AQ9" t="n">
-        <v>18033748</v>
+        <v>18035690</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.375460054116316</v>
+        <v>1.380695720540772</v>
       </c>
       <c r="AS9" t="n">
         <v>-0.1432771718372023</v>
@@ -33713,22 +33713,22 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>4455.521097849222</v>
+        <v>4455.227813890603</v>
       </c>
       <c r="D2" t="n">
-        <v>297.0347398566148</v>
+        <v>297.0151875927068</v>
       </c>
       <c r="E2" t="n">
         <v>61.577895936</v>
       </c>
       <c r="F2" t="n">
-        <v>86.33333333333333</v>
+        <v>87</v>
       </c>
       <c r="G2" t="n">
         <v>90</v>
       </c>
       <c r="H2" t="n">
-        <v>95.01674107384486</v>
+        <v>95.1379735576849</v>
       </c>
       <c r="I2" t="n">
         <v>14</v>
@@ -33737,40 +33737,40 @@
         <v>0.9333333333333333</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7375588656416152</v>
+        <v>0.7395649747935339</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7384142914976308</v>
+        <v>0.7685056729336115</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5851680965249186</v>
+        <v>0.5855327608553891</v>
       </c>
       <c r="N2" t="n">
-        <v>1.556747865883133</v>
+        <v>1.558904258970915</v>
       </c>
       <c r="O2" t="n">
         <v>1.573750421816833</v>
       </c>
       <c r="P2" t="n">
-        <v>1.270997061880617</v>
+        <v>1.271137161797991</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.942229047743495</v>
+        <v>3.946230280308651</v>
       </c>
       <c r="R2" t="n">
-        <v>2.975069249416984</v>
+        <v>2.975068962344419</v>
       </c>
       <c r="S2" t="n">
-        <v>3.48126900283602</v>
+        <v>3.480837399144012</v>
       </c>
       <c r="T2" t="n">
-        <v>994.0139484111147</v>
+        <v>994.390726651143</v>
       </c>
       <c r="U2" t="n">
-        <v>51.40804862976935</v>
+        <v>51.40803111946027</v>
       </c>
       <c r="V2" t="n">
-        <v>1443.106950768408</v>
+        <v>1443.321299213546</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -33788,10 +33788,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="n">
-        <v>229.131088168449</v>
+        <v>229.3367950969422</v>
       </c>
       <c r="D3" t="n">
-        <v>32.73301259549272</v>
+        <v>32.76239929956317</v>
       </c>
       <c r="E3" t="n">
         <v>17.264320512</v>
@@ -33803,7 +33803,7 @@
         <v>90</v>
       </c>
       <c r="H3" t="n">
-        <v>92.39667784128416</v>
+        <v>92.3885452602408</v>
       </c>
       <c r="I3" t="n">
         <v>7</v>
@@ -33812,40 +33812,40 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>2.457443390704104</v>
+        <v>2.49620643122458</v>
       </c>
       <c r="L3" t="n">
         <v>2.267312882239865</v>
       </c>
       <c r="M3" t="n">
-        <v>2.209081877462894</v>
+        <v>2.224162358902581</v>
       </c>
       <c r="N3" t="n">
-        <v>5.764322091397264</v>
+        <v>5.833799056587742</v>
       </c>
       <c r="O3" t="n">
         <v>7.050092846066804</v>
       </c>
       <c r="P3" t="n">
-        <v>5.409446113918849</v>
+        <v>5.434614243215017</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.698275174706299</v>
+        <v>5.73330554614082</v>
       </c>
       <c r="R3" t="n">
-        <v>5.399913353698032</v>
+        <v>5.399912887237076</v>
       </c>
       <c r="S3" t="n">
-        <v>6.547446978166569</v>
+        <v>6.552021755679464</v>
       </c>
       <c r="T3" t="n">
-        <v>37.63483467760842</v>
+        <v>37.74563731290523</v>
       </c>
       <c r="U3" t="n">
         <v>32.72988470878067</v>
       </c>
       <c r="V3" t="n">
-        <v>52.29896853115996</v>
+        <v>52.27331127011278</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -33863,10 +33863,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>11435.10768275756</v>
+        <v>11435.28734145017</v>
       </c>
       <c r="D4" t="n">
-        <v>1429.388460344695</v>
+        <v>1429.410917681272</v>
       </c>
       <c r="E4" t="n">
         <v>470.811475968</v>
@@ -33878,7 +33878,7 @@
         <v>85</v>
       </c>
       <c r="H4" t="n">
-        <v>90.94610787208286</v>
+        <v>90.94601445335761</v>
       </c>
       <c r="I4" t="n">
         <v>8</v>
@@ -33887,40 +33887,40 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7516421711704484</v>
+        <v>0.7516421872598474</v>
       </c>
       <c r="L4" t="n">
         <v>0.3443674746027734</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3341619703217105</v>
+        <v>0.3341638738715354</v>
       </c>
       <c r="N4" t="n">
-        <v>1.488481110894349</v>
+        <v>1.488481097747107</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7487408730011517</v>
+        <v>0.7487408204121843</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7835778964403152</v>
+        <v>0.7836050810497953</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.759471721684227</v>
+        <v>4.759472036430963</v>
       </c>
       <c r="R4" t="n">
-        <v>1.378664997029958</v>
+        <v>1.378665836238499</v>
       </c>
       <c r="S4" t="n">
-        <v>5.145055233092956</v>
+        <v>5.145208278300384</v>
       </c>
       <c r="T4" t="n">
-        <v>1212.495542377687</v>
+        <v>1212.495885991613</v>
       </c>
       <c r="U4" t="n">
-        <v>342.5043931325395</v>
+        <v>342.5044392784909</v>
       </c>
       <c r="V4" t="n">
-        <v>3441.499498108251</v>
+        <v>3441.446484351289</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -33938,13 +33938,13 @@
         <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>1743.724565844409</v>
+        <v>1743.860204104931</v>
       </c>
       <c r="D5" t="n">
-        <v>75.81411155845257</v>
+        <v>75.82000887412744</v>
       </c>
       <c r="E5" t="n">
-        <v>44.44957015873047</v>
+        <v>44.32861893835205</v>
       </c>
       <c r="F5" t="n">
         <v>90</v>
@@ -33953,7 +33953,7 @@
         <v>90</v>
       </c>
       <c r="H5" t="n">
-        <v>90.38583878407286</v>
+        <v>90.38671774873625</v>
       </c>
       <c r="I5" t="n">
         <v>23</v>
@@ -33962,40 +33962,40 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0.524419999914771</v>
+        <v>0.5250299591663564</v>
       </c>
       <c r="L5" t="n">
         <v>0.4291469644159489</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5354188632478978</v>
+        <v>0.5359316760554337</v>
       </c>
       <c r="N5" t="n">
-        <v>1.045496681217454</v>
+        <v>1.046307709461789</v>
       </c>
       <c r="O5" t="n">
         <v>0.6969826739866007</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9418599582144397</v>
+        <v>0.94214135157756</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.079560251300172</v>
+        <v>3.081200583634057</v>
       </c>
       <c r="R5" t="n">
-        <v>1.826709322356185</v>
+        <v>1.826709067861734</v>
       </c>
       <c r="S5" t="n">
-        <v>2.872185618463379</v>
+        <v>2.872993380997082</v>
       </c>
       <c r="T5" t="n">
-        <v>170.583291247855</v>
+        <v>170.5863734967965</v>
       </c>
       <c r="U5" t="n">
         <v>29.24307471368612</v>
       </c>
       <c r="V5" t="n">
-        <v>316.5362977191728</v>
+        <v>316.5165781005372</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -34013,10 +34013,10 @@
         <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>5014.723451629543</v>
+        <v>5013.267727949356</v>
       </c>
       <c r="D6" t="n">
-        <v>417.8936209691287</v>
+        <v>417.7723106624464</v>
       </c>
       <c r="E6" t="n">
         <v>222.10015232</v>
@@ -34028,7 +34028,7 @@
         <v>90</v>
       </c>
       <c r="H6" t="n">
-        <v>89.90427732292176</v>
+        <v>89.90429269611528</v>
       </c>
       <c r="I6" t="n">
         <v>12</v>
@@ -34037,40 +34037,40 @@
         <v>0.9230769230769231</v>
       </c>
       <c r="K6" t="n">
-        <v>2.085441423824022</v>
+        <v>2.085441443306362</v>
       </c>
       <c r="L6" t="n">
         <v>1.636445964659505</v>
       </c>
       <c r="M6" t="n">
-        <v>2.281875664553962</v>
+        <v>2.281304903154817</v>
       </c>
       <c r="N6" t="n">
-        <v>9.866339670633073</v>
+        <v>9.866339695541351</v>
       </c>
       <c r="O6" t="n">
         <v>6.492557117825493</v>
       </c>
       <c r="P6" t="n">
-        <v>9.034146321913454</v>
+        <v>9.031047844669759</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.041303729269953</v>
+        <v>7.041303587312576</v>
       </c>
       <c r="R6" t="n">
-        <v>4.640200401975354</v>
+        <v>4.640200214835365</v>
       </c>
       <c r="S6" t="n">
-        <v>9.769033846103149</v>
+        <v>9.769008771785794</v>
       </c>
       <c r="T6" t="n">
-        <v>322.4426107790827</v>
+        <v>322.4426269000737</v>
       </c>
       <c r="U6" t="n">
         <v>61.22083459916829</v>
       </c>
       <c r="V6" t="n">
-        <v>379.3916909247981</v>
+        <v>379.4897429697569</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -34088,13 +34088,13 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>1437.718676738964</v>
+        <v>1439.343470797963</v>
       </c>
       <c r="D7" t="n">
-        <v>89.85741729618529</v>
+        <v>89.9589669248727</v>
       </c>
       <c r="E7" t="n">
-        <v>47.84639226210962</v>
+        <v>47.83141062652979</v>
       </c>
       <c r="F7" t="n">
         <v>81.25</v>
@@ -34103,7 +34103,7 @@
         <v>85</v>
       </c>
       <c r="H7" t="n">
-        <v>86.70273510326517</v>
+        <v>86.71272313436916</v>
       </c>
       <c r="I7" t="n">
         <v>14</v>
@@ -34112,40 +34112,40 @@
         <v>0.875</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4232145995678311</v>
+        <v>0.4241544905033602</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2548084636932815</v>
+        <v>0.2623275911775139</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6762521832174013</v>
+        <v>0.6775082500770488</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7495488945640432</v>
+        <v>0.750717692673746</v>
       </c>
       <c r="O7" t="n">
         <v>0.6656460760473047</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9818509473286168</v>
+        <v>0.9834911289195825</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.957565191232618</v>
+        <v>6.968419777933658</v>
       </c>
       <c r="R7" t="n">
         <v>4.640039058392444</v>
       </c>
       <c r="S7" t="n">
-        <v>5.872398081293514</v>
+        <v>5.902101321151931</v>
       </c>
       <c r="T7" t="n">
-        <v>237.8075841962323</v>
+        <v>237.8166218046881</v>
       </c>
       <c r="U7" t="n">
-        <v>34.88661924107433</v>
+        <v>34.88661612216815</v>
       </c>
       <c r="V7" t="n">
-        <v>780.0038405480547</v>
+        <v>779.1188703669061</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -34205,22 +34205,22 @@
         <v>1.0788201480932</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9515702383921736</v>
+        <v>0.9515704509563081</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9515702383921736</v>
+        <v>0.9515704509563081</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9515702383921736</v>
+        <v>0.9515704509563081</v>
       </c>
       <c r="T8" t="n">
-        <v>15.09244272827345</v>
+        <v>15.09244612703106</v>
       </c>
       <c r="U8" t="n">
-        <v>15.09244272827345</v>
+        <v>15.09244612703106</v>
       </c>
       <c r="V8" t="n">
-        <v>28.6215291538807</v>
+        <v>28.62153559332627</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -34238,10 +34238,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>3418.641125649714</v>
+        <v>3419.30061880217</v>
       </c>
       <c r="D9" t="n">
-        <v>162.7924345547482</v>
+        <v>162.8238389905795</v>
       </c>
       <c r="E9" t="n">
         <v>59.800449024</v>
@@ -34253,7 +34253,7 @@
         <v>90</v>
       </c>
       <c r="H9" t="n">
-        <v>84.98310460624822</v>
+        <v>84.98385063664523</v>
       </c>
       <c r="I9" t="n">
         <v>18</v>
@@ -34262,40 +34262,40 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6895238720878772</v>
+        <v>0.6906311028357952</v>
       </c>
       <c r="L9" t="n">
         <v>0.715432420164215</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4077335834873281</v>
+        <v>0.4079288019388163</v>
       </c>
       <c r="N9" t="n">
-        <v>2.41782493037538</v>
+        <v>2.419290774368154</v>
       </c>
       <c r="O9" t="n">
         <v>1.706836703900194</v>
       </c>
       <c r="P9" t="n">
-        <v>1.569041657177997</v>
+        <v>1.569878634537791</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.727504759215474</v>
+        <v>7.73040742082023</v>
       </c>
       <c r="R9" t="n">
         <v>4.069713096474089</v>
       </c>
       <c r="S9" t="n">
-        <v>8.981479422665872</v>
+        <v>8.985310101263607</v>
       </c>
       <c r="T9" t="n">
-        <v>193.7907615894373</v>
+        <v>193.8019917872448</v>
       </c>
       <c r="U9" t="n">
-        <v>27.9857091435572</v>
+        <v>28.05972780837731</v>
       </c>
       <c r="V9" t="n">
-        <v>299.7320517619251</v>
+        <v>299.7077680455479</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -34313,10 +34313,10 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>457.9103843676648</v>
+        <v>459.2731376688748</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4775960919162</v>
+        <v>114.8182844172187</v>
       </c>
       <c r="E10" t="n">
         <v>93.312544768</v>
@@ -34328,7 +34328,7 @@
         <v>85</v>
       </c>
       <c r="H10" t="n">
-        <v>82.16304955080524</v>
+        <v>82.19611062981839</v>
       </c>
       <c r="I10" t="n">
         <v>3</v>
@@ -34337,40 +34337,40 @@
         <v>0.75</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2827561068874703</v>
+        <v>0.2896711774861441</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1990570789699753</v>
+        <v>0.2027634338522918</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1786390907786385</v>
+        <v>0.1840978318372211</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3918735267747355</v>
+        <v>0.4000813443636345</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2514972251648522</v>
+        <v>0.2555351926498626</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2439775045208215</v>
+        <v>0.2503109921639334</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.736449848047345</v>
+        <v>1.751699488812336</v>
       </c>
       <c r="R10" t="n">
-        <v>1.583224758108893</v>
+        <v>1.590654592751534</v>
       </c>
       <c r="S10" t="n">
-        <v>1.433856913132385</v>
+        <v>1.445138888411708</v>
       </c>
       <c r="T10" t="n">
-        <v>99.01113779157261</v>
+        <v>99.4133077924911</v>
       </c>
       <c r="U10" t="n">
-        <v>90.88650717537925</v>
+        <v>91.59880241807646</v>
       </c>
       <c r="V10" t="n">
-        <v>73.95240914437548</v>
+        <v>74.04381417646189</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -34421,31 +34421,31 @@
         <v>0.2104240623321379</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2554517734502176</v>
+        <v>0.2554517622187587</v>
       </c>
       <c r="O11" t="n">
         <v>0.271126232199195</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3812547189469704</v>
+        <v>0.3812547077211375</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.59556617701708</v>
+        <v>1.595566226742211</v>
       </c>
       <c r="R11" t="n">
         <v>0.7538460145065422</v>
       </c>
       <c r="S11" t="n">
-        <v>5.586681296087082</v>
+        <v>5.586681345787305</v>
       </c>
       <c r="T11" t="n">
-        <v>58.66870056545092</v>
+        <v>58.66871386862738</v>
       </c>
       <c r="U11" t="n">
         <v>7.999741000163517</v>
       </c>
       <c r="V11" t="n">
-        <v>224.4638314221594</v>
+        <v>224.4638976915245</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -34463,10 +34463,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>1299.188374256959</v>
+        <v>1299.0818115126</v>
       </c>
       <c r="D12" t="n">
-        <v>68.37833548720836</v>
+        <v>68.37272692171575</v>
       </c>
       <c r="E12" t="n">
         <v>48.991207424</v>
@@ -34478,7 +34478,7 @@
         <v>45</v>
       </c>
       <c r="H12" t="n">
-        <v>73.48306323363033</v>
+        <v>73.48211850761112</v>
       </c>
       <c r="I12" t="n">
         <v>6</v>
@@ -34487,40 +34487,40 @@
         <v>0.3157894736842105</v>
       </c>
       <c r="K12" t="n">
-        <v>0.01725367267990749</v>
+        <v>0.01732252769550747</v>
       </c>
       <c r="L12" t="n">
         <v>0.007728700033076352</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2200747605707781</v>
+        <v>0.220226955091362</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2785311513724499</v>
+        <v>0.2786224916923573</v>
       </c>
       <c r="O12" t="n">
         <v>0.2683822198137273</v>
       </c>
       <c r="P12" t="n">
-        <v>0.478917295530099</v>
+        <v>0.4791077617233327</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.502253432622155</v>
+        <v>2.502727370002547</v>
       </c>
       <c r="R12" t="n">
         <v>1.707184697640819</v>
       </c>
       <c r="S12" t="n">
-        <v>2.437306426660527</v>
+        <v>2.438133477407135</v>
       </c>
       <c r="T12" t="n">
-        <v>78.96965270239055</v>
+        <v>78.97005715364638</v>
       </c>
       <c r="U12" t="n">
-        <v>12.48362323482563</v>
+        <v>12.48362414231921</v>
       </c>
       <c r="V12" t="n">
-        <v>109.8082078552485</v>
+        <v>109.817614496382</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -34538,10 +34538,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>12685.54161682714</v>
+        <v>12685.54093695799</v>
       </c>
       <c r="D13" t="n">
-        <v>1057.128468068928</v>
+        <v>1057.128411413166</v>
       </c>
       <c r="E13" t="n">
         <v>317.37094144</v>
@@ -34553,7 +34553,7 @@
         <v>37.5</v>
       </c>
       <c r="H13" t="n">
-        <v>58.31035770814028</v>
+        <v>58.3103605430337</v>
       </c>
       <c r="I13" t="n">
         <v>5</v>
@@ -34562,40 +34562,40 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5225767052395507</v>
+        <v>0.5225767121599357</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.03581246546995354</v>
+        <v>-0.03581250767046662</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.004804572708692863</v>
+        <v>-0.004804531779251252</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6621414455354647</v>
+        <v>0.6621414658191354</v>
       </c>
       <c r="O13" t="n">
         <v>-0.01009155446892185</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3057360475117712</v>
+        <v>0.3057361345015824</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4601262831819526</v>
+        <v>0.4601262472819278</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4810858766784966</v>
+        <v>0.4810861069523608</v>
       </c>
       <c r="S13" t="n">
-        <v>0.998607411795945</v>
+        <v>0.9986074867662041</v>
       </c>
       <c r="T13" t="n">
-        <v>1054.446535018683</v>
+        <v>1054.446318349579</v>
       </c>
       <c r="U13" t="n">
         <v>12.08104166936328</v>
       </c>
       <c r="V13" t="n">
-        <v>2183.712998145644</v>
+        <v>2183.712268118117</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -34613,68 +34613,68 @@
         <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>2495.294233048468</v>
+        <v>2494.891548676084</v>
       </c>
       <c r="D14" t="n">
-        <v>249.5294233048468</v>
+        <v>249.4891548676084</v>
       </c>
       <c r="E14" t="n">
         <v>48.966023168</v>
       </c>
       <c r="F14" t="n">
-        <v>56.5</v>
+        <v>57</v>
       </c>
       <c r="G14" t="n">
         <v>67.5</v>
       </c>
       <c r="H14" t="n">
-        <v>9.359808240113924</v>
+        <v>9.362961451143317</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K14" t="n">
-        <v>0.08841510719490622</v>
+        <v>0.08795812714160237</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05109196076237577</v>
+        <v>0.04880699403802424</v>
       </c>
       <c r="M14" t="n">
-        <v>0.02623723423056696</v>
+        <v>0.02623851909213639</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3116200831395892</v>
+        <v>0.3111079784581177</v>
       </c>
       <c r="O14" t="n">
-        <v>0.04162442003483169</v>
+        <v>0.03701546680005374</v>
       </c>
       <c r="P14" t="n">
-        <v>0.1896245623310166</v>
+        <v>0.1897022064283781</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5139053519626562</v>
+        <v>0.5132817557789772</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3808381225296331</v>
+        <v>0.3808379815863328</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6705588568917787</v>
+        <v>0.6705196792520939</v>
       </c>
       <c r="T14" t="n">
-        <v>15.80825999533042</v>
+        <v>15.80647196612557</v>
       </c>
       <c r="U14" t="n">
-        <v>3.088962674346772</v>
+        <v>3.080007171342018</v>
       </c>
       <c r="V14" t="n">
-        <v>2.485188366723591</v>
+        <v>2.485251339849504</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Narrow momentum</t>
+          <t>Moderate breadth</t>
         </is>
       </c>
     </row>

--- a/company_radar_output.xlsx
+++ b/company_radar_output.xlsx
@@ -851,13 +851,13 @@
         <v>48.40296980201639</v>
       </c>
       <c r="AP2" t="n">
-        <v>24901800</v>
+        <v>24804700</v>
       </c>
       <c r="AQ2" t="n">
-        <v>18035690</v>
+        <v>18033748</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.380695720540772</v>
+        <v>1.375460054116316</v>
       </c>
       <c r="AS2" t="n">
         <v>-0.1432771718372023</v>
@@ -1066,13 +1066,13 @@
         <v>1.387044466912197</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.907303793290557</v>
+        <v>1.907303604068697</v>
       </c>
       <c r="AX3" t="n">
         <v>1.230366367712243</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.526158692287994</v>
+        <v>2.526157857232453</v>
       </c>
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
@@ -1241,13 +1241,13 @@
         <v>50.88631042013413</v>
       </c>
       <c r="AP4" t="n">
-        <v>48298100</v>
+        <v>48246400</v>
       </c>
       <c r="AQ4" t="n">
-        <v>51912624</v>
+        <v>51911590</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9303729281725386</v>
+        <v>0.9293955357560807</v>
       </c>
       <c r="AS4" t="n">
         <v>-0.02939767209789301</v>
@@ -1410,40 +1410,40 @@
         <v>370.8261206054688</v>
       </c>
       <c r="AG5" t="n">
-        <v>315.8090985870361</v>
+        <v>315.8090977478028</v>
       </c>
       <c r="AH5" t="n">
         <v>-0.02943729240414894</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.1396441878096149</v>
+        <v>0.1396441908381136</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.1742097433689678</v>
+        <v>0.1742097464893213</v>
       </c>
       <c r="AK5" t="n">
         <v>402.3796691894531</v>
       </c>
       <c r="AL5" t="n">
-        <v>173.8639984130859</v>
+        <v>173.864013671875</v>
       </c>
       <c r="AM5" t="n">
         <v>-0.1055462509149478</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.070066298642196</v>
+        <v>1.070066116967424</v>
       </c>
       <c r="AO5" t="n">
         <v>51.25972223020631</v>
       </c>
       <c r="AP5" t="n">
-        <v>25999300</v>
+        <v>25974800</v>
       </c>
       <c r="AQ5" t="n">
-        <v>33540342</v>
+        <v>33539852</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.7751650236601643</v>
+        <v>0.7744458741201362</v>
       </c>
       <c r="AS5" t="n">
         <v>0.003161607306750192</v>
@@ -1458,13 +1458,13 @@
         <v>1.020470022092596</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.963887400722065</v>
+        <v>1.963887586939176</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.1435142208057276</v>
+        <v>0.1435141099292949</v>
       </c>
       <c r="AY5" t="n">
-        <v>143.603700624549</v>
+        <v>143.6036867727892</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -1629,13 +1629,13 @@
         <v>50.98039124022075</v>
       </c>
       <c r="AP6" t="n">
-        <v>13301400</v>
+        <v>13258500</v>
       </c>
       <c r="AQ6" t="n">
-        <v>26933548</v>
+        <v>26932690</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.4938599251758439</v>
+        <v>0.4922827983391188</v>
       </c>
       <c r="AS6" t="n">
         <v>0.09788862731487957</v>
@@ -1825,13 +1825,13 @@
         <v>40.0199692887312</v>
       </c>
       <c r="AP7" t="n">
-        <v>32788100</v>
+        <v>32579500</v>
       </c>
       <c r="AQ7" t="n">
-        <v>30250030</v>
+        <v>30245858</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.083903057286224</v>
+        <v>1.077155754682178</v>
       </c>
       <c r="AS7" t="n">
         <v>-0.2630938202317127</v>
@@ -2015,13 +2015,13 @@
         <v>45.73855602962526</v>
       </c>
       <c r="AP8" t="n">
-        <v>3160300</v>
+        <v>3159300</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2604038</v>
+        <v>2604018</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.213615162297939</v>
+        <v>1.213240461471464</v>
       </c>
       <c r="AS8" t="n">
         <v>-0.1460656518981024</v>
@@ -2184,16 +2184,16 @@
         <v>604.8063073730468</v>
       </c>
       <c r="AG9" t="n">
-        <v>645.4064825439453</v>
+        <v>645.4064831542969</v>
       </c>
       <c r="AH9" t="n">
         <v>-0.03622032821405818</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.09684820314092024</v>
+        <v>-0.09684820399501781</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.06290636408061501</v>
+        <v>-0.0629063649668109</v>
       </c>
       <c r="AK9" t="n">
         <v>787.419189453125</v>
@@ -2211,13 +2211,13 @@
         <v>53.53899664596091</v>
       </c>
       <c r="AP9" t="n">
-        <v>21750500</v>
+        <v>21705900</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17884736</v>
+        <v>17883844</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.216148787435274</v>
+        <v>1.21371557479477</v>
       </c>
       <c r="AS9" t="n">
         <v>-0.06346869164290336</v>
@@ -2232,13 +2232,13 @@
         <v>-0.1804441077434721</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.7225262221136828</v>
+        <v>0.7225263774552615</v>
       </c>
       <c r="AX9" t="n">
         <v>-0.1021974190359378</v>
       </c>
       <c r="AY9" t="n">
-        <v>14.38108358286718</v>
+        <v>14.38108513111299</v>
       </c>
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
@@ -2380,16 +2380,16 @@
         <v>407.2164129638672</v>
       </c>
       <c r="AG10" t="n">
-        <v>443.7846463012695</v>
+        <v>443.784645690918</v>
       </c>
       <c r="AH10" t="n">
         <v>-0.0410750210379569</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.1200912571245528</v>
+        <v>-0.1200912559143855</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.08240085285099619</v>
+        <v>-0.08240085158899213</v>
       </c>
       <c r="AK10" t="n">
         <v>538.6585693359375</v>
@@ -2407,13 +2407,13 @@
         <v>50.06410542348838</v>
       </c>
       <c r="AP10" t="n">
-        <v>42194400</v>
+        <v>42128900</v>
       </c>
       <c r="AQ10" t="n">
-        <v>41453520</v>
+        <v>41452210</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01787254737354</v>
+        <v>1.016324581970419</v>
       </c>
       <c r="AS10" t="n">
         <v>-0.08623111906047509</v>
@@ -2428,13 +2428,13 @@
         <v>-0.1984991719137187</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.5353143296092888</v>
+        <v>0.5353142374997211</v>
       </c>
       <c r="AX10" t="n">
         <v>-0.1706581093930165</v>
       </c>
       <c r="AY10" t="n">
-        <v>6603.444968995992</v>
+        <v>6603.445801244294</v>
       </c>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
@@ -2576,16 +2576,16 @@
         <v>186.372600402832</v>
       </c>
       <c r="AG11" t="n">
-        <v>199.0704573059082</v>
+        <v>199.0704567718506</v>
       </c>
       <c r="AH11" t="n">
         <v>-0.2473678857875212</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.2953750839236261</v>
+        <v>-0.2953750820332889</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0.06378574236941437</v>
+        <v>-0.06378573985777924</v>
       </c>
       <c r="AK11" t="n">
         <v>325.7593383789062</v>
@@ -2603,13 +2603,13 @@
         <v>14.89667012187238</v>
       </c>
       <c r="AP11" t="n">
-        <v>44273600</v>
+        <v>44166700</v>
       </c>
       <c r="AQ11" t="n">
-        <v>27422878</v>
+        <v>27420740</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.614476788322509</v>
+        <v>1.610704160427472</v>
       </c>
       <c r="AS11" t="n">
         <v>-0.3910041976409659</v>
@@ -2621,16 +2621,16 @@
         <v>-0.2759119613371683</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.3839580958804084</v>
+        <v>-0.3839580545969761</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.9128473469272249</v>
+        <v>0.9128471479122096</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.278871825871825</v>
+        <v>-0.27887188244104</v>
       </c>
       <c r="AY11" t="n">
-        <v>2781.451170783875</v>
+        <v>2781.451787622791</v>
       </c>
       <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="n">
@@ -2759,7 +2759,7 @@
         <v>38154</v>
       </c>
       <c r="AD12" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AE12" t="n">
         <v>431.2000122070312</v>
@@ -2822,7 +2822,7 @@
         <v>-0.299801143307051</v>
       </c>
       <c r="AY12" t="n">
-        <v>612.1175422467029</v>
+        <v>612.1174902843525</v>
       </c>
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="n">
@@ -2987,13 +2987,13 @@
         <v>14.28570487774199</v>
       </c>
       <c r="AP13" t="n">
-        <v>11764200</v>
+        <v>11744600</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12128742</v>
+        <v>12128350</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.9699439562652087</v>
+        <v>0.9683592574422737</v>
       </c>
       <c r="AS13" t="n">
         <v>-0.2373009403500753</v>
@@ -3014,7 +3014,7 @@
         <v>-0.3770197493635609</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.08810543549217154</v>
+        <v>0.08810534153544447</v>
       </c>
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="n">
@@ -3183,13 +3183,13 @@
         <v>75.83420310261931</v>
       </c>
       <c r="AP14" t="n">
-        <v>10432200</v>
+        <v>10423900</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13094436</v>
+        <v>13094270</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.7966895252304108</v>
+        <v>0.796065760061462</v>
       </c>
       <c r="AS14" t="n">
         <v>0.03786733472437631</v>
@@ -3379,13 +3379,13 @@
         <v>68.26571628261831</v>
       </c>
       <c r="AP15" t="n">
-        <v>3037600</v>
+        <v>3036700</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6069526</v>
+        <v>6069508</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.5004674170602449</v>
+        <v>0.5003206190683001</v>
       </c>
       <c r="AS15" t="n">
         <v>0.04006704528879035</v>
@@ -3575,13 +3575,13 @@
         <v>84.31645102657885</v>
       </c>
       <c r="AP16" t="n">
-        <v>7699600</v>
+        <v>7697700</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8309084</v>
+        <v>8309046</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.9266484729243319</v>
+        <v>0.9264240443487736</v>
       </c>
       <c r="AS16" t="n">
         <v>0.2411653769181632</v>
@@ -3744,16 +3744,16 @@
         <v>408.8887963867188</v>
       </c>
       <c r="AG17" t="n">
-        <v>360.1986968994141</v>
+        <v>360.1986970520019</v>
       </c>
       <c r="AH17" t="n">
         <v>-0.1184644446307477</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.0006977129839182972</v>
+        <v>0.0006977125600013956</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.1351756680588476</v>
+        <v>0.135175667577963</v>
       </c>
       <c r="AK17" t="n">
         <v>480.8090515136719</v>
@@ -3771,13 +3771,13 @@
         <v>41.6450519969167</v>
       </c>
       <c r="AP17" t="n">
-        <v>26788900</v>
+        <v>26749500</v>
       </c>
       <c r="AQ17" t="n">
-        <v>27281432</v>
+        <v>27280644</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.9819462556071104</v>
+        <v>0.9805303716437193</v>
       </c>
       <c r="AS17" t="n">
         <v>-0.2466655334868972</v>
@@ -3792,13 +3792,13 @@
         <v>0.345279986806007</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.566255575012773</v>
+        <v>7.566256351612312</v>
       </c>
       <c r="AX17" t="n">
         <v>0.04072788759895696</v>
       </c>
       <c r="AY17" t="n">
-        <v>316.4116836894942</v>
+        <v>316.4117503304105</v>
       </c>
       <c r="AZ17" t="inlineStr"/>
       <c r="BA17" t="n">
@@ -3967,13 +3967,13 @@
         <v>63.28670403112168</v>
       </c>
       <c r="AP18" t="n">
-        <v>8095800</v>
+        <v>8093200</v>
       </c>
       <c r="AQ18" t="n">
-        <v>8931968</v>
+        <v>8931916</v>
       </c>
       <c r="AR18" t="n">
-        <v>0.9063847967211706</v>
+        <v>0.9060989825699212</v>
       </c>
       <c r="AS18" t="n">
         <v>0.07820787140523922</v>
@@ -4328,16 +4328,16 @@
         <v>254.9357025146484</v>
       </c>
       <c r="AG20" t="n">
-        <v>271.4952757263184</v>
+        <v>271.4952783966065</v>
       </c>
       <c r="AH20" t="n">
         <v>0.1356588589118319</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.06639052277846402</v>
+        <v>0.0663905122899946</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0.0609939645077392</v>
+        <v>-0.06099397374332027</v>
       </c>
       <c r="AK20" t="n">
         <v>329.2300109863281</v>
@@ -4355,13 +4355,13 @@
         <v>58.76238147144925</v>
       </c>
       <c r="AP20" t="n">
-        <v>5950200</v>
+        <v>5944100</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9762876</v>
+        <v>9762754</v>
       </c>
       <c r="AR20" t="n">
-        <v>0.6094720449179115</v>
+        <v>0.6088548374772118</v>
       </c>
       <c r="AS20" t="n">
         <v>-0.05271084517803704</v>
@@ -4373,16 +4373,16 @@
         <v>-0.009777814054530043</v>
       </c>
       <c r="AV20" t="n">
-        <v>0.03224386003643476</v>
+        <v>0.03224397235102461</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.507965878995356</v>
+        <v>1.507965050243282</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.006221993973904993</v>
+        <v>0.006221887250646319</v>
       </c>
       <c r="AY20" t="n">
-        <v>199.3961019018683</v>
+        <v>199.3959861553666</v>
       </c>
       <c r="AZ20" t="inlineStr"/>
       <c r="BA20" t="n">
@@ -4551,13 +4551,13 @@
         <v>50.1459359200975</v>
       </c>
       <c r="AP21" t="n">
-        <v>1612800</v>
+        <v>1612000</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2181198</v>
+        <v>2181182</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.7394101773429097</v>
+        <v>0.7390488276539968</v>
       </c>
       <c r="AS21" t="n">
         <v>-0.03649001459096823</v>
@@ -4685,7 +4685,7 @@
         </is>
       </c>
       <c r="X22" t="n">
-        <v>6079775744</v>
+        <v>6033352704</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>6079775744</v>
+        <v>6033352704</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
@@ -4933,13 +4933,13 @@
         <v>75.37064233238407</v>
       </c>
       <c r="AP23" t="n">
-        <v>2596200</v>
+        <v>2594500</v>
       </c>
       <c r="AQ23" t="n">
-        <v>4982552</v>
+        <v>4982518</v>
       </c>
       <c r="AR23" t="n">
-        <v>0.5210582849913057</v>
+        <v>0.5207206476725222</v>
       </c>
       <c r="AS23" t="n">
         <v>0.09645015393923639</v>
@@ -5102,40 +5102,40 @@
         <v>293.4565985107422</v>
       </c>
       <c r="AG24" t="n">
-        <v>270.3212226867676</v>
+        <v>270.3212237548828</v>
       </c>
       <c r="AH24" t="n">
         <v>0.05170579380076501</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.1417157773085205</v>
+        <v>0.1417157727972802</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.08558475577325475</v>
+        <v>0.08558475148380396</v>
       </c>
       <c r="AK24" t="n">
         <v>315.2000122070312</v>
       </c>
       <c r="AL24" t="n">
-        <v>201.5803070068359</v>
+        <v>201.5802917480469</v>
       </c>
       <c r="AM24" t="n">
         <v>-0.02084393105893478</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.5310523605480288</v>
+        <v>0.5310524764423199</v>
       </c>
       <c r="AO24" t="n">
         <v>58.29293135375314</v>
       </c>
       <c r="AP24" t="n">
-        <v>75400600</v>
+        <v>75352800</v>
       </c>
       <c r="AQ24" t="n">
-        <v>56524180</v>
+        <v>56523224</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.333953009136975</v>
+        <v>1.333129900728946</v>
       </c>
       <c r="AS24" t="n">
         <v>-0.005253673794582303</v>
@@ -5150,13 +5150,13 @@
         <v>0.4585500698253624</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.378665836238499</v>
+        <v>1.378665276766073</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.1409299223927112</v>
+        <v>0.1409297936775185</v>
       </c>
       <c r="AY24" t="n">
-        <v>3141.647344285259</v>
+        <v>3141.646629024458</v>
       </c>
       <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="n">
@@ -5517,13 +5517,13 @@
         <v>54.57120633420597</v>
       </c>
       <c r="AP26" t="n">
-        <v>28228900</v>
+        <v>28142500</v>
       </c>
       <c r="AQ26" t="n">
-        <v>37624848</v>
+        <v>37623120</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.7502727984442622</v>
+        <v>0.748010797615934</v>
       </c>
       <c r="AS26" t="n">
         <v>-0.0455282963168302</v>
@@ -5713,13 +5713,13 @@
         <v>45.42335820442248</v>
       </c>
       <c r="AP27" t="n">
-        <v>7576000</v>
+        <v>7553900</v>
       </c>
       <c r="AQ27" t="n">
-        <v>12236764</v>
+        <v>12236322</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.6191179301978856</v>
+        <v>0.6173341956839645</v>
       </c>
       <c r="AS27" t="n">
         <v>-0.2344413737245593</v>
@@ -5907,13 +5907,13 @@
         <v>51.85753391213613</v>
       </c>
       <c r="AP28" t="n">
-        <v>125021700</v>
+        <v>124577600</v>
       </c>
       <c r="AQ28" t="n">
-        <v>141752100</v>
+        <v>141743218</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.8819742353023341</v>
+        <v>0.8788963716062944</v>
       </c>
       <c r="AS28" t="n">
         <v>0.06778457503067226</v>
@@ -5928,13 +5928,13 @@
         <v>4.500457179629271</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.352237303679072</v>
+        <v>1.352237479057546</v>
       </c>
       <c r="AX28" t="n">
         <v>2.056119736156248</v>
       </c>
       <c r="AY28" t="n">
-        <v>662.08663313256</v>
+        <v>662.0861976164024</v>
       </c>
       <c r="AZ28" t="inlineStr"/>
       <c r="BA28" t="n">
@@ -6099,13 +6099,13 @@
         <v>62.40265095833276</v>
       </c>
       <c r="AP29" t="n">
-        <v>2832500</v>
+        <v>2832000</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4156372</v>
+        <v>4156362</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.6814837555444989</v>
+        <v>0.681365097650301</v>
       </c>
       <c r="AS29" t="n">
         <v>-0.0863829347231122</v>
@@ -6295,13 +6295,13 @@
         <v>40.41985540843898</v>
       </c>
       <c r="AP30" t="n">
-        <v>142385500</v>
+        <v>142068700</v>
       </c>
       <c r="AQ30" t="n">
-        <v>163785522</v>
+        <v>163779186</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.8693411863351389</v>
+        <v>0.8674405061458786</v>
       </c>
       <c r="AS30" t="n">
         <v>-0.09170162316524622</v>
@@ -6322,7 +6322,7 @@
         <v>0.03292362505629431</v>
       </c>
       <c r="AY30" t="n">
-        <v>5186.296244216904</v>
+        <v>5186.295215214715</v>
       </c>
       <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="n">
@@ -6464,16 +6464,16 @@
         <v>202.0392489624024</v>
       </c>
       <c r="AG31" t="n">
-        <v>166.9712875366211</v>
+        <v>166.9712877655029</v>
       </c>
       <c r="AH31" t="n">
         <v>-0.1276447477153387</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.05557070679798071</v>
+        <v>0.05557070535101971</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.2100239025712127</v>
+        <v>0.2100239009125295</v>
       </c>
       <c r="AK31" t="n">
         <v>250.0962829589844</v>
@@ -6491,13 +6491,13 @@
         <v>37.11777030562479</v>
       </c>
       <c r="AP31" t="n">
-        <v>18682500</v>
+        <v>18661200</v>
       </c>
       <c r="AQ31" t="n">
-        <v>26188184</v>
+        <v>26187758</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.7133942544469674</v>
+        <v>0.7125925021912911</v>
       </c>
       <c r="AS31" t="n">
         <v>-0.2924244145039175</v>
@@ -6518,7 +6518,7 @@
         <v>0.02923321291609837</v>
       </c>
       <c r="AY31" t="n">
-        <v>521.4038264825695</v>
+        <v>521.4035957528733</v>
       </c>
       <c r="AZ31" t="inlineStr"/>
       <c r="BA31" t="n">
@@ -6687,13 +6687,13 @@
         <v>59.79899623455247</v>
       </c>
       <c r="AP32" t="n">
-        <v>18423100</v>
+        <v>18385800</v>
       </c>
       <c r="AQ32" t="n">
-        <v>10855898</v>
+        <v>10855152</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.69705905490269</v>
+        <v>1.693739525710925</v>
       </c>
       <c r="AS32" t="n">
         <v>0.04911047586986528</v>
@@ -6708,13 +6708,13 @@
         <v>3.065048364712458</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.399912887237076</v>
+        <v>5.399913353698032</v>
       </c>
       <c r="AX32" t="n">
         <v>1.483392492060633</v>
       </c>
       <c r="AY32" t="n">
-        <v>39.36218043634423</v>
+        <v>39.36217579807088</v>
       </c>
       <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="n">
@@ -6867,13 +6867,13 @@
         <v>889.477294921875</v>
       </c>
       <c r="AL33" t="n">
-        <v>81.31228637695312</v>
+        <v>81.31227874755859</v>
       </c>
       <c r="AM33" t="n">
         <v>-0.06349492588996952</v>
       </c>
       <c r="AN33" t="n">
-        <v>9.244454277651485</v>
+        <v>9.244455238871423</v>
       </c>
       <c r="AO33" t="n">
         <v>70.49237362621658</v>
@@ -6897,7 +6897,7 @@
         <v>4.794625146055814</v>
       </c>
       <c r="AV33" t="n">
-        <v>9.244454277651485</v>
+        <v>9.244455238871423</v>
       </c>
       <c r="AW33" t="n">
         <v>7.57785412106025</v>
@@ -6906,7 +6906,7 @@
         <v>4.348884750205366</v>
       </c>
       <c r="AY33" t="n">
-        <v>35.45216580742827</v>
+        <v>35.45216276492034</v>
       </c>
       <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="n">
@@ -7044,28 +7044,28 @@
         <v>4729.92</v>
       </c>
       <c r="AG34" t="n">
-        <v>4499.441394042969</v>
+        <v>4499.441391601563</v>
       </c>
       <c r="AH34" t="n">
         <v>0.1232748122589811</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.1808132465141432</v>
+        <v>0.1808132471548547</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.05122382664260794</v>
+        <v>0.05122382721300411</v>
       </c>
       <c r="AK34" t="n">
         <v>5784.6318359375</v>
       </c>
       <c r="AL34" t="n">
-        <v>3659.134765625</v>
+        <v>3659.135009765625</v>
       </c>
       <c r="AM34" t="n">
         <v>-0.08153186742282348</v>
       </c>
       <c r="AN34" t="n">
-        <v>0.4519825970641753</v>
+        <v>0.4519825001866515</v>
       </c>
       <c r="AO34" t="n">
         <v>81.93366266760762</v>
@@ -7089,7 +7089,7 @@
         <v>0.1082138211405299</v>
       </c>
       <c r="AV34" t="n">
-        <v>0.4519825970641753</v>
+        <v>0.4519825001866515</v>
       </c>
       <c r="AW34" t="n">
         <v>2.075710912078704</v>
@@ -7098,7 +7098,7 @@
         <v>0.1476909744709201</v>
       </c>
       <c r="AY34" t="n">
-        <v>3.554787460987867</v>
+        <v>3.554785077701381</v>
       </c>
       <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
@@ -7240,16 +7240,16 @@
         <v>75.22947402954101</v>
       </c>
       <c r="AG35" t="n">
-        <v>50.30421349525452</v>
+        <v>50.30421326637268</v>
       </c>
       <c r="AH35" t="n">
         <v>-0.07416604430161455</v>
       </c>
       <c r="AI35" t="n">
-        <v>0.384575897055808</v>
+        <v>0.3845759033555642</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0.4954905126712266</v>
+        <v>0.4954905194756392</v>
       </c>
       <c r="AK35" t="n">
         <v>93.55000305175781</v>
@@ -7267,13 +7267,13 @@
         <v>44.78163251855959</v>
       </c>
       <c r="AP35" t="n">
-        <v>6995500</v>
+        <v>6962100</v>
       </c>
       <c r="AQ35" t="n">
-        <v>5805802</v>
+        <v>5805134</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.204915358808309</v>
+        <v>1.199300481263654</v>
       </c>
       <c r="AS35" t="n">
         <v>-0.07380313361160329</v>
@@ -7285,16 +7285,16 @@
         <v>0.7695539298593599</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.150252310669514</v>
+        <v>2.150252038900717</v>
       </c>
       <c r="AW35" t="n">
-        <v>2.15573253394624</v>
+        <v>2.155732806661452</v>
       </c>
       <c r="AX35" t="n">
         <v>0.627725753939528</v>
       </c>
       <c r="AY35" t="n">
-        <v>4.631299937636747</v>
+        <v>4.631299503430325</v>
       </c>
       <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="n">
@@ -7480,13 +7480,13 @@
         <v>8.809188768126631</v>
       </c>
       <c r="AW36" t="n">
-        <v>8.60531955788632</v>
+        <v>8.605318831462796</v>
       </c>
       <c r="AX36" t="n">
         <v>3.424657534246576</v>
       </c>
       <c r="AY36" t="n">
-        <v>131.8419232718276</v>
+        <v>131.841914587892</v>
       </c>
       <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="n">
@@ -7624,16 +7624,16 @@
         <v>19194.6</v>
       </c>
       <c r="AG37" t="n">
-        <v>9944.236700439453</v>
+        <v>9944.236696777343</v>
       </c>
       <c r="AH37" t="n">
         <v>0.2162274806455984</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.347590941692724</v>
+        <v>1.347590942557258</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.93022356347891</v>
+        <v>0.9302235641897429</v>
       </c>
       <c r="AK37" t="n">
         <v>26425</v>
@@ -7672,13 +7672,13 @@
         <v>7.050092846066804</v>
       </c>
       <c r="AW37" t="n">
-        <v>9.739330568603943</v>
+        <v>9.739329362456095</v>
       </c>
       <c r="AX37" t="n">
         <v>2.267312882239865</v>
       </c>
       <c r="AY37" t="n">
-        <v>32.72988470878067</v>
+        <v>32.72988173426776</v>
       </c>
       <c r="AZ37" t="inlineStr"/>
       <c r="BA37" t="n">
@@ -7864,7 +7864,7 @@
         <v>10.06557423182312</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.5792782421732</v>
+        <v>4.579277655777138</v>
       </c>
       <c r="AX38" t="n">
         <v>5.173780631409171</v>
@@ -8035,13 +8035,13 @@
         <v>29.57746531061807</v>
       </c>
       <c r="AP39" t="n">
-        <v>24641100</v>
+        <v>24591700</v>
       </c>
       <c r="AQ39" t="n">
-        <v>22745006</v>
+        <v>22744018</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.083363090781335</v>
+        <v>1.081238152379232</v>
       </c>
       <c r="AS39" t="n">
         <v>-0.2605680597123423</v>
@@ -8250,13 +8250,13 @@
         <v>0.2888253521148874</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.4112061508526457</v>
+        <v>0.4112062721592988</v>
       </c>
       <c r="AX40" t="n">
         <v>0.3250242896831437</v>
       </c>
       <c r="AY40" t="n">
-        <v>2.243856157150545</v>
+        <v>2.243855836673594</v>
       </c>
       <c r="AZ40" t="inlineStr"/>
       <c r="BA40" t="n">
@@ -8446,13 +8446,13 @@
         <v>0.2162630355228989</v>
       </c>
       <c r="AW41" t="n">
-        <v>2.298556328120133</v>
+        <v>2.298556682385386</v>
       </c>
       <c r="AX41" t="n">
         <v>0.4286727297169941</v>
       </c>
       <c r="AY41" t="n">
-        <v>100.686580685693</v>
+        <v>100.68657016467</v>
       </c>
       <c r="AZ41" t="inlineStr"/>
       <c r="BA41" t="n">
@@ -8644,7 +8644,7 @@
         <v>0.028236006560447</v>
       </c>
       <c r="AY42" t="n">
-        <v>3.029904063720521</v>
+        <v>3.029903633504128</v>
       </c>
       <c r="AZ42" t="inlineStr"/>
       <c r="BA42" t="n">
@@ -8782,16 +8782,16 @@
         <v>2664.9</v>
       </c>
       <c r="AG43" t="n">
-        <v>2593.725723876953</v>
+        <v>2593.725720214844</v>
       </c>
       <c r="AH43" t="n">
         <v>0.01410934744268078</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.04193746282488853</v>
+        <v>0.04193746429601131</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.02744094160297705</v>
+        <v>0.02744094305363198</v>
       </c>
       <c r="AK43" t="n">
         <v>2780</v>
@@ -8830,13 +8830,13 @@
         <v>0.1543973501121187</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.8713527801011207</v>
+        <v>0.8713529382826333</v>
       </c>
       <c r="AX43" t="n">
         <v>0.00339885699202247</v>
       </c>
       <c r="AY43" t="n">
-        <v>3.130110278963514</v>
+        <v>3.130112590438231</v>
       </c>
       <c r="AZ43" t="inlineStr"/>
       <c r="BA43" t="n">
@@ -9416,7 +9416,7 @@
         <v>-0.0684873374028192</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.5884235715454689</v>
+        <v>0.5884226492495777</v>
       </c>
       <c r="AZ46" t="inlineStr"/>
       <c r="BA46" t="n">
@@ -9910,40 +9910,40 @@
         <v>65.47655090332032</v>
       </c>
       <c r="AG49" t="n">
-        <v>61.19086206436157</v>
+        <v>61.19086208343506</v>
       </c>
       <c r="AH49" t="n">
         <v>0.0652668632926261</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.1398760802983259</v>
+        <v>0.1398760799430212</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.07003805297678234</v>
+        <v>0.07003805264324647</v>
       </c>
       <c r="AK49" t="n">
         <v>69.75</v>
       </c>
       <c r="AL49" t="n">
-        <v>53.93784332275391</v>
+        <v>53.93783950805664</v>
       </c>
       <c r="AM49" t="n">
         <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>0.2931551523598954</v>
+        <v>0.2931552438169407</v>
       </c>
       <c r="AO49" t="n">
         <v>68.65849392254501</v>
       </c>
       <c r="AP49" t="n">
-        <v>4304400</v>
+        <v>4301400</v>
       </c>
       <c r="AQ49" t="n">
-        <v>7573848</v>
+        <v>7573788</v>
       </c>
       <c r="AR49" t="n">
-        <v>0.5683240540343562</v>
+        <v>0.567932453350952</v>
       </c>
       <c r="AS49" t="n">
         <v>0.06553622021887473</v>
@@ -9958,13 +9958,13 @@
         <v>0.2683822198137273</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.1606241717611732</v>
+        <v>0.1606246137899099</v>
       </c>
       <c r="AX49" t="n">
         <v>0.2018768282491283</v>
       </c>
       <c r="AY49" t="n">
-        <v>187.7447607159686</v>
+        <v>187.7447150516632</v>
       </c>
       <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
@@ -10106,40 +10106,40 @@
         <v>112.1158570861816</v>
       </c>
       <c r="AG50" t="n">
-        <v>101.2313223648071</v>
+        <v>101.231322593689</v>
       </c>
       <c r="AH50" t="n">
         <v>0.02670579882262669</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.1370986560417522</v>
+        <v>0.1370986534707967</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.1075214120205792</v>
+        <v>0.1075214095164974</v>
       </c>
       <c r="AK50" t="n">
         <v>117.3600006103516</v>
       </c>
       <c r="AL50" t="n">
-        <v>78.91035461425781</v>
+        <v>78.91036224365234</v>
       </c>
       <c r="AM50" t="n">
         <v>-0.019171779041398</v>
       </c>
       <c r="AN50" t="n">
-        <v>0.4587439274991303</v>
+        <v>0.458743786461469</v>
       </c>
       <c r="AO50" t="n">
         <v>67.08115719150381</v>
       </c>
       <c r="AP50" t="n">
-        <v>2726900</v>
+        <v>2726400</v>
       </c>
       <c r="AQ50" t="n">
-        <v>3770060</v>
+        <v>3770050</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.7233041383956754</v>
+        <v>0.723173432713094</v>
       </c>
       <c r="AS50" t="n">
         <v>0.05935943982018621</v>
@@ -10148,19 +10148,19 @@
         <v>0.007295158076668695</v>
       </c>
       <c r="AU50" t="n">
-        <v>0.26040603463212</v>
+        <v>0.2604061399247568</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.4517479007784346</v>
+        <v>0.4517480404665546</v>
       </c>
       <c r="AW50" t="n">
-        <v>1.707184697640819</v>
+        <v>1.707184940515831</v>
       </c>
       <c r="AX50" t="n">
         <v>0.2412032442714338</v>
       </c>
       <c r="AY50" t="n">
-        <v>213.1717161747428</v>
+        <v>213.1716449202273</v>
       </c>
       <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
@@ -10302,40 +10302,40 @@
         <v>1041.696948242188</v>
       </c>
       <c r="AG51" t="n">
-        <v>793.7075711059571</v>
+        <v>793.7075692749023</v>
       </c>
       <c r="AH51" t="n">
         <v>0.06855452272360107</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.4024182531112159</v>
+        <v>0.4024182563465444</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.3124442630560782</v>
+        <v>0.3124442660838398</v>
       </c>
       <c r="AK51" t="n">
         <v>1174.859985351562</v>
       </c>
       <c r="AL51" t="n">
-        <v>503.7064819335938</v>
+        <v>503.7064514160156</v>
       </c>
       <c r="AM51" t="n">
         <v>-0.05255945454770261</v>
       </c>
       <c r="AN51" t="n">
-        <v>1.209838517619691</v>
+        <v>1.209838651505051</v>
       </c>
       <c r="AO51" t="n">
         <v>67.34457920145803</v>
       </c>
       <c r="AP51" t="n">
-        <v>2363000</v>
+        <v>2360300</v>
       </c>
       <c r="AQ51" t="n">
-        <v>2911592</v>
+        <v>2911538</v>
       </c>
       <c r="AR51" t="n">
-        <v>0.8115834910935323</v>
+        <v>0.810671198521194</v>
       </c>
       <c r="AS51" t="n">
         <v>0.1608559243346663</v>
@@ -10344,17 +10344,17 @@
         <v>0.2393900990658835</v>
       </c>
       <c r="AU51" t="n">
-        <v>0.7062787902830061</v>
+        <v>0.7062789499231121</v>
       </c>
       <c r="AV51" t="n">
-        <v>1.209838517619691</v>
+        <v>1.209838651505051</v>
       </c>
       <c r="AW51" t="inlineStr"/>
       <c r="AX51" t="n">
-        <v>0.6410457373307343</v>
+        <v>0.6410458849977139</v>
       </c>
       <c r="AY51" t="n">
-        <v>7.516675627130299</v>
+        <v>7.516676621441324</v>
       </c>
       <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="n">
@@ -10496,16 +10496,16 @@
         <v>93.50025115966797</v>
       </c>
       <c r="AG52" t="n">
-        <v>91.52396572113037</v>
+        <v>91.52396564483642</v>
       </c>
       <c r="AH52" t="n">
         <v>0.04791165950576604</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.0705393126809486</v>
+        <v>0.07053931357334497</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.02159309228972073</v>
+        <v>0.02159309314131574</v>
       </c>
       <c r="AK52" t="n">
         <v>98.29612731933594</v>
@@ -10523,13 +10523,13 @@
         <v>68.52873416946491</v>
       </c>
       <c r="AP52" t="n">
-        <v>5282700</v>
+        <v>5279800</v>
       </c>
       <c r="AQ52" t="n">
-        <v>6147018</v>
+        <v>6146960</v>
       </c>
       <c r="AR52" t="n">
-        <v>0.8593923102226153</v>
+        <v>0.8589286411494462</v>
       </c>
       <c r="AS52" t="n">
         <v>0.08277163962850431</v>
@@ -10541,7 +10541,7 @@
         <v>0.1418262519742559</v>
       </c>
       <c r="AV52" t="n">
-        <v>0.1100637327182925</v>
+        <v>0.1100638286690681</v>
       </c>
       <c r="AW52" t="n">
         <v>0.9152707092443282</v>
@@ -10692,28 +10692,28 @@
         <v>14.54532102584839</v>
       </c>
       <c r="AG53" t="n">
-        <v>14.17657376766205</v>
+        <v>14.17657375812531</v>
       </c>
       <c r="AH53" t="n">
         <v>0.002384196113378367</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.02845723957394086</v>
+        <v>0.02845724026579588</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.02601102806853661</v>
+        <v>0.02601102875874606</v>
       </c>
       <c r="AK53" t="n">
         <v>17.06953239440918</v>
       </c>
       <c r="AL53" t="n">
-        <v>10.52870750427246</v>
+        <v>10.52870655059814</v>
       </c>
       <c r="AM53" t="n">
         <v>-0.1458465535657278</v>
       </c>
       <c r="AN53" t="n">
-        <v>0.384785351648302</v>
+        <v>0.3847854770800647</v>
       </c>
       <c r="AO53" t="n">
         <v>37.83784480403326</v>
@@ -10737,16 +10737,16 @@
         <v>0.04146013598854292</v>
       </c>
       <c r="AV53" t="n">
-        <v>0.3773201036505531</v>
+        <v>0.3773202277335794</v>
       </c>
       <c r="AW53" t="n">
-        <v>-0.3234069065236225</v>
+        <v>-0.3234067867509463</v>
       </c>
       <c r="AX53" t="n">
         <v>0.007728700033076352</v>
       </c>
       <c r="AY53" t="n">
-        <v>6.306201255638213</v>
+        <v>6.306200382735619</v>
       </c>
       <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
@@ -10881,19 +10881,19 @@
         <v>168.1199951171875</v>
       </c>
       <c r="AF54" t="n">
-        <v>167.9943994140625</v>
+        <v>167.6051992797852</v>
       </c>
       <c r="AG54" t="n">
-        <v>139.2220529937744</v>
+        <v>139.5705495834351</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.000747618394202787</v>
+        <v>0.003071478925561255</v>
       </c>
       <c r="AI54" t="n">
-        <v>0.2075672747384736</v>
+        <v>0.2045520750542409</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.2066651496769316</v>
+        <v>0.2008636476679562</v>
       </c>
       <c r="AK54" t="n">
         <v>187.6199951171875</v>
@@ -10908,31 +10908,31 @@
         <v>1.000437565169522</v>
       </c>
       <c r="AO54" t="n">
-        <v>63.67054448734005</v>
+        <v>60.74260321749072</v>
       </c>
       <c r="AP54" t="n">
         <v>1393958</v>
       </c>
       <c r="AQ54" t="n">
-        <v>2614371.02</v>
+        <v>2604089.36</v>
       </c>
       <c r="AR54" t="n">
-        <v>0.5331905798129601</v>
+        <v>0.5352957626615394</v>
       </c>
       <c r="AS54" t="n">
-        <v>0.0541760698590017</v>
+        <v>0.06391590033950378</v>
       </c>
       <c r="AT54" t="n">
-        <v>0.1230460824612702</v>
+        <v>0.1379449632209904</v>
       </c>
       <c r="AU54" t="n">
-        <v>0.3236920972439701</v>
+        <v>0.3262915812373623</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.8240809078558617</v>
+        <v>0.7783539603111418</v>
       </c>
       <c r="AW54" t="n">
-        <v>6.466251585481487</v>
+        <v>6.449863297500273</v>
       </c>
       <c r="AX54" t="n">
         <v>0.3748935175898367</v>
@@ -11080,16 +11080,16 @@
         <v>124.7349671936035</v>
       </c>
       <c r="AG55" t="n">
-        <v>122.6580275726318</v>
+        <v>122.6580275344849</v>
       </c>
       <c r="AH55" t="n">
         <v>0.03900300789241395</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.05659620220758166</v>
+        <v>0.05659620253618591</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.0169327655276521</v>
+        <v>0.01693276584392112</v>
       </c>
       <c r="AK55" t="n">
         <v>132.3166198730469</v>
@@ -11122,19 +11122,19 @@
         <v>-0.0113453335045216</v>
       </c>
       <c r="AU55" t="n">
-        <v>0.1247611189044187</v>
+        <v>0.1247611933785884</v>
       </c>
       <c r="AV55" t="n">
-        <v>0.1458119115270744</v>
+        <v>0.1458119888150171</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.5765103381237029</v>
+        <v>0.5765101918121374</v>
       </c>
       <c r="AX55" t="n">
         <v>0.1225583250916018</v>
       </c>
       <c r="AY55" t="n">
-        <v>174.0547564371849</v>
+        <v>174.0547846244525</v>
       </c>
       <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="n">
@@ -11276,16 +11276,16 @@
         <v>45.48177169799805</v>
       </c>
       <c r="AG56" t="n">
-        <v>45.33060731887817</v>
+        <v>45.33060741424561</v>
       </c>
       <c r="AH56" t="n">
         <v>0.05272946238861542</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.0562400086833903</v>
+        <v>0.0562400064612516</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.003334708887893667</v>
+        <v>0.003334706777058161</v>
       </c>
       <c r="AK56" t="n">
         <v>49.82146072387695</v>
@@ -11303,13 +11303,13 @@
         <v>66.76096387102345</v>
       </c>
       <c r="AP56" t="n">
-        <v>12710100</v>
+        <v>12709500</v>
       </c>
       <c r="AQ56" t="n">
-        <v>8699858</v>
+        <v>8699846</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.460954879953213</v>
+        <v>1.460887928361031</v>
       </c>
       <c r="AS56" t="n">
         <v>0.07210024948425575</v>
@@ -11321,16 +11321,16 @@
         <v>0.1182408395509522</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.1558150972839467</v>
+        <v>0.1558149908494006</v>
       </c>
       <c r="AW56" t="n">
-        <v>0.7941663618366874</v>
+        <v>0.7941666183036384</v>
       </c>
       <c r="AX56" t="n">
         <v>0.1098387516070902</v>
       </c>
       <c r="AY56" t="n">
-        <v>194.2717528834614</v>
+        <v>194.2716342124765</v>
       </c>
       <c r="AZ56" t="inlineStr"/>
       <c r="BA56" t="n">
@@ -11499,13 +11499,13 @@
         <v>66.79462867100609</v>
       </c>
       <c r="AP57" t="n">
-        <v>14283600</v>
+        <v>14281800</v>
       </c>
       <c r="AQ57" t="n">
-        <v>12075652</v>
+        <v>12075616</v>
       </c>
       <c r="AR57" t="n">
-        <v>1.182842963675999</v>
+        <v>1.18269742926572</v>
       </c>
       <c r="AS57" t="n">
         <v>0.05210495044233032</v>
@@ -11526,7 +11526,7 @@
         <v>0.1070531241894106</v>
       </c>
       <c r="AY57" t="n">
-        <v>253.2130941854791</v>
+        <v>253.2129415743012</v>
       </c>
       <c r="AZ57" t="inlineStr"/>
       <c r="BA57" t="n">
@@ -11691,13 +11691,13 @@
         <v>45.73833492870085</v>
       </c>
       <c r="AP58" t="n">
-        <v>3810900</v>
+        <v>3809400</v>
       </c>
       <c r="AQ58" t="n">
-        <v>3234044</v>
+        <v>3234014</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.178369867571375</v>
+        <v>1.177916978714378</v>
       </c>
       <c r="AS58" t="n">
         <v>-0.1572974600828685</v>
@@ -11718,7 +11718,7 @@
         <v>-0.02049509631801205</v>
       </c>
       <c r="AY58" t="n">
-        <v>15.13440437503716</v>
+        <v>15.1343992318951</v>
       </c>
       <c r="AZ58" t="inlineStr"/>
       <c r="BA58" t="n">
@@ -12046,40 +12046,40 @@
         <v>202.3799096679687</v>
       </c>
       <c r="AG60" t="n">
-        <v>197.732170715332</v>
+        <v>197.7321705627441</v>
       </c>
       <c r="AH60" t="n">
         <v>-0.05593397154859303</v>
       </c>
       <c r="AI60" t="n">
-        <v>-0.03374348813650541</v>
+        <v>-0.0337434873908552</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.02350522393914289</v>
+        <v>0.02350522472897154</v>
       </c>
       <c r="AK60" t="n">
         <v>238.1012115478516</v>
       </c>
       <c r="AL60" t="n">
-        <v>135.6905517578125</v>
+        <v>135.6905670166016</v>
       </c>
       <c r="AM60" t="n">
         <v>-0.1975681420663576</v>
       </c>
       <c r="AN60" t="n">
-        <v>0.4080567518039686</v>
+        <v>0.4080565934639937</v>
       </c>
       <c r="AO60" t="n">
         <v>46.19108169811867</v>
       </c>
       <c r="AP60" t="n">
-        <v>587500</v>
+        <v>586700</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1036810</v>
+        <v>1036794</v>
       </c>
       <c r="AR60" t="n">
-        <v>0.566641911246998</v>
+        <v>0.5658790463679381</v>
       </c>
       <c r="AS60" t="n">
         <v>0.03432219735812803</v>
@@ -12091,16 +12091,16 @@
         <v>0.1084229842021078</v>
       </c>
       <c r="AV60" t="n">
-        <v>0.3648454713773188</v>
+        <v>0.3648456201479875</v>
       </c>
       <c r="AW60" t="n">
-        <v>2.412546748982577</v>
+        <v>2.412547446522185</v>
       </c>
       <c r="AX60" t="n">
         <v>0.05350470796736562</v>
       </c>
       <c r="AY60" t="n">
-        <v>12.48362414231921</v>
+        <v>12.48361960485249</v>
       </c>
       <c r="AZ60" t="inlineStr"/>
       <c r="BA60" t="n">
@@ -12265,13 +12265,13 @@
         <v>47.90209965097517</v>
       </c>
       <c r="AP61" t="n">
-        <v>4446000</v>
+        <v>4445200</v>
       </c>
       <c r="AQ61" t="n">
-        <v>6176902</v>
+        <v>6176886</v>
       </c>
       <c r="AR61" t="n">
-        <v>0.7197782966283098</v>
+        <v>0.7196506459727442</v>
       </c>
       <c r="AS61" t="n">
         <v>-0.1507936521285439</v>
@@ -12457,13 +12457,13 @@
         <v>39.08729696189509</v>
       </c>
       <c r="AP62" t="n">
-        <v>9675600</v>
+        <v>9657200</v>
       </c>
       <c r="AQ62" t="n">
-        <v>14044122</v>
+        <v>14043754</v>
       </c>
       <c r="AR62" t="n">
-        <v>0.6889430325370287</v>
+        <v>0.6876508944830563</v>
       </c>
       <c r="AS62" t="n">
         <v>-0.1970556456759841</v>
@@ -12622,16 +12622,16 @@
         <v>154.2383877563477</v>
       </c>
       <c r="AG63" t="n">
-        <v>168.1289860534668</v>
+        <v>168.1289859008789</v>
       </c>
       <c r="AH63" t="n">
         <v>-0.02067179741029568</v>
       </c>
       <c r="AI63" t="n">
-        <v>-0.101582620597484</v>
+        <v>-0.1015826197821124</v>
       </c>
       <c r="AJ63" t="n">
-        <v>-0.08261870022044726</v>
+        <v>-0.0826186993878647</v>
       </c>
       <c r="AK63" t="n">
         <v>217.0162200927734</v>
@@ -12649,13 +12649,13 @@
         <v>55.07202843033653</v>
       </c>
       <c r="AP63" t="n">
-        <v>4255900</v>
+        <v>4254100</v>
       </c>
       <c r="AQ63" t="n">
-        <v>4945764</v>
+        <v>4945728</v>
       </c>
       <c r="AR63" t="n">
-        <v>0.8605141692972006</v>
+        <v>0.8601564825239075</v>
       </c>
       <c r="AS63" t="n">
         <v>-0.0165049549737063</v>
@@ -12667,16 +12667,16 @@
         <v>-0.06113012500101955</v>
       </c>
       <c r="AV63" t="n">
-        <v>-0.1880956335346442</v>
+        <v>-0.1880957001246495</v>
       </c>
       <c r="AW63" t="n">
-        <v>8.010621545653805</v>
+        <v>8.010618469982299</v>
       </c>
       <c r="AX63" t="n">
         <v>-0.08329068135345574</v>
       </c>
       <c r="AY63" t="n">
-        <v>12.32288457999127</v>
+        <v>12.32288682132202</v>
       </c>
       <c r="AZ63" t="inlineStr"/>
       <c r="BA63" t="n">
@@ -12818,25 +12818,25 @@
         <v>278.6736727905273</v>
       </c>
       <c r="AG64" t="n">
-        <v>316.0922017669678</v>
+        <v>316.0922011566162</v>
       </c>
       <c r="AH64" t="n">
         <v>-0.1414689532590372</v>
       </c>
       <c r="AI64" t="n">
-        <v>-0.2431005932364572</v>
+        <v>-0.2431005917749383</v>
       </c>
       <c r="AJ64" t="n">
-        <v>-0.11837852616189</v>
+        <v>-0.1183785244595418</v>
       </c>
       <c r="AK64" t="n">
-        <v>402.3219604492188</v>
+        <v>402.3219299316406</v>
       </c>
       <c r="AL64" t="n">
         <v>236.5</v>
       </c>
       <c r="AM64" t="n">
-        <v>-0.4053270178618593</v>
+        <v>-0.405326972753756</v>
       </c>
       <c r="AN64" t="n">
         <v>0.01162790697674421</v>
@@ -12845,13 +12845,13 @@
         <v>44.93893479525159</v>
       </c>
       <c r="AP64" t="n">
-        <v>4271000</v>
+        <v>4267000</v>
       </c>
       <c r="AQ64" t="n">
-        <v>3882544</v>
+        <v>3882464</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.100051924717402</v>
+        <v>1.099044318247381</v>
       </c>
       <c r="AS64" t="n">
         <v>-0.1047372820580752</v>
@@ -12870,7 +12870,7 @@
         <v>-0.3448660178010061</v>
       </c>
       <c r="AY64" t="n">
-        <v>4.90855385306439</v>
+        <v>4.90855329642942</v>
       </c>
       <c r="AZ64" t="inlineStr"/>
       <c r="BA64" t="n">
@@ -13012,16 +13012,16 @@
         <v>139.1372401428223</v>
       </c>
       <c r="AG65" t="n">
-        <v>155.3622074508667</v>
+        <v>155.3622075271606</v>
       </c>
       <c r="AH65" t="n">
         <v>-0.01751682865118132</v>
       </c>
       <c r="AI65" t="n">
-        <v>-0.1201206574547831</v>
+        <v>-0.1201206578868668</v>
       </c>
       <c r="AJ65" t="n">
-        <v>-0.104433166690011</v>
+        <v>-0.1044331671297983</v>
       </c>
       <c r="AK65" t="n">
         <v>183.4681396484375</v>
@@ -13060,13 +13060,13 @@
         <v>-0.1110736815617641</v>
       </c>
       <c r="AW65" t="n">
-        <v>3.067549656395868</v>
+        <v>3.067549194698657</v>
       </c>
       <c r="AX65" t="n">
-        <v>-0.1722033776148241</v>
+        <v>-0.1722034541037961</v>
       </c>
       <c r="AY65" t="n">
-        <v>18.08119178496317</v>
+        <v>18.08119432501531</v>
       </c>
       <c r="AZ65" t="inlineStr"/>
       <c r="BA65" t="n">
@@ -13195,7 +13195,7 @@
         <v>35999</v>
       </c>
       <c r="AD66" t="n">
-        <v>27.9</v>
+        <v>28</v>
       </c>
       <c r="AE66" t="n">
         <v>162.1300048828125</v>
@@ -13231,13 +13231,13 @@
         <v>51.73245606641598</v>
       </c>
       <c r="AP66" t="n">
-        <v>649800</v>
+        <v>642900</v>
       </c>
       <c r="AQ66" t="n">
-        <v>920022</v>
+        <v>919884</v>
       </c>
       <c r="AR66" t="n">
-        <v>0.7062874583433875</v>
+        <v>0.6988924690504454</v>
       </c>
       <c r="AS66" t="n">
         <v>-0.1075576236201723</v>
@@ -13365,7 +13365,7 @@
         </is>
       </c>
       <c r="X67" t="n">
-        <v>5279677952</v>
+        <v>5329775616</v>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>1</v>
       </c>
       <c r="AA67" t="n">
-        <v>5279677952</v>
+        <v>5329775616</v>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
@@ -13423,13 +13423,13 @@
         <v>51.6509471626282</v>
       </c>
       <c r="AP67" t="n">
-        <v>6315400</v>
+        <v>6300100</v>
       </c>
       <c r="AQ67" t="n">
-        <v>10760688</v>
+        <v>10760382</v>
       </c>
       <c r="AR67" t="n">
-        <v>0.5868955590943628</v>
+        <v>0.5854903664200769</v>
       </c>
       <c r="AS67" t="n">
         <v>-0.2356280808282631</v>
@@ -13588,16 +13588,16 @@
         <v>2046908.1275</v>
       </c>
       <c r="AG68" t="n">
-        <v>1027839.74203125</v>
+        <v>1027839.7425</v>
       </c>
       <c r="AH68" t="n">
         <v>0.1847136505153186</v>
       </c>
       <c r="AI68" t="n">
-        <v>1.359317217300468</v>
+        <v>1.359317216224493</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.9914662216259844</v>
+        <v>0.9914662207177689</v>
       </c>
       <c r="AK68" t="n">
         <v>2919000</v>
@@ -13636,13 +13636,13 @@
         <v>8.383944071693334</v>
       </c>
       <c r="AW68" t="n">
-        <v>18.74907477111688</v>
+        <v>18.74907351459004</v>
       </c>
       <c r="AX68" t="n">
         <v>2.589189177188556</v>
       </c>
       <c r="AY68" t="n">
-        <v>-11.59535736290294</v>
+        <v>-11.59536025624387</v>
       </c>
       <c r="AZ68" t="inlineStr"/>
       <c r="BA68" t="n">
@@ -13784,28 +13784,28 @@
         <v>296350</v>
       </c>
       <c r="AG69" t="n">
-        <v>175546.9340625</v>
+        <v>175546.9338671875</v>
       </c>
       <c r="AH69" t="n">
         <v>0.04437320735616668</v>
       </c>
       <c r="AI69" t="n">
-        <v>0.7630612670786303</v>
+        <v>0.7630612690402019</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.6881525250363558</v>
+        <v>0.6881525269145843</v>
       </c>
       <c r="AK69" t="n">
         <v>362500</v>
       </c>
       <c r="AL69" t="n">
-        <v>56994.75390625</v>
+        <v>56994.7578125</v>
       </c>
       <c r="AM69" t="n">
         <v>-0.1462068965517241</v>
       </c>
       <c r="AN69" t="n">
-        <v>4.430324350712925</v>
+        <v>4.430323978534759</v>
       </c>
       <c r="AO69" t="n">
         <v>44.37627811860941</v>
@@ -13826,19 +13826,19 @@
         <v>0.7348654708520179</v>
       </c>
       <c r="AU69" t="n">
-        <v>1.663660187532005</v>
+        <v>1.663660366628483</v>
       </c>
       <c r="AV69" t="n">
-        <v>4.430324350712925</v>
+        <v>4.430323978534759</v>
       </c>
       <c r="AW69" t="n">
-        <v>3.190964797842229</v>
+        <v>3.190965241203188</v>
       </c>
       <c r="AX69" t="n">
         <v>1.413545585951917</v>
       </c>
       <c r="AY69" t="n">
-        <v>71.41168793662516</v>
+        <v>71.41167139201139</v>
       </c>
       <c r="AZ69" t="inlineStr"/>
       <c r="BA69" t="n">
@@ -14166,16 +14166,16 @@
         <v>320.9159280395508</v>
       </c>
       <c r="AG71" t="n">
-        <v>222.4916584777832</v>
+        <v>222.4916589736939</v>
       </c>
       <c r="AH71" t="n">
         <v>0.09502200719311249</v>
       </c>
       <c r="AI71" t="n">
-        <v>0.5794300157873076</v>
+        <v>0.5794300122669231</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.4423728522460346</v>
+        <v>0.4423728490311363</v>
       </c>
       <c r="AK71" t="n">
         <v>433.3299865722656</v>
@@ -14193,13 +14193,13 @@
         <v>48.27151631497328</v>
       </c>
       <c r="AP71" t="n">
-        <v>18973400</v>
+        <v>18954700</v>
       </c>
       <c r="AQ71" t="n">
-        <v>11511062</v>
+        <v>11510688</v>
       </c>
       <c r="AR71" t="n">
-        <v>1.64827537198566</v>
+        <v>1.646704349905062</v>
       </c>
       <c r="AS71" t="n">
         <v>0.02312283663775716</v>
@@ -14208,7 +14208,7 @@
         <v>0.609858707847909</v>
       </c>
       <c r="AU71" t="n">
-        <v>1.056775748092817</v>
+        <v>1.056775931780431</v>
       </c>
       <c r="AV71" t="n">
         <v>2.575380862185094</v>
@@ -14377,25 +14377,25 @@
         <v>1213.56005859375</v>
       </c>
       <c r="AL72" t="n">
-        <v>104.7280349731445</v>
+        <v>104.7280426025391</v>
       </c>
       <c r="AM72" t="n">
         <v>-0.1961172496983348</v>
       </c>
       <c r="AN72" t="n">
-        <v>8.315175232770835</v>
+        <v>8.315174554164177</v>
       </c>
       <c r="AO72" t="n">
         <v>48.97250957724861</v>
       </c>
       <c r="AP72" t="n">
-        <v>61844400</v>
+        <v>61316900</v>
       </c>
       <c r="AQ72" t="n">
-        <v>54281020</v>
+        <v>54270470</v>
       </c>
       <c r="AR72" t="n">
-        <v>1.139337470077018</v>
+        <v>1.129839118769379</v>
       </c>
       <c r="AS72" t="n">
         <v>-0.09634387200940042</v>
@@ -14410,13 +14410,13 @@
         <v>7.032652616102846</v>
       </c>
       <c r="AW72" t="n">
-        <v>11.1940720159052</v>
+        <v>11.19407317878183</v>
       </c>
       <c r="AX72" t="n">
         <v>2.094191142429402</v>
       </c>
       <c r="AY72" t="n">
-        <v>721.1264476342116</v>
+        <v>721.1265750762444</v>
       </c>
       <c r="AZ72" t="inlineStr"/>
       <c r="BA72" t="n">
@@ -14585,13 +14585,13 @@
         <v>33.19841922233957</v>
       </c>
       <c r="AP73" t="n">
-        <v>3530800</v>
+        <v>3529100</v>
       </c>
       <c r="AQ73" t="n">
-        <v>3199722</v>
+        <v>3199688</v>
       </c>
       <c r="AR73" t="n">
-        <v>1.103470864031313</v>
+        <v>1.102951287750556</v>
       </c>
       <c r="AS73" t="n">
         <v>-0.3383335535810945</v>
@@ -14781,13 +14781,13 @@
         <v>47.27723873943231</v>
       </c>
       <c r="AP74" t="n">
-        <v>17346200</v>
+        <v>17259300</v>
       </c>
       <c r="AQ74" t="n">
-        <v>13083564</v>
+        <v>13081826</v>
       </c>
       <c r="AR74" t="n">
-        <v>1.325800829193024</v>
+        <v>1.319334166346502</v>
       </c>
       <c r="AS74" t="n">
         <v>-0.04722904722904719</v>
@@ -14917,7 +14917,7 @@
         </is>
       </c>
       <c r="X75" t="n">
-        <v>183903649792</v>
+        <v>185562923008</v>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>1</v>
       </c>
       <c r="AA75" t="n">
-        <v>183903649792</v>
+        <v>185562923008</v>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
@@ -14948,40 +14948,40 @@
         <v>839.6896154785156</v>
       </c>
       <c r="AG75" t="n">
-        <v>455.8909461212158</v>
+        <v>455.8909464263916</v>
       </c>
       <c r="AH75" t="n">
         <v>-0.02325816822547577</v>
       </c>
       <c r="AI75" t="n">
-        <v>0.7990266753980693</v>
+        <v>0.7990266741937915</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.8418650833553787</v>
+        <v>0.8418650821224245</v>
       </c>
       <c r="AK75" t="n">
         <v>1093.260498046875</v>
       </c>
       <c r="AL75" t="n">
-        <v>140.8470611572266</v>
+        <v>140.8470458984375</v>
       </c>
       <c r="AM75" t="n">
         <v>-0.2498037067928839</v>
       </c>
       <c r="AN75" t="n">
-        <v>4.823053505028355</v>
+        <v>4.823054135873997</v>
       </c>
       <c r="AO75" t="n">
         <v>46.62238839814433</v>
       </c>
       <c r="AP75" t="n">
-        <v>6302800</v>
+        <v>6294100</v>
       </c>
       <c r="AQ75" t="n">
-        <v>4501100</v>
+        <v>4500926</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.400279931572282</v>
+        <v>1.398401129012119</v>
       </c>
       <c r="AS75" t="n">
         <v>-0.1275077454581059</v>
@@ -14993,16 +14993,16 @@
         <v>1.985498642667444</v>
       </c>
       <c r="AV75" t="n">
-        <v>4.442489446127762</v>
+        <v>4.442489997210408</v>
       </c>
       <c r="AW75" t="n">
-        <v>10.00629785435567</v>
+        <v>10.00629672748524</v>
       </c>
       <c r="AX75" t="n">
         <v>1.859346343367094</v>
       </c>
       <c r="AY75" t="n">
-        <v>154.5868171661456</v>
+        <v>154.5867749441991</v>
       </c>
       <c r="AZ75" t="inlineStr"/>
       <c r="BA75" t="n">
@@ -15142,16 +15142,16 @@
         <v>529.5487768554688</v>
       </c>
       <c r="AG76" t="n">
-        <v>290.4133644485474</v>
+        <v>290.4133642959595</v>
       </c>
       <c r="AH76" t="n">
         <v>0.01784769138860809</v>
       </c>
       <c r="AI76" t="n">
-        <v>0.8559751925448829</v>
+        <v>0.8559751935200426</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.8234311560041483</v>
+        <v>0.8234311569622086</v>
       </c>
       <c r="AK76" t="n">
         <v>746.22998046875</v>
@@ -15169,13 +15169,13 @@
         <v>50.78540989629602</v>
       </c>
       <c r="AP76" t="n">
-        <v>8956300</v>
+        <v>8925700</v>
       </c>
       <c r="AQ76" t="n">
-        <v>8810696</v>
+        <v>8810084</v>
       </c>
       <c r="AR76" t="n">
-        <v>1.016525822704585</v>
+        <v>1.013123143888299</v>
       </c>
       <c r="AS76" t="n">
         <v>-0.09252405701525201</v>
@@ -15196,7 +15196,7 @@
         <v>1.87372723288619</v>
       </c>
       <c r="AY76" t="n">
-        <v>792.1836493070787</v>
+        <v>792.1837188797826</v>
       </c>
       <c r="AZ76" t="inlineStr"/>
       <c r="BA76" t="n">
@@ -15388,7 +15388,7 @@
         <v>1.04257665453312</v>
       </c>
       <c r="AY77" t="n">
-        <v>3.846878712907007</v>
+        <v>3.84687919862932</v>
       </c>
       <c r="AZ77" t="inlineStr"/>
       <c r="BA77" t="n">
@@ -15580,7 +15580,7 @@
         <v>0.9782608695652173</v>
       </c>
       <c r="AY78" t="n">
-        <v>-0.5236897212718811</v>
+        <v>-0.5236897550866193</v>
       </c>
       <c r="AZ78" t="inlineStr"/>
       <c r="BA78" t="n">
@@ -15722,16 +15722,16 @@
         <v>139.9099995422363</v>
       </c>
       <c r="AG79" t="n">
-        <v>115.6837024688721</v>
+        <v>115.6837020874023</v>
       </c>
       <c r="AH79" t="n">
         <v>0.1019226550880241</v>
       </c>
       <c r="AI79" t="n">
-        <v>0.3326855458350242</v>
+        <v>0.3326855502295862</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0.2094184103407568</v>
+        <v>0.2094184143288425</v>
       </c>
       <c r="AK79" t="n">
         <v>181.0800018310547</v>
@@ -15749,13 +15749,13 @@
         <v>38.44462542995721</v>
       </c>
       <c r="AP79" t="n">
-        <v>1931100</v>
+        <v>1930200</v>
       </c>
       <c r="AQ79" t="n">
-        <v>3254292</v>
+        <v>3254274</v>
       </c>
       <c r="AR79" t="n">
-        <v>0.5934009609463441</v>
+        <v>0.5931276837783174</v>
       </c>
       <c r="AS79" t="n">
         <v>-0.1486083686216</v>
@@ -15764,19 +15764,19 @@
         <v>0.4917271450908591</v>
       </c>
       <c r="AU79" t="n">
-        <v>0.454064820011054</v>
+        <v>0.4540647153806965</v>
       </c>
       <c r="AV79" t="n">
         <v>0.460389388604763</v>
       </c>
       <c r="AW79" t="n">
-        <v>1.101840946798197</v>
+        <v>1.101840290938381</v>
       </c>
       <c r="AX79" t="n">
         <v>0.4554303765741006</v>
       </c>
       <c r="AY79" t="n">
-        <v>162.9126046458131</v>
+        <v>162.9125942584596</v>
       </c>
       <c r="AZ79" t="inlineStr"/>
       <c r="BA79" t="n">
@@ -16059,13 +16059,13 @@
         <v>52.45790251046104</v>
       </c>
       <c r="AP81" t="n">
-        <v>9766500</v>
+        <v>9764500</v>
       </c>
       <c r="AQ81" t="n">
-        <v>10197902</v>
+        <v>10197862</v>
       </c>
       <c r="AR81" t="n">
-        <v>0.9576969851249796</v>
+        <v>0.9575046220472487</v>
       </c>
       <c r="AS81" t="n">
         <v>-0.08246825730745244</v>
@@ -16228,40 +16228,40 @@
         <v>145.9177880859375</v>
       </c>
       <c r="AG82" t="n">
-        <v>138.3811506652832</v>
+        <v>138.3811511611939</v>
       </c>
       <c r="AH82" t="n">
         <v>0.1279638932092106</v>
       </c>
       <c r="AI82" t="n">
-        <v>0.1893960669253392</v>
+        <v>0.1893960626629509</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.05446289024495798</v>
+        <v>0.05446288646612407</v>
       </c>
       <c r="AK82" t="n">
         <v>176.3200073242188</v>
       </c>
       <c r="AL82" t="n">
-        <v>96.75052642822266</v>
+        <v>96.75051879882812</v>
       </c>
       <c r="AM82" t="n">
         <v>-0.0665268290555302</v>
       </c>
       <c r="AN82" t="n">
-        <v>0.7011793363212009</v>
+        <v>0.7011794704700249</v>
       </c>
       <c r="AO82" t="n">
         <v>61.72649480589948</v>
       </c>
       <c r="AP82" t="n">
-        <v>8304600</v>
+        <v>8303100</v>
       </c>
       <c r="AQ82" t="n">
-        <v>10561836</v>
+        <v>10561806</v>
       </c>
       <c r="AR82" t="n">
-        <v>0.7862837483937452</v>
+        <v>0.7861439606067372</v>
       </c>
       <c r="AS82" t="n">
         <v>0.1166393767357281</v>
@@ -16276,13 +16276,13 @@
         <v>0.6820128322719821</v>
       </c>
       <c r="AW82" t="n">
-        <v>4.069713096474089</v>
+        <v>4.06971250077991</v>
       </c>
       <c r="AX82" t="n">
         <v>0.1821923412758299</v>
       </c>
       <c r="AY82" t="n">
-        <v>1314.309110715601</v>
+        <v>1314.309893861354</v>
       </c>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="n">
@@ -16417,19 +16417,19 @@
         <v>146.3000030517578</v>
       </c>
       <c r="AF83" t="n">
-        <v>144.2520002746582</v>
+        <v>145.0830004882812</v>
       </c>
       <c r="AG83" t="n">
-        <v>105.3595885848999</v>
+        <v>105.9873382949829</v>
       </c>
       <c r="AH83" t="n">
-        <v>0.01419739603749126</v>
+        <v>0.00838831950938923</v>
       </c>
       <c r="AI83" t="n">
-        <v>0.3885779644428631</v>
+        <v>0.38035359133727</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.3691397452488947</v>
+        <v>0.3688710634895622</v>
       </c>
       <c r="AK83" t="n">
         <v>156.8999938964844</v>
@@ -16444,31 +16444,31 @@
         <v>1.483829290696485</v>
       </c>
       <c r="AO83" t="n">
-        <v>55.95027211031852</v>
+        <v>51.12107582406554</v>
       </c>
       <c r="AP83" t="n">
         <v>539484</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1132605.84</v>
+        <v>1136674.64</v>
       </c>
       <c r="AR83" t="n">
-        <v>0.4763210473998615</v>
+        <v>0.4746160255673515</v>
       </c>
       <c r="AS83" t="n">
-        <v>-0.05092436688643676</v>
+        <v>0.006535926442036821</v>
       </c>
       <c r="AT83" t="n">
-        <v>0.408413064040309</v>
+        <v>0.4070685407393015</v>
       </c>
       <c r="AU83" t="n">
-        <v>0.6398580282503394</v>
+        <v>0.6232426041553711</v>
       </c>
       <c r="AV83" t="n">
-        <v>1.450788768194478</v>
+        <v>1.483829290696485</v>
       </c>
       <c r="AW83" t="n">
-        <v>4.175944148660687</v>
+        <v>4.319331593680104</v>
       </c>
       <c r="AX83" t="n">
         <v>0.6398580282503394</v>
@@ -16660,7 +16660,7 @@
         <v>7.636817377417076</v>
       </c>
       <c r="AW84" t="n">
-        <v>33.57517647004597</v>
+        <v>33.57517238379871</v>
       </c>
       <c r="AX84" t="n">
         <v>0.7919851721657041</v>
@@ -16835,13 +16835,13 @@
         <v>55.57368157652713</v>
       </c>
       <c r="AP85" t="n">
-        <v>7258800</v>
+        <v>7247100</v>
       </c>
       <c r="AQ85" t="n">
-        <v>6320962</v>
+        <v>6320728</v>
       </c>
       <c r="AR85" t="n">
-        <v>1.148369504515294</v>
+        <v>1.146560965762172</v>
       </c>
       <c r="AS85" t="n">
         <v>0.117951267742004</v>
@@ -17029,13 +17029,13 @@
         <v>45.02764286885688</v>
       </c>
       <c r="AP86" t="n">
-        <v>6975900</v>
+        <v>6965900</v>
       </c>
       <c r="AQ86" t="n">
-        <v>6299264</v>
+        <v>6299064</v>
       </c>
       <c r="AR86" t="n">
-        <v>1.107415088492878</v>
+        <v>1.105862712301383</v>
       </c>
       <c r="AS86" t="n">
         <v>-0.2013990580440062</v>
@@ -17225,13 +17225,13 @@
         <v>45.1306306405907</v>
       </c>
       <c r="AP87" t="n">
-        <v>9061700</v>
+        <v>9047500</v>
       </c>
       <c r="AQ87" t="n">
-        <v>8678232</v>
+        <v>8677948</v>
       </c>
       <c r="AR87" t="n">
-        <v>1.044187341384743</v>
+        <v>1.042585182580029</v>
       </c>
       <c r="AS87" t="n">
         <v>0.127260003643338</v>
@@ -17419,13 +17419,13 @@
         <v>54.85511178212172</v>
       </c>
       <c r="AP88" t="n">
-        <v>21192200</v>
+        <v>21142600</v>
       </c>
       <c r="AQ88" t="n">
-        <v>15730742</v>
+        <v>15729750</v>
       </c>
       <c r="AR88" t="n">
-        <v>1.347183750137152</v>
+        <v>1.344115450023045</v>
       </c>
       <c r="AS88" t="n">
         <v>-0.01977486217040092</v>
@@ -17440,13 +17440,13 @@
         <v>2.773542600896861</v>
       </c>
       <c r="AW88" t="n">
-        <v>4.474716932114223</v>
+        <v>4.474717513120001</v>
       </c>
       <c r="AX88" t="n">
         <v>1.177781571539224</v>
       </c>
       <c r="AY88" t="n">
-        <v>255.7039997014336</v>
+        <v>255.7039398239531</v>
       </c>
       <c r="AZ88" t="inlineStr"/>
       <c r="BA88" t="n">
@@ -17784,40 +17784,40 @@
         <v>93.46663955688477</v>
       </c>
       <c r="AG90" t="n">
-        <v>73.11352226257324</v>
+        <v>73.11352228164672</v>
       </c>
       <c r="AH90" t="n">
         <v>-0.09443626313177067</v>
       </c>
       <c r="AI90" t="n">
-        <v>0.1576517827397244</v>
+        <v>0.1576517824377222</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0.2783769221405747</v>
+        <v>0.2783769218070784</v>
       </c>
       <c r="AK90" t="n">
         <v>102.7099990844727</v>
       </c>
       <c r="AL90" t="n">
-        <v>48.05623245239258</v>
+        <v>48.05623626708984</v>
       </c>
       <c r="AM90" t="n">
         <v>-0.1759322349907019</v>
       </c>
       <c r="AN90" t="n">
-        <v>0.7612699762408124</v>
+        <v>0.7612698364314499</v>
       </c>
       <c r="AO90" t="n">
         <v>41.7132535171701</v>
       </c>
       <c r="AP90" t="n">
-        <v>14795800</v>
+        <v>14794000</v>
       </c>
       <c r="AQ90" t="n">
-        <v>12563670</v>
+        <v>12563634</v>
       </c>
       <c r="AR90" t="n">
-        <v>1.177665443298017</v>
+        <v>1.17752554714663</v>
       </c>
       <c r="AS90" t="n">
         <v>-0.1233558082408838</v>
@@ -17829,16 +17829,16 @@
         <v>0.342838566277085</v>
       </c>
       <c r="AV90" t="n">
-        <v>0.18829792715007</v>
+        <v>0.1882977998686373</v>
       </c>
       <c r="AW90" t="n">
-        <v>0.2653073560940982</v>
+        <v>0.2653070674674776</v>
       </c>
       <c r="AX90" t="n">
         <v>0.3157878881324572</v>
       </c>
       <c r="AY90" t="n">
-        <v>480.7968798401546</v>
+        <v>480.7968389731892</v>
       </c>
       <c r="AZ90" t="inlineStr"/>
       <c r="BA90" t="n">
@@ -18003,13 +18003,13 @@
         <v>39.16539110922148</v>
       </c>
       <c r="AP91" t="n">
-        <v>4138300</v>
+        <v>4137100</v>
       </c>
       <c r="AQ91" t="n">
-        <v>3853768</v>
+        <v>3853744</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.073832155957494</v>
+        <v>1.073527457973337</v>
       </c>
       <c r="AS91" t="n">
         <v>-0.172660524327456</v>
@@ -18216,7 +18216,7 @@
         <v>4.054186089094295</v>
       </c>
       <c r="AW92" t="n">
-        <v>8.716714732819474</v>
+        <v>8.716713904211197</v>
       </c>
       <c r="AX92" t="n">
         <v>2.068332573948467</v>
@@ -18414,7 +18414,7 @@
         <v>0.7292197037105557</v>
       </c>
       <c r="AY93" t="n">
-        <v>284.2523741412754</v>
+        <v>284.2523557003436</v>
       </c>
       <c r="AZ93" t="inlineStr"/>
       <c r="BA93" t="n">
@@ -18556,16 +18556,16 @@
         <v>408.8887963867188</v>
       </c>
       <c r="AG94" t="n">
-        <v>360.1986968994141</v>
+        <v>360.1986970520019</v>
       </c>
       <c r="AH94" t="n">
         <v>-0.1184644446307477</v>
       </c>
       <c r="AI94" t="n">
-        <v>0.0006977129839182972</v>
+        <v>0.0006977125600013956</v>
       </c>
       <c r="AJ94" t="n">
-        <v>0.1351756680588476</v>
+        <v>0.135175667577963</v>
       </c>
       <c r="AK94" t="n">
         <v>480.8090515136719</v>
@@ -18583,13 +18583,13 @@
         <v>41.6450519969167</v>
       </c>
       <c r="AP94" t="n">
-        <v>26788900</v>
+        <v>26749500</v>
       </c>
       <c r="AQ94" t="n">
-        <v>27281432</v>
+        <v>27280644</v>
       </c>
       <c r="AR94" t="n">
-        <v>0.9819462556071104</v>
+        <v>0.9805303716437193</v>
       </c>
       <c r="AS94" t="n">
         <v>-0.2466655334868972</v>
@@ -18604,13 +18604,13 @@
         <v>0.345279986806007</v>
       </c>
       <c r="AW94" t="n">
-        <v>7.566255575012773</v>
+        <v>7.566256351612312</v>
       </c>
       <c r="AX94" t="n">
         <v>0.04072788759895696</v>
       </c>
       <c r="AY94" t="n">
-        <v>316.4116836894942</v>
+        <v>316.4117503304105</v>
       </c>
       <c r="AZ94" t="inlineStr"/>
       <c r="BA94" t="n">
@@ -18721,7 +18721,7 @@
         </is>
       </c>
       <c r="X95" t="n">
-        <v>214764421120</v>
+        <v>214579691520</v>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>1</v>
       </c>
       <c r="AA95" t="n">
-        <v>214764421120</v>
+        <v>214579691520</v>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
@@ -18752,40 +18752,40 @@
         <v>223.6270001220703</v>
       </c>
       <c r="AG95" t="n">
-        <v>122.570412902832</v>
+        <v>122.570412940979</v>
       </c>
       <c r="AH95" t="n">
         <v>0.0968710985356751</v>
       </c>
       <c r="AI95" t="n">
-        <v>1.001216994190817</v>
+        <v>1.001216993567988</v>
       </c>
       <c r="AJ95" t="n">
-        <v>0.8244778232031502</v>
+        <v>0.8244778226353273</v>
       </c>
       <c r="AK95" t="n">
         <v>316.4299926757812</v>
       </c>
       <c r="AL95" t="n">
-        <v>62.19286727905273</v>
+        <v>62.19287109375</v>
       </c>
       <c r="AM95" t="n">
         <v>-0.2248206587121453</v>
       </c>
       <c r="AN95" t="n">
-        <v>2.944021300473942</v>
+        <v>2.944021058561211</v>
       </c>
       <c r="AO95" t="n">
         <v>42.26502405412126</v>
       </c>
       <c r="AP95" t="n">
-        <v>38579900</v>
+        <v>38435900</v>
       </c>
       <c r="AQ95" t="n">
-        <v>46066822</v>
+        <v>46063942</v>
       </c>
       <c r="AR95" t="n">
-        <v>0.837476915598823</v>
+        <v>0.8344031867702508</v>
       </c>
       <c r="AS95" t="n">
         <v>-0.1868390576851539</v>
@@ -18800,13 +18800,13 @@
         <v>2.312499864772374</v>
       </c>
       <c r="AW95" t="n">
-        <v>3.442106225952319</v>
+        <v>3.44210591907973</v>
       </c>
       <c r="AX95" t="n">
         <v>1.747391867747758</v>
       </c>
       <c r="AY95" t="n">
-        <v>19.21793423424472</v>
+        <v>19.21793741275688</v>
       </c>
       <c r="AZ95" t="inlineStr"/>
       <c r="BA95" t="n">
@@ -18992,13 +18992,13 @@
         <v>0.324158530574518</v>
       </c>
       <c r="AW96" t="n">
-        <v>0.9685836363507518</v>
+        <v>0.9685834281369927</v>
       </c>
       <c r="AX96" t="n">
         <v>0.1270312143681791</v>
       </c>
       <c r="AY96" t="n">
-        <v>7.792589597167055</v>
+        <v>7.792590635592674</v>
       </c>
       <c r="AZ96" t="inlineStr"/>
       <c r="BA96" t="n">
@@ -19355,13 +19355,13 @@
         <v>34.36531931855089</v>
       </c>
       <c r="AP98" t="n">
-        <v>78276600</v>
+        <v>77939100</v>
       </c>
       <c r="AQ98" t="n">
-        <v>119844226</v>
+        <v>119837476</v>
       </c>
       <c r="AR98" t="n">
-        <v>0.6531528686246428</v>
+        <v>0.6503733439779723</v>
       </c>
       <c r="AS98" t="n">
         <v>-0.2785415406406639</v>
@@ -19376,13 +19376,13 @@
         <v>1.347048653512317</v>
       </c>
       <c r="AW98" t="n">
-        <v>1.465491710387839</v>
+        <v>1.465491950530859</v>
       </c>
       <c r="AX98" t="n">
         <v>0.8540705484579336</v>
       </c>
       <c r="AY98" t="n">
-        <v>19.19928990617002</v>
+        <v>19.19929192103103</v>
       </c>
       <c r="AZ98" t="inlineStr"/>
       <c r="BA98" t="n">
@@ -19551,13 +19551,13 @@
         <v>44.55866688068173</v>
       </c>
       <c r="AP99" t="n">
-        <v>2155600</v>
+        <v>2153800</v>
       </c>
       <c r="AQ99" t="n">
-        <v>2944060</v>
+        <v>2944024</v>
       </c>
       <c r="AR99" t="n">
-        <v>0.7321861646841437</v>
+        <v>0.7315837099154083</v>
       </c>
       <c r="AS99" t="n">
         <v>-0.3190193033509371</v>
@@ -19711,7 +19711,7 @@
         <v>42208</v>
       </c>
       <c r="AD100" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="AE100" t="n">
         <v>728.3200073242188</v>
@@ -19747,13 +19747,13 @@
         <v>34.91929555406399</v>
       </c>
       <c r="AP100" t="n">
-        <v>5229100</v>
+        <v>5217800</v>
       </c>
       <c r="AQ100" t="n">
-        <v>5957480</v>
+        <v>5957254</v>
       </c>
       <c r="AR100" t="n">
-        <v>0.8777368954658681</v>
+        <v>0.8758733470152523</v>
       </c>
       <c r="AS100" t="n">
         <v>-0.2235394378206623</v>
@@ -19916,28 +19916,28 @@
         <v>207.8093933105469</v>
       </c>
       <c r="AG101" t="n">
-        <v>220.1607162475586</v>
+        <v>220.1607160949707</v>
       </c>
       <c r="AH101" t="n">
         <v>-0.04989856668146264</v>
       </c>
       <c r="AI101" t="n">
-        <v>-0.1032005808911166</v>
+        <v>-0.1032005802695674</v>
       </c>
       <c r="AJ101" t="n">
-        <v>-0.05610139332542563</v>
+        <v>-0.05610139267123304</v>
       </c>
       <c r="AK101" t="n">
-        <v>247.2834320068359</v>
+        <v>247.2834167480469</v>
       </c>
       <c r="AL101" t="n">
-        <v>169.3577423095703</v>
+        <v>169.3577117919922</v>
       </c>
       <c r="AM101" t="n">
-        <v>-0.2015639671486434</v>
+        <v>-0.2015639178806126</v>
       </c>
       <c r="AN101" t="n">
-        <v>0.1658162168960906</v>
+        <v>0.1658164269714815</v>
       </c>
       <c r="AO101" t="n">
         <v>39.79793589192133</v>
@@ -19964,13 +19964,13 @@
         <v>0.1505553052992084</v>
       </c>
       <c r="AW101" t="n">
-        <v>0.5939328341951402</v>
+        <v>0.5939332268898567</v>
       </c>
       <c r="AX101" t="n">
         <v>-0.1475406250424107</v>
       </c>
       <c r="AY101" t="n">
-        <v>6.388353735355485</v>
+        <v>6.388350043980898</v>
       </c>
       <c r="AZ101" t="inlineStr"/>
       <c r="BA101" t="n">
@@ -20135,13 +20135,13 @@
         <v>37.61368387887931</v>
       </c>
       <c r="AP102" t="n">
-        <v>16848000</v>
+        <v>16845300</v>
       </c>
       <c r="AQ102" t="n">
-        <v>13072798</v>
+        <v>13072744</v>
       </c>
       <c r="AR102" t="n">
-        <v>1.288783013399274</v>
+        <v>1.288581800423844</v>
       </c>
       <c r="AS102" t="n">
         <v>-0.1415497841985546</v>
@@ -20153,10 +20153,10 @@
         <v>1.645418033758068</v>
       </c>
       <c r="AV102" t="n">
-        <v>1.179000769200366</v>
+        <v>1.179000636703284</v>
       </c>
       <c r="AW102" t="n">
-        <v>0.9515704509563081</v>
+        <v>0.951570663520489</v>
       </c>
       <c r="AX102" t="n">
         <v>1.507202654753022</v>
@@ -20327,13 +20327,13 @@
         <v>51.51515566336486</v>
       </c>
       <c r="AP103" t="n">
-        <v>28189000</v>
+        <v>28030600</v>
       </c>
       <c r="AQ103" t="n">
-        <v>35088188</v>
+        <v>35085020</v>
       </c>
       <c r="AR103" t="n">
-        <v>0.8033757685064843</v>
+        <v>0.7989335619589215</v>
       </c>
       <c r="AS103" t="n">
         <v>-0.2045639882021086</v>
@@ -20490,28 +20490,28 @@
         <v>23601.8</v>
       </c>
       <c r="AG104" t="n">
-        <v>20179.20505859375</v>
+        <v>20179.20502929687</v>
       </c>
       <c r="AH104" t="n">
         <v>0.08868815090374471</v>
       </c>
       <c r="AI104" t="n">
-        <v>0.2733405466365102</v>
+        <v>0.2733405484851907</v>
       </c>
       <c r="AJ104" t="n">
-        <v>0.1696099985835995</v>
+        <v>0.1696100002816803</v>
       </c>
       <c r="AK104" t="n">
         <v>25780</v>
       </c>
       <c r="AL104" t="n">
-        <v>15917.18359375</v>
+        <v>15917.1826171875</v>
       </c>
       <c r="AM104" t="n">
         <v>-0.003297129557796707</v>
       </c>
       <c r="AN104" t="n">
-        <v>0.6142931221883583</v>
+        <v>0.6142932212296375</v>
       </c>
       <c r="AO104" t="n">
         <v>86.88783570300158</v>
@@ -20535,16 +20535,16 @@
         <v>0.2794704351789015</v>
       </c>
       <c r="AV104" t="n">
-        <v>0.6029249715744189</v>
+        <v>0.6029248739231741</v>
       </c>
       <c r="AW104" t="n">
-        <v>0.3122075587306301</v>
+        <v>0.3122076896146215</v>
       </c>
       <c r="AX104" t="n">
         <v>0.2804182101509511</v>
       </c>
       <c r="AY104" t="n">
-        <v>22.96190109744374</v>
+        <v>22.96189836969774</v>
       </c>
       <c r="AZ104" t="inlineStr"/>
       <c r="BA104" t="n">
@@ -20876,40 +20876,40 @@
         <v>406.694769897461</v>
       </c>
       <c r="AG106" t="n">
-        <v>369.7095402526855</v>
+        <v>369.7095416259766</v>
       </c>
       <c r="AH106" t="n">
         <v>-0.02010053113259891</v>
       </c>
       <c r="AI106" t="n">
-        <v>0.07792725267867096</v>
+        <v>0.07792724867469603</v>
       </c>
       <c r="AJ106" t="n">
-        <v>0.1000386130676993</v>
+        <v>0.1000386089815912</v>
       </c>
       <c r="AK106" t="n">
         <v>435.7799987792969</v>
       </c>
       <c r="AL106" t="n">
-        <v>313.9706420898438</v>
+        <v>313.9706115722656</v>
       </c>
       <c r="AM106" t="n">
         <v>-0.08550188138509662</v>
       </c>
       <c r="AN106" t="n">
-        <v>0.2692906138008726</v>
+        <v>0.2692907371744435</v>
       </c>
       <c r="AO106" t="n">
         <v>51.51232629106249</v>
       </c>
       <c r="AP106" t="n">
-        <v>2602200</v>
+        <v>2601600</v>
       </c>
       <c r="AQ106" t="n">
-        <v>2734498</v>
+        <v>2734486</v>
       </c>
       <c r="AR106" t="n">
-        <v>0.9516189077483326</v>
+        <v>0.9514036641621131</v>
       </c>
       <c r="AS106" t="n">
         <v>-0.05386862349352917</v>
@@ -20921,7 +20921,7 @@
         <v>0.2585708173976435</v>
       </c>
       <c r="AV106" t="n">
-        <v>0.125505558188125</v>
+        <v>0.1255054611828823</v>
       </c>
       <c r="AW106" t="n">
         <v>1.942022985879928</v>
@@ -20930,7 +20930,7 @@
         <v>0.224733195479329</v>
       </c>
       <c r="AY106" t="n">
-        <v>1152.823615565617</v>
+        <v>1152.823416448421</v>
       </c>
       <c r="AZ106" t="inlineStr"/>
       <c r="BA106" t="n">
@@ -21122,7 +21122,7 @@
         <v>0.1399006719946885</v>
       </c>
       <c r="AY107" t="n">
-        <v>9.58672985928861</v>
+        <v>9.586728368019685</v>
       </c>
       <c r="AZ107" t="inlineStr"/>
       <c r="BA107" t="n">
@@ -21308,13 +21308,13 @@
         <v>0.2493768305093329</v>
       </c>
       <c r="AW108" t="n">
-        <v>1.132328012648557</v>
+        <v>1.132328260342295</v>
       </c>
       <c r="AX108" t="n">
         <v>0.2000974375378899</v>
       </c>
       <c r="AY108" t="n">
-        <v>14.05171254362061</v>
+        <v>14.05171562907322</v>
       </c>
       <c r="AZ108" t="inlineStr"/>
       <c r="BA108" t="n">
@@ -21456,16 +21456,16 @@
         <v>470.6744177246094</v>
       </c>
       <c r="AG109" t="n">
-        <v>432.5672796630859</v>
+        <v>432.5672790527344</v>
       </c>
       <c r="AH109" t="n">
         <v>0.01584022176995692</v>
       </c>
       <c r="AI109" t="n">
-        <v>0.1053309562739329</v>
+        <v>0.1053309578335526</v>
       </c>
       <c r="AJ109" t="n">
-        <v>0.08809528564251101</v>
+        <v>0.08809528717781112</v>
       </c>
       <c r="AK109" t="n">
         <v>503.4599914550781</v>
@@ -21498,10 +21498,10 @@
         <v>0.1220993649725488</v>
       </c>
       <c r="AU109" t="n">
-        <v>0.23425199347115</v>
+        <v>0.2342520907037224</v>
       </c>
       <c r="AV109" t="n">
-        <v>0.1126767275153016</v>
+        <v>0.112676806536226</v>
       </c>
       <c r="AW109" t="n">
         <v>1.823918013653156</v>
@@ -21510,7 +21510,7 @@
         <v>0.2069620222934965</v>
       </c>
       <c r="AY109" t="n">
-        <v>535.3164049287656</v>
+        <v>535.316584214782</v>
       </c>
       <c r="AZ109" t="inlineStr"/>
       <c r="BA109" t="n">
@@ -21696,13 +21696,13 @@
         <v>4.214625425425027</v>
       </c>
       <c r="AW110" t="n">
-        <v>6.592861056101114</v>
+        <v>6.592861903997761</v>
       </c>
       <c r="AX110" t="n">
         <v>1.096331813966337</v>
       </c>
       <c r="AY110" t="n">
-        <v>83.00147170841333</v>
+        <v>83.00148468067898</v>
       </c>
       <c r="AZ110" t="inlineStr"/>
       <c r="BA110" t="n">
@@ -21841,64 +21841,64 @@
         <v>377.1600036621094</v>
       </c>
       <c r="AF111" t="n">
-        <v>408.1078063964844</v>
+        <v>408.7304028320312</v>
       </c>
       <c r="AG111" t="n">
-        <v>316.0571635437012</v>
+        <v>316.7990631103515</v>
       </c>
       <c r="AH111" t="n">
-        <v>-0.07583242037842475</v>
+        <v>-0.07724015378150328</v>
       </c>
       <c r="AI111" t="n">
-        <v>0.1933284455043194</v>
+        <v>0.1905338354196209</v>
       </c>
       <c r="AJ111" t="n">
-        <v>0.2912468169387192</v>
+        <v>0.290188167916573</v>
       </c>
       <c r="AK111" t="n">
         <v>445.4800109863281</v>
       </c>
       <c r="AL111" t="n">
-        <v>217.7568664550781</v>
+        <v>218.3533325195312</v>
       </c>
       <c r="AM111" t="n">
         <v>-0.1533626776495601</v>
       </c>
       <c r="AN111" t="n">
-        <v>0.7320234709563802</v>
+        <v>0.72729217965278</v>
       </c>
       <c r="AO111" t="n">
         <v>39.70198126167281</v>
       </c>
       <c r="AP111" t="n">
-        <v>6144800</v>
+        <v>6144100</v>
       </c>
       <c r="AQ111" t="n">
-        <v>4941644</v>
+        <v>4941630</v>
       </c>
       <c r="AR111" t="n">
-        <v>1.24347281997651</v>
+        <v>1.243334689161269</v>
       </c>
       <c r="AS111" t="n">
         <v>-0.1382548676152703</v>
       </c>
       <c r="AT111" t="n">
-        <v>0.1880162878128824</v>
+        <v>0.1847710246933167</v>
       </c>
       <c r="AU111" t="n">
-        <v>0.3988836575230703</v>
+        <v>0.395062480930287</v>
       </c>
       <c r="AV111" t="n">
-        <v>0.5591390280078554</v>
+        <v>0.5548798485025002</v>
       </c>
       <c r="AW111" t="n">
-        <v>1.448391291582685</v>
+        <v>1.441702591987046</v>
       </c>
       <c r="AX111" t="n">
-        <v>0.3859036311571151</v>
+        <v>0.3821178553048039</v>
       </c>
       <c r="AY111" t="n">
-        <v>849.1983071665513</v>
+        <v>846.8760101088095</v>
       </c>
       <c r="AZ111" t="inlineStr"/>
       <c r="BA111" t="n">
@@ -22063,13 +22063,13 @@
         <v>34.63694613138524</v>
       </c>
       <c r="AP112" t="n">
-        <v>1788100</v>
+        <v>1787600</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1435676</v>
+        <v>1435666</v>
       </c>
       <c r="AR112" t="n">
-        <v>1.245475998762952</v>
+        <v>1.245136403592479</v>
       </c>
       <c r="AS112" t="n">
         <v>-0.2352746344594717</v>
@@ -22090,7 +22090,7 @@
         <v>0.6402954706720456</v>
       </c>
       <c r="AY112" t="n">
-        <v>260.6639739707714</v>
+        <v>260.6639916397898</v>
       </c>
       <c r="AZ112" t="inlineStr"/>
       <c r="BA112" t="n">
@@ -22232,16 +22232,16 @@
         <v>1540.125576171875</v>
       </c>
       <c r="AG113" t="n">
-        <v>1165.408966369629</v>
+        <v>1165.408968811035</v>
       </c>
       <c r="AH113" t="n">
         <v>-0.1636006478241023</v>
       </c>
       <c r="AI113" t="n">
-        <v>0.1053287484070431</v>
+        <v>0.1053287460914982</v>
       </c>
       <c r="AJ113" t="n">
-        <v>0.3215322866182571</v>
+        <v>0.3215322838497892</v>
       </c>
       <c r="AK113" t="n">
         <v>1687.3154296875</v>
@@ -22274,10 +22274,10 @@
         <v>0.1534528743994645</v>
       </c>
       <c r="AU113" t="n">
-        <v>0.4262599329499062</v>
+        <v>0.4262598365653227</v>
       </c>
       <c r="AV113" t="n">
-        <v>0.6969826739866007</v>
+        <v>0.6969828104339464</v>
       </c>
       <c r="AW113" t="n">
         <v>2.659032274227168</v>
@@ -22286,7 +22286,7 @@
         <v>0.3806377349946872</v>
       </c>
       <c r="AY113" t="n">
-        <v>152.4501620348754</v>
+        <v>152.4500923040569</v>
       </c>
       <c r="AZ113" t="inlineStr"/>
       <c r="BA113" t="n">
@@ -22631,25 +22631,25 @@
         <v>184.3399963378906</v>
       </c>
       <c r="AL115" t="n">
-        <v>72.85916900634766</v>
+        <v>72.85917663574219</v>
       </c>
       <c r="AM115" t="n">
         <v>-0.1746229959905325</v>
       </c>
       <c r="AN115" t="n">
-        <v>1.088275174854502</v>
+        <v>1.088274956182319</v>
       </c>
       <c r="AO115" t="n">
         <v>42.01213411573622</v>
       </c>
       <c r="AP115" t="n">
-        <v>2948300</v>
+        <v>2947700</v>
       </c>
       <c r="AQ115" t="n">
-        <v>2216300</v>
+        <v>2216288</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.33028019672427</v>
+        <v>1.330016676533014</v>
       </c>
       <c r="AS115" t="n">
         <v>-0.1374227880097527</v>
@@ -22661,10 +22661,10 @@
         <v>0.4971214579007963</v>
       </c>
       <c r="AV115" t="n">
-        <v>1.088275174854502</v>
+        <v>1.088274956182319</v>
       </c>
       <c r="AW115" t="n">
-        <v>4.175858628747855</v>
+        <v>4.175859300413301</v>
       </c>
       <c r="AX115" t="n">
         <v>0.4291469644159489</v>
@@ -22839,13 +22839,13 @@
         <v>37.63000201187118</v>
       </c>
       <c r="AP116" t="n">
-        <v>16104500</v>
+        <v>16098300</v>
       </c>
       <c r="AQ116" t="n">
-        <v>13843160</v>
+        <v>13843036</v>
       </c>
       <c r="AR116" t="n">
-        <v>1.16335432083426</v>
+        <v>1.162916863034958</v>
       </c>
       <c r="AS116" t="n">
         <v>-0.3188978853935339</v>
@@ -23008,40 +23008,40 @@
         <v>76.89070922851562</v>
       </c>
       <c r="AG117" t="n">
-        <v>51.30383783340454</v>
+        <v>51.3038378238678</v>
       </c>
       <c r="AH117" t="n">
         <v>-0.05073059416259706</v>
       </c>
       <c r="AI117" t="n">
-        <v>0.4227005414445792</v>
+        <v>0.4227005417090417</v>
       </c>
       <c r="AJ117" t="n">
-        <v>0.4987321119756689</v>
+        <v>0.4987321122542647</v>
       </c>
       <c r="AK117" t="n">
         <v>87.34999847412109</v>
       </c>
       <c r="AL117" t="n">
-        <v>30.51562881469727</v>
+        <v>30.51562690734863</v>
       </c>
       <c r="AM117" t="n">
         <v>-0.1643961174722396</v>
       </c>
       <c r="AN117" t="n">
-        <v>1.391889031911913</v>
+        <v>1.391889181414537</v>
       </c>
       <c r="AO117" t="n">
         <v>45.22904060383183</v>
       </c>
       <c r="AP117" t="n">
-        <v>1343300</v>
+        <v>1342200</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1321656</v>
+        <v>1321634</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.016376424727766</v>
+        <v>1.015561040348538</v>
       </c>
       <c r="AS117" t="n">
         <v>-0.1411930850879041</v>
@@ -23056,13 +23056,13 @@
         <v>0.2556006581605916</v>
       </c>
       <c r="AW117" t="n">
-        <v>-0.04107715509300514</v>
+        <v>-0.04107725120863348</v>
       </c>
       <c r="AX117" t="n">
         <v>0.9704226876518129</v>
       </c>
       <c r="AY117" t="n">
-        <v>40.8359698702321</v>
+        <v>40.83597272878649</v>
       </c>
       <c r="AZ117" t="inlineStr"/>
       <c r="BA117" t="n">
@@ -23231,13 +23231,13 @@
         <v>48.57101572785252</v>
       </c>
       <c r="AP118" t="n">
-        <v>9767600</v>
+        <v>9766000</v>
       </c>
       <c r="AQ118" t="n">
-        <v>9599456</v>
+        <v>9599424</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.017515992572912</v>
+        <v>1.017352707829136</v>
       </c>
       <c r="AS118" t="n">
         <v>-0.05026089617189766</v>
@@ -23249,16 +23249,16 @@
         <v>0.7089853707651266</v>
       </c>
       <c r="AV118" t="n">
-        <v>0.3975623103501944</v>
+        <v>0.3975622086606656</v>
       </c>
       <c r="AW118" t="n">
-        <v>0.7953506849187024</v>
+        <v>0.7953500136563063</v>
       </c>
       <c r="AX118" t="n">
         <v>0.6701885283684721</v>
       </c>
       <c r="AY118" t="n">
-        <v>425.2506751912186</v>
+        <v>425.2506012895879</v>
       </c>
       <c r="AZ118" t="inlineStr"/>
       <c r="BA118" t="n">
@@ -23423,13 +23423,13 @@
         <v>47.2850137831924</v>
       </c>
       <c r="AP119" t="n">
-        <v>1156100</v>
+        <v>1152900</v>
       </c>
       <c r="AQ119" t="n">
-        <v>925248</v>
+        <v>925184</v>
       </c>
       <c r="AR119" t="n">
-        <v>1.249502835996403</v>
+        <v>1.246130499446596</v>
       </c>
       <c r="AS119" t="n">
         <v>-0.1438211002155383</v>
@@ -23450,7 +23450,7 @@
         <v>1.421273410313223</v>
       </c>
       <c r="AY119" t="n">
-        <v>133.1547770563116</v>
+        <v>133.1547618913046</v>
       </c>
       <c r="AZ119" t="inlineStr"/>
       <c r="BA119" t="n">
@@ -23557,7 +23557,7 @@
         </is>
       </c>
       <c r="X120" t="n">
-        <v>497080074240</v>
+        <v>496933699584</v>
       </c>
       <c r="Y120" t="inlineStr">
         <is>
@@ -23568,7 +23568,7 @@
         <v>0.03132537752389908</v>
       </c>
       <c r="AA120" t="n">
-        <v>15571220985.17578</v>
+        <v>15566635743.81665</v>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>1.115064724598368</v>
       </c>
       <c r="AW120" t="n">
-        <v>3.574250339964125</v>
+        <v>3.574251068894228</v>
       </c>
       <c r="AX120" t="n">
         <v>0.3349349892334681</v>
@@ -23784,16 +23784,16 @@
         <v>67.07905227661132</v>
       </c>
       <c r="AG121" t="n">
-        <v>59.81053583145142</v>
+        <v>59.8105358505249</v>
       </c>
       <c r="AH121" t="n">
         <v>0.04458839707334028</v>
       </c>
       <c r="AI121" t="n">
-        <v>0.1715327194573946</v>
+        <v>0.1715327190837947</v>
       </c>
       <c r="AJ121" t="n">
-        <v>0.1215256868061321</v>
+        <v>0.1215256864484793</v>
       </c>
       <c r="AK121" t="n">
         <v>79.79306793212891</v>
@@ -23829,16 +23829,16 @@
         <v>0.3365105275025644</v>
       </c>
       <c r="AV121" t="n">
-        <v>-0.05525478052623667</v>
+        <v>-0.05525468334388395</v>
       </c>
       <c r="AW121" t="n">
-        <v>0.5925124191039448</v>
+        <v>0.5925125571721426</v>
       </c>
       <c r="AX121" t="n">
-        <v>0.3195294114266503</v>
+        <v>0.3195295062174404</v>
       </c>
       <c r="AY121" t="n">
-        <v>5.336686366292295</v>
+        <v>5.336685273286872</v>
       </c>
       <c r="AZ121" t="inlineStr"/>
       <c r="BA121" t="n">
@@ -23973,19 +23973,19 @@
         <v>77.37999725341797</v>
       </c>
       <c r="AF122" t="n">
-        <v>71.46960021972656</v>
+        <v>72.49980026245117</v>
       </c>
       <c r="AG122" t="n">
-        <v>46.40537364959717</v>
+        <v>46.85472559928894</v>
       </c>
       <c r="AH122" t="n">
-        <v>0.08269805645365924</v>
+        <v>0.0673132473924114</v>
       </c>
       <c r="AI122" t="n">
-        <v>0.6674792414712016</v>
+        <v>0.6514875770522552</v>
       </c>
       <c r="AJ122" t="n">
-        <v>0.5401147453177972</v>
+        <v>0.5473316583365375</v>
       </c>
       <c r="AK122" t="n">
         <v>88</v>
@@ -24000,37 +24000,37 @@
         <v>1.493218922586658</v>
       </c>
       <c r="AO122" t="n">
-        <v>50.43644225732518</v>
+        <v>45.18983633728305</v>
       </c>
       <c r="AP122" t="n">
         <v>2824473</v>
       </c>
       <c r="AQ122" t="n">
-        <v>6130540.08</v>
+        <v>6042352.32</v>
       </c>
       <c r="AR122" t="n">
-        <v>0.4607217248631054</v>
+        <v>0.4674459300645348</v>
       </c>
       <c r="AS122" t="n">
-        <v>-0.1206818493929777</v>
+        <v>0.001034853796921587</v>
       </c>
       <c r="AT122" t="n">
-        <v>0.9272725856197606</v>
+        <v>1.02221347151912</v>
       </c>
       <c r="AU122" t="n">
-        <v>1.037774065048793</v>
+        <v>0.8643256482957966</v>
       </c>
       <c r="AV122" t="n">
-        <v>1.112296474355136</v>
+        <v>1.101480247038667</v>
       </c>
       <c r="AW122" t="n">
-        <v>1.559822065460351</v>
+        <v>1.509800646396063</v>
       </c>
       <c r="AX122" t="n">
         <v>1.037774065048793</v>
       </c>
       <c r="AY122" t="n">
-        <v>0.5315922632350845</v>
+        <v>0.5315923788776529</v>
       </c>
       <c r="AZ122" t="inlineStr"/>
       <c r="BA122" t="n">
@@ -24145,10 +24145,10 @@
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>0.1036892607808113</v>
+        <v>0.1037075445055962</v>
       </c>
       <c r="AA123" t="n">
-        <v>3326523387.711548</v>
+        <v>3327109959.914429</v>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
@@ -24556,28 +24556,28 @@
         <v>711.5302380371094</v>
       </c>
       <c r="AG125" t="n">
-        <v>537.9320042419433</v>
+        <v>537.9320048522949</v>
       </c>
       <c r="AH125" t="n">
         <v>-0.06074266161582509</v>
       </c>
       <c r="AI125" t="n">
-        <v>0.2423689096178239</v>
+        <v>0.2423689082082001</v>
       </c>
       <c r="AJ125" t="n">
-        <v>0.3227140836132285</v>
+        <v>0.3227140821124428</v>
       </c>
       <c r="AK125" t="n">
         <v>785.1200561523438</v>
       </c>
       <c r="AL125" t="n">
-        <v>372.1830444335938</v>
+        <v>372.1830749511719</v>
       </c>
       <c r="AM125" t="n">
         <v>-0.1487798683505855</v>
       </c>
       <c r="AN125" t="n">
-        <v>0.7956486937110754</v>
+        <v>0.7956485464748011</v>
       </c>
       <c r="AO125" t="n">
         <v>47.25031454374459</v>
@@ -24598,19 +24598,19 @@
         <v>0.1922517293467882</v>
       </c>
       <c r="AU125" t="n">
-        <v>0.5844138498860121</v>
+        <v>0.5844139645189435</v>
       </c>
       <c r="AV125" t="n">
-        <v>0.7912726264996539</v>
+        <v>0.7912724799801465</v>
       </c>
       <c r="AW125" t="n">
-        <v>6.302162604561954</v>
+        <v>6.302161995845448</v>
       </c>
       <c r="AX125" t="n">
         <v>0.5205226849628715</v>
       </c>
       <c r="AY125" t="n">
-        <v>89.87554610196713</v>
+        <v>89.87553431733203</v>
       </c>
       <c r="AZ125" t="inlineStr"/>
       <c r="BA125" t="n">
@@ -24750,16 +24750,16 @@
         <v>324.550894165039</v>
       </c>
       <c r="AG126" t="n">
-        <v>232.3926043701172</v>
+        <v>232.3926042938232</v>
       </c>
       <c r="AH126" t="n">
         <v>-0.07401272286597727</v>
       </c>
       <c r="AI126" t="n">
-        <v>0.2931994957148529</v>
+        <v>0.2931994961394073</v>
       </c>
       <c r="AJ126" t="n">
-        <v>0.3965629200839245</v>
+        <v>0.3965629205424128</v>
       </c>
       <c r="AK126" t="n">
         <v>376.1517333984375</v>
@@ -24777,13 +24777,13 @@
         <v>50.61010598879461</v>
       </c>
       <c r="AP126" t="n">
-        <v>5906900</v>
+        <v>5898700</v>
       </c>
       <c r="AQ126" t="n">
-        <v>6492580</v>
+        <v>6492416</v>
       </c>
       <c r="AR126" t="n">
-        <v>0.909792409180942</v>
+        <v>0.9085523786522613</v>
       </c>
       <c r="AS126" t="n">
         <v>-0.09307108518251406</v>
@@ -24792,19 +24792,19 @@
         <v>0.1504172230224399</v>
       </c>
       <c r="AU126" t="n">
-        <v>0.8558366387907679</v>
+        <v>0.8558364639222265</v>
       </c>
       <c r="AV126" t="n">
-        <v>1.419858891465606</v>
+        <v>1.419858742809654</v>
       </c>
       <c r="AW126" t="n">
-        <v>10.12216872739327</v>
+        <v>10.12216715720711</v>
       </c>
       <c r="AX126" t="n">
-        <v>0.7121124652229793</v>
+        <v>0.7121123163908207</v>
       </c>
       <c r="AY126" t="n">
-        <v>29.24307471368612</v>
+        <v>29.24307761613235</v>
       </c>
       <c r="AZ126" t="inlineStr"/>
       <c r="BA126" t="n">
@@ -24939,19 +24939,19 @@
         <v>284.1000061035156</v>
       </c>
       <c r="AF127" t="n">
-        <v>265.9569982910156</v>
+        <v>267.2629986572265</v>
       </c>
       <c r="AG127" t="n">
-        <v>241.4760266113281</v>
+        <v>241.9940156555176</v>
       </c>
       <c r="AH127" t="n">
-        <v>0.06821782441929791</v>
+        <v>0.06299789918874277</v>
       </c>
       <c r="AI127" t="n">
-        <v>0.1765143318379743</v>
+        <v>0.1739959987603024</v>
       </c>
       <c r="AJ127" t="n">
-        <v>0.1013805470598175</v>
+        <v>0.1044198672982053</v>
       </c>
       <c r="AK127" t="n">
         <v>284.1000061035156</v>
@@ -24966,31 +24966,31 @@
         <v>0.3943558581767639</v>
       </c>
       <c r="AO127" t="n">
-        <v>73.18841901754374</v>
+        <v>61.70213981688395</v>
       </c>
       <c r="AP127" t="n">
         <v>707250</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1105966.86</v>
+        <v>1101615.7</v>
       </c>
       <c r="AR127" t="n">
-        <v>0.6394857075554686</v>
+        <v>0.64201154722105</v>
       </c>
       <c r="AS127" t="n">
-        <v>0.03309093128551144</v>
+        <v>0.0569197135616355</v>
       </c>
       <c r="AT127" t="n">
-        <v>0.319247727195108</v>
+        <v>0.352857171921503</v>
       </c>
       <c r="AU127" t="n">
-        <v>0.2034005082147816</v>
+        <v>0.1720455463374886</v>
       </c>
       <c r="AV127" t="n">
-        <v>0.3110703852997252</v>
+        <v>0.3287834381894588</v>
       </c>
       <c r="AW127" t="n">
-        <v>1.41238643499413</v>
+        <v>1.404848761960855</v>
       </c>
       <c r="AX127" t="n">
         <v>0.2034005082147816</v>
@@ -25182,13 +25182,13 @@
         <v>1.253560748298407</v>
       </c>
       <c r="AW128" t="n">
-        <v>3.200177390491762</v>
+        <v>3.200176897654452</v>
       </c>
       <c r="AX128" t="n">
         <v>0.8432040696170966</v>
       </c>
       <c r="AY128" t="n">
-        <v>128.6852234187422</v>
+        <v>128.6851940537917</v>
       </c>
       <c r="AZ128" t="inlineStr"/>
       <c r="BA128" t="n">
@@ -25770,13 +25770,13 @@
         <v>2.148141412687131</v>
       </c>
       <c r="AW131" t="n">
-        <v>4.342259145125073</v>
+        <v>4.342258764376019</v>
       </c>
       <c r="AX131" t="n">
         <v>1.000663428670688</v>
       </c>
       <c r="AY131" t="n">
-        <v>26.01420712070624</v>
+        <v>26.01421198862695</v>
       </c>
       <c r="AZ131" t="inlineStr"/>
       <c r="BA131" t="n">
@@ -25918,16 +25918,16 @@
         <v>418.8306805419922</v>
       </c>
       <c r="AG132" t="n">
-        <v>342.5128746032715</v>
+        <v>342.5128793334961</v>
       </c>
       <c r="AH132" t="n">
         <v>0.03660028701880225</v>
       </c>
       <c r="AI132" t="n">
-        <v>0.2675728004822933</v>
+        <v>0.2675727829766623</v>
       </c>
       <c r="AJ132" t="n">
-        <v>0.2228173350479707</v>
+        <v>0.2228173181604287</v>
       </c>
       <c r="AK132" t="n">
         <v>477.5700073242188</v>
@@ -25945,13 +25945,13 @@
         <v>53.1082295150535</v>
       </c>
       <c r="AP132" t="n">
-        <v>18424800</v>
+        <v>18375000</v>
       </c>
       <c r="AQ132" t="n">
-        <v>14078592</v>
+        <v>14077596</v>
       </c>
       <c r="AR132" t="n">
-        <v>1.308710416496195</v>
+        <v>1.305265472883296</v>
       </c>
       <c r="AS132" t="n">
         <v>-0.003465320110792702</v>
@@ -25966,13 +25966,13 @@
         <v>0.8791163504878894</v>
       </c>
       <c r="AW132" t="n">
-        <v>3.041808040500598</v>
+        <v>3.041808614645729</v>
       </c>
       <c r="AX132" t="n">
         <v>0.3654235008760789</v>
       </c>
       <c r="AY132" t="n">
-        <v>138.024466104924</v>
+        <v>138.0244448772366</v>
       </c>
       <c r="AZ132" t="inlineStr"/>
       <c r="BA132" t="n">
@@ -26158,13 +26158,13 @@
         <v>0.9010061486864169</v>
       </c>
       <c r="AW133" t="n">
-        <v>2.292347112698032</v>
+        <v>2.292347451768185</v>
       </c>
       <c r="AX133" t="n">
         <v>0.7685056729336115</v>
       </c>
       <c r="AY133" t="n">
-        <v>330.9221549503248</v>
+        <v>330.9220741781184</v>
       </c>
       <c r="AZ133" t="inlineStr"/>
       <c r="BA133" t="n">
@@ -26333,13 +26333,13 @@
         <v>54.8805012934833</v>
       </c>
       <c r="AP134" t="n">
-        <v>15096100</v>
+        <v>15071700</v>
       </c>
       <c r="AQ134" t="n">
-        <v>9723142</v>
+        <v>9722654</v>
       </c>
       <c r="AR134" t="n">
-        <v>1.552594829942831</v>
+        <v>1.550163155039766</v>
       </c>
       <c r="AS134" t="n">
         <v>0.2042254752827843</v>
@@ -26351,16 +26351,16 @@
         <v>1.352397752602464</v>
       </c>
       <c r="AV134" t="n">
-        <v>2.197009564375317</v>
+        <v>2.197009305755499</v>
       </c>
       <c r="AW134" t="n">
-        <v>3.61843579708243</v>
+        <v>3.618436336796621</v>
       </c>
       <c r="AX134" t="n">
         <v>1.248457290219689</v>
       </c>
       <c r="AY134" t="n">
-        <v>8739.124353280527</v>
+        <v>8739.125297079028</v>
       </c>
       <c r="AZ134" t="inlineStr"/>
       <c r="BA134" t="n">
@@ -26502,16 +26502,16 @@
         <v>1646.9611328125</v>
       </c>
       <c r="AG135" t="n">
-        <v>1311.797275085449</v>
+        <v>1311.797276000977</v>
       </c>
       <c r="AH135" t="n">
         <v>0.07429368613429976</v>
       </c>
       <c r="AI135" t="n">
-        <v>0.3487754395387128</v>
+        <v>0.3487754385973776</v>
       </c>
       <c r="AJ135" t="n">
-        <v>0.2554997361960663</v>
+        <v>0.2554997353198298</v>
       </c>
       <c r="AK135" t="n">
         <v>1989.43994140625</v>
@@ -26529,13 +26529,13 @@
         <v>43.40240321663092</v>
       </c>
       <c r="AP135" t="n">
-        <v>2701000</v>
+        <v>2699100</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1937968</v>
+        <v>1937930</v>
       </c>
       <c r="AR135" t="n">
-        <v>1.393727863411573</v>
+        <v>1.392774764826387</v>
       </c>
       <c r="AS135" t="n">
         <v>0.02488470614589189</v>
@@ -26547,7 +26547,7 @@
         <v>0.6595847657205354</v>
       </c>
       <c r="AV135" t="n">
-        <v>1.230124274730702</v>
+        <v>1.230124446296949</v>
       </c>
       <c r="AW135" t="n">
         <v>1.698998871372392</v>
@@ -26556,7 +26556,7 @@
         <v>0.525651982021345</v>
       </c>
       <c r="AY135" t="n">
-        <v>1003.135133931984</v>
+        <v>1003.13493012962</v>
       </c>
       <c r="AZ135" t="inlineStr"/>
       <c r="BA135" t="n">
@@ -26698,16 +26698,16 @@
         <v>208.7226901245117</v>
       </c>
       <c r="AG136" t="n">
-        <v>151.70390209198</v>
+        <v>151.703902053833</v>
       </c>
       <c r="AH136" t="n">
         <v>0.1285308890530421</v>
       </c>
       <c r="AI136" t="n">
-        <v>0.5526957435079085</v>
+        <v>0.5526957438983442</v>
       </c>
       <c r="AJ136" t="n">
-        <v>0.3758557772492928</v>
+        <v>0.3758557775952609</v>
       </c>
       <c r="AK136" t="n">
         <v>301.7099914550781</v>
@@ -26725,13 +26725,13 @@
         <v>48.84278947876633</v>
       </c>
       <c r="AP136" t="n">
-        <v>23648900</v>
+        <v>23622500</v>
       </c>
       <c r="AQ136" t="n">
-        <v>12816654</v>
+        <v>12816126</v>
       </c>
       <c r="AR136" t="n">
-        <v>1.845169573899709</v>
+        <v>1.843185686532732</v>
       </c>
       <c r="AS136" t="n">
         <v>0.108413217634858</v>
@@ -26740,7 +26740,7 @@
         <v>0.5548814973593614</v>
       </c>
       <c r="AU136" t="n">
-        <v>0.9435517808698641</v>
+        <v>0.9435519032185244</v>
       </c>
       <c r="AV136" t="n">
         <v>1.573750421816833</v>
@@ -26921,13 +26921,13 @@
         <v>50.69820160606887</v>
       </c>
       <c r="AP137" t="n">
-        <v>1968000</v>
+        <v>1966900</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1310700</v>
+        <v>1310678</v>
       </c>
       <c r="AR137" t="n">
-        <v>1.501487754634928</v>
+        <v>1.500673697124694</v>
       </c>
       <c r="AS137" t="n">
         <v>0.09857837882321263</v>
@@ -27105,25 +27105,25 @@
         <v>483.8399963378906</v>
       </c>
       <c r="AL138" t="n">
-        <v>89.91980743408203</v>
+        <v>89.9197998046875</v>
       </c>
       <c r="AM138" t="n">
         <v>-0.2371651803664948</v>
       </c>
       <c r="AN138" t="n">
-        <v>3.104657326011973</v>
+        <v>3.10465767427843</v>
       </c>
       <c r="AO138" t="n">
         <v>48.49455833973641</v>
       </c>
       <c r="AP138" t="n">
-        <v>5938000</v>
+        <v>5932300</v>
       </c>
       <c r="AQ138" t="n">
-        <v>4702844</v>
+        <v>4702730</v>
       </c>
       <c r="AR138" t="n">
-        <v>1.262640223660406</v>
+        <v>1.261458769693348</v>
       </c>
       <c r="AS138" t="n">
         <v>-0.09905537569203138</v>
@@ -27138,13 +27138,13 @@
         <v>2.929017194325826</v>
       </c>
       <c r="AW138" t="n">
-        <v>1.905111010051884</v>
+        <v>1.905110835596957</v>
       </c>
       <c r="AX138" t="n">
         <v>0.7796481328421168</v>
       </c>
       <c r="AY138" t="n">
-        <v>330.3906075904007</v>
+        <v>330.3905721206472</v>
       </c>
       <c r="AZ138" t="inlineStr"/>
       <c r="BA138" t="n">
@@ -27309,13 +27309,13 @@
         <v>59.85700141326977</v>
       </c>
       <c r="AP139" t="n">
-        <v>21014000</v>
+        <v>21004300</v>
       </c>
       <c r="AQ139" t="n">
-        <v>17731794</v>
+        <v>17731600</v>
       </c>
       <c r="AR139" t="n">
-        <v>1.185102872275642</v>
+        <v>1.184568792438359</v>
       </c>
       <c r="AS139" t="n">
         <v>0.1456583019664124</v>
@@ -27330,7 +27330,7 @@
         <v>2.122137468025066</v>
       </c>
       <c r="AW139" t="n">
-        <v>2.461462825373199</v>
+        <v>2.461463291007445</v>
       </c>
       <c r="AX139" t="n">
         <v>2.130102096672406</v>
@@ -27666,16 +27666,16 @@
         <v>73718.2</v>
       </c>
       <c r="AG141" t="n">
-        <v>61171.60685546875</v>
+        <v>61171.60681640625</v>
       </c>
       <c r="AH141" t="n">
         <v>0.03895645851363705</v>
       </c>
       <c r="AI141" t="n">
-        <v>0.2520514653303216</v>
+        <v>0.2520514661298472</v>
       </c>
       <c r="AJ141" t="n">
-        <v>0.2051048483028295</v>
+        <v>0.2051048490723761</v>
       </c>
       <c r="AK141" t="n">
         <v>88480</v>
@@ -27714,13 +27714,13 @@
         <v>1.138982875189889</v>
       </c>
       <c r="AW141" t="n">
-        <v>6.635624846904223</v>
+        <v>6.635624103513569</v>
       </c>
       <c r="AX141" t="n">
         <v>0.5073447446536921</v>
       </c>
       <c r="AY141" t="n">
-        <v>51.40803111946027</v>
+        <v>51.40803987461334</v>
       </c>
       <c r="AZ141" t="inlineStr"/>
       <c r="BA141" t="n">
@@ -27858,16 +27858,16 @@
         <v>28551.6</v>
       </c>
       <c r="AG142" t="n">
-        <v>22980.15449707031</v>
+        <v>22980.15448730469</v>
       </c>
       <c r="AH142" t="n">
         <v>0.02778828506983855</v>
       </c>
       <c r="AI142" t="n">
-        <v>0.2769713973742487</v>
+        <v>0.2769713979169091</v>
       </c>
       <c r="AJ142" t="n">
-        <v>0.2424459549930345</v>
+        <v>0.242445955521023</v>
       </c>
       <c r="AK142" t="n">
         <v>35900</v>
@@ -27906,7 +27906,7 @@
         <v>2.032332706838049</v>
       </c>
       <c r="AW142" t="n">
-        <v>12.10179158757624</v>
+        <v>12.10179301570498</v>
       </c>
       <c r="AX142" t="n">
         <v>0.3877186771459102</v>
@@ -28050,28 +28050,28 @@
         <v>44245.3728125</v>
       </c>
       <c r="AG143" t="n">
-        <v>33154.52732910156</v>
+        <v>33154.52735839844</v>
       </c>
       <c r="AH143" t="n">
         <v>0.07694877387355059</v>
       </c>
       <c r="AI143" t="n">
-        <v>0.4372094503719546</v>
+        <v>0.4372094491019696</v>
       </c>
       <c r="AJ143" t="n">
-        <v>0.3345197889056735</v>
+        <v>0.3345197877264299</v>
       </c>
       <c r="AK143" t="n">
         <v>57263.48828125</v>
       </c>
       <c r="AL143" t="n">
-        <v>14136.361328125</v>
+        <v>14136.3603515625</v>
       </c>
       <c r="AM143" t="n">
         <v>-0.1678816392398816</v>
       </c>
       <c r="AN143" t="n">
-        <v>2.370740100226353</v>
+        <v>2.370740333082498</v>
       </c>
       <c r="AO143" t="n">
         <v>49.30773932179242</v>
@@ -28098,13 +28098,13 @@
         <v>1.999475023021531</v>
       </c>
       <c r="AW143" t="n">
-        <v>1.873559969168782</v>
+        <v>1.873558953788407</v>
       </c>
       <c r="AX143" t="n">
         <v>0.5086245278127912</v>
       </c>
       <c r="AY143" t="n">
-        <v>366.2273403876761</v>
+        <v>366.227469941008</v>
       </c>
       <c r="AZ143" t="inlineStr"/>
       <c r="BA143" t="n">
@@ -28273,13 +28273,13 @@
         <v>38.6930032830109</v>
       </c>
       <c r="AP144" t="n">
-        <v>3796900</v>
+        <v>3792500</v>
       </c>
       <c r="AQ144" t="n">
-        <v>4974334</v>
+        <v>4974246</v>
       </c>
       <c r="AR144" t="n">
-        <v>0.7632981621258242</v>
+        <v>0.7624271095559005</v>
       </c>
       <c r="AS144" t="n">
         <v>-0.1866421221712389</v>
@@ -28463,13 +28463,13 @@
         <v>33.3573114875642</v>
       </c>
       <c r="AP145" t="n">
-        <v>671900</v>
+        <v>671100</v>
       </c>
       <c r="AQ145" t="n">
-        <v>510458</v>
+        <v>510442</v>
       </c>
       <c r="AR145" t="n">
-        <v>1.316268919284251</v>
+        <v>1.314742909086635</v>
       </c>
       <c r="AS145" t="n">
         <v>-0.2232215733412939</v>
@@ -28490,7 +28490,7 @@
         <v>0.2337662337662338</v>
       </c>
       <c r="AY145" t="n">
-        <v>24.62712080681601</v>
+        <v>24.62711641155389</v>
       </c>
       <c r="AZ145" t="inlineStr"/>
       <c r="BA145" t="n">
@@ -28680,13 +28680,13 @@
         <v>0.3475263935133022</v>
       </c>
       <c r="AW146" t="n">
-        <v>1.302541498850832</v>
+        <v>1.302541355171023</v>
       </c>
       <c r="AX146" t="n">
         <v>0.1575880559526486</v>
       </c>
       <c r="AY146" t="n">
-        <v>44.58108650003868</v>
+        <v>44.58107242368865</v>
       </c>
       <c r="AZ146" t="inlineStr"/>
       <c r="BA146" t="n">
@@ -28872,13 +28872,13 @@
         <v>0.4131853059356814</v>
       </c>
       <c r="AW147" t="n">
-        <v>4.159402240293756</v>
+        <v>4.15940331769528</v>
       </c>
       <c r="AX147" t="n">
         <v>0.3610108303249098</v>
       </c>
       <c r="AY147" t="n">
-        <v>18.00702635566122</v>
+        <v>18.00702270015946</v>
       </c>
       <c r="AZ147" t="inlineStr"/>
       <c r="BA147" t="n">
@@ -29070,7 +29070,7 @@
         <v>0.209259605048675</v>
       </c>
       <c r="AY148" t="n">
-        <v>61.77581364783913</v>
+        <v>61.77580793730989</v>
       </c>
       <c r="AZ148" t="inlineStr"/>
       <c r="BA148" t="n">
@@ -29262,7 +29262,7 @@
         <v>0.2566967994041647</v>
       </c>
       <c r="AY149" t="n">
-        <v>11.08041490377719</v>
+        <v>11.08041564397574</v>
       </c>
       <c r="AZ149" t="inlineStr"/>
       <c r="BA149" t="n">
@@ -29452,7 +29452,7 @@
         <v>0.6505246649713299</v>
       </c>
       <c r="AW150" t="n">
-        <v>1.571705671736086</v>
+        <v>1.571705461930289</v>
       </c>
       <c r="AX150" t="n">
         <v>0.06750867696625695</v>
@@ -29650,7 +29650,7 @@
         <v>0.5173961757980359</v>
       </c>
       <c r="AY151" t="n">
-        <v>7.615742226884246</v>
+        <v>7.615743274106462</v>
       </c>
       <c r="AZ151" t="inlineStr"/>
       <c r="BA151" t="n">
@@ -29842,7 +29842,7 @@
         <v>0.02580645161290329</v>
       </c>
       <c r="AY152" t="n">
-        <v>30.95734307776219</v>
+        <v>30.95734614053186</v>
       </c>
       <c r="AZ152" t="inlineStr"/>
       <c r="BA152" t="n">
@@ -30199,13 +30199,13 @@
         <v>35.3996370484801</v>
       </c>
       <c r="AP154" t="n">
-        <v>2135000</v>
+        <v>2132800</v>
       </c>
       <c r="AQ154" t="n">
-        <v>2238368</v>
+        <v>2238324</v>
       </c>
       <c r="AR154" t="n">
-        <v>0.9538199259460464</v>
+        <v>0.9528557974627444</v>
       </c>
       <c r="AS154" t="n">
         <v>-0.2661413962867328</v>
@@ -30368,40 +30368,40 @@
         <v>111.019400177002</v>
       </c>
       <c r="AG155" t="n">
-        <v>84.46414367675781</v>
+        <v>84.46414356231689</v>
       </c>
       <c r="AH155" t="n">
         <v>0.0150478408434993</v>
       </c>
       <c r="AI155" t="n">
-        <v>0.3341756340142168</v>
+        <v>0.3341756358218984</v>
       </c>
       <c r="AJ155" t="n">
-        <v>0.3143968001602011</v>
+        <v>0.3143968019410843</v>
       </c>
       <c r="AK155" t="n">
         <v>130</v>
       </c>
       <c r="AL155" t="n">
-        <v>65.09967041015625</v>
+        <v>65.09966278076172</v>
       </c>
       <c r="AM155" t="n">
         <v>-0.1331538273737981</v>
       </c>
       <c r="AN155" t="n">
-        <v>0.7310379873109987</v>
+        <v>0.7310381901810472</v>
       </c>
       <c r="AO155" t="n">
         <v>32.0078708937928</v>
       </c>
       <c r="AP155" t="n">
-        <v>24254900</v>
+        <v>24251000</v>
       </c>
       <c r="AQ155" t="n">
-        <v>26043220</v>
+        <v>26043142</v>
       </c>
       <c r="AR155" t="n">
-        <v>0.9313326078726056</v>
+        <v>0.9311856457258498</v>
       </c>
       <c r="AS155" t="n">
         <v>-0.1091699411746542</v>
@@ -30416,13 +30416,13 @@
         <v>0.6807674871232796</v>
       </c>
       <c r="AW155" t="n">
-        <v>1.450348582126885</v>
+        <v>1.450348175627068</v>
       </c>
       <c r="AX155" t="n">
         <v>0.4900135176031475</v>
       </c>
       <c r="AY155" t="n">
-        <v>2265.500196267729</v>
+        <v>2265.500026448751</v>
       </c>
       <c r="AZ155" t="inlineStr"/>
       <c r="BA155" t="n">
@@ -30564,16 +30564,16 @@
         <v>323.0927981567383</v>
       </c>
       <c r="AG156" t="n">
-        <v>186.1366176223755</v>
+        <v>186.1366179275513</v>
       </c>
       <c r="AH156" t="n">
         <v>0.2204543387343683</v>
       </c>
       <c r="AI156" t="n">
-        <v>1.11844403514517</v>
+        <v>1.118444031671927</v>
       </c>
       <c r="AJ156" t="n">
-        <v>0.7357831160992327</v>
+        <v>0.7357831132533716</v>
       </c>
       <c r="AK156" t="n">
         <v>465.9599914550781</v>
@@ -30591,13 +30591,13 @@
         <v>50.81575651172232</v>
       </c>
       <c r="AP156" t="n">
-        <v>6618400</v>
+        <v>6611600</v>
       </c>
       <c r="AQ156" t="n">
-        <v>9038906</v>
+        <v>9038770</v>
       </c>
       <c r="AR156" t="n">
-        <v>0.7322125044778649</v>
+        <v>0.7314712068124314</v>
       </c>
       <c r="AS156" t="n">
         <v>-0.06355082193737638</v>
@@ -30609,7 +30609,7 @@
         <v>2.155946371217874</v>
       </c>
       <c r="AV156" t="n">
-        <v>2.241947806485914</v>
+        <v>2.241947603131656</v>
       </c>
       <c r="AW156" t="n">
         <v>7.593164880563643</v>
@@ -30618,7 +30618,7 @@
         <v>2.108532938768634</v>
       </c>
       <c r="AY156" t="n">
-        <v>34.91083315579463</v>
+        <v>34.91084251251399</v>
       </c>
       <c r="AZ156" t="inlineStr"/>
       <c r="BA156" t="n">
@@ -30787,13 +30787,13 @@
         <v>41.80833574290553</v>
       </c>
       <c r="AP157" t="n">
-        <v>6570400</v>
+        <v>6566100</v>
       </c>
       <c r="AQ157" t="n">
-        <v>7755936</v>
+        <v>7755850</v>
       </c>
       <c r="AR157" t="n">
-        <v>0.8471446902088929</v>
+        <v>0.846599663479825</v>
       </c>
       <c r="AS157" t="n">
         <v>-0.1548721838517276</v>
@@ -30956,40 +30956,40 @@
         <v>39.29432300567627</v>
       </c>
       <c r="AG158" t="n">
-        <v>27.05629078865051</v>
+        <v>27.05629079818726</v>
       </c>
       <c r="AH158" t="n">
         <v>0.04926097177651956</v>
       </c>
       <c r="AI158" t="n">
-        <v>0.5238600096481576</v>
+        <v>0.5238600091110308</v>
       </c>
       <c r="AJ158" t="n">
-        <v>0.4523174411682227</v>
+        <v>0.4523174406563131</v>
       </c>
       <c r="AK158" t="n">
         <v>55.98620223999023</v>
       </c>
       <c r="AL158" t="n">
-        <v>19.40578460693359</v>
+        <v>19.40578269958496</v>
       </c>
       <c r="AM158" t="n">
         <v>-0.2635685598837375</v>
       </c>
       <c r="AN158" t="n">
-        <v>1.124624197235759</v>
+        <v>1.124624406060062</v>
       </c>
       <c r="AO158" t="n">
         <v>32.6744442052229</v>
       </c>
       <c r="AP158" t="n">
-        <v>18976700</v>
+        <v>18968400</v>
       </c>
       <c r="AQ158" t="n">
-        <v>27574312</v>
+        <v>27574146</v>
       </c>
       <c r="AR158" t="n">
-        <v>0.688202120872499</v>
+        <v>0.6879052573377975</v>
       </c>
       <c r="AS158" t="n">
         <v>-0.2502153302363888</v>
@@ -31010,7 +31010,7 @@
         <v>0.7218560211767862</v>
       </c>
       <c r="AY158" t="n">
-        <v>4.722385825546522</v>
+        <v>4.722385446832831</v>
       </c>
       <c r="AZ158" t="inlineStr"/>
       <c r="BA158" t="n">
@@ -31152,16 +31152,16 @@
         <v>359.1488330078125</v>
       </c>
       <c r="AG159" t="n">
-        <v>267.7773107910156</v>
+        <v>267.7773115539551</v>
       </c>
       <c r="AH159" t="n">
         <v>-0.04969762832128011</v>
       </c>
       <c r="AI159" t="n">
-        <v>0.2745664925260722</v>
+        <v>0.2745664888946329</v>
       </c>
       <c r="AJ159" t="n">
-        <v>0.3412220473306156</v>
+        <v>0.3412220435092641</v>
       </c>
       <c r="AK159" t="n">
         <v>385.6300048828125</v>
@@ -31203,10 +31203,10 @@
         <v>5.037030781792662</v>
       </c>
       <c r="AX159" t="n">
-        <v>0.4205431288416457</v>
+        <v>0.4205432190595371</v>
       </c>
       <c r="AY159" t="n">
-        <v>460.8585102574845</v>
+        <v>460.858361245368</v>
       </c>
       <c r="AZ159" t="inlineStr"/>
       <c r="BA159" t="n">
@@ -31371,13 +31371,13 @@
         <v>38.21423982321316</v>
       </c>
       <c r="AP160" t="n">
-        <v>680200</v>
+        <v>679600</v>
       </c>
       <c r="AQ160" t="n">
-        <v>1024498</v>
+        <v>1024486</v>
       </c>
       <c r="AR160" t="n">
-        <v>0.6639349222741284</v>
+        <v>0.6633570395300667</v>
       </c>
       <c r="AS160" t="n">
         <v>-0.310882778825431</v>
@@ -31567,13 +31567,13 @@
         <v>39.78494623655914</v>
       </c>
       <c r="AP161" t="n">
-        <v>42867500</v>
+        <v>42742400</v>
       </c>
       <c r="AQ161" t="n">
-        <v>55710920</v>
+        <v>55708418</v>
       </c>
       <c r="AR161" t="n">
-        <v>0.7694631501328645</v>
+        <v>0.7672520874672837</v>
       </c>
       <c r="AS161" t="n">
         <v>-0.4259805912185698</v>
@@ -32059,13 +32059,13 @@
         <v>55.57368157652713</v>
       </c>
       <c r="AP2" t="n">
-        <v>7258800</v>
+        <v>7247100</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6320962</v>
+        <v>6320728</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.148369504515294</v>
+        <v>1.146560965762172</v>
       </c>
       <c r="AS2" t="n">
         <v>0.117951267742004</v>
@@ -32259,13 +32259,13 @@
         <v>52.45790251046104</v>
       </c>
       <c r="AP3" t="n">
-        <v>9766500</v>
+        <v>9764500</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10197902</v>
+        <v>10197862</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9576969851249796</v>
+        <v>0.9575046220472487</v>
       </c>
       <c r="AS3" t="n">
         <v>-0.08246825730745244</v>
@@ -32461,13 +32461,13 @@
         <v>45.42335820442248</v>
       </c>
       <c r="AP4" t="n">
-        <v>7576000</v>
+        <v>7553900</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12236764</v>
+        <v>12236322</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.6191179301978856</v>
+        <v>0.6173341956839645</v>
       </c>
       <c r="AS4" t="n">
         <v>-0.2344413737245593</v>
@@ -32634,16 +32634,16 @@
         <v>408.8887963867188</v>
       </c>
       <c r="AG5" t="n">
-        <v>360.1986968994141</v>
+        <v>360.1986970520019</v>
       </c>
       <c r="AH5" t="n">
         <v>-0.1184644446307477</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0006977129839182972</v>
+        <v>0.0006977125600013956</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.1351756680588476</v>
+        <v>0.135175667577963</v>
       </c>
       <c r="AK5" t="n">
         <v>480.8090515136719</v>
@@ -32661,13 +32661,13 @@
         <v>41.6450519969167</v>
       </c>
       <c r="AP5" t="n">
-        <v>26788900</v>
+        <v>26749500</v>
       </c>
       <c r="AQ5" t="n">
-        <v>27281432</v>
+        <v>27280644</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9819462556071104</v>
+        <v>0.9805303716437193</v>
       </c>
       <c r="AS5" t="n">
         <v>-0.2466655334868972</v>
@@ -32682,13 +32682,13 @@
         <v>0.345279986806007</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.566255575012773</v>
+        <v>7.566256351612312</v>
       </c>
       <c r="AX5" t="n">
         <v>0.04072788759895696</v>
       </c>
       <c r="AY5" t="n">
-        <v>316.4116836894942</v>
+        <v>316.4117503304105</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -32863,13 +32863,13 @@
         <v>45.1306306405907</v>
       </c>
       <c r="AP6" t="n">
-        <v>9061700</v>
+        <v>9047500</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8678232</v>
+        <v>8677948</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.044187341384743</v>
+        <v>1.042585182580029</v>
       </c>
       <c r="AS6" t="n">
         <v>0.127260003643338</v>
@@ -33036,16 +33036,16 @@
         <v>320.9159280395508</v>
       </c>
       <c r="AG7" t="n">
-        <v>222.4916584777832</v>
+        <v>222.4916589736939</v>
       </c>
       <c r="AH7" t="n">
         <v>0.09502200719311249</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.5794300157873076</v>
+        <v>0.5794300122669231</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.4423728522460346</v>
+        <v>0.4423728490311363</v>
       </c>
       <c r="AK7" t="n">
         <v>433.3299865722656</v>
@@ -33063,13 +33063,13 @@
         <v>48.27151631497328</v>
       </c>
       <c r="AP7" t="n">
-        <v>18973400</v>
+        <v>18954700</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11511062</v>
+        <v>11510688</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.64827537198566</v>
+        <v>1.646704349905062</v>
       </c>
       <c r="AS7" t="n">
         <v>0.02312283663775716</v>
@@ -33078,7 +33078,7 @@
         <v>0.609858707847909</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.056775748092817</v>
+        <v>1.056775931780431</v>
       </c>
       <c r="AV7" t="n">
         <v>2.575380862185094</v>
@@ -33207,7 +33207,7 @@
         </is>
       </c>
       <c r="X8" t="n">
-        <v>214764421120</v>
+        <v>214579691520</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -33218,7 +33218,7 @@
         <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>214764421120</v>
+        <v>214579691520</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -33238,40 +33238,40 @@
         <v>223.6270001220703</v>
       </c>
       <c r="AG8" t="n">
-        <v>122.570412902832</v>
+        <v>122.570412940979</v>
       </c>
       <c r="AH8" t="n">
         <v>0.0968710985356751</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.001216994190817</v>
+        <v>1.001216993567988</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.8244778232031502</v>
+        <v>0.8244778226353273</v>
       </c>
       <c r="AK8" t="n">
         <v>316.4299926757812</v>
       </c>
       <c r="AL8" t="n">
-        <v>62.19286727905273</v>
+        <v>62.19287109375</v>
       </c>
       <c r="AM8" t="n">
         <v>-0.2248206587121453</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.944021300473942</v>
+        <v>2.944021058561211</v>
       </c>
       <c r="AO8" t="n">
         <v>42.26502405412126</v>
       </c>
       <c r="AP8" t="n">
-        <v>38579900</v>
+        <v>38435900</v>
       </c>
       <c r="AQ8" t="n">
-        <v>46066822</v>
+        <v>46063942</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.837476915598823</v>
+        <v>0.8344031867702508</v>
       </c>
       <c r="AS8" t="n">
         <v>-0.1868390576851539</v>
@@ -33286,13 +33286,13 @@
         <v>2.312499864772374</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.442106225952319</v>
+        <v>3.44210591907973</v>
       </c>
       <c r="AX8" t="n">
         <v>1.747391867747758</v>
       </c>
       <c r="AY8" t="n">
-        <v>19.21793423424472</v>
+        <v>19.21793741275688</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
@@ -33463,13 +33463,13 @@
         <v>48.40296980201639</v>
       </c>
       <c r="AP9" t="n">
-        <v>24901800</v>
+        <v>24804700</v>
       </c>
       <c r="AQ9" t="n">
-        <v>18035690</v>
+        <v>18033748</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.380695720540772</v>
+        <v>1.375460054116316</v>
       </c>
       <c r="AS9" t="n">
         <v>-0.1432771718372023</v>
@@ -33746,31 +33746,31 @@
         <v>0.5855327608553891</v>
       </c>
       <c r="N2" t="n">
-        <v>1.558904258970915</v>
+        <v>1.558904253167344</v>
       </c>
       <c r="O2" t="n">
         <v>1.573750421816833</v>
       </c>
       <c r="P2" t="n">
-        <v>1.271137161797991</v>
+        <v>1.271137160265251</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.946230280308651</v>
+        <v>3.946230354074183</v>
       </c>
       <c r="R2" t="n">
-        <v>2.975068962344419</v>
+        <v>2.975069249416984</v>
       </c>
       <c r="S2" t="n">
-        <v>3.480837399144012</v>
+        <v>3.480837768833038</v>
       </c>
       <c r="T2" t="n">
-        <v>994.390726651143</v>
+        <v>994.390776071652</v>
       </c>
       <c r="U2" t="n">
-        <v>51.40803111946027</v>
+        <v>51.40803987461334</v>
       </c>
       <c r="V2" t="n">
-        <v>1443.321299213546</v>
+        <v>1443.321358357945</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -33821,31 +33821,31 @@
         <v>2.224162358902581</v>
       </c>
       <c r="N3" t="n">
-        <v>5.833799056587742</v>
+        <v>5.833799141241116</v>
       </c>
       <c r="O3" t="n">
         <v>7.050092846066804</v>
       </c>
       <c r="P3" t="n">
-        <v>5.434614243215017</v>
+        <v>5.434614276466509</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.73330554614082</v>
+        <v>5.733305291884924</v>
       </c>
       <c r="R3" t="n">
-        <v>5.399912887237076</v>
+        <v>5.399913353698032</v>
       </c>
       <c r="S3" t="n">
-        <v>6.552021755679464</v>
+        <v>6.552021576180151</v>
       </c>
       <c r="T3" t="n">
-        <v>37.74563731290523</v>
+        <v>37.74563414765914</v>
       </c>
       <c r="U3" t="n">
-        <v>32.72988470878067</v>
+        <v>32.72988173426776</v>
       </c>
       <c r="V3" t="n">
-        <v>52.27331127011278</v>
+        <v>52.27330676742979</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -33887,13 +33887,13 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7516421872598474</v>
+        <v>0.7516421711704484</v>
       </c>
       <c r="L4" t="n">
         <v>0.3443674746027734</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3341638738715354</v>
+        <v>0.3341638228487089</v>
       </c>
       <c r="N4" t="n">
         <v>1.488481097747107</v>
@@ -33905,22 +33905,22 @@
         <v>0.7836050810497953</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.759472036430963</v>
+        <v>4.759471981560398</v>
       </c>
       <c r="R4" t="n">
-        <v>1.378665836238499</v>
+        <v>1.378665276766073</v>
       </c>
       <c r="S4" t="n">
-        <v>5.145208278300384</v>
+        <v>5.145208059354288</v>
       </c>
       <c r="T4" t="n">
-        <v>1212.495885991613</v>
+        <v>1212.495584678007</v>
       </c>
       <c r="U4" t="n">
-        <v>342.5044392784909</v>
+        <v>342.5043239136428</v>
       </c>
       <c r="V4" t="n">
-        <v>3441.446484351289</v>
+        <v>3441.445749399705</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -33938,10 +33938,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="n">
-        <v>1743.860204104931</v>
+        <v>1743.856205435775</v>
       </c>
       <c r="D5" t="n">
-        <v>75.82000887412744</v>
+        <v>75.81983501894672</v>
       </c>
       <c r="E5" t="n">
         <v>44.32861893835205</v>
@@ -33953,7 +33953,7 @@
         <v>90</v>
       </c>
       <c r="H5" t="n">
-        <v>90.38671774873625</v>
+        <v>90.38673010050131</v>
       </c>
       <c r="I5" t="n">
         <v>23</v>
@@ -33962,40 +33962,40 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5250299591663564</v>
+        <v>0.524865357866631</v>
       </c>
       <c r="L5" t="n">
         <v>0.4291469644159489</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5359316760554337</v>
+        <v>0.5355331687484006</v>
       </c>
       <c r="N5" t="n">
-        <v>1.046307709461789</v>
+        <v>1.045652235358969</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6969826739866007</v>
+        <v>0.6969828104339464</v>
       </c>
       <c r="P5" t="n">
-        <v>0.94214135157756</v>
+        <v>0.940978431267691</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.081200583634057</v>
+        <v>3.078622842733944</v>
       </c>
       <c r="R5" t="n">
         <v>1.826709067861734</v>
       </c>
       <c r="S5" t="n">
-        <v>2.872993380997082</v>
+        <v>2.868986295539307</v>
       </c>
       <c r="T5" t="n">
-        <v>170.5863734967965</v>
+        <v>170.4853972715942</v>
       </c>
       <c r="U5" t="n">
-        <v>29.24307471368612</v>
+        <v>29.24307761613235</v>
       </c>
       <c r="V5" t="n">
-        <v>316.5165781005372</v>
+        <v>316.2724899006705</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -34013,10 +34013,10 @@
         <v>13</v>
       </c>
       <c r="C6" t="n">
-        <v>5013.267727949356</v>
+        <v>5014.927001165356</v>
       </c>
       <c r="D6" t="n">
-        <v>417.7723106624464</v>
+        <v>417.9105834304464</v>
       </c>
       <c r="E6" t="n">
         <v>222.10015232</v>
@@ -34028,7 +34028,7 @@
         <v>90</v>
       </c>
       <c r="H6" t="n">
-        <v>89.90429269611528</v>
+        <v>89.90432436249165</v>
       </c>
       <c r="I6" t="n">
         <v>12</v>
@@ -34043,34 +34043,34 @@
         <v>1.636445964659505</v>
       </c>
       <c r="M6" t="n">
-        <v>2.281304903154817</v>
+        <v>2.281165291045537</v>
       </c>
       <c r="N6" t="n">
-        <v>9.866339695541351</v>
+        <v>9.866339710450056</v>
       </c>
       <c r="O6" t="n">
         <v>6.492557117825493</v>
       </c>
       <c r="P6" t="n">
-        <v>9.031047844669759</v>
+        <v>9.029529564519912</v>
       </c>
       <c r="Q6" t="n">
-        <v>7.041303587312576</v>
+        <v>7.041303444010628</v>
       </c>
       <c r="R6" t="n">
         <v>4.640200214835365</v>
       </c>
       <c r="S6" t="n">
-        <v>9.769008771785794</v>
+        <v>9.769096826832534</v>
       </c>
       <c r="T6" t="n">
-        <v>322.4426269000737</v>
+        <v>322.4426373516895</v>
       </c>
       <c r="U6" t="n">
-        <v>61.22083459916829</v>
+        <v>61.22082632686141</v>
       </c>
       <c r="V6" t="n">
-        <v>379.4897429697569</v>
+        <v>379.4153539651227</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -34112,40 +34112,40 @@
         <v>0.875</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4241544905033602</v>
+        <v>0.4241544961419784</v>
       </c>
       <c r="L7" t="n">
         <v>0.2623275911775139</v>
       </c>
       <c r="M7" t="n">
-        <v>0.6775082500770488</v>
+        <v>0.6775082523187218</v>
       </c>
       <c r="N7" t="n">
-        <v>0.750717692673746</v>
+        <v>0.7507176799641049</v>
       </c>
       <c r="O7" t="n">
         <v>0.6656460760473047</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9834911289195825</v>
+        <v>0.9834910929226175</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.968419777933658</v>
+        <v>6.968419797772164</v>
       </c>
       <c r="R7" t="n">
         <v>4.640039058392444</v>
       </c>
       <c r="S7" t="n">
-        <v>5.902101321151931</v>
+        <v>5.902101205836773</v>
       </c>
       <c r="T7" t="n">
-        <v>237.8166218046881</v>
+        <v>237.8166012768581</v>
       </c>
       <c r="U7" t="n">
-        <v>34.88661612216815</v>
+        <v>34.88662080052782</v>
       </c>
       <c r="V7" t="n">
-        <v>779.1188703669061</v>
+        <v>779.1188147071559</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -34196,22 +34196,22 @@
         <v>1.406653826734192</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2280973809458307</v>
+        <v>0.2280973146972898</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2280973809458307</v>
+        <v>0.2280973146972898</v>
       </c>
       <c r="P8" t="n">
-        <v>1.0788201480932</v>
+        <v>1.078820022575607</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.9515704509563081</v>
+        <v>0.951570663520489</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9515704509563081</v>
+        <v>0.951570663520489</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9515704509563081</v>
+        <v>0.951570663520489</v>
       </c>
       <c r="T8" t="n">
         <v>15.09244612703106</v>
@@ -34238,10 +34238,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>3419.30061880217</v>
+        <v>3419.11588920217</v>
       </c>
       <c r="D9" t="n">
-        <v>162.8238389905795</v>
+        <v>162.8150423429605</v>
       </c>
       <c r="E9" t="n">
         <v>59.800449024</v>
@@ -34253,7 +34253,7 @@
         <v>90</v>
       </c>
       <c r="H9" t="n">
-        <v>84.98385063664523</v>
+        <v>84.98384976411984</v>
       </c>
       <c r="I9" t="n">
         <v>18</v>
@@ -34268,34 +34268,34 @@
         <v>0.715432420164215</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4079288019388163</v>
+        <v>0.4078564327988455</v>
       </c>
       <c r="N9" t="n">
-        <v>2.419290774368154</v>
+        <v>2.420864126521514</v>
       </c>
       <c r="O9" t="n">
         <v>1.706836703900194</v>
       </c>
       <c r="P9" t="n">
-        <v>1.569878634537791</v>
+        <v>1.570311185394861</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.73040742082023</v>
+        <v>7.737953900883376</v>
       </c>
       <c r="R9" t="n">
-        <v>4.069713096474089</v>
+        <v>4.06971250077991</v>
       </c>
       <c r="S9" t="n">
-        <v>8.985310101263607</v>
+        <v>8.987742684956352</v>
       </c>
       <c r="T9" t="n">
-        <v>193.8019917872448</v>
+        <v>193.8020266987551</v>
       </c>
       <c r="U9" t="n">
         <v>28.05972780837731</v>
       </c>
       <c r="V9" t="n">
-        <v>299.7077680455479</v>
+        <v>299.7229983654187</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -34346,31 +34346,31 @@
         <v>0.1840978318372211</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4000813443636345</v>
+        <v>0.4045096075860679</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2555351926498626</v>
+        <v>0.2643917190947294</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2503109921639334</v>
+        <v>0.259872159056291</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.751699488812336</v>
+        <v>1.74981494734469</v>
       </c>
       <c r="R10" t="n">
-        <v>1.590654592751534</v>
+        <v>1.586885756234896</v>
       </c>
       <c r="S10" t="n">
-        <v>1.445138888411708</v>
+        <v>1.441070170242729</v>
       </c>
       <c r="T10" t="n">
-        <v>99.4133077924911</v>
+        <v>99.41330045125348</v>
       </c>
       <c r="U10" t="n">
-        <v>91.59880241807646</v>
+        <v>91.59878773560123</v>
       </c>
       <c r="V10" t="n">
-        <v>74.04381417646189</v>
+        <v>74.04381259456204</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -34388,10 +34388,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>2722.51958272</v>
+        <v>2722.47315968</v>
       </c>
       <c r="D11" t="n">
-        <v>272.251958272</v>
+        <v>272.247315968</v>
       </c>
       <c r="E11" t="n">
         <v>91.422887936</v>
@@ -34403,7 +34403,7 @@
         <v>75</v>
       </c>
       <c r="H11" t="n">
-        <v>81.79395102294194</v>
+        <v>81.79491946145555</v>
       </c>
       <c r="I11" t="n">
         <v>5</v>
@@ -34412,40 +34412,40 @@
         <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2257804305091501</v>
+        <v>0.2257804198368242</v>
       </c>
       <c r="L11" t="n">
         <v>0.04893539681997117</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2104240623321379</v>
+        <v>0.2104310520091545</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2554517622187587</v>
+        <v>0.2554517734502176</v>
       </c>
       <c r="O11" t="n">
         <v>0.271126232199195</v>
       </c>
       <c r="P11" t="n">
-        <v>0.3812547077211375</v>
+        <v>0.3812665178223992</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.595566226742211</v>
+        <v>1.595566221526958</v>
       </c>
       <c r="R11" t="n">
         <v>0.7538460145065422</v>
       </c>
       <c r="S11" t="n">
-        <v>5.586681345787305</v>
+        <v>5.586787415271158</v>
       </c>
       <c r="T11" t="n">
-        <v>58.66871386862738</v>
+        <v>58.66870895806884</v>
       </c>
       <c r="U11" t="n">
         <v>7.999741000163517</v>
       </c>
       <c r="V11" t="n">
-        <v>224.4638976915245</v>
+        <v>224.4677585238144</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -34463,10 +34463,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>1299.0818115126</v>
+        <v>1299.1319091766</v>
       </c>
       <c r="D12" t="n">
-        <v>68.37272692171575</v>
+        <v>68.37536364087366</v>
       </c>
       <c r="E12" t="n">
         <v>48.991207424</v>
@@ -34478,7 +34478,7 @@
         <v>45</v>
       </c>
       <c r="H12" t="n">
-        <v>73.48211850761112</v>
+        <v>73.47928485965204</v>
       </c>
       <c r="I12" t="n">
         <v>6</v>
@@ -34487,40 +34487,40 @@
         <v>0.3157894736842105</v>
       </c>
       <c r="K12" t="n">
-        <v>0.01732252769550747</v>
+        <v>0.01732253144171839</v>
       </c>
       <c r="L12" t="n">
         <v>0.007728700033076352</v>
       </c>
       <c r="M12" t="n">
-        <v>0.220226955091362</v>
+        <v>0.2202116119173067</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2786224916923573</v>
+        <v>0.276215839013232</v>
       </c>
       <c r="O12" t="n">
         <v>0.2683822198137273</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4791077617233327</v>
+        <v>0.4733534151857594</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.502727370002547</v>
+        <v>2.501634689137313</v>
       </c>
       <c r="R12" t="n">
-        <v>1.707184697640819</v>
+        <v>1.707184940515831</v>
       </c>
       <c r="S12" t="n">
-        <v>2.438133477407135</v>
+        <v>2.435150373914365</v>
       </c>
       <c r="T12" t="n">
-        <v>78.97005715364638</v>
+        <v>78.97003792479539</v>
       </c>
       <c r="U12" t="n">
-        <v>12.48362414231921</v>
+        <v>12.48361960485249</v>
       </c>
       <c r="V12" t="n">
-        <v>109.817614496382</v>
+        <v>109.813371761519</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -34562,40 +34562,40 @@
         <v>0.4166666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5225767121599357</v>
+        <v>0.5225766982061318</v>
       </c>
       <c r="L13" t="n">
         <v>-0.03581250767046662</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.004804531779251252</v>
+        <v>-0.004804571967261463</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6621414658191354</v>
+        <v>0.6621414692594215</v>
       </c>
       <c r="O13" t="n">
         <v>-0.01009155446892185</v>
       </c>
       <c r="P13" t="n">
-        <v>0.3057361345015824</v>
+        <v>0.3057361358164897</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4601262472819278</v>
+        <v>0.4601262334031525</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4810861069523608</v>
+        <v>0.4810860608975769</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9986074867662041</v>
+        <v>0.998607541883239</v>
       </c>
       <c r="T13" t="n">
-        <v>1054.446318349579</v>
+        <v>1054.44643367394</v>
       </c>
       <c r="U13" t="n">
-        <v>12.08104166936328</v>
+        <v>12.08104244348618</v>
       </c>
       <c r="V13" t="n">
-        <v>2183.712268118117</v>
+        <v>2183.712471423124</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -34655,22 +34655,22 @@
         <v>0.1897022064283781</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5132817557789772</v>
+        <v>0.5132818349981544</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3808379815863328</v>
+        <v>0.3808380422396593</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6705196792520939</v>
+        <v>0.6705197772640401</v>
       </c>
       <c r="T14" t="n">
-        <v>15.80647196612557</v>
+        <v>15.80647097787183</v>
       </c>
       <c r="U14" t="n">
-        <v>3.080007171342018</v>
+        <v>3.08000811197118</v>
       </c>
       <c r="V14" t="n">
-        <v>2.485251339849504</v>
+        <v>2.4852512112486</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>

--- a/company_radar_output.xlsx
+++ b/company_radar_output.xlsx
@@ -876,13 +876,13 @@
         <v>1.694015495883381</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.255401252426652</v>
+        <v>2.255400839571528</v>
       </c>
       <c r="AX2" t="n">
         <v>1.563350686211098</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.052599355162004</v>
+        <v>3.052598715344739</v>
       </c>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
@@ -1216,16 +1216,16 @@
         <v>372.6216882324219</v>
       </c>
       <c r="AG4" t="n">
-        <v>318.5789504241943</v>
+        <v>318.578950881958</v>
       </c>
       <c r="AH4" t="n">
         <v>-0.04144067842612775</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.1211663300421728</v>
+        <v>0.1211663284311773</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.1696368756826796</v>
+        <v>0.1696368740020371</v>
       </c>
       <c r="AK4" t="n">
         <v>402.3796691894531</v>
@@ -1264,13 +1264,13 @@
         <v>1.016658868474406</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.876851136246393</v>
+        <v>1.876851313028276</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1348402579903003</v>
+        <v>0.1348403680257064</v>
       </c>
       <c r="AY4" t="n">
-        <v>142.5068301988223</v>
+        <v>142.5068439455128</v>
       </c>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
@@ -1602,25 +1602,25 @@
         <v>600.0849096679688</v>
       </c>
       <c r="AG6" t="n">
-        <v>641.6731106567382</v>
+        <v>641.6731109619141</v>
       </c>
       <c r="AH6" t="n">
         <v>0.1151922189527061</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.04291423601611521</v>
+        <v>0.04291423552011153</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.06481212988059426</v>
+        <v>-0.06481213032536393</v>
       </c>
       <c r="AK6" t="n">
-        <v>787.419189453125</v>
+        <v>787.4192504882812</v>
       </c>
       <c r="AL6" t="n">
         <v>525.233154296875</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.1501222843737995</v>
+        <v>-0.1501223502502931</v>
       </c>
       <c r="AN6" t="n">
         <v>0.2741199151232596</v>
@@ -1650,13 +1650,13 @@
         <v>-0.07677876083840129</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.9032612657010106</v>
+        <v>0.9032607701303479</v>
       </c>
       <c r="AX6" t="n">
         <v>0.03074029207672369</v>
       </c>
       <c r="AY6" t="n">
-        <v>16.65856039000963</v>
+        <v>16.65855861251545</v>
       </c>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
@@ -2188,16 +2188,16 @@
         <v>182.4422756958008</v>
       </c>
       <c r="AG9" t="n">
-        <v>194.303373260498</v>
+        <v>194.3033737945557</v>
       </c>
       <c r="AH9" t="n">
         <v>-0.229126040807846</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.2761834391773752</v>
+        <v>-0.2761834411668401</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.06104421845932317</v>
+        <v>-0.06104422104011464</v>
       </c>
       <c r="AK9" t="n">
         <v>324.6299743652344</v>
@@ -2236,13 +2236,13 @@
         <v>-0.3947107724147052</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.8455305870177687</v>
+        <v>0.8455313260848825</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.2744543460752883</v>
+        <v>-0.2744542889615302</v>
       </c>
       <c r="AY9" t="n">
-        <v>2798.49658486407</v>
+        <v>2798.495962087439</v>
       </c>
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
@@ -2576,16 +2576,16 @@
         <v>403.3287658691406</v>
       </c>
       <c r="AG11" t="n">
-        <v>440.7076475524902</v>
+        <v>440.7076486206055</v>
       </c>
       <c r="AH11" t="n">
         <v>-0.04519578395640467</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.1261780723747289</v>
+        <v>-0.1261780744925558</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0.08481559576044717</v>
+        <v>-0.08481559797852167</v>
       </c>
       <c r="AK11" t="n">
         <v>538.6585693359375</v>
@@ -2624,13 +2624,13 @@
         <v>-0.2259391799221225</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.4452462928430114</v>
+        <v>0.4452464583667617</v>
       </c>
       <c r="AX11" t="n">
         <v>-0.1821056233913793</v>
       </c>
       <c r="AY11" t="n">
-        <v>6512.280083309905</v>
+        <v>6512.282135210159</v>
       </c>
       <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="n">
@@ -2822,7 +2822,7 @@
         <v>-0.2527098486195496</v>
       </c>
       <c r="AY12" t="n">
-        <v>653.3522551915103</v>
+        <v>653.3523106485549</v>
       </c>
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="n">
@@ -3008,13 +3008,13 @@
         <v>0.0630311205151477</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.4518192557963938</v>
+        <v>-0.4518192966162832</v>
       </c>
       <c r="AX13" t="n">
         <v>-0.2721097031519545</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.2713425814751693</v>
+        <v>0.2713426912542354</v>
       </c>
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="n">
@@ -3940,16 +3940,16 @@
         <v>405.9760382080078</v>
       </c>
       <c r="AG18" t="n">
-        <v>361.2549255371094</v>
+        <v>361.2549249267578</v>
       </c>
       <c r="AH18" t="n">
         <v>-0.0147940676839341</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.1071682984696545</v>
+        <v>0.1071683003402502</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.1237937797094604</v>
+        <v>0.1237937816081454</v>
       </c>
       <c r="AK18" t="n">
         <v>480.8090515136719</v>
@@ -3988,13 +3988,13 @@
         <v>0.4629652450487607</v>
       </c>
       <c r="AW18" t="n">
-        <v>8.384254085964638</v>
+        <v>8.384254925873597</v>
       </c>
       <c r="AX18" t="n">
         <v>0.154834014083173</v>
       </c>
       <c r="AY18" t="n">
-        <v>351.2130314740801</v>
+        <v>351.2129575265922</v>
       </c>
       <c r="AZ18" t="inlineStr"/>
       <c r="BA18" t="n">
@@ -4328,16 +4328,16 @@
         <v>261.3985458374024</v>
       </c>
       <c r="AG20" t="n">
-        <v>272.4722570037842</v>
+        <v>272.4722551727295</v>
       </c>
       <c r="AH20" t="n">
         <v>0.1000826214904216</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.05537349277581693</v>
+        <v>0.05537349986808615</v>
       </c>
       <c r="AJ20" t="n">
-        <v>-0.0406416098583865</v>
+        <v>-0.04064160341135326</v>
       </c>
       <c r="AK20" t="n">
         <v>329.2300109863281</v>
@@ -4376,13 +4376,13 @@
         <v>0.02604071728593249</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.612317035541202</v>
+        <v>1.612317397653624</v>
       </c>
       <c r="AX20" t="n">
-        <v>-0.000590030322446311</v>
+        <v>-0.0005899243216824779</v>
       </c>
       <c r="AY20" t="n">
-        <v>198.039346077303</v>
+        <v>198.0394610402244</v>
       </c>
       <c r="AZ20" t="inlineStr"/>
       <c r="BA20" t="n">
@@ -5102,16 +5102,16 @@
         <v>297.7269622802734</v>
       </c>
       <c r="AG24" t="n">
-        <v>272.096633682251</v>
+        <v>272.0966347503662</v>
       </c>
       <c r="AH24" t="n">
         <v>0.05909120527479672</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.1588530260629508</v>
+        <v>0.1588530215138737</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.09419568427279046</v>
+        <v>0.09419567997752587</v>
       </c>
       <c r="AK24" t="n">
         <v>316.2200012207031</v>
@@ -5147,16 +5147,16 @@
         <v>0.2195252819657805</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.4903770100349119</v>
+        <v>0.4903769025467106</v>
       </c>
       <c r="AW24" t="n">
         <v>1.311284607230153</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.1656612312269863</v>
+        <v>0.1656610997217054</v>
       </c>
       <c r="AY24" t="n">
-        <v>3209.76902154225</v>
+        <v>3209.76780360039</v>
       </c>
       <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="n">
@@ -5659,10 +5659,10 @@
         </is>
       </c>
       <c r="Z27" t="n">
-        <v>0.1476428806781769</v>
+        <v>0.1477825343608856</v>
       </c>
       <c r="AA27" t="n">
-        <v>129868178973.3945</v>
+        <v>129991019772.6055</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>1.789232944608137</v>
       </c>
       <c r="AY29" t="n">
-        <v>604.1799780628296</v>
+        <v>604.1797793213337</v>
       </c>
       <c r="AZ29" t="inlineStr"/>
       <c r="BA29" t="n">
@@ -6268,28 +6268,28 @@
         <v>209.0737417602539</v>
       </c>
       <c r="AG30" t="n">
-        <v>191.468422164917</v>
+        <v>191.468422088623</v>
       </c>
       <c r="AH30" t="n">
         <v>0.009022007918030539</v>
       </c>
       <c r="AI30" t="n">
-        <v>0.1018005179577943</v>
+        <v>0.1018005183968262</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.09194894592160452</v>
+        <v>0.09194894635671091</v>
       </c>
       <c r="AK30" t="n">
         <v>235.465576171875</v>
       </c>
       <c r="AL30" t="n">
-        <v>163.8517608642578</v>
+        <v>163.8517761230469</v>
       </c>
       <c r="AM30" t="n">
         <v>-0.1040728324556465</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.287505276727761</v>
+        <v>0.287505156828106</v>
       </c>
       <c r="AO30" t="n">
         <v>50.27114310993102</v>
@@ -6316,7 +6316,7 @@
         <v>0.2872698368449687</v>
       </c>
       <c r="AW30" t="n">
-        <v>9.33287917561031</v>
+        <v>9.332877244964671</v>
       </c>
       <c r="AX30" t="n">
         <v>0.1184395258885382</v>
@@ -6509,16 +6509,16 @@
         <v>0.05062759896381297</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.2140734622373373</v>
+        <v>0.2140733433376683</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.477916035136061</v>
+        <v>0.4779155946520415</v>
       </c>
       <c r="AX31" t="n">
         <v>0.1046227422659505</v>
       </c>
       <c r="AY31" t="n">
-        <v>559.668694222702</v>
+        <v>559.668793274755</v>
       </c>
       <c r="AZ31" t="inlineStr"/>
       <c r="BA31" t="n">
@@ -6714,7 +6714,7 @@
         <v>1.555702248539101</v>
       </c>
       <c r="AY32" t="n">
-        <v>40.53741713740772</v>
+        <v>40.53742678010032</v>
       </c>
       <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="n">
@@ -6906,7 +6906,7 @@
         <v>3.003615150538764</v>
       </c>
       <c r="AY33" t="n">
-        <v>119.200901666593</v>
+        <v>119.2009174139452</v>
       </c>
       <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="n">
@@ -7098,7 +7098,7 @@
         <v>4.104878002897078</v>
       </c>
       <c r="AY34" t="n">
-        <v>33.78927898932974</v>
+        <v>33.78928770047334</v>
       </c>
       <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
@@ -7290,7 +7290,7 @@
         <v>1.841141636730317</v>
       </c>
       <c r="AY35" t="n">
-        <v>28.33033194284154</v>
+        <v>28.33032159671425</v>
       </c>
       <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="n">
@@ -7482,7 +7482,7 @@
         <v>0.1234972253384632</v>
       </c>
       <c r="AY36" t="n">
-        <v>3.458769927801079</v>
+        <v>3.458769461191894</v>
       </c>
       <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="n">
@@ -7624,28 +7624,28 @@
         <v>74.7279963684082</v>
       </c>
       <c r="AG37" t="n">
-        <v>51.32824649810791</v>
+        <v>51.32824646949768</v>
       </c>
       <c r="AH37" t="n">
         <v>-0.05697991856643936</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.3729282807917631</v>
+        <v>0.3729282815570296</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.4558844586900677</v>
+        <v>0.4558844595015739</v>
       </c>
       <c r="AK37" t="n">
         <v>93.55000305175781</v>
       </c>
       <c r="AL37" t="n">
-        <v>20.95925903320312</v>
+        <v>20.95926094055176</v>
       </c>
       <c r="AM37" t="n">
         <v>-0.2467129992319227</v>
       </c>
       <c r="AN37" t="n">
-        <v>2.362237238876925</v>
+        <v>2.362236932904371</v>
       </c>
       <c r="AO37" t="n">
         <v>33.62281192475615</v>
@@ -7669,16 +7669,16 @@
         <v>0.3859702206736597</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.247039273833214</v>
+        <v>2.247039559198358</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.26196568111741</v>
+        <v>2.261965393122681</v>
       </c>
       <c r="AX37" t="n">
         <v>0.6468892082431434</v>
       </c>
       <c r="AY37" t="n">
-        <v>4.697598058658468</v>
+        <v>4.697597619340071</v>
       </c>
       <c r="AZ37" t="inlineStr"/>
       <c r="BA37" t="n">
@@ -7810,22 +7810,22 @@
         <v>18.7</v>
       </c>
       <c r="AE38" t="n">
-        <v>191.8000030517578</v>
+        <v>186.8000030517578</v>
       </c>
       <c r="AF38" t="n">
-        <v>153.6120002746582</v>
+        <v>155.4720002746582</v>
       </c>
       <c r="AG38" t="n">
-        <v>69.94800010681152</v>
+        <v>70.77200012207031</v>
       </c>
       <c r="AH38" t="n">
-        <v>0.2486003873969447</v>
+        <v>0.2015025388607292</v>
       </c>
       <c r="AI38" t="n">
-        <v>1.742036981169965</v>
+        <v>1.639461972666561</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1.196088523475877</v>
+        <v>1.196800994835444</v>
       </c>
       <c r="AK38" t="n">
         <v>239</v>
@@ -7834,13 +7834,13 @@
         <v>17.63999938964844</v>
       </c>
       <c r="AM38" t="n">
-        <v>-0.1974895269800928</v>
+        <v>-0.218410029072143</v>
       </c>
       <c r="AN38" t="n">
-        <v>9.873016422229046</v>
+        <v>9.589569700403528</v>
       </c>
       <c r="AO38" t="n">
-        <v>39.44444439211662</v>
+        <v>33.05194736351383</v>
       </c>
       <c r="AP38" t="n">
         <v>77156</v>
@@ -7852,25 +7852,25 @@
         <v>0.4156891234118705</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.341258762599705</v>
+        <v>0.2114137921446129</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.89291092342827</v>
+        <v>1.703328613266424</v>
       </c>
       <c r="AU38" t="n">
-        <v>4.616398081458695</v>
+        <v>4.461988271479282</v>
       </c>
       <c r="AV38" t="n">
-        <v>8.775738779186103</v>
+        <v>8.434343951999546</v>
       </c>
       <c r="AW38" t="n">
-        <v>4.263584246605888</v>
+        <v>4.169031013974967</v>
       </c>
       <c r="AX38" t="n">
-        <v>4.847561204667469</v>
+        <v>4.69512217673144</v>
       </c>
       <c r="AY38" t="n">
-        <v>15.71474529855174</v>
+        <v>15.27901294365783</v>
       </c>
       <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="n">
@@ -8012,16 +8012,16 @@
         <v>125.4860302734375</v>
       </c>
       <c r="AG39" t="n">
-        <v>104.0938962936401</v>
+        <v>104.0938962173462</v>
       </c>
       <c r="AH39" t="n">
         <v>-0.03168502604268508</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.1673114991628419</v>
+        <v>0.1673115000184042</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.205508053223908</v>
+        <v>0.2055080541074659</v>
       </c>
       <c r="AK39" t="n">
         <v>133.0599975585938</v>
@@ -8057,16 +8057,16 @@
         <v>0.4124845916784821</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.2697068511936827</v>
+        <v>0.2697067499693466</v>
       </c>
       <c r="AW39" t="n">
-        <v>2.452222075910021</v>
+        <v>2.452222450059847</v>
       </c>
       <c r="AX39" t="n">
         <v>0.4817174890207807</v>
       </c>
       <c r="AY39" t="n">
-        <v>104.4620601888137</v>
+        <v>104.4620383655108</v>
       </c>
       <c r="AZ39" t="inlineStr"/>
       <c r="BA39" t="n">
@@ -8204,16 +8204,16 @@
         <v>2684.7</v>
       </c>
       <c r="AG40" t="n">
-        <v>2602.836932373047</v>
+        <v>2602.83692993164</v>
       </c>
       <c r="AH40" t="n">
         <v>0.03940850001862417</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.07209943323489654</v>
+        <v>0.07209943424050325</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.03145147765838607</v>
+        <v>0.03145147862586595</v>
       </c>
       <c r="AK40" t="n">
         <v>2808</v>
@@ -8249,7 +8249,7 @@
         <v>0.03854153539012617</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.160986175495293</v>
+        <v>0.1609860575686113</v>
       </c>
       <c r="AW40" t="n">
         <v>0.7531327201194351</v>
@@ -8258,7 +8258,7 @@
         <v>0.03607197425947772</v>
       </c>
       <c r="AY40" t="n">
-        <v>3.264597949503009</v>
+        <v>3.264597551712717</v>
       </c>
       <c r="AZ40" t="inlineStr"/>
       <c r="BA40" t="n">
@@ -8400,16 +8400,16 @@
         <v>1066.220737304687</v>
       </c>
       <c r="AG41" t="n">
-        <v>906.3318444824218</v>
+        <v>906.3318453979492</v>
       </c>
       <c r="AH41" t="n">
         <v>-0.01407848847991211</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.1598510714779238</v>
+        <v>0.159851070306305</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.1764131910355342</v>
+        <v>0.1764131898471852</v>
       </c>
       <c r="AK41" t="n">
         <v>1115.93994140625</v>
@@ -8454,7 +8454,7 @@
         <v>0.3900707617105812</v>
       </c>
       <c r="AY41" t="n">
-        <v>2.403099240424091</v>
+        <v>2.403098904214745</v>
       </c>
       <c r="AZ41" t="inlineStr"/>
       <c r="BA41" t="n">
@@ -8836,13 +8836,13 @@
         <v>0.08879809751909096</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.424025524989234</v>
+        <v>0.424025782257571</v>
       </c>
       <c r="AX43" t="n">
         <v>0.1794454765270563</v>
       </c>
       <c r="AY43" t="n">
-        <v>34.3910593674331</v>
+        <v>34.39106598848021</v>
       </c>
       <c r="AZ43" t="inlineStr"/>
       <c r="BA43" t="n">
@@ -9034,7 +9034,7 @@
         <v>0.02366607311174418</v>
       </c>
       <c r="AY44" t="n">
-        <v>3.011992539465282</v>
+        <v>3.011993824378248</v>
       </c>
       <c r="AZ44" t="inlineStr"/>
       <c r="BA44" t="n">
@@ -9416,7 +9416,7 @@
         <v>-0.05892355276542649</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.6047316879760181</v>
+        <v>0.6047306231019427</v>
       </c>
       <c r="AZ46" t="inlineStr"/>
       <c r="BA46" t="n">
@@ -9912,28 +9912,28 @@
         <v>66.27910278320313</v>
       </c>
       <c r="AG49" t="n">
-        <v>61.4878981590271</v>
+        <v>61.48789806365967</v>
       </c>
       <c r="AH49" t="n">
         <v>0.05734686934861166</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.1397364998524702</v>
+        <v>0.1397365016201959</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.07792109939722547</v>
+        <v>0.0779211010690759</v>
       </c>
       <c r="AK49" t="n">
         <v>70.08000183105469</v>
       </c>
       <c r="AL49" t="n">
-        <v>54.15811157226562</v>
+        <v>54.15811538696289</v>
       </c>
       <c r="AM49" t="n">
         <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>0.2939890220792458</v>
+        <v>0.2939889309354469</v>
       </c>
       <c r="AO49" t="n">
         <v>60.91500764933151</v>
@@ -9960,13 +9960,13 @@
         <v>0.2581684321906936</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.1802576874737116</v>
+        <v>0.1802579907788389</v>
       </c>
       <c r="AX49" t="n">
         <v>0.207563158772776</v>
       </c>
       <c r="AY49" t="n">
-        <v>188.63773634206</v>
+        <v>188.6378433962856</v>
       </c>
       <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
@@ -10160,7 +10160,7 @@
         <v>0.6092896408427024</v>
       </c>
       <c r="AY50" t="n">
-        <v>7.351867541581512</v>
+        <v>7.351868516651404</v>
       </c>
       <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
@@ -10302,16 +10302,16 @@
         <v>14.5815599822998</v>
       </c>
       <c r="AG51" t="n">
-        <v>14.23315340995789</v>
+        <v>14.23315336227417</v>
       </c>
       <c r="AH51" t="n">
         <v>0.01360895205398238</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.03842060204527242</v>
+        <v>0.03842060552417514</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.02447852294616348</v>
+        <v>0.02447852637835735</v>
       </c>
       <c r="AK51" t="n">
         <v>17.06953239440918</v>
@@ -10344,19 +10344,19 @@
         <v>0.03976638797694187</v>
       </c>
       <c r="AU51" t="n">
-        <v>0.06465544779208687</v>
+        <v>0.06465552093021687</v>
       </c>
       <c r="AV51" t="n">
         <v>0.2522044132542418</v>
       </c>
       <c r="AW51" t="n">
-        <v>-0.3125524802434755</v>
+        <v>-0.3125526022167473</v>
       </c>
       <c r="AX51" t="n">
         <v>0.02155212588028221</v>
       </c>
       <c r="AY51" t="n">
-        <v>6.406423842467975</v>
+        <v>6.406424284906384</v>
       </c>
       <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="n">
@@ -10688,16 +10688,16 @@
         <v>124.7692489624023</v>
       </c>
       <c r="AG53" t="n">
-        <v>122.871420249939</v>
+        <v>122.8714202880859</v>
       </c>
       <c r="AH53" t="n">
         <v>0.005696551036749709</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.02123018600817317</v>
+        <v>0.02123018569111945</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.0154456480490166</v>
+        <v>0.01544564773375878</v>
       </c>
       <c r="AK53" t="n">
         <v>132.3166198730469</v>
@@ -10733,7 +10733,7 @@
         <v>0.08798379294662428</v>
       </c>
       <c r="AV53" t="n">
-        <v>0.09896576276649749</v>
+        <v>0.09896568933475258</v>
       </c>
       <c r="AW53" t="n">
         <v>0.529614046443887</v>
@@ -10742,7 +10742,7 @@
         <v>0.08687203524002696</v>
       </c>
       <c r="AY53" t="n">
-        <v>168.4898088985315</v>
+        <v>168.4896724426017</v>
       </c>
       <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
@@ -10929,16 +10929,16 @@
         <v>0.2768792389174044</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.4368560101023142</v>
+        <v>0.4368558731939771</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.699661016949153</v>
+        <v>1.699660533643547</v>
       </c>
       <c r="AX54" t="n">
         <v>0.2405563051351287</v>
       </c>
       <c r="AY54" t="n">
-        <v>213.0600145167256</v>
+        <v>213.0600382558457</v>
       </c>
       <c r="AZ54" t="inlineStr"/>
       <c r="BA54" t="n">
@@ -11080,28 +11080,28 @@
         <v>45.56361747741699</v>
       </c>
       <c r="AG55" t="n">
-        <v>45.45492044448852</v>
+        <v>45.45492042541504</v>
       </c>
       <c r="AH55" t="n">
         <v>0.02713528530205833</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.02959148931334488</v>
+        <v>0.02959148974537507</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.002391314996606608</v>
+        <v>0.002391315417223261</v>
       </c>
       <c r="AK55" t="n">
         <v>49.82146072387695</v>
       </c>
       <c r="AL55" t="n">
-        <v>41.35774993896484</v>
+        <v>41.35775375366211</v>
       </c>
       <c r="AM55" t="n">
         <v>-0.06064578281961874</v>
       </c>
       <c r="AN55" t="n">
-        <v>0.1315895885566138</v>
+        <v>0.1315894841826737</v>
       </c>
       <c r="AO55" t="n">
         <v>56.50457813303605</v>
@@ -11125,16 +11125,16 @@
         <v>0.09653907045408494</v>
       </c>
       <c r="AV55" t="n">
-        <v>0.1113595325389343</v>
+        <v>0.1113594318635374</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.7342669768602337</v>
+        <v>0.7342668542812223</v>
       </c>
       <c r="AX55" t="n">
         <v>0.08480475291928924</v>
       </c>
       <c r="AY55" t="n">
-        <v>189.8671427079904</v>
+        <v>189.8669339184967</v>
       </c>
       <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="n">
@@ -11276,16 +11276,16 @@
         <v>88.69704376220703</v>
       </c>
       <c r="AG56" t="n">
-        <v>85.99043495178222</v>
+        <v>85.99043476104737</v>
       </c>
       <c r="AH56" t="n">
         <v>-0.008309687070409688</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.02290445598739943</v>
+        <v>0.02290445825629761</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.03147569624391955</v>
+        <v>0.03147569853182941</v>
       </c>
       <c r="AK56" t="n">
         <v>97.16828918457031</v>
@@ -11321,7 +11321,7 @@
         <v>0.1222597138586909</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.212580508059667</v>
+        <v>0.2125803805256681</v>
       </c>
       <c r="AW56" t="n">
         <v>0.3505196278270164</v>
@@ -11330,7 +11330,7 @@
         <v>0.1022911005985252</v>
       </c>
       <c r="AY56" t="n">
-        <v>252.1195017895775</v>
+        <v>252.1195669130385</v>
       </c>
       <c r="AZ56" t="inlineStr"/>
       <c r="BA56" t="n">
@@ -11472,28 +11472,28 @@
         <v>93.83682312011719</v>
       </c>
       <c r="AG57" t="n">
-        <v>91.68827781677246</v>
+        <v>91.68827754974365</v>
       </c>
       <c r="AH57" t="n">
         <v>0.01889639302861523</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.04277234655248052</v>
+        <v>0.04277234958940368</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.02343315148353353</v>
+        <v>0.02343315446413419</v>
       </c>
       <c r="AK57" t="n">
         <v>98.29612731933594</v>
       </c>
       <c r="AL57" t="n">
-        <v>82.73965454101562</v>
+        <v>82.73964691162109</v>
       </c>
       <c r="AM57" t="n">
         <v>-0.02732688237307579</v>
       </c>
       <c r="AN57" t="n">
-        <v>0.1555523302669322</v>
+        <v>0.1555524368200172</v>
       </c>
       <c r="AO57" t="n">
         <v>58.50202575045431</v>
@@ -11514,10 +11514,10 @@
         <v>-0.007703253736871862</v>
       </c>
       <c r="AU57" t="n">
-        <v>0.1139515030236831</v>
+        <v>0.1139514040045131</v>
       </c>
       <c r="AV57" t="n">
-        <v>0.05870520556638703</v>
+        <v>0.05870511612535267</v>
       </c>
       <c r="AW57" t="n">
         <v>0.8689427817012998</v>
@@ -11526,7 +11526,7 @@
         <v>0.1144625773375663</v>
       </c>
       <c r="AY57" t="n">
-        <v>351.5557162207932</v>
+        <v>351.5555999894062</v>
       </c>
       <c r="AZ57" t="inlineStr"/>
       <c r="BA57" t="n">
@@ -11658,22 +11658,22 @@
         <v>5.8</v>
       </c>
       <c r="AE58" t="n">
-        <v>156.2400054931641</v>
+        <v>152.1199951171875</v>
       </c>
       <c r="AF58" t="n">
-        <v>166.0171997070312</v>
+        <v>165.4479995727539</v>
       </c>
       <c r="AG58" t="n">
-        <v>140.8513035583496</v>
+        <v>141.1316515350342</v>
       </c>
       <c r="AH58" t="n">
-        <v>-0.05889265829757928</v>
+        <v>-0.08055706016382236</v>
       </c>
       <c r="AI58" t="n">
-        <v>0.109254948630557</v>
+        <v>0.07785881807969641</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.1786699555695366</v>
+        <v>0.1722954969579131</v>
       </c>
       <c r="AK58" t="n">
         <v>187.6199951171875</v>
@@ -11682,43 +11682,43 @@
         <v>84.04161071777344</v>
       </c>
       <c r="AM58" t="n">
-        <v>-0.1672529071564227</v>
+        <v>-0.1892122424255831</v>
       </c>
       <c r="AN58" t="n">
-        <v>0.8590791413773062</v>
+        <v>0.8100556833451622</v>
       </c>
       <c r="AO58" t="n">
-        <v>40.53167358431317</v>
+        <v>37.99041104592384</v>
       </c>
       <c r="AP58" t="n">
-        <v>1526536</v>
+        <v>1528158</v>
       </c>
       <c r="AQ58" t="n">
-        <v>2545502.56</v>
+        <v>2545535</v>
       </c>
       <c r="AR58" t="n">
-        <v>0.5996992593871129</v>
+        <v>0.6003288110357941</v>
       </c>
       <c r="AS58" t="n">
-        <v>0.06285718022560594</v>
+        <v>-0.009506489754266712</v>
       </c>
       <c r="AT58" t="n">
-        <v>-0.05822778034185938</v>
+        <v>-0.1102012801637982</v>
       </c>
       <c r="AU58" t="n">
-        <v>0.223917913841903</v>
+        <v>0.1719883418775445</v>
       </c>
       <c r="AV58" t="n">
-        <v>0.7114558292045023</v>
+        <v>0.6598076692550514</v>
       </c>
       <c r="AW58" t="n">
-        <v>5.875139167106532</v>
+        <v>5.590419621851969</v>
       </c>
       <c r="AX58" t="n">
-        <v>0.2777383831769491</v>
+        <v>0.2440447374307393</v>
       </c>
       <c r="AY58" t="n">
-        <v>6.16889543551419</v>
+        <v>5.97985282171642</v>
       </c>
       <c r="AZ58" t="inlineStr"/>
       <c r="BA58" t="n">
@@ -11858,16 +11858,16 @@
         <v>153.8592938232422</v>
       </c>
       <c r="AG59" t="n">
-        <v>166.7918190765381</v>
+        <v>166.7918186187744</v>
       </c>
       <c r="AH59" t="n">
         <v>0.03250181814076392</v>
       </c>
       <c r="AI59" t="n">
-        <v>-0.04755520090914489</v>
+        <v>-0.0475551982951401</v>
       </c>
       <c r="AJ59" t="n">
-        <v>-0.07753692791947642</v>
+        <v>-0.07753692538775714</v>
       </c>
       <c r="AK59" t="n">
         <v>217.0162200927734</v>
@@ -11903,16 +11903,16 @@
         <v>0.05776533874442791</v>
       </c>
       <c r="AV59" t="n">
-        <v>-0.1843226309643335</v>
+        <v>-0.1843225670582255</v>
       </c>
       <c r="AW59" t="n">
-        <v>8.152996012891588</v>
+        <v>8.152997018762193</v>
       </c>
       <c r="AX59" t="n">
-        <v>-0.03589257536134183</v>
+        <v>-0.0358924860808848</v>
       </c>
       <c r="AY59" t="n">
-        <v>13.01174408365016</v>
+        <v>13.01174290504081</v>
       </c>
       <c r="AZ59" t="inlineStr"/>
       <c r="BA59" t="n">
@@ -12065,13 +12065,13 @@
         <v>238.1012115478516</v>
       </c>
       <c r="AL60" t="n">
-        <v>135.6905517578125</v>
+        <v>135.6905670166016</v>
       </c>
       <c r="AM60" t="n">
         <v>-0.2188195986452622</v>
       </c>
       <c r="AN60" t="n">
-        <v>0.3707660378003503</v>
+        <v>0.3707658836538221</v>
       </c>
       <c r="AO60" t="n">
         <v>32.9285538579864</v>
@@ -12095,7 +12095,7 @@
         <v>-0.03464766810121545</v>
       </c>
       <c r="AV60" t="n">
-        <v>0.3707660378003503</v>
+        <v>0.3707658836538221</v>
       </c>
       <c r="AW60" t="n">
         <v>2.365315022323721</v>
@@ -12104,7 +12104,7 @@
         <v>0.02560388456948459</v>
       </c>
       <c r="AY60" t="n">
-        <v>12.12652192269306</v>
+        <v>12.12652368961162</v>
       </c>
       <c r="AZ60" t="inlineStr"/>
       <c r="BA60" t="n">
@@ -12290,13 +12290,13 @@
         <v>0.3580471866742656</v>
       </c>
       <c r="AW61" t="n">
-        <v>4.074691322172047</v>
+        <v>4.074690810462737</v>
       </c>
       <c r="AX61" t="n">
         <v>-0.02607548456255149</v>
       </c>
       <c r="AY61" t="n">
-        <v>15.04248294368242</v>
+        <v>15.04247782984243</v>
       </c>
       <c r="AZ61" t="inlineStr"/>
       <c r="BA61" t="n">
@@ -12630,25 +12630,25 @@
         <v>273.078256225586</v>
       </c>
       <c r="AG63" t="n">
-        <v>314.0618740844727</v>
+        <v>314.0618737792969</v>
       </c>
       <c r="AH63" t="n">
         <v>-0.07945799728869241</v>
       </c>
       <c r="AI63" t="n">
-        <v>-0.1995844589044283</v>
+        <v>-0.1995844581266598</v>
       </c>
       <c r="AJ63" t="n">
-        <v>-0.130495361712907</v>
+        <v>-0.1304953608680042</v>
       </c>
       <c r="AK63" t="n">
-        <v>402.3219299316406</v>
+        <v>402.3219604492188</v>
       </c>
       <c r="AL63" t="n">
         <v>236.5</v>
       </c>
       <c r="AM63" t="n">
-        <v>-0.3751769759964986</v>
+        <v>-0.3751770233915884</v>
       </c>
       <c r="AN63" t="n">
         <v>0.06291756821485195</v>
@@ -12874,7 +12874,7 @@
         <v>-0.3722935667825401</v>
       </c>
       <c r="AY64" t="n">
-        <v>-0.9213619079351065</v>
+        <v>-0.9213619167614913</v>
       </c>
       <c r="AZ64" t="inlineStr"/>
       <c r="BA64" t="n">
@@ -13016,16 +13016,16 @@
         <v>137.554800567627</v>
       </c>
       <c r="AG65" t="n">
-        <v>154.7436396408081</v>
+        <v>154.7436395645142</v>
       </c>
       <c r="AH65" t="n">
         <v>0.02082949914866639</v>
       </c>
       <c r="AI65" t="n">
-        <v>-0.09256368471822762</v>
+        <v>-0.09256368427083028</v>
       </c>
       <c r="AJ65" t="n">
-        <v>-0.1110794544646875</v>
+        <v>-0.1110794540264189</v>
       </c>
       <c r="AK65" t="n">
         <v>183.4681396484375</v>
@@ -13061,7 +13061,7 @@
         <v>-0.01560841976449645</v>
       </c>
       <c r="AV65" t="n">
-        <v>-0.06166660089967213</v>
+        <v>-0.06166669657620116</v>
       </c>
       <c r="AW65" t="n">
         <v>2.883612305762729</v>
@@ -13070,7 +13070,7 @@
         <v>-0.1496766437851758</v>
       </c>
       <c r="AY65" t="n">
-        <v>18.60044344292323</v>
+        <v>18.60044083375033</v>
       </c>
       <c r="AZ65" t="inlineStr"/>
       <c r="BA65" t="n">
@@ -13594,16 +13594,16 @@
         <v>145.2885821533203</v>
       </c>
       <c r="AG68" t="n">
-        <v>116.4364813995361</v>
+        <v>116.4364813613892</v>
       </c>
       <c r="AH68" t="n">
         <v>0.1623074065034387</v>
       </c>
       <c r="AI68" t="n">
-        <v>0.4503186036490816</v>
+        <v>0.4503186041242357</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.2477926196926379</v>
+        <v>0.2477926201014404</v>
       </c>
       <c r="AK68" t="n">
         <v>180.5316925048828</v>
@@ -13639,16 +13639,16 @@
         <v>0.6129842513774852</v>
       </c>
       <c r="AV68" t="n">
-        <v>0.6145965570791305</v>
+        <v>0.6145964393007453</v>
       </c>
       <c r="AW68" t="n">
-        <v>1.293937816756738</v>
+        <v>1.293938292235311</v>
       </c>
       <c r="AX68" t="n">
         <v>0.5990466171336413</v>
       </c>
       <c r="AY68" t="n">
-        <v>179.0869021166676</v>
+        <v>179.0868906696635</v>
       </c>
       <c r="AZ68" t="inlineStr"/>
       <c r="BA68" t="n">
@@ -13949,10 +13949,10 @@
         </is>
       </c>
       <c r="Z70" t="n">
-        <v>0.0006672449526377022</v>
+        <v>0.0006671692826785147</v>
       </c>
       <c r="AA70" t="n">
-        <v>1032550685492.281</v>
+        <v>1032433587464.156</v>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
@@ -14017,16 +14017,16 @@
         <v>2.008798838852081</v>
       </c>
       <c r="AV70" t="n">
-        <v>6.496951139566664</v>
+        <v>6.496950333886184</v>
       </c>
       <c r="AW70" t="n">
-        <v>18.40183875253074</v>
+        <v>18.4018414505769</v>
       </c>
       <c r="AX70" t="n">
         <v>2.226570064441672</v>
       </c>
       <c r="AY70" t="n">
-        <v>-10.52489727727343</v>
+        <v>-10.52490182906515</v>
       </c>
       <c r="AZ70" t="inlineStr"/>
       <c r="BA70" t="n">
@@ -14145,10 +14145,10 @@
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>0.0006672449526377022</v>
+        <v>0.0006671692826785147</v>
       </c>
       <c r="AA71" t="n">
-        <v>1248729263492.984</v>
+        <v>1248587649394.547</v>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
@@ -14168,16 +14168,16 @@
         <v>303340</v>
       </c>
       <c r="AG71" t="n">
-        <v>181070.4312890625</v>
+        <v>181070.43125</v>
       </c>
       <c r="AH71" t="n">
         <v>-0.06046020966572163</v>
       </c>
       <c r="AI71" t="n">
-        <v>0.5739731659722145</v>
+        <v>0.5739731663117691</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.6752597198807422</v>
+        <v>0.6752597202421475</v>
       </c>
       <c r="AK71" t="n">
         <v>362500</v>
@@ -14408,13 +14408,13 @@
         <v>7.388845264110813</v>
       </c>
       <c r="AW72" t="n">
-        <v>5.28095282343382</v>
+        <v>5.280951970792506</v>
       </c>
       <c r="AX72" t="n">
         <v>0.9540096451224696</v>
       </c>
       <c r="AY72" t="n">
-        <v>3.636716879610193</v>
+        <v>3.636716414948917</v>
       </c>
       <c r="AZ72" t="inlineStr"/>
       <c r="BA72" t="n">
@@ -14600,13 +14600,13 @@
         <v>7.227866436434194</v>
       </c>
       <c r="AW73" t="n">
-        <v>4.912028806014082</v>
+        <v>4.912029418329285</v>
       </c>
       <c r="AX73" t="n">
         <v>1.11062651104741</v>
       </c>
       <c r="AY73" t="n">
-        <v>-0.4918197389740576</v>
+        <v>-0.4918198475537601</v>
       </c>
       <c r="AZ73" t="inlineStr"/>
       <c r="BA73" t="n">
@@ -14748,16 +14748,16 @@
         <v>329.1420672607422</v>
       </c>
       <c r="AG74" t="n">
-        <v>227.9347861862183</v>
+        <v>227.9347863006592</v>
       </c>
       <c r="AH74" t="n">
         <v>0.06437317322534364</v>
       </c>
       <c r="AI74" t="n">
-        <v>0.5369746427649391</v>
+        <v>0.5369746419932591</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.4440185842973505</v>
+        <v>0.4440185835723414</v>
       </c>
       <c r="AK74" t="n">
         <v>433.3299865722656</v>
@@ -14796,13 +14796,13 @@
         <v>2.485740056595084</v>
       </c>
       <c r="AW74" t="n">
-        <v>4.844537693193175</v>
+        <v>4.844538437090752</v>
       </c>
       <c r="AX74" t="n">
         <v>0.8966647974746411</v>
       </c>
       <c r="AY74" t="n">
-        <v>1857.200146520424</v>
+        <v>1857.199852784066</v>
       </c>
       <c r="AZ74" t="inlineStr"/>
       <c r="BA74" t="n">
@@ -14944,28 +14944,28 @@
         <v>898.9240441894531</v>
       </c>
       <c r="AG75" t="n">
-        <v>464.3001769256592</v>
+        <v>464.3001767730713</v>
       </c>
       <c r="AH75" t="n">
         <v>0.08941349841853374</v>
       </c>
       <c r="AI75" t="n">
-        <v>1.109195810084234</v>
+        <v>1.109195810777401</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.9360837855837887</v>
+        <v>0.9360837862200644</v>
       </c>
       <c r="AK75" t="n">
         <v>1213.373413085938</v>
       </c>
       <c r="AL75" t="n">
-        <v>104.7119369506836</v>
+        <v>104.7119293212891</v>
       </c>
       <c r="AM75" t="n">
         <v>-0.1929112858156803</v>
       </c>
       <c r="AN75" t="n">
-        <v>8.352324255583122</v>
+        <v>8.352324937000912</v>
       </c>
       <c r="AO75" t="n">
         <v>40.4435338385203</v>
@@ -14989,16 +14989,16 @@
         <v>1.996336946400833</v>
       </c>
       <c r="AV75" t="n">
-        <v>6.96744168695323</v>
+        <v>6.967442181505431</v>
       </c>
       <c r="AW75" t="n">
-        <v>11.50179167064778</v>
+        <v>11.50178801772941</v>
       </c>
       <c r="AX75" t="n">
-        <v>2.106530793808759</v>
+        <v>2.106531094544943</v>
       </c>
       <c r="AY75" t="n">
-        <v>724.0062980070579</v>
+        <v>724.0062340221026</v>
       </c>
       <c r="AZ75" t="inlineStr"/>
       <c r="BA75" t="n">
@@ -15530,28 +15530,28 @@
         <v>868.2855505371094</v>
       </c>
       <c r="AG78" t="n">
-        <v>472.2589469909668</v>
+        <v>472.2589468383789</v>
       </c>
       <c r="AH78" t="n">
         <v>0.04843392394626966</v>
       </c>
       <c r="AI78" t="n">
-        <v>0.9276289685050294</v>
+        <v>0.9276289691278508</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.8385793558162438</v>
+        <v>0.838579356410293</v>
       </c>
       <c r="AK78" t="n">
         <v>1093.260498046875</v>
       </c>
       <c r="AL78" t="n">
-        <v>143.3166656494141</v>
+        <v>143.316650390625</v>
       </c>
       <c r="AM78" t="n">
         <v>-0.1673164552439206</v>
       </c>
       <c r="AN78" t="n">
-        <v>5.351948133389961</v>
+        <v>5.351948809675908</v>
       </c>
       <c r="AO78" t="n">
         <v>38.12116368120392</v>
@@ -15575,16 +15575,16 @@
         <v>2.20799457899861</v>
       </c>
       <c r="AV78" t="n">
-        <v>5.351948133389961</v>
+        <v>5.351948809675908</v>
       </c>
       <c r="AW78" t="n">
-        <v>11.14208755627236</v>
+        <v>11.142091263033</v>
       </c>
       <c r="AX78" t="n">
         <v>2.173743552772943</v>
       </c>
       <c r="AY78" t="n">
-        <v>171.6941981062739</v>
+        <v>171.6942605921833</v>
       </c>
       <c r="AZ78" t="inlineStr"/>
       <c r="BA78" t="n">
@@ -15724,16 +15724,16 @@
         <v>546.2103399658204</v>
       </c>
       <c r="AG79" t="n">
-        <v>301.8788362121582</v>
+        <v>301.8788361740112</v>
       </c>
       <c r="AH79" t="n">
         <v>0.06660380484910799</v>
       </c>
       <c r="AI79" t="n">
-        <v>0.9298803260458737</v>
+        <v>0.9298803262897435</v>
       </c>
       <c r="AJ79" t="n">
-        <v>0.8093694371537454</v>
+        <v>0.8093694373823868</v>
       </c>
       <c r="AK79" t="n">
         <v>746.22998046875</v>
@@ -15778,7 +15778,7 @@
         <v>2.106131402193798</v>
       </c>
       <c r="AY79" t="n">
-        <v>856.330175539636</v>
+        <v>856.3301003404326</v>
       </c>
       <c r="AZ79" t="inlineStr"/>
       <c r="BA79" t="n">
@@ -16278,13 +16278,13 @@
         <v>0.6289717605625493</v>
       </c>
       <c r="AW82" t="n">
-        <v>3.757894722428535</v>
+        <v>3.757894179517444</v>
       </c>
       <c r="AX82" t="n">
         <v>0.1424722954066484</v>
       </c>
       <c r="AY82" t="n">
-        <v>1270.11682618042</v>
+        <v>1270.116977547045</v>
       </c>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="n">
@@ -16399,10 +16399,10 @@
         </is>
       </c>
       <c r="Z83" t="n">
-        <v>0.1476428806781769</v>
+        <v>0.1477825343608856</v>
       </c>
       <c r="AA83" t="n">
-        <v>180130868353.9062</v>
+        <v>180301252046.0938</v>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
@@ -16470,13 +16470,13 @@
         <v>6.921959468381198</v>
       </c>
       <c r="AW83" t="n">
-        <v>33.3001757526419</v>
+        <v>33.30017780386748</v>
       </c>
       <c r="AX83" t="n">
         <v>0.7566271538047729</v>
       </c>
       <c r="AY83" t="n">
-        <v>235.375636016669</v>
+        <v>235.3755873091461</v>
       </c>
       <c r="AZ83" t="inlineStr"/>
       <c r="BA83" t="n">
@@ -16608,22 +16608,22 @@
         <v>25.1</v>
       </c>
       <c r="AE84" t="n">
-        <v>132.8000030517578</v>
+        <v>134</v>
       </c>
       <c r="AF84" t="n">
-        <v>152.6272821044922</v>
+        <v>152.2020959472656</v>
       </c>
       <c r="AG84" t="n">
-        <v>130.9495380401611</v>
+        <v>130.9763069152832</v>
       </c>
       <c r="AH84" t="n">
-        <v>-0.129906519852461</v>
+        <v>-0.1195916247669297</v>
       </c>
       <c r="AI84" t="n">
-        <v>0.01413113050486015</v>
+        <v>0.02308580197388332</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0.1655427303430628</v>
+        <v>0.1620582342859269</v>
       </c>
       <c r="AK84" t="n">
         <v>164.8832092285156</v>
@@ -16632,13 +16632,13 @@
         <v>108.1217498779297</v>
       </c>
       <c r="AM84" t="n">
-        <v>-0.1945814029631903</v>
+        <v>-0.1873035427501526</v>
       </c>
       <c r="AN84" t="n">
-        <v>0.2282450404445919</v>
+        <v>0.2393436117274004</v>
       </c>
       <c r="AO84" t="n">
-        <v>21.86146070926314</v>
+        <v>23.51693887882772</v>
       </c>
       <c r="AP84" t="n">
         <v>145970</v>
@@ -16650,25 +16650,25 @@
         <v>1.114166114176037</v>
       </c>
       <c r="AS84" t="n">
-        <v>-0.09413371403281867</v>
+        <v>-0.08156267576630183</v>
       </c>
       <c r="AT84" t="n">
-        <v>0.04343959838661671</v>
+        <v>0.02364382542268406</v>
       </c>
       <c r="AU84" t="n">
-        <v>0.09942912480414901</v>
+        <v>0.1013053149894143</v>
       </c>
       <c r="AV84" t="n">
-        <v>0.2020424490466763</v>
+        <v>0.2393436117274004</v>
       </c>
       <c r="AW84" t="n">
-        <v>0.8421877191097866</v>
+        <v>0.8348419057289813</v>
       </c>
       <c r="AX84" t="n">
-        <v>0.05401231484169378</v>
+        <v>0.06353649806574668</v>
       </c>
       <c r="AY84" t="n">
-        <v>7.222928080519338</v>
+        <v>7.297231456840741</v>
       </c>
       <c r="AZ84" t="inlineStr"/>
       <c r="BA84" t="n">
@@ -16783,10 +16783,10 @@
         </is>
       </c>
       <c r="Z85" t="n">
-        <v>0.1476428806781769</v>
+        <v>0.1477825343608856</v>
       </c>
       <c r="AA85" t="n">
-        <v>28523875980.19678</v>
+        <v>28550856382.55322</v>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
@@ -16854,13 +16854,13 @@
         <v>3.811417863679924</v>
       </c>
       <c r="AW85" t="n">
-        <v>9.551426845298769</v>
+        <v>9.551425935681793</v>
       </c>
       <c r="AX85" t="n">
         <v>2.295919679701158</v>
       </c>
       <c r="AY85" t="n">
-        <v>25.81189019778624</v>
+        <v>25.8118813876588</v>
       </c>
       <c r="AZ85" t="inlineStr"/>
       <c r="BA85" t="n">
@@ -16975,10 +16975,10 @@
         </is>
       </c>
       <c r="Z86" t="n">
-        <v>0.1476428806781769</v>
+        <v>0.1477825343608856</v>
       </c>
       <c r="AA86" t="n">
-        <v>107670922721.084</v>
+        <v>107772767393.916</v>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
@@ -17388,16 +17388,16 @@
         <v>405.9760382080078</v>
       </c>
       <c r="AG88" t="n">
-        <v>361.2549255371094</v>
+        <v>361.2549252319336</v>
       </c>
       <c r="AH88" t="n">
         <v>-0.0147940676839341</v>
       </c>
       <c r="AI88" t="n">
-        <v>0.1071682984696545</v>
+        <v>0.1071682994049523</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.1237937797094604</v>
+        <v>0.1237937806588028</v>
       </c>
       <c r="AK88" t="n">
         <v>480.8090515136719</v>
@@ -17436,13 +17436,13 @@
         <v>0.4629652450487607</v>
       </c>
       <c r="AW88" t="n">
-        <v>8.384254085964638</v>
+        <v>8.384253246055829</v>
       </c>
       <c r="AX88" t="n">
         <v>0.154834014083173</v>
       </c>
       <c r="AY88" t="n">
-        <v>351.2130314740801</v>
+        <v>351.2129205528598</v>
       </c>
       <c r="AZ88" t="inlineStr"/>
       <c r="BA88" t="n">
@@ -17974,28 +17974,28 @@
         <v>190.6975485229492</v>
       </c>
       <c r="AG91" t="n">
-        <v>129.671023979187</v>
+        <v>129.6710235977173</v>
       </c>
       <c r="AH91" t="n">
         <v>0.001009194235530808</v>
       </c>
       <c r="AI91" t="n">
-        <v>0.4721099096147143</v>
+        <v>0.472109913945407</v>
       </c>
       <c r="AJ91" t="n">
-        <v>0.470625762572503</v>
+        <v>0.4706257668988294</v>
       </c>
       <c r="AK91" t="n">
         <v>255.6900024414062</v>
       </c>
       <c r="AL91" t="n">
-        <v>51.04203796386719</v>
+        <v>51.04204177856445</v>
       </c>
       <c r="AM91" t="n">
         <v>-0.253431899695051</v>
       </c>
       <c r="AN91" t="n">
-        <v>2.739858497123098</v>
+        <v>2.739858217619624</v>
       </c>
       <c r="AO91" t="n">
         <v>48.92653588973677</v>
@@ -18022,13 +18022,13 @@
         <v>2.692627270706699</v>
       </c>
       <c r="AW91" t="n">
-        <v>4.271910426759877</v>
+        <v>4.271909871350892</v>
       </c>
       <c r="AX91" t="n">
-        <v>1.112489314214237</v>
+        <v>1.112489135854879</v>
       </c>
       <c r="AY91" t="n">
-        <v>248.0077526202706</v>
+        <v>248.0077332595004</v>
       </c>
       <c r="AZ91" t="inlineStr"/>
       <c r="BA91" t="n">
@@ -18170,28 +18170,28 @@
         <v>93.51835311889648</v>
       </c>
       <c r="AG92" t="n">
-        <v>73.68087131500243</v>
+        <v>73.68087148666382</v>
       </c>
       <c r="AH92" t="n">
         <v>-0.05269935383421576</v>
       </c>
       <c r="AI92" t="n">
-        <v>0.2023472952586065</v>
+        <v>0.2023472924573828</v>
       </c>
       <c r="AJ92" t="n">
-        <v>0.269235168502342</v>
+        <v>0.2692351655452832</v>
       </c>
       <c r="AK92" t="n">
         <v>102.7099990844727</v>
       </c>
       <c r="AL92" t="n">
-        <v>48.05623245239258</v>
+        <v>48.05623626708984</v>
       </c>
       <c r="AM92" t="n">
         <v>-0.1374744705719372</v>
       </c>
       <c r="AN92" t="n">
-        <v>0.8434652867482537</v>
+        <v>0.843465140414239</v>
       </c>
       <c r="AO92" t="n">
         <v>36.58184653775317</v>
@@ -18212,19 +18212,19 @@
         <v>0.24419557916485</v>
       </c>
       <c r="AU92" t="n">
-        <v>0.2179910775302019</v>
+        <v>0.2179909497705974</v>
       </c>
       <c r="AV92" t="n">
         <v>0.2119475223825824</v>
       </c>
       <c r="AW92" t="n">
-        <v>0.3290019358750822</v>
+        <v>0.3290020879846971</v>
       </c>
       <c r="AX92" t="n">
         <v>0.3771933486728183</v>
       </c>
       <c r="AY92" t="n">
-        <v>503.2814332234295</v>
+        <v>503.2812193527712</v>
       </c>
       <c r="AZ92" t="inlineStr"/>
       <c r="BA92" t="n">
@@ -18420,7 +18420,7 @@
         <v>1.641861886780454</v>
       </c>
       <c r="AY93" t="n">
-        <v>18.44134625341344</v>
+        <v>18.44135083917955</v>
       </c>
       <c r="AZ93" t="inlineStr"/>
       <c r="BA93" t="n">
@@ -18552,67 +18552,67 @@
         <v>25.2</v>
       </c>
       <c r="AE94" t="n">
-        <v>939.5</v>
+        <v>936.5</v>
       </c>
       <c r="AF94" t="n">
-        <v>995.65</v>
+        <v>996.13</v>
       </c>
       <c r="AG94" t="n">
-        <v>833.88</v>
+        <v>835.4025</v>
       </c>
       <c r="AH94" t="n">
-        <v>-0.05639531964043587</v>
+        <v>-0.05986166464216514</v>
       </c>
       <c r="AI94" t="n">
-        <v>0.1266609104427496</v>
+        <v>0.1210165159907948</v>
       </c>
       <c r="AJ94" t="n">
-        <v>0.1939967381397802</v>
+        <v>0.1923952825135189</v>
       </c>
       <c r="AK94" t="n">
         <v>1112</v>
       </c>
       <c r="AL94" t="n">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AM94" t="n">
-        <v>-0.1551258992805755</v>
+        <v>-0.1578237410071942</v>
       </c>
       <c r="AN94" t="n">
-        <v>0.8640873015873016</v>
+        <v>0.8507905138339922</v>
       </c>
       <c r="AO94" t="n">
-        <v>32.45778611632271</v>
+        <v>23.59081419624218</v>
       </c>
       <c r="AP94" t="n">
-        <v>119831</v>
+        <v>122555</v>
       </c>
       <c r="AQ94" t="n">
-        <v>147696.82</v>
+        <v>147751.3</v>
       </c>
       <c r="AR94" t="n">
-        <v>0.8113309413161366</v>
+        <v>0.8294681671159577</v>
       </c>
       <c r="AS94" t="n">
-        <v>-0.04327902240325865</v>
+        <v>-0.04487506374298822</v>
       </c>
       <c r="AT94" t="n">
-        <v>0.03526170798898076</v>
+        <v>0.02126499454743724</v>
       </c>
       <c r="AU94" t="n">
-        <v>0.1380981223500908</v>
+        <v>0.1469687691365584</v>
       </c>
       <c r="AV94" t="n">
-        <v>0.8640873015873016</v>
+        <v>0.8507905138339922</v>
       </c>
       <c r="AW94" t="n">
-        <v>2.54061155078386</v>
+        <v>2.544021081724945</v>
       </c>
       <c r="AX94" t="n">
-        <v>0.1401699029126213</v>
+        <v>0.1365291262135921</v>
       </c>
       <c r="AY94" t="n">
-        <v>26.81621423939938</v>
+        <v>26.72739497324481</v>
       </c>
       <c r="AZ94" t="inlineStr"/>
       <c r="BA94" t="n">
@@ -18798,13 +18798,13 @@
         <v>1.485924787553267</v>
       </c>
       <c r="AW95" t="n">
-        <v>1.569356231173189</v>
+        <v>1.569356484218569</v>
       </c>
       <c r="AX95" t="n">
         <v>0.9109061663612272</v>
       </c>
       <c r="AY95" t="n">
-        <v>19.81849540221389</v>
+        <v>19.81849124896149</v>
       </c>
       <c r="AZ95" t="inlineStr"/>
       <c r="BA95" t="n">
@@ -18936,22 +18936,22 @@
         <v>19.2</v>
       </c>
       <c r="AE96" t="n">
-        <v>136.5500030517578</v>
+        <v>135.0500030517578</v>
       </c>
       <c r="AF96" t="n">
-        <v>146.0310006713867</v>
+        <v>146.173000793457</v>
       </c>
       <c r="AG96" t="n">
-        <v>107.1124338150024</v>
+        <v>107.3725777816773</v>
       </c>
       <c r="AH96" t="n">
-        <v>-0.06492455421136212</v>
+        <v>-0.07609474856041332</v>
       </c>
       <c r="AI96" t="n">
-        <v>0.2748286841058807</v>
+        <v>0.2577699617714089</v>
       </c>
       <c r="AJ96" t="n">
-        <v>0.3633431289928661</v>
+        <v>0.3613624988185851</v>
       </c>
       <c r="AK96" t="n">
         <v>156.8999938964844</v>
@@ -18960,13 +18960,13 @@
         <v>60.389892578125</v>
       </c>
       <c r="AM96" t="n">
-        <v>-0.1297003928384636</v>
+        <v>-0.1392606226558697</v>
       </c>
       <c r="AN96" t="n">
-        <v>1.261140022315924</v>
+        <v>1.236301428704262</v>
       </c>
       <c r="AO96" t="n">
-        <v>29.86699946935585</v>
+        <v>26.2394304763915</v>
       </c>
       <c r="AP96" t="n">
         <v>588526</v>
@@ -18978,25 +18978,25 @@
         <v>0.5216668961249582</v>
       </c>
       <c r="AS96" t="n">
-        <v>-0.0447708571746358</v>
+        <v>-0.06150098137664184</v>
       </c>
       <c r="AT96" t="n">
-        <v>0.1492712019877682</v>
+        <v>0.1152179117567009</v>
       </c>
       <c r="AU96" t="n">
-        <v>0.6037277193233976</v>
+        <v>0.5769191640328666</v>
       </c>
       <c r="AV96" t="n">
-        <v>1.243440325510321</v>
+        <v>1.226785420008177</v>
       </c>
       <c r="AW96" t="n">
-        <v>3.91501631415559</v>
+        <v>3.830330546155774</v>
       </c>
       <c r="AX96" t="n">
-        <v>0.5305715248879002</v>
+        <v>0.5137582166782941</v>
       </c>
       <c r="AY96" t="n">
-        <v>12.04192381667881</v>
+        <v>11.89865492924968</v>
       </c>
       <c r="AZ96" t="inlineStr"/>
       <c r="BA96" t="n">
@@ -19918,28 +19918,28 @@
         <v>206.4163836669922</v>
       </c>
       <c r="AG101" t="n">
-        <v>219.7730899810791</v>
+        <v>219.7730899047852</v>
       </c>
       <c r="AH101" t="n">
         <v>-0.02934061215998851</v>
       </c>
       <c r="AI101" t="n">
-        <v>-0.08833242219235693</v>
+        <v>-0.08833242187587276</v>
       </c>
       <c r="AJ101" t="n">
-        <v>-0.06077498530523839</v>
+        <v>-0.06077498497918776</v>
       </c>
       <c r="AK101" t="n">
-        <v>247.2834320068359</v>
+        <v>247.2834167480469</v>
       </c>
       <c r="AL101" t="n">
-        <v>173.2072296142578</v>
+        <v>173.2072143554688</v>
       </c>
       <c r="AM101" t="n">
-        <v>-0.1897556622199712</v>
+        <v>-0.189755612223301</v>
       </c>
       <c r="AN101" t="n">
-        <v>0.1567646515481167</v>
+        <v>0.1567647534539631</v>
       </c>
       <c r="AO101" t="n">
         <v>29.29049506978377</v>
@@ -19963,16 +19963,16 @@
         <v>-0.1152442960791923</v>
       </c>
       <c r="AV101" t="n">
-        <v>0.1567646515481167</v>
+        <v>0.1567647534539631</v>
       </c>
       <c r="AW101" t="n">
-        <v>0.5652151057380206</v>
+        <v>0.5652156654679326</v>
       </c>
       <c r="AX101" t="n">
         <v>-0.1349333530448573</v>
       </c>
       <c r="AY101" t="n">
-        <v>6.49762173299658</v>
+        <v>6.497619592443621</v>
       </c>
       <c r="AZ101" t="inlineStr"/>
       <c r="BA101" t="n">
@@ -20110,16 +20110,16 @@
         <v>68.33011245727539</v>
       </c>
       <c r="AG102" t="n">
-        <v>39.5800168800354</v>
+        <v>39.58001675605774</v>
       </c>
       <c r="AH102" t="n">
         <v>0.04580537796062134</v>
       </c>
       <c r="AI102" t="n">
-        <v>0.8054565085473187</v>
+        <v>0.8054565142026038</v>
       </c>
       <c r="AJ102" t="n">
-        <v>0.7263790630605278</v>
+        <v>0.7263790684681162</v>
       </c>
       <c r="AK102" t="n">
         <v>79.81999969482422</v>
@@ -20155,16 +20155,16 @@
         <v>1.558649224932994</v>
       </c>
       <c r="AV102" t="n">
-        <v>1.179157582388999</v>
+        <v>1.179157835886916</v>
       </c>
       <c r="AW102" t="n">
-        <v>1.001995282711361</v>
+        <v>1.001995068756024</v>
       </c>
       <c r="AX102" t="n">
         <v>1.621283151616665</v>
       </c>
       <c r="AY102" t="n">
-        <v>31.63501736469518</v>
+        <v>31.63502802491553</v>
       </c>
       <c r="AZ102" t="inlineStr"/>
       <c r="BA102" t="n">
@@ -20492,16 +20492,16 @@
         <v>24019.4</v>
       </c>
       <c r="AG104" t="n">
-        <v>20367.691328125</v>
+        <v>20367.69135742187</v>
       </c>
       <c r="AH104" t="n">
         <v>0.04540496432050745</v>
       </c>
       <c r="AI104" t="n">
-        <v>0.2328348655464214</v>
+        <v>0.2328348637731126</v>
       </c>
       <c r="AJ104" t="n">
-        <v>0.1792892779572168</v>
+        <v>0.1792892762609282</v>
       </c>
       <c r="AK104" t="n">
         <v>26150</v>
@@ -20537,7 +20537,7 @@
         <v>0.2472633118227161</v>
       </c>
       <c r="AV104" t="n">
-        <v>0.5024855957921166</v>
+        <v>0.5024857713838278</v>
       </c>
       <c r="AW104" t="n">
         <v>0.2956386056429623</v>
@@ -20546,7 +20546,7 @@
         <v>0.2512668323366565</v>
       </c>
       <c r="AY104" t="n">
-        <v>22.41635869067181</v>
+        <v>22.41636402196004</v>
       </c>
       <c r="AZ104" t="inlineStr"/>
       <c r="BA104" t="n">
@@ -20688,28 +20688,28 @@
         <v>405.4028820800781</v>
       </c>
       <c r="AG105" t="n">
-        <v>370.6051461791992</v>
+        <v>370.6051469421387</v>
       </c>
       <c r="AH105" t="n">
         <v>0.004630250011019799</v>
       </c>
       <c r="AI105" t="n">
-        <v>0.09895937220030993</v>
+        <v>0.0989593699379574</v>
       </c>
       <c r="AJ105" t="n">
-        <v>0.09389436779178761</v>
+        <v>0.09389436553986208</v>
       </c>
       <c r="AK105" t="n">
         <v>435.7799987792969</v>
       </c>
       <c r="AL105" t="n">
-        <v>313.9706420898438</v>
+        <v>313.9706115722656</v>
       </c>
       <c r="AM105" t="n">
         <v>-0.06539997264636732</v>
       </c>
       <c r="AN105" t="n">
-        <v>0.2971913426948765</v>
+        <v>0.2971914687803656</v>
       </c>
       <c r="AO105" t="n">
         <v>45.81093261114604</v>
@@ -20733,7 +20733,7 @@
         <v>0.2779306941870878</v>
       </c>
       <c r="AV105" t="n">
-        <v>0.1520144487025483</v>
+        <v>0.1520145481452402</v>
       </c>
       <c r="AW105" t="n">
         <v>1.913155524064541</v>
@@ -20742,7 +20742,7 @@
         <v>0.2516544918972008</v>
       </c>
       <c r="AY105" t="n">
-        <v>1178.185307538381</v>
+        <v>1178.185918020038</v>
       </c>
       <c r="AZ105" t="inlineStr"/>
       <c r="BA105" t="n">
@@ -20874,22 +20874,22 @@
         <v>26.5</v>
       </c>
       <c r="AE106" t="n">
-        <v>270</v>
+        <v>269.6499938964844</v>
       </c>
       <c r="AF106" t="n">
-        <v>272.7169253540039</v>
+        <v>272.8206924438476</v>
       </c>
       <c r="AG106" t="n">
-        <v>249.4604872894287</v>
+        <v>249.6712863922119</v>
       </c>
       <c r="AH106" t="n">
-        <v>-0.009962437609903341</v>
+        <v>-0.01162191371541899</v>
       </c>
       <c r="AI106" t="n">
-        <v>0.08233573554572993</v>
+        <v>0.08002004472748081</v>
       </c>
       <c r="AJ106" t="n">
-        <v>0.09322694073628046</v>
+        <v>0.09271953690049073</v>
       </c>
       <c r="AK106" t="n">
         <v>292.75</v>
@@ -20898,13 +20898,13 @@
         <v>206.813720703125</v>
       </c>
       <c r="AM106" t="n">
-        <v>-0.07771135781383431</v>
+        <v>-0.07890693801371695</v>
       </c>
       <c r="AN106" t="n">
-        <v>0.3055226659143038</v>
+        <v>0.3038302922056075</v>
       </c>
       <c r="AO106" t="n">
-        <v>35.79337073215996</v>
+        <v>32.12075689183986</v>
       </c>
       <c r="AP106" t="n">
         <v>643592</v>
@@ -20916,25 +20916,25 @@
         <v>0.6584889291963153</v>
       </c>
       <c r="AS106" t="n">
-        <v>0.02156644899846216</v>
+        <v>0.01639655598819778</v>
       </c>
       <c r="AT106" t="n">
-        <v>0.05349618615843066</v>
+        <v>0.02362012891099896</v>
       </c>
       <c r="AU106" t="n">
-        <v>0.1580449039262368</v>
+        <v>0.1485408113326865</v>
       </c>
       <c r="AV106" t="n">
-        <v>0.2141910055945619</v>
+        <v>0.2305978932784376</v>
       </c>
       <c r="AW106" t="n">
-        <v>1.00120221057459</v>
+        <v>0.9851765960608947</v>
       </c>
       <c r="AX106" t="n">
-        <v>0.1568236382525496</v>
+        <v>0.1553240259041069</v>
       </c>
       <c r="AY106" t="n">
-        <v>13.50897077742911</v>
+        <v>13.49015806885431</v>
       </c>
       <c r="AZ106" t="inlineStr"/>
       <c r="BA106" t="n">
@@ -21076,16 +21076,16 @@
         <v>470.2074084472656</v>
       </c>
       <c r="AG107" t="n">
-        <v>434.4708938598633</v>
+        <v>434.4708941650391</v>
       </c>
       <c r="AH107" t="n">
         <v>0.02018812036822726</v>
       </c>
       <c r="AI107" t="n">
-        <v>0.1041016072339163</v>
+        <v>0.1041016064583866</v>
       </c>
       <c r="AJ107" t="n">
-        <v>0.08225295432317026</v>
+        <v>0.08225295356298745</v>
       </c>
       <c r="AK107" t="n">
         <v>503.4599914550781</v>
@@ -21118,19 +21118,19 @@
         <v>0.03237760243543963</v>
       </c>
       <c r="AU107" t="n">
-        <v>0.2737823113022542</v>
+        <v>0.2737824145239043</v>
       </c>
       <c r="AV107" t="n">
         <v>0.1116547221922246</v>
       </c>
       <c r="AW107" t="n">
-        <v>1.722768135450301</v>
+        <v>1.722767663820131</v>
       </c>
       <c r="AX107" t="n">
         <v>0.2109252523683778</v>
       </c>
       <c r="AY107" t="n">
-        <v>537.0775834311247</v>
+        <v>537.0777992808987</v>
       </c>
       <c r="AZ107" t="inlineStr"/>
       <c r="BA107" t="n">
@@ -21272,16 +21272,16 @@
         <v>299.4725476074219</v>
       </c>
       <c r="AG108" t="n">
-        <v>217.126110534668</v>
+        <v>217.1261102294922</v>
       </c>
       <c r="AH108" t="n">
         <v>0.04002852329346251</v>
       </c>
       <c r="AI108" t="n">
-        <v>0.4344658534531622</v>
+        <v>0.4344658554693372</v>
       </c>
       <c r="AJ108" t="n">
-        <v>0.3792562620404232</v>
+        <v>0.3792562639789998</v>
       </c>
       <c r="AK108" t="n">
         <v>332.2799987792969</v>
@@ -21326,7 +21326,7 @@
         <v>0.7749315156521179</v>
       </c>
       <c r="AY108" t="n">
-        <v>451.9822104087669</v>
+        <v>451.9821711406484</v>
       </c>
       <c r="AZ108" t="inlineStr"/>
       <c r="BA108" t="n">
@@ -21518,7 +21518,7 @@
         <v>0.3014092246636779</v>
       </c>
       <c r="AY109" t="n">
-        <v>54.94409013938794</v>
+        <v>54.94411460459389</v>
       </c>
       <c r="AZ109" t="inlineStr"/>
       <c r="BA109" t="n">
@@ -21704,13 +21704,13 @@
         <v>3.457147487656786</v>
       </c>
       <c r="AW110" t="n">
-        <v>6.426257549583001</v>
+        <v>6.426257997195557</v>
       </c>
       <c r="AX110" t="n">
         <v>0.8993271374731151</v>
       </c>
       <c r="AY110" t="n">
-        <v>75.10735162307959</v>
+        <v>75.10736925285615</v>
       </c>
       <c r="AZ110" t="inlineStr"/>
       <c r="BA110" t="n">
@@ -21852,28 +21852,28 @@
         <v>407.8515246582031</v>
       </c>
       <c r="AG111" t="n">
-        <v>319.6667751312256</v>
+        <v>319.6667750549316</v>
       </c>
       <c r="AH111" t="n">
         <v>-0.02991659960556514</v>
       </c>
       <c r="AI111" t="n">
-        <v>0.2376950771129316</v>
+        <v>0.2376950774083286</v>
       </c>
       <c r="AJ111" t="n">
-        <v>0.2758646077334033</v>
+        <v>0.2758646080379101</v>
       </c>
       <c r="AK111" t="n">
         <v>445.4800109863281</v>
       </c>
       <c r="AL111" t="n">
-        <v>217.7568969726562</v>
+        <v>217.7568817138672</v>
       </c>
       <c r="AM111" t="n">
         <v>-0.1118569090889536</v>
       </c>
       <c r="AN111" t="n">
-        <v>0.816934385991761</v>
+        <v>0.8169345133090624</v>
       </c>
       <c r="AO111" t="n">
         <v>37.81781564690416</v>
@@ -21897,16 +21897,16 @@
         <v>0.3303114170092663</v>
       </c>
       <c r="AV111" t="n">
-        <v>0.6357079710719991</v>
+        <v>0.6357078678860844</v>
       </c>
       <c r="AW111" t="n">
-        <v>1.523124023030024</v>
+        <v>1.523124268549611</v>
       </c>
       <c r="AX111" t="n">
         <v>0.4538465316690081</v>
       </c>
       <c r="AY111" t="n">
-        <v>890.8785904570318</v>
+        <v>890.8788301252961</v>
       </c>
       <c r="AZ111" t="inlineStr"/>
       <c r="BA111" t="n">
@@ -22048,25 +22048,25 @@
         <v>67.81264907836913</v>
       </c>
       <c r="AG112" t="n">
-        <v>60.02419466018677</v>
+        <v>60.02419464111328</v>
       </c>
       <c r="AH112" t="n">
         <v>0.02252304371351688</v>
       </c>
       <c r="AI112" t="n">
-        <v>0.1552007774605413</v>
+        <v>0.1552007778276216</v>
       </c>
       <c r="AJ112" t="n">
-        <v>0.1297552505664576</v>
+        <v>0.1297552509254525</v>
       </c>
       <c r="AK112" t="n">
-        <v>79.79306030273438</v>
+        <v>79.79306793212891</v>
       </c>
       <c r="AL112" t="n">
         <v>49.96692657470703</v>
       </c>
       <c r="AM112" t="n">
-        <v>-0.1310021689252786</v>
+        <v>-0.1310022520142922</v>
       </c>
       <c r="AN112" t="n">
         <v>0.3877178584161733</v>
@@ -22090,19 +22090,19 @@
         <v>0.09862607854849625</v>
       </c>
       <c r="AU112" t="n">
-        <v>0.2975393523804519</v>
+        <v>0.2975394450031381</v>
       </c>
       <c r="AV112" t="n">
-        <v>-0.08348584145152504</v>
+        <v>-0.08348593387548497</v>
       </c>
       <c r="AW112" t="n">
         <v>0.5285008870605208</v>
       </c>
       <c r="AX112" t="n">
-        <v>0.305782288490881</v>
+        <v>0.3057823822941217</v>
       </c>
       <c r="AY112" t="n">
-        <v>5.270668951794295</v>
+        <v>5.270667329367306</v>
       </c>
       <c r="AZ112" t="inlineStr"/>
       <c r="BA112" t="n">
@@ -22234,22 +22234,22 @@
         <v>26.3</v>
       </c>
       <c r="AE113" t="n">
-        <v>73.34999847412109</v>
+        <v>72.48000335693359</v>
       </c>
       <c r="AF113" t="n">
-        <v>74.0086003112793</v>
+        <v>74.31560035705566</v>
       </c>
       <c r="AG113" t="n">
-        <v>47.65660281181336</v>
+        <v>47.85129332542419</v>
       </c>
       <c r="AH113" t="n">
-        <v>-0.008898990582015154</v>
+        <v>-0.02470002248925907</v>
       </c>
       <c r="AI113" t="n">
-        <v>0.5391361143337461</v>
+        <v>0.5146926722338716</v>
       </c>
       <c r="AJ113" t="n">
-        <v>0.5529558538514556</v>
+        <v>0.5530531192052552</v>
       </c>
       <c r="AK113" t="n">
         <v>88</v>
@@ -22258,43 +22258,43 @@
         <v>31.03618240356445</v>
       </c>
       <c r="AM113" t="n">
-        <v>-0.1664772900668058</v>
+        <v>-0.1763635982166637</v>
       </c>
       <c r="AN113" t="n">
-        <v>1.363370517686382</v>
+        <v>1.335338876878407</v>
       </c>
       <c r="AO113" t="n">
-        <v>38.18530434024252</v>
+        <v>29.83822619533856</v>
       </c>
       <c r="AP113" t="n">
-        <v>3699154</v>
+        <v>3700611</v>
       </c>
       <c r="AQ113" t="n">
-        <v>5852464.78</v>
+        <v>5852493.92</v>
       </c>
       <c r="AR113" t="n">
-        <v>0.6320677080606028</v>
+        <v>0.6323135146460775</v>
       </c>
       <c r="AS113" t="n">
-        <v>-0.04814429278500432</v>
+        <v>-0.09467892121920896</v>
       </c>
       <c r="AT113" t="n">
-        <v>0.70859534015139</v>
+        <v>0.6304127853235546</v>
       </c>
       <c r="AU113" t="n">
-        <v>0.7740168747042462</v>
+        <v>0.7171205345503193</v>
       </c>
       <c r="AV113" t="n">
-        <v>0.9461403778849484</v>
+        <v>0.9552328380197033</v>
       </c>
       <c r="AW113" t="n">
-        <v>1.386862455077032</v>
+        <v>1.268544110126878</v>
       </c>
       <c r="AX113" t="n">
-        <v>0.9316455139229178</v>
+        <v>0.9087345091484189</v>
       </c>
       <c r="AY113" t="n">
-        <v>0.451825868137077</v>
+        <v>0.4346061605423841</v>
       </c>
       <c r="AZ113" t="inlineStr"/>
       <c r="BA113" t="n">
@@ -22486,7 +22486,7 @@
         <v>0.7463959088542806</v>
       </c>
       <c r="AY114" t="n">
-        <v>277.5895089070024</v>
+        <v>277.5894148473691</v>
       </c>
       <c r="AZ114" t="inlineStr"/>
       <c r="BA114" t="n">
@@ -22628,28 +22628,28 @@
         <v>1516.832399902344</v>
       </c>
       <c r="AG115" t="n">
-        <v>1176.413474731445</v>
+        <v>1176.413475036621</v>
       </c>
       <c r="AH115" t="n">
         <v>-0.1081809761437936</v>
       </c>
       <c r="AI115" t="n">
-        <v>0.1498848145573832</v>
+        <v>0.1498848142590894</v>
       </c>
       <c r="AJ115" t="n">
-        <v>0.2893701342962005</v>
+        <v>0.2893701339617225</v>
       </c>
       <c r="AK115" t="n">
         <v>1687.3154296875</v>
       </c>
       <c r="AL115" t="n">
-        <v>706.2978515625</v>
+        <v>706.2977905273438</v>
       </c>
       <c r="AM115" t="n">
         <v>-0.1982886149005881</v>
       </c>
       <c r="AN115" t="n">
-        <v>0.9152542900163014</v>
+        <v>0.9152544555241742</v>
       </c>
       <c r="AO115" t="n">
         <v>35.08824170085371</v>
@@ -22676,13 +22676,13 @@
         <v>0.8396994829103939</v>
       </c>
       <c r="AW115" t="n">
-        <v>2.727947675193613</v>
+        <v>2.727947361666347</v>
       </c>
       <c r="AX115" t="n">
         <v>0.4498539207849714</v>
       </c>
       <c r="AY115" t="n">
-        <v>160.1430990241444</v>
+        <v>160.1431173308092</v>
       </c>
       <c r="AZ115" t="inlineStr"/>
       <c r="BA115" t="n">
@@ -23219,13 +23219,13 @@
         <v>184.3399963378906</v>
       </c>
       <c r="AL118" t="n">
-        <v>73.89095306396484</v>
+        <v>73.89094543457031</v>
       </c>
       <c r="AM118" t="n">
         <v>-0.1281327741478991</v>
       </c>
       <c r="AN118" t="n">
-        <v>1.175097147299932</v>
+        <v>1.175097371883258</v>
       </c>
       <c r="AO118" t="n">
         <v>39.49742360530085</v>
@@ -23249,16 +23249,16 @@
         <v>0.569901672349572</v>
       </c>
       <c r="AV118" t="n">
-        <v>1.169562933713982</v>
+        <v>1.169562710272086</v>
       </c>
       <c r="AW118" t="n">
         <v>4.500466991153932</v>
       </c>
       <c r="AX118" t="n">
-        <v>0.5096451599056084</v>
+        <v>0.5096452680913273</v>
       </c>
       <c r="AY118" t="n">
-        <v>7.404463173433207</v>
+        <v>7.404462335170647</v>
       </c>
       <c r="AZ118" t="inlineStr"/>
       <c r="BA118" t="n">
@@ -23596,28 +23596,28 @@
         <v>76.80261856079102</v>
       </c>
       <c r="AG120" t="n">
-        <v>51.9581580734253</v>
+        <v>51.95815791130066</v>
       </c>
       <c r="AH120" t="n">
         <v>-0.06162054047962995</v>
       </c>
       <c r="AI120" t="n">
-        <v>0.3870776479985614</v>
+        <v>0.3870776523266488</v>
       </c>
       <c r="AJ120" t="n">
-        <v>0.4781628411895678</v>
+        <v>0.4781628458018679</v>
       </c>
       <c r="AK120" t="n">
         <v>87.34999847412109</v>
       </c>
       <c r="AL120" t="n">
-        <v>30.51562881469727</v>
+        <v>30.51562690734863</v>
       </c>
       <c r="AM120" t="n">
         <v>-0.1749284378502174</v>
       </c>
       <c r="AN120" t="n">
-        <v>1.36174060618122</v>
+        <v>1.361740753799446</v>
       </c>
       <c r="AO120" t="n">
         <v>33.27401999356185</v>
@@ -23644,13 +23644,13 @@
         <v>0.2497011302380263</v>
       </c>
       <c r="AW120" t="n">
-        <v>-0.08558284376219083</v>
+        <v>-0.08558275524567183</v>
       </c>
       <c r="AX120" t="n">
         <v>0.9455866098638481</v>
       </c>
       <c r="AY120" t="n">
-        <v>40.30864236165512</v>
+        <v>40.30863671661076</v>
       </c>
       <c r="AZ120" t="inlineStr"/>
       <c r="BA120" t="n">
@@ -23837,10 +23837,10 @@
         <v>0.5944768253767467</v>
       </c>
       <c r="AV121" t="n">
-        <v>0.7341175920367033</v>
+        <v>0.7341177313882654</v>
       </c>
       <c r="AW121" t="n">
-        <v>6.414155878825276</v>
+        <v>6.414155242003194</v>
       </c>
       <c r="AX121" t="n">
         <v>0.4983397216186964</v>
@@ -24038,7 +24038,7 @@
         <v>1.327999198802591</v>
       </c>
       <c r="AY122" t="n">
-        <v>127.9867750897095</v>
+        <v>127.9867313472839</v>
       </c>
       <c r="AZ122" t="inlineStr"/>
       <c r="BA122" t="n">
@@ -24226,13 +24226,13 @@
         <v>1.644228207456331</v>
       </c>
       <c r="AW123" t="n">
-        <v>10.8881064438188</v>
+        <v>10.88810559843212</v>
       </c>
       <c r="AX123" t="n">
         <v>0.8165378176623308</v>
       </c>
       <c r="AY123" t="n">
-        <v>31.08766645380388</v>
+        <v>31.0876695332767</v>
       </c>
       <c r="AZ123" t="inlineStr"/>
       <c r="BA123" t="n">
@@ -24364,22 +24364,22 @@
         <v>20.3</v>
       </c>
       <c r="AE124" t="n">
-        <v>141.3500061035156</v>
+        <v>140.6999969482422</v>
       </c>
       <c r="AF124" t="n">
-        <v>146.5197937011719</v>
+        <v>146.3463369750976</v>
       </c>
       <c r="AG124" t="n">
-        <v>138.3345943832397</v>
+        <v>138.3392007064819</v>
       </c>
       <c r="AH124" t="n">
-        <v>-0.03528388531722926</v>
+        <v>-0.03858203863220877</v>
       </c>
       <c r="AI124" t="n">
-        <v>0.0217979583033443</v>
+        <v>0.01706527310916894</v>
       </c>
       <c r="AJ124" t="n">
-        <v>0.05916957616007457</v>
+        <v>0.05788045780027806</v>
       </c>
       <c r="AK124" t="n">
         <v>157.5401306152344</v>
@@ -24388,13 +24388,13 @@
         <v>109.7664031982422</v>
       </c>
       <c r="AM124" t="n">
-        <v>-0.1027682562436135</v>
+        <v>-0.1068942472069001</v>
       </c>
       <c r="AN124" t="n">
-        <v>0.2877346982776896</v>
+        <v>0.2818129486682075</v>
       </c>
       <c r="AO124" t="n">
-        <v>33.49592850443869</v>
+        <v>26.86305476455431</v>
       </c>
       <c r="AP124" t="n">
         <v>504696</v>
@@ -24406,25 +24406,25 @@
         <v>0.8360170737673056</v>
       </c>
       <c r="AS124" t="n">
-        <v>0.05682247554030373</v>
+        <v>0.05353795382328341</v>
       </c>
       <c r="AT124" t="n">
-        <v>-0.02446988308715459</v>
+        <v>-0.04196822538484479</v>
       </c>
       <c r="AU124" t="n">
-        <v>0.1333081433086076</v>
+        <v>0.1254327817754612</v>
       </c>
       <c r="AV124" t="n">
-        <v>0.264496557157895</v>
+        <v>0.2818129486682075</v>
       </c>
       <c r="AW124" t="n">
-        <v>0.6417862912691255</v>
+        <v>0.6209334560339062</v>
       </c>
       <c r="AX124" t="n">
-        <v>0.1239969311720819</v>
+        <v>0.1188281426031867</v>
       </c>
       <c r="AY124" t="n">
-        <v>9.439024493313735</v>
+        <v>9.391019815565024</v>
       </c>
       <c r="AZ124" t="inlineStr"/>
       <c r="BA124" t="n">
@@ -24539,10 +24539,10 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>0.1036290898919106</v>
+        <v>0.1035312414169312</v>
       </c>
       <c r="AA125" t="n">
-        <v>3111781235.35556</v>
+        <v>3108843034.811035</v>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
@@ -24556,22 +24556,22 @@
         <v>9.1</v>
       </c>
       <c r="AE125" t="n">
-        <v>163.3500061035156</v>
+        <v>164.5</v>
       </c>
       <c r="AF125" t="n">
-        <v>191.6571319580078</v>
+        <v>191.1065481567383</v>
       </c>
       <c r="AG125" t="n">
-        <v>170.4853285980224</v>
+        <v>170.6139610671997</v>
       </c>
       <c r="AH125" t="n">
-        <v>-0.1476966996495299</v>
+        <v>-0.1392236342153834</v>
       </c>
       <c r="AI125" t="n">
-        <v>-0.04185300021523142</v>
+        <v>-0.03583505727759062</v>
       </c>
       <c r="AJ125" t="n">
-        <v>0.1241854858367617</v>
+        <v>0.1201108453338537</v>
       </c>
       <c r="AK125" t="n">
         <v>210.6000061035156</v>
@@ -24580,43 +24580,43 @@
         <v>110.4240570068359</v>
       </c>
       <c r="AM125" t="n">
-        <v>-0.2243589678567024</v>
+        <v>-0.2188984082025915</v>
       </c>
       <c r="AN125" t="n">
-        <v>0.4792972702805445</v>
+        <v>0.4897116122967338</v>
       </c>
       <c r="AO125" t="n">
-        <v>33.94738772348092</v>
+        <v>37.54579030972526</v>
       </c>
       <c r="AP125" t="n">
-        <v>233500</v>
+        <v>229757</v>
       </c>
       <c r="AQ125" t="n">
-        <v>427990.12</v>
+        <v>427915.26</v>
       </c>
       <c r="AR125" t="n">
-        <v>0.5455733417397579</v>
+        <v>0.5369217260445445</v>
       </c>
       <c r="AS125" t="n">
-        <v>-0.1590733276524292</v>
+        <v>-0.1463414498953859</v>
       </c>
       <c r="AT125" t="n">
-        <v>-0.0893631985311818</v>
+        <v>-0.1391175226975724</v>
       </c>
       <c r="AU125" t="n">
-        <v>-0.0448124941557223</v>
+        <v>-0.01690292658327586</v>
       </c>
       <c r="AV125" t="n">
-        <v>0.2325633822276465</v>
+        <v>0.2477735054937384</v>
       </c>
       <c r="AW125" t="n">
-        <v>1.157943873897437</v>
+        <v>1.115560280928108</v>
       </c>
       <c r="AX125" t="n">
-        <v>-0.1515483858798228</v>
+        <v>-0.1455752353365518</v>
       </c>
       <c r="AY125" t="n">
-        <v>1.618313189244213</v>
+        <v>1.636746272037043</v>
       </c>
       <c r="AZ125" t="inlineStr"/>
       <c r="BA125" t="n">
@@ -25110,22 +25110,22 @@
         <v>29.7</v>
       </c>
       <c r="AE128" t="n">
-        <v>273.7999877929688</v>
+        <v>272.8500061035156</v>
       </c>
       <c r="AF128" t="n">
-        <v>269.2169982910156</v>
+        <v>269.6229983520508</v>
       </c>
       <c r="AG128" t="n">
-        <v>242.9978480529785</v>
+        <v>243.2409336853027</v>
       </c>
       <c r="AH128" t="n">
-        <v>0.01702340316936102</v>
+        <v>0.01196859233518088</v>
       </c>
       <c r="AI128" t="n">
-        <v>0.1267588992527815</v>
+        <v>0.1217273423909815</v>
       </c>
       <c r="AJ128" t="n">
-        <v>0.107898693128841</v>
+        <v>0.1084606290028483</v>
       </c>
       <c r="AK128" t="n">
         <v>284.1000061035156</v>
@@ -25134,43 +25134,43 @@
         <v>203.75</v>
       </c>
       <c r="AM128" t="n">
-        <v>-0.03625490351729854</v>
+        <v>-0.03959873198982233</v>
       </c>
       <c r="AN128" t="n">
-        <v>0.3438036210697852</v>
+        <v>0.3391411342503834</v>
       </c>
       <c r="AO128" t="n">
-        <v>49.5442628136099</v>
+        <v>45.80205019883304</v>
       </c>
       <c r="AP128" t="n">
-        <v>645459</v>
+        <v>645662</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1068654.3</v>
+        <v>1068658.36</v>
       </c>
       <c r="AR128" t="n">
-        <v>0.6039923294184096</v>
+        <v>0.6041799925656315</v>
       </c>
       <c r="AS128" t="n">
-        <v>0.05918757366719052</v>
+        <v>0.03156902118531435</v>
       </c>
       <c r="AT128" t="n">
-        <v>0.1972015367142015</v>
+        <v>0.1500527127650817</v>
       </c>
       <c r="AU128" t="n">
-        <v>0.08233356557818805</v>
+        <v>0.06456815076546629</v>
       </c>
       <c r="AV128" t="n">
-        <v>0.2536241821971628</v>
+        <v>0.2648693162751559</v>
       </c>
       <c r="AW128" t="n">
-        <v>1.367685404961981</v>
+        <v>1.297994897542174</v>
       </c>
       <c r="AX128" t="n">
-        <v>0.1597713388967867</v>
+        <v>0.1557473740135686</v>
       </c>
       <c r="AY128" t="n">
-        <v>27.80212166529779</v>
+        <v>27.70218639208188</v>
       </c>
       <c r="AZ128" t="inlineStr"/>
       <c r="BA128" t="n">
@@ -25302,22 +25302,22 @@
         <v>28</v>
       </c>
       <c r="AE129" t="n">
-        <v>254.8000030517578</v>
+        <v>255.3000030517578</v>
       </c>
       <c r="AF129" t="n">
-        <v>276.9779989624024</v>
+        <v>277.1399990844727</v>
       </c>
       <c r="AG129" t="n">
-        <v>190.6347431945801</v>
+        <v>191.2817120361328</v>
       </c>
       <c r="AH129" t="n">
-        <v>-0.08007132694194619</v>
+        <v>-0.0788049220785989</v>
       </c>
       <c r="AI129" t="n">
-        <v>0.3365874382702871</v>
+        <v>0.334680667242941</v>
       </c>
       <c r="AJ129" t="n">
-        <v>0.4529250771444746</v>
+        <v>0.448857792699604</v>
       </c>
       <c r="AK129" t="n">
         <v>320.2999877929688</v>
@@ -25326,13 +25326,13 @@
         <v>105.1371765136719</v>
       </c>
       <c r="AM129" t="n">
-        <v>-0.2044957453559066</v>
+        <v>-0.2029347087681588</v>
       </c>
       <c r="AN129" t="n">
-        <v>1.423500530458168</v>
+        <v>1.428256222179973</v>
       </c>
       <c r="AO129" t="n">
-        <v>30.57910436309706</v>
+        <v>25.30396117404072</v>
       </c>
       <c r="AP129" t="n">
         <v>286489</v>
@@ -25344,25 +25344,25 @@
         <v>0.6751865518979857</v>
       </c>
       <c r="AS129" t="n">
-        <v>-0.1724585641355314</v>
+        <v>-0.1946372143477672</v>
       </c>
       <c r="AT129" t="n">
-        <v>0.2392767793861716</v>
+        <v>0.1784839599916688</v>
       </c>
       <c r="AU129" t="n">
-        <v>0.581291233680177</v>
+        <v>0.5365401377228389</v>
       </c>
       <c r="AV129" t="n">
-        <v>1.030137350528242</v>
+        <v>1.14180506156428</v>
       </c>
       <c r="AW129" t="n">
-        <v>2.73421332633239</v>
+        <v>2.780996602573403</v>
       </c>
       <c r="AX129" t="n">
-        <v>0.7196938559768227</v>
+        <v>0.7230684514151664</v>
       </c>
       <c r="AY129" t="n">
-        <v>119.9952063100407</v>
+        <v>120.2326517562336</v>
       </c>
       <c r="AZ129" t="inlineStr"/>
       <c r="BA129" t="n">
@@ -25748,13 +25748,13 @@
         <v>1.686475000035968</v>
       </c>
       <c r="AW131" t="n">
-        <v>4.504476840210782</v>
+        <v>4.504477245874732</v>
       </c>
       <c r="AX131" t="n">
         <v>0.9935572470934426</v>
       </c>
       <c r="AY131" t="n">
-        <v>25.91825501891138</v>
+        <v>25.9182525935969</v>
       </c>
       <c r="AZ131" t="inlineStr"/>
       <c r="BA131" t="n">
@@ -25896,28 +25896,28 @@
         <v>1683.27759765625</v>
       </c>
       <c r="AG132" t="n">
-        <v>1333.788044738769</v>
+        <v>1333.788038635254</v>
       </c>
       <c r="AH132" t="n">
         <v>0.06775017310965348</v>
       </c>
       <c r="AI132" t="n">
-        <v>0.3475304066329958</v>
+        <v>0.3475304127993974</v>
       </c>
       <c r="AJ132" t="n">
-        <v>0.2620278044147037</v>
+        <v>0.262027810189839</v>
       </c>
       <c r="AK132" t="n">
         <v>1989.43994140625</v>
       </c>
       <c r="AL132" t="n">
-        <v>686.0034790039062</v>
+        <v>686.00341796875</v>
       </c>
       <c r="AM132" t="n">
         <v>-0.09656988940384204</v>
       </c>
       <c r="AN132" t="n">
-        <v>1.619986634614178</v>
+        <v>1.619986867719859</v>
       </c>
       <c r="AO132" t="n">
         <v>42.68130261249851</v>
@@ -25950,7 +25950,7 @@
         <v>0.5497958659956337</v>
       </c>
       <c r="AY132" t="n">
-        <v>1019.026207960825</v>
+        <v>1019.025793905437</v>
       </c>
       <c r="AZ132" t="inlineStr"/>
       <c r="BA132" t="n">
@@ -26092,16 +26092,16 @@
         <v>423.3733288574219</v>
       </c>
       <c r="AG133" t="n">
-        <v>346.8720091247558</v>
+        <v>346.8720056152344</v>
       </c>
       <c r="AH133" t="n">
         <v>0.02535978476281486</v>
       </c>
       <c r="AI133" t="n">
-        <v>0.2514990369125769</v>
+        <v>0.2514990495747769</v>
       </c>
       <c r="AJ133" t="n">
-        <v>0.2205462468006509</v>
+        <v>0.2205462591496821</v>
       </c>
       <c r="AK133" t="n">
         <v>477.5700073242188</v>
@@ -26134,19 +26134,19 @@
         <v>0.1741139081278711</v>
       </c>
       <c r="AU133" t="n">
-        <v>0.3721351987022659</v>
+        <v>0.3721350663461367</v>
       </c>
       <c r="AV133" t="n">
-        <v>0.9103021558541806</v>
+        <v>0.9103020275843869</v>
       </c>
       <c r="AW133" t="n">
-        <v>2.960454247991606</v>
+        <v>2.960454523655781</v>
       </c>
       <c r="AX133" t="n">
         <v>0.3652661944081437</v>
       </c>
       <c r="AY133" t="n">
-        <v>138.008396437675</v>
+        <v>138.0084070502903</v>
       </c>
       <c r="AZ133" t="inlineStr"/>
       <c r="BA133" t="n">
@@ -26524,13 +26524,13 @@
         <v>0.7165034425969403</v>
       </c>
       <c r="AW135" t="n">
-        <v>6.572757964363883</v>
+        <v>6.572757192553036</v>
       </c>
       <c r="AX135" t="n">
         <v>0.4280315272499267</v>
       </c>
       <c r="AY135" t="n">
-        <v>48.65044641518445</v>
+        <v>48.65044226794548</v>
       </c>
       <c r="AZ135" t="inlineStr"/>
       <c r="BA135" t="n">
@@ -26716,13 +26716,13 @@
         <v>1.809065102870577</v>
       </c>
       <c r="AW136" t="n">
-        <v>12.62433233805926</v>
+        <v>12.62433385726749</v>
       </c>
       <c r="AX136" t="n">
         <v>0.4106542218184528</v>
       </c>
       <c r="AY136" t="n">
-        <v>11.57841765842173</v>
+        <v>11.57842024823771</v>
       </c>
       <c r="AZ136" t="inlineStr"/>
       <c r="BA136" t="n">
@@ -26908,13 +26908,13 @@
         <v>1.305639352180217</v>
       </c>
       <c r="AW137" t="n">
-        <v>1.608889339984027</v>
+        <v>1.608889040444591</v>
       </c>
       <c r="AX137" t="n">
         <v>0.4050945759565934</v>
       </c>
       <c r="AY137" t="n">
-        <v>341.0263403144162</v>
+        <v>341.0263805353297</v>
       </c>
       <c r="AZ137" t="inlineStr"/>
       <c r="BA137" t="n">
@@ -27104,13 +27104,13 @@
         <v>2.064787417039764</v>
       </c>
       <c r="AW138" t="n">
-        <v>3.548506572078137</v>
+        <v>3.548504476226856</v>
       </c>
       <c r="AX138" t="n">
         <v>1.246443706176061</v>
       </c>
       <c r="AY138" t="n">
-        <v>8731.29255587387</v>
+        <v>8731.296327683798</v>
       </c>
       <c r="AZ138" t="inlineStr"/>
       <c r="BA138" t="n">
@@ -27242,22 +27242,22 @@
         <v>27.5</v>
       </c>
       <c r="AE139" t="n">
-        <v>926.7999877929688</v>
+        <v>910.4000244140625</v>
       </c>
       <c r="AF139" t="n">
-        <v>921.4593237304688</v>
+        <v>923.1197509765625</v>
       </c>
       <c r="AG139" t="n">
-        <v>694.351842956543</v>
+        <v>696.4230020141601</v>
       </c>
       <c r="AH139" t="n">
-        <v>0.005795876090198604</v>
+        <v>-0.01377906447028554</v>
       </c>
       <c r="AI139" t="n">
-        <v>0.33476996884845</v>
+        <v>0.3072515149284969</v>
       </c>
       <c r="AJ139" t="n">
-        <v>0.3270783869556744</v>
+        <v>0.3255158837470349</v>
       </c>
       <c r="AK139" t="n">
         <v>1079</v>
@@ -27266,13 +27266,13 @@
         <v>400.14208984375</v>
       </c>
       <c r="AM139" t="n">
-        <v>-0.1410565451409002</v>
+        <v>-0.1562557697738067</v>
       </c>
       <c r="AN139" t="n">
-        <v>1.316177206339057</v>
+        <v>1.275191856896537</v>
       </c>
       <c r="AO139" t="n">
-        <v>34.94936027490418</v>
+        <v>31.98717739716291</v>
       </c>
       <c r="AP139" t="n">
         <v>107476</v>
@@ -27284,25 +27284,25 @@
         <v>0.6619580571017354</v>
       </c>
       <c r="AS139" t="n">
-        <v>-0.04806901085304904</v>
+        <v>-0.1030541631388546</v>
       </c>
       <c r="AT139" t="n">
-        <v>0.2535817586396945</v>
+        <v>0.214060249351276</v>
       </c>
       <c r="AU139" t="n">
-        <v>0.4853262722247138</v>
+        <v>0.4736287916120494</v>
       </c>
       <c r="AV139" t="n">
-        <v>0.7502039833078895</v>
+        <v>0.8133820500635158</v>
       </c>
       <c r="AW139" t="n">
-        <v>1.971036452042661</v>
+        <v>1.944103461316486</v>
       </c>
       <c r="AX139" t="n">
-        <v>0.6800441544724991</v>
+        <v>0.6503153424621462</v>
       </c>
       <c r="AY139" t="n">
-        <v>314.3192464682254</v>
+        <v>308.7396166912947</v>
       </c>
       <c r="AZ139" t="inlineStr"/>
       <c r="BA139" t="n">
@@ -27638,28 +27638,28 @@
         <v>212.8434069824219</v>
       </c>
       <c r="AG141" t="n">
-        <v>154.8032143783569</v>
+        <v>154.8032144165039</v>
       </c>
       <c r="AH141" t="n">
         <v>0.08774806584251649</v>
       </c>
       <c r="AI141" t="n">
-        <v>0.4955762075236974</v>
+        <v>0.4955762071551537</v>
       </c>
       <c r="AJ141" t="n">
-        <v>0.3749288594370399</v>
+        <v>0.3749288590982265</v>
       </c>
       <c r="AK141" t="n">
         <v>301.7099914550781</v>
       </c>
       <c r="AL141" t="n">
-        <v>84.03205871582031</v>
+        <v>84.03206634521484</v>
       </c>
       <c r="AM141" t="n">
         <v>-0.2326405792665565</v>
       </c>
       <c r="AN141" t="n">
-        <v>1.755139024445604</v>
+        <v>1.755138774302492</v>
       </c>
       <c r="AO141" t="n">
         <v>43.63074780758868</v>
@@ -27680,19 +27680,19 @@
         <v>0.3343589022001288</v>
       </c>
       <c r="AU141" t="n">
-        <v>0.7523533299101399</v>
+        <v>0.7523531275267559</v>
       </c>
       <c r="AV141" t="n">
-        <v>1.509230660718758</v>
+        <v>1.509230453235678</v>
       </c>
       <c r="AW141" t="n">
-        <v>6.81089603857342</v>
+        <v>6.810894530701525</v>
       </c>
       <c r="AX141" t="n">
         <v>0.821280415926525</v>
       </c>
       <c r="AY141" t="n">
-        <v>3814.855705709633</v>
+        <v>3814.853831383067</v>
       </c>
       <c r="AZ141" t="inlineStr"/>
       <c r="BA141" t="n">
@@ -28074,13 +28074,13 @@
         <v>2.276219758479249</v>
       </c>
       <c r="AW143" t="n">
-        <v>2.504804932643056</v>
+        <v>2.50480517328828</v>
       </c>
       <c r="AX143" t="n">
         <v>2.159211975137846</v>
       </c>
       <c r="AY143" t="n">
-        <v>3.026105131180706</v>
+        <v>3.026104178514217</v>
       </c>
       <c r="AZ143" t="inlineStr"/>
       <c r="BA143" t="n">
@@ -28222,28 +28222,28 @@
         <v>380.8338464355469</v>
       </c>
       <c r="AG144" t="n">
-        <v>273.7488339233398</v>
+        <v>273.7488342285156</v>
       </c>
       <c r="AH144" t="n">
         <v>-0.0557561795800755</v>
       </c>
       <c r="AI144" t="n">
-        <v>0.3136129237511838</v>
+        <v>0.313612922286765</v>
       </c>
       <c r="AJ144" t="n">
-        <v>0.3911797941838722</v>
+        <v>0.3911797926329816</v>
       </c>
       <c r="AK144" t="n">
         <v>483.8399963378906</v>
       </c>
       <c r="AL144" t="n">
-        <v>89.91980743408203</v>
+        <v>89.91981506347656</v>
       </c>
       <c r="AM144" t="n">
         <v>-0.2567790822890379</v>
       </c>
       <c r="AN144" t="n">
-        <v>2.999118952374642</v>
+        <v>2.99911861306282</v>
       </c>
       <c r="AO144" t="n">
         <v>39.53668502102783</v>
@@ -28267,16 +28267,16 @@
         <v>0.6637522390864634</v>
       </c>
       <c r="AV144" t="n">
-        <v>2.655653491751345</v>
+        <v>2.655653208220445</v>
       </c>
       <c r="AW144" t="n">
-        <v>1.852877252201813</v>
+        <v>1.852877597557493</v>
       </c>
       <c r="AX144" t="n">
         <v>0.7338900695814854</v>
       </c>
       <c r="AY144" t="n">
-        <v>321.8698005225353</v>
+        <v>321.8699733112988</v>
       </c>
       <c r="AZ144" t="inlineStr"/>
       <c r="BA144" t="n">
@@ -28610,28 +28610,28 @@
         <v>113.3724143981934</v>
       </c>
       <c r="AG146" t="n">
-        <v>85.38335865020753</v>
+        <v>85.3833589553833</v>
       </c>
       <c r="AH146" t="n">
         <v>0.07001335556391641</v>
       </c>
       <c r="AI146" t="n">
-        <v>0.4207686307535397</v>
+        <v>0.4207686256754521</v>
       </c>
       <c r="AJ146" t="n">
-        <v>0.3278045767987343</v>
+        <v>0.3278045720529175</v>
       </c>
       <c r="AK146" t="n">
         <v>129.5154876708984</v>
       </c>
       <c r="AL146" t="n">
-        <v>64.85703277587891</v>
+        <v>64.85704040527344</v>
       </c>
       <c r="AM146" t="n">
         <v>-0.06335528097732224</v>
       </c>
       <c r="AN146" t="n">
-        <v>0.8704216392044128</v>
+        <v>0.8704214191791921</v>
       </c>
       <c r="AO146" t="n">
         <v>53.45739456180635</v>
@@ -28658,13 +28658,13 @@
         <v>0.8007837203613268</v>
       </c>
       <c r="AW146" t="n">
-        <v>1.605746185163595</v>
+        <v>1.605746612192991</v>
       </c>
       <c r="AX146" t="n">
         <v>0.6099895768087134</v>
       </c>
       <c r="AY146" t="n">
-        <v>2447.999423320764</v>
+        <v>2447.998318245272</v>
       </c>
       <c r="AZ146" t="inlineStr"/>
       <c r="BA146" t="n">
@@ -28806,16 +28806,16 @@
         <v>344.7219982910156</v>
       </c>
       <c r="AG147" t="n">
-        <v>193.6150336074829</v>
+        <v>193.6150331878662</v>
       </c>
       <c r="AH147" t="n">
         <v>0.2617993727615253</v>
       </c>
       <c r="AI147" t="n">
-        <v>1.246571421217842</v>
+        <v>1.246571426086776</v>
       </c>
       <c r="AJ147" t="n">
-        <v>0.7804505769416279</v>
+        <v>0.780450580800351</v>
       </c>
       <c r="AK147" t="n">
         <v>465.9599914550781</v>
@@ -28848,19 +28848,19 @@
         <v>1.453969996448112</v>
       </c>
       <c r="AU147" t="n">
-        <v>2.698098364517853</v>
+        <v>2.698098604394358</v>
       </c>
       <c r="AV147" t="n">
         <v>2.452300900624646</v>
       </c>
       <c r="AW147" t="n">
-        <v>8.49142477948886</v>
+        <v>8.491426359621924</v>
       </c>
       <c r="AX147" t="n">
         <v>2.42898800734462</v>
       </c>
       <c r="AY147" t="n">
-        <v>38.61284288930269</v>
+        <v>38.6128463297336</v>
       </c>
       <c r="AZ147" t="inlineStr"/>
       <c r="BA147" t="n">
@@ -29050,13 +29050,13 @@
         <v>0.3509508024738093</v>
       </c>
       <c r="AW148" t="n">
-        <v>1.265500221123102</v>
+        <v>1.265499946928041</v>
       </c>
       <c r="AX148" t="n">
         <v>0.1744469586237913</v>
       </c>
       <c r="AY148" t="n">
-        <v>45.24491761337382</v>
+        <v>45.24490690235807</v>
       </c>
       <c r="AZ148" t="inlineStr"/>
       <c r="BA148" t="n">
@@ -29171,10 +29171,10 @@
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>1.339818000793457</v>
+        <v>1.340141177177429</v>
       </c>
       <c r="AA149" t="n">
-        <v>159578281347.0078</v>
+        <v>159616773091.3311</v>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
@@ -29188,67 +29188,67 @@
         <v>38</v>
       </c>
       <c r="AE149" t="n">
-        <v>1436.400024414062</v>
+        <v>1438.400024414062</v>
       </c>
       <c r="AF149" t="n">
-        <v>1307.171987304687</v>
+        <v>1313.96798828125</v>
       </c>
       <c r="AG149" t="n">
-        <v>1219.082796630859</v>
+        <v>1220.455052490234</v>
       </c>
       <c r="AH149" t="n">
-        <v>0.09886077606041388</v>
+        <v>0.09469944263678531</v>
       </c>
       <c r="AI149" t="n">
-        <v>0.1782628943528659</v>
+        <v>0.1785768115582218</v>
       </c>
       <c r="AJ149" t="n">
-        <v>0.07225857908689837</v>
+        <v>0.07662136807104081</v>
       </c>
       <c r="AK149" t="n">
         <v>1504.199951171875</v>
       </c>
       <c r="AL149" t="n">
-        <v>975.3168334960938</v>
+        <v>977.11669921875</v>
       </c>
       <c r="AM149" t="n">
-        <v>-0.04507374614989967</v>
+        <v>-0.04374413568259317</v>
       </c>
       <c r="AN149" t="n">
-        <v>0.4727522124940495</v>
+        <v>0.4720862160723789</v>
       </c>
       <c r="AO149" t="n">
-        <v>54.26498101929751</v>
+        <v>54.04254798122121</v>
       </c>
       <c r="AP149" t="n">
-        <v>7263301</v>
+        <v>7271649</v>
       </c>
       <c r="AQ149" t="n">
-        <v>28273056.36</v>
+        <v>28273223.32</v>
       </c>
       <c r="AR149" t="n">
-        <v>0.2568983313129151</v>
+        <v>0.2571920759687898</v>
       </c>
       <c r="AS149" t="n">
-        <v>0.1465516989384521</v>
+        <v>0.09969420826763198</v>
       </c>
       <c r="AT149" t="n">
-        <v>0.1335725844535003</v>
+        <v>0.1331835612707564</v>
       </c>
       <c r="AU149" t="n">
-        <v>0.1105242062320975</v>
+        <v>0.1176870197894437</v>
       </c>
       <c r="AV149" t="n">
-        <v>0.4727522124940495</v>
+        <v>0.4559946857814443</v>
       </c>
       <c r="AW149" t="n">
-        <v>14.00565717438729</v>
+        <v>14.36846390410763</v>
       </c>
       <c r="AX149" t="n">
-        <v>0.2000527668804299</v>
+        <v>0.2017236840991483</v>
       </c>
       <c r="AY149" t="n">
-        <v>10.53590605585391</v>
+        <v>10.55196405602961</v>
       </c>
       <c r="AZ149" t="inlineStr"/>
       <c r="BA149" t="n">
@@ -29405,13 +29405,13 @@
         <v>300.0641784667969</v>
       </c>
       <c r="AL150" t="n">
-        <v>150.8650207519531</v>
+        <v>150.8650054931641</v>
       </c>
       <c r="AM150" t="n">
         <v>-0.2085026569531685</v>
       </c>
       <c r="AN150" t="n">
-        <v>0.5742549122138061</v>
+        <v>0.5742550714371035</v>
       </c>
       <c r="AO150" t="n">
         <v>22.26511331067071</v>
@@ -29444,7 +29444,7 @@
         <v>0.05419256041366327</v>
       </c>
       <c r="AY150" t="n">
-        <v>647.3817382215242</v>
+        <v>647.3816327153274</v>
       </c>
       <c r="AZ150" t="inlineStr"/>
       <c r="BA150" t="n">
@@ -29636,7 +29636,7 @@
         <v>0.5667789954459108</v>
       </c>
       <c r="AY151" t="n">
-        <v>7.8961362537878</v>
+        <v>7.89613517248471</v>
       </c>
       <c r="AZ151" t="inlineStr"/>
       <c r="BA151" t="n">
@@ -29822,13 +29822,13 @@
         <v>0.3706422018348623</v>
       </c>
       <c r="AW152" t="n">
-        <v>4.364330746063897</v>
+        <v>4.364331333865288</v>
       </c>
       <c r="AX152" t="n">
         <v>0.348375451263538</v>
       </c>
       <c r="AY152" t="n">
-        <v>17.83057217286446</v>
+        <v>17.83057398364805</v>
       </c>
       <c r="AZ152" t="inlineStr"/>
       <c r="BA152" t="n">
@@ -30014,13 +30014,13 @@
         <v>0.238007897929065</v>
       </c>
       <c r="AW153" t="n">
-        <v>5.212913593236616</v>
+        <v>5.212914102746834</v>
       </c>
       <c r="AX153" t="n">
         <v>-0.03355509631330522</v>
       </c>
       <c r="AY153" t="n">
-        <v>29.10802381311947</v>
+        <v>29.10802680446643</v>
       </c>
       <c r="AZ153" t="inlineStr"/>
       <c r="BA153" t="n">
@@ -30212,7 +30212,7 @@
         <v>0.2543080898858463</v>
       </c>
       <c r="AY154" t="n">
-        <v>-0.1357731724427537</v>
+        <v>-0.1357731035394411</v>
       </c>
       <c r="AZ154" t="inlineStr"/>
       <c r="BA154" t="n">
@@ -30398,13 +30398,13 @@
         <v>1.049789295238969</v>
       </c>
       <c r="AW155" t="n">
-        <v>5.68485230001632</v>
+        <v>5.684852841185671</v>
       </c>
       <c r="AX155" t="n">
         <v>0.157581844149159</v>
       </c>
       <c r="AY155" t="n">
-        <v>59.09308656887164</v>
+        <v>59.09308110238211</v>
       </c>
       <c r="AZ155" t="inlineStr"/>
       <c r="BA155" t="n">
@@ -30988,7 +30988,7 @@
         <v>1.027137855257762</v>
       </c>
       <c r="AY158" t="n">
-        <v>5.736954961447857</v>
+        <v>5.7369558531661</v>
       </c>
       <c r="AZ158" t="inlineStr"/>
       <c r="BA158" t="n">
@@ -31178,7 +31178,7 @@
         <v>0.49674677477929</v>
       </c>
       <c r="AW159" t="n">
-        <v>4.749214113669887</v>
+        <v>4.749214495422165</v>
       </c>
       <c r="AX159" t="n">
         <v>0.3747178990470601</v>
@@ -32612,16 +32612,16 @@
         <v>405.9760382080078</v>
       </c>
       <c r="AG5" t="n">
-        <v>361.2549255371094</v>
+        <v>361.2549252319336</v>
       </c>
       <c r="AH5" t="n">
         <v>-0.0147940676839341</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.1071682984696545</v>
+        <v>0.1071682994049523</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.1237937797094604</v>
+        <v>0.1237937806588028</v>
       </c>
       <c r="AK5" t="n">
         <v>480.8090515136719</v>
@@ -32660,13 +32660,13 @@
         <v>0.4629652450487607</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.384254085964638</v>
+        <v>8.384253246055829</v>
       </c>
       <c r="AX5" t="n">
         <v>0.154834014083173</v>
       </c>
       <c r="AY5" t="n">
-        <v>351.2130314740801</v>
+        <v>351.2129205528598</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -33014,16 +33014,16 @@
         <v>329.1420672607422</v>
       </c>
       <c r="AG7" t="n">
-        <v>227.9347861862183</v>
+        <v>227.9347863006592</v>
       </c>
       <c r="AH7" t="n">
         <v>0.06437317322534364</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.5369746427649391</v>
+        <v>0.5369746419932591</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.4440185842973505</v>
+        <v>0.4440185835723414</v>
       </c>
       <c r="AK7" t="n">
         <v>433.3299865722656</v>
@@ -33062,13 +33062,13 @@
         <v>2.485740056595084</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.844537693193175</v>
+        <v>4.844538437090752</v>
       </c>
       <c r="AX7" t="n">
         <v>0.8966647974746411</v>
       </c>
       <c r="AY7" t="n">
-        <v>1857.200146520424</v>
+        <v>1857.199852784066</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
@@ -33270,7 +33270,7 @@
         <v>1.641861886780454</v>
       </c>
       <c r="AY8" t="n">
-        <v>18.44134625341344</v>
+        <v>18.44135083917955</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
@@ -33715,40 +33715,40 @@
         <v>0.8666666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7273344398567564</v>
+        <v>0.7253525190560661</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6800441544724991</v>
+        <v>0.6503153424621462</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5839277583758825</v>
+        <v>0.583588452388129</v>
       </c>
       <c r="N2" t="n">
-        <v>1.411908074996111</v>
+        <v>1.416119904827568</v>
       </c>
       <c r="O2" t="n">
         <v>1.305639352180217</v>
       </c>
       <c r="P2" t="n">
-        <v>1.231261274528154</v>
+        <v>1.231982266768718</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.982212128027574</v>
+        <v>3.980288208080263</v>
       </c>
       <c r="R2" t="n">
-        <v>3.006203090497208</v>
+        <v>3.006203228329295</v>
       </c>
       <c r="S2" t="n">
-        <v>3.453522603261745</v>
+        <v>3.453212444826061</v>
       </c>
       <c r="T2" t="n">
-        <v>987.015703225061</v>
+        <v>986.643841380923</v>
       </c>
       <c r="U2" t="n">
-        <v>48.65044641518445</v>
+        <v>48.65044226794548</v>
       </c>
       <c r="V2" t="n">
-        <v>1437.128496160032</v>
+        <v>1437.065034929149</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -33766,10 +33766,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>1496.124004928353</v>
+        <v>1496.162496672676</v>
       </c>
       <c r="D3" t="n">
-        <v>93.50775030802203</v>
+        <v>93.51015604204223</v>
       </c>
       <c r="E3" t="n">
         <v>47.30320301158594</v>
@@ -33781,7 +33781,7 @@
         <v>85</v>
       </c>
       <c r="H3" t="n">
-        <v>90.48120946802321</v>
+        <v>90.48132572286195</v>
       </c>
       <c r="I3" t="n">
         <v>14</v>
@@ -33790,40 +33790,40 @@
         <v>0.875</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4614154242241409</v>
+        <v>0.4615198565503109</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2271804283831381</v>
+        <v>0.2280158869924973</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8044305441012297</v>
+        <v>0.8045932556116576</v>
       </c>
       <c r="N3" t="n">
-        <v>0.75107079682039</v>
+        <v>0.7500234514008521</v>
       </c>
       <c r="O3" t="n">
         <v>0.5824449702370634</v>
       </c>
       <c r="P3" t="n">
-        <v>1.062701744882527</v>
+        <v>1.060898805341253</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.27399492076843</v>
+        <v>7.296670575950991</v>
       </c>
       <c r="R3" t="n">
-        <v>4.556772429866892</v>
+        <v>4.556772914643727</v>
       </c>
       <c r="S3" t="n">
-        <v>6.185699833358934</v>
+        <v>6.224607212746751</v>
       </c>
       <c r="T3" t="n">
-        <v>247.8259257455878</v>
+        <v>247.8268532057666</v>
       </c>
       <c r="U3" t="n">
-        <v>37.99842177017218</v>
+        <v>37.99842349038764</v>
       </c>
       <c r="V3" t="n">
-        <v>858.2266920626638</v>
+        <v>858.2062360303023</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -33841,10 +33841,10 @@
         <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>11972.54559490939</v>
+        <v>11972.66843570861</v>
       </c>
       <c r="D4" t="n">
-        <v>1496.568199363674</v>
+        <v>1496.583554463576</v>
       </c>
       <c r="E4" t="n">
         <v>448.730906624</v>
@@ -33856,7 +33856,7 @@
         <v>85</v>
       </c>
       <c r="H4" t="n">
-        <v>89.70758604960038</v>
+        <v>89.70753774928741</v>
       </c>
       <c r="I4" t="n">
         <v>8</v>
@@ -33865,40 +33865,40 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7956142003891827</v>
+        <v>0.7956141839510227</v>
       </c>
       <c r="L4" t="n">
         <v>0.4358825263117641</v>
       </c>
       <c r="M4" t="n">
-        <v>0.373437047611498</v>
+        <v>0.3734383211174508</v>
       </c>
       <c r="N4" t="n">
-        <v>1.461536661793594</v>
+        <v>1.461536633495111</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8336772562959124</v>
+        <v>0.8336772025518118</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7660153783260093</v>
+        <v>0.766033813408493</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.046953241505195</v>
+        <v>5.046952902772387</v>
       </c>
       <c r="R4" t="n">
         <v>1.531597834322677</v>
       </c>
       <c r="S4" t="n">
-        <v>5.266256114974095</v>
+        <v>5.266375729823522</v>
       </c>
       <c r="T4" t="n">
-        <v>1274.067947302685</v>
+        <v>1274.067782598772</v>
       </c>
       <c r="U4" t="n">
-        <v>368.0056166780973</v>
+        <v>368.0056662041238</v>
       </c>
       <c r="V4" t="n">
-        <v>3689.204468094933</v>
+        <v>3689.166228473247</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -33940,40 +33940,40 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>2.303326382422048</v>
+        <v>2.281549378431186</v>
       </c>
       <c r="L5" t="n">
         <v>1.841141636730317</v>
       </c>
       <c r="M5" t="n">
-        <v>2.028906411629726</v>
+        <v>2.023149242458056</v>
       </c>
       <c r="N5" t="n">
-        <v>5.03797526641854</v>
+        <v>4.989204617586909</v>
       </c>
       <c r="O5" t="n">
         <v>5.429883716020687</v>
       </c>
       <c r="P5" t="n">
-        <v>4.582935046181752</v>
+        <v>4.570041600597397</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.606826823379718</v>
+        <v>5.593319177576054</v>
       </c>
       <c r="R5" t="n">
         <v>5.771676410395915</v>
       </c>
       <c r="S5" t="n">
-        <v>6.323647196347297</v>
+        <v>6.320076178753674</v>
       </c>
       <c r="T5" t="n">
-        <v>35.10414900302618</v>
+        <v>35.04190478791755</v>
       </c>
       <c r="U5" t="n">
-        <v>28.33033194284154</v>
+        <v>28.33032159671425</v>
       </c>
       <c r="V5" t="n">
-        <v>48.2469449782201</v>
+        <v>48.23049466471921</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -33991,10 +33991,10 @@
         <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>1750.926637813314</v>
+        <v>1750.923699612769</v>
       </c>
       <c r="D6" t="n">
-        <v>76.12724512231799</v>
+        <v>76.12711737446823</v>
       </c>
       <c r="E6" t="n">
         <v>43.22962687916699</v>
@@ -34006,7 +34006,7 @@
         <v>85</v>
       </c>
       <c r="H6" t="n">
-        <v>88.63419468922891</v>
+        <v>88.63431825373999</v>
       </c>
       <c r="I6" t="n">
         <v>20</v>
@@ -34015,40 +34015,40 @@
         <v>0.8695652173913043</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5210620311618787</v>
+        <v>0.5200356810245045</v>
       </c>
       <c r="L6" t="n">
         <v>0.4983397216186964</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5390307555256388</v>
+        <v>0.5373625032870161</v>
       </c>
       <c r="N6" t="n">
-        <v>1.002775391335191</v>
+        <v>1.005412930331974</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6849127815543512</v>
+        <v>0.6849127996371749</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8597937437412457</v>
+        <v>0.8624194491710256</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.118208769985672</v>
+        <v>3.109227775740857</v>
       </c>
       <c r="R6" t="n">
-        <v>1.622946079240163</v>
+        <v>1.622945966184871</v>
       </c>
       <c r="S6" t="n">
-        <v>2.896820324421084</v>
+        <v>2.887392977911969</v>
       </c>
       <c r="T6" t="n">
-        <v>175.1181854964813</v>
+        <v>175.1153744367016</v>
       </c>
       <c r="U6" t="n">
-        <v>31.08766645380388</v>
+        <v>31.0876695332767</v>
       </c>
       <c r="V6" t="n">
-        <v>336.5079937325692</v>
+        <v>336.5046055009283</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -34066,10 +34066,10 @@
         <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>4886.694706455062</v>
+        <v>4886.4359943285</v>
       </c>
       <c r="D7" t="n">
-        <v>407.2245588712552</v>
+        <v>407.202999527375</v>
       </c>
       <c r="E7" t="n">
         <v>232.3807105032109</v>
@@ -34081,7 +34081,7 @@
         <v>85</v>
       </c>
       <c r="H7" t="n">
-        <v>85.33438429557582</v>
+        <v>85.33440199953682</v>
       </c>
       <c r="I7" t="n">
         <v>12</v>
@@ -34090,40 +34090,40 @@
         <v>0.9230769230769231</v>
       </c>
       <c r="K7" t="n">
-        <v>2.105832567555217</v>
+        <v>2.105832592616566</v>
       </c>
       <c r="L7" t="n">
         <v>1.664310437762967</v>
       </c>
       <c r="M7" t="n">
-        <v>2.190735940288443</v>
+        <v>2.190763210442809</v>
       </c>
       <c r="N7" t="n">
-        <v>9.886561599551063</v>
+        <v>9.886561620166002</v>
       </c>
       <c r="O7" t="n">
-        <v>6.732196413259947</v>
+        <v>6.732196257695808</v>
       </c>
       <c r="P7" t="n">
-        <v>8.704597341596575</v>
+        <v>8.704791764428737</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.412159889257294</v>
+        <v>7.412160262351141</v>
       </c>
       <c r="R7" t="n">
-        <v>5.096490814723951</v>
+        <v>5.096490694560895</v>
       </c>
       <c r="S7" t="n">
-        <v>9.726786369303451</v>
+        <v>9.72677353701183</v>
       </c>
       <c r="T7" t="n">
-        <v>329.9796135730608</v>
+        <v>329.979581322507</v>
       </c>
       <c r="U7" t="n">
         <v>58.94978088356092</v>
       </c>
       <c r="V7" t="n">
-        <v>394.0965509432351</v>
+        <v>394.1157227797556</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -34165,40 +34165,40 @@
         <v>0.75</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2611099799062427</v>
+        <v>0.2609476375450241</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1987162444835392</v>
+        <v>0.1967042620419301</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1627585029045427</v>
+        <v>0.160815145947719</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3153085004829326</v>
+        <v>0.3460367117614402</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2221291571549595</v>
+        <v>0.2277517241939561</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1904252267567244</v>
+        <v>0.2020411536850994</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.620702308913479</v>
+        <v>1.614975501118781</v>
       </c>
       <c r="R8" t="n">
-        <v>1.576368462334159</v>
+        <v>1.541523208624256</v>
       </c>
       <c r="S8" t="n">
-        <v>1.389659618635162</v>
+        <v>1.355407295924796</v>
       </c>
       <c r="T8" t="n">
-        <v>98.61344081515855</v>
+        <v>98.6478183584028</v>
       </c>
       <c r="U8" t="n">
-        <v>87.78331744073463</v>
+        <v>87.90204016383107</v>
       </c>
       <c r="V8" t="n">
-        <v>76.02879389579181</v>
+        <v>75.98837766026236</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -34216,10 +34216,10 @@
         <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>3639.364546616234</v>
+        <v>3639.66375538361</v>
       </c>
       <c r="D9" t="n">
-        <v>173.3030736483921</v>
+        <v>173.3173216849338</v>
       </c>
       <c r="E9" t="n">
         <v>63.484960768</v>
@@ -34231,7 +34231,7 @@
         <v>85</v>
       </c>
       <c r="H9" t="n">
-        <v>83.82058521833815</v>
+        <v>83.82091624059321</v>
       </c>
       <c r="I9" t="n">
         <v>17</v>
@@ -34240,40 +34240,40 @@
         <v>0.8095238095238095</v>
       </c>
       <c r="K9" t="n">
-        <v>0.723236616641208</v>
+        <v>0.7227161366391155</v>
       </c>
       <c r="L9" t="n">
         <v>0.7195215682835878</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4569560371075359</v>
+        <v>0.4567927085220017</v>
       </c>
       <c r="N9" t="n">
-        <v>2.346580830523993</v>
+        <v>2.346930810111189</v>
       </c>
       <c r="O9" t="n">
         <v>1.649707124257812</v>
       </c>
       <c r="P9" t="n">
-        <v>1.513633691248002</v>
+        <v>1.513834657166214</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.927923568162472</v>
+        <v>7.923259258574319</v>
       </c>
       <c r="R9" t="n">
-        <v>3.757894722428535</v>
+        <v>3.757894179517444</v>
       </c>
       <c r="S9" t="n">
-        <v>9.39246567419897</v>
+        <v>9.393711037368867</v>
       </c>
       <c r="T9" t="n">
-        <v>193.3861672047686</v>
+        <v>193.3786416433888</v>
       </c>
       <c r="U9" t="n">
-        <v>26.81621423939938</v>
+        <v>26.72739497324481</v>
       </c>
       <c r="V9" t="n">
-        <v>310.9244825403918</v>
+        <v>310.9161614111101</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -34315,13 +34315,13 @@
         <v>0.5</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2102573472522999</v>
+        <v>0.2102573578523762</v>
       </c>
       <c r="L10" t="n">
         <v>0.09311950856431284</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2520480258477386</v>
+        <v>0.2520480357927934</v>
       </c>
       <c r="N10" t="n">
         <v>0.2458892035961248</v>
@@ -34333,22 +34333,22 @@
         <v>0.4432512953737321</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.646266112248328</v>
+        <v>1.646266232450466</v>
       </c>
       <c r="R10" t="n">
         <v>0.7604729894282652</v>
       </c>
       <c r="S10" t="n">
-        <v>6.253500885573207</v>
+        <v>6.253501474352138</v>
       </c>
       <c r="T10" t="n">
-        <v>61.6433730625065</v>
+        <v>61.64337716404984</v>
       </c>
       <c r="U10" t="n">
         <v>7.762627632492336</v>
       </c>
       <c r="V10" t="n">
-        <v>254.9729418945152</v>
+        <v>254.9729038340867</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -34399,31 +34399,31 @@
         <v>1.52461168451704</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2150646302695592</v>
+        <v>0.2150647570185179</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2150646302695592</v>
+        <v>0.2150647570185179</v>
       </c>
       <c r="P11" t="n">
-        <v>1.088979265447312</v>
+        <v>1.088979507089518</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.001995282711361</v>
+        <v>1.001995068756024</v>
       </c>
       <c r="R11" t="n">
-        <v>1.001995282711361</v>
+        <v>1.001995068756024</v>
       </c>
       <c r="S11" t="n">
-        <v>1.001995282711361</v>
+        <v>1.001995068756024</v>
       </c>
       <c r="T11" t="n">
-        <v>15.76681283666081</v>
+        <v>15.76681816677099</v>
       </c>
       <c r="U11" t="n">
-        <v>15.76681283666081</v>
+        <v>15.76681816677099</v>
       </c>
       <c r="V11" t="n">
-        <v>30.15075386699116</v>
+        <v>30.15076402864925</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -34465,40 +34465,40 @@
         <v>0.2105263157894737</v>
       </c>
       <c r="K12" t="n">
-        <v>0.01168974001694152</v>
+        <v>0.009916394939796638</v>
       </c>
       <c r="L12" t="n">
         <v>0.02155212588028221</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1941747190447664</v>
+        <v>0.1902767800191833</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2532544291639344</v>
+        <v>0.2505360673819916</v>
       </c>
       <c r="O12" t="n">
         <v>0.2522044132542418</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4030073905286187</v>
+        <v>0.3970322874329167</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.492409329334427</v>
+        <v>2.473428030958024</v>
       </c>
       <c r="R12" t="n">
-        <v>1.699661016949153</v>
+        <v>1.699660533643547</v>
       </c>
       <c r="S12" t="n">
-        <v>2.291578248968016</v>
+        <v>2.243072145301392</v>
       </c>
       <c r="T12" t="n">
-        <v>78.00173570356627</v>
+        <v>77.99177181410191</v>
       </c>
       <c r="U12" t="n">
-        <v>13.01174408365016</v>
+        <v>13.01174290504081</v>
       </c>
       <c r="V12" t="n">
-        <v>108.6302089828917</v>
+        <v>108.6083264718735</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -34540,13 +34540,13 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>0.5548069150076028</v>
+        <v>0.5548069289366998</v>
       </c>
       <c r="L13" t="n">
         <v>0.05695954192774511</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01272236499219526</v>
+        <v>0.01272240383025292</v>
       </c>
       <c r="N13" t="n">
         <v>0.7305351261040899</v>
@@ -34558,22 +34558,22 @@
         <v>0.3106504585193416</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5024626683807663</v>
+        <v>0.5024626815934734</v>
       </c>
       <c r="R13" t="n">
-        <v>0.421402410238742</v>
+        <v>0.4214024930006172</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9555870704686314</v>
+        <v>0.9555871230072505</v>
       </c>
       <c r="T13" t="n">
-        <v>1054.194266907383</v>
+        <v>1054.194391575702</v>
       </c>
       <c r="U13" t="n">
-        <v>13.32053004241692</v>
+        <v>13.32052915366983</v>
       </c>
       <c r="V13" t="n">
-        <v>2114.389039377671</v>
+        <v>2114.389480019465</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -34624,31 +34624,31 @@
         <v>-0.0511859355338434</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3715001660228982</v>
+        <v>0.3715001416727851</v>
       </c>
       <c r="O14" t="n">
         <v>0.08879809751909096</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2403582871187377</v>
+        <v>0.2403582566820559</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5256373482043928</v>
+        <v>0.5256374271316632</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4364418153609975</v>
+        <v>0.436441943995166</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6773288453664682</v>
+        <v>0.6773289300522866</v>
       </c>
       <c r="T14" t="n">
-        <v>16.36577907330306</v>
+        <v>16.36577750168141</v>
       </c>
       <c r="U14" t="n">
-        <v>3.138295244484146</v>
+        <v>3.138295688045482</v>
       </c>
       <c r="V14" t="n">
-        <v>2.869338379592058</v>
+        <v>2.869338172427715</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>

--- a/company_radar_output.xlsx
+++ b/company_radar_output.xlsx
@@ -876,13 +876,13 @@
         <v>1.528606448484714</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.300458717820811</v>
+        <v>2.300457864213741</v>
       </c>
       <c r="AX2" t="n">
         <v>1.548691064551167</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.029421553155386</v>
+        <v>3.029423143550747</v>
       </c>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
@@ -1844,13 +1844,13 @@
         <v>0.6685858600899632</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.589343367375404</v>
+        <v>1.589343207392941</v>
       </c>
       <c r="AX7" t="n">
         <v>0.01588514371095506</v>
       </c>
       <c r="AY7" t="n">
-        <v>127.4642730048494</v>
+        <v>127.4642976163415</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
@@ -1992,25 +1992,25 @@
         <v>171.0482208251953</v>
       </c>
       <c r="AG8" t="n">
-        <v>186.1441626739502</v>
+        <v>186.1441630554199</v>
       </c>
       <c r="AH8" t="n">
         <v>-0.3277334466911241</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.3822530010506652</v>
+        <v>-0.382253002316629</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0.08109812111162962</v>
+        <v>-0.08109812299475738</v>
       </c>
       <c r="AK8" t="n">
-        <v>324.6299438476562</v>
+        <v>324.6299743652344</v>
       </c>
       <c r="AL8" t="n">
         <v>114.9899978637695</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0.6457812963867173</v>
+        <v>-0.6457813296858512</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
@@ -2040,13 +2040,13 @@
         <v>-0.5210616070093947</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.4142089824599067</v>
+        <v>0.4142087170683484</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.4067797670865845</v>
+        <v>-0.4067797203892654</v>
       </c>
       <c r="AY8" t="n">
-        <v>2287.922666660734</v>
+        <v>2287.921648272549</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
@@ -2238,7 +2238,7 @@
         <v>-0.2942801048754975</v>
       </c>
       <c r="AY9" t="n">
-        <v>616.951843445177</v>
+        <v>616.9520005613909</v>
       </c>
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
@@ -2430,7 +2430,7 @@
         <v>-0.2733409052459868</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.2691922576099308</v>
+        <v>0.2691921480165524</v>
       </c>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
@@ -2764,25 +2764,25 @@
         <v>605.8271325683594</v>
       </c>
       <c r="AG12" t="n">
-        <v>637.1217367553711</v>
+        <v>637.121735534668</v>
       </c>
       <c r="AH12" t="n">
         <v>-0.01755802861099631</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.06581432070974047</v>
+        <v>-0.06581431891987322</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0.04911871998965811</v>
+        <v>-0.04911871816780256</v>
       </c>
       <c r="AK12" t="n">
-        <v>787.419189453125</v>
+        <v>787.4192504882812</v>
       </c>
       <c r="AL12" t="n">
         <v>525.233154296875</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0.2441256062672602</v>
+        <v>-0.2441256648572828</v>
       </c>
       <c r="AN12" t="n">
         <v>0.133191988305045</v>
@@ -2812,7 +2812,7 @@
         <v>-0.1646043904304488</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.7819161221898747</v>
+        <v>0.7819162849953445</v>
       </c>
       <c r="AX12" t="n">
         <v>-0.08326788778625338</v>
@@ -2960,16 +2960,16 @@
         <v>399.0711993408203</v>
       </c>
       <c r="AG13" t="n">
-        <v>434.7114598083496</v>
+        <v>434.7114582824707</v>
       </c>
       <c r="AH13" t="n">
         <v>-0.04352904234252564</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.1219462850707672</v>
+        <v>-0.1219462819887144</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.08198601546699946</v>
+        <v>-0.08198601224468238</v>
       </c>
       <c r="AK13" t="n">
         <v>538.6585693359375</v>
@@ -3008,13 +3008,13 @@
         <v>-0.2468899665580032</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.4357957987328769</v>
+        <v>0.4357956339116291</v>
       </c>
       <c r="AX13" t="n">
         <v>-0.1893266980326783</v>
       </c>
       <c r="AY13" t="n">
-        <v>6454.77646800941</v>
+        <v>6454.778501794493</v>
       </c>
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="n">
@@ -3346,22 +3346,22 @@
         <v>5.9</v>
       </c>
       <c r="AE15" t="n">
-        <v>268.0599975585938</v>
+        <v>265.1300048828125</v>
       </c>
       <c r="AF15" t="n">
-        <v>235.095998840332</v>
+        <v>232.7743988037109</v>
       </c>
       <c r="AG15" t="n">
-        <v>209.5536502838135</v>
+        <v>209.4259503173828</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.1402150563210969</v>
+        <v>0.1389998481163974</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.2791950757982069</v>
+        <v>0.265984489892541</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.1218893038700339</v>
+        <v>0.1114878478571724</v>
       </c>
       <c r="AK15" t="n">
         <v>280.1600036621094</v>
@@ -3370,43 +3370,43 @@
         <v>121.1100006103516</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0.04318962716073127</v>
+        <v>-0.05364791041844785</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.213359724280953</v>
+        <v>1.189166902375122</v>
       </c>
       <c r="AO15" t="n">
-        <v>55.58884818731334</v>
+        <v>54.7501101765911</v>
       </c>
       <c r="AP15" t="n">
-        <v>3443800</v>
+        <v>3129192</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8043354</v>
+        <v>8037061.84</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.4281547225199836</v>
+        <v>0.3893452684942885</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.1805690145373131</v>
+        <v>0.1734012324131395</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.9103476593984436</v>
+        <v>0.8109973766138203</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.2783632716752811</v>
+        <v>0.2557665833900429</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.2466746918064591</v>
+        <v>0.2473184415130953</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.06254954358510889</v>
+        <v>0.05705285519785575</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.2369525598904461</v>
+        <v>0.2234322212581379</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.05564527740074299</v>
+        <v>0.04410669290780267</v>
       </c>
       <c r="AZ15" t="inlineStr"/>
       <c r="BA15" t="n">
@@ -3735,7 +3735,7 @@
         <v>43727</v>
       </c>
       <c r="AD17" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="AE17" t="n">
         <v>246.8600006103516</v>
@@ -4177,16 +4177,16 @@
         <v>0.1977093682899687</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.3325425942828277</v>
+        <v>0.3325427361689419</v>
       </c>
       <c r="AW19" t="n">
-        <v>8.008866690817957</v>
+        <v>8.00886425889888</v>
       </c>
       <c r="AX19" t="n">
         <v>0.1027182559175892</v>
       </c>
       <c r="AY19" t="n">
-        <v>335.3182371164312</v>
+        <v>335.3182018112477</v>
       </c>
       <c r="AZ19" t="inlineStr"/>
       <c r="BA19" t="n">
@@ -4489,7 +4489,7 @@
         </is>
       </c>
       <c r="X21" t="n">
-        <v>6099881984</v>
+        <v>6146816512</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>1</v>
       </c>
       <c r="AA21" t="n">
-        <v>6099881984</v>
+        <v>6146816512</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
@@ -4906,16 +4906,16 @@
         <v>260.0723986816406</v>
       </c>
       <c r="AG23" t="n">
-        <v>269.6400504302978</v>
+        <v>269.6400508880615</v>
       </c>
       <c r="AH23" t="n">
         <v>-0.1764216290264613</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.2056447026337634</v>
+        <v>-0.205644703982328</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-0.03548305132486418</v>
+        <v>-0.03548305296230947</v>
       </c>
       <c r="AK23" t="n">
         <v>329.2300109863281</v>
@@ -4954,13 +4954,13 @@
         <v>-0.1567759898220743</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.9754196189622977</v>
+        <v>0.9754197579606441</v>
       </c>
       <c r="AX23" t="n">
         <v>-0.2555861442240872</v>
       </c>
       <c r="AY23" t="n">
-        <v>147.2551797551469</v>
+        <v>147.2553020845942</v>
       </c>
       <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="n">
@@ -5102,28 +5102,28 @@
         <v>306.2314001464844</v>
       </c>
       <c r="AG24" t="n">
-        <v>275.6634300994873</v>
+        <v>275.6634301757812</v>
       </c>
       <c r="AH24" t="n">
         <v>0.08747825616306271</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.2080673482640933</v>
+        <v>0.2080673479297428</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.1108887386185575</v>
+        <v>0.1108887383111026</v>
       </c>
       <c r="AK24" t="n">
         <v>333.739990234375</v>
       </c>
       <c r="AL24" t="n">
-        <v>201.5803070068359</v>
+        <v>201.5802917480469</v>
       </c>
       <c r="AM24" t="n">
         <v>-0.002157371731800861</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.6520462437949288</v>
+        <v>0.6520463688479532</v>
       </c>
       <c r="AO24" t="n">
         <v>67.69819197013604</v>
@@ -5147,16 +5147,16 @@
         <v>0.3451004363281185</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.5640961049740723</v>
+        <v>0.5640959928815594</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.398356596783458</v>
+        <v>1.398356333224834</v>
       </c>
       <c r="AX24" t="n">
         <v>0.2310936115888242</v>
       </c>
       <c r="AY24" t="n">
-        <v>3390.000378799345</v>
+        <v>3389.999349752013</v>
       </c>
       <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="n">
@@ -5538,13 +5538,13 @@
         <v>3.079540570857752</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.8463316748914853</v>
+        <v>0.8463315340327804</v>
       </c>
       <c r="AX26" t="n">
         <v>1.344337155683138</v>
       </c>
       <c r="AY26" t="n">
-        <v>507.6509635812565</v>
+        <v>507.6507547796251</v>
       </c>
       <c r="AZ26" t="inlineStr"/>
       <c r="BA26" t="n">
@@ -6141,12 +6141,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>NVIDIA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -6156,16 +6156,16 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Edge/on-device AI chips</t>
+          <t>GPU + CUDA + NVLink/networking + rack-scale systems</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Edge/on-device AI chips</t>
+          <t>GPU, networking, CUDA, racks AI, full-stack AI infra</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G30" t="n">
         <v>1</v>
@@ -6203,7 +6203,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="Q30" s="1" t="n">
         <v>46192</v>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>QUALCOMM Incorporated</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -6237,7 +6237,7 @@
         </is>
       </c>
       <c r="X30" t="n">
-        <v>175986376704</v>
+        <v>5009871732736</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -6248,101 +6248,101 @@
         <v>1</v>
       </c>
       <c r="AA30" t="n">
-        <v>175986376704</v>
+        <v>5009871732736</v>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Mega cap</t>
         </is>
       </c>
       <c r="AC30" s="2" t="n">
-        <v>33585</v>
+        <v>36182</v>
       </c>
       <c r="AD30" t="n">
-        <v>34.6</v>
+        <v>27.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>166.9700012207031</v>
+        <v>208.7599945068359</v>
       </c>
       <c r="AF30" t="n">
-        <v>202.7853863525391</v>
+        <v>209.381159362793</v>
       </c>
       <c r="AG30" t="n">
-        <v>167.9382158660889</v>
+        <v>192.6087390899658</v>
       </c>
       <c r="AH30" t="n">
-        <v>-0.1766171901044756</v>
+        <v>-0.002966670247922076</v>
       </c>
       <c r="AI30" t="n">
-        <v>-0.005765302676299489</v>
+        <v>0.0838552575193694</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0.2074999445881738</v>
+        <v>0.08708026620221476</v>
       </c>
       <c r="AK30" t="n">
-        <v>250.0962829589844</v>
+        <v>235.465576171875</v>
       </c>
       <c r="AL30" t="n">
-        <v>123.6134414672852</v>
+        <v>164.9777221679688</v>
       </c>
       <c r="AM30" t="n">
-        <v>-0.3323771179434678</v>
+        <v>-0.1134160759258741</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.3507430845608523</v>
+        <v>0.2653829363354354</v>
       </c>
       <c r="AO30" t="n">
-        <v>29.98974296053153</v>
+        <v>62.12357677626078</v>
       </c>
       <c r="AP30" t="n">
-        <v>9990800</v>
+        <v>110844026</v>
       </c>
       <c r="AQ30" t="n">
-        <v>19932330</v>
+        <v>154245120.52</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.5012359317751612</v>
+        <v>0.7186225770145354</v>
       </c>
       <c r="AS30" t="n">
-        <v>-0.1851146598615494</v>
+        <v>0.04904519852681366</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.1258762995109546</v>
+        <v>0.04690093091903691</v>
       </c>
       <c r="AU30" t="n">
-        <v>0.08241985428123066</v>
+        <v>0.1307867472766364</v>
       </c>
       <c r="AV30" t="n">
-        <v>0.07333940109629733</v>
+        <v>0.2240194478995963</v>
       </c>
       <c r="AW30" t="n">
-        <v>0.3401681519700819</v>
+        <v>10.53472335514016</v>
       </c>
       <c r="AX30" t="n">
-        <v>-0.02495846344970698</v>
+        <v>0.1067757956483397</v>
       </c>
       <c r="AY30" t="n">
-        <v>493.897840740584</v>
+        <v>5557.178541655405</v>
       </c>
       <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>Positive momentum</t>
+          <t>Strong momentum</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6352,16 +6352,16 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>GPU + CUDA + NVLink/networking + rack-scale systems</t>
+          <t>Edge/on-device AI chips</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>GPU, networking, CUDA, racks AI, full-stack AI infra</t>
+          <t>Edge/on-device AI chips</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G31" t="n">
         <v>1</v>
@@ -6399,7 +6399,7 @@
         <v>1</v>
       </c>
       <c r="P31" t="n">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="Q31" s="1" t="n">
         <v>46192</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>QUALCOMM Incorporated</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -6433,7 +6433,7 @@
         </is>
       </c>
       <c r="X31" t="n">
-        <v>5009871732736</v>
+        <v>175986376704</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -6444,85 +6444,85 @@
         <v>1</v>
       </c>
       <c r="AA31" t="n">
-        <v>5009871732736</v>
+        <v>175986376704</v>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>Mega cap</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC31" s="2" t="n">
-        <v>36182</v>
+        <v>33585</v>
       </c>
       <c r="AD31" t="n">
-        <v>27.5</v>
+        <v>34.6</v>
       </c>
       <c r="AE31" t="n">
-        <v>206.8399963378906</v>
+        <v>166.9700012207031</v>
       </c>
       <c r="AF31" t="n">
-        <v>209.1074996948242</v>
+        <v>202.7853863525391</v>
       </c>
       <c r="AG31" t="n">
-        <v>192.7164206695557</v>
+        <v>167.9382161712647</v>
       </c>
       <c r="AH31" t="n">
-        <v>-0.01084372086244079</v>
+        <v>-0.1766171901044756</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.07328683056309027</v>
+        <v>-0.005765304483013822</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.08505284068851493</v>
+        <v>0.2074999423939159</v>
       </c>
       <c r="AK31" t="n">
-        <v>235.465576171875</v>
+        <v>250.0962829589844</v>
       </c>
       <c r="AL31" t="n">
-        <v>164.9777221679688</v>
+        <v>123.6134414672852</v>
       </c>
       <c r="AM31" t="n">
-        <v>-0.1215701262977376</v>
+        <v>-0.3323771179434678</v>
       </c>
       <c r="AN31" t="n">
-        <v>0.2537450124769007</v>
+        <v>0.3507430845608523</v>
       </c>
       <c r="AO31" t="n">
-        <v>59.62488620951706</v>
+        <v>29.98974296053153</v>
       </c>
       <c r="AP31" t="n">
-        <v>114672100</v>
+        <v>9990800</v>
       </c>
       <c r="AQ31" t="n">
-        <v>154321682</v>
+        <v>19932330</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.743071864652175</v>
+        <v>0.5012359317751612</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.05670782943302921</v>
+        <v>-0.1851146598615494</v>
       </c>
       <c r="AT31" t="n">
-        <v>-0.005708598795610142</v>
+        <v>0.1258762995109546</v>
       </c>
       <c r="AU31" t="n">
-        <v>0.1034916678863949</v>
+        <v>0.08241985428123066</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.192100134727748</v>
+        <v>0.07333940109629733</v>
       </c>
       <c r="AW31" t="n">
-        <v>10.05208907775403</v>
+        <v>0.3401682340373988</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.09659660635444367</v>
+        <v>-0.02495846344970698</v>
       </c>
       <c r="AY31" t="n">
-        <v>5506.059108318286</v>
+        <v>493.8977533081246</v>
       </c>
       <c r="AZ31" t="inlineStr"/>
       <c r="BA31" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
@@ -6704,13 +6704,13 @@
         <v>4.617775498128106</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.864364687898345</v>
+        <v>5.864365350177327</v>
       </c>
       <c r="AX32" t="n">
         <v>1.431065528571705</v>
       </c>
       <c r="AY32" t="n">
-        <v>24.09694141749926</v>
+        <v>24.09694363070544</v>
       </c>
       <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="n">
@@ -6896,13 +6896,13 @@
         <v>5.779983988621255</v>
       </c>
       <c r="AW33" t="n">
-        <v>8.910596690165521</v>
+        <v>8.910595797008781</v>
       </c>
       <c r="AX33" t="n">
         <v>2.838894984345169</v>
       </c>
       <c r="AY33" t="n">
-        <v>114.2554931408817</v>
+        <v>114.2554780414245</v>
       </c>
       <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="n">
@@ -7088,13 +7088,13 @@
         <v>6.887232910797824</v>
       </c>
       <c r="AW34" t="n">
-        <v>8.048177425935142</v>
+        <v>8.048178304437096</v>
       </c>
       <c r="AX34" t="n">
         <v>3.565494666741915</v>
       </c>
       <c r="AY34" t="n">
-        <v>30.11342804638126</v>
+        <v>30.11343324019388</v>
       </c>
       <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
@@ -7277,10 +7277,10 @@
         <v>0.07368260456062181</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.2413442285946141</v>
+        <v>0.2413441510585608</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.770339658711045</v>
+        <v>1.770339272535083</v>
       </c>
       <c r="AX35" t="n">
         <v>0.04810777491678975</v>
@@ -7476,13 +7476,13 @@
         <v>2.520396855427071</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.640708439362538</v>
+        <v>4.640708027532765</v>
       </c>
       <c r="AX36" t="n">
         <v>1.207034026322465</v>
       </c>
       <c r="AY36" t="n">
-        <v>34.87056449918622</v>
+        <v>34.87057282634787</v>
       </c>
       <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="n">
@@ -7614,22 +7614,22 @@
         <v>18.7</v>
       </c>
       <c r="AE37" t="n">
-        <v>168.3999938964844</v>
+        <v>158.6000061035156</v>
       </c>
       <c r="AF37" t="n">
-        <v>168.7140003967285</v>
+        <v>169.8780004882813</v>
       </c>
       <c r="AG37" t="n">
-        <v>77.58550017356873</v>
+        <v>78.2462502002716</v>
       </c>
       <c r="AH37" t="n">
-        <v>-0.001861176307276002</v>
+        <v>-0.06638878696681871</v>
       </c>
       <c r="AI37" t="n">
-        <v>1.170508581110542</v>
+        <v>1.026934270940502</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.174555812868302</v>
+        <v>1.171068901749002</v>
       </c>
       <c r="AK37" t="n">
         <v>239</v>
@@ -7638,13 +7638,13 @@
         <v>17.63999938964844</v>
       </c>
       <c r="AM37" t="n">
-        <v>-0.2953975150774713</v>
+        <v>-0.3364016481024451</v>
       </c>
       <c r="AN37" t="n">
-        <v>8.54648524507917</v>
+        <v>7.990930362309753</v>
       </c>
       <c r="AO37" t="n">
-        <v>34.62578963184086</v>
+        <v>34.59459808698801</v>
       </c>
       <c r="AP37" t="n">
         <v>88675</v>
@@ -7656,25 +7656,25 @@
         <v>0.4994787509037651</v>
       </c>
       <c r="AS37" t="n">
-        <v>-0.1580000305175782</v>
+        <v>-0.1790889823564326</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.8324264537586887</v>
+        <v>0.804323132540808</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.158024540653935</v>
+        <v>2.901599019683837</v>
       </c>
       <c r="AV37" t="n">
-        <v>6.906103283021714</v>
+        <v>6.552381243024554</v>
       </c>
       <c r="AW37" t="n">
-        <v>3.795037540720301</v>
+        <v>3.52223841449447</v>
       </c>
       <c r="AX37" t="n">
-        <v>4.134146274802657</v>
+        <v>3.835366152213635</v>
       </c>
       <c r="AY37" t="n">
-        <v>13.67551196770161</v>
+        <v>12.82147374446937</v>
       </c>
       <c r="AZ37" t="inlineStr"/>
       <c r="BA37" t="n">
@@ -7831,13 +7831,13 @@
         <v>93.55000305175781</v>
       </c>
       <c r="AL38" t="n">
-        <v>20.95925903320312</v>
+        <v>20.95926094055176</v>
       </c>
       <c r="AM38" t="n">
         <v>-0.3056120046459789</v>
       </c>
       <c r="AN38" t="n">
-        <v>2.099346163982452</v>
+        <v>2.099345881933687</v>
       </c>
       <c r="AO38" t="n">
         <v>43.10538379082971</v>
@@ -7861,16 +7861,16 @@
         <v>0.3107566044217522</v>
       </c>
       <c r="AV38" t="n">
-        <v>2.099346163982452</v>
+        <v>2.099345881933687</v>
       </c>
       <c r="AW38" t="n">
-        <v>2.254791219433784</v>
+        <v>2.254790597333705</v>
       </c>
       <c r="AX38" t="n">
         <v>0.5181200455020381</v>
       </c>
       <c r="AY38" t="n">
-        <v>4.252106687425631</v>
+        <v>4.25210709239408</v>
       </c>
       <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="n">
@@ -8012,16 +8012,16 @@
         <v>184.4580838012695</v>
       </c>
       <c r="AG39" t="n">
-        <v>173.7526622772217</v>
+        <v>173.7526624298096</v>
       </c>
       <c r="AH39" t="n">
         <v>0.07926959734406891</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.1457666272383404</v>
+        <v>0.1457666262321393</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.06161299276650745</v>
+        <v>0.06161299183420921</v>
       </c>
       <c r="AK39" t="n">
         <v>202.5594635009766</v>
@@ -8060,13 +8060,13 @@
         <v>0.1378028919253964</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.5105761927697452</v>
+        <v>0.5105763676648907</v>
       </c>
       <c r="AX39" t="n">
         <v>0.3015021498830017</v>
       </c>
       <c r="AY39" t="n">
-        <v>38.05354859783606</v>
+        <v>38.05355955718704</v>
       </c>
       <c r="AZ39" t="inlineStr"/>
       <c r="BA39" t="n">
@@ -8262,7 +8262,7 @@
         <v>0.5646378600011388</v>
       </c>
       <c r="AY40" t="n">
-        <v>110.3639276368795</v>
+        <v>110.3639622037507</v>
       </c>
       <c r="AZ40" t="inlineStr"/>
       <c r="BA40" t="n">
@@ -8448,13 +8448,13 @@
         <v>0.2442514530139828</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.8651339109732366</v>
+        <v>0.8651342015799457</v>
       </c>
       <c r="AX41" t="n">
         <v>0.0850816501606606</v>
       </c>
       <c r="AY41" t="n">
-        <v>3.466326471885613</v>
+        <v>3.466328554921145</v>
       </c>
       <c r="AZ41" t="inlineStr"/>
       <c r="BA41" t="n">
@@ -8596,16 +8596,16 @@
         <v>1057.170812988281</v>
       </c>
       <c r="AG42" t="n">
-        <v>919.2710092163086</v>
+        <v>919.2710089111329</v>
       </c>
       <c r="AH42" t="n">
         <v>0.02560530135104444</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.179456307622172</v>
+        <v>0.179456308013723</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.1500099561385431</v>
+        <v>0.1500099565203186</v>
       </c>
       <c r="AK42" t="n">
         <v>1115.93994140625</v>
@@ -8641,16 +8641,16 @@
         <v>0.3845353465467611</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.4044881476022042</v>
+        <v>0.4044880365593126</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.4338404724875691</v>
+        <v>0.433840588220338</v>
       </c>
       <c r="AX42" t="n">
         <v>0.4337481236936074</v>
       </c>
       <c r="AY42" t="n">
-        <v>2.510026855452107</v>
+        <v>2.510028936092522</v>
       </c>
       <c r="AZ42" t="inlineStr"/>
       <c r="BA42" t="n">
@@ -8836,13 +8836,13 @@
         <v>-0.006740393292402502</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.08336228136012647</v>
+        <v>0.08336203262627451</v>
       </c>
       <c r="AX43" t="n">
         <v>0.028236006560447</v>
       </c>
       <c r="AY43" t="n">
-        <v>3.029904063720521</v>
+        <v>3.029904493937006</v>
       </c>
       <c r="AZ43" t="inlineStr"/>
       <c r="BA43" t="n">
@@ -9416,7 +9416,7 @@
         <v>-0.03533290345076101</v>
       </c>
       <c r="AY46" t="n">
-        <v>0.644957984761622</v>
+        <v>0.6449583940996746</v>
       </c>
       <c r="AZ46" t="inlineStr"/>
       <c r="BA46" t="n">
@@ -9959,16 +9959,16 @@
         <v>0.217738845779528</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.2636617246617812</v>
+        <v>0.2636616389871744</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.171390928991483</v>
+        <v>0.1713914443297955</v>
       </c>
       <c r="AX49" t="n">
         <v>0.2251389341160506</v>
       </c>
       <c r="AY49" t="n">
-        <v>191.3980051163229</v>
+        <v>191.3979120199659</v>
       </c>
       <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
@@ -10110,16 +10110,16 @@
         <v>125.0646705627441</v>
       </c>
       <c r="AG50" t="n">
-        <v>123.2161139297485</v>
+        <v>123.2161138534546</v>
       </c>
       <c r="AH50" t="n">
         <v>0.04362010218529222</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.05927707107267399</v>
+        <v>0.05927707172856578</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.01500255586740518</v>
+        <v>0.01500255649588267</v>
       </c>
       <c r="AK50" t="n">
         <v>132.3166198730469</v>
@@ -10155,7 +10155,7 @@
         <v>0.1306233956416372</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.1280241251516971</v>
+        <v>0.1280241995306053</v>
       </c>
       <c r="AW50" t="n">
         <v>0.5239735960661345</v>
@@ -10164,7 +10164,7 @@
         <v>0.1305270870899129</v>
       </c>
       <c r="AY50" t="n">
-        <v>175.2974265591195</v>
+        <v>175.2974833338526</v>
       </c>
       <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
@@ -10321,13 +10321,13 @@
         <v>117.3600006103516</v>
       </c>
       <c r="AL51" t="n">
-        <v>84.51685333251953</v>
+        <v>84.51686096191406</v>
       </c>
       <c r="AM51" t="n">
         <v>-0.01201434607001017</v>
       </c>
       <c r="AN51" t="n">
-        <v>0.3719156875381224</v>
+        <v>0.3719155636943601</v>
       </c>
       <c r="AO51" t="n">
         <v>57.95792613704706</v>
@@ -10354,7 +10354,7 @@
         <v>0.3490371583101679</v>
       </c>
       <c r="AW51" t="n">
-        <v>1.726134792457271</v>
+        <v>1.726134303451589</v>
       </c>
       <c r="AX51" t="n">
         <v>0.2502607212433539</v>
@@ -10502,16 +10502,16 @@
         <v>45.87536437988281</v>
       </c>
       <c r="AG52" t="n">
-        <v>45.61095186233521</v>
+        <v>45.61095182418823</v>
       </c>
       <c r="AH52" t="n">
         <v>0.0360680382985612</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.04207425713793067</v>
+        <v>0.04207425800947528</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.005797127811444591</v>
+        <v>0.005797128652648587</v>
       </c>
       <c r="AK52" t="n">
         <v>49.82146072387695</v>
@@ -10556,7 +10556,7 @@
         <v>0.1017258423628071</v>
       </c>
       <c r="AY52" t="n">
-        <v>192.8443067061516</v>
+        <v>192.8442006830068</v>
       </c>
       <c r="AZ52" t="inlineStr"/>
       <c r="BA52" t="n">
@@ -10698,28 +10698,28 @@
         <v>94.25651718139649</v>
       </c>
       <c r="AG53" t="n">
-        <v>91.86444068908692</v>
+        <v>91.86444061279298</v>
       </c>
       <c r="AH53" t="n">
         <v>0.03175889485543548</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.0586250704899014</v>
+        <v>0.05862507136909545</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.0260391994374134</v>
+        <v>0.02603920028954487</v>
       </c>
       <c r="AK53" t="n">
         <v>98.29612731933594</v>
       </c>
       <c r="AL53" t="n">
-        <v>82.73965454101562</v>
+        <v>82.73964691162109</v>
       </c>
       <c r="AM53" t="n">
         <v>-0.01064260971276487</v>
       </c>
       <c r="AN53" t="n">
-        <v>0.1753735320684875</v>
+        <v>0.1753736404492787</v>
       </c>
       <c r="AO53" t="n">
         <v>54.60526572626679</v>
@@ -10746,13 +10746,13 @@
         <v>0.05714157521720664</v>
       </c>
       <c r="AW53" t="n">
-        <v>0.862853765691783</v>
+        <v>0.8628534934480268</v>
       </c>
       <c r="AX53" t="n">
         <v>0.1335789661562246</v>
       </c>
       <c r="AY53" t="n">
-        <v>357.6029506564524</v>
+        <v>357.6029900648035</v>
       </c>
       <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
@@ -10894,28 +10894,28 @@
         <v>14.67920000076294</v>
       </c>
       <c r="AG54" t="n">
-        <v>14.31036792755127</v>
+        <v>14.31036798000336</v>
       </c>
       <c r="AH54" t="n">
         <v>0.01095428577964697</v>
       </c>
       <c r="AI54" t="n">
-        <v>0.03701038489841602</v>
+        <v>0.03701038109744048</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.02577376592125002</v>
+        <v>0.02577376216146021</v>
       </c>
       <c r="AK54" t="n">
         <v>17.06953239440918</v>
       </c>
       <c r="AL54" t="n">
-        <v>12.05970287322998</v>
+        <v>12.05970191955566</v>
       </c>
       <c r="AM54" t="n">
         <v>-0.1306147227882781</v>
       </c>
       <c r="AN54" t="n">
-        <v>0.2305444262254246</v>
+        <v>0.2305445235361725</v>
       </c>
       <c r="AO54" t="n">
         <v>80.0001271568989</v>
@@ -10942,13 +10942,13 @@
         <v>0.1306479472037207</v>
       </c>
       <c r="AW54" t="n">
-        <v>-0.2342396261250661</v>
+        <v>-0.2342397768592885</v>
       </c>
       <c r="AX54" t="n">
         <v>0.02569918659209103</v>
       </c>
       <c r="AY54" t="n">
-        <v>6.436491614999035</v>
+        <v>6.436490726529946</v>
       </c>
       <c r="AZ54" t="inlineStr"/>
       <c r="BA54" t="n">
@@ -11105,13 +11105,13 @@
         <v>97.16828918457031</v>
       </c>
       <c r="AL55" t="n">
-        <v>68.33090209960938</v>
+        <v>68.33089447021484</v>
       </c>
       <c r="AM55" t="n">
         <v>-0.0760360243786885</v>
       </c>
       <c r="AN55" t="n">
-        <v>0.3139003879740982</v>
+        <v>0.3139005346758867</v>
       </c>
       <c r="AO55" t="n">
         <v>63.26527434657145</v>
@@ -11138,13 +11138,13 @@
         <v>0.2835863842792998</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.3299425252606876</v>
+        <v>0.3299426755666723</v>
       </c>
       <c r="AX55" t="n">
         <v>0.125098955867404</v>
       </c>
       <c r="AY55" t="n">
-        <v>257.3570746647337</v>
+        <v>257.3568974087441</v>
       </c>
       <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="n">
@@ -11276,22 +11276,22 @@
         <v>5.8</v>
       </c>
       <c r="AE56" t="n">
-        <v>150.4600067138672</v>
+        <v>151.3399963378906</v>
       </c>
       <c r="AF56" t="n">
-        <v>160.6619998168945</v>
+        <v>160.2979998779297</v>
       </c>
       <c r="AG56" t="n">
-        <v>143.3935517501831</v>
+        <v>143.6279788970947</v>
       </c>
       <c r="AH56" t="n">
-        <v>-0.06349972684676208</v>
+        <v>-0.05588343926225392</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.04928014459112573</v>
+        <v>0.05369439506157314</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.1204269498589179</v>
+        <v>0.1160638832965726</v>
       </c>
       <c r="AK56" t="n">
         <v>187.6199951171875</v>
@@ -11300,43 +11300,43 @@
         <v>84.04161071777344</v>
       </c>
       <c r="AM56" t="n">
-        <v>-0.1980598516704479</v>
+        <v>-0.1933695753303712</v>
       </c>
       <c r="AN56" t="n">
-        <v>0.7903037010932412</v>
+        <v>0.8007745811312095</v>
       </c>
       <c r="AO56" t="n">
-        <v>34.98811490730199</v>
+        <v>33.35656633131725</v>
       </c>
       <c r="AP56" t="n">
-        <v>1155186</v>
+        <v>1155743</v>
       </c>
       <c r="AQ56" t="n">
-        <v>2436128.76</v>
+        <v>2436139.9</v>
       </c>
       <c r="AR56" t="n">
-        <v>0.4741892214268675</v>
+        <v>0.4744156934501176</v>
       </c>
       <c r="AS56" t="n">
-        <v>-0.07953015701728305</v>
+        <v>-0.01676196635750238</v>
       </c>
       <c r="AT56" t="n">
-        <v>-0.1519557644759184</v>
+        <v>-0.1251011673265019</v>
       </c>
       <c r="AU56" t="n">
-        <v>0.07278391566166742</v>
+        <v>0.06881414777954387</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.5600002373093862</v>
+        <v>0.5995092881743418</v>
       </c>
       <c r="AW56" t="n">
-        <v>5.357518016938364</v>
+        <v>5.478770132010695</v>
       </c>
       <c r="AX56" t="n">
-        <v>0.2304692713274448</v>
+        <v>0.237665869380953</v>
       </c>
       <c r="AY56" t="n">
-        <v>5.903686747538357</v>
+        <v>5.944064073301043</v>
       </c>
       <c r="AZ56" t="inlineStr"/>
       <c r="BA56" t="n">
@@ -11478,16 +11478,16 @@
         <v>1032.862692871094</v>
       </c>
       <c r="AG57" t="n">
-        <v>827.3050595092774</v>
+        <v>827.3050588989258</v>
       </c>
       <c r="AH57" t="n">
         <v>-0.01753639955834307</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.2265729410646988</v>
+        <v>0.2265729419696136</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.2484665493086002</v>
+        <v>0.2484665502296675</v>
       </c>
       <c r="AK57" t="n">
         <v>1174.859985351562</v>
@@ -11530,7 +11530,7 @@
         <v>0.4960348336786149</v>
       </c>
       <c r="AY57" t="n">
-        <v>6.764102140214785</v>
+        <v>6.764099420868015</v>
       </c>
       <c r="AZ57" t="inlineStr"/>
       <c r="BA57" t="n">
@@ -11670,16 +11670,16 @@
         <v>155.0461624145508</v>
       </c>
       <c r="AG58" t="n">
-        <v>164.7768145751953</v>
+        <v>164.7768146514892</v>
       </c>
       <c r="AH58" t="n">
         <v>0.05375071745393667</v>
       </c>
       <c r="AI58" t="n">
-        <v>-0.008476979579826627</v>
+        <v>-0.008476980038915505</v>
       </c>
       <c r="AJ58" t="n">
-        <v>-0.05905352755926696</v>
+        <v>-0.05905352799493813</v>
       </c>
       <c r="AK58" t="n">
         <v>217.0162200927734</v>
@@ -11718,13 +11718,13 @@
         <v>-0.1630807538163002</v>
       </c>
       <c r="AW58" t="n">
-        <v>9.074848568249555</v>
+        <v>9.074849753222086</v>
       </c>
       <c r="AX58" t="n">
-        <v>-0.008461065467503359</v>
+        <v>-0.008460973646771563</v>
       </c>
       <c r="AY58" t="n">
-        <v>13.41042040596664</v>
+        <v>13.41041555738928</v>
       </c>
       <c r="AZ58" t="inlineStr"/>
       <c r="BA58" t="n">
@@ -12100,13 +12100,13 @@
         <v>0.1014898443010266</v>
       </c>
       <c r="AW60" t="n">
-        <v>4.407265587638213</v>
+        <v>4.407264952900603</v>
       </c>
       <c r="AX60" t="n">
         <v>-0.1085632834140551</v>
       </c>
       <c r="AY60" t="n">
-        <v>13.68374172247443</v>
+        <v>13.68373587158091</v>
       </c>
       <c r="AZ60" t="inlineStr"/>
       <c r="BA60" t="n">
@@ -12244,16 +12244,16 @@
         <v>191.8701541137695</v>
       </c>
       <c r="AG61" t="n">
-        <v>197.7330612182617</v>
+        <v>197.7330605316162</v>
       </c>
       <c r="AH61" t="n">
         <v>-0.09042651746149544</v>
       </c>
       <c r="AI61" t="n">
-        <v>-0.1173959316807307</v>
+        <v>-0.1173959286158102</v>
       </c>
       <c r="AJ61" t="n">
-        <v>-0.02965061618107756</v>
+        <v>-0.02965061281145365</v>
       </c>
       <c r="AK61" t="n">
         <v>238.1012115478516</v>
@@ -12298,7 +12298,7 @@
         <v>-0.03769680474774728</v>
       </c>
       <c r="AY61" t="n">
-        <v>11.31634267173945</v>
+        <v>11.31635013212327</v>
       </c>
       <c r="AZ61" t="inlineStr"/>
       <c r="BA61" t="n">
@@ -12440,25 +12440,25 @@
         <v>263.7058331298828</v>
       </c>
       <c r="AG62" t="n">
-        <v>310.0693769836426</v>
+        <v>310.0693772888184</v>
       </c>
       <c r="AH62" t="n">
         <v>0.0403638131447408</v>
       </c>
       <c r="AI62" t="n">
-        <v>-0.1151979960988256</v>
+        <v>-0.1151979969696635</v>
       </c>
       <c r="AJ62" t="n">
-        <v>-0.1495263553749961</v>
+        <v>-0.1495263562120474</v>
       </c>
       <c r="AK62" t="n">
-        <v>402.3219604492188</v>
+        <v>402.3219299316406</v>
       </c>
       <c r="AL62" t="n">
         <v>236.5</v>
       </c>
       <c r="AM62" t="n">
-        <v>-0.3180834429291757</v>
+        <v>-0.3180833912033306</v>
       </c>
       <c r="AN62" t="n">
         <v>0.1600423091057743</v>
@@ -12485,14 +12485,14 @@
         <v>-0.04814058197262172</v>
       </c>
       <c r="AV62" t="n">
-        <v>-0.1426235246095509</v>
+        <v>-0.1426236063784547</v>
       </c>
       <c r="AW62" t="inlineStr"/>
       <c r="AX62" t="n">
         <v>-0.2487523008781004</v>
       </c>
       <c r="AY62" t="n">
-        <v>5.77539077864059</v>
+        <v>5.775390140342184</v>
       </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="n">
@@ -12684,7 +12684,7 @@
         <v>-0.3985688095792718</v>
       </c>
       <c r="AY63" t="n">
-        <v>-0.9246536212970703</v>
+        <v>-0.9246536297539922</v>
       </c>
       <c r="AZ63" t="inlineStr"/>
       <c r="BA63" t="n">
@@ -12871,16 +12871,16 @@
         <v>-0.04954117496435473</v>
       </c>
       <c r="AV64" t="n">
-        <v>-0.09702406667835128</v>
+        <v>-0.09702389024080948</v>
       </c>
       <c r="AW64" t="n">
         <v>3.139391036428491</v>
       </c>
       <c r="AX64" t="n">
-        <v>-0.1459827413991127</v>
+        <v>-0.1459828203108895</v>
       </c>
       <c r="AY64" t="n">
-        <v>18.68559395265775</v>
+        <v>18.68559657316694</v>
       </c>
       <c r="AZ64" t="inlineStr"/>
       <c r="BA64" t="n">
@@ -13012,22 +13012,22 @@
         <v>12.9</v>
       </c>
       <c r="AE65" t="n">
-        <v>9.140000343322754</v>
+        <v>9.369999885559082</v>
       </c>
       <c r="AF65" t="n">
-        <v>10.17359994888306</v>
+        <v>10.23719993591309</v>
       </c>
       <c r="AG65" t="n">
-        <v>10.59789999723434</v>
+        <v>10.597399995327</v>
       </c>
       <c r="AH65" t="n">
-        <v>-0.101596250172367</v>
+        <v>-0.08471066852096754</v>
       </c>
       <c r="AI65" t="n">
-        <v>-0.1375649566699109</v>
+        <v>-0.1158208721298757</v>
       </c>
       <c r="AJ65" t="n">
-        <v>-0.0400362381662418</v>
+        <v>-0.03398947473651481</v>
       </c>
       <c r="AK65" t="n">
         <v>13.92000007629395</v>
@@ -13036,43 +13036,43 @@
         <v>6.460000038146973</v>
       </c>
       <c r="AM65" t="n">
-        <v>-0.3433907835325111</v>
+        <v>-0.3268678280026456</v>
       </c>
       <c r="AN65" t="n">
-        <v>0.4148607259055883</v>
+        <v>0.4504643700043742</v>
       </c>
       <c r="AO65" t="n">
-        <v>42.93193534285727</v>
+        <v>46.42856768573597</v>
       </c>
       <c r="AP65" t="n">
-        <v>3936900</v>
+        <v>3767999</v>
       </c>
       <c r="AQ65" t="n">
-        <v>5679444</v>
+        <v>5676065.98</v>
       </c>
       <c r="AR65" t="n">
-        <v>0.6931840511148627</v>
+        <v>0.6638398872170967</v>
       </c>
       <c r="AS65" t="n">
-        <v>-0.05284966791378942</v>
+        <v>-0.06951338932263551</v>
       </c>
       <c r="AT65" t="n">
-        <v>-0.2629031754433163</v>
+        <v>-0.2627852197138812</v>
       </c>
       <c r="AU65" t="n">
-        <v>-0.2734498888112775</v>
+        <v>-0.2533864746490954</v>
       </c>
       <c r="AV65" t="n">
-        <v>0.230148123080979</v>
+        <v>0.3215796451201738</v>
       </c>
       <c r="AW65" t="n">
-        <v>1.589235245722767</v>
+        <v>1.539295322563533</v>
       </c>
       <c r="AX65" t="n">
-        <v>-0.1082926494319264</v>
+        <v>-0.08585366970155295</v>
       </c>
       <c r="AY65" t="n">
-        <v>22.25699793400901</v>
+        <v>22.84223848955463</v>
       </c>
       <c r="AZ65" t="inlineStr"/>
       <c r="BA65" t="n">
@@ -13643,7 +13643,7 @@
         <v>0.7358988338000212</v>
       </c>
       <c r="AV68" t="n">
-        <v>0.6307623566714526</v>
+        <v>0.6307624776295115</v>
       </c>
       <c r="AW68" t="n">
         <v>1.431491247423883</v>
@@ -13652,7 +13652,7 @@
         <v>0.5883466340819636</v>
       </c>
       <c r="AY68" t="n">
-        <v>177.8818434513098</v>
+        <v>177.8817638585028</v>
       </c>
       <c r="AZ68" t="inlineStr"/>
       <c r="BA68" t="n">
@@ -14222,13 +14222,13 @@
         <v>4.622485770364584</v>
       </c>
       <c r="AW71" t="n">
-        <v>10.72908951569062</v>
+        <v>10.72909074804943</v>
       </c>
       <c r="AX71" t="n">
         <v>1.96927035444827</v>
       </c>
       <c r="AY71" t="n">
-        <v>160.5681586898578</v>
+        <v>160.5681294597774</v>
       </c>
       <c r="AZ71" t="inlineStr"/>
       <c r="BA71" t="n">
@@ -14366,16 +14366,16 @@
         <v>2199135.56</v>
       </c>
       <c r="AG72" t="n">
-        <v>1144375.7509375</v>
+        <v>1144375.75</v>
       </c>
       <c r="AH72" t="n">
         <v>-0.2001402587478509</v>
       </c>
       <c r="AI72" t="n">
-        <v>0.5370825522639615</v>
+        <v>0.5370825535231762</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.9216901076402706</v>
+        <v>0.9216901092145653</v>
       </c>
       <c r="AK72" t="n">
         <v>2919000</v>
@@ -14414,13 +14414,13 @@
         <v>4.997794514801248</v>
       </c>
       <c r="AW72" t="n">
-        <v>13.84091132602942</v>
+        <v>13.84090936955006</v>
       </c>
       <c r="AX72" t="n">
         <v>1.603457221721514</v>
       </c>
       <c r="AY72" t="n">
-        <v>-8.685458729231353</v>
+        <v>-8.685458204552276</v>
       </c>
       <c r="AZ72" t="inlineStr"/>
       <c r="BA72" t="n">
@@ -14562,16 +14562,16 @@
         <v>304610</v>
       </c>
       <c r="AG73" t="n">
-        <v>189201.9460546875</v>
+        <v>189201.9463671875</v>
       </c>
       <c r="AH73" t="n">
         <v>-0.1809198647450839</v>
       </c>
       <c r="AI73" t="n">
-        <v>0.3186967956866775</v>
+        <v>0.3186967935086196</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.6099728694754261</v>
+        <v>0.6099728668162752</v>
       </c>
       <c r="AK73" t="n">
         <v>362500</v>
@@ -14607,10 +14607,10 @@
         <v>0.674590945400344</v>
       </c>
       <c r="AV73" t="n">
-        <v>3.031193276632055</v>
+        <v>3.031193022208861</v>
       </c>
       <c r="AW73" t="n">
-        <v>2.454421986807517</v>
+        <v>2.454422360462094</v>
       </c>
       <c r="AX73" t="n">
         <v>0.9456530652504145</v>
@@ -14802,13 +14802,13 @@
         <v>7.417826411685745</v>
       </c>
       <c r="AW74" t="n">
-        <v>5.0468829502863</v>
+        <v>5.04688385309302</v>
       </c>
       <c r="AX74" t="n">
         <v>0.7104503692431816</v>
       </c>
       <c r="AY74" t="n">
-        <v>3.058769166570963</v>
+        <v>3.058769573314202</v>
       </c>
       <c r="AZ74" t="inlineStr"/>
       <c r="BA74" t="n">
@@ -14994,13 +14994,13 @@
         <v>8.366445056559673</v>
       </c>
       <c r="AW75" t="n">
-        <v>5.001082161248877</v>
+        <v>5.001081476068689</v>
       </c>
       <c r="AX75" t="n">
         <v>0.9434241812399802</v>
       </c>
       <c r="AY75" t="n">
-        <v>-0.5320774841689391</v>
+        <v>-0.5320774508429071</v>
       </c>
       <c r="AZ75" t="inlineStr"/>
       <c r="BA75" t="n">
@@ -15142,28 +15142,28 @@
         <v>338.3413366699219</v>
       </c>
       <c r="AG76" t="n">
-        <v>237.221819152832</v>
+        <v>237.2218195343017</v>
       </c>
       <c r="AH76" t="n">
         <v>-0.09792284188782385</v>
       </c>
       <c r="AI76" t="n">
-        <v>0.2866016816878221</v>
+        <v>0.2866016796188744</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.4262656693140978</v>
+        <v>0.4262656670205605</v>
       </c>
       <c r="AK76" t="n">
         <v>433.3299865722656</v>
       </c>
       <c r="AL76" t="n">
-        <v>94.3179931640625</v>
+        <v>94.31800079345703</v>
       </c>
       <c r="AM76" t="n">
         <v>-0.2956638106922729</v>
       </c>
       <c r="AN76" t="n">
-        <v>2.235967827731207</v>
+        <v>2.235967565973376</v>
       </c>
       <c r="AO76" t="n">
         <v>36.19005920099731</v>
@@ -15338,28 +15338,28 @@
         <v>955.2847766113281</v>
       </c>
       <c r="AG77" t="n">
-        <v>501.8894593048096</v>
+        <v>501.8894589996338</v>
       </c>
       <c r="AH77" t="n">
         <v>-0.03594191517014667</v>
       </c>
       <c r="AI77" t="n">
-        <v>0.8349658378613529</v>
+        <v>0.8349658389771106</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.90337684703428</v>
+        <v>0.9033768481916356</v>
       </c>
       <c r="AK77" t="n">
         <v>1213.373413085938</v>
       </c>
       <c r="AL77" t="n">
-        <v>104.7119369506836</v>
+        <v>104.7119293212891</v>
       </c>
       <c r="AM77" t="n">
         <v>-0.2410003365206381</v>
       </c>
       <c r="AN77" t="n">
-        <v>7.795081430312697</v>
+        <v>7.795082071129332</v>
       </c>
       <c r="AO77" t="n">
         <v>44.3814305483843</v>
@@ -15383,16 +15383,16 @@
         <v>1.305714016551832</v>
       </c>
       <c r="AV77" t="n">
-        <v>7.255867777819725</v>
+        <v>7.255868342469947</v>
       </c>
       <c r="AW77" t="n">
         <v>11.66333378967626</v>
       </c>
       <c r="AX77" t="n">
-        <v>1.921433559792421</v>
+        <v>1.921433276975107</v>
       </c>
       <c r="AY77" t="n">
-        <v>680.8079927730276</v>
+        <v>680.8079326005104</v>
       </c>
       <c r="AZ77" t="inlineStr"/>
       <c r="BA77" t="n">
@@ -15532,28 +15532,28 @@
         <v>558.819814453125</v>
       </c>
       <c r="AG78" t="n">
-        <v>322.1782535552978</v>
+        <v>322.178253288269</v>
       </c>
       <c r="AH78" t="n">
         <v>-0.06982541715766111</v>
       </c>
       <c r="AI78" t="n">
-        <v>0.6133925305537471</v>
+        <v>0.6133925318909641</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.7345050706757605</v>
+        <v>0.7345050721133586</v>
       </c>
       <c r="AK78" t="n">
         <v>746.22998046875</v>
       </c>
       <c r="AL78" t="n">
-        <v>68.63400268554688</v>
+        <v>68.63399505615234</v>
       </c>
       <c r="AM78" t="n">
         <v>-0.3034319159001727</v>
       </c>
       <c r="AN78" t="n">
-        <v>6.573505368388337</v>
+        <v>6.573506210263568</v>
       </c>
       <c r="AO78" t="n">
         <v>41.92798620301204</v>
@@ -15586,7 +15586,7 @@
         <v>1.77136040640357</v>
       </c>
       <c r="AY78" t="n">
-        <v>763.9292230564042</v>
+        <v>763.9291559619991</v>
       </c>
       <c r="AZ78" t="inlineStr"/>
       <c r="BA78" t="n">
@@ -16082,13 +16082,13 @@
         <v>3.027598075675268</v>
       </c>
       <c r="AW81" t="n">
-        <v>7.44294890876672</v>
+        <v>7.442949636616179</v>
       </c>
       <c r="AX81" t="n">
         <v>1.637300553758524</v>
       </c>
       <c r="AY81" t="n">
-        <v>20.4541021164614</v>
+        <v>20.45410446633197</v>
       </c>
       <c r="AZ81" t="inlineStr"/>
       <c r="BA81" t="n">
@@ -16226,28 +16226,28 @@
         <v>1157.496208496094</v>
       </c>
       <c r="AG82" t="n">
-        <v>731.4611743164063</v>
+        <v>731.4611740112305</v>
       </c>
       <c r="AH82" t="n">
         <v>-0.09588471903045825</v>
       </c>
       <c r="AI82" t="n">
-        <v>0.4307116310631942</v>
+        <v>0.430711631660107</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.582443811290247</v>
+        <v>0.5824438119504647</v>
       </c>
       <c r="AK82" t="n">
         <v>1382.329956054688</v>
       </c>
       <c r="AL82" t="n">
-        <v>144.9594421386719</v>
+        <v>144.9594573974609</v>
       </c>
       <c r="AM82" t="n">
         <v>-0.242937617620273</v>
       </c>
       <c r="AN82" t="n">
-        <v>6.21932972647968</v>
+        <v>6.219328966555274</v>
       </c>
       <c r="AO82" t="n">
         <v>46.56160855435446</v>
@@ -16271,10 +16271,10 @@
         <v>0.6763438110076587</v>
       </c>
       <c r="AV82" t="n">
-        <v>6.21932972647968</v>
+        <v>6.219328966555274</v>
       </c>
       <c r="AW82" t="n">
-        <v>28.81724330160023</v>
+        <v>28.81724006080477</v>
       </c>
       <c r="AX82" t="n">
         <v>0.6804036021711346</v>
@@ -16466,7 +16466,7 @@
         <v>4.090255618683367</v>
       </c>
       <c r="AW83" t="n">
-        <v>45.63094919459494</v>
+        <v>45.63094483823889</v>
       </c>
       <c r="AX83" t="n">
         <v>0.5649109208412997</v>
@@ -16808,16 +16808,16 @@
         <v>150.9233413696289</v>
       </c>
       <c r="AG85" t="n">
-        <v>141.0176536560058</v>
+        <v>141.0176555252075</v>
       </c>
       <c r="AH85" t="n">
         <v>0.011573138942363</v>
       </c>
       <c r="AI85" t="n">
-        <v>0.08263039563375396</v>
+        <v>0.08263038128339106</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.07024430953720651</v>
+        <v>0.07024429535102228</v>
       </c>
       <c r="AK85" t="n">
         <v>176.3200073242188</v>
@@ -16856,13 +16856,13 @@
         <v>0.4714785590354056</v>
       </c>
       <c r="AW85" t="n">
-        <v>3.740233264605332</v>
+        <v>3.740234948935448</v>
       </c>
       <c r="AX85" t="n">
-        <v>0.0965751661322094</v>
+        <v>0.09657528631526158</v>
       </c>
       <c r="AY85" t="n">
-        <v>1219.052174907116</v>
+        <v>1219.051739049822</v>
       </c>
       <c r="AZ85" t="inlineStr"/>
       <c r="BA85" t="n">
@@ -17198,16 +17198,16 @@
         <v>239.1006469726562</v>
       </c>
       <c r="AG87" t="n">
-        <v>132.7225814056397</v>
+        <v>132.7225813293457</v>
       </c>
       <c r="AH87" t="n">
         <v>-0.1876642820219915</v>
       </c>
       <c r="AI87" t="n">
-        <v>0.4634284058559295</v>
+        <v>0.4634284066971635</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.8015069059114637</v>
+        <v>0.801506906947038</v>
       </c>
       <c r="AK87" t="n">
         <v>316.3519592285156</v>
@@ -17240,19 +17240,19 @@
         <v>0.1823864499806978</v>
       </c>
       <c r="AU87" t="n">
-        <v>1.422724171642454</v>
+        <v>1.422723941083668</v>
       </c>
       <c r="AV87" t="n">
-        <v>1.628900969832727</v>
+        <v>1.628900698362516</v>
       </c>
       <c r="AW87" t="n">
-        <v>2.610774748687912</v>
+        <v>2.610774492626262</v>
       </c>
       <c r="AX87" t="n">
         <v>1.176026581971421</v>
       </c>
       <c r="AY87" t="n">
-        <v>15.01328458857992</v>
+        <v>15.0132871066899</v>
       </c>
       <c r="AZ87" t="inlineStr"/>
       <c r="BA87" t="n">
@@ -17384,22 +17384,22 @@
         <v>19.2</v>
       </c>
       <c r="AE88" t="n">
-        <v>126.0999984741211</v>
+        <v>126.9000015258789</v>
       </c>
       <c r="AF88" t="n">
-        <v>143.1690008544922</v>
+        <v>142.6440010070801</v>
       </c>
       <c r="AG88" t="n">
-        <v>109.4546841430664</v>
+        <v>109.6551194000244</v>
       </c>
       <c r="AH88" t="n">
-        <v>-0.1192227526803721</v>
+        <v>-0.110372671616381</v>
       </c>
       <c r="AI88" t="n">
-        <v>0.1520749382392614</v>
+        <v>0.157264724348571</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.308020775678804</v>
+        <v>0.3008421475217355</v>
       </c>
       <c r="AK88" t="n">
         <v>156.8999938964844</v>
@@ -17408,13 +17408,13 @@
         <v>65.19408416748047</v>
       </c>
       <c r="AM88" t="n">
-        <v>-0.1963033564085652</v>
+        <v>-0.191204547722278</v>
       </c>
       <c r="AN88" t="n">
-        <v>0.9342245555620701</v>
+        <v>0.9464956544197922</v>
       </c>
       <c r="AO88" t="n">
-        <v>28.27956140654555</v>
+        <v>31.52542226766334</v>
       </c>
       <c r="AP88" t="n">
         <v>743002</v>
@@ -17426,25 +17426,25 @@
         <v>0.6809047654884155</v>
       </c>
       <c r="AS88" t="n">
-        <v>-0.1485483235835754</v>
+        <v>-0.1116556100535174</v>
       </c>
       <c r="AT88" t="n">
-        <v>0.0124447642262937</v>
+        <v>0.03003250543253766</v>
       </c>
       <c r="AU88" t="n">
-        <v>0.3069945831639445</v>
+        <v>0.285141050348783</v>
       </c>
       <c r="AV88" t="n">
-        <v>0.9103739417090286</v>
+        <v>0.9464956544197922</v>
       </c>
       <c r="AW88" t="n">
-        <v>3.380645854671898</v>
+        <v>3.349470964377917</v>
       </c>
       <c r="AX88" t="n">
-        <v>0.4134387597175</v>
+        <v>0.4224058916360531</v>
       </c>
       <c r="AY88" t="n">
-        <v>11.04384135209018</v>
+        <v>11.12024652510562</v>
       </c>
       <c r="AZ88" t="inlineStr"/>
       <c r="BA88" t="n">
@@ -18018,13 +18018,13 @@
         <v>1.120165670820509</v>
       </c>
       <c r="AW91" t="n">
-        <v>0.8090314292707277</v>
+        <v>0.8090316007536777</v>
       </c>
       <c r="AX91" t="n">
         <v>0.3978494718168009</v>
       </c>
       <c r="AY91" t="n">
-        <v>14.22896483055467</v>
+        <v>14.22896179240357</v>
       </c>
       <c r="AZ91" t="inlineStr"/>
       <c r="BA91" t="n">
@@ -18214,13 +18214,13 @@
         <v>0.3325427361689419</v>
       </c>
       <c r="AW92" t="n">
-        <v>8.008865069538427</v>
+        <v>8.00886425889888</v>
       </c>
       <c r="AX92" t="n">
         <v>0.1027182559175892</v>
       </c>
       <c r="AY92" t="n">
-        <v>335.3181665060716</v>
+        <v>335.3182018112477</v>
       </c>
       <c r="AZ92" t="inlineStr"/>
       <c r="BA92" t="n">
@@ -18754,28 +18754,28 @@
         <v>188.3</v>
       </c>
       <c r="AG95" t="n">
-        <v>133.7697877883911</v>
+        <v>133.7697878646851</v>
       </c>
       <c r="AH95" t="n">
         <v>-0.2211896234918515</v>
       </c>
       <c r="AI95" t="n">
-        <v>0.09628636122581224</v>
+        <v>0.09628636060055862</v>
       </c>
       <c r="AJ95" t="n">
-        <v>0.4076422121403795</v>
+        <v>0.4076422113375482</v>
       </c>
       <c r="AK95" t="n">
         <v>255.6900024414062</v>
       </c>
       <c r="AL95" t="n">
-        <v>54.76138305664062</v>
+        <v>54.76138687133789</v>
       </c>
       <c r="AM95" t="n">
         <v>-0.4264539383776236</v>
       </c>
       <c r="AN95" t="n">
-        <v>1.677981922859797</v>
+        <v>1.677981736310644</v>
       </c>
       <c r="AO95" t="n">
         <v>25.05956585882404</v>
@@ -18799,16 +18799,16 @@
         <v>0.5771584083668286</v>
       </c>
       <c r="AV95" t="n">
-        <v>1.660679516200776</v>
+        <v>1.660679700347159</v>
       </c>
       <c r="AW95" t="n">
-        <v>3.242679104278302</v>
+        <v>3.242678167820314</v>
       </c>
       <c r="AX95" t="n">
         <v>0.6229059661064003</v>
       </c>
       <c r="AY95" t="n">
-        <v>190.2985331915247</v>
+        <v>190.2985183177465</v>
       </c>
       <c r="AZ95" t="inlineStr"/>
       <c r="BA95" t="n">
@@ -19140,67 +19140,67 @@
         <v>11</v>
       </c>
       <c r="AE97" t="n">
-        <v>762.989990234375</v>
+        <v>833.6400146484375</v>
       </c>
       <c r="AF97" t="n">
-        <v>854.2382006835937</v>
+        <v>858.82580078125</v>
       </c>
       <c r="AG97" t="n">
-        <v>588.2339499664307</v>
+        <v>585.2220000457763</v>
       </c>
       <c r="AH97" t="n">
-        <v>-0.1068182274876006</v>
+        <v>-0.02932583780075271</v>
       </c>
       <c r="AI97" t="n">
-        <v>0.297085947313849</v>
+        <v>0.4244850921244072</v>
       </c>
       <c r="AJ97" t="n">
-        <v>0.4522082595408567</v>
+        <v>0.4675213862672152</v>
       </c>
       <c r="AK97" t="n">
         <v>1053.089965820312</v>
       </c>
       <c r="AL97" t="n">
-        <v>102.8499984741211</v>
+        <v>102.129997253418</v>
       </c>
       <c r="AM97" t="n">
-        <v>-0.2754750163818738</v>
+        <v>-0.208386707968424</v>
       </c>
       <c r="AN97" t="n">
-        <v>6.418473520214557</v>
+        <v>7.1625383047833</v>
       </c>
       <c r="AO97" t="n">
-        <v>52.9481689908326</v>
+        <v>61.1904462046155</v>
       </c>
       <c r="AP97" t="n">
-        <v>3645300</v>
+        <v>3636627</v>
       </c>
       <c r="AQ97" t="n">
-        <v>5295054</v>
+        <v>5294880.54</v>
       </c>
       <c r="AR97" t="n">
-        <v>0.6884349054797175</v>
+        <v>0.6868194612753247</v>
       </c>
       <c r="AS97" t="n">
-        <v>-0.1148299637260103</v>
+        <v>-0.01055157007977103</v>
       </c>
       <c r="AT97" t="n">
-        <v>-0.1345787650772354</v>
+        <v>-0.01564547907144753</v>
       </c>
       <c r="AU97" t="n">
-        <v>1.249447167494798</v>
+        <v>1.351660237563456</v>
       </c>
       <c r="AV97" t="n">
-        <v>6.418473520214557</v>
+        <v>7.1625383047833</v>
       </c>
       <c r="AW97" t="n">
-        <v>8.461681498131536</v>
+        <v>9.385449726070794</v>
       </c>
       <c r="AX97" t="n">
-        <v>0.9760949449148644</v>
+        <v>1.159073958911962</v>
       </c>
       <c r="AY97" t="n">
-        <v>43.88176413143383</v>
+        <v>48.03764792049633</v>
       </c>
       <c r="AZ97" t="inlineStr"/>
       <c r="BA97" t="n">
@@ -19333,7 +19333,7 @@
         <v>34047</v>
       </c>
       <c r="AD98" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="AE98" t="n">
         <v>78.86000061035156</v>
@@ -19342,16 +19342,16 @@
         <v>90.77994918823242</v>
       </c>
       <c r="AG98" t="n">
-        <v>74.63431425094605</v>
+        <v>74.63431432723999</v>
       </c>
       <c r="AH98" t="n">
         <v>-0.1313059622138014</v>
       </c>
       <c r="AI98" t="n">
-        <v>0.05661854606444594</v>
+        <v>0.0566185449843315</v>
       </c>
       <c r="AJ98" t="n">
-        <v>0.2163299160624594</v>
+        <v>0.2163299148190823</v>
       </c>
       <c r="AK98" t="n">
         <v>102.7099990844727</v>
@@ -19384,19 +19384,19 @@
         <v>-0.1138662621356102</v>
       </c>
       <c r="AU98" t="n">
-        <v>0.06709226453607564</v>
+        <v>0.06709237469946427</v>
       </c>
       <c r="AV98" t="n">
-        <v>0.1945008072092977</v>
+        <v>0.1945009452497086</v>
       </c>
       <c r="AW98" t="n">
-        <v>0.3288759505423871</v>
+        <v>0.3288756088525471</v>
       </c>
       <c r="AX98" t="n">
         <v>0.2259337713784189</v>
       </c>
       <c r="AY98" t="n">
-        <v>447.8952368140225</v>
+        <v>447.8954652711976</v>
       </c>
       <c r="AZ98" t="inlineStr"/>
       <c r="BA98" t="n">
@@ -19528,22 +19528,22 @@
         <v>25.1</v>
       </c>
       <c r="AE99" t="n">
-        <v>133.8000030517578</v>
+        <v>132.1999969482422</v>
       </c>
       <c r="AF99" t="n">
-        <v>147.5287078857422</v>
+        <v>146.9634265136719</v>
       </c>
       <c r="AG99" t="n">
-        <v>131.326181640625</v>
+        <v>131.3464055633545</v>
       </c>
       <c r="AH99" t="n">
-        <v>-0.09305785315097426</v>
+        <v>-0.100456487138698</v>
       </c>
       <c r="AI99" t="n">
-        <v>0.01883722941022103</v>
+        <v>0.006498779934072552</v>
       </c>
       <c r="AJ99" t="n">
-        <v>0.123376207567319</v>
+        <v>0.1188994924020554</v>
       </c>
       <c r="AK99" t="n">
         <v>164.8832092285156</v>
@@ -19552,13 +19552,13 @@
         <v>110.5768280029297</v>
       </c>
       <c r="AM99" t="n">
-        <v>-0.18851650402849</v>
+        <v>-0.1982203793412159</v>
       </c>
       <c r="AN99" t="n">
-        <v>0.2100184592762313</v>
+        <v>0.1955488264208447</v>
       </c>
       <c r="AO99" t="n">
-        <v>33.33335400918131</v>
+        <v>32.28348159575542</v>
       </c>
       <c r="AP99" t="n">
         <v>111709</v>
@@ -19570,25 +19570,25 @@
         <v>0.8347930447986943</v>
       </c>
       <c r="AS99" t="n">
-        <v>-0.08731243191572324</v>
+        <v>-0.06307589489928223</v>
       </c>
       <c r="AT99" t="n">
-        <v>-0.004034534277696733</v>
+        <v>-0.0904135651528658</v>
       </c>
       <c r="AU99" t="n">
-        <v>0.06443809262415523</v>
+        <v>0.03792445274919976</v>
       </c>
       <c r="AV99" t="n">
-        <v>0.1497728046943818</v>
+        <v>0.05253158375051381</v>
       </c>
       <c r="AW99" t="n">
-        <v>0.8021959795695204</v>
+        <v>0.7838803281783762</v>
       </c>
       <c r="AX99" t="n">
-        <v>0.06194915437949788</v>
+        <v>0.04925016267638727</v>
       </c>
       <c r="AY99" t="n">
-        <v>7.284848696716944</v>
+        <v>7.185778820228103</v>
       </c>
       <c r="AZ99" t="inlineStr"/>
       <c r="BA99" t="n">
@@ -19720,22 +19720,22 @@
         <v>25.2</v>
       </c>
       <c r="AE100" t="n">
-        <v>897</v>
+        <v>889</v>
       </c>
       <c r="AF100" t="n">
-        <v>990.45</v>
+        <v>988.45</v>
       </c>
       <c r="AG100" t="n">
-        <v>848.4125</v>
+        <v>849.7725</v>
       </c>
       <c r="AH100" t="n">
-        <v>-0.09435105255187037</v>
+        <v>-0.1006120694015884</v>
       </c>
       <c r="AI100" t="n">
-        <v>0.05726872246696035</v>
+        <v>0.04616235521860257</v>
       </c>
       <c r="AJ100" t="n">
-        <v>0.1674156144564112</v>
+        <v>0.1631936783080177</v>
       </c>
       <c r="AK100" t="n">
         <v>1112</v>
@@ -19744,43 +19744,43 @@
         <v>534.5</v>
       </c>
       <c r="AM100" t="n">
-        <v>-0.1933453237410072</v>
+        <v>-0.2005395683453237</v>
       </c>
       <c r="AN100" t="n">
-        <v>0.6782039289055193</v>
+        <v>0.6632366697848457</v>
       </c>
       <c r="AO100" t="n">
-        <v>21.92691029900332</v>
+        <v>24.6268656716418</v>
       </c>
       <c r="AP100" t="n">
-        <v>72274</v>
+        <v>73463</v>
       </c>
       <c r="AQ100" t="n">
-        <v>142947.96</v>
+        <v>142971.74</v>
       </c>
       <c r="AR100" t="n">
-        <v>0.5055965821408015</v>
+        <v>0.5138288167997396</v>
       </c>
       <c r="AS100" t="n">
-        <v>-0.08047155304971809</v>
+        <v>-0.05324813631522896</v>
       </c>
       <c r="AT100" t="n">
-        <v>-0.03806970509383378</v>
+        <v>-0.04715969989281887</v>
       </c>
       <c r="AU100" t="n">
-        <v>0.1290119572057897</v>
+        <v>0.1091703056768558</v>
       </c>
       <c r="AV100" t="n">
-        <v>0.5709281961471104</v>
+        <v>0.5734513274336284</v>
       </c>
       <c r="AW100" t="n">
-        <v>2.48412526252828</v>
+        <v>2.462931599653597</v>
       </c>
       <c r="AX100" t="n">
-        <v>0.08859223300970864</v>
+        <v>0.07888349514563098</v>
       </c>
       <c r="AY100" t="n">
-        <v>25.5578999370001</v>
+        <v>25.32103721003304</v>
       </c>
       <c r="AZ100" t="inlineStr"/>
       <c r="BA100" t="n">
@@ -19922,25 +19922,25 @@
         <v>205.2112457275391</v>
       </c>
       <c r="AG101" t="n">
-        <v>218.9980995178223</v>
+        <v>218.9980996704102</v>
       </c>
       <c r="AH101" t="n">
         <v>-0.01106783050841353</v>
       </c>
       <c r="AI101" t="n">
-        <v>-0.07332528050139164</v>
+        <v>-0.0733252811470565</v>
       </c>
       <c r="AJ101" t="n">
-        <v>-0.06295421659200839</v>
+        <v>-0.06295421724489936</v>
       </c>
       <c r="AK101" t="n">
-        <v>247.2834320068359</v>
+        <v>247.2834167480469</v>
       </c>
       <c r="AL101" t="n">
         <v>195.0859069824219</v>
       </c>
       <c r="AM101" t="n">
-        <v>-0.17932228295911</v>
+        <v>-0.1793222323186412</v>
       </c>
       <c r="AN101" t="n">
         <v>0.04025967626504179</v>
@@ -19964,19 +19964,19 @@
         <v>-0.05098783098178294</v>
       </c>
       <c r="AU101" t="n">
-        <v>-0.08707667419343501</v>
+        <v>-0.08707673685784945</v>
       </c>
       <c r="AV101" t="n">
         <v>-0.002550195441986869</v>
       </c>
       <c r="AW101" t="n">
-        <v>0.6559085765596235</v>
+        <v>0.6559086796445466</v>
       </c>
       <c r="AX101" t="n">
         <v>-0.1237940361835591</v>
       </c>
       <c r="AY101" t="n">
-        <v>6.594166797579237</v>
+        <v>6.594167339608477</v>
       </c>
       <c r="AZ101" t="inlineStr"/>
       <c r="BA101" t="n">
@@ -20168,7 +20168,7 @@
         <v>0.8905812729507157</v>
       </c>
       <c r="AY102" t="n">
-        <v>22.53776979494349</v>
+        <v>22.5377595434746</v>
       </c>
       <c r="AZ102" t="inlineStr"/>
       <c r="BA102" t="n">
@@ -20300,22 +20300,22 @@
         <v>4.4</v>
       </c>
       <c r="AE103" t="n">
-        <v>8.090000152587891</v>
+        <v>8.810000419616699</v>
       </c>
       <c r="AF103" t="n">
-        <v>10.25580001831055</v>
+        <v>10.33400001525879</v>
       </c>
       <c r="AG103" t="n">
-        <v>17.24009999275208</v>
+        <v>17.40934998512268</v>
       </c>
       <c r="AH103" t="n">
-        <v>-0.211178051625019</v>
+        <v>-0.1474743171464884</v>
       </c>
       <c r="AI103" t="n">
-        <v>-0.5307451722444176</v>
+        <v>-0.4939500655024245</v>
       </c>
       <c r="AJ103" t="n">
-        <v>-0.4051194585517371</v>
+        <v>-0.4064109214824331</v>
       </c>
       <c r="AK103" t="n">
         <v>53.43000030517578</v>
@@ -20324,41 +20324,41 @@
         <v>7.639999866485596</v>
       </c>
       <c r="AM103" t="n">
-        <v>-0.8485869341871554</v>
+        <v>-0.8351113537470208</v>
       </c>
       <c r="AN103" t="n">
-        <v>0.05890056203748273</v>
+        <v>0.1531414363321586</v>
       </c>
       <c r="AO103" t="n">
-        <v>34.7389593995145</v>
+        <v>39.22902673315716</v>
       </c>
       <c r="AP103" t="n">
-        <v>34796400</v>
+        <v>34753110</v>
       </c>
       <c r="AQ103" t="n">
-        <v>32780440</v>
+        <v>32779574.2</v>
       </c>
       <c r="AR103" t="n">
-        <v>1.061498869447756</v>
+        <v>1.060206267108863</v>
       </c>
       <c r="AS103" t="n">
-        <v>-0.1966235950586979</v>
+        <v>-0.1371204322526488</v>
       </c>
       <c r="AT103" t="n">
-        <v>-0.3235785847170183</v>
+        <v>-0.3073899186580303</v>
       </c>
       <c r="AU103" t="n">
-        <v>-0.5907941342808138</v>
+        <v>-0.5731588817761704</v>
       </c>
       <c r="AV103" t="n">
-        <v>-0.8414657976462652</v>
+        <v>-0.8158829529664156</v>
       </c>
       <c r="AW103" t="inlineStr"/>
       <c r="AX103" t="n">
-        <v>-0.503985259504087</v>
+        <v>-0.4598405451813016</v>
       </c>
       <c r="AY103" t="n">
-        <v>-0.1958250680772704</v>
+        <v>-0.1242544679782058</v>
       </c>
       <c r="AZ103" t="inlineStr"/>
       <c r="BA103" t="n">
@@ -20544,13 +20544,13 @@
         <v>0.2739881682700198</v>
       </c>
       <c r="AW104" t="n">
-        <v>0.1765259470980181</v>
+        <v>0.1765258338843936</v>
       </c>
       <c r="AX104" t="n">
         <v>0.1899741918040363</v>
       </c>
       <c r="AY104" t="n">
-        <v>21.26931320456422</v>
+        <v>21.26931827469866</v>
       </c>
       <c r="AZ104" t="inlineStr"/>
       <c r="BA104" t="n">
@@ -20565,12 +20565,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MYRG</t>
+          <t>SU.PA</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MYR Group</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -20580,16 +20580,16 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Power distribution / UPS / electrical</t>
+          <t>Power, cooling and energy management</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Electrical infrastructure</t>
+          <t>Power, cooling, data center energy management</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -20638,7 +20638,7 @@
       </c>
       <c r="T105" t="inlineStr">
         <is>
-          <t>MYR Group Inc.</t>
+          <t>Schneider Electric S.E.</t>
         </is>
       </c>
       <c r="U105" t="inlineStr">
@@ -20648,105 +20648,105 @@
       </c>
       <c r="V105" t="inlineStr">
         <is>
-          <t>Engineering &amp; Construction</t>
+          <t>Specialty Industrial Machinery</t>
         </is>
       </c>
       <c r="W105" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="X105" t="n">
-        <v>5904070144</v>
+        <v>151098245120</v>
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="Z105" t="n">
-        <v>1</v>
+        <v>1.137526988983154</v>
       </c>
       <c r="AA105" t="n">
-        <v>5904070144</v>
+        <v>171878331811.9922</v>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>Mid cap</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC105" s="2" t="n">
-        <v>39673</v>
+        <v>36528</v>
       </c>
       <c r="AD105" t="n">
-        <v>17.9</v>
+        <v>26.6</v>
       </c>
       <c r="AE105" t="n">
-        <v>379.1700134277344</v>
+        <v>268.0499877929688</v>
       </c>
       <c r="AF105" t="n">
-        <v>442.5682000732422</v>
+        <v>272.5910000610352</v>
       </c>
       <c r="AG105" t="n">
-        <v>307.4368504333496</v>
+        <v>251.0032049560547</v>
       </c>
       <c r="AH105" t="n">
-        <v>-0.1432506597514593</v>
+        <v>-0.01665870211067</v>
       </c>
       <c r="AI105" t="n">
-        <v>0.2333264958097014</v>
+        <v>0.06791460228525215</v>
       </c>
       <c r="AJ105" t="n">
-        <v>0.4395418098039232</v>
+        <v>0.086006053622941</v>
       </c>
       <c r="AK105" t="n">
-        <v>501.1300048828125</v>
+        <v>292.75</v>
       </c>
       <c r="AL105" t="n">
-        <v>173.8099975585938</v>
+        <v>206.813720703125</v>
       </c>
       <c r="AM105" t="n">
-        <v>-0.243369964413921</v>
+        <v>-0.0843723730385354</v>
       </c>
       <c r="AN105" t="n">
-        <v>1.181520158527768</v>
+        <v>0.2960938320806414</v>
       </c>
       <c r="AO105" t="n">
-        <v>27.14193823160076</v>
+        <v>39.7410263502649</v>
       </c>
       <c r="AP105" t="n">
-        <v>393700</v>
+        <v>508410</v>
       </c>
       <c r="AQ105" t="n">
-        <v>281350</v>
+        <v>921830.66</v>
       </c>
       <c r="AR105" t="n">
-        <v>1.399324684556602</v>
+        <v>0.5515221201256204</v>
       </c>
       <c r="AS105" t="n">
-        <v>-0.2219440135529036</v>
+        <v>-0.02898025848130015</v>
       </c>
       <c r="AT105" t="n">
-        <v>0.1175725500824059</v>
+        <v>0.005334298134901383</v>
       </c>
       <c r="AU105" t="n">
-        <v>0.5501635485130292</v>
+        <v>0.1587338316123639</v>
       </c>
       <c r="AV105" t="n">
-        <v>0.9410772014752298</v>
+        <v>0.1381460093384483</v>
       </c>
       <c r="AW105" t="n">
-        <v>3.299467092992272</v>
+        <v>0.9245090081587397</v>
       </c>
       <c r="AX105" t="n">
-        <v>0.6724153642652246</v>
+        <v>0.1484687485637541</v>
       </c>
       <c r="AY105" t="n">
-        <v>21.84156654905833</v>
+        <v>13.40417868121905</v>
       </c>
       <c r="AZ105" t="inlineStr"/>
       <c r="BA105" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
@@ -20757,12 +20757,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2301.TW</t>
+          <t>MYRG</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Lite-On Technology</t>
+          <t>MYR Group</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -20777,7 +20777,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Power supplies/components</t>
+          <t>Electrical infrastructure</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -20830,115 +20830,115 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>Lite-On Technology Corporation</t>
+          <t>MYR Group Inc.</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Engineering &amp; Construction</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X106" t="n">
-        <v>486722732032</v>
+        <v>5904070144</v>
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>0.03092145919799805</v>
+        <v>1</v>
       </c>
       <c r="AA106" t="n">
-        <v>15050177099.26562</v>
+        <v>5904070144</v>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Mid cap</t>
         </is>
       </c>
       <c r="AC106" s="2" t="n">
-        <v>36529</v>
+        <v>39673</v>
       </c>
       <c r="AD106" t="n">
-        <v>26.6</v>
+        <v>17.9</v>
       </c>
       <c r="AE106" t="n">
-        <v>214.5</v>
+        <v>379.1700134277344</v>
       </c>
       <c r="AF106" t="n">
-        <v>217.9</v>
+        <v>442.5682000732422</v>
       </c>
       <c r="AG106" t="n">
-        <v>177.9218057250977</v>
+        <v>307.4368504333496</v>
       </c>
       <c r="AH106" t="n">
-        <v>-0.015603487838458</v>
+        <v>-0.1432506597514593</v>
       </c>
       <c r="AI106" t="n">
-        <v>0.2055857859908321</v>
+        <v>0.2333264958097014</v>
       </c>
       <c r="AJ106" t="n">
-        <v>0.224695304276934</v>
+        <v>0.4395418098039232</v>
       </c>
       <c r="AK106" t="n">
-        <v>250</v>
+        <v>501.1300048828125</v>
       </c>
       <c r="AL106" t="n">
-        <v>111.2844619750977</v>
+        <v>173.8099975585938</v>
       </c>
       <c r="AM106" t="n">
-        <v>-0.142</v>
+        <v>-0.243369964413921</v>
       </c>
       <c r="AN106" t="n">
-        <v>0.9274928071090383</v>
+        <v>1.181520158527768</v>
       </c>
       <c r="AO106" t="n">
-        <v>44.63276836158192</v>
+        <v>27.14193823160076</v>
       </c>
       <c r="AP106" t="n">
-        <v>15483101</v>
+        <v>393700</v>
       </c>
       <c r="AQ106" t="n">
-        <v>28774390.32</v>
+        <v>281350</v>
       </c>
       <c r="AR106" t="n">
-        <v>0.5380861532707533</v>
+        <v>1.399324684556602</v>
       </c>
       <c r="AS106" t="n">
-        <v>0.06451612903225801</v>
+        <v>-0.2219440135529036</v>
       </c>
       <c r="AT106" t="n">
-        <v>0.2470930232558139</v>
+        <v>0.1175725500824059</v>
       </c>
       <c r="AU106" t="n">
-        <v>0.3075048182218216</v>
+        <v>0.5501635485130292</v>
       </c>
       <c r="AV106" t="n">
-        <v>0.8784888247231135</v>
+        <v>0.9410772014752298</v>
       </c>
       <c r="AW106" t="n">
-        <v>3.616241847879627</v>
+        <v>3.299467092992272</v>
       </c>
       <c r="AX106" t="n">
-        <v>0.3075048182218216</v>
+        <v>0.6724153642652246</v>
       </c>
       <c r="AY106" t="n">
-        <v>55.20614090546744</v>
+        <v>21.84156654905833</v>
       </c>
       <c r="AZ106" t="inlineStr"/>
       <c r="BA106" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
@@ -20949,12 +20949,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CARR</t>
+          <t>2301.TW</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Carrier Global</t>
+          <t>Lite-On Technology</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -20964,19 +20964,19 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Cooling / thermal management</t>
+          <t>Power distribution / UPS / electrical</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>HVAC/cooling</t>
+          <t>Power supplies/components</t>
         </is>
       </c>
       <c r="F107" t="n">
         <v>6</v>
       </c>
       <c r="G107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -20984,11 +20984,7 @@
       <c r="I107" t="n">
         <v>0</v>
       </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
-        </is>
-      </c>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" s="1" t="n">
         <v>46195</v>
       </c>
@@ -21026,37 +21022,37 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>Carrier Global Corporation</t>
+          <t>Lite-On Technology Corporation</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="V107" t="inlineStr">
         <is>
-          <t>Building Products &amp; Equipment</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="W107" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TWD</t>
         </is>
       </c>
       <c r="X107" t="n">
-        <v>57210376192</v>
+        <v>486722732032</v>
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TWD</t>
         </is>
       </c>
       <c r="Z107" t="n">
-        <v>1</v>
+        <v>0.03092145919799805</v>
       </c>
       <c r="AA107" t="n">
-        <v>57210376192</v>
+        <v>15050177099.26562</v>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
@@ -21064,73 +21060,73 @@
         </is>
       </c>
       <c r="AC107" s="2" t="n">
-        <v>43909</v>
+        <v>36529</v>
       </c>
       <c r="AD107" t="n">
-        <v>6.3</v>
+        <v>26.6</v>
       </c>
       <c r="AE107" t="n">
-        <v>68.87999725341797</v>
+        <v>214.5</v>
       </c>
       <c r="AF107" t="n">
-        <v>68.10033111572265</v>
+        <v>217.9</v>
       </c>
       <c r="AG107" t="n">
-        <v>60.30649614334106</v>
+        <v>177.9218057250977</v>
       </c>
       <c r="AH107" t="n">
-        <v>0.01144878629694812</v>
+        <v>-0.015603487838458</v>
       </c>
       <c r="AI107" t="n">
-        <v>0.1421654657186309</v>
+        <v>0.2055857859908321</v>
       </c>
       <c r="AJ107" t="n">
-        <v>0.1292370718049447</v>
+        <v>0.224695304276934</v>
       </c>
       <c r="AK107" t="n">
-        <v>79.50715637207031</v>
+        <v>250</v>
       </c>
       <c r="AL107" t="n">
-        <v>49.78788757324219</v>
+        <v>111.2844619750977</v>
       </c>
       <c r="AM107" t="n">
-        <v>-0.1336629254971758</v>
+        <v>-0.142</v>
       </c>
       <c r="AN107" t="n">
-        <v>0.3834689642554061</v>
+        <v>0.9274928071090383</v>
       </c>
       <c r="AO107" t="n">
-        <v>46.67245252088201</v>
+        <v>44.63276836158192</v>
       </c>
       <c r="AP107" t="n">
-        <v>5711200</v>
+        <v>15483101</v>
       </c>
       <c r="AQ107" t="n">
-        <v>6134684</v>
+        <v>28774390.32</v>
       </c>
       <c r="AR107" t="n">
-        <v>0.930968897501485</v>
+        <v>0.5380861532707533</v>
       </c>
       <c r="AS107" t="n">
-        <v>-0.09042514446473171</v>
+        <v>0.06451612903225801</v>
       </c>
       <c r="AT107" t="n">
-        <v>0.1378368828984733</v>
+        <v>0.2470930232558139</v>
       </c>
       <c r="AU107" t="n">
-        <v>0.2107140529497702</v>
+        <v>0.3075048182218216</v>
       </c>
       <c r="AV107" t="n">
-        <v>-0.1195946536977069</v>
+        <v>0.8784888247231135</v>
       </c>
       <c r="AW107" t="n">
-        <v>0.532348015061014</v>
+        <v>3.616241468905246</v>
       </c>
       <c r="AX107" t="n">
-        <v>0.3017842609249908</v>
+        <v>0.3075048182218216</v>
       </c>
       <c r="AY107" t="n">
-        <v>5.251470299550921</v>
+        <v>55.20613388266784</v>
       </c>
       <c r="AZ107" t="inlineStr"/>
       <c r="BA107" t="n">
@@ -21145,12 +21141,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>IFX.DE</t>
+          <t>CARR</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Infineon</t>
+          <t>Carrier Global</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -21160,19 +21156,19 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Power semiconductors / modules</t>
+          <t>Cooling / thermal management</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Power semiconductors</t>
+          <t>HVAC/cooling</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -21180,7 +21176,11 @@
       <c r="I108" t="n">
         <v>0</v>
       </c>
-      <c r="J108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
       <c r="K108" s="1" t="n">
         <v>46195</v>
       </c>
@@ -21218,37 +21218,37 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>Infineon Technologies AG</t>
+          <t>Carrier Global Corporation</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Building Products &amp; Equipment</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X108" t="n">
-        <v>83700776960</v>
+        <v>57210376192</v>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>1.137526988983154</v>
+        <v>1</v>
       </c>
       <c r="AA108" t="n">
-        <v>95211892790.85938</v>
+        <v>57210376192</v>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
@@ -21256,73 +21256,73 @@
         </is>
       </c>
       <c r="AC108" s="2" t="n">
-        <v>36598</v>
+        <v>43909</v>
       </c>
       <c r="AD108" t="n">
-        <v>26.4</v>
+        <v>6.4</v>
       </c>
       <c r="AE108" t="n">
-        <v>65.48999786376953</v>
+        <v>68.87999725341797</v>
       </c>
       <c r="AF108" t="n">
-        <v>75.40840034484863</v>
+        <v>68.10033111572265</v>
       </c>
       <c r="AG108" t="n">
-        <v>49.37766348838806</v>
+        <v>60.30649625778198</v>
       </c>
       <c r="AH108" t="n">
-        <v>-0.1315291457678648</v>
+        <v>0.01144878629694812</v>
       </c>
       <c r="AI108" t="n">
-        <v>0.3263081571117787</v>
+        <v>0.1421654635511951</v>
       </c>
       <c r="AJ108" t="n">
-        <v>0.5271763590551852</v>
+        <v>0.1292370696620424</v>
       </c>
       <c r="AK108" t="n">
-        <v>88</v>
+        <v>79.50715637207031</v>
       </c>
       <c r="AL108" t="n">
-        <v>31.03618240356445</v>
+        <v>49.78788757324219</v>
       </c>
       <c r="AM108" t="n">
-        <v>-0.2557954788208008</v>
+        <v>-0.1336629254971758</v>
       </c>
       <c r="AN108" t="n">
-        <v>1.110117701081951</v>
+        <v>0.3834689642554061</v>
       </c>
       <c r="AO108" t="n">
-        <v>32.07717398129614</v>
+        <v>46.67245252088201</v>
       </c>
       <c r="AP108" t="n">
-        <v>2288010</v>
+        <v>5711200</v>
       </c>
       <c r="AQ108" t="n">
-        <v>5319782.02</v>
+        <v>6134684</v>
       </c>
       <c r="AR108" t="n">
-        <v>0.4300946902331912</v>
+        <v>0.930968897501485</v>
       </c>
       <c r="AS108" t="n">
-        <v>-0.2014388957705283</v>
+        <v>-0.09042514446473171</v>
       </c>
       <c r="AT108" t="n">
-        <v>0.2218283531367844</v>
+        <v>0.1378368828984733</v>
       </c>
       <c r="AU108" t="n">
-        <v>0.576727545114212</v>
+        <v>0.2107140529497702</v>
       </c>
       <c r="AV108" t="n">
-        <v>0.912867519087661</v>
+        <v>-0.1195947395520467</v>
       </c>
       <c r="AW108" t="n">
-        <v>0.9789813896688373</v>
+        <v>0.5323484051854397</v>
       </c>
       <c r="AX108" t="n">
-        <v>0.7246552585137964</v>
+        <v>0.3017842609249908</v>
       </c>
       <c r="AY108" t="n">
-        <v>0.2962517764387926</v>
+        <v>5.251469758458723</v>
       </c>
       <c r="AZ108" t="inlineStr"/>
       <c r="BA108" t="n">
@@ -21337,12 +21337,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>IFX.DE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nVent Electric</t>
+          <t>Infineon</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -21352,12 +21352,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Cooling / thermal management</t>
+          <t>Power semiconductors / modules</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Enclosures, electrical/thermal infra</t>
+          <t>Power semiconductors</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -21410,37 +21410,37 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>nVent Electric plc</t>
+          <t>Infineon Technologies AG</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="X109" t="n">
-        <v>24547545088</v>
+        <v>83700776960</v>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>1</v>
+        <v>1.137526988983154</v>
       </c>
       <c r="AA109" t="n">
-        <v>24547545088</v>
+        <v>95211892790.85938</v>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
@@ -21448,73 +21448,73 @@
         </is>
       </c>
       <c r="AC109" s="2" t="n">
-        <v>43214</v>
+        <v>36598</v>
       </c>
       <c r="AD109" t="n">
-        <v>8.300000000000001</v>
+        <v>26.4</v>
       </c>
       <c r="AE109" t="n">
-        <v>151.7899932861328</v>
+        <v>64.41000366210938</v>
       </c>
       <c r="AF109" t="n">
-        <v>163.9287268066406</v>
+        <v>75.3928003692627</v>
       </c>
       <c r="AG109" t="n">
-        <v>127.1966328048706</v>
+        <v>49.53329407691955</v>
       </c>
       <c r="AH109" t="n">
-        <v>-0.07404884889288399</v>
+        <v>-0.1456743436158522</v>
       </c>
       <c r="AI109" t="n">
-        <v>0.1933491472135926</v>
+        <v>0.3003375782375384</v>
       </c>
       <c r="AJ109" t="n">
-        <v>0.288781968451318</v>
+        <v>0.522063124899109</v>
       </c>
       <c r="AK109" t="n">
-        <v>184.09619140625</v>
+        <v>88</v>
       </c>
       <c r="AL109" t="n">
-        <v>76.57746124267578</v>
+        <v>31.03618240356445</v>
       </c>
       <c r="AM109" t="n">
-        <v>-0.1754854235350597</v>
+        <v>-0.2680681402033026</v>
       </c>
       <c r="AN109" t="n">
-        <v>0.9821758363744488</v>
+        <v>1.075319793671273</v>
       </c>
       <c r="AO109" t="n">
-        <v>44.23093185649795</v>
+        <v>31.22065659383219</v>
       </c>
       <c r="AP109" t="n">
-        <v>1883300</v>
+        <v>2288577</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1968914</v>
+        <v>5319793.36</v>
       </c>
       <c r="AR109" t="n">
-        <v>0.9565171460002824</v>
+        <v>0.4302003565040729</v>
       </c>
       <c r="AS109" t="n">
-        <v>-0.115868753685099</v>
+        <v>-0.1773946213062965</v>
       </c>
       <c r="AT109" t="n">
-        <v>0.06907940199442653</v>
+        <v>0.2198864506213802</v>
       </c>
       <c r="AU109" t="n">
-        <v>0.3801334056995016</v>
+        <v>0.5336868551995508</v>
       </c>
       <c r="AV109" t="n">
-        <v>0.9821758363744488</v>
+        <v>0.8547114693643603</v>
       </c>
       <c r="AW109" t="n">
-        <v>4.637896523606336</v>
+        <v>0.9622230685119295</v>
       </c>
       <c r="AX109" t="n">
-        <v>0.4276536039046637</v>
+        <v>0.6962140042793381</v>
       </c>
       <c r="AY109" t="n">
-        <v>6.948002499603257</v>
+        <v>0.2748759889904906</v>
       </c>
       <c r="AZ109" t="inlineStr"/>
       <c r="BA109" t="n">
@@ -21529,12 +21529,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Quanta Services</t>
+          <t>nVent Electric</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -21544,19 +21544,19 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Power distribution / UPS / electrical</t>
+          <t>Cooling / thermal management</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Grid/electrical infrastructure construction</t>
+          <t>Enclosures, electrical/thermal infra</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -21564,11 +21564,7 @@
       <c r="I110" t="n">
         <v>0</v>
       </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
-        </is>
-      </c>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" s="1" t="n">
         <v>46195</v>
       </c>
@@ -21606,7 +21602,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>Quanta Services, Inc.</t>
+          <t>nVent Electric plc</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -21616,7 +21612,7 @@
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>Engineering &amp; Construction</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
@@ -21625,7 +21621,7 @@
         </is>
       </c>
       <c r="X110" t="n">
-        <v>93913645056</v>
+        <v>24547545088</v>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
@@ -21636,7 +21632,7 @@
         <v>1</v>
       </c>
       <c r="AA110" t="n">
-        <v>93913645056</v>
+        <v>24547545088</v>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
@@ -21644,73 +21640,73 @@
         </is>
       </c>
       <c r="AC110" s="2" t="n">
-        <v>35838</v>
+        <v>43214</v>
       </c>
       <c r="AD110" t="n">
-        <v>28.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AE110" t="n">
-        <v>625.8400268554688</v>
+        <v>151.7899932861328</v>
       </c>
       <c r="AF110" t="n">
-        <v>694.332412109375</v>
+        <v>163.9287268066406</v>
       </c>
       <c r="AG110" t="n">
-        <v>556.4191688537597</v>
+        <v>127.1966327667236</v>
       </c>
       <c r="AH110" t="n">
-        <v>-0.09864494881612551</v>
+        <v>-0.07404884889288399</v>
       </c>
       <c r="AI110" t="n">
-        <v>0.1247635988974249</v>
+        <v>0.1933491475714846</v>
       </c>
       <c r="AJ110" t="n">
-        <v>0.2478585407826994</v>
+        <v>0.2887819688378306</v>
       </c>
       <c r="AK110" t="n">
-        <v>785.1200561523438</v>
+        <v>184.09619140625</v>
       </c>
       <c r="AL110" t="n">
-        <v>372.1830749511719</v>
+        <v>76.57746124267578</v>
       </c>
       <c r="AM110" t="n">
-        <v>-0.2028734689029119</v>
+        <v>-0.1754854235350597</v>
       </c>
       <c r="AN110" t="n">
-        <v>0.6815381165239045</v>
+        <v>0.9821758363744488</v>
       </c>
       <c r="AO110" t="n">
-        <v>33.93119193251046</v>
+        <v>44.23093185649795</v>
       </c>
       <c r="AP110" t="n">
-        <v>777300</v>
+        <v>1883300</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1217348</v>
+        <v>1968914</v>
       </c>
       <c r="AR110" t="n">
-        <v>0.6385191416094658</v>
+        <v>0.9565171460002824</v>
       </c>
       <c r="AS110" t="n">
-        <v>-0.1289391058804341</v>
+        <v>-0.115868753685099</v>
       </c>
       <c r="AT110" t="n">
-        <v>0.001753450995353178</v>
+        <v>0.06907940199442653</v>
       </c>
       <c r="AU110" t="n">
-        <v>0.3355631875422704</v>
+        <v>0.3801334056995016</v>
       </c>
       <c r="AV110" t="n">
-        <v>0.5381684301858807</v>
+        <v>0.9821758363744488</v>
       </c>
       <c r="AW110" t="n">
-        <v>6.383069579964807</v>
+        <v>4.637896923018395</v>
       </c>
       <c r="AX110" t="n">
-        <v>0.4238961373320826</v>
+        <v>0.4276536039046637</v>
       </c>
       <c r="AY110" t="n">
-        <v>84.10054771801882</v>
+        <v>6.948003293388415</v>
       </c>
       <c r="AZ110" t="inlineStr"/>
       <c r="BA110" t="n">
@@ -21725,12 +21721,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Quanta Services</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -21740,29 +21736,29 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Power semiconductors / modules</t>
+          <t>Power distribution / UPS / electrical</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Analog/power semiconductors</t>
+          <t>Grid/electrical infrastructure construction</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="K111" s="1" t="n">
@@ -21802,17 +21798,17 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>Texas Instruments Incorporated</t>
+          <t>Quanta Services, Inc.</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Engineering &amp; Construction</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
@@ -21821,7 +21817,7 @@
         </is>
       </c>
       <c r="X111" t="n">
-        <v>255282479104</v>
+        <v>93913645056</v>
       </c>
       <c r="Y111" t="inlineStr">
         <is>
@@ -21832,81 +21828,81 @@
         <v>1</v>
       </c>
       <c r="AA111" t="n">
-        <v>255282479104</v>
+        <v>93913645056</v>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>Mega cap</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC111" s="2" t="n">
-        <v>26451</v>
+        <v>35838</v>
       </c>
       <c r="AD111" t="n">
-        <v>54.1</v>
+        <v>28.4</v>
       </c>
       <c r="AE111" t="n">
-        <v>279.5799865722656</v>
+        <v>625.8400268554688</v>
       </c>
       <c r="AF111" t="n">
-        <v>300.9061993408203</v>
+        <v>694.332412109375</v>
       </c>
       <c r="AG111" t="n">
-        <v>222.759951171875</v>
+        <v>556.4191693115234</v>
       </c>
       <c r="AH111" t="n">
-        <v>-0.07087329146183396</v>
+        <v>-0.09864494881612551</v>
       </c>
       <c r="AI111" t="n">
-        <v>0.2550729388360746</v>
+        <v>0.1247635979720867</v>
       </c>
       <c r="AJ111" t="n">
-        <v>0.3508092354924695</v>
+        <v>0.2478585397560913</v>
       </c>
       <c r="AK111" t="n">
-        <v>332.2799987792969</v>
+        <v>785.1200561523438</v>
       </c>
       <c r="AL111" t="n">
-        <v>151.5655517578125</v>
+        <v>372.1830444335938</v>
       </c>
       <c r="AM111" t="n">
-        <v>-0.1586012170477797</v>
+        <v>-0.2028734689029119</v>
       </c>
       <c r="AN111" t="n">
-        <v>0.8446143159166415</v>
+        <v>0.6815382544035624</v>
       </c>
       <c r="AO111" t="n">
-        <v>37.34926419201217</v>
+        <v>33.93119193251046</v>
       </c>
       <c r="AP111" t="n">
-        <v>8268500</v>
+        <v>777300</v>
       </c>
       <c r="AQ111" t="n">
-        <v>8903878</v>
+        <v>1217348</v>
       </c>
       <c r="AR111" t="n">
-        <v>0.9286403070662019</v>
+        <v>0.6385191416094658</v>
       </c>
       <c r="AS111" t="n">
-        <v>-0.1033642642592678</v>
+        <v>-0.1289391058804341</v>
       </c>
       <c r="AT111" t="n">
-        <v>0.01392985269630675</v>
+        <v>0.001753450995353178</v>
       </c>
       <c r="AU111" t="n">
-        <v>0.4631147639163784</v>
+        <v>0.3355631875422704</v>
       </c>
       <c r="AV111" t="n">
-        <v>0.5478580065269616</v>
+        <v>0.5381684301858807</v>
       </c>
       <c r="AW111" t="n">
-        <v>0.7304003986921432</v>
+        <v>6.383068915456183</v>
       </c>
       <c r="AX111" t="n">
-        <v>0.593255451508873</v>
+        <v>0.4238960384669115</v>
       </c>
       <c r="AY111" t="n">
-        <v>405.6164636809355</v>
+        <v>84.10056427163208</v>
       </c>
       <c r="AZ111" t="inlineStr"/>
       <c r="BA111" t="n">
@@ -21921,12 +21917,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ETN</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Eaton</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -21936,29 +21932,29 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Power distribution + UPS</t>
+          <t>Power semiconductors / modules</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Power distribution, electrical infra, UPS</t>
+          <t>Analog/power semiconductors</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G112" t="n">
         <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
         </is>
       </c>
       <c r="K112" s="1" t="n">
@@ -21998,17 +21994,17 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>Eaton Corporation plc</t>
+          <t>Texas Instruments Incorporated</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>Specialty Industrial Machinery</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
@@ -22017,7 +22013,7 @@
         </is>
       </c>
       <c r="X112" t="n">
-        <v>156900376576</v>
+        <v>255282479104</v>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
@@ -22028,11 +22024,11 @@
         <v>1</v>
       </c>
       <c r="AA112" t="n">
-        <v>156900376576</v>
+        <v>255282479104</v>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Mega cap</t>
         </is>
       </c>
       <c r="AC112" s="2" t="n">
@@ -22042,87 +22038,87 @@
         <v>54.1</v>
       </c>
       <c r="AE112" t="n">
-        <v>404.0700073242188</v>
+        <v>279.5799865722656</v>
       </c>
       <c r="AF112" t="n">
-        <v>403.8189996337891</v>
+        <v>300.9061993408203</v>
       </c>
       <c r="AG112" t="n">
-        <v>372.4719799804687</v>
+        <v>222.7599517059326</v>
       </c>
       <c r="AH112" t="n">
-        <v>0.0006215846472239495</v>
+        <v>-0.07087329146183396</v>
       </c>
       <c r="AI112" t="n">
-        <v>0.08483330033418057</v>
+        <v>0.25507293582709</v>
       </c>
       <c r="AJ112" t="n">
-        <v>0.08415940349382534</v>
+        <v>0.3508092322539611</v>
       </c>
       <c r="AK112" t="n">
-        <v>435.7799987792969</v>
+        <v>332.2799987792969</v>
       </c>
       <c r="AL112" t="n">
-        <v>313.9706115722656</v>
+        <v>151.5655517578125</v>
       </c>
       <c r="AM112" t="n">
-        <v>-0.07276605522030355</v>
+        <v>-0.1586012170477797</v>
       </c>
       <c r="AN112" t="n">
-        <v>0.2869676091681441</v>
+        <v>0.8446143159166415</v>
       </c>
       <c r="AO112" t="n">
-        <v>45.11034172595851</v>
+        <v>37.34926419201217</v>
       </c>
       <c r="AP112" t="n">
-        <v>1564100</v>
+        <v>8268500</v>
       </c>
       <c r="AQ112" t="n">
-        <v>2380056</v>
+        <v>8903878</v>
       </c>
       <c r="AR112" t="n">
-        <v>0.6571694111399059</v>
+        <v>0.9286403070662019</v>
       </c>
       <c r="AS112" t="n">
-        <v>-0.03763066657944658</v>
+        <v>-0.1033642642592678</v>
       </c>
       <c r="AT112" t="n">
-        <v>-0.04419078724488146</v>
+        <v>0.01392985269630675</v>
       </c>
       <c r="AU112" t="n">
-        <v>0.2271303587692186</v>
+        <v>0.4631147639163784</v>
       </c>
       <c r="AV112" t="n">
-        <v>0.06198826825831905</v>
+        <v>0.5478580065269616</v>
       </c>
       <c r="AW112" t="n">
-        <v>1.933009298393914</v>
+        <v>0.7304003986921432</v>
       </c>
       <c r="AX112" t="n">
-        <v>0.2417895335497682</v>
+        <v>0.593255451508873</v>
       </c>
       <c r="AY112" t="n">
-        <v>1168.89293081557</v>
+        <v>405.6164284321705</v>
       </c>
       <c r="AZ112" t="inlineStr"/>
       <c r="BA112" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>Positive momentum</t>
+          <t>Strong momentum</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SU.PA</t>
+          <t>ETN</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>Eaton</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -22132,19 +22128,19 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Power, cooling and energy management</t>
+          <t>Power distribution + UPS</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Power, cooling, data center energy management</t>
+          <t>Power distribution, electrical infra, UPS</t>
         </is>
       </c>
       <c r="F113" t="n">
         <v>9</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -22152,7 +22148,11 @@
       <c r="I113" t="n">
         <v>0</v>
       </c>
-      <c r="J113" t="inlineStr"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
       <c r="K113" s="1" t="n">
         <v>46195</v>
       </c>
@@ -22190,7 +22190,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>Schneider Electric S.E.</t>
+          <t>Eaton Corporation plc</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -22205,22 +22205,22 @@
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X113" t="n">
-        <v>151098245120</v>
+        <v>156900376576</v>
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>1.137526988983154</v>
+        <v>1</v>
       </c>
       <c r="AA113" t="n">
-        <v>171878331811.9922</v>
+        <v>156900376576</v>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
@@ -22228,73 +22228,73 @@
         </is>
       </c>
       <c r="AC113" s="2" t="n">
-        <v>36528</v>
+        <v>26451</v>
       </c>
       <c r="AD113" t="n">
-        <v>26.6</v>
+        <v>54.1</v>
       </c>
       <c r="AE113" t="n">
-        <v>265.3999938964844</v>
+        <v>404.0700073242188</v>
       </c>
       <c r="AF113" t="n">
-        <v>272.5050003051758</v>
+        <v>403.8189996337891</v>
       </c>
       <c r="AG113" t="n">
-        <v>250.8887730407715</v>
+        <v>372.4719795227051</v>
       </c>
       <c r="AH113" t="n">
-        <v>-0.02607293958178591</v>
+        <v>0.0006215846472239495</v>
       </c>
       <c r="AI113" t="n">
-        <v>0.0578392595245969</v>
+        <v>0.08483330166742808</v>
       </c>
       <c r="AJ113" t="n">
-        <v>0.08615860726813573</v>
+        <v>0.08415940482624462</v>
       </c>
       <c r="AK113" t="n">
-        <v>292.75</v>
+        <v>435.7799987792969</v>
       </c>
       <c r="AL113" t="n">
-        <v>206.813720703125</v>
+        <v>313.9706115722656</v>
       </c>
       <c r="AM113" t="n">
-        <v>-0.09342444441849918</v>
+        <v>-0.07276605522030355</v>
       </c>
       <c r="AN113" t="n">
-        <v>0.2832803983902898</v>
+        <v>0.2869676091681441</v>
       </c>
       <c r="AO113" t="n">
-        <v>35.09128027613119</v>
+        <v>45.11034172595851</v>
       </c>
       <c r="AP113" t="n">
-        <v>508410</v>
+        <v>1564100</v>
       </c>
       <c r="AQ113" t="n">
-        <v>921830.66</v>
+        <v>2380056</v>
       </c>
       <c r="AR113" t="n">
-        <v>0.5515221201256204</v>
+        <v>0.6571694111399059</v>
       </c>
       <c r="AS113" t="n">
-        <v>-0.05061704351410556</v>
+        <v>-0.03763066657944658</v>
       </c>
       <c r="AT113" t="n">
-        <v>-0.0201633942265691</v>
+        <v>-0.04419078724488146</v>
       </c>
       <c r="AU113" t="n">
-        <v>0.1603660813796153</v>
+        <v>0.2271303587692186</v>
       </c>
       <c r="AV113" t="n">
-        <v>0.1313873945133099</v>
+        <v>0.06198809790020876</v>
       </c>
       <c r="AW113" t="n">
-        <v>0.9057324313166224</v>
+        <v>1.933008648682894</v>
       </c>
       <c r="AX113" t="n">
-        <v>0.1371147649316129</v>
+        <v>0.2417895335497682</v>
       </c>
       <c r="AY113" t="n">
-        <v>13.26178203870275</v>
+        <v>1168.892829870366</v>
       </c>
       <c r="AZ113" t="inlineStr"/>
       <c r="BA113" t="n">
@@ -22481,7 +22481,7 @@
         <v>0.2512150084705262</v>
       </c>
       <c r="AV114" t="n">
-        <v>0.04898162244906445</v>
+        <v>0.04898155263390147</v>
       </c>
       <c r="AW114" t="n">
         <v>1.69626054630091</v>
@@ -22490,7 +22490,7 @@
         <v>0.2141815936828673</v>
       </c>
       <c r="AY114" t="n">
-        <v>538.5246548356439</v>
+        <v>538.5245826922459</v>
       </c>
       <c r="AZ114" t="inlineStr"/>
       <c r="BA114" t="n">
@@ -22682,7 +22682,7 @@
         <v>0.8056648417315213</v>
       </c>
       <c r="AY115" t="n">
-        <v>99.04593584892821</v>
+        <v>99.0459471582359</v>
       </c>
       <c r="AZ115" t="inlineStr"/>
       <c r="BA115" t="n">
@@ -22868,13 +22868,13 @@
         <v>2.714976834936897</v>
       </c>
       <c r="AW116" t="n">
-        <v>6.101179726285145</v>
+        <v>6.101180157350266</v>
       </c>
       <c r="AX116" t="n">
         <v>0.8033505002071863</v>
       </c>
       <c r="AY116" t="n">
-        <v>71.26150698771941</v>
+        <v>71.26151814699374</v>
       </c>
       <c r="AZ116" t="inlineStr"/>
       <c r="BA116" t="n">
@@ -23016,16 +23016,16 @@
         <v>402.9855029296875</v>
       </c>
       <c r="AG117" t="n">
-        <v>326.6473628997803</v>
+        <v>326.6473625946045</v>
       </c>
       <c r="AH117" t="n">
         <v>-0.0772373133818558</v>
       </c>
       <c r="AI117" t="n">
-        <v>0.1384141664283207</v>
+        <v>0.1384141674919033</v>
       </c>
       <c r="AJ117" t="n">
-        <v>0.2337019939552636</v>
+        <v>0.2337019951078705</v>
       </c>
       <c r="AK117" t="n">
         <v>445.4800109863281</v>
@@ -23064,13 +23064,13 @@
         <v>0.6647600539822867</v>
       </c>
       <c r="AW117" t="n">
-        <v>1.545783850555351</v>
+        <v>1.545784116495386</v>
       </c>
       <c r="AX117" t="n">
         <v>0.3664283035760743</v>
       </c>
       <c r="AY117" t="n">
-        <v>837.2507212353189</v>
+        <v>837.2511154354609</v>
       </c>
       <c r="AZ117" t="inlineStr"/>
       <c r="BA117" t="n">
@@ -23262,7 +23262,7 @@
         <v>0.7171365490970862</v>
       </c>
       <c r="AY118" t="n">
-        <v>272.92192606836</v>
+        <v>272.9218335846523</v>
       </c>
       <c r="AZ118" t="inlineStr"/>
       <c r="BA118" t="n">
@@ -23404,28 +23404,28 @@
         <v>1467.392192382812</v>
       </c>
       <c r="AG119" t="n">
-        <v>1198.37722442627</v>
+        <v>1198.377226257324</v>
       </c>
       <c r="AH119" t="n">
         <v>-0.09103369534231076</v>
       </c>
       <c r="AI119" t="n">
-        <v>0.1130135247958504</v>
+        <v>0.1130135230952265</v>
       </c>
       <c r="AJ119" t="n">
-        <v>0.2244827108470253</v>
+        <v>0.2244827089760828</v>
       </c>
       <c r="AK119" t="n">
         <v>1687.3154296875</v>
       </c>
       <c r="AL119" t="n">
-        <v>706.2977905273438</v>
+        <v>706.2978515625</v>
       </c>
       <c r="AM119" t="n">
         <v>-0.2095075792433316</v>
       </c>
       <c r="AN119" t="n">
-        <v>0.8884528261059492</v>
+        <v>0.8884526629141554</v>
       </c>
       <c r="AO119" t="n">
         <v>48.92047670379635</v>
@@ -23449,16 +23449,16 @@
         <v>0.2583112311238724</v>
       </c>
       <c r="AV119" t="n">
-        <v>0.8837910387548251</v>
+        <v>0.8837913635290811</v>
       </c>
       <c r="AW119" t="n">
-        <v>2.633010956233005</v>
+        <v>2.633010654245165</v>
       </c>
       <c r="AX119" t="n">
         <v>0.42956499918327</v>
       </c>
       <c r="AY119" t="n">
-        <v>157.8880454856113</v>
+        <v>157.8881357380186</v>
       </c>
       <c r="AZ119" t="inlineStr"/>
       <c r="BA119" t="n">
@@ -23590,22 +23590,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AE120" t="n">
-        <v>180</v>
+        <v>179.6000061035156</v>
       </c>
       <c r="AF120" t="n">
-        <v>185.9030001831055</v>
+        <v>185.4450003051758</v>
       </c>
       <c r="AG120" t="n">
-        <v>173.0676626586914</v>
+        <v>173.4011519241333</v>
       </c>
       <c r="AH120" t="n">
-        <v>-0.03175311951550697</v>
+        <v>-0.03151874783381259</v>
       </c>
       <c r="AI120" t="n">
-        <v>0.04005564780163429</v>
+        <v>0.03574863321608412</v>
       </c>
       <c r="AJ120" t="n">
-        <v>0.07416369602059492</v>
+        <v>0.06945656500777986</v>
       </c>
       <c r="AK120" t="n">
         <v>210.6000061035156</v>
@@ -23614,43 +23614,43 @@
         <v>110.4240570068359</v>
       </c>
       <c r="AM120" t="n">
-        <v>-0.1452991700697049</v>
+        <v>-0.147198476265773</v>
       </c>
       <c r="AN120" t="n">
-        <v>0.630079575765423</v>
+        <v>0.6264572319815895</v>
       </c>
       <c r="AO120" t="n">
-        <v>53.80483604102962</v>
+        <v>55.03663228872995</v>
       </c>
       <c r="AP120" t="n">
-        <v>169616</v>
+        <v>170467</v>
       </c>
       <c r="AQ120" t="n">
-        <v>441298.7</v>
+        <v>441315.72</v>
       </c>
       <c r="AR120" t="n">
-        <v>0.3843564460987535</v>
+        <v>0.386269947510594</v>
       </c>
       <c r="AS120" t="n">
-        <v>0.04681595344361011</v>
+        <v>0.09079874133752064</v>
       </c>
       <c r="AT120" t="n">
-        <v>-0.06747923474749096</v>
+        <v>-0.0842004573759022</v>
       </c>
       <c r="AU120" t="n">
-        <v>0.0006783739688982493</v>
+        <v>0.02513322511469118</v>
       </c>
       <c r="AV120" t="n">
-        <v>0.4527269664216491</v>
+        <v>0.3521442950047955</v>
       </c>
       <c r="AW120" t="n">
-        <v>1.444424804929016</v>
+        <v>1.39382614259397</v>
       </c>
       <c r="AX120" t="n">
-        <v>-0.06506712681203242</v>
+        <v>-0.06714472371702007</v>
       </c>
       <c r="AY120" t="n">
-        <v>1.885193665574878</v>
+        <v>1.878782045904408</v>
       </c>
       <c r="AZ120" t="inlineStr"/>
       <c r="BA120" t="n">
@@ -24180,16 +24180,16 @@
         <v>76.2314794921875</v>
       </c>
       <c r="AG123" t="n">
-        <v>53.51886251449585</v>
+        <v>53.51886247634888</v>
       </c>
       <c r="AH123" t="n">
         <v>-0.1675355180404667</v>
       </c>
       <c r="AI123" t="n">
-        <v>0.1857501468250413</v>
+        <v>0.1857501476702159</v>
       </c>
       <c r="AJ123" t="n">
-        <v>0.4243852711095986</v>
+        <v>0.4243852721248664</v>
       </c>
       <c r="AK123" t="n">
         <v>87.34999847412109</v>
@@ -24225,16 +24225,16 @@
         <v>0.4362911154986215</v>
       </c>
       <c r="AV123" t="n">
-        <v>0.2322329919315078</v>
+        <v>0.2322329006578092</v>
       </c>
       <c r="AW123" t="n">
-        <v>-0.1402758946306759</v>
+        <v>-0.1402759834910577</v>
       </c>
       <c r="AX123" t="n">
         <v>0.7131528375681255</v>
       </c>
       <c r="AY123" t="n">
-        <v>35.37362472625372</v>
+        <v>35.37362224092882</v>
       </c>
       <c r="AZ123" t="inlineStr"/>
       <c r="BA123" t="n">
@@ -24374,28 +24374,28 @@
         <v>316.3182409667968</v>
       </c>
       <c r="AG124" t="n">
-        <v>244.2018686676025</v>
+        <v>244.2018682098389</v>
       </c>
       <c r="AH124" t="n">
         <v>-0.0820637328277225</v>
       </c>
       <c r="AI124" t="n">
-        <v>0.1890162304482137</v>
+        <v>0.1890162326770599</v>
       </c>
       <c r="AJ124" t="n">
-        <v>0.2953145800753725</v>
+        <v>0.2953145825034782</v>
       </c>
       <c r="AK124" t="n">
         <v>376.1517333984375</v>
       </c>
       <c r="AL124" t="n">
-        <v>121.6859512329102</v>
+        <v>121.6859588623047</v>
       </c>
       <c r="AM124" t="n">
         <v>-0.2280775028517558</v>
       </c>
       <c r="AN124" t="n">
-        <v>1.386142216169274</v>
+        <v>1.386142066564336</v>
       </c>
       <c r="AO124" t="n">
         <v>36.27576342275629</v>
@@ -24419,16 +24419,16 @@
         <v>0.5918105670814564</v>
       </c>
       <c r="AV124" t="n">
-        <v>1.221134204066902</v>
+        <v>1.221134463325372</v>
       </c>
       <c r="AW124" t="n">
-        <v>9.955623509528689</v>
+        <v>9.955621932653035</v>
       </c>
       <c r="AX124" t="n">
         <v>0.6541739897072631</v>
       </c>
       <c r="AY124" t="n">
-        <v>28.21964399319492</v>
+        <v>28.21964118896822</v>
       </c>
       <c r="AZ124" t="inlineStr"/>
       <c r="BA124" t="n">
@@ -24560,22 +24560,22 @@
         <v>20.3</v>
       </c>
       <c r="AE125" t="n">
-        <v>134.9499969482422</v>
+        <v>134.3000030517578</v>
       </c>
       <c r="AF125" t="n">
-        <v>143.6015405273438</v>
+        <v>143.2941796875</v>
       </c>
       <c r="AG125" t="n">
-        <v>138.2200375747681</v>
+        <v>138.1768997573853</v>
       </c>
       <c r="AH125" t="n">
-        <v>-0.06024687163752396</v>
+        <v>-0.06276721535624774</v>
       </c>
       <c r="AI125" t="n">
-        <v>-0.02365822411788165</v>
+        <v>-0.02805748799136909</v>
       </c>
       <c r="AJ125" t="n">
-        <v>0.03893431840274708</v>
+        <v>0.03703426505515606</v>
       </c>
       <c r="AK125" t="n">
         <v>157.5401306152344</v>
@@ -24584,13 +24584,13 @@
         <v>121.6237258911133</v>
       </c>
       <c r="AM125" t="n">
-        <v>-0.1433928839513586</v>
+        <v>-0.1475187780581236</v>
       </c>
       <c r="AN125" t="n">
-        <v>0.1095696662759664</v>
+        <v>0.1042253644818716</v>
       </c>
       <c r="AO125" t="n">
-        <v>27.89469499663905</v>
+        <v>27.46111572740648</v>
       </c>
       <c r="AP125" t="n">
         <v>388638</v>
@@ -24602,25 +24602,25 @@
         <v>0.629210713721025</v>
       </c>
       <c r="AS125" t="n">
-        <v>-0.08601420571101415</v>
+        <v>-0.07347357102937513</v>
       </c>
       <c r="AT125" t="n">
-        <v>-0.08844927444067296</v>
+        <v>-0.07719908817489662</v>
       </c>
       <c r="AU125" t="n">
-        <v>0.06642921033611504</v>
+        <v>0.03709914338280962</v>
       </c>
       <c r="AV125" t="n">
-        <v>0.08156784285861907</v>
+        <v>0.0691911111758996</v>
       </c>
       <c r="AW125" t="n">
-        <v>0.5373625215081412</v>
+        <v>0.5290112640453122</v>
       </c>
       <c r="AX125" t="n">
-        <v>0.07310488773819301</v>
+        <v>0.0679362205052112</v>
       </c>
       <c r="AY125" t="n">
-        <v>8.966369734028385</v>
+        <v>8.918366878356613</v>
       </c>
       <c r="AZ125" t="inlineStr"/>
       <c r="BA125" t="n">
@@ -24866,22 +24866,22 @@
         <v>29.7</v>
       </c>
       <c r="AE127" t="n">
-        <v>268.2000122070312</v>
+        <v>272.25</v>
       </c>
       <c r="AF127" t="n">
-        <v>270.4659985351562</v>
+        <v>270.718998413086</v>
       </c>
       <c r="AG127" t="n">
-        <v>245.1286183929443</v>
+        <v>245.3035883331299</v>
       </c>
       <c r="AH127" t="n">
-        <v>-0.00837808205244861</v>
+        <v>0.005655316382996878</v>
       </c>
       <c r="AI127" t="n">
-        <v>0.09411954412072432</v>
+        <v>0.109849235594043</v>
       </c>
       <c r="AJ127" t="n">
-        <v>0.1033636150210571</v>
+        <v>0.1036079832857608</v>
       </c>
       <c r="AK127" t="n">
         <v>284.1000061035156</v>
@@ -24890,43 +24890,43 @@
         <v>203.75</v>
       </c>
       <c r="AM127" t="n">
-        <v>-0.05596618639526185</v>
+        <v>-0.04171068584629989</v>
       </c>
       <c r="AN127" t="n">
-        <v>0.3163190783167178</v>
+        <v>0.336196319018405</v>
       </c>
       <c r="AO127" t="n">
-        <v>33.64198364232901</v>
+        <v>40.67795888189422</v>
       </c>
       <c r="AP127" t="n">
-        <v>700995</v>
+        <v>700997</v>
       </c>
       <c r="AQ127" t="n">
-        <v>988820.64</v>
+        <v>988820.6800000001</v>
       </c>
       <c r="AR127" t="n">
-        <v>0.7089202749651342</v>
+        <v>0.7089222688991496</v>
       </c>
       <c r="AS127" t="n">
-        <v>-0.0154184353287804</v>
+        <v>0.01775700934579438</v>
       </c>
       <c r="AT127" t="n">
-        <v>0.06491961765843834</v>
+        <v>0.08401356407045091</v>
       </c>
       <c r="AU127" t="n">
-        <v>0.07602378561650225</v>
+        <v>0.09722948904613937</v>
       </c>
       <c r="AV127" t="n">
-        <v>0.2050235033235102</v>
+        <v>0.232164607059594</v>
       </c>
       <c r="AW127" t="n">
-        <v>1.147257066106371</v>
+        <v>1.185833994884008</v>
       </c>
       <c r="AX127" t="n">
-        <v>0.1360507710638803</v>
+        <v>0.1532058476693572</v>
       </c>
       <c r="AY127" t="n">
-        <v>27.21304337663148</v>
+        <v>27.63906934376135</v>
       </c>
       <c r="AZ127" t="inlineStr"/>
       <c r="BA127" t="n">
@@ -25058,22 +25058,22 @@
         <v>28</v>
       </c>
       <c r="AE128" t="n">
-        <v>229.8999938964844</v>
+        <v>227</v>
       </c>
       <c r="AF128" t="n">
-        <v>273.9499990844727</v>
+        <v>273.2539993286133</v>
       </c>
       <c r="AG128" t="n">
-        <v>196.0090330123901</v>
+        <v>196.421587562561</v>
       </c>
       <c r="AH128" t="n">
-        <v>-0.1607957851257573</v>
+        <v>-0.1692710790775602</v>
       </c>
       <c r="AI128" t="n">
-        <v>0.1729050970929076</v>
+        <v>0.1556774528548173</v>
       </c>
       <c r="AJ128" t="n">
-        <v>0.3976396642248405</v>
+        <v>0.3911607309536731</v>
       </c>
       <c r="AK128" t="n">
         <v>320.2999877929688</v>
@@ -25082,13 +25082,13 @@
         <v>105.1371765136719</v>
       </c>
       <c r="AM128" t="n">
-        <v>-0.282235396009181</v>
+        <v>-0.2912893891624959</v>
       </c>
       <c r="AN128" t="n">
-        <v>1.186666995632972</v>
+        <v>1.159084041699382</v>
       </c>
       <c r="AO128" t="n">
-        <v>33.33333333333333</v>
+        <v>36.76595828676699</v>
       </c>
       <c r="AP128" t="n">
         <v>506208</v>
@@ -25100,25 +25100,25 @@
         <v>1.169182733397937</v>
       </c>
       <c r="AS128" t="n">
-        <v>-0.2047734726986965</v>
+        <v>-0.1970286869540004</v>
       </c>
       <c r="AT128" t="n">
-        <v>-0.072983895578692</v>
+        <v>-0.03527413065919982</v>
       </c>
       <c r="AU128" t="n">
-        <v>0.3231304569585747</v>
+        <v>0.2997501090793702</v>
       </c>
       <c r="AV128" t="n">
-        <v>0.9279114109428077</v>
+        <v>0.8662671024940312</v>
       </c>
       <c r="AW128" t="n">
-        <v>2.636798689985213</v>
+        <v>2.54899925294507</v>
       </c>
       <c r="AX128" t="n">
-        <v>0.5516389413566207</v>
+        <v>0.5320663290080194</v>
       </c>
       <c r="AY128" t="n">
-        <v>108.1710899124997</v>
+        <v>106.7939889867757</v>
       </c>
       <c r="AZ128" t="inlineStr"/>
       <c r="BA128" t="n">
@@ -25702,7 +25702,7 @@
         <v>0.3688027640139162</v>
       </c>
       <c r="AY131" t="n">
-        <v>11.20524091867666</v>
+        <v>11.20524217516729</v>
       </c>
       <c r="AZ131" t="inlineStr"/>
       <c r="BA131" t="n">
@@ -25898,7 +25898,7 @@
         <v>0.7125897601161928</v>
       </c>
       <c r="AY132" t="n">
-        <v>22.12446069955416</v>
+        <v>22.12445861605731</v>
       </c>
       <c r="AZ132" t="inlineStr"/>
       <c r="BA132" t="n">
@@ -26040,16 +26040,16 @@
         <v>537.4219989013671</v>
       </c>
       <c r="AG133" t="n">
-        <v>366.1350757598877</v>
+        <v>366.1350760650635</v>
       </c>
       <c r="AH133" t="n">
         <v>-0.00218077954338125</v>
       </c>
       <c r="AI133" t="n">
-        <v>0.4646234013145305</v>
+        <v>0.4646234000937581</v>
       </c>
       <c r="AJ133" t="n">
-        <v>0.4678244027453131</v>
+        <v>0.4678244015218729</v>
       </c>
       <c r="AK133" t="n">
         <v>723</v>
@@ -26088,13 +26088,13 @@
         <v>1.871485474533964</v>
       </c>
       <c r="AW133" t="n">
-        <v>3.348633831773504</v>
+        <v>3.348634638915202</v>
       </c>
       <c r="AX133" t="n">
         <v>0.9994283394352941</v>
       </c>
       <c r="AY133" t="n">
-        <v>7771.102710518444</v>
+        <v>7771.106067585788</v>
       </c>
       <c r="AZ133" t="inlineStr"/>
       <c r="BA133" t="n">
@@ -26223,25 +26223,25 @@
         <v>36166</v>
       </c>
       <c r="AD134" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="AE134" t="n">
-        <v>873.5999755859375</v>
+        <v>859.4000244140625</v>
       </c>
       <c r="AF134" t="n">
-        <v>928.7699975585938</v>
+        <v>928.6939978027344</v>
       </c>
       <c r="AG134" t="n">
-        <v>712.8177711486817</v>
+        <v>714.3923707580566</v>
       </c>
       <c r="AH134" t="n">
-        <v>-0.05940116726173184</v>
+        <v>-0.07461443010573954</v>
       </c>
       <c r="AI134" t="n">
-        <v>0.2255586363653095</v>
+        <v>0.2029804062746852</v>
       </c>
       <c r="AJ134" t="n">
-        <v>0.3029557274672212</v>
+        <v>0.2999774855060082</v>
       </c>
       <c r="AK134" t="n">
         <v>1079</v>
@@ -26250,13 +26250,13 @@
         <v>400.14208984375</v>
       </c>
       <c r="AM134" t="n">
-        <v>-0.1903614684096965</v>
+        <v>-0.2035217567988299</v>
       </c>
       <c r="AN134" t="n">
-        <v>1.18322440392878</v>
+        <v>1.147737131951418</v>
       </c>
       <c r="AO134" t="n">
-        <v>35.1571584331372</v>
+        <v>34.85285525157721</v>
       </c>
       <c r="AP134" t="n">
         <v>157662</v>
@@ -26268,25 +26268,25 @@
         <v>0.943398710206145</v>
       </c>
       <c r="AS134" t="n">
-        <v>-0.1184662203976413</v>
+        <v>-0.09345988985858389</v>
       </c>
       <c r="AT134" t="n">
-        <v>0.04829220222071751</v>
+        <v>0.06249507629367845</v>
       </c>
       <c r="AU134" t="n">
-        <v>0.2348652020151518</v>
+        <v>0.191309010805738</v>
       </c>
       <c r="AV134" t="n">
-        <v>0.9801337265822498</v>
+        <v>0.9279240299558904</v>
       </c>
       <c r="AW134" t="n">
-        <v>1.823325821198029</v>
+        <v>1.775693166306392</v>
       </c>
       <c r="AX134" t="n">
-        <v>0.5836065512101931</v>
+        <v>0.5578657816004371</v>
       </c>
       <c r="AY134" t="n">
-        <v>296.2193939720369</v>
+        <v>291.3882581200621</v>
       </c>
       <c r="AZ134" t="inlineStr"/>
       <c r="BA134" t="n">
@@ -26428,28 +26428,28 @@
         <v>1741.728598632812</v>
       </c>
       <c r="AG135" t="n">
-        <v>1373.550565795898</v>
+        <v>1373.550560913086</v>
       </c>
       <c r="AH135" t="n">
         <v>0.008819610127294375</v>
       </c>
       <c r="AI135" t="n">
-        <v>0.2792320935066368</v>
+        <v>0.2792320980541581</v>
       </c>
       <c r="AJ135" t="n">
-        <v>0.2680484009873891</v>
+        <v>0.2680484054951535</v>
       </c>
       <c r="AK135" t="n">
         <v>1989.43994140625</v>
       </c>
       <c r="AL135" t="n">
-        <v>686.00341796875</v>
+        <v>686.0034790039062</v>
       </c>
       <c r="AM135" t="n">
         <v>-0.1167916511325792</v>
       </c>
       <c r="AN135" t="n">
-        <v>1.561342873513721</v>
+        <v>1.561342645625719</v>
       </c>
       <c r="AO135" t="n">
         <v>43.03968523777147</v>
@@ -26473,7 +26473,7 @@
         <v>0.2694021479355795</v>
       </c>
       <c r="AV135" t="n">
-        <v>1.442295038575285</v>
+        <v>1.44229483137885</v>
       </c>
       <c r="AW135" t="n">
         <v>1.689003226823077</v>
@@ -26482,7 +26482,7 @@
         <v>0.5151062952554408</v>
       </c>
       <c r="AY135" t="n">
-        <v>996.1943016072649</v>
+        <v>996.1942341427119</v>
       </c>
       <c r="AZ135" t="inlineStr"/>
       <c r="BA135" t="n">
@@ -26624,28 +26624,28 @@
         <v>220.7670791625977</v>
       </c>
       <c r="AG136" t="n">
-        <v>160.2603728866577</v>
+        <v>160.2603727722168</v>
       </c>
       <c r="AH136" t="n">
         <v>-0.0464157741679847</v>
       </c>
       <c r="AI136" t="n">
-        <v>0.3136123452136779</v>
+        <v>0.3136123461517202</v>
       </c>
       <c r="AJ136" t="n">
-        <v>0.3775525114916127</v>
+        <v>0.3775525124753143</v>
       </c>
       <c r="AK136" t="n">
         <v>301.7099914550781</v>
       </c>
       <c r="AL136" t="n">
-        <v>84.03206634521484</v>
+        <v>84.03205871582031</v>
       </c>
       <c r="AM136" t="n">
         <v>-0.3022438426477982</v>
       </c>
       <c r="AN136" t="n">
-        <v>1.505234173435852</v>
+        <v>1.505234400889756</v>
       </c>
       <c r="AO136" t="n">
         <v>38.26829873306283</v>
@@ -26678,7 +26678,7 @@
         <v>0.6560813487675303</v>
       </c>
       <c r="AY136" t="n">
-        <v>3468.737598079234</v>
+        <v>3468.737172000402</v>
       </c>
       <c r="AZ136" t="inlineStr"/>
       <c r="BA136" t="n">
@@ -26820,28 +26820,28 @@
         <v>425.6804748535156</v>
       </c>
       <c r="AG137" t="n">
-        <v>353.4806147766113</v>
+        <v>353.4806149291992</v>
       </c>
       <c r="AH137" t="n">
         <v>-0.05231734248339659</v>
       </c>
       <c r="AI137" t="n">
-        <v>0.1412507130470275</v>
+        <v>0.1412507125543812</v>
       </c>
       <c r="AJ137" t="n">
-        <v>0.204254086528995</v>
+        <v>0.2042540860091515</v>
       </c>
       <c r="AK137" t="n">
         <v>477.5700073242188</v>
       </c>
       <c r="AL137" t="n">
-        <v>224.8433685302734</v>
+        <v>224.8433532714844</v>
       </c>
       <c r="AM137" t="n">
         <v>-0.155286141350503</v>
       </c>
       <c r="AN137" t="n">
-        <v>0.7941823514701227</v>
+        <v>0.7941824732306713</v>
       </c>
       <c r="AO137" t="n">
         <v>27.94492700878187</v>
@@ -26868,13 +26868,13 @@
         <v>0.6882097563367864</v>
       </c>
       <c r="AW137" t="n">
-        <v>2.793959414147854</v>
+        <v>2.793960230824469</v>
       </c>
       <c r="AX137" t="n">
         <v>0.2687154386460626</v>
       </c>
       <c r="AY137" t="n">
-        <v>128.1778407591334</v>
+        <v>128.1778506212358</v>
       </c>
       <c r="AZ137" t="inlineStr"/>
       <c r="BA137" t="n">
@@ -27060,13 +27060,13 @@
         <v>1.708021559957533</v>
       </c>
       <c r="AW138" t="n">
-        <v>1.844331770521075</v>
+        <v>1.844331968555952</v>
       </c>
       <c r="AX138" t="n">
         <v>1.528407865394755</v>
       </c>
       <c r="AY138" t="n">
-        <v>2.222206280887596</v>
+        <v>2.222207297482566</v>
       </c>
       <c r="AZ138" t="inlineStr"/>
       <c r="BA138" t="n">
@@ -27204,28 +27204,28 @@
         <v>44482.264453125</v>
       </c>
       <c r="AG139" t="n">
-        <v>35020.70248046875</v>
+        <v>35020.7025</v>
       </c>
       <c r="AH139" t="n">
         <v>-0.02950084644426876</v>
       </c>
       <c r="AI139" t="n">
-        <v>0.232699430403378</v>
+        <v>0.2326994297158944</v>
       </c>
       <c r="AJ139" t="n">
-        <v>0.2701705363544038</v>
+        <v>0.2701705356460224</v>
       </c>
       <c r="AK139" t="n">
         <v>57263.48828125</v>
       </c>
       <c r="AL139" t="n">
-        <v>14136.361328125</v>
+        <v>14136.3603515625</v>
       </c>
       <c r="AM139" t="n">
         <v>-0.2461164819724174</v>
       </c>
       <c r="AN139" t="n">
-        <v>2.053826865199825</v>
+        <v>2.053827076163094</v>
       </c>
       <c r="AO139" t="n">
         <v>41.49582384206529</v>
@@ -27252,7 +27252,7 @@
         <v>1.259657634322771</v>
       </c>
       <c r="AW139" t="n">
-        <v>1.166379571008027</v>
+        <v>1.166379358675244</v>
       </c>
       <c r="AX139" t="n">
         <v>0.3667853277162265</v>
@@ -27982,28 +27982,28 @@
         <v>380.2771588134765</v>
       </c>
       <c r="AG143" t="n">
-        <v>284.2338338470459</v>
+        <v>284.2338335418701</v>
       </c>
       <c r="AH143" t="n">
         <v>-0.07982900019675432</v>
       </c>
       <c r="AI143" t="n">
-        <v>0.2310990872959762</v>
+        <v>0.2310990886177811</v>
       </c>
       <c r="AJ143" t="n">
-        <v>0.3379025067723438</v>
+        <v>0.337902508208821</v>
       </c>
       <c r="AK143" t="n">
         <v>483.8399963378906</v>
       </c>
       <c r="AL143" t="n">
-        <v>89.91980743408203</v>
+        <v>89.9197998046875</v>
       </c>
       <c r="AM143" t="n">
         <v>-0.2767856810593909</v>
       </c>
       <c r="AN143" t="n">
-        <v>2.89146755773751</v>
+        <v>2.891467887915528</v>
       </c>
       <c r="AO143" t="n">
         <v>42.78683131097601</v>
@@ -28027,16 +28027,16 @@
         <v>0.5280501639336617</v>
       </c>
       <c r="AV143" t="n">
-        <v>2.841188465123945</v>
+        <v>2.841188786825056</v>
       </c>
       <c r="AW143" t="n">
-        <v>1.971928594996424</v>
+        <v>1.971928017274029</v>
       </c>
       <c r="AX143" t="n">
         <v>0.687215867998388</v>
       </c>
       <c r="AY143" t="n">
-        <v>313.1785737183141</v>
+        <v>313.1787082283294</v>
       </c>
       <c r="AZ143" t="inlineStr"/>
       <c r="BA143" t="n">
@@ -28222,13 +28222,13 @@
         <v>0.4061301517252378</v>
       </c>
       <c r="AW144" t="n">
-        <v>4.862339292198379</v>
+        <v>4.862339843381628</v>
       </c>
       <c r="AX144" t="n">
         <v>0.1983577686638374</v>
       </c>
       <c r="AY144" t="n">
-        <v>40.665041754344</v>
+        <v>40.66503479388871</v>
       </c>
       <c r="AZ144" t="inlineStr"/>
       <c r="BA144" t="n">
@@ -28606,13 +28606,13 @@
         <v>0.5528377712945363</v>
       </c>
       <c r="AW146" t="n">
-        <v>7.104808224094768</v>
+        <v>7.104808924037608</v>
       </c>
       <c r="AX146" t="n">
         <v>0.1971878045669091</v>
       </c>
       <c r="AY146" t="n">
-        <v>36.2964336068907</v>
+        <v>36.29644101797499</v>
       </c>
       <c r="AZ146" t="inlineStr"/>
       <c r="BA146" t="n">
@@ -28798,7 +28798,7 @@
         <v>1.263320589541411</v>
       </c>
       <c r="AW147" t="n">
-        <v>7.316852207967017</v>
+        <v>7.316851471177619</v>
       </c>
       <c r="AX147" t="n">
         <v>0.3160603109076747</v>
@@ -28919,10 +28919,10 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>1.331859469413757</v>
+        <v>1.332054495811462</v>
       </c>
       <c r="AA148" t="n">
-        <v>155856890368.1689</v>
+        <v>155879712751.8994</v>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
@@ -28936,22 +28936,22 @@
         <v>38.1</v>
       </c>
       <c r="AE148" t="n">
-        <v>1359</v>
+        <v>1415.599975585938</v>
       </c>
       <c r="AF148" t="n">
-        <v>1342.94798828125</v>
+        <v>1347.315988769531</v>
       </c>
       <c r="AG148" t="n">
-        <v>1229.892869262695</v>
+        <v>1231.203622436523</v>
       </c>
       <c r="AH148" t="n">
-        <v>0.01195281712979357</v>
+        <v>0.05068149371460229</v>
       </c>
       <c r="AI148" t="n">
-        <v>0.1049742900084483</v>
+        <v>0.1497691769168921</v>
       </c>
       <c r="AJ148" t="n">
-        <v>0.09192273721070499</v>
+        <v>0.09430801227113372</v>
       </c>
       <c r="AK148" t="n">
         <v>1504.199951171875</v>
@@ -28960,43 +28960,43 @@
         <v>977.11669921875</v>
       </c>
       <c r="AM148" t="n">
-        <v>-0.09652968746525636</v>
+        <v>-0.05890172747107991</v>
       </c>
       <c r="AN148" t="n">
-        <v>0.3908267058444332</v>
+        <v>0.4487522081218909</v>
       </c>
       <c r="AO148" t="n">
-        <v>25.06868552217345</v>
+        <v>37.28423034767917</v>
       </c>
       <c r="AP148" t="n">
-        <v>28370595</v>
+        <v>28452542</v>
       </c>
       <c r="AQ148" t="n">
-        <v>25926483.86</v>
+        <v>25928122.8</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.094270829519264</v>
+        <v>1.097362204717728</v>
       </c>
       <c r="AS148" t="n">
-        <v>-0.05097765363128492</v>
+        <v>0.006684699715875375</v>
       </c>
       <c r="AT148" t="n">
-        <v>0.203293758298841</v>
+        <v>0.2523000221268634</v>
       </c>
       <c r="AU148" t="n">
-        <v>0.08464462387198135</v>
+        <v>0.1458213015589425</v>
       </c>
       <c r="AV148" t="n">
-        <v>0.3789731432931809</v>
+        <v>0.4487522081218909</v>
       </c>
       <c r="AW148" t="n">
-        <v>13.00977705160586</v>
+        <v>13.40763319384523</v>
       </c>
       <c r="AX148" t="n">
-        <v>0.1353882501190926</v>
+        <v>0.1826751870118821</v>
       </c>
       <c r="AY148" t="n">
-        <v>9.91429087868857</v>
+        <v>10.36885759737734</v>
       </c>
       <c r="AZ148" t="inlineStr"/>
       <c r="BA148" t="n">
@@ -29182,13 +29182,13 @@
         <v>0.1547295190310001</v>
       </c>
       <c r="AW149" t="n">
-        <v>0.7056694159557297</v>
+        <v>0.7056695415001923</v>
       </c>
       <c r="AX149" t="n">
         <v>0.340759868821106</v>
       </c>
       <c r="AY149" t="n">
-        <v>-0.07620730720728386</v>
+        <v>-0.0762071599024795</v>
       </c>
       <c r="AZ149" t="inlineStr"/>
       <c r="BA149" t="n">
@@ -29330,16 +29330,16 @@
         <v>382.5761428833008</v>
       </c>
       <c r="AG150" t="n">
-        <v>207.3743054199219</v>
+        <v>207.3743055725098</v>
       </c>
       <c r="AH150" t="n">
         <v>0.1435632047068154</v>
       </c>
       <c r="AI150" t="n">
-        <v>1.109711707600832</v>
+        <v>1.109711706048488</v>
       </c>
       <c r="AJ150" t="n">
-        <v>0.8448579832906713</v>
+        <v>0.844857981933208</v>
       </c>
       <c r="AK150" t="n">
         <v>465.1912841796875</v>
@@ -29384,7 +29384,7 @@
         <v>2.454631811577981</v>
       </c>
       <c r="AY150" t="n">
-        <v>38.90908684405624</v>
+        <v>38.90909031594378</v>
       </c>
       <c r="AZ150" t="inlineStr"/>
       <c r="BA150" t="n">
@@ -29526,16 +29526,16 @@
         <v>141.7825784301758</v>
       </c>
       <c r="AG151" t="n">
-        <v>129.3087047958374</v>
+        <v>129.3087043380737</v>
       </c>
       <c r="AH151" t="n">
         <v>0.01119613357711269</v>
       </c>
       <c r="AI151" t="n">
-        <v>0.1087420243173201</v>
+        <v>0.1087420282423597</v>
       </c>
       <c r="AJ151" t="n">
-        <v>0.09646584624007404</v>
+        <v>0.09646585012165532</v>
       </c>
       <c r="AK151" t="n">
         <v>148.2100067138672</v>
@@ -29568,10 +29568,10 @@
         <v>0.01301232835417965</v>
       </c>
       <c r="AU151" t="n">
-        <v>0.269565043498893</v>
+        <v>0.2695649577276535</v>
       </c>
       <c r="AV151" t="n">
-        <v>0.3107607309259952</v>
+        <v>0.3107606394981222</v>
       </c>
       <c r="AW151" t="n">
         <v>1.312830103013279</v>
@@ -29580,7 +29580,7 @@
         <v>0.1790522904686949</v>
       </c>
       <c r="AY151" t="n">
-        <v>45.42623523908412</v>
+        <v>45.42624240775799</v>
       </c>
       <c r="AZ151" t="inlineStr"/>
       <c r="BA151" t="n">
@@ -29713,7 +29713,7 @@
         <v>33974</v>
       </c>
       <c r="AD152" t="n">
-        <v>33.5</v>
+        <v>33.6</v>
       </c>
       <c r="AE152" t="n">
         <v>252.5</v>
@@ -29770,13 +29770,13 @@
         <v>0.6100270198771374</v>
       </c>
       <c r="AW152" t="n">
-        <v>1.980214644885388</v>
+        <v>1.980214913249118</v>
       </c>
       <c r="AX152" t="n">
         <v>0.1207731431766315</v>
       </c>
       <c r="AY152" t="n">
-        <v>688.3323320480974</v>
+        <v>688.3319394539543</v>
       </c>
       <c r="AZ152" t="inlineStr"/>
       <c r="BA152" t="n">
@@ -30154,13 +30154,13 @@
         <v>0.2527592595506554</v>
       </c>
       <c r="AW154" t="n">
-        <v>4.167564946571683</v>
+        <v>4.167564636002688</v>
       </c>
       <c r="AX154" t="n">
         <v>0.2346689120962564</v>
       </c>
       <c r="AY154" t="n">
-        <v>16.24261694102647</v>
+        <v>16.24261521215561</v>
       </c>
       <c r="AZ154" t="inlineStr"/>
       <c r="BA154" t="n">
@@ -30302,28 +30302,28 @@
         <v>117.3123500061035</v>
       </c>
       <c r="AG155" t="n">
-        <v>87.70713092803955</v>
+        <v>87.70713134765624</v>
       </c>
       <c r="AH155" t="n">
         <v>-0.02678619801746973</v>
       </c>
       <c r="AI155" t="n">
-        <v>0.3017185371462847</v>
+        <v>0.3017185309184807</v>
       </c>
       <c r="AJ155" t="n">
-        <v>0.3375463176689015</v>
+        <v>0.3375463112696866</v>
       </c>
       <c r="AK155" t="n">
         <v>129.5154876708984</v>
       </c>
       <c r="AL155" t="n">
-        <v>64.85703277587891</v>
+        <v>64.85704040527344</v>
       </c>
       <c r="AM155" t="n">
         <v>-0.1184838182515</v>
       </c>
       <c r="AN155" t="n">
-        <v>0.7603333560367023</v>
+        <v>0.7603331489616092</v>
       </c>
       <c r="AO155" t="n">
         <v>50.31300629582194</v>
@@ -30350,13 +30350,13 @@
         <v>0.7064583982851134</v>
       </c>
       <c r="AW155" t="n">
-        <v>1.474564160491827</v>
+        <v>1.474564365091794</v>
       </c>
       <c r="AX155" t="n">
         <v>0.5152296656134121</v>
       </c>
       <c r="AY155" t="n">
-        <v>2303.85699629152</v>
+        <v>2303.856822952609</v>
       </c>
       <c r="AZ155" t="inlineStr"/>
       <c r="BA155" t="n">
@@ -30694,16 +30694,16 @@
         <v>44.53508098602295</v>
       </c>
       <c r="AG157" t="n">
-        <v>28.73352772712708</v>
+        <v>28.73352780342102</v>
       </c>
       <c r="AH157" t="n">
         <v>0.07084117892760067</v>
       </c>
       <c r="AI157" t="n">
-        <v>0.659733502951859</v>
+        <v>0.659733498544895</v>
       </c>
       <c r="AJ157" t="n">
-        <v>0.5499343279028617</v>
+        <v>0.5499343237874394</v>
       </c>
       <c r="AK157" t="n">
         <v>55.98620223999023</v>
@@ -30736,19 +30736,19 @@
         <v>0.6984916867407596</v>
       </c>
       <c r="AU157" t="n">
-        <v>1.28683777215615</v>
+        <v>1.286837981313691</v>
       </c>
       <c r="AV157" t="n">
         <v>1.373640379910901</v>
       </c>
       <c r="AW157" t="n">
-        <v>3.018197142297195</v>
+        <v>3.018196819421597</v>
       </c>
       <c r="AX157" t="n">
         <v>0.9916398786566072</v>
       </c>
       <c r="AY157" t="n">
-        <v>5.618982474780201</v>
+        <v>5.618983788935179</v>
       </c>
       <c r="AZ157" t="inlineStr"/>
       <c r="BA157" t="n">
@@ -30890,16 +30890,16 @@
         <v>351.7297955322265</v>
       </c>
       <c r="AG158" t="n">
-        <v>275.4976197052002</v>
+        <v>275.4976194000244</v>
       </c>
       <c r="AH158" t="n">
         <v>-0.111278031294195</v>
       </c>
       <c r="AI158" t="n">
-        <v>0.1346377390569895</v>
+        <v>0.1346377403138568</v>
       </c>
       <c r="AJ158" t="n">
-        <v>0.2767072031642219</v>
+        <v>0.2767072045784631</v>
       </c>
       <c r="AK158" t="n">
         <v>385.6300048828125</v>
@@ -30935,16 +30935,16 @@
         <v>0.2863324642833125</v>
       </c>
       <c r="AV158" t="n">
-        <v>0.4330755426106001</v>
+        <v>0.4330756428603257</v>
       </c>
       <c r="AW158" t="n">
-        <v>4.926353281380813</v>
+        <v>4.926352852773038</v>
       </c>
       <c r="AX158" t="n">
         <v>0.3010478040596756</v>
       </c>
       <c r="AY158" t="n">
-        <v>422.0070912947435</v>
+        <v>422.006920698229</v>
       </c>
       <c r="AZ158" t="inlineStr"/>
       <c r="BA158" t="n">
@@ -32612,13 +32612,13 @@
         <v>0.3325427361689419</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.008865069538427</v>
+        <v>8.00886425889888</v>
       </c>
       <c r="AX5" t="n">
         <v>0.1027182559175892</v>
       </c>
       <c r="AY5" t="n">
-        <v>335.3181665060716</v>
+        <v>335.3182018112477</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -32966,28 +32966,28 @@
         <v>338.3413366699219</v>
       </c>
       <c r="AG7" t="n">
-        <v>237.221819152832</v>
+        <v>237.2218195343017</v>
       </c>
       <c r="AH7" t="n">
         <v>-0.09792284188782385</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.2866016816878221</v>
+        <v>0.2866016796188744</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.4262656693140978</v>
+        <v>0.4262656670205605</v>
       </c>
       <c r="AK7" t="n">
         <v>433.3299865722656</v>
       </c>
       <c r="AL7" t="n">
-        <v>94.3179931640625</v>
+        <v>94.31800079345703</v>
       </c>
       <c r="AM7" t="n">
         <v>-0.2956638106922729</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.235967827731207</v>
+        <v>2.235967565973376</v>
       </c>
       <c r="AO7" t="n">
         <v>36.19005920099731</v>
@@ -33168,16 +33168,16 @@
         <v>239.1006469726562</v>
       </c>
       <c r="AG8" t="n">
-        <v>132.7225814056397</v>
+        <v>132.7225813293457</v>
       </c>
       <c r="AH8" t="n">
         <v>-0.1876642820219915</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.4634284058559295</v>
+        <v>0.4634284066971635</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.8015069059114637</v>
+        <v>0.801506906947038</v>
       </c>
       <c r="AK8" t="n">
         <v>316.3519592285156</v>
@@ -33210,19 +33210,19 @@
         <v>0.1823864499806978</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.422724171642454</v>
+        <v>1.422723941083668</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.628900969832727</v>
+        <v>1.628900698362516</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.610774748687912</v>
+        <v>2.610774492626262</v>
       </c>
       <c r="AX8" t="n">
         <v>1.176026581971421</v>
       </c>
       <c r="AY8" t="n">
-        <v>15.01328458857992</v>
+        <v>15.0132871066899</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
@@ -33499,7 +33499,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.294248870941623</v>
+        <v>1.294248837007847</v>
       </c>
     </row>
   </sheetData>
@@ -33636,71 +33636,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Servers / Racks / ODM</t>
+          <t>Accelerators / Full-Stack Compute</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>1466.249001442474</v>
+        <v>11878.21006143622</v>
       </c>
       <c r="D2" t="n">
-        <v>91.6405625901546</v>
+        <v>1484.776257679527</v>
       </c>
       <c r="E2" t="n">
-        <v>41.2571356046875</v>
+        <v>371.6866048</v>
       </c>
       <c r="F2" t="n">
-        <v>79.0625</v>
+        <v>85.625</v>
       </c>
       <c r="G2" t="n">
         <v>85</v>
       </c>
       <c r="H2" t="n">
-        <v>87.52336053449194</v>
+        <v>89.09580949990689</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J2" t="n">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4448063519400982</v>
+        <v>0.6139064614478473</v>
       </c>
       <c r="L2" t="n">
-        <v>0.267858358077966</v>
+        <v>0.3260329585128673</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7741914636641573</v>
+        <v>0.3234878388696328</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7160292988773236</v>
+        <v>1.181598378575055</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5735245641940394</v>
+        <v>0.5946300354380049</v>
       </c>
       <c r="P2" t="n">
-        <v>1.027358911787491</v>
+        <v>0.6471107221027181</v>
       </c>
       <c r="Q2" t="n">
-        <v>7.473884092500905</v>
+        <v>4.987296973806465</v>
       </c>
       <c r="R2" t="n">
-        <v>4.612258536234526</v>
+        <v>1.484363175097864</v>
       </c>
       <c r="S2" t="n">
-        <v>6.210858769524401</v>
+        <v>5.708855147671338</v>
       </c>
       <c r="T2" t="n">
-        <v>239.7067168422345</v>
+        <v>1267.237598646485</v>
       </c>
       <c r="U2" t="n">
-        <v>37.60276022547347</v>
+        <v>329.407827374737</v>
       </c>
       <c r="V2" t="n">
-        <v>788.9950312152213</v>
+        <v>3779.063988285342</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -33711,71 +33711,71 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Memory / Storage</t>
+          <t>Servers / Racks / ODM</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>4271.256202037751</v>
+        <v>1466.271823826204</v>
       </c>
       <c r="D3" t="n">
-        <v>355.9380168364792</v>
+        <v>91.64198898913776</v>
       </c>
       <c r="E3" t="n">
-        <v>189.915904665731</v>
+        <v>41.2571356046875</v>
       </c>
       <c r="F3" t="n">
-        <v>81.25</v>
+        <v>79.0625</v>
       </c>
       <c r="G3" t="n">
         <v>85</v>
       </c>
       <c r="H3" t="n">
-        <v>85.60046460478623</v>
+        <v>87.52355473221772</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.75</v>
       </c>
       <c r="K3" t="n">
-        <v>1.602245691988171</v>
+        <v>0.4477617854958976</v>
       </c>
       <c r="L3" t="n">
-        <v>1.274555143485964</v>
+        <v>0.267858358077966</v>
       </c>
       <c r="M3" t="n">
-        <v>1.657084317962226</v>
+        <v>0.7792086064668478</v>
       </c>
       <c r="N3" t="n">
-        <v>8.347910855834566</v>
+        <v>0.7203904909804837</v>
       </c>
       <c r="O3" t="n">
-        <v>5.774677258129941</v>
+        <v>0.5735245641940394</v>
       </c>
       <c r="P3" t="n">
-        <v>6.948392261723487</v>
+        <v>1.034767045792789</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.783538007081454</v>
+        <v>7.498750070116442</v>
       </c>
       <c r="R3" t="n">
-        <v>5.023982555767589</v>
+        <v>4.612258321930638</v>
       </c>
       <c r="S3" t="n">
-        <v>8.428386373806195</v>
+        <v>6.253260787333068</v>
       </c>
       <c r="T3" t="n">
-        <v>294.7386408474162</v>
+        <v>239.7350823405691</v>
       </c>
       <c r="U3" t="n">
-        <v>48.13915348572864</v>
+        <v>37.60276566695939</v>
       </c>
       <c r="V3" t="n">
-        <v>367.8012259170962</v>
+        <v>789.0311449124525</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -33786,300 +33786,300 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Other / Indirect AI Infrastructure</t>
+          <t>Memory / Storage</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>48.779045888</v>
+        <v>4271.256202037751</v>
       </c>
       <c r="D4" t="n">
-        <v>24.389522944</v>
+        <v>355.9380168364792</v>
       </c>
       <c r="E4" t="n">
-        <v>24.389522944</v>
+        <v>189.915904665731</v>
       </c>
       <c r="F4" t="n">
-        <v>47.5</v>
+        <v>81.25</v>
       </c>
       <c r="G4" t="n">
-        <v>47.5</v>
+        <v>85</v>
       </c>
       <c r="H4" t="n">
-        <v>85.12086291342263</v>
+        <v>85.60046460478623</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1932980067233143</v>
+        <v>1.602245668420061</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1932980067233143</v>
+        <v>1.274555143485964</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8105309048542471</v>
+        <v>1.657084249091988</v>
       </c>
       <c r="N4" t="n">
-        <v>0.053569165996873</v>
+        <v>8.347910891766658</v>
       </c>
       <c r="O4" t="n">
-        <v>0.053569165996873</v>
+        <v>5.774677258129941</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8458512288189604</v>
+        <v>6.948392333407767</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4505497549368007</v>
+        <v>6.783537993797509</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4505497549368007</v>
+        <v>5.023982664580855</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4505497549368007</v>
+        <v>8.428386109925762</v>
       </c>
       <c r="T4" t="n">
-        <v>11.17097236343311</v>
+        <v>294.7386212536611</v>
       </c>
       <c r="U4" t="n">
-        <v>11.17097236343311</v>
+        <v>48.13915348572864</v>
       </c>
       <c r="V4" t="n">
-        <v>21.23282478544479</v>
+        <v>367.8012066259373</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Moderate breadth</t>
+          <t>Broad strong momentum</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Advanced Packaging / Substrates</t>
+          <t>Other / Indirect AI Infrastructure</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>194.2809598471676</v>
+        <v>48.779045888</v>
       </c>
       <c r="D5" t="n">
-        <v>27.75442283530966</v>
+        <v>24.389522944</v>
       </c>
       <c r="E5" t="n">
-        <v>16.101797888</v>
+        <v>24.389522944</v>
       </c>
       <c r="F5" t="n">
-        <v>82.85714285714286</v>
+        <v>47.5</v>
       </c>
       <c r="G5" t="n">
-        <v>85</v>
+        <v>47.5</v>
       </c>
       <c r="H5" t="n">
-        <v>84.10456322470495</v>
+        <v>85.12086291342263</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.5</v>
       </c>
       <c r="K5" t="n">
-        <v>1.963266185886106</v>
+        <v>0.215370363884707</v>
       </c>
       <c r="L5" t="n">
-        <v>1.431065528571705</v>
+        <v>0.215370363884707</v>
       </c>
       <c r="M5" t="n">
-        <v>1.723770843281814</v>
+        <v>0.8130648826522314</v>
       </c>
       <c r="N5" t="n">
-        <v>4.150311846939005</v>
+        <v>0.06636058833679781</v>
       </c>
       <c r="O5" t="n">
-        <v>4.617775498128106</v>
+        <v>0.06636058833679781</v>
       </c>
       <c r="P5" t="n">
-        <v>3.811506274878449</v>
+        <v>0.8473197253631675</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.040573666032382</v>
+        <v>0.4505497549368007</v>
       </c>
       <c r="R5" t="n">
-        <v>4.640708439362538</v>
+        <v>0.4505497549368007</v>
       </c>
       <c r="S5" t="n">
-        <v>5.576936259372254</v>
+        <v>0.4505497549368007</v>
       </c>
       <c r="T5" t="n">
-        <v>32.06051724719575</v>
+        <v>11.2067525377482</v>
       </c>
       <c r="U5" t="n">
-        <v>24.09694141749926</v>
+        <v>11.2067525377482</v>
       </c>
       <c r="V5" t="n">
-        <v>44.97313222150245</v>
+        <v>21.2369233903003</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Broad strong momentum</t>
+          <t>Moderate breadth</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Semiconductor Manufacturing</t>
+          <t>Advanced Packaging / Substrates</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>4112.922077986114</v>
+        <v>194.2809598471676</v>
       </c>
       <c r="D6" t="n">
-        <v>274.1948051990742</v>
+        <v>27.75442283530966</v>
       </c>
       <c r="E6" t="n">
-        <v>54.777233408</v>
+        <v>16.101797888</v>
       </c>
       <c r="F6" t="n">
-        <v>71.33333333333333</v>
+        <v>82.85714285714286</v>
       </c>
       <c r="G6" t="n">
         <v>85</v>
       </c>
       <c r="H6" t="n">
-        <v>83.13167051535106</v>
+        <v>84.10456322470495</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5474838325229776</v>
+        <v>1.920583311230531</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5151062952554408</v>
+        <v>1.431065528571705</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4531916550797351</v>
+        <v>1.712991870054273</v>
       </c>
       <c r="N6" t="n">
-        <v>1.250128258003781</v>
+        <v>4.099780075570151</v>
       </c>
       <c r="O6" t="n">
-        <v>1.34330374559653</v>
+        <v>4.617775498128106</v>
       </c>
       <c r="P6" t="n">
-        <v>1.077737494148795</v>
+        <v>3.798745156966475</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.528836120823275</v>
+        <v>5.001602251931318</v>
       </c>
       <c r="R6" t="n">
-        <v>3.028155434243149</v>
+        <v>4.640708027532765</v>
       </c>
       <c r="S6" t="n">
-        <v>3.175820624723287</v>
+        <v>5.567094318539129</v>
       </c>
       <c r="T6" t="n">
-        <v>894.3907686866804</v>
+        <v>31.93851193526138</v>
       </c>
       <c r="U6" t="n">
-        <v>40.665041754344</v>
+        <v>24.09694363070544</v>
       </c>
       <c r="V6" t="n">
-        <v>1276.375418386961</v>
+        <v>44.94232239063506</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Moderate breadth</t>
+          <t>Broad strong momentum</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Accelerators / Full-Stack Compute</t>
+          <t>Semiconductor Manufacturing</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>11878.21006143622</v>
+        <v>4112.922077986114</v>
       </c>
       <c r="D7" t="n">
-        <v>1484.776257679527</v>
+        <v>274.1948051990742</v>
       </c>
       <c r="E7" t="n">
-        <v>371.6866048</v>
+        <v>54.777233408</v>
       </c>
       <c r="F7" t="n">
-        <v>82.5</v>
+        <v>71.33333333333333</v>
       </c>
       <c r="G7" t="n">
         <v>85</v>
       </c>
       <c r="H7" t="n">
-        <v>78.55156144648795</v>
+        <v>83.13167051535106</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J7" t="n">
-        <v>0.75</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6126340627861102</v>
+        <v>0.5457677812156605</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3260329585128673</v>
+        <v>0.5151062952554408</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3191945629937309</v>
+        <v>0.4528925572439077</v>
       </c>
       <c r="N7" t="n">
-        <v>1.177608478440138</v>
+        <v>1.246647619195669</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5946300914842613</v>
+        <v>1.34330374559653</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6336481620287744</v>
+        <v>1.077130807853535</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.918349265944163</v>
+        <v>3.525433901401104</v>
       </c>
       <c r="R7" t="n">
-        <v>1.484363175097864</v>
+        <v>3.028155842581456</v>
       </c>
       <c r="S7" t="n">
-        <v>5.500421484286665</v>
+        <v>3.175263672039848</v>
       </c>
       <c r="T7" t="n">
-        <v>1260.847835139523</v>
+        <v>894.0688930382296</v>
       </c>
       <c r="U7" t="n">
-        <v>329.4078710909667</v>
+        <v>40.66503479388871</v>
       </c>
       <c r="V7" t="n">
-        <v>3757.503782086941</v>
+        <v>1276.319597108493</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Broad strong momentum</t>
+          <t>Moderate breadth</t>
         </is>
       </c>
     </row>
@@ -34102,55 +34102,55 @@
         <v>48.89527363064734</v>
       </c>
       <c r="F8" t="n">
-        <v>70.45454545454545</v>
+        <v>71.59090909090909</v>
       </c>
       <c r="G8" t="n">
         <v>67.5</v>
       </c>
       <c r="H8" t="n">
-        <v>71.31987475500237</v>
+        <v>73.91738318964116</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3478260869565217</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4430367177769315</v>
+        <v>0.441930643522138</v>
       </c>
       <c r="L8" t="n">
         <v>0.4286093015439668</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4378432604190055</v>
+        <v>0.4372566230228992</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8099565394249847</v>
+        <v>0.8024857816401522</v>
       </c>
       <c r="O8" t="n">
         <v>0.6152984947846457</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7046816080483844</v>
+        <v>0.7015317640220287</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.023189765220866</v>
+        <v>3.020601858325296</v>
       </c>
       <c r="R8" t="n">
-        <v>1.621022198428131</v>
+        <v>1.621022331398148</v>
       </c>
       <c r="S8" t="n">
-        <v>2.73278723439393</v>
+        <v>2.733468032882954</v>
       </c>
       <c r="T8" t="n">
-        <v>175.4800816644124</v>
+        <v>175.483119030043</v>
       </c>
       <c r="U8" t="n">
-        <v>31.79663435972432</v>
+        <v>31.79663171494852</v>
       </c>
       <c r="V8" t="n">
-        <v>325.0635616774562</v>
+        <v>325.0759795011403</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -34192,40 +34192,40 @@
         <v>0.25</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1290257251924645</v>
+        <v>0.1284213412566834</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09354084405216989</v>
+        <v>0.1021183823549083</v>
       </c>
       <c r="M9" t="n">
-        <v>0.07673759220206129</v>
+        <v>0.08547144362916871</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1876076582047221</v>
+        <v>0.1789818570265489</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1049759820611872</v>
+        <v>0.1185465339292291</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0959914743671765</v>
+        <v>0.108309277644887</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.378391390256</v>
+        <v>1.366085763190373</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25806066833744</v>
+        <v>1.277349132726258</v>
       </c>
       <c r="S9" t="n">
-        <v>1.133252887299686</v>
+        <v>1.15075188754216</v>
       </c>
       <c r="T9" t="n">
-        <v>85.98222261652262</v>
+        <v>85.74445387687408</v>
       </c>
       <c r="U9" t="n">
-        <v>77.29792598613575</v>
+        <v>76.60937552327374</v>
       </c>
       <c r="V9" t="n">
-        <v>63.48751793148187</v>
+        <v>63.66084454417735</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -34267,40 +34267,40 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5044303907177258</v>
+        <v>0.5125036543620834</v>
       </c>
       <c r="L10" t="n">
         <v>0.488269739420115</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3011227740979289</v>
+        <v>0.3044301841754123</v>
       </c>
       <c r="N10" t="n">
-        <v>1.785100894121718</v>
+        <v>1.81774221309383</v>
       </c>
       <c r="O10" t="n">
         <v>1.120165670820509</v>
       </c>
       <c r="P10" t="n">
-        <v>1.136385110591486</v>
+        <v>1.149831036475088</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.085151921983243</v>
+        <v>7.130050699253052</v>
       </c>
       <c r="R10" t="n">
-        <v>3.242679104278302</v>
+        <v>3.242678167820314</v>
       </c>
       <c r="S10" t="n">
-        <v>8.749358346260184</v>
+        <v>8.765679724625725</v>
       </c>
       <c r="T10" t="n">
-        <v>176.3723246826773</v>
+        <v>176.5578566713326</v>
       </c>
       <c r="U10" t="n">
-        <v>25.5578999370001</v>
+        <v>25.32103721003304</v>
       </c>
       <c r="V10" t="n">
-        <v>299.8130177554729</v>
+        <v>299.8868685814553</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -34318,10 +34318,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>2715.3402112</v>
+        <v>2715.387145728</v>
       </c>
       <c r="D11" t="n">
-        <v>271.53402112</v>
+        <v>271.5387145728</v>
       </c>
       <c r="E11" t="n">
         <v>90.39096217599999</v>
@@ -34333,7 +34333,7 @@
         <v>72.5</v>
       </c>
       <c r="H11" t="n">
-        <v>62.22705840236776</v>
+        <v>62.2264149455341</v>
       </c>
       <c r="I11" t="n">
         <v>5</v>
@@ -34342,40 +34342,40 @@
         <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1533852483364541</v>
+        <v>0.1520332144732233</v>
       </c>
       <c r="L11" t="n">
         <v>0.04274047897959321</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2000585340861576</v>
+        <v>0.1995891583245737</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1501004192024316</v>
+        <v>0.1501648083617067</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2574162636115355</v>
+        <v>0.2577381384648536</v>
       </c>
       <c r="P11" t="n">
-        <v>0.33737162269287</v>
+        <v>0.3373820616227983</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.497608230531317</v>
+        <v>1.497058332400518</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5189845812737033</v>
+        <v>0.5162363065792499</v>
       </c>
       <c r="S11" t="n">
-        <v>5.991192590551485</v>
+        <v>5.99088936397284</v>
       </c>
       <c r="T11" t="n">
-        <v>54.7604134897183</v>
+        <v>54.7592683336954</v>
       </c>
       <c r="U11" t="n">
         <v>6.936600708597043</v>
       </c>
       <c r="V11" t="n">
-        <v>239.8704426770545</v>
+        <v>239.8658844667521</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -34417,40 +34417,40 @@
         <v>0.3157894736842105</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.009887639755045906</v>
+        <v>-0.008327871823843975</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.008461065467503359</v>
+        <v>-0.008460973646771563</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1657029404619991</v>
+        <v>0.1666424686977066</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1072829803628091</v>
+        <v>0.1141745938510769</v>
       </c>
       <c r="O12" t="n">
         <v>0.1258561815581098</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2745285121798265</v>
+        <v>0.279534770485967</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.699837437190736</v>
+        <v>2.704294468178777</v>
       </c>
       <c r="R12" t="n">
-        <v>2.032291702336249</v>
+        <v>2.032291457833407</v>
       </c>
       <c r="S12" t="n">
-        <v>2.271788650309472</v>
+        <v>2.291604455874041</v>
       </c>
       <c r="T12" t="n">
-        <v>79.08841027200307</v>
+        <v>79.12132252546373</v>
       </c>
       <c r="U12" t="n">
-        <v>13.41042040596664</v>
+        <v>13.41041555738928</v>
       </c>
       <c r="V12" t="n">
-        <v>113.5370162486442</v>
+        <v>113.5444540492378</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -34501,31 +34501,31 @@
         <v>-0.1781106727625517</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2655687637174556</v>
+        <v>0.2655687513793566</v>
       </c>
       <c r="O13" t="n">
         <v>0.1378028919253964</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2442377959912816</v>
+        <v>0.2442377654402574</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5697134782637123</v>
+        <v>0.5697135198263088</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4722083326286571</v>
+        <v>0.4722084779426143</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7417810745391279</v>
+        <v>0.7417811904702009</v>
       </c>
       <c r="T13" t="n">
-        <v>17.21367169409374</v>
+        <v>17.21367674703901</v>
       </c>
       <c r="U13" t="n">
-        <v>3.248115267803067</v>
+        <v>3.248116524429076</v>
       </c>
       <c r="V13" t="n">
-        <v>3.833061366548706</v>
+        <v>3.833062698660045</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -34567,13 +34567,13 @@
         <v>0.25</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3401737093220341</v>
+        <v>0.3401737132134774</v>
       </c>
       <c r="L14" t="n">
         <v>-0.08853259788979156</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.06605000086786561</v>
+        <v>-0.06604999958049385</v>
       </c>
       <c r="N14" t="n">
         <v>0.443716607946512</v>
@@ -34585,22 +34585,22 @@
         <v>0.131052900287204</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.402572223267801</v>
+        <v>0.4025720951681139</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3610109730264375</v>
+        <v>0.3610108403306583</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7884750515542421</v>
+        <v>0.7884749704214444</v>
       </c>
       <c r="T14" t="n">
-        <v>990.8848836678721</v>
+        <v>990.8849835516561</v>
       </c>
       <c r="U14" t="n">
         <v>11.54693999384689</v>
       </c>
       <c r="V14" t="n">
-        <v>2147.82918552512</v>
+        <v>2147.829651955649</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>

--- a/company_radar_output.xlsx
+++ b/company_radar_output.xlsx
@@ -1262,13 +1262,13 @@
         <v>1.425382315558814</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.292953246071055</v>
+        <v>2.292953462776987</v>
       </c>
       <c r="AX4" t="n">
         <v>1.498429333383664</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.949959543700303</v>
+        <v>2.949958296475354</v>
       </c>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
@@ -1650,13 +1650,13 @@
         <v>-0.121964415098069</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.6752683816483742</v>
+        <v>0.6752680130466313</v>
       </c>
       <c r="AX6" t="n">
         <v>-0.0130047528646493</v>
       </c>
       <c r="AY6" t="n">
-        <v>7858.912342614089</v>
+        <v>7858.914323521892</v>
       </c>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
@@ -1789,7 +1789,7 @@
         <v>38218</v>
       </c>
       <c r="AD7" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AE7" t="n">
         <v>356.1300048828125</v>
@@ -1798,16 +1798,16 @@
         <v>358.6835296630859</v>
       </c>
       <c r="AG7" t="n">
-        <v>325.976455078125</v>
+        <v>325.9764558410645</v>
       </c>
       <c r="AH7" t="n">
         <v>-0.007119158168963025</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.09250223240037614</v>
+        <v>0.09250222984340284</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.1003356962610142</v>
+        <v>0.1003356936857072</v>
       </c>
       <c r="AK7" t="n">
         <v>402.3796691894531</v>
@@ -1849,10 +1849,10 @@
         <v>1.680552953854702</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1315042133005269</v>
+        <v>0.1315043230124664</v>
       </c>
       <c r="AY7" t="n">
-        <v>142.0849825942612</v>
+        <v>142.0849551817039</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
@@ -2044,7 +2044,7 @@
         <v>-0.2283522824018764</v>
       </c>
       <c r="AY8" t="n">
-        <v>674.6804404612965</v>
+        <v>674.6805549905486</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
@@ -2230,13 +2230,13 @@
         <v>0.02273680762519348</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.3225503192947156</v>
+        <v>-0.3225502620117725</v>
       </c>
       <c r="AX9" t="n">
         <v>-0.2078288316641607</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.3836162612959486</v>
+        <v>0.3836165002435039</v>
       </c>
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="n">
@@ -2570,16 +2570,16 @@
         <v>601.9942590332031</v>
       </c>
       <c r="AG11" t="n">
-        <v>633.5842388916016</v>
+        <v>633.584241027832</v>
       </c>
       <c r="AH11" t="n">
         <v>-0.07522370252047406</v>
       </c>
       <c r="AI11" t="n">
-        <v>-0.1213322747002511</v>
+        <v>-0.1213322776628197</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0.04985916302725946</v>
+        <v>-0.0498591662308111</v>
       </c>
       <c r="AK11" t="n">
         <v>787.419189453125</v>
@@ -2621,7 +2621,7 @@
         <v>0.507809753668319</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.1425361577604483</v>
+        <v>-0.1425360771516042</v>
       </c>
       <c r="AY11" t="n">
         <v>13.69000198801654</v>
@@ -2766,16 +2766,16 @@
         <v>164.4866416931152</v>
       </c>
       <c r="AG12" t="n">
-        <v>181.9404849624634</v>
+        <v>181.9404841995239</v>
       </c>
       <c r="AH12" t="n">
         <v>-0.2104526314088925</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.2861951800118522</v>
+        <v>-0.2861951770186213</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0.09593160792634514</v>
+        <v>-0.09593160413527335</v>
       </c>
       <c r="AK12" t="n">
         <v>324.6299743652344</v>
@@ -2811,16 +2811,16 @@
         <v>-0.2053896183131703</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0.4824045169528034</v>
+        <v>-0.4824044854758837</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.5812138016878226</v>
+        <v>0.5812139485677612</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.3300155649784914</v>
+        <v>-0.3300155122384208</v>
       </c>
       <c r="AY12" t="n">
-        <v>2584.115062746769</v>
+        <v>2584.114871051665</v>
       </c>
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="n">
@@ -4132,28 +4132,28 @@
         <v>395.0326873779297</v>
       </c>
       <c r="AG19" t="n">
-        <v>364.8947799682617</v>
+        <v>364.8947801208496</v>
       </c>
       <c r="AH19" t="n">
         <v>-0.01456256351041951</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.06682808346328262</v>
+        <v>0.06682808301716769</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.08259341888170968</v>
+        <v>0.08259341842900225</v>
       </c>
       <c r="AK19" t="n">
         <v>480.8090515136719</v>
       </c>
       <c r="AL19" t="n">
-        <v>286.5404968261719</v>
+        <v>286.54052734375</v>
       </c>
       <c r="AM19" t="n">
         <v>-0.1903646623253563</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.3585514197508051</v>
+        <v>0.3585512750602811</v>
       </c>
       <c r="AO19" t="n">
         <v>52.42782072288501</v>
@@ -4174,19 +4174,19 @@
         <v>-0.07449649339109377</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.1793360030339692</v>
+        <v>0.1793358939996921</v>
       </c>
       <c r="AV19" t="n">
         <v>0.3351456710249647</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.866962563961266</v>
+        <v>7.866961793505519</v>
       </c>
       <c r="AX19" t="n">
         <v>0.1239687532078804</v>
       </c>
       <c r="AY19" t="n">
-        <v>341.7994300668201</v>
+        <v>341.799250139145</v>
       </c>
       <c r="AZ19" t="inlineStr"/>
       <c r="BA19" t="n">
@@ -4906,16 +4906,16 @@
         <v>260.4377987670898</v>
       </c>
       <c r="AG23" t="n">
-        <v>268.2162158966065</v>
+        <v>268.2162174224853</v>
       </c>
       <c r="AH23" t="n">
         <v>-0.1412537083509329</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.1661578210368225</v>
+        <v>-0.1661578257805407</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-0.02900054757507697</v>
+        <v>-0.02900055309908123</v>
       </c>
       <c r="AK23" t="n">
         <v>329.2300109863281</v>
@@ -4954,13 +4954,13 @@
         <v>-0.09393540953062707</v>
       </c>
       <c r="AW23" t="n">
-        <v>0.9925963115057752</v>
+        <v>0.9925967178379105</v>
       </c>
       <c r="AX23" t="n">
-        <v>-0.2227080984030254</v>
+        <v>-0.2227081808451954</v>
       </c>
       <c r="AY23" t="n">
-        <v>153.803032175818</v>
+        <v>153.8030194026066</v>
       </c>
       <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="n">
@@ -5102,28 +5102,28 @@
         <v>309.4994000244141</v>
       </c>
       <c r="AG24" t="n">
-        <v>277.661273727417</v>
+        <v>277.6612744903564</v>
       </c>
       <c r="AH24" t="n">
         <v>-0.001904353812182458</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.1125426297848422</v>
+        <v>0.1125426267278704</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.1146653469876857</v>
+        <v>0.1146653439248813</v>
       </c>
       <c r="AK24" t="n">
         <v>340.0799865722656</v>
       </c>
       <c r="AL24" t="n">
-        <v>201.5802917480469</v>
+        <v>201.5803070068359</v>
       </c>
       <c r="AM24" t="n">
         <v>-0.09165485809478169</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.5324414950654641</v>
+        <v>0.5324413790660301</v>
       </c>
       <c r="AO24" t="n">
         <v>45.07620275273701</v>
@@ -5144,19 +5144,19 @@
         <v>0.1037145936977779</v>
       </c>
       <c r="AU24" t="n">
-        <v>0.192708197707212</v>
+        <v>0.1927080571715805</v>
       </c>
       <c r="AV24" t="n">
-        <v>0.4941250091423681</v>
+        <v>0.4941248988712101</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.127064985682962</v>
+        <v>1.127065209168621</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.1419650096508489</v>
+        <v>0.141964880818882</v>
       </c>
       <c r="AY24" t="n">
-        <v>3144.497974831282</v>
+        <v>3144.497736194748</v>
       </c>
       <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="n">
@@ -5880,16 +5880,16 @@
         <v>206.1238037109375</v>
       </c>
       <c r="AG28" t="n">
-        <v>192.9279959106445</v>
+        <v>192.9279960632324</v>
       </c>
       <c r="AH28" t="n">
         <v>-0.02607075754566213</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.04054364454694404</v>
+        <v>0.04054364372397212</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0.06839757878584218</v>
+        <v>0.06839757794084034</v>
       </c>
       <c r="AK28" t="n">
         <v>235.465576171875</v>
@@ -5928,13 +5928,13 @@
         <v>0.130136513848913</v>
       </c>
       <c r="AW28" t="n">
-        <v>9.440778577454203</v>
+        <v>9.440776506024456</v>
       </c>
       <c r="AX28" t="n">
         <v>0.06430947893672534</v>
       </c>
       <c r="AY28" t="n">
-        <v>5343.914068437142</v>
+        <v>5343.913538302751</v>
       </c>
       <c r="AZ28" t="inlineStr"/>
       <c r="BA28" t="n">
@@ -6322,7 +6322,7 @@
         <v>1.290502653674998</v>
       </c>
       <c r="AY30" t="n">
-        <v>495.9702846675321</v>
+        <v>495.9705294756966</v>
       </c>
       <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="n">
@@ -6464,16 +6464,16 @@
         <v>198.336413269043</v>
       </c>
       <c r="AG31" t="n">
-        <v>167.8673146057129</v>
+        <v>167.8673149108887</v>
       </c>
       <c r="AH31" t="n">
         <v>-0.2557594534589124</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.1206745580159053</v>
+        <v>-0.1206745596144823</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.1815070356900386</v>
+        <v>0.1815070335421081</v>
       </c>
       <c r="AK31" t="n">
         <v>250.0962829589844</v>
@@ -6509,10 +6509,10 @@
         <v>-0.01638349310958864</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.02699095188112954</v>
+        <v>0.02699084285327258</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.1458900724744805</v>
+        <v>0.1458899367400111</v>
       </c>
       <c r="AX31" t="n">
         <v>-0.1380135308553794</v>
@@ -6704,7 +6704,7 @@
         <v>6.619047536665643</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.963789623943382</v>
+        <v>2.963790069889175</v>
       </c>
       <c r="AX32" t="n">
         <v>3.09756088483766</v>
@@ -6902,7 +6902,7 @@
         <v>3.077481172125339</v>
       </c>
       <c r="AY33" t="n">
-        <v>26.78766773074407</v>
+        <v>26.78766541142491</v>
       </c>
       <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="n">
@@ -7085,16 +7085,16 @@
         <v>1.085032302555191</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.317335419149967</v>
+        <v>4.317335833735327</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.246675078808876</v>
+        <v>5.246676223145303</v>
       </c>
       <c r="AX34" t="n">
         <v>1.33029597298324</v>
       </c>
       <c r="AY34" t="n">
-        <v>23.0566558118161</v>
+        <v>23.05664944741603</v>
       </c>
       <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
@@ -7284,13 +7284,13 @@
         <v>2.739346612369455</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.501932435366861</v>
+        <v>4.501932024947141</v>
       </c>
       <c r="AX35" t="n">
         <v>1.106986491396864</v>
       </c>
       <c r="AY35" t="n">
-        <v>33.24452013652432</v>
+        <v>33.24451218684118</v>
       </c>
       <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="n">
@@ -7476,13 +7476,13 @@
         <v>4.929410163343555</v>
       </c>
       <c r="AW36" t="n">
-        <v>7.707276162789471</v>
+        <v>7.707275427801989</v>
       </c>
       <c r="AX36" t="n">
         <v>2.600965855398865</v>
       </c>
       <c r="AY36" t="n">
-        <v>107.1121394340284</v>
+        <v>107.1121252704099</v>
       </c>
       <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="n">
@@ -7624,28 +7624,28 @@
         <v>71.14596229553223</v>
       </c>
       <c r="AG37" t="n">
-        <v>53.6437762260437</v>
+        <v>53.6437762928009</v>
       </c>
       <c r="AH37" t="n">
         <v>-0.2990466735873152</v>
       </c>
       <c r="AI37" t="n">
-        <v>-0.07034883745426534</v>
+        <v>-0.07034883861117336</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.3262668533202802</v>
+        <v>0.3262668516698022</v>
       </c>
       <c r="AK37" t="n">
         <v>93.55000305175781</v>
       </c>
       <c r="AL37" t="n">
-        <v>21.56404685974121</v>
+        <v>21.56404495239258</v>
       </c>
       <c r="AM37" t="n">
         <v>-0.4669161164613377</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.312645639116519</v>
+        <v>1.312645843670975</v>
       </c>
       <c r="AO37" t="n">
         <v>32.98297243129194</v>
@@ -7669,10 +7669,10 @@
         <v>0.03500473478813237</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.229612106001188</v>
+        <v>1.229611915871772</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.326539100016942</v>
+        <v>1.326538478958351</v>
       </c>
       <c r="AX37" t="n">
         <v>0.1654656113712303</v>
@@ -7864,13 +7864,13 @@
         <v>0.173594770828158</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.509374091384069</v>
+        <v>1.509374261181225</v>
       </c>
       <c r="AX38" t="n">
         <v>-0.02209730069078586</v>
       </c>
       <c r="AY38" t="n">
-        <v>2.880955460645203</v>
+        <v>2.880955054504204</v>
       </c>
       <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="n">
@@ -8056,13 +8056,13 @@
         <v>0.2234202179624647</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.8400645199788626</v>
+        <v>0.8400642369866198</v>
       </c>
       <c r="AX39" t="n">
         <v>0.08452472202541994</v>
       </c>
       <c r="AY39" t="n">
-        <v>3.464035754325014</v>
+        <v>3.464035337931657</v>
       </c>
       <c r="AZ39" t="inlineStr"/>
       <c r="BA39" t="n">
@@ -8200,16 +8200,16 @@
         <v>2.213439564704895</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.206731199026108</v>
+        <v>2.206731196641922</v>
       </c>
       <c r="AH40" t="n">
         <v>0.007481773901877098</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.01054447413334625</v>
+        <v>0.01054447522515378</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.003039955968243024</v>
+        <v>0.003039957051942599</v>
       </c>
       <c r="AK40" t="n">
         <v>2.330364942550659</v>
@@ -8242,7 +8242,7 @@
         <v>-0.03090378682510453</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.0268390240410783</v>
+        <v>0.02683891131097349</v>
       </c>
       <c r="AV40" t="n">
         <v>0.004803847116977344</v>
@@ -8251,10 +8251,10 @@
         <v>0.09699055572007875</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.04517532249051093</v>
+        <v>0.0451754392826389</v>
       </c>
       <c r="AY40" t="n">
-        <v>3.096293329578627</v>
+        <v>3.096293778073395</v>
       </c>
       <c r="AZ40" t="inlineStr"/>
       <c r="BA40" t="n">
@@ -8396,16 +8396,16 @@
         <v>1054.275805664063</v>
       </c>
       <c r="AG41" t="n">
-        <v>925.3497473144531</v>
+        <v>925.3497485351562</v>
       </c>
       <c r="AH41" t="n">
         <v>-0.03319413779503799</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.1015078701377787</v>
+        <v>0.1015078686846913</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.1393268423358609</v>
+        <v>0.1393268408328834</v>
       </c>
       <c r="AK41" t="n">
         <v>1115.93994140625</v>
@@ -8444,13 +8444,13 @@
         <v>0.3276896854410978</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.3557185947026755</v>
+        <v>0.3557184846436618</v>
       </c>
       <c r="AX41" t="n">
         <v>0.347848117285231</v>
       </c>
       <c r="AY41" t="n">
-        <v>2.299731297259841</v>
+        <v>2.299732927246015</v>
       </c>
       <c r="AZ41" t="inlineStr"/>
       <c r="BA41" t="n">
@@ -8592,28 +8592,28 @@
         <v>125.0171809387207</v>
       </c>
       <c r="AG42" t="n">
-        <v>105.8638522338867</v>
+        <v>105.8638520431519</v>
       </c>
       <c r="AH42" t="n">
         <v>-0.02157448459199018</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.1554463314312489</v>
+        <v>0.1554463335130161</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.1809241615591148</v>
+        <v>0.1809241636867855</v>
       </c>
       <c r="AK42" t="n">
         <v>133.0599975585938</v>
       </c>
       <c r="AL42" t="n">
-        <v>77.69111633300781</v>
+        <v>77.69110870361328</v>
       </c>
       <c r="AM42" t="n">
         <v>-0.08071545213308839</v>
       </c>
       <c r="AN42" t="n">
-        <v>0.5744399806346379</v>
+        <v>0.574440135247231</v>
       </c>
       <c r="AO42" t="n">
         <v>49.90206989048085</v>
@@ -8640,13 +8640,13 @@
         <v>0.2991760022475245</v>
       </c>
       <c r="AW42" t="n">
-        <v>2.408296802591991</v>
+        <v>2.408296440317817</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.4915947627227999</v>
+        <v>0.4915946239532238</v>
       </c>
       <c r="AY42" t="n">
-        <v>105.1650586280289</v>
+        <v>105.1650476436428</v>
       </c>
       <c r="AZ42" t="inlineStr"/>
       <c r="BA42" t="n">
@@ -8836,7 +8836,7 @@
         <v>0.09931096239704895</v>
       </c>
       <c r="AW43" t="n">
-        <v>0.4540762776316165</v>
+        <v>0.4540761064973586</v>
       </c>
       <c r="AX43" t="n">
         <v>0.2324652833024374</v>
@@ -9226,7 +9226,7 @@
         <v>-0.02831951975604874</v>
       </c>
       <c r="AY45" t="n">
-        <v>0.6569176745819545</v>
+        <v>0.6569175371439155</v>
       </c>
       <c r="AZ45" t="inlineStr"/>
       <c r="BA45" t="n">
@@ -9962,13 +9962,13 @@
         <v>0.2356695216260396</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.1512799286749307</v>
+        <v>0.1512797824793917</v>
       </c>
       <c r="AX49" t="n">
         <v>0.1918826954736919</v>
       </c>
       <c r="AY49" t="n">
-        <v>186.1753407520885</v>
+        <v>186.1753105623372</v>
       </c>
       <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
@@ -10110,28 +10110,28 @@
         <v>14.53933664321899</v>
       </c>
       <c r="AG50" t="n">
-        <v>14.16336886882782</v>
+        <v>14.16336890220642</v>
       </c>
       <c r="AH50" t="n">
         <v>0.009674695992570648</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.03647659261950142</v>
+        <v>0.03647659017685245</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.02654508103779207</v>
+        <v>0.02654507861854838</v>
       </c>
       <c r="AK50" t="n">
         <v>16.86722755432129</v>
       </c>
       <c r="AL50" t="n">
-        <v>11.91677188873291</v>
+        <v>11.91677284240723</v>
       </c>
       <c r="AM50" t="n">
         <v>-0.1296731927106274</v>
       </c>
       <c r="AN50" t="n">
-        <v>0.2318772602381902</v>
+        <v>0.231877161653639</v>
       </c>
       <c r="AO50" t="n">
         <v>67.39986925408405</v>
@@ -10152,19 +10152,19 @@
         <v>0.04034123898982434</v>
       </c>
       <c r="AU50" t="n">
-        <v>0.02656987417344903</v>
+        <v>0.02656994263568535</v>
       </c>
       <c r="AV50" t="n">
         <v>0.1878206432109371</v>
       </c>
       <c r="AW50" t="n">
-        <v>-0.2468257816586366</v>
+        <v>-0.2468257079539758</v>
       </c>
       <c r="AX50" t="n">
         <v>0.02681002738810045</v>
       </c>
       <c r="AY50" t="n">
-        <v>6.444545032524341</v>
+        <v>6.444546382673317</v>
       </c>
       <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
@@ -10351,7 +10351,7 @@
         <v>0.05143300328399314</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.06719029246863228</v>
+        <v>0.0671902231942989</v>
       </c>
       <c r="AW51" t="n">
         <v>0.4548789897343903</v>
@@ -10360,7 +10360,7 @@
         <v>0.08643892305339729</v>
       </c>
       <c r="AY51" t="n">
-        <v>168.4221590738922</v>
+        <v>168.4222272746632</v>
       </c>
       <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="n">
@@ -10493,7 +10493,7 @@
         <v>26786</v>
       </c>
       <c r="AD52" t="n">
-        <v>53.2</v>
+        <v>53.3</v>
       </c>
       <c r="AE52" t="n">
         <v>45.81999969482422</v>
@@ -10547,16 +10547,16 @@
         <v>0.04169137243709331</v>
       </c>
       <c r="AV52" t="n">
-        <v>0.05636979808954523</v>
+        <v>0.05636970518501094</v>
       </c>
       <c r="AW52" t="n">
-        <v>0.6511208854501911</v>
+        <v>0.6511206584832114</v>
       </c>
       <c r="AX52" t="n">
         <v>0.06208876619690407</v>
       </c>
       <c r="AY52" t="n">
-        <v>185.8702971319327</v>
+        <v>185.8703652711267</v>
       </c>
       <c r="AZ52" t="inlineStr"/>
       <c r="BA52" t="n">
@@ -10698,16 +10698,16 @@
         <v>112.2212005615234</v>
       </c>
       <c r="AG53" t="n">
-        <v>103.4635041046143</v>
+        <v>103.4635038375854</v>
       </c>
       <c r="AH53" t="n">
         <v>-0.0410011458790166</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.04017357306751412</v>
+        <v>0.04017357575209668</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.08464527209569539</v>
+        <v>0.0846452748950548</v>
       </c>
       <c r="AK53" t="n">
         <v>117.3600006103516</v>
@@ -10746,13 +10746,13 @@
         <v>0.2205512168851422</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.477378286625535</v>
+        <v>1.47737850417187</v>
       </c>
       <c r="AX53" t="n">
         <v>0.1604404122081626</v>
       </c>
       <c r="AY53" t="n">
-        <v>199.2358864767663</v>
+        <v>199.2358642707381</v>
       </c>
       <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
@@ -10909,13 +10909,13 @@
         <v>98.29612731933594</v>
       </c>
       <c r="AL54" t="n">
-        <v>82.73965454101562</v>
+        <v>82.73964691162109</v>
       </c>
       <c r="AM54" t="n">
         <v>-0.03821235389677169</v>
       </c>
       <c r="AN54" t="n">
-        <v>0.1426202035767754</v>
+        <v>0.1426203089373934</v>
       </c>
       <c r="AO54" t="n">
         <v>42.38358554883744</v>
@@ -10936,19 +10936,19 @@
         <v>-0.01434423377058691</v>
       </c>
       <c r="AU54" t="n">
-        <v>0.07570844006243704</v>
+        <v>0.07570834668034787</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.03333907894867405</v>
+        <v>0.03333899277787045</v>
       </c>
       <c r="AW54" t="n">
-        <v>0.7842320646228937</v>
+        <v>0.784232193076762</v>
       </c>
       <c r="AX54" t="n">
         <v>0.1019902981823344</v>
       </c>
       <c r="AY54" t="n">
-        <v>347.6100846756167</v>
+        <v>347.60996974506</v>
       </c>
       <c r="AZ54" t="inlineStr"/>
       <c r="BA54" t="n">
@@ -11090,28 +11090,28 @@
         <v>87.23242263793945</v>
       </c>
       <c r="AG55" t="n">
-        <v>86.8403466796875</v>
+        <v>86.84034675598144</v>
       </c>
       <c r="AH55" t="n">
         <v>-0.00358151773785842</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.0009172175411920058</v>
+        <v>0.0009172166618320876</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.004514905493159027</v>
+        <v>0.004514904610638304</v>
       </c>
       <c r="AK55" t="n">
         <v>97.16828918457031</v>
       </c>
       <c r="AL55" t="n">
-        <v>68.33090209960938</v>
+        <v>68.33090972900391</v>
       </c>
       <c r="AM55" t="n">
         <v>-0.1054695014353753</v>
       </c>
       <c r="AN55" t="n">
-        <v>0.2720452313396606</v>
+        <v>0.2720450893111852</v>
       </c>
       <c r="AO55" t="n">
         <v>41.79775935865091</v>
@@ -11144,7 +11144,7 @@
         <v>0.08925808825504866</v>
       </c>
       <c r="AY55" t="n">
-        <v>249.1268980880915</v>
+        <v>249.1266835764718</v>
       </c>
       <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="n">
@@ -11286,16 +11286,16 @@
         <v>1024.638475341797</v>
       </c>
       <c r="AG56" t="n">
-        <v>835.8096368408203</v>
+        <v>835.8096371459961</v>
       </c>
       <c r="AH56" t="n">
         <v>-0.03352255272572635</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.1848271835802537</v>
+        <v>0.1848271831476425</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.2259232607256227</v>
+        <v>0.2259232602780061</v>
       </c>
       <c r="AK56" t="n">
         <v>1174.859985351562</v>
@@ -11331,7 +11331,7 @@
         <v>0.3648624026084366</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.503185937847715</v>
+        <v>0.5031860771130812</v>
       </c>
       <c r="AW56" t="inlineStr"/>
       <c r="AX56" t="n">
@@ -11530,7 +11530,7 @@
         <v>0.1953036367022631</v>
       </c>
       <c r="AY57" t="n">
-        <v>5.706385984823059</v>
+        <v>5.706385397903489</v>
       </c>
       <c r="AZ57" t="inlineStr"/>
       <c r="BA57" t="n">
@@ -11906,13 +11906,13 @@
         <v>0.1550537943755139</v>
       </c>
       <c r="AW59" t="n">
-        <v>4.034608601613103</v>
+        <v>4.034609161304165</v>
       </c>
       <c r="AX59" t="n">
         <v>-0.1235795516120503</v>
       </c>
       <c r="AY59" t="n">
-        <v>13.4363926674926</v>
+        <v>13.43639381795998</v>
       </c>
       <c r="AZ59" t="inlineStr"/>
       <c r="BA59" t="n">
@@ -12102,13 +12102,13 @@
         <v>-0.1876433547501449</v>
       </c>
       <c r="AW60" t="n">
-        <v>2.777937848044618</v>
+        <v>2.777937442605175</v>
       </c>
       <c r="AX60" t="n">
         <v>-0.186797327402441</v>
       </c>
       <c r="AY60" t="n">
-        <v>17.74478779584323</v>
+        <v>17.74480526274733</v>
       </c>
       <c r="AZ60" t="inlineStr"/>
       <c r="BA60" t="n">
@@ -12438,28 +12438,28 @@
         <v>188.2155999755859</v>
       </c>
       <c r="AG62" t="n">
-        <v>197.0855248260498</v>
+        <v>197.085524520874</v>
       </c>
       <c r="AH62" t="n">
         <v>-0.1036874893997904</v>
       </c>
       <c r="AI62" t="n">
-        <v>-0.1440264469085746</v>
+        <v>-0.144026445583148</v>
       </c>
       <c r="AJ62" t="n">
-        <v>-0.0450054607424496</v>
+        <v>-0.04500545926369459</v>
       </c>
       <c r="AK62" t="n">
         <v>238.1012115478516</v>
       </c>
       <c r="AL62" t="n">
-        <v>148.6679382324219</v>
+        <v>148.6679229736328</v>
       </c>
       <c r="AM62" t="n">
         <v>-0.291477788577576</v>
       </c>
       <c r="AN62" t="n">
-        <v>0.134743637088065</v>
+        <v>0.1347437535544382</v>
       </c>
       <c r="AO62" t="n">
         <v>42.2682259822184</v>
@@ -12483,16 +12483,16 @@
         <v>-0.1765613435907374</v>
       </c>
       <c r="AV62" t="n">
-        <v>0.1165943272250134</v>
+        <v>0.1165944399956087</v>
       </c>
       <c r="AW62" t="n">
-        <v>2.101056914930357</v>
+        <v>2.101056480025345</v>
       </c>
       <c r="AX62" t="n">
         <v>-0.06978832152162695</v>
       </c>
       <c r="AY62" t="n">
-        <v>10.9056148244028</v>
+        <v>10.9056140231148</v>
       </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="n">
@@ -12634,16 +12634,16 @@
         <v>263.2041009521485</v>
       </c>
       <c r="AG63" t="n">
-        <v>307.3683452606201</v>
+        <v>307.3683459472657</v>
       </c>
       <c r="AH63" t="n">
         <v>-0.001725280687138731</v>
       </c>
       <c r="AI63" t="n">
-        <v>-0.1451624604439598</v>
+        <v>-0.1451624623536241</v>
       </c>
       <c r="AJ63" t="n">
-        <v>-0.1436850768449316</v>
+        <v>-0.1436850787578964</v>
       </c>
       <c r="AK63" t="n">
         <v>402.3219604492188</v>
@@ -12676,17 +12676,17 @@
         <v>-0.1450627272006006</v>
       </c>
       <c r="AU63" t="n">
-        <v>-0.06116960375384206</v>
+        <v>-0.06116970612593386</v>
       </c>
       <c r="AV63" t="n">
-        <v>-0.240652948405928</v>
+        <v>-0.2406528814347404</v>
       </c>
       <c r="AW63" t="inlineStr"/>
       <c r="AX63" t="n">
         <v>-0.2805163894554413</v>
       </c>
       <c r="AY63" t="n">
-        <v>5.488914597301684</v>
+        <v>5.488913985991784</v>
       </c>
       <c r="AZ63" t="inlineStr"/>
       <c r="BA63" t="n">
@@ -12878,7 +12878,7 @@
         <v>-0.3507156232081422</v>
       </c>
       <c r="AY64" t="n">
-        <v>-0.918658665634652</v>
+        <v>-0.9186586565048528</v>
       </c>
       <c r="AZ64" t="inlineStr"/>
       <c r="BA64" t="n">
@@ -13402,16 +13402,16 @@
         <v>156.0594189453125</v>
       </c>
       <c r="AG67" t="n">
-        <v>163.4118193817139</v>
+        <v>163.4118197631836</v>
       </c>
       <c r="AH67" t="n">
         <v>-0.05042577088322953</v>
       </c>
       <c r="AI67" t="n">
-        <v>-0.0931500365022615</v>
+        <v>-0.09315003861921856</v>
       </c>
       <c r="AJ67" t="n">
-        <v>-0.04499307616927561</v>
+        <v>-0.04499307839865063</v>
       </c>
       <c r="AK67" t="n">
         <v>217.0162200927734</v>
@@ -13450,10 +13450,10 @@
         <v>-0.2856653201486368</v>
       </c>
       <c r="AW67" t="n">
-        <v>7.511402070976553</v>
+        <v>7.511403003400542</v>
       </c>
       <c r="AX67" t="n">
-        <v>-0.1006477760762259</v>
+        <v>-0.1006478593600676</v>
       </c>
       <c r="AY67" t="n">
         <v>12.07063063066094</v>
@@ -13598,16 +13598,16 @@
         <v>161.1359284973145</v>
       </c>
       <c r="AG68" t="n">
-        <v>120.1981661224365</v>
+        <v>120.1981659698486</v>
       </c>
       <c r="AH68" t="n">
         <v>0.1077603962357465</v>
       </c>
       <c r="AI68" t="n">
-        <v>0.485047615603186</v>
+        <v>0.4850476174884084</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.3405855820893127</v>
+        <v>0.3405855837911451</v>
       </c>
       <c r="AK68" t="n">
         <v>180.5316925048828</v>
@@ -13640,7 +13640,7 @@
         <v>0.5974495813415015</v>
       </c>
       <c r="AU68" t="n">
-        <v>0.8677656802022291</v>
+        <v>0.8677658293087613</v>
       </c>
       <c r="AV68" t="n">
         <v>0.7442035328759826</v>
@@ -13652,7 +13652,7 @@
         <v>0.6902340819059103</v>
       </c>
       <c r="AY68" t="n">
-        <v>189.3564792696982</v>
+        <v>189.3564913694717</v>
       </c>
       <c r="AZ68" t="inlineStr"/>
       <c r="BA68" t="n">
@@ -13790,16 +13790,16 @@
         <v>2168306.825</v>
       </c>
       <c r="AG69" t="n">
-        <v>1174687.07046875</v>
+        <v>1174687.06984375</v>
       </c>
       <c r="AH69" t="n">
         <v>-0.2076767087609938</v>
       </c>
       <c r="AI69" t="n">
-        <v>0.4625171615402601</v>
+        <v>0.4625171623184023</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.8458591053826392</v>
+        <v>0.8458591063647407</v>
       </c>
       <c r="AK69" t="n">
         <v>2919000</v>
@@ -13835,16 +13835,16 @@
         <v>1.338937463119063</v>
       </c>
       <c r="AV69" t="n">
-        <v>5.413305181798</v>
+        <v>5.41330443364465</v>
       </c>
       <c r="AW69" t="n">
-        <v>13.10018476740953</v>
+        <v>13.10018567150961</v>
       </c>
       <c r="AX69" t="n">
         <v>1.542774023261831</v>
       </c>
       <c r="AY69" t="n">
-        <v>-8.506320691767748</v>
+        <v>-8.506320179318255</v>
       </c>
       <c r="AZ69" t="inlineStr"/>
       <c r="BA69" t="n">
@@ -13986,16 +13986,16 @@
         <v>299323.4525</v>
       </c>
       <c r="AG70" t="n">
-        <v>192686.1678515625</v>
+        <v>192686.1681640625</v>
       </c>
       <c r="AH70" t="n">
         <v>-0.1230222763784271</v>
       </c>
       <c r="AI70" t="n">
-        <v>0.3623188572737572</v>
+        <v>0.3623188550643375</v>
       </c>
       <c r="AJ70" t="n">
-        <v>0.5534247000572792</v>
+        <v>0.5534246975379224</v>
       </c>
       <c r="AK70" t="n">
         <v>362100.65625</v>
@@ -14028,10 +14028,10 @@
         <v>0.1627853859471573</v>
       </c>
       <c r="AU70" t="n">
-        <v>0.7313178183210731</v>
+        <v>0.7313176399007708</v>
       </c>
       <c r="AV70" t="n">
-        <v>2.961164087096095</v>
+        <v>2.961164554084868</v>
       </c>
       <c r="AW70" t="n">
         <v>2.545466920054997</v>
@@ -14040,7 +14040,7 @@
         <v>1.049287311544855</v>
       </c>
       <c r="AY70" t="n">
-        <v>60.48312250546469</v>
+        <v>60.48313656861654</v>
       </c>
       <c r="AZ70" t="inlineStr"/>
       <c r="BA70" t="n">
@@ -14182,28 +14182,28 @@
         <v>337.834677734375</v>
       </c>
       <c r="AG71" t="n">
-        <v>240.7902880859375</v>
+        <v>240.7902875518799</v>
       </c>
       <c r="AH71" t="n">
         <v>-0.1326527194343827</v>
       </c>
       <c r="AI71" t="n">
-        <v>0.2169094997265575</v>
+        <v>0.2169095024255858</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.4030245173916758</v>
+        <v>0.4030245205034952</v>
       </c>
       <c r="AK71" t="n">
         <v>433.3299865722656</v>
       </c>
       <c r="AL71" t="n">
-        <v>94.31798553466797</v>
+        <v>94.31800079345703</v>
       </c>
       <c r="AM71" t="n">
         <v>-0.3237948028210009</v>
       </c>
       <c r="AN71" t="n">
-        <v>2.106724421144131</v>
+        <v>2.1067239185375</v>
       </c>
       <c r="AO71" t="n">
         <v>40.36351406493076</v>
@@ -14227,16 +14227,16 @@
         <v>0.2575074967410385</v>
       </c>
       <c r="AV71" t="n">
-        <v>2.106724421144131</v>
+        <v>2.1067239185375</v>
       </c>
       <c r="AW71" t="n">
-        <v>3.820117257714903</v>
+        <v>3.820118165116153</v>
       </c>
       <c r="AX71" t="n">
         <v>0.5863920287166053</v>
       </c>
       <c r="AY71" t="n">
-        <v>1553.21938824062</v>
+        <v>1553.219265398452</v>
       </c>
       <c r="AZ71" t="inlineStr"/>
       <c r="BA71" t="n">
@@ -14378,28 +14378,28 @@
         <v>964.75291015625</v>
       </c>
       <c r="AG72" t="n">
-        <v>517.9365456390381</v>
+        <v>517.9365460968017</v>
       </c>
       <c r="AH72" t="n">
         <v>-0.1469007031410994</v>
       </c>
       <c r="AI72" t="n">
-        <v>0.589055717783745</v>
+        <v>0.5890557163793027</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.8626855321937614</v>
+        <v>0.862685530547479</v>
       </c>
       <c r="AK72" t="n">
         <v>1213.373413085938</v>
       </c>
       <c r="AL72" t="n">
-        <v>104.7119216918945</v>
+        <v>104.7119369506836</v>
       </c>
       <c r="AM72" t="n">
         <v>-0.3217009533745374</v>
       </c>
       <c r="AN72" t="n">
-        <v>6.859945801764266</v>
+        <v>6.859944656400533</v>
       </c>
       <c r="AO72" t="n">
         <v>42.71971346779943</v>
@@ -14426,13 +14426,13 @@
         <v>6.553152390158598</v>
       </c>
       <c r="AW72" t="n">
-        <v>10.06179009214997</v>
+        <v>10.061791226443</v>
       </c>
       <c r="AX72" t="n">
         <v>1.610811969886992</v>
       </c>
       <c r="AY72" t="n">
-        <v>608.3147780323621</v>
+        <v>608.3146704830195</v>
       </c>
       <c r="AZ72" t="inlineStr"/>
       <c r="BA72" t="n">
@@ -14768,28 +14768,28 @@
         <v>890.0659387207031</v>
       </c>
       <c r="AG74" t="n">
-        <v>517.5533813476562</v>
+        <v>517.5533818054199</v>
       </c>
       <c r="AH74" t="n">
         <v>-0.03812743793641504</v>
       </c>
       <c r="AI74" t="n">
-        <v>0.6541868640748463</v>
+        <v>0.6541868626117573</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.7197567841273922</v>
+        <v>0.719756782606308</v>
       </c>
       <c r="AK74" t="n">
         <v>1093.260498046875</v>
       </c>
       <c r="AL74" t="n">
-        <v>146.0639953613281</v>
+        <v>146.0639801025391</v>
       </c>
       <c r="AM74" t="n">
         <v>-0.2169020956923802</v>
       </c>
       <c r="AN74" t="n">
-        <v>4.861334976939028</v>
+        <v>4.86133558925203</v>
       </c>
       <c r="AO74" t="n">
         <v>49.61819463405504</v>
@@ -14816,13 +14816,13 @@
         <v>4.497732114570691</v>
       </c>
       <c r="AW74" t="n">
-        <v>10.51963569039227</v>
+        <v>10.51963687296508</v>
       </c>
       <c r="AX74" t="n">
         <v>1.984749657463633</v>
       </c>
       <c r="AY74" t="n">
-        <v>161.4103670698142</v>
+        <v>161.4103817610358</v>
       </c>
       <c r="AZ74" t="inlineStr"/>
       <c r="BA74" t="n">
@@ -14962,28 +14962,28 @@
         <v>561.2644219970703</v>
       </c>
       <c r="AG75" t="n">
-        <v>331.7141410446167</v>
+        <v>331.7141413116455</v>
       </c>
       <c r="AH75" t="n">
         <v>-0.02926320375547919</v>
       </c>
       <c r="AI75" t="n">
-        <v>0.6424986439820961</v>
+        <v>0.6424986426598902</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.6920123460204797</v>
+        <v>0.6920123446584154</v>
       </c>
       <c r="AK75" t="n">
         <v>746.22998046875</v>
       </c>
       <c r="AL75" t="n">
-        <v>73.58058166503906</v>
+        <v>73.58059692382812</v>
       </c>
       <c r="AM75" t="n">
         <v>-0.2698765245089411</v>
       </c>
       <c r="AN75" t="n">
-        <v>6.404671375604836</v>
+        <v>6.404669840059824</v>
       </c>
       <c r="AO75" t="n">
         <v>48.57135762222948</v>
@@ -15007,16 +15007,16 @@
         <v>1.17896697836987</v>
       </c>
       <c r="AV75" t="n">
-        <v>5.942642652568787</v>
+        <v>5.942641977620266</v>
       </c>
       <c r="AW75" t="n">
-        <v>10.26689702715693</v>
+        <v>10.26689791594815</v>
       </c>
       <c r="AX75" t="n">
         <v>1.904863627762341</v>
       </c>
       <c r="AY75" t="n">
-        <v>800.7774567084939</v>
+        <v>800.7779489940431</v>
       </c>
       <c r="AZ75" t="inlineStr"/>
       <c r="BA75" t="n">
@@ -15202,13 +15202,13 @@
         <v>6.404001548207064</v>
       </c>
       <c r="AW76" t="n">
-        <v>3.574300579211694</v>
+        <v>3.574300886210126</v>
       </c>
       <c r="AX76" t="n">
         <v>0.4392139029230653</v>
       </c>
       <c r="AY76" t="n">
-        <v>2.415145919293503</v>
+        <v>2.415145577050001</v>
       </c>
       <c r="AZ76" t="inlineStr"/>
       <c r="BA76" t="n">
@@ -15400,7 +15400,7 @@
         <v>0.7471431853790844</v>
       </c>
       <c r="AY77" t="n">
-        <v>-0.5793364614186236</v>
+        <v>-0.5793364314584335</v>
       </c>
       <c r="AZ77" t="inlineStr"/>
       <c r="BA77" t="n">
@@ -16234,28 +16234,28 @@
         <v>153.8262132263184</v>
       </c>
       <c r="AG82" t="n">
-        <v>141.7433330917358</v>
+        <v>141.7433353042603</v>
       </c>
       <c r="AH82" t="n">
         <v>0.04468538604542438</v>
       </c>
       <c r="AI82" t="n">
-        <v>0.1337393684981123</v>
+        <v>0.1337393508011531</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.08524478626985954</v>
+        <v>0.08524476932987013</v>
       </c>
       <c r="AK82" t="n">
         <v>176.3200073242188</v>
       </c>
       <c r="AL82" t="n">
-        <v>103.6037979125977</v>
+        <v>103.6038055419922</v>
       </c>
       <c r="AM82" t="n">
         <v>-0.08858898438708862</v>
       </c>
       <c r="AN82" t="n">
-        <v>0.5511014092727766</v>
+        <v>0.5511012950495149</v>
       </c>
       <c r="AO82" t="n">
         <v>54.87072785249556</v>
@@ -16279,16 +16279,16 @@
         <v>0.1192430500536419</v>
       </c>
       <c r="AV82" t="n">
-        <v>0.5190627928934475</v>
+        <v>0.5190626833401064</v>
       </c>
       <c r="AW82" t="n">
-        <v>3.753268408411166</v>
+        <v>3.753269481063497</v>
       </c>
       <c r="AX82" t="n">
-        <v>0.1542518370633552</v>
+        <v>0.1542519635676871</v>
       </c>
       <c r="AY82" t="n">
-        <v>1283.223072253246</v>
+        <v>1283.222919325908</v>
       </c>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="n">
@@ -16474,13 +16474,13 @@
         <v>2.315897310697115</v>
       </c>
       <c r="AW83" t="n">
-        <v>6.165358587292876</v>
+        <v>6.165357981491561</v>
       </c>
       <c r="AX83" t="n">
         <v>1.282224900714468</v>
       </c>
       <c r="AY83" t="n">
-        <v>17.56560717089294</v>
+        <v>17.56560513740004</v>
       </c>
       <c r="AZ83" t="inlineStr"/>
       <c r="BA83" t="n">
@@ -16672,7 +16672,7 @@
         <v>0.4483768482482455</v>
       </c>
       <c r="AY84" t="n">
-        <v>193.8967929562967</v>
+        <v>193.8967728760948</v>
       </c>
       <c r="AZ84" t="inlineStr"/>
       <c r="BA84" t="n">
@@ -16858,13 +16858,13 @@
         <v>2.046404982255948</v>
       </c>
       <c r="AW85" t="n">
-        <v>36.63585540498371</v>
+        <v>36.635858816108</v>
       </c>
       <c r="AX85" t="n">
         <v>0.3018789196831337</v>
       </c>
       <c r="AY85" t="n">
-        <v>213.7581246406392</v>
+        <v>213.7581385242736</v>
       </c>
       <c r="AZ85" t="inlineStr"/>
       <c r="BA85" t="n">
@@ -17394,16 +17394,16 @@
         <v>239.4106005859375</v>
       </c>
       <c r="AG88" t="n">
-        <v>134.9904850387573</v>
+        <v>134.9904849624634</v>
       </c>
       <c r="AH88" t="n">
         <v>-0.2165760534430962</v>
       </c>
       <c r="AI88" t="n">
-        <v>0.3894312440224443</v>
+        <v>0.3894312448077235</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.7735368571881192</v>
+        <v>0.7735368581904871</v>
       </c>
       <c r="AK88" t="n">
         <v>316.3519592285156</v>
@@ -17442,13 +17442,13 @@
         <v>1.338678565098987</v>
       </c>
       <c r="AW88" t="n">
-        <v>2.241313527687087</v>
+        <v>2.241313741366151</v>
       </c>
       <c r="AX88" t="n">
-        <v>1.101300259381754</v>
+        <v>1.101300438989937</v>
       </c>
       <c r="AY88" t="n">
-        <v>14.46337927561398</v>
+        <v>14.46337562815987</v>
       </c>
       <c r="AZ88" t="inlineStr"/>
       <c r="BA88" t="n">
@@ -18028,7 +18028,7 @@
         <v>0.04448813161764087</v>
       </c>
       <c r="AY91" t="n">
-        <v>7.148624704197935</v>
+        <v>7.148623741826434</v>
       </c>
       <c r="AZ91" t="inlineStr"/>
       <c r="BA91" t="n">
@@ -18220,7 +18220,7 @@
         <v>0.3433833088441416</v>
       </c>
       <c r="AY92" t="n">
-        <v>10.44690338314961</v>
+        <v>10.44690129785219</v>
       </c>
       <c r="AZ92" t="inlineStr"/>
       <c r="BA92" t="n">
@@ -18362,28 +18362,28 @@
         <v>395.0326873779297</v>
       </c>
       <c r="AG93" t="n">
-        <v>364.8947802734375</v>
+        <v>364.8947793579102</v>
       </c>
       <c r="AH93" t="n">
         <v>-0.01456256351041951</v>
       </c>
       <c r="AI93" t="n">
-        <v>0.06682808257105255</v>
+        <v>0.06682808524774275</v>
       </c>
       <c r="AJ93" t="n">
-        <v>0.0825934179762946</v>
+        <v>0.08259342069254005</v>
       </c>
       <c r="AK93" t="n">
         <v>480.8090515136719</v>
       </c>
       <c r="AL93" t="n">
-        <v>286.5404968261719</v>
+        <v>286.54052734375</v>
       </c>
       <c r="AM93" t="n">
         <v>-0.1903646623253563</v>
       </c>
       <c r="AN93" t="n">
-        <v>0.3585514197508051</v>
+        <v>0.3585512750602811</v>
       </c>
       <c r="AO93" t="n">
         <v>52.42782072288501</v>
@@ -18404,13 +18404,13 @@
         <v>-0.07449649339109377</v>
       </c>
       <c r="AU93" t="n">
-        <v>0.1793358939996921</v>
+        <v>0.1793360030339692</v>
       </c>
       <c r="AV93" t="n">
         <v>0.3351456710249647</v>
       </c>
       <c r="AW93" t="n">
-        <v>7.866961023049903</v>
+        <v>7.866961793505519</v>
       </c>
       <c r="AX93" t="n">
         <v>0.1239687532078804</v>
@@ -18754,16 +18754,16 @@
         <v>182.4476118469238</v>
       </c>
       <c r="AG95" t="n">
-        <v>134.9797373962402</v>
+        <v>134.9797370910645</v>
       </c>
       <c r="AH95" t="n">
         <v>-0.2422482344356814</v>
       </c>
       <c r="AI95" t="n">
-        <v>0.02422780386777412</v>
+        <v>0.02422780618345133</v>
       </c>
       <c r="AJ95" t="n">
-        <v>0.3516666676520424</v>
+        <v>0.3516666707080265</v>
       </c>
       <c r="AK95" t="n">
         <v>255.6900024414062</v>
@@ -18799,16 +18799,16 @@
         <v>0.3435381919629434</v>
       </c>
       <c r="AV95" t="n">
-        <v>1.210013631546743</v>
+        <v>1.210013496779354</v>
       </c>
       <c r="AW95" t="n">
-        <v>2.831141999609289</v>
+        <v>2.83114118961615</v>
       </c>
       <c r="AX95" t="n">
-        <v>0.5299473446693075</v>
+        <v>0.5299472154944873</v>
       </c>
       <c r="AY95" t="n">
-        <v>179.3411629024612</v>
+        <v>179.3411348588057</v>
       </c>
       <c r="AZ95" t="inlineStr"/>
       <c r="BA95" t="n">
@@ -19392,7 +19392,7 @@
         <v>0.08313106796116498</v>
       </c>
       <c r="AY98" t="n">
-        <v>25.42466632527602</v>
+        <v>25.4246633407812</v>
       </c>
       <c r="AZ98" t="inlineStr"/>
       <c r="BA98" t="n">
@@ -19578,13 +19578,13 @@
         <v>1.240196204469647</v>
       </c>
       <c r="AW99" t="n">
-        <v>0.7423129003619613</v>
+        <v>0.7423125836196365</v>
       </c>
       <c r="AX99" t="n">
         <v>0.4039938589821908</v>
       </c>
       <c r="AY99" t="n">
-        <v>14.29590069140085</v>
+        <v>14.29590221715319</v>
       </c>
       <c r="AZ99" t="inlineStr"/>
       <c r="BA99" t="n">
@@ -19726,16 +19726,16 @@
         <v>88.86930938720702</v>
       </c>
       <c r="AG100" t="n">
-        <v>74.92472110748291</v>
+        <v>74.92472122192383</v>
       </c>
       <c r="AH100" t="n">
         <v>-0.164053356239746</v>
       </c>
       <c r="AI100" t="n">
-        <v>-0.008471438833186018</v>
+        <v>-0.008471440347658787</v>
       </c>
       <c r="AJ100" t="n">
-        <v>0.1861146504598925</v>
+        <v>0.1861146486482068</v>
       </c>
       <c r="AK100" t="n">
         <v>102.7099990844727</v>
@@ -19771,16 +19771,16 @@
         <v>-0.01076810060169664</v>
       </c>
       <c r="AV100" t="n">
-        <v>0.128941316689072</v>
+        <v>0.1289411858002996</v>
       </c>
       <c r="AW100" t="n">
-        <v>0.1853166570267433</v>
+        <v>0.1853165127393352</v>
       </c>
       <c r="AX100" t="n">
         <v>0.1548899352420714</v>
       </c>
       <c r="AY100" t="n">
-        <v>421.8812935550081</v>
+        <v>421.8814729031519</v>
       </c>
       <c r="AZ100" t="inlineStr"/>
       <c r="BA100" t="n">
@@ -19934,13 +19934,13 @@
         <v>-0.05914461274743921</v>
       </c>
       <c r="AK101" t="n">
-        <v>247.2834167480469</v>
+        <v>247.2834320068359</v>
       </c>
       <c r="AL101" t="n">
         <v>195.0859069824219</v>
       </c>
       <c r="AM101" t="n">
-        <v>-0.1682013895376554</v>
+        <v>-0.1682014408643434</v>
       </c>
       <c r="AN101" t="n">
         <v>0.05435603023820601</v>
@@ -19970,13 +19970,13 @@
         <v>0.01022901751909977</v>
       </c>
       <c r="AW101" t="n">
-        <v>0.6023338746915263</v>
+        <v>0.6023340651555549</v>
       </c>
       <c r="AX101" t="n">
         <v>-0.1119207417541332</v>
       </c>
       <c r="AY101" t="n">
-        <v>6.697073856030528</v>
+        <v>6.6970744054047</v>
       </c>
       <c r="AZ101" t="inlineStr"/>
       <c r="BA101" t="n">
@@ -20114,16 +20114,16 @@
         <v>68.51589706420899</v>
       </c>
       <c r="AG102" t="n">
-        <v>41.89391582489014</v>
+        <v>41.89391571044922</v>
       </c>
       <c r="AH102" t="n">
         <v>-0.2353599436850156</v>
       </c>
       <c r="AI102" t="n">
-        <v>0.2505395678129074</v>
+        <v>0.2505395712289857</v>
       </c>
       <c r="AJ102" t="n">
-        <v>0.6354617541743883</v>
+        <v>0.635461758641952</v>
       </c>
       <c r="AK102" t="n">
         <v>79.81999969482422</v>
@@ -20156,7 +20156,7 @@
         <v>-0.05920947895296824</v>
       </c>
       <c r="AU102" t="n">
-        <v>0.8859302368933351</v>
+        <v>0.8859303663823617</v>
       </c>
       <c r="AV102" t="n">
         <v>1.081997229405414</v>
@@ -20168,7 +20168,7 @@
         <v>0.9217607678801751</v>
       </c>
       <c r="AY102" t="n">
-        <v>22.92597068099426</v>
+        <v>22.92595505017285</v>
       </c>
       <c r="AZ102" t="inlineStr"/>
       <c r="BA102" t="n">
@@ -20550,7 +20550,7 @@
         <v>0.2193778315087658</v>
       </c>
       <c r="AY104" t="n">
-        <v>14.29352713094868</v>
+        <v>14.29352869845947</v>
       </c>
       <c r="AZ104" t="inlineStr"/>
       <c r="BA104" t="n">
@@ -20703,13 +20703,13 @@
         <v>26150</v>
       </c>
       <c r="AL105" t="n">
-        <v>16864.458984375</v>
+        <v>16864.4609375</v>
       </c>
       <c r="AM105" t="n">
         <v>-0.1091778202676864</v>
       </c>
       <c r="AN105" t="n">
-        <v>0.3813072818750323</v>
+        <v>0.3813071219015951</v>
       </c>
       <c r="AO105" t="n">
         <v>17.05989110707804</v>
@@ -20736,7 +20736,7 @@
         <v>0.3136373203474547</v>
       </c>
       <c r="AW105" t="n">
-        <v>0.2137025098636531</v>
+        <v>0.213702633370737</v>
       </c>
       <c r="AX105" t="n">
         <v>0.1608228139897416</v>
@@ -20925,16 +20925,16 @@
         <v>0.3214565499441588</v>
       </c>
       <c r="AV106" t="n">
-        <v>0.8618796809431368</v>
+        <v>0.8618798074887346</v>
       </c>
       <c r="AW106" t="n">
-        <v>3.434126691100668</v>
+        <v>3.434127049964774</v>
       </c>
       <c r="AX106" t="n">
         <v>0.2739790536520312</v>
       </c>
       <c r="AY106" t="n">
-        <v>53.76495780532725</v>
+        <v>53.76495096259943</v>
       </c>
       <c r="AZ106" t="inlineStr"/>
       <c r="BA106" t="n">
@@ -21076,28 +21076,28 @@
         <v>403.4318005371094</v>
       </c>
       <c r="AG107" t="n">
-        <v>372.9502442932129</v>
+        <v>372.950244140625</v>
       </c>
       <c r="AH107" t="n">
         <v>0.02917026286538205</v>
       </c>
       <c r="AI107" t="n">
-        <v>0.1132852667622912</v>
+        <v>0.113285267217778</v>
       </c>
       <c r="AJ107" t="n">
-        <v>0.08173089228474106</v>
+        <v>0.08173089272731771</v>
       </c>
       <c r="AK107" t="n">
         <v>435.7799987792969</v>
       </c>
       <c r="AL107" t="n">
-        <v>313.9706115722656</v>
+        <v>313.9706420898438</v>
       </c>
       <c r="AM107" t="n">
         <v>-0.04722563364522026</v>
       </c>
       <c r="AN107" t="n">
-        <v>0.3224168024129417</v>
+        <v>0.3224166738755796</v>
       </c>
       <c r="AO107" t="n">
         <v>53.92437420542295</v>
@@ -21118,19 +21118,19 @@
         <v>-0.02162513673061683</v>
       </c>
       <c r="AU107" t="n">
-        <v>0.1884516102037588</v>
+        <v>0.1884515063898182</v>
       </c>
       <c r="AV107" t="n">
-        <v>0.09175088680404286</v>
+        <v>0.09175079919684714</v>
       </c>
       <c r="AW107" t="n">
-        <v>1.881679316959384</v>
+        <v>1.881679622137971</v>
       </c>
       <c r="AX107" t="n">
         <v>0.2759943082702649</v>
       </c>
       <c r="AY107" t="n">
-        <v>1201.11712457268</v>
+        <v>1201.115879865729</v>
       </c>
       <c r="AZ107" t="inlineStr"/>
       <c r="BA107" t="n">
@@ -21320,13 +21320,13 @@
         <v>0.04575564389709519</v>
       </c>
       <c r="AW108" t="n">
-        <v>1.42133885997571</v>
+        <v>1.421338663337688</v>
       </c>
       <c r="AX108" t="n">
         <v>0.1484478722694533</v>
       </c>
       <c r="AY108" t="n">
-        <v>509.3158463384471</v>
+        <v>509.315539268878</v>
       </c>
       <c r="AZ108" t="inlineStr"/>
       <c r="BA108" t="n">
@@ -21518,7 +21518,7 @@
         <v>0.6568598433276109</v>
       </c>
       <c r="AY109" t="n">
-        <v>65.39152975376139</v>
+        <v>65.3915348801511</v>
       </c>
       <c r="AZ109" t="inlineStr"/>
       <c r="BA109" t="n">
@@ -21660,16 +21660,16 @@
         <v>67.97727241516114</v>
       </c>
       <c r="AG110" t="n">
-        <v>60.45350605010987</v>
+        <v>60.45350631713868</v>
       </c>
       <c r="AH110" t="n">
         <v>-0.09072548548586101</v>
       </c>
       <c r="AI110" t="n">
-        <v>0.02243865429503389</v>
+        <v>0.02243864977882626</v>
       </c>
       <c r="AJ110" t="n">
-        <v>0.1244554180003197</v>
+        <v>0.1244554130334945</v>
       </c>
       <c r="AK110" t="n">
         <v>75.72768402099609</v>
@@ -21702,19 +21702,19 @@
         <v>-0.07936676497363004</v>
       </c>
       <c r="AU110" t="n">
-        <v>0.04486778229742927</v>
+        <v>0.0448677149185206</v>
       </c>
       <c r="AV110" t="n">
         <v>-0.08538834833082787</v>
       </c>
       <c r="AW110" t="n">
-        <v>0.2880387933432986</v>
+        <v>0.2880384861721916</v>
       </c>
       <c r="AX110" t="n">
         <v>0.1681662335070657</v>
       </c>
       <c r="AY110" t="n">
-        <v>4.609803563131717</v>
+        <v>4.609804534237885</v>
       </c>
       <c r="AZ110" t="inlineStr"/>
       <c r="BA110" t="n">
@@ -21900,13 +21900,13 @@
         <v>0.7730063024235261</v>
       </c>
       <c r="AW111" t="n">
-        <v>0.8114638206972327</v>
+        <v>0.8114642416676292</v>
       </c>
       <c r="AX111" t="n">
         <v>0.5661208379096441</v>
       </c>
       <c r="AY111" t="n">
-        <v>0.1770976690229957</v>
+        <v>0.1770974912699461</v>
       </c>
       <c r="AZ111" t="inlineStr"/>
       <c r="BA111" t="n">
@@ -22048,28 +22048,28 @@
         <v>1444.494509277344</v>
       </c>
       <c r="AG112" t="n">
-        <v>1207.603322143555</v>
+        <v>1207.603319396973</v>
       </c>
       <c r="AH112" t="n">
         <v>-0.01278265847455951</v>
       </c>
       <c r="AI112" t="n">
-        <v>0.1808762059097373</v>
+        <v>0.1808762085955309</v>
       </c>
       <c r="AJ112" t="n">
-        <v>0.1961663923823063</v>
+        <v>0.196166395102876</v>
       </c>
       <c r="AK112" t="n">
         <v>1687.3154296875</v>
       </c>
       <c r="AL112" t="n">
-        <v>706.2977294921875</v>
+        <v>706.2977905273438</v>
       </c>
       <c r="AM112" t="n">
         <v>-0.1548527298414005</v>
       </c>
       <c r="AN112" t="n">
-        <v>1.01902111496544</v>
+        <v>1.019020940490493</v>
       </c>
       <c r="AO112" t="n">
         <v>61.48715115052403</v>
@@ -22093,16 +22093,16 @@
         <v>0.273016326201472</v>
       </c>
       <c r="AV112" t="n">
-        <v>1.01902111496544</v>
+        <v>1.019020940490493</v>
       </c>
       <c r="AW112" t="n">
-        <v>2.581317399046809</v>
+        <v>2.581318496957828</v>
       </c>
       <c r="AX112" t="n">
         <v>0.5284054911209966</v>
       </c>
       <c r="AY112" t="n">
-        <v>168.8736830338175</v>
+        <v>168.8736251383283</v>
       </c>
       <c r="AZ112" t="inlineStr"/>
       <c r="BA112" t="n">
@@ -22432,28 +22432,28 @@
         <v>161.7204083251953</v>
       </c>
       <c r="AG114" t="n">
-        <v>128.3896025848389</v>
+        <v>128.3896026611328</v>
       </c>
       <c r="AH114" t="n">
         <v>-0.04879041906865711</v>
       </c>
       <c r="AI114" t="n">
-        <v>0.1981499960591047</v>
+        <v>0.1981499953471186</v>
       </c>
       <c r="AJ114" t="n">
-        <v>0.2596067365994976</v>
+        <v>0.2596067358509917</v>
       </c>
       <c r="AK114" t="n">
         <v>184.09619140625</v>
       </c>
       <c r="AL114" t="n">
-        <v>77.89862060546875</v>
+        <v>77.89861297607422</v>
       </c>
       <c r="AM114" t="n">
         <v>-0.1644042136016063</v>
       </c>
       <c r="AN114" t="n">
-        <v>0.9747461589872528</v>
+        <v>0.9747463523940028</v>
       </c>
       <c r="AO114" t="n">
         <v>47.02338562261222</v>
@@ -22477,16 +22477,16 @@
         <v>0.3741371180271991</v>
       </c>
       <c r="AV114" t="n">
-        <v>0.9747461589872528</v>
+        <v>0.9747463523940028</v>
       </c>
       <c r="AW114" t="n">
-        <v>4.288642653249128</v>
+        <v>4.288643346846656</v>
       </c>
       <c r="AX114" t="n">
         <v>0.4468408078046198</v>
       </c>
       <c r="AY114" t="n">
-        <v>7.054818675949726</v>
+        <v>7.054821893762258</v>
       </c>
       <c r="AZ114" t="inlineStr"/>
       <c r="BA114" t="n">
@@ -22628,16 +22628,16 @@
         <v>681.0273022460938</v>
       </c>
       <c r="AG115" t="n">
-        <v>561.1839535522461</v>
+        <v>561.1839540100098</v>
       </c>
       <c r="AH115" t="n">
         <v>-0.02006867690833414</v>
       </c>
       <c r="AI115" t="n">
-        <v>0.1892000495153707</v>
+        <v>0.1892000485453276</v>
       </c>
       <c r="AJ115" t="n">
-        <v>0.2135544823319513</v>
+        <v>0.213554481342042</v>
       </c>
       <c r="AK115" t="n">
         <v>785.1200561523438</v>
@@ -22676,13 +22676,13 @@
         <v>0.6446169344452346</v>
       </c>
       <c r="AW115" t="n">
-        <v>6.628252968355017</v>
+        <v>6.628251637869951</v>
       </c>
       <c r="AX115" t="n">
         <v>0.5183612402485029</v>
       </c>
       <c r="AY115" t="n">
-        <v>89.74637109914636</v>
+        <v>89.74635933126176</v>
       </c>
       <c r="AZ115" t="inlineStr"/>
       <c r="BA115" t="n">
@@ -22824,28 +22824,28 @@
         <v>397.4129534912109</v>
       </c>
       <c r="AG116" t="n">
-        <v>329.9801006317139</v>
+        <v>329.9801012420654</v>
       </c>
       <c r="AH116" t="n">
         <v>-0.07549565147670789</v>
       </c>
       <c r="AI116" t="n">
-        <v>0.1134307885800983</v>
+        <v>0.1134307865206281</v>
       </c>
       <c r="AJ116" t="n">
-        <v>0.2043543011545352</v>
+        <v>0.2043542989268872</v>
       </c>
       <c r="AK116" t="n">
         <v>445.4800109863281</v>
       </c>
       <c r="AL116" t="n">
-        <v>217.7568969726562</v>
+        <v>217.7568817138672</v>
       </c>
       <c r="AM116" t="n">
         <v>-0.175249181554444</v>
       </c>
       <c r="AN116" t="n">
-        <v>0.6872485270041531</v>
+        <v>0.6872486452340303</v>
       </c>
       <c r="AO116" t="n">
         <v>39.52231586757532</v>
@@ -22869,16 +22869,16 @@
         <v>0.1887864569895132</v>
       </c>
       <c r="AV116" t="n">
-        <v>0.6575791833243221</v>
+        <v>0.6575790692159182</v>
       </c>
       <c r="AW116" t="n">
-        <v>1.439813659404044</v>
+        <v>1.439813906623391</v>
       </c>
       <c r="AX116" t="n">
         <v>0.3500765013645097</v>
       </c>
       <c r="AY116" t="n">
-        <v>827.220081738826</v>
+        <v>827.2196366154541</v>
       </c>
       <c r="AZ116" t="inlineStr"/>
       <c r="BA116" t="n">
@@ -23011,7 +23011,7 @@
         <v>36648</v>
       </c>
       <c r="AD117" t="n">
-        <v>26.2</v>
+        <v>26.3</v>
       </c>
       <c r="AE117" t="n">
         <v>81.61000061035156</v>
@@ -23264,13 +23264,13 @@
         <v>0.2735886102423664</v>
       </c>
       <c r="AW118" t="n">
-        <v>-0.2379285405225049</v>
+        <v>-0.2379283945566348</v>
       </c>
       <c r="AX118" t="n">
         <v>0.6389144138164766</v>
       </c>
       <c r="AY118" t="n">
-        <v>33.797386576609</v>
+        <v>33.79740084235731</v>
       </c>
       <c r="AZ118" t="inlineStr"/>
       <c r="BA118" t="n">
@@ -23412,16 +23412,16 @@
         <v>296.6581231689453</v>
       </c>
       <c r="AG119" t="n">
-        <v>224.1979586029053</v>
+        <v>224.1979588317871</v>
       </c>
       <c r="AH119" t="n">
         <v>-0.07051259109684838</v>
       </c>
       <c r="AI119" t="n">
-        <v>0.2298951870599317</v>
+        <v>0.2298951858043419</v>
       </c>
       <c r="AJ119" t="n">
-        <v>0.32319725396956</v>
+        <v>0.3231972526187188</v>
       </c>
       <c r="AK119" t="n">
         <v>330.5873718261719</v>
@@ -23457,16 +23457,16 @@
         <v>0.2923220567197558</v>
       </c>
       <c r="AV119" t="n">
-        <v>0.5623597015219586</v>
+        <v>0.5623598365992701</v>
       </c>
       <c r="AW119" t="n">
-        <v>0.6875540700254457</v>
+        <v>0.6875542276180191</v>
       </c>
       <c r="AX119" t="n">
         <v>0.5794177892183991</v>
       </c>
       <c r="AY119" t="n">
-        <v>402.0844089527855</v>
+        <v>402.0846548030351</v>
       </c>
       <c r="AZ119" t="inlineStr"/>
       <c r="BA119" t="n">
@@ -23658,7 +23658,7 @@
         <v>0.7745164644370066</v>
       </c>
       <c r="AY120" t="n">
-        <v>97.32011806922098</v>
+        <v>97.32009584078746</v>
       </c>
       <c r="AZ120" t="inlineStr"/>
       <c r="BA120" t="n">
@@ -23850,7 +23850,7 @@
         <v>0.4278815499228228</v>
       </c>
       <c r="AY121" t="n">
-        <v>226.7791205765172</v>
+        <v>226.7793205286258</v>
       </c>
       <c r="AZ121" t="inlineStr"/>
       <c r="BA121" t="n">
@@ -24182,28 +24182,28 @@
         <v>305.7206442260742</v>
       </c>
       <c r="AG123" t="n">
-        <v>246.2359702301025</v>
+        <v>246.235969543457</v>
       </c>
       <c r="AH123" t="n">
         <v>-0.209834167608313</v>
       </c>
       <c r="AI123" t="n">
-        <v>-0.01894915231728145</v>
+        <v>-0.01894914958155536</v>
       </c>
       <c r="AJ123" t="n">
-        <v>0.2415758913711286</v>
+        <v>0.2415758948333462</v>
       </c>
       <c r="AK123" t="n">
         <v>376.1517333984375</v>
       </c>
       <c r="AL123" t="n">
-        <v>121.6859588623047</v>
+        <v>121.6859512329102</v>
       </c>
       <c r="AM123" t="n">
         <v>-0.3577857394363341</v>
       </c>
       <c r="AN123" t="n">
-        <v>0.9851921255563298</v>
+        <v>0.9851922500227435</v>
       </c>
       <c r="AO123" t="n">
         <v>26.86719151252531</v>
@@ -24236,7 +24236,7 @@
         <v>0.3762186353787311</v>
       </c>
       <c r="AY123" t="n">
-        <v>23.30979007771317</v>
+        <v>23.30978774468786</v>
       </c>
       <c r="AZ123" t="inlineStr"/>
       <c r="BA123" t="n">
@@ -24543,10 +24543,10 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>0.1051602065563202</v>
+        <v>0.1051584407687187</v>
       </c>
       <c r="AA125" t="n">
-        <v>3244140132.036987</v>
+        <v>3244085658.366669</v>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
@@ -24566,16 +24566,16 @@
         <v>182.8390002441406</v>
       </c>
       <c r="AG125" t="n">
-        <v>174.4954419708252</v>
+        <v>174.4954420089722</v>
       </c>
       <c r="AH125" t="n">
         <v>-0.07705686546813273</v>
       </c>
       <c r="AI125" t="n">
-        <v>-0.03292602893195229</v>
+        <v>-0.03292602914336717</v>
       </c>
       <c r="AJ125" t="n">
-        <v>0.04781533648718717</v>
+        <v>0.04781533625812107</v>
       </c>
       <c r="AK125" t="n">
         <v>210.6000061035156</v>
@@ -24614,13 +24614,13 @@
         <v>0.2499371312997969</v>
       </c>
       <c r="AW125" t="n">
-        <v>1.211088451035493</v>
+        <v>1.21108800896815</v>
       </c>
       <c r="AX125" t="n">
         <v>-0.1235004313862804</v>
       </c>
       <c r="AY125" t="n">
-        <v>1.704868730696837</v>
+        <v>1.704868896086633</v>
       </c>
       <c r="AZ125" t="inlineStr"/>
       <c r="BA125" t="n">
@@ -24920,13 +24920,13 @@
         <v>0.3480915628336445</v>
       </c>
       <c r="AW127" t="n">
-        <v>1.308026192886291</v>
+        <v>1.30802604830548</v>
       </c>
       <c r="AX127" t="n">
         <v>0.1906930057611249</v>
       </c>
       <c r="AY127" t="n">
-        <v>28.57003401176623</v>
+        <v>28.57003104527659</v>
       </c>
       <c r="AZ127" t="inlineStr"/>
       <c r="BA127" t="n">
@@ -25314,7 +25314,7 @@
         <v>0.3329651981457438</v>
       </c>
       <c r="AY129" t="n">
-        <v>92.78554028846602</v>
+        <v>92.7855190523709</v>
       </c>
       <c r="AZ129" t="inlineStr"/>
       <c r="BA129" t="n">
@@ -25702,7 +25702,7 @@
         <v>0.5369179419745129</v>
       </c>
       <c r="AY131" t="n">
-        <v>12.70427528710055</v>
+        <v>12.7042766979117</v>
       </c>
       <c r="AZ131" t="inlineStr"/>
       <c r="BA131" t="n">
@@ -25889,7 +25889,7 @@
         <v>0.3296697537565416</v>
       </c>
       <c r="AV132" t="n">
-        <v>1.03165945452346</v>
+        <v>1.031659309265863</v>
       </c>
       <c r="AW132" t="n">
         <v>2.900279076662184</v>
@@ -25898,7 +25898,7 @@
         <v>0.5168964520658905</v>
       </c>
       <c r="AY132" t="n">
-        <v>19.48208511316918</v>
+        <v>19.48208695859011</v>
       </c>
       <c r="AZ132" t="inlineStr"/>
       <c r="BA132" t="n">
@@ -26040,16 +26040,16 @@
         <v>221.2432205200195</v>
       </c>
       <c r="AG133" t="n">
-        <v>162.3046439743042</v>
+        <v>162.3046439361572</v>
       </c>
       <c r="AH133" t="n">
         <v>-0.1736695619666411</v>
       </c>
       <c r="AI133" t="n">
-        <v>0.1264003471962423</v>
+        <v>0.1264003474609838</v>
       </c>
       <c r="AJ133" t="n">
-        <v>0.3631354907814366</v>
+        <v>0.363135491101819</v>
       </c>
       <c r="AK133" t="n">
         <v>301.7099914550781</v>
@@ -26082,19 +26082,19 @@
         <v>0.0604042182543858</v>
       </c>
       <c r="AU133" t="n">
-        <v>0.283605655869436</v>
+        <v>0.2836057933874647</v>
       </c>
       <c r="AV133" t="n">
-        <v>1.093197152755206</v>
+        <v>1.093196969908734</v>
       </c>
       <c r="AW133" t="n">
-        <v>5.03605638393693</v>
+        <v>5.036056003823767</v>
       </c>
       <c r="AX133" t="n">
         <v>0.4381759365695965</v>
       </c>
       <c r="AY133" t="n">
-        <v>3012.193236843113</v>
+        <v>3012.193051835185</v>
       </c>
       <c r="AZ133" t="inlineStr"/>
       <c r="BA133" t="n">
@@ -26236,28 +26236,28 @@
         <v>543.5743981933593</v>
       </c>
       <c r="AG134" t="n">
-        <v>372.9612100982666</v>
+        <v>372.9612097167969</v>
       </c>
       <c r="AH134" t="n">
         <v>-0.06605238378584033</v>
       </c>
       <c r="AI134" t="n">
-        <v>0.3611871682150944</v>
+        <v>0.3611871696073348</v>
       </c>
       <c r="AJ134" t="n">
-        <v>0.4574555837861534</v>
+        <v>0.4574555852768585</v>
       </c>
       <c r="AK134" t="n">
         <v>723</v>
       </c>
       <c r="AL134" t="n">
-        <v>155.5567016601562</v>
+        <v>155.5566864013672</v>
       </c>
       <c r="AM134" t="n">
         <v>-0.297828473820561</v>
       </c>
       <c r="AN134" t="n">
-        <v>2.263568898091179</v>
+        <v>2.263569218219555</v>
       </c>
       <c r="AO134" t="n">
         <v>40.22065487818131</v>
@@ -26278,19 +26278,19 @@
         <v>0.3064180958905154</v>
       </c>
       <c r="AU134" t="n">
-        <v>0.5789745895981673</v>
+        <v>0.5789744397267569</v>
       </c>
       <c r="AV134" t="n">
         <v>1.840132086135813</v>
       </c>
       <c r="AW134" t="n">
-        <v>2.823742428089041</v>
+        <v>2.823741549176395</v>
       </c>
       <c r="AX134" t="n">
-        <v>0.8928667821518104</v>
+        <v>0.892866566770208</v>
       </c>
       <c r="AY134" t="n">
-        <v>7356.883012815494</v>
+        <v>7356.882218278148</v>
       </c>
       <c r="AZ134" t="inlineStr"/>
       <c r="BA134" t="n">
@@ -26432,28 +26432,28 @@
         <v>1749.024680175781</v>
       </c>
       <c r="AG135" t="n">
-        <v>1387.814980773926</v>
+        <v>1387.814989318848</v>
       </c>
       <c r="AH135" t="n">
         <v>-0.06862377731783542</v>
       </c>
       <c r="AI135" t="n">
-        <v>0.1737875888121452</v>
+        <v>0.1737875815850123</v>
       </c>
       <c r="AJ135" t="n">
-        <v>0.2602722296601987</v>
+        <v>0.2602722219005709</v>
       </c>
       <c r="AK135" t="n">
         <v>1986.870361328125</v>
       </c>
       <c r="AL135" t="n">
-        <v>685.1173706054688</v>
+        <v>685.117431640625</v>
       </c>
       <c r="AM135" t="n">
         <v>-0.1801176203005547</v>
       </c>
       <c r="AN135" t="n">
-        <v>1.377694786165442</v>
+        <v>1.377694574343401</v>
       </c>
       <c r="AO135" t="n">
         <v>42.12973724684237</v>
@@ -26486,7 +26486,7 @@
         <v>0.4064733256563533</v>
       </c>
       <c r="AY135" t="n">
-        <v>924.6957180897114</v>
+        <v>924.6954672562919</v>
       </c>
       <c r="AZ135" t="inlineStr"/>
       <c r="BA135" t="n">
@@ -26628,28 +26628,28 @@
         <v>380.4425982666016</v>
       </c>
       <c r="AG136" t="n">
-        <v>289.2736173248291</v>
+        <v>289.2736167907715</v>
       </c>
       <c r="AH136" t="n">
         <v>-0.03352042038220637</v>
       </c>
       <c r="AI136" t="n">
-        <v>0.2710803212604154</v>
+        <v>0.2710803236070869</v>
       </c>
       <c r="AJ136" t="n">
-        <v>0.3151652120400514</v>
+        <v>0.3151652144681125</v>
       </c>
       <c r="AK136" t="n">
         <v>483.8399963378906</v>
       </c>
       <c r="AL136" t="n">
-        <v>103.8940353393555</v>
+        <v>103.89404296875</v>
       </c>
       <c r="AM136" t="n">
         <v>-0.2400586862921742</v>
       </c>
       <c r="AN136" t="n">
-        <v>2.539086736215393</v>
+        <v>2.539086476324756</v>
       </c>
       <c r="AO136" t="n">
         <v>56.44270056481461</v>
@@ -26682,7 +26682,7 @@
         <v>0.7728977561085575</v>
       </c>
       <c r="AY136" t="n">
-        <v>329.1336817760302</v>
+        <v>329.1336111055811</v>
       </c>
       <c r="AZ136" t="inlineStr"/>
       <c r="BA136" t="n">
@@ -26824,28 +26824,28 @@
         <v>425.0384173583984</v>
       </c>
       <c r="AG137" t="n">
-        <v>355.9967967224121</v>
+        <v>355.9967970275879</v>
       </c>
       <c r="AH137" t="n">
         <v>-0.04890950208124201</v>
       </c>
       <c r="AI137" t="n">
-        <v>0.1355439254561979</v>
+        <v>0.1355439244827608</v>
       </c>
       <c r="AJ137" t="n">
-        <v>0.1939388816743242</v>
+        <v>0.1939388806508284</v>
       </c>
       <c r="AK137" t="n">
         <v>477.5700073242188</v>
       </c>
       <c r="AL137" t="n">
-        <v>224.8433685302734</v>
+        <v>224.8433532714844</v>
       </c>
       <c r="AM137" t="n">
         <v>-0.1535272445918957</v>
       </c>
       <c r="AN137" t="n">
-        <v>0.7979182692487141</v>
+        <v>0.7979183912627974</v>
       </c>
       <c r="AO137" t="n">
         <v>43.28138535718739</v>
@@ -26872,13 +26872,13 @@
         <v>0.691585023241559</v>
       </c>
       <c r="AW137" t="n">
-        <v>2.791998179355002</v>
+        <v>2.791997365218088</v>
       </c>
       <c r="AX137" t="n">
         <v>0.2713572083409475</v>
       </c>
       <c r="AY137" t="n">
-        <v>128.4468101090132</v>
+        <v>128.4468199916494</v>
       </c>
       <c r="AZ137" t="inlineStr"/>
       <c r="BA137" t="n">
@@ -27070,7 +27070,7 @@
         <v>1.47000023332949</v>
       </c>
       <c r="AY138" t="n">
-        <v>2.14777176669351</v>
+        <v>2.147773008082629</v>
       </c>
       <c r="AZ138" t="inlineStr"/>
       <c r="BA138" t="n">
@@ -27256,13 +27256,13 @@
         <v>1.187591537445895</v>
       </c>
       <c r="AW139" t="n">
-        <v>0.9207914207858792</v>
+        <v>0.9207916108660055</v>
       </c>
       <c r="AX139" t="n">
         <v>0.2002509097457066</v>
       </c>
       <c r="AY139" t="n">
-        <v>291.1635547841262</v>
+        <v>291.1634860696471</v>
       </c>
       <c r="AZ139" t="inlineStr"/>
       <c r="BA139" t="n">
@@ -27448,7 +27448,7 @@
         <v>0.9113236904383977</v>
       </c>
       <c r="AW140" t="n">
-        <v>1.437046192777261</v>
+        <v>1.437046652452283</v>
       </c>
       <c r="AX140" t="n">
         <v>0.4295239497740109</v>
@@ -28036,7 +28036,7 @@
         <v>0.1509272838144393</v>
       </c>
       <c r="AY143" t="n">
-        <v>39.01595732951284</v>
+        <v>39.01596067199541</v>
       </c>
       <c r="AZ143" t="inlineStr"/>
       <c r="BA143" t="n">
@@ -28420,7 +28420,7 @@
         <v>0.1468398849685471</v>
       </c>
       <c r="AY145" t="n">
-        <v>22.82153399388024</v>
+        <v>22.8215319510855</v>
       </c>
       <c r="AZ145" t="inlineStr"/>
       <c r="BA145" t="n">
@@ -28606,13 +28606,13 @@
         <v>0.533227660593907</v>
       </c>
       <c r="AW146" t="n">
-        <v>6.874586492139127</v>
+        <v>6.874587164144842</v>
       </c>
       <c r="AX146" t="n">
         <v>0.1771232044903688</v>
       </c>
       <c r="AY146" t="n">
-        <v>35.67136828779302</v>
+        <v>35.67135735747551</v>
       </c>
       <c r="AZ146" t="inlineStr"/>
       <c r="BA146" t="n">
@@ -28804,7 +28804,7 @@
         <v>0.2379694722150727</v>
       </c>
       <c r="AY147" t="n">
-        <v>63.26621758059885</v>
+        <v>63.2662058883862</v>
       </c>
       <c r="AZ147" t="inlineStr"/>
       <c r="BA147" t="n">
@@ -28946,16 +28946,16 @@
         <v>142.0012661743164</v>
       </c>
       <c r="AG148" t="n">
-        <v>130.2103258132935</v>
+        <v>130.2103253936768</v>
       </c>
       <c r="AH148" t="n">
         <v>0.03280771794016291</v>
       </c>
       <c r="AI148" t="n">
-        <v>0.126331592721785</v>
+        <v>0.126331596351509</v>
       </c>
       <c r="AJ148" t="n">
-        <v>0.0905530363078102</v>
+        <v>0.09055303982223406</v>
       </c>
       <c r="AK148" t="n">
         <v>148.2100067138672</v>
@@ -28988,19 +28988,19 @@
         <v>0.01368769634476918</v>
       </c>
       <c r="AU148" t="n">
-        <v>0.2369541783693405</v>
+        <v>0.2369542579643125</v>
       </c>
       <c r="AV148" t="n">
         <v>0.4049444227864603</v>
       </c>
       <c r="AW148" t="n">
-        <v>1.278489624781521</v>
+        <v>1.278490164916859</v>
       </c>
       <c r="AX148" t="n">
         <v>0.2061088032863247</v>
       </c>
       <c r="AY148" t="n">
-        <v>46.49161688939405</v>
+        <v>46.49160955621576</v>
       </c>
       <c r="AZ148" t="inlineStr"/>
       <c r="BA148" t="n">
@@ -29115,10 +29115,10 @@
         </is>
       </c>
       <c r="Z149" t="n">
-        <v>1.348672270774841</v>
+        <v>1.348199486732483</v>
       </c>
       <c r="AA149" t="n">
-        <v>163594765056.6885</v>
+        <v>163537416065.3818</v>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
@@ -29132,22 +29132,22 @@
         <v>38.1</v>
       </c>
       <c r="AE149" t="n">
-        <v>1463</v>
+        <v>1467.800048828125</v>
       </c>
       <c r="AF149" t="n">
-        <v>1367.099990234375</v>
+        <v>1372.2919921875</v>
       </c>
       <c r="AG149" t="n">
-        <v>1236.712127685547</v>
+        <v>1238.431374511719</v>
       </c>
       <c r="AH149" t="n">
-        <v>0.0701484971477353</v>
+        <v>0.06959747428707241</v>
       </c>
       <c r="AI149" t="n">
-        <v>0.1829753806473469</v>
+        <v>0.1852090305826113</v>
       </c>
       <c r="AJ149" t="n">
-        <v>0.1054310535410075</v>
+        <v>0.1080888456403641</v>
       </c>
       <c r="AK149" t="n">
         <v>1504.199951171875</v>
@@ -29156,43 +29156,43 @@
         <v>1025.954956054688</v>
       </c>
       <c r="AM149" t="n">
-        <v>-0.02738994316532017</v>
+        <v>-0.02419884558259155</v>
       </c>
       <c r="AN149" t="n">
-        <v>0.4259885303600173</v>
+        <v>0.430667145926712</v>
       </c>
       <c r="AO149" t="n">
-        <v>53.68042642050985</v>
+        <v>58.29113990063635</v>
       </c>
       <c r="AP149" t="n">
-        <v>22157366</v>
+        <v>26126502</v>
       </c>
       <c r="AQ149" t="n">
-        <v>26205716.18</v>
+        <v>26285098.9</v>
       </c>
       <c r="AR149" t="n">
-        <v>0.8455165219605916</v>
+        <v>0.9939662810247216</v>
       </c>
       <c r="AS149" t="n">
-        <v>-0.008270032250328851</v>
+        <v>-0.02419884558259155</v>
       </c>
       <c r="AT149" t="n">
-        <v>0.2199800363320028</v>
+        <v>0.2211314882097546</v>
       </c>
       <c r="AU149" t="n">
-        <v>0.208145582755616</v>
+        <v>0.1929009000464592</v>
       </c>
       <c r="AV149" t="n">
-        <v>0.3648552141964394</v>
+        <v>0.3783335488373329</v>
       </c>
       <c r="AW149" t="n">
-        <v>13.14037526592705</v>
+        <v>13.23353587354353</v>
       </c>
       <c r="AX149" t="n">
-        <v>0.2222759454924448</v>
+        <v>0.2262861876112461</v>
       </c>
       <c r="AY149" t="n">
-        <v>10.7495337460738</v>
+        <v>10.78808064208778</v>
       </c>
       <c r="AZ149" t="inlineStr"/>
       <c r="BA149" t="n">
@@ -29382,13 +29382,13 @@
         <v>0.5586695418166461</v>
       </c>
       <c r="AW150" t="n">
-        <v>1.862105979788717</v>
+        <v>1.862105480808089</v>
       </c>
       <c r="AX150" t="n">
         <v>0.111895732141569</v>
       </c>
       <c r="AY150" t="n">
-        <v>682.8720514098509</v>
+        <v>682.8721070504919</v>
       </c>
       <c r="AZ150" t="inlineStr"/>
       <c r="BA150" t="n">
@@ -29574,13 +29574,13 @@
         <v>0.4769268287346409</v>
       </c>
       <c r="AW151" t="n">
-        <v>2.127608782170785</v>
+        <v>2.127608480268487</v>
       </c>
       <c r="AX151" t="n">
         <v>0.4321714861141548</v>
       </c>
       <c r="AY151" t="n">
-        <v>7.13183864369125</v>
+        <v>7.131839153913218</v>
       </c>
       <c r="AZ151" t="inlineStr"/>
       <c r="BA151" t="n">
@@ -29709,7 +29709,7 @@
         <v>39825</v>
       </c>
       <c r="AD152" t="n">
-        <v>17.5</v>
+        <v>17.6</v>
       </c>
       <c r="AE152" t="n">
         <v>84.40000152587891</v>
@@ -29772,7 +29772,7 @@
         <v>0.2800920025008276</v>
       </c>
       <c r="AY152" t="n">
-        <v>-0.1180077401808445</v>
+        <v>-0.1180078105005644</v>
       </c>
       <c r="AZ152" t="inlineStr"/>
       <c r="BA152" t="n">
@@ -29914,16 +29914,16 @@
         <v>117.4010284423828</v>
       </c>
       <c r="AG153" t="n">
-        <v>88.86939746856689</v>
+        <v>88.86939708709717</v>
       </c>
       <c r="AH153" t="n">
         <v>-0.01201889453043226</v>
       </c>
       <c r="AI153" t="n">
-        <v>0.3051736724646434</v>
+        <v>0.3051736780670695</v>
       </c>
       <c r="AJ153" t="n">
-        <v>0.321051248084669</v>
+        <v>0.3210512537552492</v>
       </c>
       <c r="AK153" t="n">
         <v>129.5154876708984</v>
@@ -29962,13 +29962,13 @@
         <v>0.7390090020325177</v>
       </c>
       <c r="AW153" t="n">
-        <v>1.404785166329207</v>
+        <v>1.404785356521161</v>
       </c>
       <c r="AX153" t="n">
         <v>0.5393841507954493</v>
       </c>
       <c r="AY153" t="n">
-        <v>2340.599215812621</v>
+        <v>2340.59851140415</v>
       </c>
       <c r="AZ153" t="inlineStr"/>
       <c r="BA153" t="n">
@@ -30158,13 +30158,13 @@
         <v>2.0939452544059</v>
       </c>
       <c r="AW154" t="n">
-        <v>8.127436470385629</v>
+        <v>8.12743725436774</v>
       </c>
       <c r="AX154" t="n">
         <v>2.200923612779535</v>
       </c>
       <c r="AY154" t="n">
-        <v>35.97816306081483</v>
+        <v>35.97816627772691</v>
       </c>
       <c r="AZ154" t="inlineStr"/>
       <c r="BA154" t="n">
@@ -30502,28 +30502,28 @@
         <v>45.91150299072265</v>
       </c>
       <c r="AG156" t="n">
-        <v>29.27725481987</v>
+        <v>29.27725478172302</v>
       </c>
       <c r="AH156" t="n">
         <v>0.04331155387263341</v>
       </c>
       <c r="AI156" t="n">
-        <v>0.6360824066527562</v>
+        <v>0.6360824087844994</v>
       </c>
       <c r="AJ156" t="n">
-        <v>0.5681628374379986</v>
+        <v>0.5681628394812457</v>
       </c>
       <c r="AK156" t="n">
         <v>55.98620223999023</v>
       </c>
       <c r="AL156" t="n">
-        <v>19.40578269958496</v>
+        <v>19.40578460693359</v>
       </c>
       <c r="AM156" t="n">
         <v>-0.1444320277244213</v>
       </c>
       <c r="AN156" t="n">
-        <v>1.468336488530471</v>
+        <v>1.468336245923521</v>
       </c>
       <c r="AO156" t="n">
         <v>51.60818672682437</v>
@@ -30550,7 +30550,7 @@
         <v>1.363351492573201</v>
       </c>
       <c r="AW156" t="n">
-        <v>2.823327976932206</v>
+        <v>2.823328559005576</v>
       </c>
       <c r="AX156" t="n">
         <v>1.000410064453721</v>
@@ -30890,16 +30890,16 @@
         <v>347.8120007324219</v>
       </c>
       <c r="AG158" t="n">
-        <v>278.0893357086181</v>
+        <v>278.0893355560303</v>
       </c>
       <c r="AH158" t="n">
         <v>-0.09419460188395734</v>
       </c>
       <c r="AI158" t="n">
-        <v>0.1329092753239483</v>
+        <v>0.1329092759455766</v>
       </c>
       <c r="AJ158" t="n">
-        <v>0.2507203839591285</v>
+        <v>0.2507203846454</v>
       </c>
       <c r="AK158" t="n">
         <v>385.6300048828125</v>
@@ -30938,13 +30938,13 @@
         <v>0.4135468331375087</v>
       </c>
       <c r="AW158" t="n">
-        <v>4.570772965026375</v>
+        <v>4.570772213504777</v>
       </c>
       <c r="AX158" t="n">
         <v>0.3112865848457733</v>
       </c>
       <c r="AY158" t="n">
-        <v>425.3359984668344</v>
+        <v>425.3360672424857</v>
       </c>
       <c r="AZ158" t="inlineStr"/>
       <c r="BA158" t="n">
@@ -31130,13 +31130,13 @@
         <v>0.1113162409550188</v>
       </c>
       <c r="AW159" t="n">
-        <v>3.645061112829704</v>
+        <v>3.645061677551346</v>
       </c>
       <c r="AX159" t="n">
         <v>0.0972743532806668</v>
       </c>
       <c r="AY159" t="n">
-        <v>14.32384704383416</v>
+        <v>14.32384858031512</v>
       </c>
       <c r="AZ159" t="inlineStr"/>
       <c r="BA159" t="n">
@@ -32564,28 +32564,28 @@
         <v>395.0326873779297</v>
       </c>
       <c r="AG5" t="n">
-        <v>364.8947802734375</v>
+        <v>364.8947793579102</v>
       </c>
       <c r="AH5" t="n">
         <v>-0.01456256351041951</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.06682808257105255</v>
+        <v>0.06682808524774275</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.0825934179762946</v>
+        <v>0.08259342069254005</v>
       </c>
       <c r="AK5" t="n">
         <v>480.8090515136719</v>
       </c>
       <c r="AL5" t="n">
-        <v>286.5404968261719</v>
+        <v>286.54052734375</v>
       </c>
       <c r="AM5" t="n">
         <v>-0.1903646623253563</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.3585514197508051</v>
+        <v>0.3585512750602811</v>
       </c>
       <c r="AO5" t="n">
         <v>52.42782072288501</v>
@@ -32606,13 +32606,13 @@
         <v>-0.07449649339109377</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.1793358939996921</v>
+        <v>0.1793360030339692</v>
       </c>
       <c r="AV5" t="n">
         <v>0.3351456710249647</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.866961023049903</v>
+        <v>7.866961793505519</v>
       </c>
       <c r="AX5" t="n">
         <v>0.1239687532078804</v>
@@ -32966,28 +32966,28 @@
         <v>337.834677734375</v>
       </c>
       <c r="AG7" t="n">
-        <v>240.7902880859375</v>
+        <v>240.7902875518799</v>
       </c>
       <c r="AH7" t="n">
         <v>-0.1326527194343827</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.2169094997265575</v>
+        <v>0.2169095024255858</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.4030245173916758</v>
+        <v>0.4030245205034952</v>
       </c>
       <c r="AK7" t="n">
         <v>433.3299865722656</v>
       </c>
       <c r="AL7" t="n">
-        <v>94.31798553466797</v>
+        <v>94.31800079345703</v>
       </c>
       <c r="AM7" t="n">
         <v>-0.3237948028210009</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.106724421144131</v>
+        <v>2.1067239185375</v>
       </c>
       <c r="AO7" t="n">
         <v>40.36351406493076</v>
@@ -33011,16 +33011,16 @@
         <v>0.2575074967410385</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.106724421144131</v>
+        <v>2.1067239185375</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.820117257714903</v>
+        <v>3.820118165116153</v>
       </c>
       <c r="AX7" t="n">
         <v>0.5863920287166053</v>
       </c>
       <c r="AY7" t="n">
-        <v>1553.21938824062</v>
+        <v>1553.219265398452</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
@@ -33168,16 +33168,16 @@
         <v>239.4106005859375</v>
       </c>
       <c r="AG8" t="n">
-        <v>134.9904850387573</v>
+        <v>134.9904849624634</v>
       </c>
       <c r="AH8" t="n">
         <v>-0.2165760534430962</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.3894312440224443</v>
+        <v>0.3894312448077235</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.7735368571881192</v>
+        <v>0.7735368581904871</v>
       </c>
       <c r="AK8" t="n">
         <v>316.3519592285156</v>
@@ -33216,13 +33216,13 @@
         <v>1.338678565098987</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.241313527687087</v>
+        <v>2.241313741366151</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.101300259381754</v>
+        <v>1.101300438989937</v>
       </c>
       <c r="AY8" t="n">
-        <v>14.46337927561398</v>
+        <v>14.46337562815987</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
@@ -33237,7 +33237,7 @@
         <v>0.125</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.1376625324227193</v>
+        <v>0.1376625548737422</v>
       </c>
     </row>
     <row r="9">
@@ -33489,7 +33489,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6932683064197428</v>
+        <v>0.6932683288707657</v>
       </c>
     </row>
     <row r="5">
@@ -33499,7 +33499,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.196210511569676</v>
+        <v>1.196210448743847</v>
       </c>
     </row>
   </sheetData>
@@ -33676,31 +33676,31 @@
         <v>1.487222033541388</v>
       </c>
       <c r="N2" t="n">
-        <v>7.373393335113946</v>
+        <v>7.373393213553968</v>
       </c>
       <c r="O2" t="n">
-        <v>5.677973917183394</v>
+        <v>5.677973205632458</v>
       </c>
       <c r="P2" t="n">
-        <v>6.085796100202613</v>
+        <v>6.085796007580738</v>
       </c>
       <c r="Q2" t="n">
-        <v>6.254485965788808</v>
+        <v>6.254486498204489</v>
       </c>
       <c r="R2" t="n">
-        <v>4.000754648749874</v>
+        <v>4.000755102450499</v>
       </c>
       <c r="S2" t="n">
-        <v>7.632499923285284</v>
+        <v>7.632500591724625</v>
       </c>
       <c r="T2" t="n">
-        <v>286.5598107553797</v>
+        <v>286.5598360010757</v>
       </c>
       <c r="U2" t="n">
-        <v>46.61419953126968</v>
+        <v>46.6142065628456</v>
       </c>
       <c r="V2" t="n">
-        <v>335.8779968428382</v>
+        <v>335.8779891637088</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -33742,40 +33742,40 @@
         <v>0.625</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5236063867878719</v>
+        <v>0.5236063706838759</v>
       </c>
       <c r="L3" t="n">
         <v>0.3051053182967278</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2437277624278005</v>
+        <v>0.2437277104416319</v>
       </c>
       <c r="N3" t="n">
-        <v>1.097259088562221</v>
+        <v>1.097259061149845</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5947725043639559</v>
+        <v>0.5947724492283769</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5529723049976432</v>
+        <v>0.5529722589982131</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.395926085211326</v>
+        <v>4.395925801828675</v>
       </c>
       <c r="R3" t="n">
         <v>1.389959761529957</v>
       </c>
       <c r="S3" t="n">
-        <v>5.115306725406217</v>
+        <v>5.115305899113053</v>
       </c>
       <c r="T3" t="n">
-        <v>1199.411517756071</v>
+        <v>1199.411452260726</v>
       </c>
       <c r="U3" t="n">
         <v>293.4368324549614</v>
       </c>
       <c r="V3" t="n">
-        <v>3616.56425075315</v>
+        <v>3616.563935107883</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -33793,10 +33793,10 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>1449.381132751935</v>
+        <v>1449.323783760628</v>
       </c>
       <c r="D4" t="n">
-        <v>90.58632079699593</v>
+        <v>90.58273648503926</v>
       </c>
       <c r="E4" t="n">
         <v>39.89323776000001</v>
@@ -33808,7 +33808,7 @@
         <v>85</v>
       </c>
       <c r="H4" t="n">
-        <v>84.36822945870995</v>
+        <v>84.36780876505738</v>
       </c>
       <c r="I4" t="n">
         <v>11</v>
@@ -33817,40 +33817,40 @@
         <v>0.6875</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4077960338188118</v>
+        <v>0.4080466739512369</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2301227088537587</v>
+        <v>0.2321278299131594</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7110846061998466</v>
+        <v>0.7115564519842057</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6287457734642369</v>
+        <v>0.6295881693792927</v>
       </c>
       <c r="O4" t="n">
         <v>0.5050772446642739</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9247766001478096</v>
+        <v>0.926319611427821</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.17172383197651</v>
+        <v>7.17754648124664</v>
       </c>
       <c r="R4" t="n">
-        <v>4.135651065113308</v>
+        <v>4.135650689352509</v>
       </c>
       <c r="S4" t="n">
-        <v>5.915310458582025</v>
+        <v>5.92553676029209</v>
       </c>
       <c r="T4" t="n">
-        <v>240.9692250839042</v>
+        <v>240.9715964677431</v>
       </c>
       <c r="U4" t="n">
-        <v>35.82476567430393</v>
+        <v>35.82476181760121</v>
       </c>
       <c r="V4" t="n">
-        <v>818.9051144469244</v>
+        <v>818.9412250932431</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -33892,40 +33892,40 @@
         <v>0.5333333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4661379095491973</v>
+        <v>0.4661378951904238</v>
       </c>
       <c r="L5" t="n">
         <v>0.4295239497740109</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4004101106721831</v>
+        <v>0.4004100889792749</v>
       </c>
       <c r="N5" t="n">
-        <v>1.16284789345855</v>
+        <v>1.162847871584945</v>
       </c>
       <c r="O5" t="n">
-        <v>1.093197152755206</v>
+        <v>1.093196969908734</v>
       </c>
       <c r="P5" t="n">
-        <v>1.029401650794422</v>
+        <v>1.029401634064357</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.238781414286464</v>
+        <v>3.238781312614493</v>
       </c>
       <c r="R5" t="n">
-        <v>2.805211581496009</v>
+        <v>2.805211174427552</v>
       </c>
       <c r="S5" t="n">
-        <v>3.007935781912356</v>
+        <v>3.007935246730497</v>
       </c>
       <c r="T5" t="n">
-        <v>827.5960964319517</v>
+        <v>827.5960061597065</v>
       </c>
       <c r="U5" t="n">
-        <v>39.01595732951284</v>
+        <v>39.01596067199541</v>
       </c>
       <c r="V5" t="n">
-        <v>1143.676161707149</v>
+        <v>1143.676035387181</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -33976,31 +33976,31 @@
         <v>1.520616717238965</v>
       </c>
       <c r="N6" t="n">
-        <v>3.615176902822783</v>
+        <v>3.615176934887917</v>
       </c>
       <c r="O6" t="n">
-        <v>4.317335419149967</v>
+        <v>4.317335833735327</v>
       </c>
       <c r="P6" t="n">
-        <v>3.511933917874787</v>
+        <v>3.511933972332394</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.167919368411661</v>
+        <v>4.167919367499316</v>
       </c>
       <c r="R6" t="n">
-        <v>4.501932435366861</v>
+        <v>4.501932024947141</v>
       </c>
       <c r="S6" t="n">
-        <v>4.981654033740928</v>
+        <v>4.981653869922702</v>
       </c>
       <c r="T6" t="n">
-        <v>29.54664578347294</v>
+        <v>29.54664132587838</v>
       </c>
       <c r="U6" t="n">
-        <v>23.0566558118161</v>
+        <v>23.05664944741603</v>
       </c>
       <c r="V6" t="n">
-        <v>42.67338077659225</v>
+        <v>42.67337322557533</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -34060,22 +34060,22 @@
         <v>0.1484067181638313</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.235463059387899</v>
+        <v>1.235463023242696</v>
       </c>
       <c r="R7" t="n">
-        <v>1.32673844013692</v>
+        <v>1.326738367846514</v>
       </c>
       <c r="S7" t="n">
-        <v>1.180841614540481</v>
+        <v>1.180841531909729</v>
       </c>
       <c r="T7" t="n">
-        <v>84.68297981337419</v>
+        <v>84.682973762728</v>
       </c>
       <c r="U7" t="n">
-        <v>70.5759453674473</v>
+        <v>70.57593474939974</v>
       </c>
       <c r="V7" t="n">
-        <v>64.9206402737959</v>
+        <v>64.92063769459392</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -34117,40 +34117,40 @@
         <v>0.4285714285714285</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4396483923864443</v>
+        <v>0.4396484008120488</v>
       </c>
       <c r="L8" t="n">
         <v>0.4039938589821908</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2773548085565402</v>
+        <v>0.2773548205084115</v>
       </c>
       <c r="N8" t="n">
-        <v>1.394421872214809</v>
+        <v>1.394421854347689</v>
       </c>
       <c r="O8" t="n">
-        <v>1.210013631546743</v>
+        <v>1.210013496779354</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8447022040631077</v>
+        <v>0.8447021911941218</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.086546198078717</v>
+        <v>6.086546397107725</v>
       </c>
       <c r="R8" t="n">
         <v>2.900445232890659</v>
       </c>
       <c r="S8" t="n">
-        <v>7.810626856850606</v>
+        <v>7.81062742218959</v>
       </c>
       <c r="T8" t="n">
-        <v>171.5432108145982</v>
+        <v>171.5432099832935</v>
       </c>
       <c r="U8" t="n">
-        <v>25.42466632527602</v>
+        <v>25.4246633407812</v>
       </c>
       <c r="V8" t="n">
-        <v>307.3275565198109</v>
+        <v>307.3275478782226</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -34168,10 +34168,10 @@
         <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>1624.713494625412</v>
+        <v>1624.713440151741</v>
       </c>
       <c r="D9" t="n">
-        <v>73.85061339206418</v>
+        <v>73.85061091598824</v>
       </c>
       <c r="E9" t="n">
         <v>46.26578765953126</v>
@@ -34183,7 +34183,7 @@
         <v>65</v>
       </c>
       <c r="H9" t="n">
-        <v>67.28765346446193</v>
+        <v>67.28765504993045</v>
       </c>
       <c r="I9" t="n">
         <v>3</v>
@@ -34198,34 +34198,34 @@
         <v>0.402050092650777</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3923980984364109</v>
+        <v>0.392398115733545</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6991056711254183</v>
+        <v>0.6991056747090143</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5282815199291984</v>
+        <v>0.5282815874678541</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6296318712486256</v>
+        <v>0.629631880234633</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.590774630062592</v>
+        <v>2.590774687991909</v>
       </c>
       <c r="R9" t="n">
-        <v>1.430576259689877</v>
+        <v>1.430576284980539</v>
       </c>
       <c r="S9" t="n">
-        <v>2.359514122467846</v>
+        <v>2.35951422662578</v>
       </c>
       <c r="T9" t="n">
-        <v>172.5372609819361</v>
+        <v>172.5371870260775</v>
       </c>
       <c r="U9" t="n">
-        <v>28.55358832716108</v>
+        <v>28.55359429352259</v>
       </c>
       <c r="V9" t="n">
-        <v>329.0994248213339</v>
+        <v>329.0992809033211</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -34267,40 +34267,40 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4090320609395321</v>
+        <v>0.4090320811946033</v>
       </c>
       <c r="L10" t="n">
         <v>-0.05409442812676296</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05166678778061725</v>
+        <v>0.0516668330309766</v>
       </c>
       <c r="N10" t="n">
-        <v>0.521896191669365</v>
+        <v>0.5218961942924416</v>
       </c>
       <c r="O10" t="n">
         <v>0.09139485689923443</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2463653416642398</v>
+        <v>0.2463653425350221</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4685509865375918</v>
+        <v>0.4685509917642987</v>
       </c>
       <c r="R10" t="n">
         <v>0.4879405610426889</v>
       </c>
       <c r="S10" t="n">
-        <v>0.884028211733101</v>
+        <v>0.8840281230046564</v>
       </c>
       <c r="T10" t="n">
-        <v>1172.168653334773</v>
+        <v>1172.168809611533</v>
       </c>
       <c r="U10" t="n">
         <v>11.105251085561</v>
       </c>
       <c r="V10" t="n">
-        <v>2750.488102615312</v>
+        <v>2750.488598613675</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -34342,13 +34342,13 @@
         <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2274072951337713</v>
+        <v>0.2274072868895542</v>
       </c>
       <c r="L11" t="n">
         <v>0.08524295147622662</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2378269414381068</v>
+        <v>0.23782693522514</v>
       </c>
       <c r="N11" t="n">
         <v>0.26352820268963</v>
@@ -34360,22 +34360,22 @@
         <v>0.3915495269025548</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.500609859096636</v>
+        <v>1.500609822684275</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5418338925423973</v>
+        <v>0.541834095708465</v>
       </c>
       <c r="S11" t="n">
-        <v>5.848723148678534</v>
+        <v>5.848722668955427</v>
       </c>
       <c r="T11" t="n">
-        <v>56.44334676789794</v>
+        <v>56.44332749780929</v>
       </c>
       <c r="U11" t="n">
         <v>7.82979129246751</v>
       </c>
       <c r="V11" t="n">
-        <v>242.7125033942211</v>
+        <v>242.7123832486824</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -34444,13 +34444,13 @@
         <v>0.3865273555916469</v>
       </c>
       <c r="T12" t="n">
-        <v>11.38147439243967</v>
+        <v>11.38146657702896</v>
       </c>
       <c r="U12" t="n">
-        <v>11.38147439243967</v>
+        <v>11.38146657702896</v>
       </c>
       <c r="V12" t="n">
-        <v>21.57047814971345</v>
+        <v>21.57046343653544</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -34492,40 +34492,40 @@
         <v>0.1052631578947368</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.04061449288722497</v>
+        <v>-0.04061449727058506</v>
       </c>
       <c r="L13" t="n">
         <v>-0.06978832152162695</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1278003763286081</v>
+        <v>0.1278003729372724</v>
       </c>
       <c r="N13" t="n">
-        <v>0.06861028574650743</v>
+        <v>0.06861028946532202</v>
       </c>
       <c r="O13" t="n">
         <v>0.1072664702412918</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2073005435773317</v>
+        <v>0.2073005633204435</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.428073761410561</v>
+        <v>2.42807380505512</v>
       </c>
       <c r="R13" t="n">
-        <v>1.789217600777946</v>
+        <v>1.789217492098607</v>
       </c>
       <c r="S13" t="n">
-        <v>2.058729284250258</v>
+        <v>2.058729349269009</v>
       </c>
       <c r="T13" t="n">
-        <v>76.08588053115872</v>
+        <v>76.08586855637672</v>
       </c>
       <c r="U13" t="n">
         <v>12.07063063066094</v>
       </c>
       <c r="V13" t="n">
-        <v>109.7852253597317</v>
+        <v>109.7851894578004</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -34567,13 +34567,13 @@
         <v>0.1</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0740318919749057</v>
+        <v>0.07403188977716091</v>
       </c>
       <c r="L14" t="n">
-        <v>0.05528302397726015</v>
+        <v>0.05528308237332413</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2174590830873701</v>
+        <v>-0.2174590856016937</v>
       </c>
       <c r="N14" t="n">
         <v>0.2113013069744836</v>
@@ -34585,22 +34585,22 @@
         <v>0.2022501164267818</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5381103179906815</v>
+        <v>0.5381102021832205</v>
       </c>
       <c r="R14" t="n">
-        <v>0.404897436167146</v>
+        <v>0.4048972955705102</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6798185747011379</v>
+        <v>0.6798184244731462</v>
       </c>
       <c r="T14" t="n">
-        <v>16.47993602702629</v>
+        <v>16.47993508105263</v>
       </c>
       <c r="U14" t="n">
-        <v>3.28016454195182</v>
+        <v>3.280164558002526</v>
       </c>
       <c r="V14" t="n">
-        <v>3.622312833503379</v>
+        <v>3.622312682105172</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>

--- a/company_radar_output.xlsx
+++ b/company_radar_output.xlsx
@@ -828,16 +828,16 @@
         <v>23.34882186889648</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.45783304691315</v>
+        <v>13.457833070755</v>
       </c>
       <c r="AH2" t="n">
         <v>0.2034868628169373</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.088003342255393</v>
+        <v>1.088003338556292</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.7349614746671311</v>
+        <v>0.7349614715934785</v>
       </c>
       <c r="AK2" t="n">
         <v>28.10000038146973</v>
@@ -873,16 +873,16 @@
         <v>2.207374930279158</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.833400854819125</v>
+        <v>1.833400582354729</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.926403714980666</v>
+        <v>2.926403453371088</v>
       </c>
       <c r="AX2" t="n">
         <v>1.982354855962263</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.715034855509677</v>
+        <v>3.715034478255943</v>
       </c>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
@@ -1410,25 +1410,25 @@
         <v>407.0119970703125</v>
       </c>
       <c r="AG5" t="n">
-        <v>431.8307922363281</v>
+        <v>431.830792388916</v>
       </c>
       <c r="AH5" t="n">
         <v>0.2284404239514353</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.1578377439113823</v>
+        <v>0.1578377435022591</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.0574734261942883</v>
+        <v>-0.05747342652733112</v>
       </c>
       <c r="AK5" t="n">
-        <v>538.6585693359375</v>
+        <v>538.6585083007812</v>
       </c>
       <c r="AL5" t="n">
         <v>352.8299865722656</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.07178680764186751</v>
+        <v>-0.07178670246644314</v>
       </c>
       <c r="AN5" t="n">
         <v>0.4170847412709024</v>
@@ -1458,13 +1458,13 @@
         <v>-0.03236377991410644</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.8291815677686039</v>
+        <v>0.8291819762125663</v>
       </c>
       <c r="AX5" t="n">
         <v>0.06190338844962495</v>
       </c>
       <c r="AY5" t="n">
-        <v>8455.437218620273</v>
+        <v>8455.443612364279</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -1606,28 +1606,28 @@
         <v>356.4744580078125</v>
       </c>
       <c r="AG6" t="n">
-        <v>328.8279871368408</v>
+        <v>328.827986831665</v>
       </c>
       <c r="AH6" t="n">
         <v>-0.00609993273289744</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.07746299479529339</v>
+        <v>0.07746299579525573</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.08407578415600825</v>
+        <v>0.08407578516210767</v>
       </c>
       <c r="AK6" t="n">
         <v>402.3796691894531</v>
       </c>
       <c r="AL6" t="n">
-        <v>195.9609680175781</v>
+        <v>195.9609832763672</v>
       </c>
       <c r="AM6" t="n">
         <v>-0.1194883466486646</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.8080130516664281</v>
+        <v>0.8080129108828429</v>
       </c>
       <c r="AO6" t="n">
         <v>50.93363442243781</v>
@@ -1651,16 +1651,16 @@
         <v>0.09880809860337991</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.8080130516664281</v>
+        <v>0.8080129108828429</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.65057271876519</v>
+        <v>1.650572416193473</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.1256898420900709</v>
+        <v>0.1256899512382423</v>
       </c>
       <c r="AY6" t="n">
-        <v>141.3497231107654</v>
+        <v>141.3497094749168</v>
       </c>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
@@ -2038,13 +2038,13 @@
         <v>-0.1177077399345985</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.05654278436729876</v>
+        <v>-0.0565426709000818</v>
       </c>
       <c r="AX8" t="n">
         <v>-0.2225065061541112</v>
       </c>
       <c r="AY8" t="n">
-        <v>679.7993122282882</v>
+        <v>679.7993699267488</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
@@ -2380,25 +2380,25 @@
         <v>159.9215922546387</v>
       </c>
       <c r="AG10" t="n">
-        <v>178.203175163269</v>
+        <v>178.2031758499145</v>
       </c>
       <c r="AH10" t="n">
         <v>-0.08067445927898786</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.1749866177313519</v>
+        <v>-0.1749866209102612</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.1025884240944688</v>
+        <v>-0.10258842755234</v>
       </c>
       <c r="AK10" t="n">
-        <v>324.6299743652344</v>
+        <v>324.6299438476562</v>
       </c>
       <c r="AL10" t="n">
         <v>114.9899978637695</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.5471151283551783</v>
+        <v>-0.5471150857807032</v>
       </c>
       <c r="AN10" t="n">
         <v>0.2785460214256015</v>
@@ -2425,16 +2425,16 @@
         <v>0.03659668987607123</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.4037624015785307</v>
+        <v>-0.4037624384747892</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.7953337659355131</v>
+        <v>0.7953339332001303</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.241540631379384</v>
+        <v>-0.2415405716747124</v>
       </c>
       <c r="AY10" t="n">
-        <v>2925.492751800519</v>
+        <v>2925.49253479111</v>
       </c>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
@@ -2620,13 +2620,13 @@
         <v>0.07134027112471664</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0.318038821848714</v>
+        <v>-0.3180387665849386</v>
       </c>
       <c r="AX11" t="n">
         <v>-0.1679124529486905</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.4533348427124233</v>
+        <v>0.4533347172185427</v>
       </c>
       <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="n">
@@ -2960,25 +2960,25 @@
         <v>599.6241174316406</v>
       </c>
       <c r="AG13" t="n">
-        <v>630.4387203979492</v>
+        <v>630.4387194824219</v>
       </c>
       <c r="AH13" t="n">
         <v>-0.01254809742798724</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.06081280158016189</v>
+        <v>-0.06081280021626811</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.04887803044022676</v>
+        <v>-0.04887802905900118</v>
       </c>
       <c r="AK13" t="n">
-        <v>787.4192504882812</v>
+        <v>787.419189453125</v>
       </c>
       <c r="AL13" t="n">
         <v>525.233154296875</v>
       </c>
       <c r="AM13" t="n">
-        <v>-0.2480499108717823</v>
+        <v>-0.2480498525859394</v>
       </c>
       <c r="AN13" t="n">
         <v>0.1273088355943115</v>
@@ -3008,13 +3008,13 @@
         <v>-0.2202452092657475</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.6971146238663157</v>
+        <v>0.6971147723153619</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.08802725342477469</v>
+        <v>-0.08802733915790817</v>
       </c>
       <c r="AY13" t="n">
-        <v>14.62384113746343</v>
+        <v>14.62384585550811</v>
       </c>
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="n">
@@ -4535,13 +4535,13 @@
         <v>480.8090515136719</v>
       </c>
       <c r="AL21" t="n">
-        <v>287.4934692382812</v>
+        <v>287.4934997558594</v>
       </c>
       <c r="AM21" t="n">
         <v>-0.1103328682790791</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.4878947020917808</v>
+        <v>0.4878945441510174</v>
       </c>
       <c r="AO21" t="n">
         <v>73.57863850003642</v>
@@ -4574,7 +4574,7 @@
         <v>0.2350721494968062</v>
       </c>
       <c r="AY21" t="n">
-        <v>375.6848351306893</v>
+        <v>375.6847165026617</v>
       </c>
       <c r="AZ21" t="inlineStr"/>
       <c r="BA21" t="n">
@@ -4906,16 +4906,16 @@
         <v>259.045598449707</v>
       </c>
       <c r="AG23" t="n">
-        <v>267.1958892822266</v>
+        <v>267.1958905029297</v>
       </c>
       <c r="AH23" t="n">
         <v>-0.08402227175705468</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.1119623905266407</v>
+        <v>-0.1119623945837026</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-0.03050305472293691</v>
+        <v>-0.03050305915215146</v>
       </c>
       <c r="AK23" t="n">
         <v>329.2300109863281</v>
@@ -4954,13 +4954,13 @@
         <v>-0.02722708853905231</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.134213183994234</v>
+        <v>1.134212891084047</v>
       </c>
       <c r="AX23" t="n">
-        <v>-0.1753372390099284</v>
+        <v>-0.1753373264764095</v>
       </c>
       <c r="AY23" t="n">
-        <v>163.237373283137</v>
+        <v>163.237278421473</v>
       </c>
       <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="n">
@@ -5342,13 +5342,13 @@
         <v>0.4296825050364115</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.208946351516505</v>
+        <v>1.208945876270639</v>
       </c>
       <c r="AX25" t="n">
         <v>0.1583046094268865</v>
       </c>
       <c r="AY25" t="n">
-        <v>3189.504521579152</v>
+        <v>3189.503553375435</v>
       </c>
       <c r="AZ25" t="inlineStr"/>
       <c r="BA25" t="n">
@@ -5490,16 +5490,16 @@
         <v>206.0486834716797</v>
       </c>
       <c r="AG26" t="n">
-        <v>193.7998765563965</v>
+        <v>193.7998763275147</v>
       </c>
       <c r="AH26" t="n">
         <v>0.08692762768682938</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.1556251257399226</v>
+        <v>0.1556251271047409</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.06320337831442702</v>
+        <v>0.06320337957009325</v>
       </c>
       <c r="AK26" t="n">
         <v>235.465576171875</v>
@@ -5532,19 +5532,19 @@
         <v>0.04191928560156732</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.2093909416822872</v>
+        <v>0.2093908420309836</v>
       </c>
       <c r="AV26" t="n">
         <v>0.2405725208421641</v>
       </c>
       <c r="AW26" t="n">
-        <v>10.37896871178468</v>
+        <v>10.37897091722595</v>
       </c>
       <c r="AX26" t="n">
         <v>0.187361185794777</v>
       </c>
       <c r="AY26" t="n">
-        <v>5961.875357958157</v>
+        <v>5961.874175104486</v>
       </c>
       <c r="AZ26" t="inlineStr"/>
       <c r="BA26" t="n">
@@ -6318,7 +6318,7 @@
         <v>1.58125949133561</v>
       </c>
       <c r="AY30" t="n">
-        <v>559.0560619587236</v>
+        <v>559.0559240166102</v>
       </c>
       <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="n">
@@ -6460,16 +6460,16 @@
         <v>191.6944421386719</v>
       </c>
       <c r="AG31" t="n">
-        <v>167.8327414703369</v>
+        <v>167.8327410888672</v>
       </c>
       <c r="AH31" t="n">
         <v>-0.1243355898189186</v>
       </c>
       <c r="AI31" t="n">
-        <v>0.0001624184874526868</v>
+        <v>0.0001624207607378025</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.1421754805366886</v>
+        <v>0.1421754831327575</v>
       </c>
       <c r="AK31" t="n">
         <v>250.0962829589844</v>
@@ -6505,16 +6505,16 @@
         <v>0.23461267213624</v>
       </c>
       <c r="AV31" t="n">
-        <v>0.1747634908210198</v>
+        <v>0.1747636162719186</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.2561696443517845</v>
+        <v>0.2561692140327632</v>
       </c>
       <c r="AX31" t="n">
         <v>-0.01976120426501915</v>
       </c>
       <c r="AY31" t="n">
-        <v>496.5357923065977</v>
+        <v>496.5357044080974</v>
       </c>
       <c r="AZ31" t="inlineStr"/>
       <c r="BA31" t="n">
@@ -6700,13 +6700,13 @@
         <v>7.244089019320127</v>
       </c>
       <c r="AW32" t="n">
-        <v>6.795457035334137</v>
+        <v>6.795457598677828</v>
       </c>
       <c r="AX32" t="n">
         <v>4.284672448282133</v>
       </c>
       <c r="AY32" t="n">
-        <v>35.01456177134386</v>
+        <v>35.01456477732709</v>
       </c>
       <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="n">
@@ -6892,13 +6892,13 @@
         <v>5.040586953107727</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.907304293636252</v>
+        <v>5.907304903168351</v>
       </c>
       <c r="AX33" t="n">
         <v>1.674591954577161</v>
       </c>
       <c r="AY33" t="n">
-        <v>26.61096765653703</v>
+        <v>26.61098226599517</v>
       </c>
       <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="n">
@@ -7090,7 +7090,7 @@
         <v>3.369659964302309</v>
       </c>
       <c r="AY34" t="n">
-        <v>130.1906983903958</v>
+        <v>130.1907241710627</v>
       </c>
       <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
@@ -7223,7 +7223,7 @@
         <v>36801</v>
       </c>
       <c r="AD35" t="n">
-        <v>25.8</v>
+        <v>25.9</v>
       </c>
       <c r="AE35" t="n">
         <v>37.38999938964844</v>
@@ -7280,7 +7280,7 @@
         <v>2.810910996767463</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.369886564181203</v>
+        <v>4.369887299668052</v>
       </c>
       <c r="AX35" t="n">
         <v>1.239983728429313</v>
@@ -7418,22 +7418,22 @@
         <v>18.8</v>
       </c>
       <c r="AE36" t="n">
-        <v>147.8000030517578</v>
+        <v>143.6000061035156</v>
       </c>
       <c r="AF36" t="n">
-        <v>171.6540005493164</v>
+        <v>171.7060006713867</v>
       </c>
       <c r="AG36" t="n">
-        <v>83.11650019645691</v>
+        <v>83.68950022697449</v>
       </c>
       <c r="AH36" t="n">
-        <v>-0.1389655785546653</v>
+        <v>-0.1636867346392904</v>
       </c>
       <c r="AI36" t="n">
-        <v>0.7782269790283858</v>
+        <v>0.7158664553385754</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1.065221708608872</v>
+        <v>1.051703023744944</v>
       </c>
       <c r="AK36" t="n">
         <v>239</v>
@@ -7442,13 +7442,13 @@
         <v>18.39999961853027</v>
       </c>
       <c r="AM36" t="n">
-        <v>-0.3815899453901347</v>
+        <v>-0.3991631543785957</v>
       </c>
       <c r="AN36" t="n">
-        <v>7.032609028041032</v>
+        <v>6.804348319599905</v>
       </c>
       <c r="AO36" t="n">
-        <v>44.28341493673315</v>
+        <v>43.37539849751455</v>
       </c>
       <c r="AP36" t="n">
         <v>70813</v>
@@ -7460,25 +7460,25 @@
         <v>0.4073150007742166</v>
       </c>
       <c r="AS36" t="n">
-        <v>-0.2294056272153785</v>
+        <v>-0.231263363182454</v>
       </c>
       <c r="AT36" t="n">
-        <v>0.5190133444614282</v>
+        <v>0.4078431970932905</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.826003923667834</v>
+        <v>1.788349633077973</v>
       </c>
       <c r="AV36" t="n">
-        <v>6.054892490181479</v>
+        <v>5.920482221856175</v>
       </c>
       <c r="AW36" t="n">
-        <v>3.297508491334303</v>
+        <v>3.128800471275274</v>
       </c>
       <c r="AX36" t="n">
-        <v>3.506097758830414</v>
+        <v>3.378049068405549</v>
       </c>
       <c r="AY36" t="n">
-        <v>11.88028866959218</v>
+        <v>11.51427262096043</v>
       </c>
       <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="n">
@@ -7620,16 +7620,16 @@
         <v>69.63793495178223</v>
       </c>
       <c r="AG37" t="n">
-        <v>54.2164563369751</v>
+        <v>54.21645660400391</v>
       </c>
       <c r="AH37" t="n">
         <v>-0.2063233854359267</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.01943218336219554</v>
+        <v>0.0194321783412521</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.2844427625250348</v>
+        <v>0.2844427561988518</v>
       </c>
       <c r="AK37" t="n">
         <v>93.55000305175781</v>
@@ -7668,13 +7668,13 @@
         <v>1.43754311612773</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.340621548171821</v>
+        <v>1.340621170048958</v>
       </c>
       <c r="AX37" t="n">
         <v>0.2916640516070137</v>
       </c>
       <c r="AY37" t="n">
-        <v>3.468657104249114</v>
+        <v>3.468656415129503</v>
       </c>
       <c r="AZ37" t="inlineStr"/>
       <c r="BA37" t="n">
@@ -7860,13 +7860,13 @@
         <v>0.1726504845476564</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.665548530264276</v>
+        <v>1.665548345647908</v>
       </c>
       <c r="AX38" t="n">
         <v>0.01484136985966167</v>
       </c>
       <c r="AY38" t="n">
-        <v>3.027552187786871</v>
+        <v>3.027553030751756</v>
       </c>
       <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="n">
@@ -8058,7 +8058,7 @@
         <v>0.1068018474350487</v>
       </c>
       <c r="AY39" t="n">
-        <v>3.555731538826325</v>
+        <v>3.555730688933335</v>
       </c>
       <c r="AZ39" t="inlineStr"/>
       <c r="BA39" t="n">
@@ -8244,13 +8244,13 @@
         <v>0.08267288704612241</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.6081229012068829</v>
+        <v>0.6081227767269783</v>
       </c>
       <c r="AX40" t="n">
         <v>0.01057324335115384</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.7232373674760566</v>
+        <v>0.723237939232608</v>
       </c>
       <c r="AZ40" t="inlineStr"/>
       <c r="BA40" t="n">
@@ -8392,16 +8392,16 @@
         <v>184.9805242919922</v>
       </c>
       <c r="AG41" t="n">
-        <v>174.905675201416</v>
+        <v>174.9056748199463</v>
       </c>
       <c r="AH41" t="n">
         <v>0.04767787740640217</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.108025813505386</v>
+        <v>0.1080258159219933</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.05760161343520886</v>
+        <v>0.05760161574184086</v>
       </c>
       <c r="AK41" t="n">
         <v>202.5594635009766</v>
@@ -8437,16 +8437,16 @@
         <v>0.1445081459923894</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.1644855158548426</v>
+        <v>0.164485622621221</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.4855275165028372</v>
+        <v>0.4855276902540089</v>
       </c>
       <c r="AX41" t="n">
         <v>0.2669837165927196</v>
       </c>
       <c r="AY41" t="n">
-        <v>37.01777769629298</v>
+        <v>37.01776702760784</v>
       </c>
       <c r="AZ41" t="inlineStr"/>
       <c r="BA41" t="n">
@@ -8588,16 +8588,16 @@
         <v>1051.546401367187</v>
       </c>
       <c r="AG42" t="n">
-        <v>931.3983990478515</v>
+        <v>931.3983978271484</v>
       </c>
       <c r="AH42" t="n">
         <v>-0.008488837238560309</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.1194135572737032</v>
+        <v>0.1194135587408214</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.1289974327228398</v>
+        <v>0.1289974342025189</v>
       </c>
       <c r="AK42" t="n">
         <v>1115.93994140625</v>
@@ -8630,19 +8630,19 @@
         <v>-0.02266920921749049</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.2421442707291079</v>
+        <v>0.2421443610520602</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.3682511612759205</v>
+        <v>0.3682512708696477</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.4045755242711142</v>
+        <v>0.4045756397610765</v>
       </c>
       <c r="AX42" t="n">
         <v>0.3787117936883788</v>
       </c>
       <c r="AY42" t="n">
-        <v>2.375290136323319</v>
+        <v>2.375290803247275</v>
       </c>
       <c r="AZ42" t="inlineStr"/>
       <c r="BA42" t="n">
@@ -8784,28 +8784,28 @@
         <v>124.7998197937012</v>
       </c>
       <c r="AG43" t="n">
-        <v>106.4021580123901</v>
+        <v>106.4021577453613</v>
       </c>
       <c r="AH43" t="n">
         <v>-0.02924538091365481</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.1386047406272666</v>
+        <v>0.13860474348473</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.1729068481784806</v>
+        <v>0.1729068511220291</v>
       </c>
       <c r="AK43" t="n">
         <v>133.0599975585938</v>
       </c>
       <c r="AL43" t="n">
-        <v>77.69111633300781</v>
+        <v>77.69110870361328</v>
       </c>
       <c r="AM43" t="n">
         <v>-0.08950846423599401</v>
       </c>
       <c r="AN43" t="n">
-        <v>0.5593803673330302</v>
+        <v>0.5593805204667446</v>
       </c>
       <c r="AO43" t="n">
         <v>44.99023367211446</v>
@@ -8829,16 +8829,16 @@
         <v>0.2839083227387849</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.364237189044949</v>
+        <v>0.3642373062500344</v>
       </c>
       <c r="AW43" t="n">
         <v>2.364124978364305</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.4773275689233549</v>
+        <v>0.4773274314811182</v>
       </c>
       <c r="AY43" t="n">
-        <v>104.14959432332</v>
+        <v>104.1496160819709</v>
       </c>
       <c r="AZ43" t="inlineStr"/>
       <c r="BA43" t="n">
@@ -9216,13 +9216,13 @@
         <v>-0.0001311130227846791</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.05830873495582267</v>
+        <v>0.05830885633444849</v>
       </c>
       <c r="AX45" t="n">
         <v>0.03111468145740592</v>
       </c>
       <c r="AY45" t="n">
-        <v>3.041185854991779</v>
+        <v>3.04118541253076</v>
       </c>
       <c r="AZ45" t="inlineStr"/>
       <c r="BA45" t="n">
@@ -9910,16 +9910,16 @@
         <v>125.4766003417969</v>
       </c>
       <c r="AG49" t="n">
-        <v>123.3250713348389</v>
+        <v>123.3250712203979</v>
       </c>
       <c r="AH49" t="n">
         <v>-0.004993774663713646</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.01236510243032352</v>
+        <v>0.01236510336975938</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.0174459984792259</v>
+        <v>0.01744599942337666</v>
       </c>
       <c r="AK49" t="n">
         <v>132.3166198730469</v>
@@ -9955,16 +9955,16 @@
         <v>0.04219098346425421</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.02606813681135045</v>
+        <v>0.02606807247537235</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.4261950629085061</v>
+        <v>0.42619531150183</v>
       </c>
       <c r="AX49" t="n">
         <v>0.08141511245651523</v>
       </c>
       <c r="AY49" t="n">
-        <v>167.6387870707617</v>
+        <v>167.6387734936789</v>
       </c>
       <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
@@ -10156,7 +10156,7 @@
         <v>0.08042608884881464</v>
       </c>
       <c r="AY50" t="n">
-        <v>340.7884862561958</v>
+        <v>340.7882608929775</v>
       </c>
       <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
@@ -10298,28 +10298,28 @@
         <v>68.76764038085938</v>
       </c>
       <c r="AG51" t="n">
-        <v>62.58517879486084</v>
+        <v>62.58517864227295</v>
       </c>
       <c r="AH51" t="n">
         <v>-0.0200332741327327</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.07677249929310981</v>
+        <v>0.07677250191837093</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.09878475551317289</v>
+        <v>0.09878475819210175</v>
       </c>
       <c r="AK51" t="n">
         <v>71.69000244140625</v>
       </c>
       <c r="AL51" t="n">
-        <v>55.91819381713867</v>
+        <v>55.91819763183594</v>
       </c>
       <c r="AM51" t="n">
         <v>-0.05998051200057208</v>
       </c>
       <c r="AN51" t="n">
-        <v>0.2051533640379084</v>
+        <v>0.2051532818232549</v>
       </c>
       <c r="AO51" t="n">
         <v>33.51832407532855</v>
@@ -10346,13 +10346,13 @@
         <v>0.1397193043756966</v>
       </c>
       <c r="AW51" t="n">
-        <v>0.117782996438649</v>
+        <v>0.1177827135343774</v>
       </c>
       <c r="AX51" t="n">
         <v>0.1612111644751451</v>
       </c>
       <c r="AY51" t="n">
-        <v>181.3585417014451</v>
+        <v>181.3585711142839</v>
       </c>
       <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="n">
@@ -10490,16 +10490,16 @@
         <v>46.19388656616211</v>
       </c>
       <c r="AG52" t="n">
-        <v>45.61528141021729</v>
+        <v>45.61528144836426</v>
       </c>
       <c r="AH52" t="n">
         <v>-0.01263989673123223</v>
       </c>
       <c r="AI52" t="n">
-        <v>-0.0001157682185106701</v>
+        <v>-0.0001157690546900181</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.01268445876155933</v>
+        <v>0.01268445791467543</v>
       </c>
       <c r="AK52" t="n">
         <v>49.82146072387695</v>
@@ -10532,19 +10532,19 @@
         <v>0.04848406191081689</v>
       </c>
       <c r="AU52" t="n">
-        <v>0.04744300267529078</v>
+        <v>0.04744291091373642</v>
       </c>
       <c r="AV52" t="n">
-        <v>0.03767408856707033</v>
+        <v>0.03767399850915143</v>
       </c>
       <c r="AW52" t="n">
-        <v>0.6218870048350496</v>
+        <v>0.6218868948303693</v>
       </c>
       <c r="AX52" t="n">
         <v>0.05722107370420337</v>
       </c>
       <c r="AY52" t="n">
-        <v>185.0137329397968</v>
+        <v>185.0138459845253</v>
       </c>
       <c r="AZ52" t="inlineStr"/>
       <c r="BA52" t="n">
@@ -10686,28 +10686,28 @@
         <v>111.7686004638672</v>
       </c>
       <c r="AG53" t="n">
-        <v>103.7809627151489</v>
+        <v>103.780962638855</v>
       </c>
       <c r="AH53" t="n">
         <v>-0.04105446556230985</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.03275203371697666</v>
+        <v>0.03275203447619801</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.07696631000275245</v>
+        <v>0.0769663107944778</v>
       </c>
       <c r="AK53" t="n">
         <v>117.3600006103516</v>
       </c>
       <c r="AL53" t="n">
-        <v>85.22573852539062</v>
+        <v>85.22573089599609</v>
       </c>
       <c r="AM53" t="n">
         <v>-0.08674165177430881</v>
       </c>
       <c r="AN53" t="n">
-        <v>0.2576013087084543</v>
+        <v>0.2576014212887332</v>
       </c>
       <c r="AO53" t="n">
         <v>36.2098917069972</v>
@@ -10740,7 +10740,7 @@
         <v>0.1556959724994926</v>
       </c>
       <c r="AY53" t="n">
-        <v>198.4173583556454</v>
+        <v>198.4172920098541</v>
       </c>
       <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
@@ -10882,16 +10882,16 @@
         <v>14.55814701080322</v>
       </c>
       <c r="AG54" t="n">
-        <v>14.18356306552887</v>
+        <v>14.18356305599213</v>
       </c>
       <c r="AH54" t="n">
         <v>0.01180456079373138</v>
       </c>
       <c r="AI54" t="n">
-        <v>0.03852603708834601</v>
+        <v>0.03852603778663011</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.02640972113592022</v>
+        <v>0.0264097218260575</v>
       </c>
       <c r="AK54" t="n">
         <v>16.86722755432129</v>
@@ -10924,7 +10924,7 @@
         <v>0.04024223587717857</v>
       </c>
       <c r="AU54" t="n">
-        <v>-0.05978367662087303</v>
+        <v>-0.05978361938702403</v>
       </c>
       <c r="AV54" t="n">
         <v>0.2033674134329424</v>
@@ -10936,7 +10936,7 @@
         <v>0.03030728330828092</v>
       </c>
       <c r="AY54" t="n">
-        <v>6.46990162807016</v>
+        <v>6.46989982174048</v>
       </c>
       <c r="AZ54" t="inlineStr"/>
       <c r="BA54" t="n">
@@ -10951,12 +10951,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>ENR.DE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -10966,19 +10966,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Grid + power generation equipment</t>
+          <t>Grid + gas/power equipment</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Grid, gas turbines, power equipment</t>
+          <t>Grid/gas/power equipment</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>8</v>
       </c>
       <c r="G55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -10986,11 +10986,7 @@
       <c r="I55" t="n">
         <v>0</v>
       </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
-        </is>
-      </c>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" s="1" t="n">
         <v>46195</v>
       </c>
@@ -11028,7 +11024,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>GE Vernova Inc.</t>
+          <t>Siemens Energy AG</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -11043,94 +11039,96 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="X55" t="n">
-        <v>263755481088</v>
+        <v>130639282176</v>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>1</v>
+        <v>1.156203031539917</v>
       </c>
       <c r="AA55" t="n">
-        <v>263755481088</v>
+        <v>151045534090.0898</v>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>Mega cap</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC55" s="2" t="n">
-        <v>45378</v>
+        <v>44103</v>
       </c>
       <c r="AD55" t="n">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="AE55" t="n">
-        <v>990.3200073242188</v>
+        <v>153.5399932861328</v>
       </c>
       <c r="AF55" t="n">
-        <v>1021.180285644531</v>
+        <v>155.1707995605469</v>
       </c>
       <c r="AG55" t="n">
-        <v>845.7302249145508</v>
+        <v>145.7463712692261</v>
       </c>
       <c r="AH55" t="n">
-        <v>-0.03022020573069983</v>
+        <v>-0.01050974976627428</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.1709644259483296</v>
+        <v>0.05347386661524611</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.2074539321894369</v>
+        <v>0.06466321054341573</v>
       </c>
       <c r="AK55" t="n">
-        <v>1174.859985351562</v>
+        <v>187.6199951171875</v>
       </c>
       <c r="AL55" t="n">
-        <v>546.9464721679688</v>
+        <v>84.04161071777344</v>
       </c>
       <c r="AM55" t="n">
-        <v>-0.1570740176091047</v>
+        <v>-0.181643762487939</v>
       </c>
       <c r="AN55" t="n">
-        <v>0.8106342351909142</v>
+        <v>0.8269520535695967</v>
       </c>
       <c r="AO55" t="n">
-        <v>39.36266113831303</v>
+        <v>50.92099280219657</v>
       </c>
       <c r="AP55" t="n">
-        <v>2475900</v>
+        <v>1888022</v>
       </c>
       <c r="AQ55" t="n">
-        <v>3038674</v>
+        <v>2493520.8</v>
       </c>
       <c r="AR55" t="n">
-        <v>0.8147961907068675</v>
+        <v>0.7571711453138872</v>
       </c>
       <c r="AS55" t="n">
-        <v>-0.09275625378754371</v>
+        <v>0.009334723997666439</v>
       </c>
       <c r="AT55" t="n">
-        <v>-0.04742004309957648</v>
+        <v>-0.1337170586351925</v>
       </c>
       <c r="AU55" t="n">
-        <v>0.2721180753413897</v>
+        <v>0.02386950421925049</v>
       </c>
       <c r="AV55" t="n">
-        <v>0.5368172485999918</v>
-      </c>
-      <c r="AW55" t="inlineStr"/>
+        <v>0.549384608929397</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>5.269829590518301</v>
+      </c>
       <c r="AX55" t="n">
-        <v>0.4600179624990315</v>
+        <v>0.2556575516954047</v>
       </c>
       <c r="AY55" t="n">
-        <v>6.577181365546957</v>
+        <v>6.045008437906104</v>
       </c>
       <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="n">
@@ -11145,12 +11143,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Talen Energy</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -11160,19 +11158,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Grid / power equipment</t>
+          <t>Grid + power generation equipment</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Power generation/data center deals</t>
+          <t>Grid, gas turbines, power equipment</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -11180,7 +11178,11 @@
       <c r="I56" t="n">
         <v>0</v>
       </c>
-      <c r="J56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
       <c r="K56" s="1" t="n">
         <v>46195</v>
       </c>
@@ -11218,17 +11220,17 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>Talen Energy Corporation</t>
+          <t>GE Vernova Inc.</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>Utilities - Independent Power Producers</t>
+          <t>Specialty Industrial Machinery</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
@@ -11237,7 +11239,7 @@
         </is>
       </c>
       <c r="X56" t="n">
-        <v>16660267008</v>
+        <v>263755481088</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
@@ -11248,99 +11250,99 @@
         <v>1</v>
       </c>
       <c r="AA56" t="n">
-        <v>16660267008</v>
+        <v>263755481088</v>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Mega cap</t>
         </is>
       </c>
       <c r="AC56" s="2" t="n">
-        <v>45079</v>
+        <v>45378</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="AE56" t="n">
-        <v>347.7099914550781</v>
+        <v>990.3200073242188</v>
       </c>
       <c r="AF56" t="n">
-        <v>373.1906005859375</v>
+        <v>1021.180285644531</v>
       </c>
       <c r="AG56" t="n">
-        <v>364.5555995178223</v>
+        <v>845.7302255249024</v>
       </c>
       <c r="AH56" t="n">
-        <v>-0.06827773553474514</v>
+        <v>-0.03022020573069983</v>
       </c>
       <c r="AI56" t="n">
-        <v>-0.0462086114848459</v>
+        <v>0.1709644251032612</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.02368637617838343</v>
+        <v>0.2074539313180346</v>
       </c>
       <c r="AK56" t="n">
-        <v>445.8399963378906</v>
+        <v>1174.859985351562</v>
       </c>
       <c r="AL56" t="n">
-        <v>302.9700012207031</v>
+        <v>546.9464721679688</v>
       </c>
       <c r="AM56" t="n">
-        <v>-0.2201013944214245</v>
+        <v>-0.1570740176091047</v>
       </c>
       <c r="AN56" t="n">
-        <v>0.1476713537779717</v>
+        <v>0.8106342351909142</v>
       </c>
       <c r="AO56" t="n">
-        <v>45.58627206223068</v>
+        <v>39.36266113831303</v>
       </c>
       <c r="AP56" t="n">
-        <v>860500</v>
+        <v>2475900</v>
       </c>
       <c r="AQ56" t="n">
-        <v>836238</v>
+        <v>3038674</v>
       </c>
       <c r="AR56" t="n">
-        <v>1.029013271341412</v>
+        <v>0.8147961907068675</v>
       </c>
       <c r="AS56" t="n">
-        <v>-0.09872990550308358</v>
+        <v>-0.09275625378754371</v>
       </c>
       <c r="AT56" t="n">
-        <v>-0.1000595391740594</v>
+        <v>-0.04742004309957648</v>
       </c>
       <c r="AU56" t="n">
-        <v>0.007855047695878525</v>
+        <v>0.2721180753413897</v>
       </c>
       <c r="AV56" t="n">
-        <v>-0.07420521889769283</v>
+        <v>0.5368172485999918</v>
       </c>
       <c r="AW56" t="inlineStr"/>
       <c r="AX56" t="n">
-        <v>-0.1235601496578974</v>
+        <v>0.4600179624990315</v>
       </c>
       <c r="AY56" t="n">
-        <v>6.47763422484039</v>
+        <v>6.57718048092069</v>
       </c>
       <c r="AZ56" t="inlineStr"/>
       <c r="BA56" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive momentum</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ENR.DE</t>
+          <t>TLN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Talen Energy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -11350,16 +11352,16 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Grid + gas/power equipment</t>
+          <t>Grid / power equipment</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Grid/gas/power equipment</t>
+          <t>Power generation/data center deals</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -11408,37 +11410,37 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>Siemens Energy AG</t>
+          <t>Talen Energy Corporation</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>Specialty Industrial Machinery</t>
+          <t>Utilities - Independent Power Producers</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X57" t="n">
-        <v>130639282176</v>
+        <v>16660267008</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>1.156203031539917</v>
+        <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>151045534090.0898</v>
+        <v>16660267008</v>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
@@ -11446,81 +11448,79 @@
         </is>
       </c>
       <c r="AC57" s="2" t="n">
-        <v>44103</v>
+        <v>45079</v>
       </c>
       <c r="AD57" t="n">
-        <v>5.9</v>
+        <v>3.2</v>
       </c>
       <c r="AE57" t="n">
-        <v>153.6799926757812</v>
+        <v>347.7099914550781</v>
       </c>
       <c r="AF57" t="n">
-        <v>155.3647998046875</v>
+        <v>373.1906005859375</v>
       </c>
       <c r="AG57" t="n">
-        <v>145.4739591979981</v>
+        <v>364.5555995178223</v>
       </c>
       <c r="AH57" t="n">
-        <v>-0.01084420107401585</v>
+        <v>-0.06827773553474514</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.0564089512860122</v>
+        <v>-0.0462086114848459</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.06799045451995611</v>
+        <v>0.02368637617838343</v>
       </c>
       <c r="AK57" t="n">
-        <v>187.6199951171875</v>
+        <v>445.8399963378906</v>
       </c>
       <c r="AL57" t="n">
-        <v>84.04161071777344</v>
+        <v>302.9700012207031</v>
       </c>
       <c r="AM57" t="n">
-        <v>-0.1808975766160068</v>
+        <v>-0.2201013944214245</v>
       </c>
       <c r="AN57" t="n">
-        <v>0.8286178877730674</v>
+        <v>0.1476713537779717</v>
       </c>
       <c r="AO57" t="n">
-        <v>55.60520583459921</v>
+        <v>45.58627206223068</v>
       </c>
       <c r="AP57" t="n">
-        <v>1887650</v>
+        <v>860500</v>
       </c>
       <c r="AQ57" t="n">
-        <v>2493513.36</v>
+        <v>836238</v>
       </c>
       <c r="AR57" t="n">
-        <v>0.7570242174278946</v>
+        <v>1.029013271341412</v>
       </c>
       <c r="AS57" t="n">
-        <v>-0.01638513010353693</v>
+        <v>-0.09872990550308358</v>
       </c>
       <c r="AT57" t="n">
-        <v>-0.09322635974783922</v>
+        <v>-0.1000595391740594</v>
       </c>
       <c r="AU57" t="n">
-        <v>-0.02257537295739709</v>
+        <v>0.007855047695878525</v>
       </c>
       <c r="AV57" t="n">
-        <v>0.6076598863113325</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>5.389270745593035</v>
-      </c>
+        <v>-0.07420521889769283</v>
+      </c>
+      <c r="AW57" t="inlineStr"/>
       <c r="AX57" t="n">
-        <v>0.2568024735303118</v>
+        <v>-0.1235601496578974</v>
       </c>
       <c r="AY57" t="n">
-        <v>6.051431533987828</v>
+        <v>6.47763422484039</v>
       </c>
       <c r="AZ57" t="inlineStr"/>
       <c r="BA57" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>Weak momentum</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11706,7 +11706,7 @@
         <v>-0.2609650154550651</v>
       </c>
       <c r="AY58" t="n">
-        <v>5.665243618492831</v>
+        <v>5.66524487433596</v>
       </c>
       <c r="AZ58" t="inlineStr"/>
       <c r="BA58" t="n">
@@ -11844,28 +11844,28 @@
         <v>87.03867248535157</v>
       </c>
       <c r="AG59" t="n">
-        <v>86.90480491638183</v>
+        <v>86.90480495452881</v>
       </c>
       <c r="AH59" t="n">
         <v>-0.02744378896489574</v>
       </c>
       <c r="AI59" t="n">
-        <v>-0.02594567000837822</v>
+        <v>-0.02594567043594065</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.001540393181925115</v>
+        <v>0.001540392742297669</v>
       </c>
       <c r="AK59" t="n">
         <v>97.16828918457031</v>
       </c>
       <c r="AL59" t="n">
-        <v>68.33090209960938</v>
+        <v>68.33089447021484</v>
       </c>
       <c r="AM59" t="n">
         <v>-0.1288309978877268</v>
       </c>
       <c r="AN59" t="n">
-        <v>0.2388245863120666</v>
+        <v>0.2388247246313671</v>
       </c>
       <c r="AO59" t="n">
         <v>32.12378363105925</v>
@@ -11892,13 +11892,13 @@
         <v>0.2000711914751074</v>
       </c>
       <c r="AW59" t="n">
-        <v>0.2249915952748056</v>
+        <v>0.2249920010175104</v>
       </c>
       <c r="AX59" t="n">
         <v>0.06081120100106996</v>
       </c>
       <c r="AY59" t="n">
-        <v>242.5944133488904</v>
+        <v>242.5945595854922</v>
       </c>
       <c r="AZ59" t="inlineStr"/>
       <c r="BA59" t="n">
@@ -12084,13 +12084,13 @@
         <v>-0.2194897999819536</v>
       </c>
       <c r="AW60" t="n">
-        <v>2.277734298675255</v>
+        <v>2.27773499254422</v>
       </c>
       <c r="AX60" t="n">
         <v>-0.2821161148537437</v>
       </c>
       <c r="AY60" t="n">
-        <v>15.54764473996479</v>
+        <v>15.54763589752667</v>
       </c>
       <c r="AZ60" t="inlineStr"/>
       <c r="BA60" t="n">
@@ -12422,16 +12422,16 @@
         <v>155.0342684936523</v>
       </c>
       <c r="AG62" t="n">
-        <v>161.9298694610596</v>
+        <v>161.9298695373535</v>
       </c>
       <c r="AH62" t="n">
         <v>-0.09316825432277331</v>
       </c>
       <c r="AI62" t="n">
-        <v>-0.1317846620527333</v>
+        <v>-0.1317846624617965</v>
       </c>
       <c r="AJ62" t="n">
-        <v>-0.04258387282320053</v>
+        <v>-0.04258387327429114</v>
       </c>
       <c r="AK62" t="n">
         <v>217.0162200927734</v>
@@ -12467,7 +12467,7 @@
         <v>-0.05794228357619136</v>
       </c>
       <c r="AV62" t="n">
-        <v>-0.3125761103399044</v>
+        <v>-0.3125760590520036</v>
       </c>
       <c r="AW62" t="n">
         <v>7.125945592394846</v>
@@ -12476,7 +12476,7 @@
         <v>-0.1467716305016187</v>
       </c>
       <c r="AY62" t="n">
-        <v>11.40029716442156</v>
+        <v>11.40029507829921</v>
       </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="n">
@@ -12614,16 +12614,16 @@
         <v>185.0085992431641</v>
       </c>
       <c r="AG63" t="n">
-        <v>196.2314179229736</v>
+        <v>196.23141746521</v>
       </c>
       <c r="AH63" t="n">
         <v>-0.08166434105488174</v>
       </c>
       <c r="AI63" t="n">
-        <v>-0.1341855667415351</v>
+        <v>-0.1341855647217852</v>
       </c>
       <c r="AJ63" t="n">
-        <v>-0.05719175246552433</v>
+        <v>-0.05719175026616519</v>
       </c>
       <c r="AK63" t="n">
         <v>238.1012115478516</v>
@@ -12659,16 +12659,16 @@
         <v>-0.1360502682383328</v>
       </c>
       <c r="AV63" t="n">
-        <v>-0.0483435532484715</v>
+        <v>-0.04834347191166233</v>
       </c>
       <c r="AW63" t="n">
-        <v>2.1604254464612</v>
+        <v>2.160425670724313</v>
       </c>
       <c r="AX63" t="n">
         <v>-0.06317153909373063</v>
       </c>
       <c r="AY63" t="n">
-        <v>10.9903026599305</v>
+        <v>10.99030185294266</v>
       </c>
       <c r="AZ63" t="inlineStr"/>
       <c r="BA63" t="n">
@@ -12850,13 +12850,13 @@
         <v>0.277721863643293</v>
       </c>
       <c r="AW64" t="n">
-        <v>4.656780415864207</v>
+        <v>4.656781042556578</v>
       </c>
       <c r="AX64" t="n">
         <v>-0.0118709232744223</v>
       </c>
       <c r="AY64" t="n">
-        <v>15.27645915569013</v>
+        <v>15.27645526437194</v>
       </c>
       <c r="AZ64" t="inlineStr"/>
       <c r="BA64" t="n">
@@ -13048,7 +13048,7 @@
         <v>-0.2977247885607798</v>
       </c>
       <c r="AY65" t="n">
-        <v>-0.9120200663678448</v>
+        <v>-0.9120200367430831</v>
       </c>
       <c r="AZ65" t="inlineStr"/>
       <c r="BA65" t="n">
@@ -13610,13 +13610,13 @@
         <v>9.600434901678154</v>
       </c>
       <c r="AW68" t="n">
-        <v>5.151950967537058</v>
+        <v>5.151951599366194</v>
       </c>
       <c r="AX68" t="n">
         <v>1.214825064405663</v>
       </c>
       <c r="AY68" t="n">
-        <v>-0.466731734401994</v>
+        <v>-0.4667316204618699</v>
       </c>
       <c r="AZ68" t="inlineStr"/>
       <c r="BA68" t="n">
@@ -13758,16 +13758,16 @@
         <v>166.7163391113281</v>
       </c>
       <c r="AG69" t="n">
-        <v>121.9530445480347</v>
+        <v>121.953044128418</v>
       </c>
       <c r="AH69" t="n">
         <v>0.1367812254196945</v>
       </c>
       <c r="AI69" t="n">
-        <v>0.5540407783572234</v>
+        <v>0.5540407837043753</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.367053522355173</v>
+        <v>0.3670535270589381</v>
       </c>
       <c r="AK69" t="n">
         <v>191.4799957275391</v>
@@ -13803,7 +13803,7 @@
         <v>0.848938631049049</v>
       </c>
       <c r="AV69" t="n">
-        <v>0.8568779921518677</v>
+        <v>0.8568778533479506</v>
       </c>
       <c r="AW69" t="n">
         <v>1.650180647343206</v>
@@ -13812,7 +13812,7 @@
         <v>0.7945835878110208</v>
       </c>
       <c r="AY69" t="n">
-        <v>201.1084893601252</v>
+        <v>201.1085279004612</v>
       </c>
       <c r="AZ69" t="inlineStr"/>
       <c r="BA69" t="n">
@@ -14184,13 +14184,13 @@
         <v>4.533226446693768</v>
       </c>
       <c r="AW71" t="n">
-        <v>9.66050660034268</v>
+        <v>9.660504466741012</v>
       </c>
       <c r="AX71" t="n">
         <v>1.833547646867189</v>
       </c>
       <c r="AY71" t="n">
-        <v>153.1830636660477</v>
+        <v>153.1830078780286</v>
       </c>
       <c r="AZ71" t="inlineStr"/>
       <c r="BA71" t="n">
@@ -14376,13 +14376,13 @@
         <v>8.418682596622679</v>
       </c>
       <c r="AW72" t="n">
-        <v>4.165340187746766</v>
+        <v>4.165339876496194</v>
       </c>
       <c r="AX72" t="n">
         <v>0.8100882548301631</v>
       </c>
       <c r="AY72" t="n">
-        <v>3.295202321905194</v>
+        <v>3.29520189146826</v>
       </c>
       <c r="AZ72" t="inlineStr"/>
       <c r="BA72" t="n">
@@ -14524,28 +14524,28 @@
         <v>337.7683770751953</v>
       </c>
       <c r="AG73" t="n">
-        <v>244.932223815918</v>
+        <v>244.9322232818604</v>
       </c>
       <c r="AH73" t="n">
         <v>-0.07821445927070403</v>
       </c>
       <c r="AI73" t="n">
-        <v>0.2711680041639388</v>
+        <v>0.2711680069356319</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.3790279278607684</v>
+        <v>0.3790279308676425</v>
       </c>
       <c r="AK73" t="n">
         <v>433.3299865722656</v>
       </c>
       <c r="AL73" t="n">
-        <v>96.49594879150391</v>
+        <v>96.49594116210938</v>
       </c>
       <c r="AM73" t="n">
         <v>-0.2814944366847034</v>
       </c>
       <c r="AN73" t="n">
-        <v>2.226560389351069</v>
+        <v>2.226560644457158</v>
       </c>
       <c r="AO73" t="n">
         <v>51.28780555467554</v>
@@ -14569,16 +14569,16 @@
         <v>0.3503425054150335</v>
       </c>
       <c r="AV73" t="n">
-        <v>2.157570955706555</v>
+        <v>2.157571200020055</v>
       </c>
       <c r="AW73" t="n">
-        <v>4.110391380226764</v>
+        <v>4.110391060249222</v>
       </c>
       <c r="AX73" t="n">
         <v>0.68562960324334</v>
       </c>
       <c r="AY73" t="n">
-        <v>1650.444647642039</v>
+        <v>1650.444517115374</v>
       </c>
       <c r="AZ73" t="inlineStr"/>
       <c r="BA73" t="n">
@@ -14760,13 +14760,13 @@
         <v>6.85714238874368</v>
       </c>
       <c r="AW74" t="n">
-        <v>10.59125607552883</v>
+        <v>10.5912525713164</v>
       </c>
       <c r="AX74" t="n">
-        <v>1.7838236999642</v>
+        <v>1.783823430468583</v>
       </c>
       <c r="AY74" t="n">
-        <v>648.6923660080628</v>
+        <v>648.6923086698941</v>
       </c>
       <c r="AZ74" t="inlineStr"/>
       <c r="BA74" t="n">
@@ -15092,28 +15092,28 @@
         <v>561.1805792236328</v>
       </c>
       <c r="AG76" t="n">
-        <v>341.0865713500976</v>
+        <v>341.0865718078613</v>
       </c>
       <c r="AH76" t="n">
         <v>-0.2260958346174371</v>
       </c>
       <c r="AI76" t="n">
-        <v>0.2732837475070078</v>
+        <v>0.2732837457981658</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.6452731545611818</v>
+        <v>0.6452731523531021</v>
       </c>
       <c r="AK76" t="n">
         <v>746.22998046875</v>
       </c>
       <c r="AL76" t="n">
-        <v>74.23880767822266</v>
+        <v>74.23881530761719</v>
       </c>
       <c r="AM76" t="n">
         <v>-0.4180078539324299</v>
       </c>
       <c r="AN76" t="n">
-        <v>4.850039910061312</v>
+        <v>4.850039308862838</v>
       </c>
       <c r="AO76" t="n">
         <v>43.41204272369416</v>
@@ -15137,7 +15137,7 @@
         <v>0.5380465760513267</v>
       </c>
       <c r="AV76" t="n">
-        <v>4.850039910061312</v>
+        <v>4.850039308862838</v>
       </c>
       <c r="AW76" t="n">
         <v>7.922699912708136</v>
@@ -15146,7 +15146,7 @@
         <v>1.315509463132905</v>
       </c>
       <c r="AY76" t="n">
-        <v>638.1087550950417</v>
+        <v>638.1088672116349</v>
       </c>
       <c r="AZ76" t="inlineStr"/>
       <c r="BA76" t="n">
@@ -15261,10 +15261,10 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>0.0007105048280209303</v>
+        <v>0.0007063643424771726</v>
       </c>
       <c r="AA77" t="n">
-        <v>717193295162.8125</v>
+        <v>713013832401.1406</v>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
@@ -15284,28 +15284,28 @@
         <v>2124500</v>
       </c>
       <c r="AG77" t="n">
-        <v>1202997.78578125</v>
+        <v>1202997.7871875</v>
       </c>
       <c r="AH77" t="n">
         <v>-0.3306660390680159</v>
       </c>
       <c r="AI77" t="n">
-        <v>0.182047063433725</v>
+        <v>0.1820470620519656</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.766004912985196</v>
+        <v>0.7660049109208165</v>
       </c>
       <c r="AK77" t="n">
         <v>2919000</v>
       </c>
       <c r="AL77" t="n">
-        <v>243980.46875</v>
+        <v>243980.453125</v>
       </c>
       <c r="AM77" t="n">
         <v>-0.512846865364851</v>
       </c>
       <c r="AN77" t="n">
-        <v>4.828335388014538</v>
+        <v>4.828335761272884</v>
       </c>
       <c r="AO77" t="n">
         <v>40.34988713318284</v>
@@ -15329,16 +15329,16 @@
         <v>0.7167014101518985</v>
       </c>
       <c r="AV77" t="n">
-        <v>4.368204642038879</v>
+        <v>4.368203375441909</v>
       </c>
       <c r="AW77" t="n">
-        <v>10.71640551678324</v>
+        <v>10.7164062709706</v>
       </c>
       <c r="AX77" t="n">
         <v>1.104670931943145</v>
       </c>
       <c r="AY77" t="n">
-        <v>-7.213031021531175</v>
+        <v>-7.21303144568902</v>
       </c>
       <c r="AZ77" t="inlineStr"/>
       <c r="BA77" t="n">
@@ -15457,10 +15457,10 @@
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>0.0007105048280209303</v>
+        <v>0.0007063643424771726</v>
       </c>
       <c r="AA78" t="n">
-        <v>1077747827023.75</v>
+        <v>1071467223259.188</v>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
@@ -15528,13 +15528,13 @@
         <v>2.549299254074573</v>
       </c>
       <c r="AW78" t="n">
-        <v>2.166233693917893</v>
+        <v>2.166233015817673</v>
       </c>
       <c r="AX78" t="n">
         <v>0.8033728341594726</v>
       </c>
       <c r="AY78" t="n">
-        <v>53.10514161702424</v>
+        <v>53.10514780480893</v>
       </c>
       <c r="AZ78" t="inlineStr"/>
       <c r="BA78" t="n">
@@ -16169,7 +16169,7 @@
         <v>33550</v>
       </c>
       <c r="AD82" t="n">
-        <v>34.7</v>
+        <v>34.8</v>
       </c>
       <c r="AE82" t="n">
         <v>169.1799926757812</v>
@@ -16178,16 +16178,16 @@
         <v>157.5846905517578</v>
       </c>
       <c r="AG82" t="n">
-        <v>142.8491946411133</v>
+        <v>142.8491962814331</v>
       </c>
       <c r="AH82" t="n">
         <v>0.07358139983918699</v>
       </c>
       <c r="AI82" t="n">
-        <v>0.1843258416739419</v>
+        <v>0.1843258280744733</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.103154210618164</v>
+        <v>0.1031541979507795</v>
       </c>
       <c r="AK82" t="n">
         <v>176.3200073242188</v>
@@ -16226,13 +16226,13 @@
         <v>0.5691679746156471</v>
       </c>
       <c r="AW82" t="n">
-        <v>3.870522859307906</v>
+        <v>3.870523394195218</v>
       </c>
       <c r="AX82" t="n">
-        <v>0.2151606785859466</v>
+        <v>0.2151608117657993</v>
       </c>
       <c r="AY82" t="n">
-        <v>1350.990863102656</v>
+        <v>1350.990058116577</v>
       </c>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="n">
@@ -16958,16 +16958,16 @@
         <v>240.8528381347656</v>
       </c>
       <c r="AG86" t="n">
-        <v>138.071287689209</v>
+        <v>138.0712878417969</v>
       </c>
       <c r="AH86" t="n">
         <v>-0.09189361057758594</v>
       </c>
       <c r="AI86" t="n">
-        <v>0.5841092299582955</v>
+        <v>0.5841092282076354</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.7444092987450972</v>
+        <v>0.7444092968172835</v>
       </c>
       <c r="AK86" t="n">
         <v>316.3519592285156</v>
@@ -17003,16 +17003,16 @@
         <v>1.726500796368783</v>
       </c>
       <c r="AV86" t="n">
-        <v>1.889729871176091</v>
+        <v>1.889729579892497</v>
       </c>
       <c r="AW86" t="n">
-        <v>2.678710303790584</v>
+        <v>2.678710067763018</v>
       </c>
       <c r="AX86" t="n">
         <v>1.450396679886195</v>
       </c>
       <c r="AY86" t="n">
-        <v>17.03236073945209</v>
+        <v>17.03236357506422</v>
       </c>
       <c r="AZ86" t="inlineStr"/>
       <c r="BA86" t="n">
@@ -17586,13 +17586,13 @@
         <v>3.038493647850606</v>
       </c>
       <c r="AW89" t="n">
-        <v>7.072549175377423</v>
+        <v>7.072548531498585</v>
       </c>
       <c r="AX89" t="n">
         <v>1.725398677054621</v>
       </c>
       <c r="AY89" t="n">
-        <v>21.17077391916478</v>
+        <v>21.17077149079706</v>
       </c>
       <c r="AZ89" t="inlineStr"/>
       <c r="BA89" t="n">
@@ -17778,13 +17778,13 @@
         <v>3.977346462683689</v>
       </c>
       <c r="AW90" t="n">
-        <v>21.72846933573218</v>
+        <v>21.72846719346339</v>
       </c>
       <c r="AX90" t="n">
         <v>0.4770550103675077</v>
       </c>
       <c r="AY90" t="n">
-        <v>197.7557898959985</v>
+        <v>197.7557489404146</v>
       </c>
       <c r="AZ90" t="inlineStr"/>
       <c r="BA90" t="n">
@@ -17970,7 +17970,7 @@
         <v>2.413308515312289</v>
       </c>
       <c r="AW91" t="n">
-        <v>32.67602153077486</v>
+        <v>32.67601896149694</v>
       </c>
       <c r="AX91" t="n">
         <v>0.3838689265885882</v>
@@ -18314,28 +18314,28 @@
         <v>87.27320022583008</v>
       </c>
       <c r="AG93" t="n">
-        <v>75.28370296478272</v>
+        <v>75.28370292663574</v>
       </c>
       <c r="AH93" t="n">
         <v>-0.02959898087545187</v>
       </c>
       <c r="AI93" t="n">
-        <v>0.1249446972743058</v>
+        <v>0.124944697844326</v>
       </c>
       <c r="AJ93" t="n">
-        <v>0.1592575390009174</v>
+        <v>0.1592575395883244</v>
       </c>
       <c r="AK93" t="n">
         <v>102.7099990844727</v>
       </c>
       <c r="AL93" t="n">
-        <v>48.05623626708984</v>
+        <v>48.05623245239258</v>
       </c>
       <c r="AM93" t="n">
         <v>-0.1754453977576815</v>
       </c>
       <c r="AN93" t="n">
-        <v>0.7623103476250419</v>
+        <v>0.7623104875170001</v>
       </c>
       <c r="AO93" t="n">
         <v>54.58937376120724</v>
@@ -18362,13 +18362,13 @@
         <v>0.3136096999302989</v>
       </c>
       <c r="AW93" t="n">
-        <v>0.2990616155286041</v>
+        <v>0.2990619195803677</v>
       </c>
       <c r="AX93" t="n">
         <v>0.3165652204853286</v>
       </c>
       <c r="AY93" t="n">
-        <v>481.0812672262766</v>
+        <v>481.0811445530966</v>
       </c>
       <c r="AZ93" t="inlineStr"/>
       <c r="BA93" t="n">
@@ -18496,22 +18496,22 @@
         <v>25.2</v>
       </c>
       <c r="AE94" t="n">
-        <v>140.5</v>
+        <v>139.6000061035156</v>
       </c>
       <c r="AF94" t="n">
-        <v>142.2080003356934</v>
+        <v>141.832000579834</v>
       </c>
       <c r="AG94" t="n">
-        <v>131.9514346694946</v>
+        <v>132.0474489593506</v>
       </c>
       <c r="AH94" t="n">
-        <v>-0.01201057838983377</v>
+        <v>-0.0157368891871621</v>
       </c>
       <c r="AI94" t="n">
-        <v>0.06478569446340154</v>
+        <v>0.05719578230163314</v>
       </c>
       <c r="AJ94" t="n">
-        <v>0.07772985335012739</v>
+        <v>0.07409875539129485</v>
       </c>
       <c r="AK94" t="n">
         <v>164.8832092285156</v>
@@ -18520,13 +18520,13 @@
         <v>110.5768280029297</v>
       </c>
       <c r="AM94" t="n">
-        <v>-0.1478816996746003</v>
+        <v>-0.1533400716986252</v>
       </c>
       <c r="AN94" t="n">
-        <v>0.2706097881219518</v>
+        <v>0.2624707058862006</v>
       </c>
       <c r="AO94" t="n">
-        <v>57.30335898750323</v>
+        <v>58.95954968077839</v>
       </c>
       <c r="AP94" t="n">
         <v>207524</v>
@@ -18538,25 +18538,25 @@
         <v>1.2323785790222</v>
       </c>
       <c r="AS94" t="n">
-        <v>0.05798190339830911</v>
+        <v>0.04179109032474337</v>
       </c>
       <c r="AT94" t="n">
-        <v>-0.1195652121946585</v>
+        <v>-0.1467335613914449</v>
       </c>
       <c r="AU94" t="n">
-        <v>0.01110004114542629</v>
+        <v>0.01611295472585916</v>
       </c>
       <c r="AV94" t="n">
-        <v>0.04127118250184636</v>
+        <v>0.06085226472901195</v>
       </c>
       <c r="AW94" t="n">
-        <v>0.752573289183097</v>
+        <v>0.6994787410652139</v>
       </c>
       <c r="AX94" t="n">
-        <v>0.1151259550614732</v>
+        <v>0.1079828479200735</v>
       </c>
       <c r="AY94" t="n">
-        <v>7.699711157047682</v>
+        <v>7.643982826973444</v>
       </c>
       <c r="AZ94" t="inlineStr"/>
       <c r="BA94" t="n">
@@ -18684,22 +18684,22 @@
         <v>19.3</v>
       </c>
       <c r="AE95" t="n">
-        <v>124.5</v>
+        <v>126</v>
       </c>
       <c r="AF95" t="n">
-        <v>137.6700006103516</v>
+        <v>137.2300006103516</v>
       </c>
       <c r="AG95" t="n">
-        <v>111.0970948791504</v>
+        <v>111.2873723220825</v>
       </c>
       <c r="AH95" t="n">
-        <v>-0.09566354726493187</v>
+        <v>-0.08183342243244485</v>
       </c>
       <c r="AI95" t="n">
-        <v>0.1206413645237896</v>
+        <v>0.1322039272823956</v>
       </c>
       <c r="AJ95" t="n">
-        <v>0.2391863239998018</v>
+        <v>0.2331138542222666</v>
       </c>
       <c r="AK95" t="n">
         <v>156.8999938964844</v>
@@ -18708,13 +18708,13 @@
         <v>72.51947784423828</v>
       </c>
       <c r="AM95" t="n">
-        <v>-0.2065009251552964</v>
+        <v>-0.1969406953378903</v>
       </c>
       <c r="AN95" t="n">
-        <v>0.7167801492918719</v>
+        <v>0.7374642474761115</v>
       </c>
       <c r="AO95" t="n">
-        <v>48.86211712336476</v>
+        <v>51.29870129870131</v>
       </c>
       <c r="AP95" t="n">
         <v>1234932</v>
@@ -18726,25 +18726,25 @@
         <v>1.015157823152269</v>
       </c>
       <c r="AS95" t="n">
-        <v>-0.08824608408972634</v>
+        <v>-0.06701223878010132</v>
       </c>
       <c r="AT95" t="n">
-        <v>-0.1633064687727556</v>
+        <v>-0.185520345923758</v>
       </c>
       <c r="AU95" t="n">
-        <v>0.1821673267601445</v>
+        <v>0.2229202467689018</v>
       </c>
       <c r="AV95" t="n">
-        <v>0.6949722515650367</v>
+        <v>0.717250057761323</v>
       </c>
       <c r="AW95" t="n">
-        <v>3.250965235124014</v>
+        <v>3.265642331517872</v>
       </c>
       <c r="AX95" t="n">
-        <v>0.3955045813973017</v>
+        <v>0.412317889606908</v>
       </c>
       <c r="AY95" t="n">
-        <v>10.89102402775854</v>
+        <v>11.03429047364181</v>
       </c>
       <c r="AZ95" t="inlineStr"/>
       <c r="BA95" t="n">
@@ -18901,13 +18901,13 @@
         <v>480.8090515136719</v>
       </c>
       <c r="AL96" t="n">
-        <v>287.4934692382812</v>
+        <v>287.4934997558594</v>
       </c>
       <c r="AM96" t="n">
         <v>-0.1103328682790791</v>
       </c>
       <c r="AN96" t="n">
-        <v>0.4878947020917808</v>
+        <v>0.4878945441510174</v>
       </c>
       <c r="AO96" t="n">
         <v>73.57863850003642</v>
@@ -18940,7 +18940,7 @@
         <v>0.2350721494968062</v>
       </c>
       <c r="AY96" t="n">
-        <v>375.6847560453293</v>
+        <v>375.6847165026617</v>
       </c>
       <c r="AZ96" t="inlineStr"/>
       <c r="BA96" t="n">
@@ -19289,13 +19289,13 @@
         <v>255.6900024414062</v>
       </c>
       <c r="AL98" t="n">
-        <v>63.82233428955078</v>
+        <v>63.82233047485352</v>
       </c>
       <c r="AM98" t="n">
         <v>-0.3520278810519846</v>
       </c>
       <c r="AN98" t="n">
-        <v>1.595956329709284</v>
+        <v>1.595956484871082</v>
       </c>
       <c r="AO98" t="n">
         <v>56.3101863446074</v>
@@ -19322,13 +19322,13 @@
         <v>1.586335469119707</v>
       </c>
       <c r="AW98" t="n">
-        <v>3.586805462047716</v>
+        <v>3.586805946455038</v>
       </c>
       <c r="AX98" t="n">
         <v>0.8335019418261018</v>
       </c>
       <c r="AY98" t="n">
-        <v>215.1223045931866</v>
+        <v>215.1223550047973</v>
       </c>
       <c r="AZ98" t="inlineStr"/>
       <c r="BA98" t="n">
@@ -19452,22 +19452,22 @@
         <v>25.3</v>
       </c>
       <c r="AE99" t="n">
-        <v>933.5</v>
+        <v>923</v>
       </c>
       <c r="AF99" t="n">
-        <v>956.49</v>
+        <v>953.8099999999999</v>
       </c>
       <c r="AG99" t="n">
-        <v>858.705</v>
+        <v>859.765</v>
       </c>
       <c r="AH99" t="n">
-        <v>-0.02403579755146423</v>
+        <v>-0.03230203080278038</v>
       </c>
       <c r="AI99" t="n">
-        <v>0.08710208977471878</v>
+        <v>0.07354916750507412</v>
       </c>
       <c r="AJ99" t="n">
-        <v>0.113874962880151</v>
+        <v>0.1093845411246095</v>
       </c>
       <c r="AK99" t="n">
         <v>1112</v>
@@ -19476,43 +19476,43 @@
         <v>534.5</v>
       </c>
       <c r="AM99" t="n">
-        <v>-0.1605215827338129</v>
+        <v>-0.1699640287769785</v>
       </c>
       <c r="AN99" t="n">
-        <v>0.7464920486435922</v>
+        <v>0.7268475210477081</v>
       </c>
       <c r="AO99" t="n">
-        <v>57.96703296703296</v>
+        <v>51.39664804469274</v>
       </c>
       <c r="AP99" t="n">
-        <v>80861</v>
+        <v>84105</v>
       </c>
       <c r="AQ99" t="n">
-        <v>139394.44</v>
+        <v>139459.32</v>
       </c>
       <c r="AR99" t="n">
-        <v>0.5800876993372189</v>
+        <v>0.6030790914511844</v>
       </c>
       <c r="AS99" t="n">
-        <v>-0.006386375731772254</v>
+        <v>-0.01441537640149493</v>
       </c>
       <c r="AT99" t="n">
-        <v>-0.04598875830352578</v>
+        <v>-0.05816326530612248</v>
       </c>
       <c r="AU99" t="n">
-        <v>0.1377209018890919</v>
+        <v>0.09750297265160524</v>
       </c>
       <c r="AV99" t="n">
-        <v>0.6507515473032714</v>
+        <v>0.625</v>
       </c>
       <c r="AW99" t="n">
-        <v>2.579936438979489</v>
+        <v>2.430942235468854</v>
       </c>
       <c r="AX99" t="n">
-        <v>0.1328883495145632</v>
+        <v>0.1201456310679612</v>
       </c>
       <c r="AY99" t="n">
-        <v>26.6385694438311</v>
+        <v>26.32768796510136</v>
       </c>
       <c r="AZ99" t="inlineStr"/>
       <c r="BA99" t="n">
@@ -19690,13 +19690,13 @@
         <v>1.277372105259189</v>
       </c>
       <c r="AW100" t="n">
-        <v>0.699840090171616</v>
+        <v>0.6998402373725046</v>
       </c>
       <c r="AX100" t="n">
         <v>0.4377879151449628</v>
       </c>
       <c r="AY100" t="n">
-        <v>14.66407219280621</v>
+        <v>14.66407844271657</v>
       </c>
       <c r="AZ100" t="inlineStr"/>
       <c r="BA100" t="n">
@@ -19882,13 +19882,13 @@
         <v>0.09347035427524952</v>
       </c>
       <c r="AW101" t="n">
-        <v>0.5735530510489519</v>
+        <v>0.5735534003470222</v>
       </c>
       <c r="AX101" t="n">
         <v>-0.06598188885151257</v>
       </c>
       <c r="AY101" t="n">
-        <v>7.095229441941385</v>
+        <v>7.095231175318268</v>
       </c>
       <c r="AZ101" t="inlineStr"/>
       <c r="BA101" t="n">
@@ -20070,7 +20070,7 @@
         <v>1.283306636260416</v>
       </c>
       <c r="AW102" t="n">
-        <v>0.4177837391396646</v>
+        <v>0.4177838758235302</v>
       </c>
       <c r="AX102" t="n">
         <v>1.057850303525782</v>
@@ -20419,13 +20419,13 @@
         <v>252.5</v>
       </c>
       <c r="AL104" t="n">
-        <v>113.7036895751953</v>
+        <v>113.7036819458008</v>
       </c>
       <c r="AM104" t="n">
         <v>-0.0217821782178218</v>
       </c>
       <c r="AN104" t="n">
-        <v>1.172312973508676</v>
+        <v>1.172313119268536</v>
       </c>
       <c r="AO104" t="n">
         <v>69.59706959706961</v>
@@ -20449,16 +20449,16 @@
         <v>0.4576066187262842</v>
       </c>
       <c r="AV104" t="n">
-        <v>1.172312973508676</v>
+        <v>1.172313119268536</v>
       </c>
       <c r="AW104" t="n">
-        <v>4.072577354187105</v>
+        <v>4.072576956793891</v>
       </c>
       <c r="AX104" t="n">
         <v>0.5056116088614915</v>
       </c>
       <c r="AY104" t="n">
-        <v>63.72220668712302</v>
+        <v>63.72222690427212</v>
       </c>
       <c r="AZ104" t="inlineStr"/>
       <c r="BA104" t="n">
@@ -20596,28 +20596,28 @@
         <v>407.7526507568359</v>
       </c>
       <c r="AG105" t="n">
-        <v>373.8393664550781</v>
+        <v>373.839365234375</v>
       </c>
       <c r="AH105" t="n">
         <v>0.1003729634693471</v>
       </c>
       <c r="AI105" t="n">
-        <v>0.2001946101353034</v>
+        <v>0.200194614054316</v>
       </c>
       <c r="AJ105" t="n">
-        <v>0.09071619349064175</v>
+        <v>0.09071619705217326</v>
       </c>
       <c r="AK105" t="n">
         <v>448.6799926757812</v>
       </c>
       <c r="AL105" t="n">
-        <v>313.2000427246094</v>
+        <v>313.2000122070312</v>
       </c>
       <c r="AM105" t="n">
         <v>0</v>
       </c>
       <c r="AN105" t="n">
-        <v>0.4325668310023083</v>
+        <v>0.4325669705887341</v>
       </c>
       <c r="AO105" t="n">
         <v>65.61718881791322</v>
@@ -20641,16 +20641,16 @@
         <v>0.2102971455704101</v>
       </c>
       <c r="AV105" t="n">
-        <v>0.2596691814048004</v>
+        <v>0.2596692893308814</v>
       </c>
       <c r="AW105" t="n">
-        <v>2.112531826910721</v>
+        <v>2.112531167978308</v>
       </c>
       <c r="AX105" t="n">
         <v>0.3822776469942279</v>
       </c>
       <c r="AY105" t="n">
-        <v>1301.246121988245</v>
+        <v>1301.246459913708</v>
       </c>
       <c r="AZ105" t="inlineStr"/>
       <c r="BA105" t="n">
@@ -20782,25 +20782,25 @@
         <v>26.6</v>
       </c>
       <c r="AE106" t="n">
-        <v>300.6000061035156</v>
+        <v>303.7000122070312</v>
       </c>
       <c r="AF106" t="n">
-        <v>275.5359997558594</v>
+        <v>276.2109997558593</v>
       </c>
       <c r="AG106" t="n">
-        <v>252.7827911376953</v>
+        <v>253.0749808502197</v>
       </c>
       <c r="AH106" t="n">
-        <v>0.09096454318079794</v>
+        <v>0.09952178760248231</v>
       </c>
       <c r="AI106" t="n">
-        <v>0.189163252571942</v>
+        <v>0.2000396530179864</v>
       </c>
       <c r="AJ106" t="n">
-        <v>0.09001090824165314</v>
+        <v>0.09141962128343484</v>
       </c>
       <c r="AK106" t="n">
-        <v>300.6000061035156</v>
+        <v>303.7000122070312</v>
       </c>
       <c r="AL106" t="n">
         <v>206.813720703125</v>
@@ -20809,10 +20809,10 @@
         <v>0</v>
       </c>
       <c r="AN106" t="n">
-        <v>0.4534819308967324</v>
+        <v>0.4684712947212224</v>
       </c>
       <c r="AO106" t="n">
-        <v>78.11347860328905</v>
+        <v>78.38427443249309</v>
       </c>
       <c r="AP106" t="n">
         <v>786357</v>
@@ -20824,25 +20824,25 @@
         <v>0.8167489470591441</v>
       </c>
       <c r="AS106" t="n">
-        <v>0.1133333559389467</v>
+        <v>0.1262748714306232</v>
       </c>
       <c r="AT106" t="n">
-        <v>0.1330569918385893</v>
+        <v>0.1315201904369687</v>
       </c>
       <c r="AU106" t="n">
-        <v>0.1886465767733623</v>
+        <v>0.1985715625174449</v>
       </c>
       <c r="AV106" t="n">
-        <v>0.3740048813836603</v>
+        <v>0.4149192335275125</v>
       </c>
       <c r="AW106" t="n">
-        <v>1.129732327817613</v>
+        <v>1.154761714015246</v>
       </c>
       <c r="AX106" t="n">
-        <v>0.2879303434052132</v>
+        <v>0.3012124187358578</v>
       </c>
       <c r="AY106" t="n">
-        <v>15.15332278249101</v>
+        <v>15.31990927955594</v>
       </c>
       <c r="AZ106" t="inlineStr"/>
       <c r="BA106" t="n">
@@ -21032,13 +21032,13 @@
         <v>0.1344644287524521</v>
       </c>
       <c r="AW107" t="n">
-        <v>1.548834945459407</v>
+        <v>1.548835150990374</v>
       </c>
       <c r="AX107" t="n">
         <v>0.2175137391102846</v>
       </c>
       <c r="AY107" t="n">
-        <v>540.0054829176973</v>
+        <v>540.0051573813989</v>
       </c>
       <c r="AZ107" t="inlineStr"/>
       <c r="BA107" t="n">
@@ -21053,12 +21053,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>IFX.DE</t>
+          <t>2308.TW</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Infineon</t>
+          <t>Delta Electronics</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -21068,16 +21068,16 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Power semiconductors / modules</t>
+          <t>Cooling / thermal management</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Power semiconductors</t>
+          <t>Power supplies, thermal, data center power</t>
         </is>
       </c>
       <c r="F108" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -21126,7 +21126,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>Infineon Technologies AG</t>
+          <t>Delta Electronics, Inc.</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -21136,27 +21136,27 @@
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>TWD</t>
         </is>
       </c>
       <c r="X108" t="n">
-        <v>80672940032</v>
+        <v>4285946658816</v>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>TWD</t>
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>1.156203031539917</v>
+        <v>0.03102217987179756</v>
       </c>
       <c r="AA108" t="n">
-        <v>93274297828.23633</v>
+        <v>132959408170.7197</v>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
@@ -21164,93 +21164,93 @@
         </is>
       </c>
       <c r="AC108" s="2" t="n">
-        <v>36598</v>
+        <v>36529</v>
       </c>
       <c r="AD108" t="n">
-        <v>26.4</v>
+        <v>26.6</v>
       </c>
       <c r="AE108" t="n">
-        <v>60.31999969482422</v>
+        <v>1650</v>
       </c>
       <c r="AF108" t="n">
-        <v>73.17320022583007</v>
+        <v>1964.469541015625</v>
       </c>
       <c r="AG108" t="n">
-        <v>50.77041878700256</v>
+        <v>1495.316409301758</v>
       </c>
       <c r="AH108" t="n">
-        <v>-0.1756544813037805</v>
+        <v>-0.1600786036382347</v>
       </c>
       <c r="AI108" t="n">
-        <v>0.1880934043086204</v>
+        <v>0.1034453910463486</v>
       </c>
       <c r="AJ108" t="n">
-        <v>0.4412565815699498</v>
+        <v>0.3137484005361377</v>
       </c>
       <c r="AK108" t="n">
-        <v>88</v>
+        <v>2506.891357421875</v>
       </c>
       <c r="AL108" t="n">
-        <v>31.03618240356445</v>
+        <v>514.3106689453125</v>
       </c>
       <c r="AM108" t="n">
-        <v>-0.3145454580133612</v>
+        <v>-0.3418143171162851</v>
       </c>
       <c r="AN108" t="n">
-        <v>0.9435379941540931</v>
+        <v>2.208177663091502</v>
       </c>
       <c r="AO108" t="n">
-        <v>45.22584305846683</v>
+        <v>46.92737430167598</v>
       </c>
       <c r="AP108" t="n">
-        <v>3521024</v>
+        <v>9625558</v>
       </c>
       <c r="AQ108" t="n">
-        <v>5149612.32</v>
+        <v>11904469.32</v>
       </c>
       <c r="AR108" t="n">
-        <v>0.6837454513469083</v>
+        <v>0.8085667442419012</v>
       </c>
       <c r="AS108" t="n">
-        <v>-0.1776414321793618</v>
+        <v>-0.1223404255319149</v>
       </c>
       <c r="AT108" t="n">
-        <v>0.03749570567700977</v>
+        <v>-0.2443608820798681</v>
       </c>
       <c r="AU108" t="n">
-        <v>0.4475862494500327</v>
+        <v>0.2958030296566603</v>
       </c>
       <c r="AV108" t="n">
-        <v>0.7141611101740077</v>
+        <v>2.208177663091502</v>
       </c>
       <c r="AW108" t="n">
-        <v>0.7477529874506845</v>
+        <v>5.210492496769102</v>
       </c>
       <c r="AX108" t="n">
-        <v>0.5885052383668115</v>
+        <v>0.6669626472503403</v>
       </c>
       <c r="AY108" t="n">
-        <v>0.1939217120865828</v>
+        <v>65.79636646999613</v>
       </c>
       <c r="AZ108" t="inlineStr"/>
       <c r="BA108" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>Strong momentum</t>
+          <t>Positive momentum</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2308.TW</t>
+          <t>6367.T</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Delta Electronics</t>
+          <t>Daikin Industries</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -21265,11 +21265,11 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Power supplies, thermal, data center power</t>
+          <t>HVAC/cooling</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -21318,37 +21318,37 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>Delta Electronics, Inc.</t>
+          <t>Daikin Industries,Ltd.</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Building Products &amp; Equipment</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="X109" t="n">
-        <v>4285946658816</v>
+        <v>6181845204992</v>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>0.03102217987179756</v>
+        <v>0.006339345127344131</v>
       </c>
       <c r="AA109" t="n">
-        <v>132959408170.7197</v>
+        <v>39188850278.26172</v>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
@@ -21362,67 +21362,67 @@
         <v>26.6</v>
       </c>
       <c r="AE109" t="n">
-        <v>1650</v>
+        <v>22210</v>
       </c>
       <c r="AF109" t="n">
-        <v>1964.469541015625</v>
+        <v>24001.6</v>
       </c>
       <c r="AG109" t="n">
-        <v>1495.316409301758</v>
+        <v>20995.11024414063</v>
       </c>
       <c r="AH109" t="n">
-        <v>-0.1600786036382347</v>
+        <v>-0.07464502366508896</v>
       </c>
       <c r="AI109" t="n">
-        <v>0.1034453910463486</v>
+        <v>0.05786536682742249</v>
       </c>
       <c r="AJ109" t="n">
-        <v>0.3137484005361377</v>
+        <v>0.1431995222172473</v>
       </c>
       <c r="AK109" t="n">
-        <v>2506.891357421875</v>
+        <v>26150</v>
       </c>
       <c r="AL109" t="n">
-        <v>514.3106689453125</v>
+        <v>16864.458984375</v>
       </c>
       <c r="AM109" t="n">
-        <v>-0.3418143171162851</v>
+        <v>-0.1506692160611854</v>
       </c>
       <c r="AN109" t="n">
-        <v>2.208177663091502</v>
+        <v>0.3169707976151306</v>
       </c>
       <c r="AO109" t="n">
-        <v>46.92737430167598</v>
+        <v>22.80285035629454</v>
       </c>
       <c r="AP109" t="n">
-        <v>9625558</v>
+        <v>1168200</v>
       </c>
       <c r="AQ109" t="n">
-        <v>11904469.32</v>
+        <v>1335934</v>
       </c>
       <c r="AR109" t="n">
-        <v>0.8085667442419012</v>
+        <v>0.8744443962052018</v>
       </c>
       <c r="AS109" t="n">
-        <v>-0.1223404255319149</v>
+        <v>-0.1177755710029792</v>
       </c>
       <c r="AT109" t="n">
-        <v>-0.2443608820798681</v>
+        <v>-0.07880547490667777</v>
       </c>
       <c r="AU109" t="n">
-        <v>0.2958030296566603</v>
+        <v>0.1446273321810077</v>
       </c>
       <c r="AV109" t="n">
-        <v>2.208177663091502</v>
+        <v>0.1756590668106905</v>
       </c>
       <c r="AW109" t="n">
-        <v>5.210493923520475</v>
+        <v>0.1608497018995476</v>
       </c>
       <c r="AX109" t="n">
-        <v>0.6669626472503403</v>
+        <v>0.1067557286418612</v>
       </c>
       <c r="AY109" t="n">
-        <v>65.79635099705156</v>
+        <v>19.71195571931356</v>
       </c>
       <c r="AZ109" t="inlineStr"/>
       <c r="BA109" t="n">
@@ -21437,12 +21437,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>6367.T</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Daikin Industries</t>
+          <t>Analog Devices</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -21452,27 +21452,31 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Cooling / thermal management</t>
+          <t>Power semiconductors / modules</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>HVAC/cooling</t>
+          <t>Analog/power semiconductors</t>
         </is>
       </c>
       <c r="F110" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
+        </is>
+      </c>
       <c r="K110" s="1" t="n">
         <v>46195</v>
       </c>
@@ -21508,113 +21512,105 @@
       <c r="S110" t="n">
         <v>0</v>
       </c>
-      <c r="T110" t="inlineStr">
-        <is>
-          <t>Daikin Industries,Ltd.</t>
-        </is>
-      </c>
+      <c r="T110" t="inlineStr"/>
       <c r="U110" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="V110" t="inlineStr">
         <is>
-          <t>Building Products &amp; Equipment</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W110" t="inlineStr">
         <is>
-          <t>JPY</t>
-        </is>
-      </c>
-      <c r="X110" t="n">
-        <v>6181845204992</v>
-      </c>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr"/>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z110" t="n">
-        <v>0.006339345127344131</v>
-      </c>
-      <c r="AA110" t="n">
-        <v>39188850278.26172</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AA110" t="inlineStr"/>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AC110" s="2" t="n">
-        <v>36529</v>
+        <v>29297</v>
       </c>
       <c r="AD110" t="n">
-        <v>26.6</v>
+        <v>46.4</v>
       </c>
       <c r="AE110" t="n">
-        <v>22210</v>
+        <v>389.9299926757812</v>
       </c>
       <c r="AF110" t="n">
-        <v>24001.6</v>
+        <v>394.9421014404297</v>
       </c>
       <c r="AG110" t="n">
-        <v>20995.11024414063</v>
+        <v>333.4506100463867</v>
       </c>
       <c r="AH110" t="n">
-        <v>-0.07464502366508896</v>
+        <v>-0.01269074314024332</v>
       </c>
       <c r="AI110" t="n">
-        <v>0.05786536682742249</v>
+        <v>0.1693785554074638</v>
       </c>
       <c r="AJ110" t="n">
-        <v>0.1431995222172473</v>
+        <v>0.1844095933292453</v>
       </c>
       <c r="AK110" t="n">
-        <v>26150</v>
+        <v>445.4800109863281</v>
       </c>
       <c r="AL110" t="n">
-        <v>16864.4609375</v>
+        <v>220.1645812988281</v>
       </c>
       <c r="AM110" t="n">
-        <v>-0.1506692160611854</v>
+        <v>-0.1246969941200161</v>
       </c>
       <c r="AN110" t="n">
-        <v>0.316970645092699</v>
+        <v>0.7710841152352816</v>
       </c>
       <c r="AO110" t="n">
-        <v>22.80285035629454</v>
+        <v>58.62544784127622</v>
       </c>
       <c r="AP110" t="n">
-        <v>1168200</v>
+        <v>2837500</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1335934</v>
+        <v>4771490</v>
       </c>
       <c r="AR110" t="n">
-        <v>0.8744443962052018</v>
+        <v>0.5946779727087346</v>
       </c>
       <c r="AS110" t="n">
-        <v>-0.1177755710029792</v>
+        <v>-0.0144572256007659</v>
       </c>
       <c r="AT110" t="n">
-        <v>-0.07880547490667777</v>
+        <v>-0.06127419360052611</v>
       </c>
       <c r="AU110" t="n">
-        <v>0.1446273321810077</v>
+        <v>0.2239733993336805</v>
       </c>
       <c r="AV110" t="n">
-        <v>0.1756590668106905</v>
+        <v>0.7710841152352816</v>
       </c>
       <c r="AW110" t="n">
-        <v>0.160849820403685</v>
+        <v>1.531893024705584</v>
       </c>
       <c r="AX110" t="n">
-        <v>0.1067557286418612</v>
+        <v>0.4328279443717782</v>
       </c>
       <c r="AY110" t="n">
-        <v>19.71196515044733</v>
+        <v>877.9847366696275</v>
       </c>
       <c r="AZ110" t="inlineStr"/>
       <c r="BA110" t="n">
@@ -21629,12 +21625,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>CARR</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Analog Devices</t>
+          <t>Carrier Global</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -21644,29 +21640,29 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Power semiconductors / modules</t>
+          <t>Cooling / thermal management</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Analog/power semiconductors</t>
+          <t>HVAC/cooling</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G111" t="n">
         <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="K111" s="1" t="n">
@@ -21704,15 +21700,19 @@
       <c r="S111" t="n">
         <v>0</v>
       </c>
-      <c r="T111" t="inlineStr"/>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Carrier Global Corporation</t>
+        </is>
+      </c>
       <c r="U111" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="V111" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Building Products &amp; Equipment</t>
         </is>
       </c>
       <c r="W111" t="inlineStr">
@@ -21720,7 +21720,9 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="X111" t="inlineStr"/>
+      <c r="X111" t="n">
+        <v>52765048832</v>
+      </c>
       <c r="Y111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,80 +21731,82 @@
       <c r="Z111" t="n">
         <v>1</v>
       </c>
-      <c r="AA111" t="inlineStr"/>
+      <c r="AA111" t="n">
+        <v>52765048832</v>
+      </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC111" s="2" t="n">
-        <v>29297</v>
+        <v>43909</v>
       </c>
       <c r="AD111" t="n">
-        <v>46.4</v>
+        <v>6.4</v>
       </c>
       <c r="AE111" t="n">
-        <v>389.9299926757812</v>
+        <v>64.01000213623047</v>
       </c>
       <c r="AF111" t="n">
-        <v>394.9421014404297</v>
+        <v>68.07908325195312</v>
       </c>
       <c r="AG111" t="n">
-        <v>333.4506102752686</v>
+        <v>60.6597661781311</v>
       </c>
       <c r="AH111" t="n">
-        <v>-0.01269074314024332</v>
+        <v>-0.05976991641710916</v>
       </c>
       <c r="AI111" t="n">
-        <v>0.1693785546047977</v>
+        <v>0.05522995173211176</v>
       </c>
       <c r="AJ111" t="n">
-        <v>0.1844095925162619</v>
+        <v>0.1223103473896479</v>
       </c>
       <c r="AK111" t="n">
-        <v>445.4800109863281</v>
+        <v>75.72768402099609</v>
       </c>
       <c r="AL111" t="n">
-        <v>220.1645812988281</v>
+        <v>49.78788757324219</v>
       </c>
       <c r="AM111" t="n">
-        <v>-0.1246969941200161</v>
+        <v>-0.1547344545954529</v>
       </c>
       <c r="AN111" t="n">
-        <v>0.7710841152352816</v>
+        <v>0.2856541069766487</v>
       </c>
       <c r="AO111" t="n">
-        <v>58.62544784127622</v>
+        <v>43.23922750871295</v>
       </c>
       <c r="AP111" t="n">
-        <v>2837500</v>
+        <v>5059600</v>
       </c>
       <c r="AQ111" t="n">
-        <v>4771490</v>
+        <v>6752774</v>
       </c>
       <c r="AR111" t="n">
-        <v>0.5946779727087346</v>
+        <v>0.7492624512533664</v>
       </c>
       <c r="AS111" t="n">
-        <v>-0.0144572256007659</v>
+        <v>-0.07354797118849921</v>
       </c>
       <c r="AT111" t="n">
-        <v>-0.06127419360052611</v>
+        <v>-0.03875229071894348</v>
       </c>
       <c r="AU111" t="n">
-        <v>0.2239733993336805</v>
+        <v>0.008588835955829932</v>
       </c>
       <c r="AV111" t="n">
-        <v>0.7710841152352816</v>
+        <v>-0.02057718329053526</v>
       </c>
       <c r="AW111" t="n">
-        <v>1.531893526417266</v>
+        <v>0.2581641243707995</v>
       </c>
       <c r="AX111" t="n">
-        <v>0.4328279443717782</v>
+        <v>0.209744724816826</v>
       </c>
       <c r="AY111" t="n">
-        <v>877.9847957204789</v>
+        <v>4.809474572440788</v>
       </c>
       <c r="AZ111" t="inlineStr"/>
       <c r="BA111" t="n">
@@ -21817,12 +21821,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>CARR</t>
+          <t>IFX.DE</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Carrier Global</t>
+          <t>Infineon</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -21832,19 +21836,19 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Cooling / thermal management</t>
+          <t>Power semiconductors / modules</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>HVAC/cooling</t>
+          <t>Power semiconductors</t>
         </is>
       </c>
       <c r="F112" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -21852,11 +21856,7 @@
       <c r="I112" t="n">
         <v>0</v>
       </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
-        </is>
-      </c>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" s="1" t="n">
         <v>46195</v>
       </c>
@@ -21894,37 +21894,37 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>Carrier Global Corporation</t>
+          <t>Infineon Technologies AG</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>Building Products &amp; Equipment</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="X112" t="n">
-        <v>52765048832</v>
+        <v>80672940032</v>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>1</v>
+        <v>1.156203031539917</v>
       </c>
       <c r="AA112" t="n">
-        <v>52765048832</v>
+        <v>93274297828.23633</v>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
@@ -21932,73 +21932,73 @@
         </is>
       </c>
       <c r="AC112" s="2" t="n">
-        <v>43909</v>
+        <v>36598</v>
       </c>
       <c r="AD112" t="n">
-        <v>6.4</v>
+        <v>26.4</v>
       </c>
       <c r="AE112" t="n">
-        <v>64.01000213623047</v>
+        <v>62.08000183105469</v>
       </c>
       <c r="AF112" t="n">
-        <v>68.07908325195312</v>
+        <v>72.79260025024413</v>
       </c>
       <c r="AG112" t="n">
-        <v>60.65976627349853</v>
+        <v>50.90596426963806</v>
       </c>
       <c r="AH112" t="n">
-        <v>-0.05976991641710916</v>
+        <v>-0.1471660358657613</v>
       </c>
       <c r="AI112" t="n">
-        <v>0.05522995007311149</v>
+        <v>0.2195035045840625</v>
       </c>
       <c r="AJ112" t="n">
-        <v>0.1223103456251857</v>
+        <v>0.4299424693082567</v>
       </c>
       <c r="AK112" t="n">
-        <v>75.72768402099609</v>
+        <v>88</v>
       </c>
       <c r="AL112" t="n">
-        <v>49.78788757324219</v>
+        <v>31.03618240356445</v>
       </c>
       <c r="AM112" t="n">
-        <v>-0.1547344545954529</v>
+        <v>-0.2945454337380149</v>
       </c>
       <c r="AN112" t="n">
-        <v>0.2856541069766487</v>
+        <v>1.000246068405788</v>
       </c>
       <c r="AO112" t="n">
-        <v>43.23922750871295</v>
+        <v>47.36263998837984</v>
       </c>
       <c r="AP112" t="n">
-        <v>5059600</v>
+        <v>3524447</v>
       </c>
       <c r="AQ112" t="n">
-        <v>6752774</v>
+        <v>5149680.78</v>
       </c>
       <c r="AR112" t="n">
-        <v>0.7492624512533664</v>
+        <v>0.6844010630111329</v>
       </c>
       <c r="AS112" t="n">
-        <v>-0.07354797118849921</v>
+        <v>-0.1434878731263748</v>
       </c>
       <c r="AT112" t="n">
-        <v>-0.03875229071894348</v>
+        <v>-0.03542571096449254</v>
       </c>
       <c r="AU112" t="n">
-        <v>0.008588835955829932</v>
+        <v>0.4594119737085416</v>
       </c>
       <c r="AV112" t="n">
-        <v>-0.02057706895460831</v>
+        <v>0.772926138118484</v>
       </c>
       <c r="AW112" t="n">
-        <v>0.2581639356947554</v>
+        <v>0.7826948061195205</v>
       </c>
       <c r="AX112" t="n">
-        <v>0.209744724816826</v>
+        <v>0.6348542540677973</v>
       </c>
       <c r="AY112" t="n">
-        <v>4.809473063934595</v>
+        <v>0.228757573792163</v>
       </c>
       <c r="AZ112" t="inlineStr"/>
       <c r="BA112" t="n">
@@ -22013,12 +22013,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MPWR</t>
+          <t>LR.PA</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Monolithic Power Systems</t>
+          <t>Legrand</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -22028,31 +22028,27 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Power semiconductors / modules</t>
+          <t>Power distribution / UPS / electrical</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Power management semiconductors</t>
+          <t>Electrical/data center infrastructure</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I113" t="n">
-        <v>1</v>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J113" t="inlineStr"/>
       <c r="K113" s="1" t="n">
         <v>46195</v>
       </c>
@@ -22090,37 +22086,37 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>Monolithic Power Systems, Inc.</t>
+          <t>Legrand SA</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="V113" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="W113" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="X113" t="n">
-        <v>68875878400</v>
+        <v>36749987840</v>
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>1</v>
+        <v>1.156203031539917</v>
       </c>
       <c r="AA113" t="n">
-        <v>68875878400</v>
+        <v>42490447349.66309</v>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
@@ -22128,73 +22124,73 @@
         </is>
       </c>
       <c r="AC113" s="2" t="n">
-        <v>38310</v>
+        <v>38814</v>
       </c>
       <c r="AD113" t="n">
-        <v>21.7</v>
+        <v>20.3</v>
       </c>
       <c r="AE113" t="n">
-        <v>1401.5400390625</v>
+        <v>140.1999969482422</v>
       </c>
       <c r="AF113" t="n">
-        <v>1420.697885742188</v>
+        <v>140.4699993896485</v>
       </c>
       <c r="AG113" t="n">
-        <v>1216.465447998047</v>
+        <v>137.7360414505005</v>
       </c>
       <c r="AH113" t="n">
-        <v>-0.01348481395795087</v>
+        <v>-0.001922135990456653</v>
       </c>
       <c r="AI113" t="n">
-        <v>0.1521412641592352</v>
+        <v>0.01788896698201681</v>
       </c>
       <c r="AJ113" t="n">
-        <v>0.1678900441276394</v>
+        <v>0.01984925594170273</v>
       </c>
       <c r="AK113" t="n">
-        <v>1687.3154296875</v>
+        <v>157.5401306152344</v>
       </c>
       <c r="AL113" t="n">
-        <v>791.9683837890625</v>
+        <v>121.6237258911133</v>
       </c>
       <c r="AM113" t="n">
-        <v>-0.1693669041347694</v>
+        <v>-0.1100680417064182</v>
       </c>
       <c r="AN113" t="n">
-        <v>0.7696919065847385</v>
+        <v>0.1527355860957571</v>
       </c>
       <c r="AO113" t="n">
-        <v>56.44104709090013</v>
+        <v>60.94419926299307</v>
       </c>
       <c r="AP113" t="n">
-        <v>605700</v>
+        <v>400656</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1021946</v>
+        <v>670564.08</v>
       </c>
       <c r="AR113" t="n">
-        <v>0.5926927645883442</v>
+        <v>0.5974909959388222</v>
       </c>
       <c r="AS113" t="n">
-        <v>0.03607496575869695</v>
+        <v>-0.003553660347156429</v>
       </c>
       <c r="AT113" t="n">
-        <v>-0.1231612522951173</v>
+        <v>-0.07661621234191029</v>
       </c>
       <c r="AU113" t="n">
-        <v>0.1436511680537538</v>
+        <v>0.01371829739975716</v>
       </c>
       <c r="AV113" t="n">
-        <v>0.7687384003441529</v>
+        <v>0.09178629326303289</v>
       </c>
       <c r="AW113" t="n">
-        <v>2.198240182032076</v>
+        <v>0.5737837649193829</v>
       </c>
       <c r="AX113" t="n">
-        <v>0.5021573513324016</v>
+        <v>0.1148522073975351</v>
       </c>
       <c r="AY113" t="n">
-        <v>165.9562549354252</v>
+        <v>9.354092931230282</v>
       </c>
       <c r="AZ113" t="inlineStr"/>
       <c r="BA113" t="n">
@@ -22209,12 +22205,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MYRG</t>
+          <t>MPWR</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MYR Group</t>
+          <t>Monolithic Power Systems</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -22224,27 +22220,31 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Power distribution / UPS / electrical</t>
+          <t>Power semiconductors / modules</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Electrical infrastructure</t>
+          <t>Power management semiconductors</t>
         </is>
       </c>
       <c r="F114" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I114" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
+        </is>
+      </c>
       <c r="K114" s="1" t="n">
         <v>46195</v>
       </c>
@@ -22282,17 +22282,17 @@
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>MYR Group Inc.</t>
+          <t>Monolithic Power Systems, Inc.</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="V114" t="inlineStr">
         <is>
-          <t>Engineering &amp; Construction</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W114" t="inlineStr">
@@ -22301,7 +22301,7 @@
         </is>
       </c>
       <c r="X114" t="n">
-        <v>5253376512</v>
+        <v>68875878400</v>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
@@ -22312,81 +22312,81 @@
         <v>1</v>
       </c>
       <c r="AA114" t="n">
-        <v>5253376512</v>
+        <v>68875878400</v>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>Mid cap</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC114" s="2" t="n">
-        <v>39673</v>
+        <v>38310</v>
       </c>
       <c r="AD114" t="n">
-        <v>18</v>
+        <v>21.7</v>
       </c>
       <c r="AE114" t="n">
-        <v>337.4200134277344</v>
+        <v>1401.5400390625</v>
       </c>
       <c r="AF114" t="n">
-        <v>418.7590002441406</v>
+        <v>1420.697885742188</v>
       </c>
       <c r="AG114" t="n">
-        <v>314.0757004547119</v>
+        <v>1216.465449829102</v>
       </c>
       <c r="AH114" t="n">
-        <v>-0.1942381817918775</v>
+        <v>-0.01348481395795087</v>
       </c>
       <c r="AI114" t="n">
-        <v>0.0743270266984204</v>
+        <v>0.1521412624250029</v>
       </c>
       <c r="AJ114" t="n">
-        <v>0.3333059502466142</v>
+        <v>0.1678900423697016</v>
       </c>
       <c r="AK114" t="n">
-        <v>501.1300048828125</v>
+        <v>1687.3154296875</v>
       </c>
       <c r="AL114" t="n">
-        <v>173.8099975585938</v>
+        <v>791.9683227539062</v>
       </c>
       <c r="AM114" t="n">
-        <v>-0.3266816791250828</v>
+        <v>-0.1693669041347694</v>
       </c>
       <c r="AN114" t="n">
-        <v>0.941315333797099</v>
+        <v>0.769692042970777</v>
       </c>
       <c r="AO114" t="n">
-        <v>31.04214518992667</v>
+        <v>56.44104709090013</v>
       </c>
       <c r="AP114" t="n">
-        <v>194800</v>
+        <v>605700</v>
       </c>
       <c r="AQ114" t="n">
-        <v>310606</v>
+        <v>1021946</v>
       </c>
       <c r="AR114" t="n">
-        <v>0.6271610979826533</v>
+        <v>0.5926927645883442</v>
       </c>
       <c r="AS114" t="n">
-        <v>-0.1953545658071398</v>
+        <v>0.03607496575869695</v>
       </c>
       <c r="AT114" t="n">
-        <v>-0.2293883325355337</v>
+        <v>-0.1231612522951173</v>
       </c>
       <c r="AU114" t="n">
-        <v>0.2554695682664436</v>
+        <v>0.1436510541359353</v>
       </c>
       <c r="AV114" t="n">
-        <v>0.8176040429708675</v>
+        <v>0.7687382641050649</v>
       </c>
       <c r="AW114" t="n">
-        <v>2.602605170132396</v>
+        <v>2.198240404755933</v>
       </c>
       <c r="AX114" t="n">
-        <v>0.4882675176914324</v>
+        <v>0.5021573513324016</v>
       </c>
       <c r="AY114" t="n">
-        <v>19.32650636589081</v>
+        <v>165.9563308036907</v>
       </c>
       <c r="AZ114" t="inlineStr"/>
       <c r="BA114" t="n">
@@ -22401,12 +22401,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NVT</t>
+          <t>MYRG</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>nVent Electric</t>
+          <t>MYR Group</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -22416,16 +22416,16 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Cooling / thermal management</t>
+          <t>Power distribution / UPS / electrical</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Enclosures, electrical/thermal infra</t>
+          <t>Electrical infrastructure</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -22474,7 +22474,7 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>nVent Electric plc</t>
+          <t>MYR Group Inc.</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -22484,7 +22484,7 @@
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Engineering &amp; Construction</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
@@ -22493,7 +22493,7 @@
         </is>
       </c>
       <c r="X115" t="n">
-        <v>26656382976</v>
+        <v>5253376512</v>
       </c>
       <c r="Y115" t="inlineStr">
         <is>
@@ -22504,81 +22504,81 @@
         <v>1</v>
       </c>
       <c r="AA115" t="n">
-        <v>26656382976</v>
+        <v>5253376512</v>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Mid cap</t>
         </is>
       </c>
       <c r="AC115" s="2" t="n">
-        <v>43214</v>
+        <v>39673</v>
       </c>
       <c r="AD115" t="n">
-        <v>8.300000000000001</v>
+        <v>18</v>
       </c>
       <c r="AE115" t="n">
-        <v>164.6900024414062</v>
+        <v>337.4200134277344</v>
       </c>
       <c r="AF115" t="n">
-        <v>161.4322882080078</v>
+        <v>418.7590002441406</v>
       </c>
       <c r="AG115" t="n">
-        <v>129.9591222000122</v>
+        <v>314.0757004547119</v>
       </c>
       <c r="AH115" t="n">
-        <v>0.02018006601752953</v>
+        <v>-0.1942381817918775</v>
       </c>
       <c r="AI115" t="n">
-        <v>0.2672446508829278</v>
+        <v>0.0743270266984204</v>
       </c>
       <c r="AJ115" t="n">
-        <v>0.2421774283728781</v>
+        <v>0.3333059502466142</v>
       </c>
       <c r="AK115" t="n">
-        <v>184.09619140625</v>
+        <v>501.1300048828125</v>
       </c>
       <c r="AL115" t="n">
-        <v>87.42486572265625</v>
+        <v>173.8099975585938</v>
       </c>
       <c r="AM115" t="n">
-        <v>-0.10541331038196</v>
+        <v>-0.3266816791250828</v>
       </c>
       <c r="AN115" t="n">
-        <v>0.8837890236384618</v>
+        <v>0.941315333797099</v>
       </c>
       <c r="AO115" t="n">
-        <v>57.79867847483893</v>
+        <v>31.04214518992667</v>
       </c>
       <c r="AP115" t="n">
-        <v>1434600</v>
+        <v>194800</v>
       </c>
       <c r="AQ115" t="n">
-        <v>2163808</v>
+        <v>310606</v>
       </c>
       <c r="AR115" t="n">
-        <v>0.6629978260548071</v>
+        <v>0.6271610979826533</v>
       </c>
       <c r="AS115" t="n">
-        <v>0.02605842847452933</v>
+        <v>-0.1953545658071398</v>
       </c>
       <c r="AT115" t="n">
-        <v>-0.02966687739905882</v>
+        <v>-0.2293883325355337</v>
       </c>
       <c r="AU115" t="n">
-        <v>0.4661847453061367</v>
+        <v>0.2554695682664436</v>
       </c>
       <c r="AV115" t="n">
-        <v>0.8607438924839257</v>
+        <v>0.8176040429708675</v>
       </c>
       <c r="AW115" t="n">
-        <v>4.57426540026128</v>
+        <v>2.602605170132396</v>
       </c>
       <c r="AX115" t="n">
-        <v>0.5489841411420775</v>
+        <v>0.4882675176914324</v>
       </c>
       <c r="AY115" t="n">
-        <v>7.623467198413071</v>
+        <v>19.32650636589081</v>
       </c>
       <c r="AZ115" t="inlineStr"/>
       <c r="BA115" t="n">
@@ -22593,12 +22593,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ON</t>
+          <t>NVT</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ON Semiconductor</t>
+          <t>nVent Electric</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -22608,31 +22608,27 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Power semiconductors / modules</t>
+          <t>Cooling / thermal management</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Power semiconductors</t>
+          <t>Enclosures, electrical/thermal infra</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>S&amp;P 500, SOXX</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" s="1" t="n">
         <v>46195</v>
       </c>
@@ -22670,17 +22666,17 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>ON Semiconductor Corporation</t>
+          <t>nVent Electric plc</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="V116" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="W116" t="inlineStr">
@@ -22689,7 +22685,7 @@
         </is>
       </c>
       <c r="X116" t="n">
-        <v>31600431104</v>
+        <v>26656382976</v>
       </c>
       <c r="Y116" t="inlineStr">
         <is>
@@ -22700,7 +22696,7 @@
         <v>1</v>
       </c>
       <c r="AA116" t="n">
-        <v>31600431104</v>
+        <v>26656382976</v>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
@@ -22708,73 +22704,73 @@
         </is>
       </c>
       <c r="AC116" s="2" t="n">
-        <v>36648</v>
+        <v>43214</v>
       </c>
       <c r="AD116" t="n">
-        <v>26.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AE116" t="n">
-        <v>81.16999816894531</v>
+        <v>164.6900024414062</v>
       </c>
       <c r="AF116" t="n">
-        <v>101.3394001770019</v>
+        <v>161.4322882080078</v>
       </c>
       <c r="AG116" t="n">
-        <v>75.70005001068115</v>
+        <v>129.9591220855713</v>
       </c>
       <c r="AH116" t="n">
-        <v>-0.1990282355414404</v>
+        <v>0.02018006601752953</v>
       </c>
       <c r="AI116" t="n">
-        <v>0.07225818420849595</v>
+        <v>0.2672446519988529</v>
       </c>
       <c r="AJ116" t="n">
-        <v>0.3386966080300229</v>
+        <v>0.2421774294667294</v>
       </c>
       <c r="AK116" t="n">
-        <v>133.9299926757812</v>
+        <v>184.09619140625</v>
       </c>
       <c r="AL116" t="n">
-        <v>44.90000152587891</v>
+        <v>87.42486572265625</v>
       </c>
       <c r="AM116" t="n">
-        <v>-0.3939371118652842</v>
+        <v>-0.10541331038196</v>
       </c>
       <c r="AN116" t="n">
-        <v>0.8077949980059924</v>
+        <v>0.8837890236384618</v>
       </c>
       <c r="AO116" t="n">
-        <v>43.13725527325886</v>
+        <v>57.79867847483893</v>
       </c>
       <c r="AP116" t="n">
-        <v>9837600</v>
+        <v>1434600</v>
       </c>
       <c r="AQ116" t="n">
-        <v>12353726</v>
+        <v>2163808</v>
       </c>
       <c r="AR116" t="n">
-        <v>0.7963265495770264</v>
+        <v>0.6629978260548071</v>
       </c>
       <c r="AS116" t="n">
-        <v>-0.1541267304776426</v>
+        <v>0.02605842847452933</v>
       </c>
       <c r="AT116" t="n">
-        <v>-0.2134689867320981</v>
+        <v>-0.02966687739905882</v>
       </c>
       <c r="AU116" t="n">
-        <v>0.2449386804938138</v>
+        <v>0.4661847453061367</v>
       </c>
       <c r="AV116" t="n">
-        <v>0.7056103784133183</v>
+        <v>0.8607438924839257</v>
       </c>
       <c r="AW116" t="n">
-        <v>0.8599908181529243</v>
+        <v>4.574265760125077</v>
       </c>
       <c r="AX116" t="n">
-        <v>0.4315696133464617</v>
+        <v>0.5489840299902136</v>
       </c>
       <c r="AY116" t="n">
-        <v>2.382083257039388</v>
+        <v>7.623469782148632</v>
       </c>
       <c r="AZ116" t="inlineStr"/>
       <c r="BA116" t="n">
@@ -22789,12 +22785,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>POWI</t>
+          <t>ON</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Power Integrations</t>
+          <t>ON Semiconductor</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -22809,14 +22805,14 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Power conversion semiconductors</t>
+          <t>Power semiconductors</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -22826,7 +22822,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>S&amp;P 500, SOXX</t>
         </is>
       </c>
       <c r="K117" s="1" t="n">
@@ -22866,7 +22862,7 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>Power Integrations, Inc.</t>
+          <t>ON Semiconductor Corporation</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -22885,7 +22881,7 @@
         </is>
       </c>
       <c r="X117" t="n">
-        <v>3608856064</v>
+        <v>31600431104</v>
       </c>
       <c r="Y117" t="inlineStr">
         <is>
@@ -22896,81 +22892,81 @@
         <v>1</v>
       </c>
       <c r="AA117" t="n">
-        <v>3608856064</v>
+        <v>31600431104</v>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>Mid cap</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC117" s="2" t="n">
-        <v>35776</v>
+        <v>36648</v>
       </c>
       <c r="AD117" t="n">
-        <v>28.7</v>
+        <v>26.3</v>
       </c>
       <c r="AE117" t="n">
-        <v>64.58999633789062</v>
+        <v>81.16999816894531</v>
       </c>
       <c r="AF117" t="n">
-        <v>73.8244995880127</v>
+        <v>101.3394001770019</v>
       </c>
       <c r="AG117" t="n">
-        <v>54.47736031532288</v>
+        <v>75.70005001068115</v>
       </c>
       <c r="AH117" t="n">
-        <v>-0.1250872447718092</v>
+        <v>-0.1990282355414404</v>
       </c>
       <c r="AI117" t="n">
-        <v>0.1856300665824178</v>
+        <v>0.07225818420849595</v>
       </c>
       <c r="AJ117" t="n">
-        <v>0.3551409091906395</v>
+        <v>0.3386966080300229</v>
       </c>
       <c r="AK117" t="n">
-        <v>87.34999847412109</v>
+        <v>133.9299926757812</v>
       </c>
       <c r="AL117" t="n">
-        <v>30.51562690734863</v>
+        <v>44.90000152587891</v>
       </c>
       <c r="AM117" t="n">
-        <v>-0.2605609906561532</v>
+        <v>-0.3939371118652842</v>
       </c>
       <c r="AN117" t="n">
-        <v>1.11662033141244</v>
+        <v>0.8077949980059924</v>
       </c>
       <c r="AO117" t="n">
-        <v>42.0388265914097</v>
+        <v>43.13725527325886</v>
       </c>
       <c r="AP117" t="n">
-        <v>668700</v>
+        <v>9837600</v>
       </c>
       <c r="AQ117" t="n">
-        <v>945838</v>
+        <v>12353726</v>
       </c>
       <c r="AR117" t="n">
-        <v>0.7069921064706641</v>
+        <v>0.7963265495770264</v>
       </c>
       <c r="AS117" t="n">
-        <v>-0.1037880309228137</v>
+        <v>-0.1541267304776426</v>
       </c>
       <c r="AT117" t="n">
-        <v>-0.1164043727960834</v>
+        <v>-0.2134689867320981</v>
       </c>
       <c r="AU117" t="n">
-        <v>0.3738580515127394</v>
+        <v>0.2449386804938138</v>
       </c>
       <c r="AV117" t="n">
-        <v>0.5243178219781863</v>
+        <v>0.7056103784133183</v>
       </c>
       <c r="AW117" t="n">
-        <v>-0.29004571799185</v>
+        <v>0.8599908181529243</v>
       </c>
       <c r="AX117" t="n">
-        <v>0.7436580066362866</v>
+        <v>0.4315696133464617</v>
       </c>
       <c r="AY117" t="n">
-        <v>36.02130477000191</v>
+        <v>2.382083257039388</v>
       </c>
       <c r="AZ117" t="inlineStr"/>
       <c r="BA117" t="n">
@@ -22985,12 +22981,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>PWR</t>
+          <t>POWI</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Quanta Services</t>
+          <t>Power Integrations</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -23000,29 +22996,29 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Power distribution / UPS / electrical</t>
+          <t>Power semiconductors / modules</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Grid/electrical infrastructure construction</t>
+          <t>Power conversion semiconductors</t>
         </is>
       </c>
       <c r="F118" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" t="n">
         <v>1</v>
       </c>
-      <c r="H118" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" t="n">
-        <v>0</v>
-      </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="K118" s="1" t="n">
@@ -23062,17 +23058,17 @@
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>Quanta Services, Inc.</t>
+          <t>Power Integrations, Inc.</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="V118" t="inlineStr">
         <is>
-          <t>Engineering &amp; Construction</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W118" t="inlineStr">
@@ -23081,7 +23077,7 @@
         </is>
       </c>
       <c r="X118" t="n">
-        <v>101009711104</v>
+        <v>3608856064</v>
       </c>
       <c r="Y118" t="inlineStr">
         <is>
@@ -23092,81 +23088,81 @@
         <v>1</v>
       </c>
       <c r="AA118" t="n">
-        <v>101009711104</v>
+        <v>3608856064</v>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Mid cap</t>
         </is>
       </c>
       <c r="AC118" s="2" t="n">
-        <v>35838</v>
+        <v>35776</v>
       </c>
       <c r="AD118" t="n">
-        <v>28.5</v>
+        <v>28.7</v>
       </c>
       <c r="AE118" t="n">
-        <v>671.8599853515625</v>
+        <v>64.58999633789062</v>
       </c>
       <c r="AF118" t="n">
-        <v>676.4345825195312</v>
+        <v>73.8244995880127</v>
       </c>
       <c r="AG118" t="n">
-        <v>567.266852722168</v>
+        <v>54.47736036300659</v>
       </c>
       <c r="AH118" t="n">
-        <v>-0.006762807943570204</v>
+        <v>-0.1250872447718092</v>
       </c>
       <c r="AI118" t="n">
-        <v>0.1843808291062292</v>
+        <v>0.1856300655446428</v>
       </c>
       <c r="AJ118" t="n">
-        <v>0.1924451063436816</v>
+        <v>0.3551409080044925</v>
       </c>
       <c r="AK118" t="n">
-        <v>785.1200561523438</v>
+        <v>87.34999847412109</v>
       </c>
       <c r="AL118" t="n">
-        <v>372.1830444335938</v>
+        <v>30.51562881469727</v>
       </c>
       <c r="AM118" t="n">
-        <v>-0.1442582824285976</v>
+        <v>-0.2605609906561532</v>
       </c>
       <c r="AN118" t="n">
-        <v>0.8051869782892225</v>
+        <v>1.116620199115219</v>
       </c>
       <c r="AO118" t="n">
-        <v>57.14701478372736</v>
+        <v>42.0388265914097</v>
       </c>
       <c r="AP118" t="n">
-        <v>750100</v>
+        <v>668700</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1282646</v>
+        <v>945838</v>
       </c>
       <c r="AR118" t="n">
-        <v>0.584806719858792</v>
+        <v>0.7069921064706641</v>
       </c>
       <c r="AS118" t="n">
-        <v>0.02019555977021725</v>
+        <v>-0.1037880309228137</v>
       </c>
       <c r="AT118" t="n">
-        <v>-0.09803670289322175</v>
+        <v>-0.1164043727960834</v>
       </c>
       <c r="AU118" t="n">
-        <v>0.3227345576631968</v>
+        <v>0.3738580515127394</v>
       </c>
       <c r="AV118" t="n">
-        <v>0.7359804577978024</v>
+        <v>0.5243179592071905</v>
       </c>
       <c r="AW118" t="n">
-        <v>6.600392559934566</v>
+        <v>-0.290045598918205</v>
       </c>
       <c r="AX118" t="n">
-        <v>0.5285996371577715</v>
+        <v>0.7436580066362866</v>
       </c>
       <c r="AY118" t="n">
-        <v>90.35824904533689</v>
+        <v>36.02131488832148</v>
       </c>
       <c r="AZ118" t="inlineStr"/>
       <c r="BA118" t="n">
@@ -23181,12 +23177,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>PWR</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Texas Instruments</t>
+          <t>Quanta Services</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -23196,29 +23192,29 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Power semiconductors / modules</t>
+          <t>Power distribution / UPS / electrical</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Analog/power semiconductors</t>
+          <t>Grid/electrical infrastructure construction</t>
         </is>
       </c>
       <c r="F119" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G119" t="n">
         <v>1</v>
       </c>
       <c r="H119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="K119" s="1" t="n">
@@ -23258,17 +23254,17 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>Texas Instruments Incorporated</t>
+          <t>Quanta Services, Inc.</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Engineering &amp; Construction</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
@@ -23277,7 +23273,7 @@
         </is>
       </c>
       <c r="X119" t="n">
-        <v>261261885440</v>
+        <v>101009711104</v>
       </c>
       <c r="Y119" t="inlineStr">
         <is>
@@ -23288,81 +23284,81 @@
         <v>1</v>
       </c>
       <c r="AA119" t="n">
-        <v>261261885440</v>
+        <v>101009711104</v>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>Mega cap</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC119" s="2" t="n">
-        <v>26451</v>
+        <v>35838</v>
       </c>
       <c r="AD119" t="n">
-        <v>54.2</v>
+        <v>28.5</v>
       </c>
       <c r="AE119" t="n">
-        <v>286.0799865722656</v>
+        <v>671.8599853515625</v>
       </c>
       <c r="AF119" t="n">
-        <v>293.6175274658203</v>
+        <v>676.4345825195312</v>
       </c>
       <c r="AG119" t="n">
-        <v>226.8791889190674</v>
+        <v>567.266852722168</v>
       </c>
       <c r="AH119" t="n">
-        <v>-0.02567129067058893</v>
+        <v>-0.006762807943570204</v>
       </c>
       <c r="AI119" t="n">
-        <v>0.2609353371512466</v>
+        <v>0.1843808291062292</v>
       </c>
       <c r="AJ119" t="n">
-        <v>0.2941580444848995</v>
+        <v>0.1924451063436816</v>
       </c>
       <c r="AK119" t="n">
-        <v>330.5873718261719</v>
+        <v>785.1200561523438</v>
       </c>
       <c r="AL119" t="n">
-        <v>150.7934722900391</v>
+        <v>372.1830749511719</v>
       </c>
       <c r="AM119" t="n">
-        <v>-0.1346312323064444</v>
+        <v>-0.1442582824285976</v>
       </c>
       <c r="AN119" t="n">
-        <v>0.8971642620047497</v>
+        <v>0.8051868302708456</v>
       </c>
       <c r="AO119" t="n">
-        <v>52.23253701975229</v>
+        <v>57.14701478372736</v>
       </c>
       <c r="AP119" t="n">
-        <v>7713700</v>
+        <v>750100</v>
       </c>
       <c r="AQ119" t="n">
-        <v>9183484</v>
+        <v>1282646</v>
       </c>
       <c r="AR119" t="n">
-        <v>0.8399535513972692</v>
+        <v>0.584806719858792</v>
       </c>
       <c r="AS119" t="n">
-        <v>-0.07678434324752226</v>
+        <v>0.02019555977021725</v>
       </c>
       <c r="AT119" t="n">
-        <v>-0.0008868553352538999</v>
+        <v>-0.09803670289322175</v>
       </c>
       <c r="AU119" t="n">
-        <v>0.3051198938336177</v>
+        <v>0.3227345576631968</v>
       </c>
       <c r="AV119" t="n">
-        <v>0.5786596732062796</v>
+        <v>0.7359805946844185</v>
       </c>
       <c r="AW119" t="n">
-        <v>0.7282526915371328</v>
+        <v>6.600392559934566</v>
       </c>
       <c r="AX119" t="n">
-        <v>0.6386445054543586</v>
+        <v>0.5285996371577715</v>
       </c>
       <c r="AY119" t="n">
-        <v>417.2002141526328</v>
+        <v>90.35825496895262</v>
       </c>
       <c r="AZ119" t="inlineStr"/>
       <c r="BA119" t="n">
@@ -23377,12 +23373,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>VICR</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Vicor</t>
+          <t>Texas Instruments</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -23397,22 +23393,26 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>High-density power modules</t>
+          <t>Analog/power semiconductors</t>
         </is>
       </c>
       <c r="F120" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
+        </is>
+      </c>
       <c r="K120" s="1" t="n">
         <v>46195</v>
       </c>
@@ -23450,7 +23450,7 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>Vicor Corporation</t>
+          <t>Texas Instruments Incorporated</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -23460,7 +23460,7 @@
       </c>
       <c r="V120" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W120" t="inlineStr">
@@ -23469,7 +23469,7 @@
         </is>
       </c>
       <c r="X120" t="n">
-        <v>10198808576</v>
+        <v>261261885440</v>
       </c>
       <c r="Y120" t="inlineStr">
         <is>
@@ -23480,81 +23480,81 @@
         <v>1</v>
       </c>
       <c r="AA120" t="n">
-        <v>10198808576</v>
+        <v>261261885440</v>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Mega cap</t>
         </is>
       </c>
       <c r="AC120" s="2" t="n">
-        <v>32966</v>
+        <v>26451</v>
       </c>
       <c r="AD120" t="n">
-        <v>36.3</v>
+        <v>54.2</v>
       </c>
       <c r="AE120" t="n">
-        <v>221.1999969482422</v>
+        <v>286.0799865722656</v>
       </c>
       <c r="AF120" t="n">
-        <v>276.8756002807617</v>
+        <v>293.6175274658203</v>
       </c>
       <c r="AG120" t="n">
-        <v>190.7356502914429</v>
+        <v>226.87918800354</v>
       </c>
       <c r="AH120" t="n">
-        <v>-0.2010852645594717</v>
+        <v>-0.02567129067058893</v>
       </c>
       <c r="AI120" t="n">
-        <v>0.1597202547622847</v>
+        <v>0.2609353422395089</v>
       </c>
       <c r="AJ120" t="n">
-        <v>0.4516195575273816</v>
+        <v>0.2941580497072256</v>
       </c>
       <c r="AK120" t="n">
-        <v>379.7799987792969</v>
+        <v>330.5873718261719</v>
       </c>
       <c r="AL120" t="n">
-        <v>46.02000045776367</v>
+        <v>150.7934722900391</v>
       </c>
       <c r="AM120" t="n">
-        <v>-0.4175575394722431</v>
+        <v>-0.1346312323064444</v>
       </c>
       <c r="AN120" t="n">
-        <v>3.806605709429655</v>
+        <v>0.8971642620047497</v>
       </c>
       <c r="AO120" t="n">
-        <v>46.38825033826483</v>
+        <v>52.23253701975229</v>
       </c>
       <c r="AP120" t="n">
-        <v>341500</v>
+        <v>7713700</v>
       </c>
       <c r="AQ120" t="n">
-        <v>852046</v>
+        <v>9183484</v>
       </c>
       <c r="AR120" t="n">
-        <v>0.4007999568098436</v>
+        <v>0.8399535513972692</v>
       </c>
       <c r="AS120" t="n">
-        <v>-0.1869141449233354</v>
+        <v>-0.07678434324752226</v>
       </c>
       <c r="AT120" t="n">
-        <v>-0.1375209736210421</v>
+        <v>-0.0008868553352538999</v>
       </c>
       <c r="AU120" t="n">
-        <v>0.3836242178283593</v>
+        <v>0.305119984685398</v>
       </c>
       <c r="AV120" t="n">
-        <v>3.806605709429655</v>
+        <v>0.5786596732062796</v>
       </c>
       <c r="AW120" t="n">
-        <v>0.8715626734833521</v>
+        <v>0.7282526915371328</v>
       </c>
       <c r="AX120" t="n">
-        <v>0.8928632191761952</v>
+        <v>0.6386445054543586</v>
       </c>
       <c r="AY120" t="n">
-        <v>103.8773223173978</v>
+        <v>417.2002505911896</v>
       </c>
       <c r="AZ120" t="inlineStr"/>
       <c r="BA120" t="n">
@@ -23569,12 +23569,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>VRT</t>
+          <t>VICR</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Vertiv</t>
+          <t>Vicor</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -23584,19 +23584,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Critical power + liquid/thermal cooling</t>
+          <t>Power semiconductors / modules</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Power, cooling, thermal management AI data centers</t>
+          <t>High-density power modules</t>
         </is>
       </c>
       <c r="F121" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -23604,11 +23604,7 @@
       <c r="I121" t="n">
         <v>0</v>
       </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
-        </is>
-      </c>
+      <c r="J121" t="inlineStr"/>
       <c r="K121" s="1" t="n">
         <v>46195</v>
       </c>
@@ -23641,20 +23637,22 @@
           <t>https://www.blackrock.com/es/profesionales/productos/338777/ishares-ai-infrastructure-ucits-etf</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr"/>
+      <c r="S121" t="n">
+        <v>0</v>
+      </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>Vertiv Holdings Co</t>
+          <t>Vicor Corporation</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
@@ -23663,7 +23661,7 @@
         </is>
       </c>
       <c r="X121" t="n">
-        <v>104870772736</v>
+        <v>10198808576</v>
       </c>
       <c r="Y121" t="inlineStr">
         <is>
@@ -23674,7 +23672,7 @@
         <v>1</v>
       </c>
       <c r="AA121" t="n">
-        <v>104870772736</v>
+        <v>10198808576</v>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
@@ -23682,73 +23680,73 @@
         </is>
       </c>
       <c r="AC121" s="2" t="n">
-        <v>43314</v>
+        <v>32966</v>
       </c>
       <c r="AD121" t="n">
-        <v>8</v>
+        <v>36.4</v>
       </c>
       <c r="AE121" t="n">
-        <v>272.3999938964844</v>
+        <v>221.1999969482422</v>
       </c>
       <c r="AF121" t="n">
-        <v>300.6927432250977</v>
+        <v>276.8756002807617</v>
       </c>
       <c r="AG121" t="n">
-        <v>248.615984954834</v>
+        <v>190.7356502914429</v>
       </c>
       <c r="AH121" t="n">
-        <v>-0.09409189269138241</v>
+        <v>-0.2010852645594717</v>
       </c>
       <c r="AI121" t="n">
-        <v>0.09566564654308629</v>
+        <v>0.1597202547622847</v>
       </c>
       <c r="AJ121" t="n">
-        <v>0.2094666530783387</v>
+        <v>0.4516195575273816</v>
       </c>
       <c r="AK121" t="n">
-        <v>376.1517333984375</v>
+        <v>379.7799987792969</v>
       </c>
       <c r="AL121" t="n">
-        <v>121.6859588623047</v>
+        <v>46.02000045776367</v>
       </c>
       <c r="AM121" t="n">
-        <v>-0.2758241695833272</v>
+        <v>-0.4175575394722431</v>
       </c>
       <c r="AN121" t="n">
-        <v>1.238549101665231</v>
+        <v>3.806605709429655</v>
       </c>
       <c r="AO121" t="n">
-        <v>43.99650537741753</v>
+        <v>46.38825033826483</v>
       </c>
       <c r="AP121" t="n">
-        <v>3907000</v>
+        <v>341500</v>
       </c>
       <c r="AQ121" t="n">
-        <v>6581268</v>
+        <v>852046</v>
       </c>
       <c r="AR121" t="n">
-        <v>0.5936545966521953</v>
+        <v>0.4007999568098436</v>
       </c>
       <c r="AS121" t="n">
-        <v>-0.1457065595855597</v>
+        <v>-0.1869141449233354</v>
       </c>
       <c r="AT121" t="n">
-        <v>-0.1985861685679963</v>
+        <v>-0.1375209736210421</v>
       </c>
       <c r="AU121" t="n">
-        <v>0.3934016848197008</v>
+        <v>0.3836242178283593</v>
       </c>
       <c r="AV121" t="n">
-        <v>0.9563816464022183</v>
+        <v>3.806605709429655</v>
       </c>
       <c r="AW121" t="n">
-        <v>8.870261968645812</v>
+        <v>0.8715626734833521</v>
       </c>
       <c r="AX121" t="n">
-        <v>0.5518564767949636</v>
+        <v>0.8928632191761952</v>
       </c>
       <c r="AY121" t="n">
-        <v>26.41228560046457</v>
+        <v>103.8772867510503</v>
       </c>
       <c r="AZ121" t="inlineStr"/>
       <c r="BA121" t="n">
@@ -23763,12 +23761,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MTZ</t>
+          <t>VRT</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>MasTec</t>
+          <t>Vertiv</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -23778,19 +23776,19 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Power distribution / UPS / electrical</t>
+          <t>Critical power + liquid/thermal cooling</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Infrastructure/electrical construction</t>
+          <t>Power, cooling, thermal management AI data centers</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -23798,7 +23796,11 @@
       <c r="I122" t="n">
         <v>0</v>
       </c>
-      <c r="J122" t="inlineStr"/>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
       <c r="K122" s="1" t="n">
         <v>46195</v>
       </c>
@@ -23831,10 +23833,12 @@
           <t>https://www.blackrock.com/es/profesionales/productos/338777/ishares-ai-infrastructure-ucits-etf</t>
         </is>
       </c>
-      <c r="S122" t="n">
-        <v>0</v>
-      </c>
-      <c r="T122" t="inlineStr"/>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Vertiv Holdings Co</t>
+        </is>
+      </c>
       <c r="U122" t="inlineStr">
         <is>
           <t>Industrials</t>
@@ -23842,7 +23846,7 @@
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>Engineering &amp; Construction</t>
+          <t>Electrical Equipment &amp; Parts</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
@@ -23851,7 +23855,7 @@
         </is>
       </c>
       <c r="X122" t="n">
-        <v>21879883776</v>
+        <v>104870772736</v>
       </c>
       <c r="Y122" t="inlineStr">
         <is>
@@ -23862,7 +23866,7 @@
         <v>1</v>
       </c>
       <c r="AA122" t="n">
-        <v>21879883776</v>
+        <v>104870772736</v>
       </c>
       <c r="AB122" t="inlineStr">
         <is>
@@ -23870,93 +23874,93 @@
         </is>
       </c>
       <c r="AC122" s="2" t="n">
-        <v>26716</v>
+        <v>43314</v>
       </c>
       <c r="AD122" t="n">
-        <v>53.5</v>
+        <v>8</v>
       </c>
       <c r="AE122" t="n">
-        <v>272.4599914550781</v>
+        <v>272.3999938964844</v>
       </c>
       <c r="AF122" t="n">
-        <v>353.9061999511719</v>
+        <v>300.6927432250977</v>
       </c>
       <c r="AG122" t="n">
-        <v>298.5885990905762</v>
+        <v>248.6159850311279</v>
       </c>
       <c r="AH122" t="n">
-        <v>-0.2301350146093253</v>
+        <v>-0.09409189269138241</v>
       </c>
       <c r="AI122" t="n">
-        <v>-0.08750705055410368</v>
+        <v>0.09566564620685414</v>
       </c>
       <c r="AJ122" t="n">
-        <v>0.18526360694641</v>
+        <v>0.209466652707184</v>
       </c>
       <c r="AK122" t="n">
-        <v>437.510009765625</v>
+        <v>376.1517333984375</v>
       </c>
       <c r="AL122" t="n">
-        <v>172.5099945068359</v>
+        <v>121.6859512329102</v>
       </c>
       <c r="AM122" t="n">
-        <v>-0.3772485534650156</v>
+        <v>-0.2758241695833272</v>
       </c>
       <c r="AN122" t="n">
-        <v>0.5793867029790065</v>
+        <v>1.238549242016472</v>
       </c>
       <c r="AO122" t="n">
-        <v>36.13452329015823</v>
+        <v>43.99650537741753</v>
       </c>
       <c r="AP122" t="n">
-        <v>1771200</v>
+        <v>3907000</v>
       </c>
       <c r="AQ122" t="n">
-        <v>1387360</v>
+        <v>6581268</v>
       </c>
       <c r="AR122" t="n">
-        <v>1.276669357628878</v>
+        <v>0.5936545966521953</v>
       </c>
       <c r="AS122" t="n">
-        <v>-0.2693288080884796</v>
+        <v>-0.1457065595855597</v>
       </c>
       <c r="AT122" t="n">
-        <v>-0.3423447685547187</v>
+        <v>-0.1985861685679963</v>
       </c>
       <c r="AU122" t="n">
-        <v>0.0513196002663634</v>
+        <v>0.3934016848197008</v>
       </c>
       <c r="AV122" t="n">
-        <v>0.4890151809861041</v>
+        <v>0.9563818607999486</v>
       </c>
       <c r="AW122" t="n">
-        <v>1.725690215591457</v>
+        <v>8.870262650796588</v>
       </c>
       <c r="AX122" t="n">
-        <v>0.1968372447177376</v>
+        <v>0.5518564767949636</v>
       </c>
       <c r="AY122" t="n">
-        <v>19.09950646653296</v>
+        <v>26.41228296969114</v>
       </c>
       <c r="AZ122" t="inlineStr"/>
       <c r="BA122" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive momentum</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>LR.PA</t>
+          <t>MTZ</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Legrand</t>
+          <t>MasTec</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -23971,11 +23975,11 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Electrical/data center infrastructure</t>
+          <t>Infrastructure/electrical construction</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -24022,11 +24026,7 @@
       <c r="S123" t="n">
         <v>0</v>
       </c>
-      <c r="T123" t="inlineStr">
-        <is>
-          <t>Legrand SA</t>
-        </is>
-      </c>
+      <c r="T123" t="inlineStr"/>
       <c r="U123" t="inlineStr">
         <is>
           <t>Industrials</t>
@@ -24034,27 +24034,27 @@
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>Electrical Equipment &amp; Parts</t>
+          <t>Engineering &amp; Construction</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X123" t="n">
-        <v>36749987840</v>
+        <v>21879883776</v>
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z123" t="n">
-        <v>1.156203031539917</v>
+        <v>1</v>
       </c>
       <c r="AA123" t="n">
-        <v>42490447349.66309</v>
+        <v>21879883776</v>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
@@ -24062,81 +24062,81 @@
         </is>
       </c>
       <c r="AC123" s="2" t="n">
-        <v>38814</v>
+        <v>26716</v>
       </c>
       <c r="AD123" t="n">
-        <v>20.3</v>
+        <v>53.5</v>
       </c>
       <c r="AE123" t="n">
-        <v>139.0500030517578</v>
+        <v>272.4599914550781</v>
       </c>
       <c r="AF123" t="n">
-        <v>140.6189993286133</v>
+        <v>353.9061999511719</v>
       </c>
       <c r="AG123" t="n">
-        <v>137.7543532943725</v>
+        <v>298.5885990905762</v>
       </c>
       <c r="AH123" t="n">
-        <v>-0.01115778297631653</v>
+        <v>-0.2301350146093253</v>
       </c>
       <c r="AI123" t="n">
-        <v>0.009405508620236036</v>
+        <v>-0.08750705055410368</v>
       </c>
       <c r="AJ123" t="n">
-        <v>0.02079532127829875</v>
+        <v>0.18526360694641</v>
       </c>
       <c r="AK123" t="n">
-        <v>157.5401306152344</v>
+        <v>437.510009765625</v>
       </c>
       <c r="AL123" t="n">
-        <v>121.6237258911133</v>
+        <v>172.5099945068359</v>
       </c>
       <c r="AM123" t="n">
-        <v>-0.1173677303127013</v>
+        <v>-0.3772485534650156</v>
       </c>
       <c r="AN123" t="n">
-        <v>0.1432802443188252</v>
+        <v>0.5793867029790065</v>
       </c>
       <c r="AO123" t="n">
-        <v>58.12920849246337</v>
+        <v>36.13452329015823</v>
       </c>
       <c r="AP123" t="n">
-        <v>400656</v>
+        <v>1771200</v>
       </c>
       <c r="AQ123" t="n">
-        <v>670564.08</v>
+        <v>1387360</v>
       </c>
       <c r="AR123" t="n">
-        <v>0.5974909959388222</v>
+        <v>1.276669357628878</v>
       </c>
       <c r="AS123" t="n">
-        <v>-0.01627168696457948</v>
+        <v>-0.2693288080884796</v>
       </c>
       <c r="AT123" t="n">
-        <v>-0.07124912402001327</v>
+        <v>-0.3423447685547187</v>
       </c>
       <c r="AU123" t="n">
-        <v>-0.003459597260273672</v>
+        <v>0.0513196002663634</v>
       </c>
       <c r="AV123" t="n">
-        <v>0.07541427988113858</v>
+        <v>0.4890151809861041</v>
       </c>
       <c r="AW123" t="n">
-        <v>0.5759383894103665</v>
+        <v>1.725690215591457</v>
       </c>
       <c r="AX123" t="n">
-        <v>0.1057076049589016</v>
+        <v>0.1968372447177376</v>
       </c>
       <c r="AY123" t="n">
-        <v>9.269163231274991</v>
+        <v>19.09950646653296</v>
       </c>
       <c r="AZ123" t="inlineStr"/>
       <c r="BA123" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>Weak momentum</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -24260,22 +24260,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AE124" t="n">
-        <v>181.3500061035156</v>
+        <v>179.8999938964844</v>
       </c>
       <c r="AF124" t="n">
-        <v>180.0170001220703</v>
+        <v>179.7529998779297</v>
       </c>
       <c r="AG124" t="n">
-        <v>176.088699798584</v>
+        <v>176.4043598175049</v>
       </c>
       <c r="AH124" t="n">
-        <v>0.007404889430117301</v>
+        <v>0.0008177555793478231</v>
       </c>
       <c r="AI124" t="n">
-        <v>0.02987872765799104</v>
+        <v>0.01981602995864629</v>
       </c>
       <c r="AJ124" t="n">
-        <v>0.02230864517700248</v>
+        <v>0.01898275112865155</v>
       </c>
       <c r="AK124" t="n">
         <v>210.6000061035156</v>
@@ -24284,43 +24284,43 @@
         <v>110.4240570068359</v>
       </c>
       <c r="AM124" t="n">
-        <v>-0.1388888848636729</v>
+        <v>-0.1457740328456656</v>
       </c>
       <c r="AN124" t="n">
-        <v>0.6423052278570867</v>
+        <v>0.6291739207276856</v>
       </c>
       <c r="AO124" t="n">
-        <v>50.16287637929668</v>
+        <v>48.78562973976928</v>
       </c>
       <c r="AP124" t="n">
-        <v>193840</v>
+        <v>195639</v>
       </c>
       <c r="AQ124" t="n">
-        <v>471046.76</v>
+        <v>471082.74</v>
       </c>
       <c r="AR124" t="n">
-        <v>0.411509039994246</v>
+        <v>0.4152964721229226</v>
       </c>
       <c r="AS124" t="n">
-        <v>0.110192833348248</v>
+        <v>0.09361698417315734</v>
       </c>
       <c r="AT124" t="n">
-        <v>-0.1388888848636729</v>
+        <v>-0.1342637571969825</v>
       </c>
       <c r="AU124" t="n">
-        <v>-0.01579487644927557</v>
+        <v>-0.04885664429032077</v>
       </c>
       <c r="AV124" t="n">
-        <v>0.3632847248087006</v>
+        <v>0.3564272563285091</v>
       </c>
       <c r="AW124" t="n">
-        <v>1.434250456359722</v>
+        <v>1.391715564607662</v>
       </c>
       <c r="AX124" t="n">
-        <v>-0.05805509856102598</v>
+        <v>-0.06558656566590015</v>
       </c>
       <c r="AY124" t="n">
-        <v>1.906831827204627</v>
+        <v>1.883590682372755</v>
       </c>
       <c r="AZ124" t="inlineStr"/>
       <c r="BA124" t="n">
@@ -24512,7 +24512,7 @@
         <v>0.3891059547964462</v>
       </c>
       <c r="AY125" t="n">
-        <v>220.5935288347388</v>
+        <v>220.5936784671521</v>
       </c>
       <c r="AZ125" t="inlineStr"/>
       <c r="BA125" t="n">
@@ -24750,22 +24750,22 @@
         <v>29.7</v>
       </c>
       <c r="AE127" t="n">
-        <v>273.1000061035156</v>
+        <v>279.7999877929688</v>
       </c>
       <c r="AF127" t="n">
-        <v>272.7639996337891</v>
+        <v>272.9639996337891</v>
       </c>
       <c r="AG127" t="n">
-        <v>247.1652080535889</v>
+        <v>247.3798863220215</v>
       </c>
       <c r="AH127" t="n">
-        <v>0.001231857833796424</v>
+        <v>0.02504355214735621</v>
       </c>
       <c r="AI127" t="n">
-        <v>0.1049289997332623</v>
+        <v>0.1310539104571544</v>
       </c>
       <c r="AJ127" t="n">
-        <v>0.1035695589269587</v>
+        <v>0.1034203454943139</v>
       </c>
       <c r="AK127" t="n">
         <v>287.4500122070312</v>
@@ -24774,43 +24774,43 @@
         <v>203.75</v>
       </c>
       <c r="AM127" t="n">
-        <v>-0.04992174463078558</v>
+        <v>-0.02661340785942523</v>
       </c>
       <c r="AN127" t="n">
-        <v>0.3403681281154141</v>
+        <v>0.3732514738305215</v>
       </c>
       <c r="AO127" t="n">
-        <v>59.22331950879545</v>
+        <v>63.96568065859807</v>
       </c>
       <c r="AP127" t="n">
-        <v>1203934</v>
+        <v>1204239</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1035011.92</v>
+        <v>1035018.02</v>
       </c>
       <c r="AR127" t="n">
-        <v>1.163207859480498</v>
+        <v>1.163495684838415</v>
       </c>
       <c r="AS127" t="n">
-        <v>-0.002556543903071362</v>
+        <v>0.02547180331312293</v>
       </c>
       <c r="AT127" t="n">
-        <v>0.03212395995438744</v>
+        <v>0.04872563941077734</v>
       </c>
       <c r="AU127" t="n">
-        <v>0.08968950159010003</v>
+        <v>0.1071229587596823</v>
       </c>
       <c r="AV127" t="n">
-        <v>0.200111979004272</v>
+        <v>0.2530078692184963</v>
       </c>
       <c r="AW127" t="n">
-        <v>1.20886800075456</v>
+        <v>1.251216889124606</v>
       </c>
       <c r="AX127" t="n">
-        <v>0.1568063325513733</v>
+        <v>0.1851863438041004</v>
       </c>
       <c r="AY127" t="n">
-        <v>27.72848777675885</v>
+        <v>28.43327988574663</v>
       </c>
       <c r="AZ127" t="inlineStr"/>
       <c r="BA127" t="n">
@@ -24942,22 +24942,22 @@
         <v>28.1</v>
       </c>
       <c r="AE128" t="n">
-        <v>217.1999969482422</v>
+        <v>221.3999938964844</v>
       </c>
       <c r="AF128" t="n">
-        <v>261.0589993286133</v>
+        <v>259.7989993286133</v>
       </c>
       <c r="AG128" t="n">
-        <v>199.242303276062</v>
+        <v>199.6325717544556</v>
       </c>
       <c r="AH128" t="n">
-        <v>-0.1680041771904698</v>
+        <v>-0.1478027457048013</v>
       </c>
       <c r="AI128" t="n">
-        <v>0.09012992410200527</v>
+        <v>0.1090374278642383</v>
       </c>
       <c r="AJ128" t="n">
-        <v>0.3102588909891317</v>
+        <v>0.3013858261975471</v>
       </c>
       <c r="AK128" t="n">
         <v>320.2999877929688</v>
@@ -24966,13 +24966,13 @@
         <v>105.1371765136719</v>
       </c>
       <c r="AM128" t="n">
-        <v>-0.3218857158101641</v>
+        <v>-0.3087730180008937</v>
       </c>
       <c r="AN128" t="n">
-        <v>1.065872454925569</v>
+        <v>1.105820236362291</v>
       </c>
       <c r="AO128" t="n">
-        <v>46.46206187731492</v>
+        <v>49.12133635836167</v>
       </c>
       <c r="AP128" t="n">
         <v>328870</v>
@@ -24984,25 +24984,25 @@
         <v>0.684685439432435</v>
       </c>
       <c r="AS128" t="n">
-        <v>-0.147566741182016</v>
+        <v>-0.1327849931454986</v>
       </c>
       <c r="AT128" t="n">
-        <v>-0.1305044263620806</v>
+        <v>-0.142525238461413</v>
       </c>
       <c r="AU128" t="n">
-        <v>0.3056709065018919</v>
+        <v>0.3179283294092812</v>
       </c>
       <c r="AV128" t="n">
-        <v>0.7662165866976935</v>
+        <v>0.8040144274703811</v>
       </c>
       <c r="AW128" t="n">
-        <v>2.242588923971228</v>
+        <v>2.311300852787763</v>
       </c>
       <c r="AX128" t="n">
-        <v>0.4659242378195878</v>
+        <v>0.4942708189047786</v>
       </c>
       <c r="AY128" t="n">
-        <v>102.1403263390596</v>
+        <v>104.1347749237715</v>
       </c>
       <c r="AZ128" t="inlineStr"/>
       <c r="BA128" t="n">
@@ -25331,7 +25331,7 @@
         <v>33660</v>
       </c>
       <c r="AD130" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="AE130" t="n">
         <v>415.989990234375</v>
@@ -25776,7 +25776,7 @@
         <v>2.086339830934895</v>
       </c>
       <c r="AW132" t="n">
-        <v>12.04643562825177</v>
+        <v>12.04643950104411</v>
       </c>
       <c r="AX132" t="n">
         <v>0.5222581092972174</v>
@@ -25972,13 +25972,13 @@
         <v>1.033012112465263</v>
       </c>
       <c r="AW133" t="n">
-        <v>2.734833512876335</v>
+        <v>2.734833762822262</v>
       </c>
       <c r="AX133" t="n">
         <v>0.4895649844610999</v>
       </c>
       <c r="AY133" t="n">
-        <v>19.11303853455352</v>
+        <v>19.1130349102143</v>
       </c>
       <c r="AZ133" t="inlineStr"/>
       <c r="BA133" t="n">
@@ -26120,16 +26120,16 @@
         <v>553.1085980224609</v>
       </c>
       <c r="AG134" t="n">
-        <v>380.6816046142578</v>
+        <v>380.6816049194336</v>
       </c>
       <c r="AH134" t="n">
         <v>-0.02525468492799698</v>
       </c>
       <c r="AI134" t="n">
-        <v>0.4162491912230553</v>
+        <v>0.4162491900877101</v>
       </c>
       <c r="AJ134" t="n">
-        <v>0.452942803955348</v>
+        <v>0.4529428027905873</v>
       </c>
       <c r="AK134" t="n">
         <v>723</v>
@@ -26162,19 +26162,19 @@
         <v>0.2396891623210571</v>
       </c>
       <c r="AU134" t="n">
-        <v>0.6758658130314172</v>
+        <v>0.6758656540571102</v>
       </c>
       <c r="AV134" t="n">
-        <v>1.965302024890588</v>
+        <v>1.965301776029878</v>
       </c>
       <c r="AW134" t="n">
-        <v>2.959831332390065</v>
+        <v>2.959830444821776</v>
       </c>
       <c r="AX134" t="n">
-        <v>1.010203639260833</v>
+        <v>1.010203867993745</v>
       </c>
       <c r="AY134" t="n">
-        <v>7812.991471598939</v>
+        <v>7812.989784019137</v>
       </c>
       <c r="AZ134" t="inlineStr"/>
       <c r="BA134" t="n">
@@ -26316,28 +26316,28 @@
         <v>1758.692668457031</v>
       </c>
       <c r="AG135" t="n">
-        <v>1404.951274719238</v>
+        <v>1404.951268920898</v>
       </c>
       <c r="AH135" t="n">
         <v>-0.0100658168082246</v>
       </c>
       <c r="AI135" t="n">
-        <v>0.2391817578031594</v>
+        <v>0.2391817629173558</v>
       </c>
       <c r="AJ135" t="n">
-        <v>0.2517819657542812</v>
+        <v>0.2517819709204798</v>
       </c>
       <c r="AK135" t="n">
         <v>1986.870361328125</v>
       </c>
       <c r="AL135" t="n">
-        <v>708.4537353515625</v>
+        <v>708.45361328125</v>
       </c>
       <c r="AM135" t="n">
         <v>-0.1237525990016737</v>
       </c>
       <c r="AN135" t="n">
-        <v>1.457450505741815</v>
+        <v>1.457450929173562</v>
       </c>
       <c r="AO135" t="n">
         <v>50.34200165282481</v>
@@ -26361,16 +26361,16 @@
         <v>0.2380334575343341</v>
       </c>
       <c r="AV135" t="n">
-        <v>1.457450505741815</v>
+        <v>1.457450929173562</v>
       </c>
       <c r="AW135" t="n">
-        <v>1.370924363084391</v>
+        <v>1.370924757223249</v>
       </c>
       <c r="AX135" t="n">
         <v>0.5031651206257604</v>
       </c>
       <c r="AY135" t="n">
-        <v>988.3349611253117</v>
+        <v>988.335363241878</v>
       </c>
       <c r="AZ135" t="inlineStr"/>
       <c r="BA135" t="n">
@@ -26512,16 +26512,16 @@
         <v>221.432600402832</v>
       </c>
       <c r="AG136" t="n">
-        <v>164.3923615264893</v>
+        <v>164.3923616409302</v>
       </c>
       <c r="AH136" t="n">
         <v>-0.1053259535861106</v>
       </c>
       <c r="AI136" t="n">
-        <v>0.2051046579705544</v>
+        <v>0.2051046571316268</v>
       </c>
       <c r="AJ136" t="n">
-        <v>0.3469762119522302</v>
+        <v>0.3469762110145393</v>
       </c>
       <c r="AK136" t="n">
         <v>301.7099914550781</v>
@@ -26560,13 +26560,13 @@
         <v>1.186115370620537</v>
       </c>
       <c r="AW136" t="n">
-        <v>5.025033426744528</v>
+        <v>5.025034125737244</v>
       </c>
       <c r="AX136" t="n">
         <v>0.558456537890379</v>
       </c>
       <c r="AY136" t="n">
-        <v>3264.198447212119</v>
+        <v>3264.199449616654</v>
       </c>
       <c r="AZ136" t="inlineStr"/>
       <c r="BA136" t="n">
@@ -26704,28 +26704,28 @@
         <v>382.4803985595703</v>
       </c>
       <c r="AG137" t="n">
-        <v>295.4204998016357</v>
+        <v>295.4205001831054</v>
       </c>
       <c r="AH137" t="n">
         <v>-0.008289054845467492</v>
       </c>
       <c r="AI137" t="n">
-        <v>0.2839664065739744</v>
+        <v>0.283966404916018</v>
       </c>
       <c r="AJ137" t="n">
-        <v>0.2946982312208941</v>
+        <v>0.2946982295490801</v>
       </c>
       <c r="AK137" t="n">
         <v>483.8399963378906</v>
       </c>
       <c r="AL137" t="n">
-        <v>104.4127044677734</v>
+        <v>104.412712097168</v>
       </c>
       <c r="AM137" t="n">
         <v>-0.2160424924984873</v>
       </c>
       <c r="AN137" t="n">
-        <v>2.632795448523855</v>
+        <v>2.632795183076965</v>
       </c>
       <c r="AO137" t="n">
         <v>60.56011000872214</v>
@@ -26746,19 +26746,19 @@
         <v>0.0547107164229057</v>
       </c>
       <c r="AU137" t="n">
-        <v>0.2649094022479941</v>
+        <v>0.2649092735195344</v>
       </c>
       <c r="AV137" t="n">
         <v>2.572055341548659</v>
       </c>
       <c r="AW137" t="n">
-        <v>2.045019532021571</v>
+        <v>2.045019159024096</v>
       </c>
       <c r="AX137" t="n">
         <v>0.8289261037178648</v>
       </c>
       <c r="AY137" t="n">
-        <v>339.5667230302863</v>
+        <v>339.5666501264917</v>
       </c>
       <c r="AZ137" t="inlineStr"/>
       <c r="BA137" t="n">
@@ -26900,28 +26900,28 @@
         <v>425.6777319335937</v>
       </c>
       <c r="AG138" t="n">
-        <v>358.9664178466797</v>
+        <v>358.9664196777344</v>
       </c>
       <c r="AH138" t="n">
         <v>-0.01324411160307382</v>
       </c>
       <c r="AI138" t="n">
-        <v>0.1701373378172877</v>
+        <v>0.1701373318485246</v>
       </c>
       <c r="AJ138" t="n">
-        <v>0.1858427718311175</v>
+        <v>0.1858427657822426</v>
       </c>
       <c r="AK138" t="n">
         <v>477.5700073242188</v>
       </c>
       <c r="AL138" t="n">
-        <v>224.8433532714844</v>
+        <v>224.8433685302734</v>
       </c>
       <c r="AM138" t="n">
         <v>-0.1204640113428233</v>
       </c>
       <c r="AN138" t="n">
-        <v>0.868145099391707</v>
+        <v>0.8681449726117527</v>
       </c>
       <c r="AO138" t="n">
         <v>57.15554290691522</v>
@@ -26945,10 +26945,10 @@
         <v>0.2102909992776349</v>
       </c>
       <c r="AV138" t="n">
-        <v>0.7504138736224693</v>
+        <v>0.7504139849265103</v>
       </c>
       <c r="AW138" t="n">
-        <v>2.899316019733885</v>
+        <v>2.899316295903767</v>
       </c>
       <c r="AX138" t="n">
         <v>0.3210164320474449</v>
@@ -27140,13 +27140,13 @@
         <v>1.855973990705625</v>
       </c>
       <c r="AW139" t="n">
-        <v>1.387358712549031</v>
+        <v>1.387359293259582</v>
       </c>
       <c r="AX139" t="n">
         <v>1.42976358400038</v>
       </c>
       <c r="AY139" t="n">
-        <v>2.096494856972399</v>
+        <v>2.096494368505751</v>
       </c>
       <c r="AZ139" t="inlineStr"/>
       <c r="BA139" t="n">
@@ -27338,7 +27338,7 @@
         <v>0.1860036686645783</v>
       </c>
       <c r="AY140" t="n">
-        <v>287.6955433720922</v>
+        <v>287.6955094226686</v>
       </c>
       <c r="AZ140" t="inlineStr"/>
       <c r="BA140" t="n">
@@ -27664,22 +27664,22 @@
         <v>27.6</v>
       </c>
       <c r="AE142" t="n">
-        <v>833</v>
+        <v>854</v>
       </c>
       <c r="AF142" t="n">
-        <v>913.15</v>
+        <v>912.2619995117187</v>
       </c>
       <c r="AG142" t="n">
-        <v>725.7428498840331</v>
+        <v>727.3033988952636</v>
       </c>
       <c r="AH142" t="n">
-        <v>-0.08777309313913373</v>
+        <v>-0.06386542412476137</v>
       </c>
       <c r="AI142" t="n">
-        <v>0.1477894685880894</v>
+        <v>0.1742004798783863</v>
       </c>
       <c r="AJ142" t="n">
-        <v>0.258228035103498</v>
+        <v>0.2543073508214009</v>
       </c>
       <c r="AK142" t="n">
         <v>1079</v>
@@ -27688,13 +27688,13 @@
         <v>400.14208984375</v>
       </c>
       <c r="AM142" t="n">
-        <v>-0.2279888785912882</v>
+        <v>-0.2085264133456904</v>
       </c>
       <c r="AN142" t="n">
-        <v>1.081760507436933</v>
+        <v>1.134241864767276</v>
       </c>
       <c r="AO142" t="n">
-        <v>45.02731906911714</v>
+        <v>49.62606996970576</v>
       </c>
       <c r="AP142" t="n">
         <v>148300</v>
@@ -27706,25 +27706,25 @@
         <v>0.7557507382201749</v>
       </c>
       <c r="AS142" t="n">
-        <v>-0.101208447376374</v>
+        <v>-0.06195081601668651</v>
       </c>
       <c r="AT142" t="n">
-        <v>-0.002096436058700246</v>
+        <v>-0.02333031089258331</v>
       </c>
       <c r="AU142" t="n">
-        <v>0.194974615307026</v>
+        <v>0.2479256663861675</v>
       </c>
       <c r="AV142" t="n">
-        <v>0.9479226946611816</v>
+        <v>1.004032288384888</v>
       </c>
       <c r="AW142" t="n">
-        <v>1.50881060710367</v>
+        <v>1.518335454003946</v>
       </c>
       <c r="AX142" t="n">
-        <v>0.5100094940745845</v>
+        <v>0.5480769603117588</v>
       </c>
       <c r="AY142" t="n">
-        <v>282.4063210826537</v>
+        <v>289.5509946845733</v>
       </c>
       <c r="AZ142" t="inlineStr"/>
       <c r="BA142" t="n">
@@ -28294,13 +28294,13 @@
         <v>0.3626578853073692</v>
       </c>
       <c r="AW145" t="n">
-        <v>4.377997078355521</v>
+        <v>4.377998528303203</v>
       </c>
       <c r="AX145" t="n">
         <v>0.150140055850134</v>
       </c>
       <c r="AY145" t="n">
-        <v>38.98858329346925</v>
+        <v>38.98858997386135</v>
       </c>
       <c r="AZ145" t="inlineStr"/>
       <c r="BA145" t="n">
@@ -28492,7 +28492,7 @@
         <v>0.2272847046817197</v>
       </c>
       <c r="AY146" t="n">
-        <v>37.2340648422659</v>
+        <v>37.23406104356654</v>
       </c>
       <c r="AZ146" t="inlineStr"/>
       <c r="BA146" t="n">
@@ -28684,7 +28684,7 @@
         <v>0.3210427659811068</v>
       </c>
       <c r="AY147" t="n">
-        <v>-0.08979230781496661</v>
+        <v>-0.08979245295354188</v>
       </c>
       <c r="AZ147" t="inlineStr"/>
       <c r="BA147" t="n">
@@ -28870,13 +28870,13 @@
         <v>1.495692449375667</v>
       </c>
       <c r="AW148" t="n">
-        <v>7.081864066213734</v>
+        <v>7.08186341267208</v>
       </c>
       <c r="AX148" t="n">
         <v>0.4010415177202122</v>
       </c>
       <c r="AY148" t="n">
-        <v>71.73170530248629</v>
+        <v>71.73171191867401</v>
       </c>
       <c r="AZ148" t="inlineStr"/>
       <c r="BA148" t="n">
@@ -29018,28 +29018,28 @@
         <v>117.6540788269043</v>
       </c>
       <c r="AG149" t="n">
-        <v>90.16120594024659</v>
+        <v>90.16120582580567</v>
       </c>
       <c r="AH149" t="n">
         <v>0.03209341755016171</v>
       </c>
       <c r="AI149" t="n">
-        <v>0.3468098506319033</v>
+        <v>0.3468098523413987</v>
       </c>
       <c r="AJ149" t="n">
-        <v>0.3049301814449812</v>
+        <v>0.3049301831013189</v>
       </c>
       <c r="AK149" t="n">
         <v>129.5154876708984</v>
       </c>
       <c r="AL149" t="n">
-        <v>64.85704040527344</v>
+        <v>64.85703277587891</v>
       </c>
       <c r="AM149" t="n">
         <v>-0.06242872965330637</v>
       </c>
       <c r="AN149" t="n">
-        <v>0.8722716847144705</v>
+        <v>0.8722719049573453</v>
       </c>
       <c r="AO149" t="n">
         <v>78.37124698061908</v>
@@ -29072,7 +29072,7 @@
         <v>0.6115822169461609</v>
       </c>
       <c r="AY149" t="n">
-        <v>2450.421294588843</v>
+        <v>2450.421847673214</v>
       </c>
       <c r="AZ149" t="inlineStr"/>
       <c r="BA149" t="n">
@@ -29214,16 +29214,16 @@
         <v>415.4798052978516</v>
       </c>
       <c r="AG150" t="n">
-        <v>221.0837461471558</v>
+        <v>221.0837464904785</v>
       </c>
       <c r="AH150" t="n">
         <v>0.09215895267971108</v>
       </c>
       <c r="AI150" t="n">
-        <v>1.05248009825036</v>
+        <v>1.052480095063047</v>
       </c>
       <c r="AJ150" t="n">
-        <v>0.8792869785248874</v>
+        <v>0.8792869756065274</v>
       </c>
       <c r="AK150" t="n">
         <v>467.2699890136719</v>
@@ -29262,10 +29262,10 @@
         <v>2.43128803669638</v>
       </c>
       <c r="AW150" t="n">
-        <v>9.235262979646681</v>
+        <v>9.235264741023961</v>
       </c>
       <c r="AX150" t="n">
-        <v>2.583104762571462</v>
+        <v>2.583104546710907</v>
       </c>
       <c r="AY150" t="n">
         <v>40.39325497062877</v>
@@ -29410,16 +29410,16 @@
         <v>47.53984031677246</v>
       </c>
       <c r="AG151" t="n">
-        <v>30.001917552948</v>
+        <v>30.00191758155823</v>
       </c>
       <c r="AH151" t="n">
         <v>0.1194821199667904</v>
       </c>
       <c r="AI151" t="n">
-        <v>0.7738866566371758</v>
+        <v>0.7738866549455738</v>
       </c>
       <c r="AJ151" t="n">
-        <v>0.5845600612985213</v>
+        <v>0.5845600597874636</v>
       </c>
       <c r="AK151" t="n">
         <v>55.98620223999023</v>
@@ -29458,7 +29458,7 @@
         <v>1.663164725585572</v>
       </c>
       <c r="AW151" t="n">
-        <v>3.230375639680277</v>
+        <v>3.230374677615693</v>
       </c>
       <c r="AX151" t="n">
         <v>1.222585024650067</v>
@@ -29650,13 +29650,13 @@
         <v>0.4677566115175937</v>
       </c>
       <c r="AW152" t="n">
-        <v>1.36270687113449</v>
+        <v>1.36270603169836</v>
       </c>
       <c r="AX152" t="n">
         <v>0.2517511554739953</v>
       </c>
       <c r="AY152" t="n">
-        <v>48.28883309197764</v>
+        <v>48.28881025992209</v>
       </c>
       <c r="AZ152" t="inlineStr"/>
       <c r="BA152" t="n">
@@ -29771,10 +29771,10 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>1.349272727966309</v>
+        <v>1.349236369132996</v>
       </c>
       <c r="AA153" t="n">
-        <v>170529785225.7422</v>
+        <v>170525189962.0068</v>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
@@ -29788,22 +29788,22 @@
         <v>38.1</v>
       </c>
       <c r="AE153" t="n">
-        <v>1533.400024414062</v>
+        <v>1530</v>
       </c>
       <c r="AF153" t="n">
-        <v>1392.60396484375</v>
+        <v>1396.456987304688</v>
       </c>
       <c r="AG153" t="n">
-        <v>1246.672521362305</v>
+        <v>1248.650485839844</v>
       </c>
       <c r="AH153" t="n">
-        <v>0.1011027277852896</v>
+        <v>0.09562987897899022</v>
       </c>
       <c r="AI153" t="n">
-        <v>0.2299942431862023</v>
+        <v>0.2253228724537117</v>
       </c>
       <c r="AJ153" t="n">
-        <v>0.1170567578741355</v>
+        <v>0.1183729980014616</v>
       </c>
       <c r="AK153" t="n">
         <v>1570.339965820312</v>
@@ -29812,43 +29812,43 @@
         <v>1025.915771484375</v>
       </c>
       <c r="AM153" t="n">
-        <v>-0.0235235313437071</v>
+        <v>-0.02568868315036466</v>
       </c>
       <c r="AN153" t="n">
-        <v>0.4946646372298378</v>
+        <v>0.4913505012075958</v>
       </c>
       <c r="AO153" t="n">
-        <v>70.6854248496783</v>
+        <v>71.42474951365047</v>
       </c>
       <c r="AP153" t="n">
-        <v>10778557</v>
+        <v>10788338</v>
       </c>
       <c r="AQ153" t="n">
-        <v>25310007.28</v>
+        <v>25310202.9</v>
       </c>
       <c r="AR153" t="n">
-        <v>0.4258614737150719</v>
+        <v>0.4262446272210643</v>
       </c>
       <c r="AS153" t="n">
-        <v>0.06757076146180285</v>
+        <v>0.06372247361711514</v>
       </c>
       <c r="AT153" t="n">
-        <v>0.249151685317839</v>
+        <v>0.2846838744897016</v>
       </c>
       <c r="AU153" t="n">
-        <v>0.2477835564238149</v>
+        <v>0.2000985834658981</v>
       </c>
       <c r="AV153" t="n">
-        <v>0.423886759315484</v>
+        <v>0.4280221036624443</v>
       </c>
       <c r="AW153" t="n">
-        <v>13.06047255618203</v>
+        <v>12.90943338906396</v>
       </c>
       <c r="AX153" t="n">
-        <v>0.2811412482873565</v>
+        <v>0.2783005599785742</v>
       </c>
       <c r="AY153" t="n">
-        <v>11.31539439863666</v>
+        <v>11.28808809474921</v>
       </c>
       <c r="AZ153" t="inlineStr"/>
       <c r="BA153" t="n">
@@ -30044,7 +30044,7 @@
         <v>0.1540634345581156</v>
       </c>
       <c r="AY154" t="n">
-        <v>708.8073765793529</v>
+        <v>708.8071455763491</v>
       </c>
       <c r="AZ154" t="inlineStr"/>
       <c r="BA154" t="n">
@@ -30230,7 +30230,7 @@
         <v>0.5259712376725314</v>
       </c>
       <c r="AW155" t="n">
-        <v>2.177017151259538</v>
+        <v>2.177017452067459</v>
       </c>
       <c r="AX155" t="n">
         <v>0.4831549553861383</v>
@@ -30422,7 +30422,7 @@
         <v>0.1572533001436602</v>
       </c>
       <c r="AW156" t="n">
-        <v>3.727004545297219</v>
+        <v>3.727005117362909</v>
       </c>
       <c r="AX156" t="n">
         <v>0.1217418774533061</v>
@@ -30950,16 +30950,16 @@
         <v>345.1192010498047</v>
       </c>
       <c r="AG159" t="n">
-        <v>281.3558094787597</v>
+        <v>281.3558088684082</v>
       </c>
       <c r="AH159" t="n">
         <v>-0.01129812487175663</v>
       </c>
       <c r="AI159" t="n">
-        <v>0.2127704128549821</v>
+        <v>0.2127704154858725</v>
       </c>
       <c r="AJ159" t="n">
-        <v>0.2266290207021959</v>
+        <v>0.2266290233631503</v>
       </c>
       <c r="AK159" t="n">
         <v>385.6300048828125</v>
@@ -30992,19 +30992,19 @@
         <v>-0.03900583132150293</v>
       </c>
       <c r="AU159" t="n">
-        <v>0.3219916084233581</v>
+        <v>0.3219917647284165</v>
       </c>
       <c r="AV159" t="n">
         <v>0.5495733755640733</v>
       </c>
       <c r="AW159" t="n">
-        <v>4.864132260445772</v>
+        <v>4.86413149155783</v>
       </c>
       <c r="AX159" t="n">
-        <v>0.420210302602134</v>
+        <v>0.4202102124053861</v>
       </c>
       <c r="AY159" t="n">
-        <v>460.7500835425156</v>
+        <v>460.749971809701</v>
       </c>
       <c r="AZ159" t="inlineStr"/>
       <c r="BA159" t="n">
@@ -32443,13 +32443,13 @@
         <v>480.8090515136719</v>
       </c>
       <c r="AL5" t="n">
-        <v>287.4934692382812</v>
+        <v>287.4934997558594</v>
       </c>
       <c r="AM5" t="n">
         <v>-0.1103328682790791</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.4878947020917808</v>
+        <v>0.4878945441510174</v>
       </c>
       <c r="AO5" t="n">
         <v>73.57863850003642</v>
@@ -32482,7 +32482,7 @@
         <v>0.2350721494968062</v>
       </c>
       <c r="AY5" t="n">
-        <v>375.6847560453293</v>
+        <v>375.6847165026617</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -32830,28 +32830,28 @@
         <v>337.7683770751953</v>
       </c>
       <c r="AG7" t="n">
-        <v>244.932223815918</v>
+        <v>244.9322232818604</v>
       </c>
       <c r="AH7" t="n">
         <v>-0.07821445927070403</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.2711680041639388</v>
+        <v>0.2711680069356319</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.3790279278607684</v>
+        <v>0.3790279308676425</v>
       </c>
       <c r="AK7" t="n">
         <v>433.3299865722656</v>
       </c>
       <c r="AL7" t="n">
-        <v>96.49594879150391</v>
+        <v>96.49594116210938</v>
       </c>
       <c r="AM7" t="n">
         <v>-0.2814944366847034</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.226560389351069</v>
+        <v>2.226560644457158</v>
       </c>
       <c r="AO7" t="n">
         <v>51.28780555467554</v>
@@ -32875,16 +32875,16 @@
         <v>0.3503425054150335</v>
       </c>
       <c r="AV7" t="n">
-        <v>2.157570955706555</v>
+        <v>2.157571200020055</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.110391380226764</v>
+        <v>4.110391060249222</v>
       </c>
       <c r="AX7" t="n">
         <v>0.68562960324334</v>
       </c>
       <c r="AY7" t="n">
-        <v>1650.444647642039</v>
+        <v>1650.444517115374</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
@@ -33032,16 +33032,16 @@
         <v>240.8528381347656</v>
       </c>
       <c r="AG8" t="n">
-        <v>138.071287689209</v>
+        <v>138.0712878417969</v>
       </c>
       <c r="AH8" t="n">
         <v>-0.09189361057758594</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.5841092299582955</v>
+        <v>0.5841092282076354</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.7444092987450972</v>
+        <v>0.7444092968172835</v>
       </c>
       <c r="AK8" t="n">
         <v>316.3519592285156</v>
@@ -33077,16 +33077,16 @@
         <v>1.726500796368783</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.889729871176091</v>
+        <v>1.889729579892497</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.678710303790584</v>
+        <v>2.678710067763018</v>
       </c>
       <c r="AX8" t="n">
         <v>1.450396679886195</v>
       </c>
       <c r="AY8" t="n">
-        <v>17.03236073945209</v>
+        <v>17.03236357506422</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
@@ -33363,7 +33363,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.228073221760904</v>
+        <v>1.228073215889642</v>
       </c>
     </row>
   </sheetData>
@@ -33540,31 +33540,31 @@
         <v>0.3330897518179773</v>
       </c>
       <c r="N2" t="n">
-        <v>1.245017596250422</v>
+        <v>1.245017611931784</v>
       </c>
       <c r="O2" t="n">
         <v>0.7569965673307444</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6173477193918842</v>
+        <v>0.6173477212351203</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.568810084333022</v>
+        <v>4.568810270029648</v>
       </c>
       <c r="R2" t="n">
         <v>1.532000997437697</v>
       </c>
       <c r="S2" t="n">
-        <v>5.719359368867556</v>
+        <v>5.719360199586927</v>
       </c>
       <c r="T2" t="n">
-        <v>1298.271945760483</v>
+        <v>1298.271648648233</v>
       </c>
       <c r="U2" t="n">
-        <v>324.5933320519785</v>
+        <v>324.5932881027284</v>
       </c>
       <c r="V2" t="n">
-        <v>3953.341716501945</v>
+        <v>3953.340805346036</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -33582,10 +33582,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>1531.086502073228</v>
+        <v>1531.081906809492</v>
       </c>
       <c r="D3" t="n">
-        <v>102.0724334715485</v>
+        <v>102.0721271206328</v>
       </c>
       <c r="E3" t="n">
         <v>44.827049984</v>
@@ -33597,7 +33597,7 @@
         <v>90</v>
       </c>
       <c r="H3" t="n">
-        <v>89.06454875034335</v>
+        <v>89.06453093616649</v>
       </c>
       <c r="I3" t="n">
         <v>10</v>
@@ -33606,40 +33606,40 @@
         <v>0.625</v>
       </c>
       <c r="K3" t="n">
-        <v>0.513367766493307</v>
+        <v>0.5131902043454265</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3010920071342317</v>
+        <v>0.2996716629798405</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8746682920085986</v>
+        <v>0.8743536465194296</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7590397984911563</v>
+        <v>0.7592982575128413</v>
       </c>
       <c r="O3" t="n">
         <v>0.5645833578458648</v>
       </c>
       <c r="P3" t="n">
-        <v>1.080575796431043</v>
+        <v>1.081038343886206</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.912364590038381</v>
+        <v>6.902924605238539</v>
       </c>
       <c r="R3" t="n">
-        <v>4.944601093514495</v>
+        <v>4.944600709070524</v>
       </c>
       <c r="S3" t="n">
-        <v>6.015890802489165</v>
+        <v>5.999047774274203</v>
       </c>
       <c r="T3" t="n">
-        <v>253.9952078946295</v>
+        <v>253.9935131374394</v>
       </c>
       <c r="U3" t="n">
-        <v>38.81365990644734</v>
+        <v>38.81365800709766</v>
       </c>
       <c r="V3" t="n">
-        <v>850.8189491650901</v>
+        <v>850.8185798039475</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -33681,40 +33681,40 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="K4" t="n">
-        <v>2.054501610841144</v>
+        <v>2.036208940780448</v>
       </c>
       <c r="L4" t="n">
         <v>1.674591954577161</v>
       </c>
       <c r="M4" t="n">
-        <v>1.958694367217515</v>
+        <v>1.954670431167297</v>
       </c>
       <c r="N4" t="n">
-        <v>4.152239609508919</v>
+        <v>4.133038142605304</v>
       </c>
       <c r="O4" t="n">
         <v>5.040586953107727</v>
       </c>
       <c r="P4" t="n">
-        <v>4.17510817025595</v>
+        <v>4.17088432132443</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.451370459707759</v>
+        <v>4.427269506216955</v>
       </c>
       <c r="R4" t="n">
-        <v>4.369886564181203</v>
+        <v>4.369887299668052</v>
       </c>
       <c r="S4" t="n">
-        <v>5.220649750279208</v>
+        <v>5.215348492133582</v>
       </c>
       <c r="T4" t="n">
-        <v>35.08554580651369</v>
+        <v>35.03326402098823</v>
       </c>
       <c r="U4" t="n">
-        <v>26.61096765653703</v>
+        <v>26.61098226599517</v>
       </c>
       <c r="V4" t="n">
-        <v>51.52608410975044</v>
+        <v>51.514590560554</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -33756,40 +33756,40 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0.53792273623982</v>
+        <v>0.5404605825711591</v>
       </c>
       <c r="L5" t="n">
         <v>0.5031651206257604</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4639085822551054</v>
+        <v>0.464349035296327</v>
       </c>
       <c r="N5" t="n">
-        <v>1.31903679621124</v>
+        <v>1.322777454851159</v>
       </c>
       <c r="O5" t="n">
         <v>1.186115370620537</v>
       </c>
       <c r="P5" t="n">
-        <v>1.110725812665491</v>
+        <v>1.111375084761617</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.264426349712605</v>
+        <v>3.265107143214924</v>
       </c>
       <c r="R5" t="n">
-        <v>2.81707476630511</v>
+        <v>2.817075029363015</v>
       </c>
       <c r="S5" t="n">
-        <v>3.054035932729045</v>
+        <v>3.054147241227746</v>
       </c>
       <c r="T5" t="n">
-        <v>881.1999657110689</v>
+        <v>881.6762514615748</v>
       </c>
       <c r="U5" t="n">
-        <v>38.98858329346925</v>
+        <v>38.98858997386135</v>
       </c>
       <c r="V5" t="n">
-        <v>1241.060236195859</v>
+        <v>1241.142850314779</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -33822,53 +33822,53 @@
         <v>60</v>
       </c>
       <c r="H6" t="n">
-        <v>71.83136436070642</v>
+        <v>70.98773551894804</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2173913043478261</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4253784452937656</v>
+        <v>0.4281622687125622</v>
       </c>
       <c r="L6" t="n">
         <v>0.4605477310316053</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4532626244776041</v>
+        <v>0.4581183650810024</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7690269758973944</v>
+        <v>0.7739903584707721</v>
       </c>
       <c r="O6" t="n">
         <v>0.642135025809799</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6701809866817897</v>
+        <v>0.6796364313312933</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.653580967266656</v>
+        <v>2.654275529237097</v>
       </c>
       <c r="R6" t="n">
-        <v>1.540364235938337</v>
+        <v>1.540364087847979</v>
       </c>
       <c r="S6" t="n">
-        <v>2.590151589548375</v>
+        <v>2.595441454008023</v>
       </c>
       <c r="T6" t="n">
-        <v>182.2113799555414</v>
+        <v>182.2233497004258</v>
       </c>
       <c r="U6" t="n">
-        <v>31.21679518523325</v>
+        <v>31.21679892900631</v>
       </c>
       <c r="V6" t="n">
-        <v>289.0293424080502</v>
+        <v>289.0557255167541</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Narrow momentum</t>
+          <t>Weak breadth</t>
         </is>
       </c>
     </row>
@@ -33882,10 +33882,10 @@
         <v>13</v>
       </c>
       <c r="C7" t="n">
-        <v>2826.255306923504</v>
+        <v>2815.795240397269</v>
       </c>
       <c r="D7" t="n">
-        <v>282.6255306923504</v>
+        <v>281.579524039727</v>
       </c>
       <c r="E7" t="n">
         <v>171.282805446418</v>
@@ -33897,7 +33897,7 @@
         <v>85</v>
       </c>
       <c r="H7" t="n">
-        <v>68.50333040347438</v>
+        <v>68.53491842537272</v>
       </c>
       <c r="I7" t="n">
         <v>7</v>
@@ -33906,40 +33906,40 @@
         <v>0.5384615384615384</v>
       </c>
       <c r="K7" t="n">
-        <v>1.414841048104724</v>
+        <v>1.414841025646756</v>
       </c>
       <c r="L7" t="n">
         <v>1.159747998174404</v>
       </c>
       <c r="M7" t="n">
-        <v>1.237623673659668</v>
+        <v>1.238789606623576</v>
       </c>
       <c r="N7" t="n">
-        <v>7.653640497500095</v>
+        <v>7.653640350642939</v>
       </c>
       <c r="O7" t="n">
-        <v>4.69163317837754</v>
+        <v>4.691632877778304</v>
       </c>
       <c r="P7" t="n">
-        <v>5.787448142729127</v>
+        <v>5.796777085402929</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.945129128601252</v>
+        <v>5.945128572488658</v>
       </c>
       <c r="R7" t="n">
-        <v>4.658645577641912</v>
+        <v>4.658645737931193</v>
       </c>
       <c r="S7" t="n">
-        <v>5.564526627001125</v>
+        <v>5.564450030622821</v>
       </c>
       <c r="T7" t="n">
-        <v>284.5139292309217</v>
+        <v>284.5139219351889</v>
       </c>
       <c r="U7" t="n">
-        <v>42.8888202659774</v>
+        <v>42.88882335986975</v>
       </c>
       <c r="V7" t="n">
-        <v>262.3583166163779</v>
+        <v>263.2251574579711</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -33981,40 +33981,40 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6240850795438094</v>
+        <v>0.6239387755343552</v>
       </c>
       <c r="L8" t="n">
         <v>0.4770550103675077</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4238172336044352</v>
+        <v>0.4240010931795615</v>
       </c>
       <c r="N8" t="n">
-        <v>1.659822774013612</v>
+        <v>1.660589776386783</v>
       </c>
       <c r="O8" t="n">
         <v>1.114542643229167</v>
       </c>
       <c r="P8" t="n">
-        <v>1.004338532138164</v>
+        <v>1.004638778333778</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.212010512395388</v>
+        <v>6.202146542561576</v>
       </c>
       <c r="R8" t="n">
-        <v>3.586805462047716</v>
+        <v>3.586805946455038</v>
       </c>
       <c r="S8" t="n">
-        <v>8.293174463745117</v>
+        <v>8.293245497254979</v>
       </c>
       <c r="T8" t="n">
-        <v>197.5367847797015</v>
+        <v>197.5261041740687</v>
       </c>
       <c r="U8" t="n">
-        <v>26.6385694438311</v>
+        <v>26.32768796510136</v>
       </c>
       <c r="V8" t="n">
-        <v>343.4119584360716</v>
+        <v>343.4134653095337</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -34056,13 +34056,13 @@
         <v>0.6</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3207051478981538</v>
+        <v>0.3207051391515057</v>
       </c>
       <c r="L9" t="n">
         <v>0.1956943154225714</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3464186739509562</v>
+        <v>0.3464186675473536</v>
       </c>
       <c r="N9" t="n">
         <v>0.4287928005769806</v>
@@ -34074,22 +34074,22 @@
         <v>0.5097264054326101</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.708089264581258</v>
+        <v>1.708089235290239</v>
       </c>
       <c r="R9" t="n">
         <v>0.6637111084063636</v>
       </c>
       <c r="S9" t="n">
-        <v>6.515366092812478</v>
+        <v>6.515366071367915</v>
       </c>
       <c r="T9" t="n">
-        <v>61.50050932531984</v>
+        <v>61.50048797635068</v>
       </c>
       <c r="U9" t="n">
         <v>8.332562176392107</v>
       </c>
       <c r="V9" t="n">
-        <v>267.5384929945203</v>
+        <v>267.538406984852</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -34131,40 +34131,40 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5546118756513103</v>
+        <v>0.5546118825779528</v>
       </c>
       <c r="L10" t="n">
-        <v>0.09379661526984795</v>
+        <v>0.09379666984393364</v>
       </c>
       <c r="M10" t="n">
-        <v>0.08119478447334243</v>
+        <v>0.08119481087028246</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5756916640729238</v>
+        <v>0.5756916265609037</v>
       </c>
       <c r="O10" t="n">
         <v>0.1507375961902657</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2638990407354103</v>
+        <v>0.2638989951017127</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6104968531750755</v>
+        <v>0.6104968860458077</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6724554068884159</v>
+        <v>0.672455481112939</v>
       </c>
       <c r="S10" t="n">
-        <v>0.974481521071595</v>
+        <v>0.9744815619874879</v>
       </c>
       <c r="T10" t="n">
-        <v>1253.331587670957</v>
+        <v>1253.332106421999</v>
       </c>
       <c r="U10" t="n">
-        <v>11.51117059924929</v>
+        <v>11.51117295827163</v>
       </c>
       <c r="V10" t="n">
-        <v>3000.718070976272</v>
+        <v>3000.719761484623</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -34224,13 +34224,13 @@
         <v>1.129456205977184</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4177837391396646</v>
+        <v>0.4177838758235302</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4177837391396646</v>
+        <v>0.4177838758235302</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4177837391396647</v>
+        <v>0.4177838758235302</v>
       </c>
       <c r="T11" t="n">
         <v>12.29820481571351</v>
@@ -34266,13 +34266,13 @@
         <v>47.19718195199999</v>
       </c>
       <c r="F12" t="n">
-        <v>36.57894736842105</v>
+        <v>37.89473684210526</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
       </c>
       <c r="H12" t="n">
-        <v>49.83184405107777</v>
+        <v>52.91723650523819</v>
       </c>
       <c r="I12" t="n">
         <v>3</v>
@@ -34281,40 +34281,40 @@
         <v>0.1578947368421053</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.01807681299092534</v>
+        <v>-0.01813707203486782</v>
       </c>
       <c r="L12" t="n">
         <v>0.01756100538300309</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1315908293806249</v>
+        <v>0.1314495280530239</v>
       </c>
       <c r="N12" t="n">
-        <v>0.07691913163650073</v>
+        <v>0.07385201062854692</v>
       </c>
       <c r="O12" t="n">
-        <v>0.03767408856707033</v>
+        <v>0.03767399850915143</v>
       </c>
       <c r="P12" t="n">
-        <v>0.216557285236821</v>
+        <v>0.2093651956390273</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.614761819618195</v>
+        <v>2.607296860316745</v>
       </c>
       <c r="R12" t="n">
-        <v>1.836839237145455</v>
+        <v>1.836839349277011</v>
       </c>
       <c r="S12" t="n">
-        <v>2.097349509287353</v>
+        <v>2.076070720572219</v>
       </c>
       <c r="T12" t="n">
-        <v>75.22958077539029</v>
+        <v>75.22924094800294</v>
       </c>
       <c r="U12" t="n">
-        <v>11.40029716442156</v>
+        <v>11.40029507829921</v>
       </c>
       <c r="V12" t="n">
-        <v>106.3664510257359</v>
+        <v>106.3656612396362</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -34356,40 +34356,40 @@
         <v>0.25</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1453827670449738</v>
+        <v>0.1595644151294533</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1248593468571665</v>
+        <v>0.13904935248353</v>
       </c>
       <c r="M13" t="n">
-        <v>0.038481263214515</v>
+        <v>0.04145247669697699</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1485839512932214</v>
+        <v>0.1712573840399493</v>
       </c>
       <c r="O13" t="n">
-        <v>0.07876228460875545</v>
+        <v>0.1052102297158676</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.07597368879237315</v>
+        <v>-0.07201181932479093</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.300259175225212</v>
+        <v>1.328024379521858</v>
       </c>
       <c r="R13" t="n">
-        <v>1.256039695597018</v>
+        <v>1.277214139782041</v>
       </c>
       <c r="S13" t="n">
-        <v>1.048673125158564</v>
+        <v>1.055875327381544</v>
       </c>
       <c r="T13" t="n">
-        <v>87.5782337442634</v>
+        <v>88.2530439176883</v>
       </c>
       <c r="U13" t="n">
-        <v>76.9822260415536</v>
+        <v>77.97945033390954</v>
       </c>
       <c r="V13" t="n">
-        <v>113.5343264848501</v>
+        <v>113.7433792982093</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -34431,40 +34431,40 @@
         <v>0.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1111696797877798</v>
+        <v>0.1111696660435561</v>
       </c>
       <c r="L14" t="n">
         <v>0.07314476361260724</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1021279891793827</v>
+        <v>-0.1021279914906521</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2356282238447942</v>
+        <v>0.2356282609075933</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1644855158548426</v>
+        <v>0.164485622621221</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2436573262230547</v>
+        <v>0.2436573859388654</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5607151111935627</v>
+        <v>0.5607151469610445</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4450515203869757</v>
+        <v>0.4450516650075427</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7210135977615295</v>
+        <v>0.7210136368504568</v>
       </c>
       <c r="T14" t="n">
-        <v>16.60596628876169</v>
+        <v>16.60596739239092</v>
       </c>
       <c r="U14" t="n">
-        <v>3.298458696909052</v>
+        <v>3.298458050732048</v>
       </c>
       <c r="V14" t="n">
-        <v>3.188727042945415</v>
+        <v>3.188727070882999</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>

--- a/company_radar_output.xlsx
+++ b/company_radar_output.xlsx
@@ -797,7 +797,7 @@
         </is>
       </c>
       <c r="X2" t="n">
-        <v>348570943488</v>
+        <v>350803755008</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>0.1274827271699905</v>
+        <v>0.1274684220552444</v>
       </c>
       <c r="AA2" t="n">
-        <v>44436774488.06689</v>
+        <v>44716401101.92432</v>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
@@ -822,25 +822,25 @@
         <v>26.4</v>
       </c>
       <c r="AE2" t="n">
-        <v>28.10000038146973</v>
+        <v>28.28000068664551</v>
       </c>
       <c r="AF2" t="n">
-        <v>23.34882186889648</v>
+        <v>23.52609386444092</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.457833070755</v>
+        <v>13.5439733171463</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.2034868628169373</v>
+        <v>0.2020695339225012</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.088003338556292</v>
+        <v>1.088013614944427</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.7349614715934785</v>
+        <v>0.7370156684122762</v>
       </c>
       <c r="AK2" t="n">
-        <v>28.10000038146973</v>
+        <v>28.28000068664551</v>
       </c>
       <c r="AL2" t="n">
         <v>8.524273872375488</v>
@@ -849,40 +849,40 @@
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>2.296468508893533</v>
+        <v>2.317584712792038</v>
       </c>
       <c r="AO2" t="n">
-        <v>76.13290786135367</v>
+        <v>72.84114185600448</v>
       </c>
       <c r="AP2" t="n">
-        <v>118021162</v>
+        <v>73204846</v>
       </c>
       <c r="AQ2" t="n">
-        <v>159524208.84</v>
+        <v>156690521.42</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.7398322979202058</v>
+        <v>0.4671938374866887</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.163459573265017</v>
+        <v>0.2302118452881055</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.271251279289732</v>
+        <v>1.137504477202255</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.207374930279158</v>
+        <v>2.170789082865447</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.833400582354729</v>
+        <v>1.857186490686118</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.926403453371088</v>
+        <v>2.951555361089751</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.982354855962263</v>
+        <v>2.00145894055045</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.715034478255943</v>
+        <v>3.745237596885083</v>
       </c>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
@@ -1410,16 +1410,16 @@
         <v>407.0119970703125</v>
       </c>
       <c r="AG5" t="n">
-        <v>431.830792388916</v>
+        <v>431.8307920837402</v>
       </c>
       <c r="AH5" t="n">
         <v>0.2284404239514353</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.1578377435022591</v>
+        <v>0.1578377443205055</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.05747342652733112</v>
+        <v>-0.05747342586124549</v>
       </c>
       <c r="AK5" t="n">
         <v>538.6585083007812</v>
@@ -1458,13 +1458,13 @@
         <v>-0.03236377991410644</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.8291819762125663</v>
+        <v>0.8291811593248239</v>
       </c>
       <c r="AX5" t="n">
         <v>0.06190338844962495</v>
       </c>
       <c r="AY5" t="n">
-        <v>8455.443612364279</v>
+        <v>8455.4398826791</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -1654,13 +1654,13 @@
         <v>0.8080129108828429</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.650572416193473</v>
+        <v>1.65057271876519</v>
       </c>
       <c r="AX6" t="n">
         <v>0.1256899512382423</v>
       </c>
       <c r="AY6" t="n">
-        <v>141.3497094749168</v>
+        <v>141.3496958390708</v>
       </c>
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="n">
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4309979758592</v>
+        <v>4306379210752</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>0.1274827271699905</v>
+        <v>0.1274684220552444</v>
       </c>
       <c r="AA8" t="n">
-        <v>549447973672.7656</v>
+        <v>548927362766.0664</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
@@ -1984,22 +1984,22 @@
         <v>22.1</v>
       </c>
       <c r="AE8" t="n">
-        <v>478.7999877929688</v>
+        <v>478.2000122070312</v>
       </c>
       <c r="AF8" t="n">
-        <v>454.1480023193359</v>
+        <v>455.2120025634766</v>
       </c>
       <c r="AG8" t="n">
-        <v>530.7147299194336</v>
+        <v>530.0364895629883</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.05428183179874191</v>
+        <v>0.05049956836397151</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.09782042818812642</v>
+        <v>-0.09779794104118367</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0.1442709675906697</v>
+        <v>-0.1411685581519191</v>
       </c>
       <c r="AK8" t="n">
         <v>669.6973876953125</v>
@@ -2008,43 +2008,43 @@
         <v>411.7999877929688</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0.2850502382266944</v>
+        <v>-0.2859461288139374</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.1627003447938034</v>
+        <v>0.1612433860669391</v>
       </c>
       <c r="AO8" t="n">
-        <v>50.3875968992248</v>
+        <v>51.66932138894294</v>
       </c>
       <c r="AP8" t="n">
-        <v>16319939</v>
+        <v>11808698</v>
       </c>
       <c r="AQ8" t="n">
-        <v>34353661</v>
+        <v>33745912.9</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.4750567632369662</v>
+        <v>0.3499297243785632</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.04041715578566718</v>
+        <v>0.04501749525513699</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.02753171176672531</v>
+        <v>0.04171297249478689</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.2006956542649045</v>
+        <v>-0.191693439719184</v>
       </c>
       <c r="AV8" t="n">
-        <v>-0.1177077399345985</v>
+        <v>-0.1204154513877195</v>
       </c>
       <c r="AW8" t="n">
-        <v>-0.0565426709000818</v>
+        <v>-0.07228386672945519</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.2225065061541112</v>
+        <v>-0.2234807691583418</v>
       </c>
       <c r="AY8" t="n">
-        <v>679.7993699267488</v>
+        <v>678.9462149503562</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
@@ -2380,25 +2380,25 @@
         <v>159.9215922546387</v>
       </c>
       <c r="AG10" t="n">
-        <v>178.2031758499145</v>
+        <v>178.2031765365601</v>
       </c>
       <c r="AH10" t="n">
         <v>-0.08067445927898786</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.1749866209102612</v>
+        <v>-0.1749866240891704</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.10258842755234</v>
+        <v>-0.1025884310102112</v>
       </c>
       <c r="AK10" t="n">
-        <v>324.6299438476562</v>
+        <v>324.6299743652344</v>
       </c>
       <c r="AL10" t="n">
         <v>114.9899978637695</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.5471150857807032</v>
+        <v>-0.5471151283551783</v>
       </c>
       <c r="AN10" t="n">
         <v>0.2785460214256015</v>
@@ -2425,10 +2425,10 @@
         <v>0.03659668987607123</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.4037624384747892</v>
+        <v>-0.4037624015785307</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.7953339332001303</v>
+        <v>0.7953342677294584</v>
       </c>
       <c r="AX10" t="n">
         <v>-0.2415405716747124</v>
@@ -2960,16 +2960,16 @@
         <v>599.6241174316406</v>
       </c>
       <c r="AG13" t="n">
-        <v>630.4387194824219</v>
+        <v>630.4387188720704</v>
       </c>
       <c r="AH13" t="n">
         <v>-0.01254809742798724</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.06081280021626811</v>
+        <v>-0.06081279930700545</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.04887802905900118</v>
+        <v>-0.04887802813818409</v>
       </c>
       <c r="AK13" t="n">
         <v>787.419189453125</v>
@@ -3011,10 +3011,10 @@
         <v>0.6971147723153619</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.08802733915790817</v>
+        <v>-0.08802725342477469</v>
       </c>
       <c r="AY13" t="n">
-        <v>14.62384585550811</v>
+        <v>14.62384428282623</v>
       </c>
       <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="n">
@@ -4568,7 +4568,7 @@
         <v>0.4185350617050061</v>
       </c>
       <c r="AW21" t="n">
-        <v>8.694404395003593</v>
+        <v>8.694403556891469</v>
       </c>
       <c r="AX21" t="n">
         <v>0.2350721494968062</v>
@@ -4954,7 +4954,7 @@
         <v>-0.02722708853905231</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.134212891084047</v>
+        <v>1.13421303753913</v>
       </c>
       <c r="AX23" t="n">
         <v>-0.1753373264764095</v>
@@ -5294,16 +5294,16 @@
         <v>309.785400390625</v>
       </c>
       <c r="AG25" t="n">
-        <v>279.1312841796875</v>
+        <v>279.131284866333</v>
       </c>
       <c r="AH25" t="n">
         <v>0.01144206982372653</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.1225183429119436</v>
+        <v>0.1225183401506185</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.1098197083176256</v>
+        <v>0.1098197055875383</v>
       </c>
       <c r="AK25" t="n">
         <v>340.0799865722656</v>
@@ -5342,13 +5342,13 @@
         <v>0.4296825050364115</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.208945876270639</v>
+        <v>1.208946351516505</v>
       </c>
       <c r="AX25" t="n">
-        <v>0.1583046094268865</v>
+        <v>0.1583044787515506</v>
       </c>
       <c r="AY25" t="n">
-        <v>3189.503553375435</v>
+        <v>3189.504521579152</v>
       </c>
       <c r="AZ25" t="inlineStr"/>
       <c r="BA25" t="n">
@@ -5490,16 +5490,16 @@
         <v>206.0486834716797</v>
       </c>
       <c r="AG26" t="n">
-        <v>193.7998763275147</v>
+        <v>193.7998762512207</v>
       </c>
       <c r="AH26" t="n">
         <v>0.08692762768682938</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.1556251271047409</v>
+        <v>0.1556251275596803</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.06320337957009325</v>
+        <v>0.06320337998864867</v>
       </c>
       <c r="AK26" t="n">
         <v>235.465576171875</v>
@@ -5532,19 +5532,19 @@
         <v>0.04191928560156732</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.2093908420309836</v>
+        <v>0.2093909416822872</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.2405725208421641</v>
+        <v>0.2405724159860221</v>
       </c>
       <c r="AW26" t="n">
-        <v>10.37897091722595</v>
+        <v>10.37896871178468</v>
       </c>
       <c r="AX26" t="n">
         <v>0.187361185794777</v>
       </c>
       <c r="AY26" t="n">
-        <v>5961.874175104486</v>
+        <v>5961.871809398554</v>
       </c>
       <c r="AZ26" t="inlineStr"/>
       <c r="BA26" t="n">
@@ -6037,7 +6037,7 @@
         </is>
       </c>
       <c r="X29" t="n">
-        <v>753907662848</v>
+        <v>709971083264</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -6045,10 +6045,10 @@
         </is>
       </c>
       <c r="Z29" t="n">
-        <v>0.148187667131424</v>
+        <v>0.1482843458652496</v>
       </c>
       <c r="AA29" t="n">
-        <v>111719817789.9492</v>
+        <v>105277597665.0449</v>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
@@ -6062,67 +6062,67 @@
         <v>6.1</v>
       </c>
       <c r="AE29" t="n">
-        <v>1199.930053710938</v>
+        <v>1130</v>
       </c>
       <c r="AF29" t="n">
-        <v>1309.630400390625</v>
+        <v>1306.030400390625</v>
       </c>
       <c r="AG29" t="n">
-        <v>1004.16990447998</v>
+        <v>1005.657105712891</v>
       </c>
       <c r="AH29" t="n">
-        <v>-0.08376435568918306</v>
+        <v>-0.1347827740747654</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.1949472378704014</v>
+        <v>0.1236434303310223</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0.3041920441429982</v>
+        <v>0.2986836099216994</v>
       </c>
       <c r="AK29" t="n">
         <v>1595.550048828125</v>
       </c>
       <c r="AL29" t="n">
-        <v>451.3385314941406</v>
+        <v>455.1594848632812</v>
       </c>
       <c r="AM29" t="n">
-        <v>-0.2479521061766482</v>
+        <v>-0.2917802855322872</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.658603176951479</v>
+        <v>1.482646275820055</v>
       </c>
       <c r="AO29" t="n">
-        <v>49.45489840191274</v>
+        <v>35.54136184923838</v>
       </c>
       <c r="AP29" t="n">
-        <v>15948922</v>
+        <v>19296902</v>
       </c>
       <c r="AQ29" t="n">
-        <v>13794360.72</v>
+        <v>13890238.98</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.1561914556052</v>
+        <v>1.389241900573837</v>
       </c>
       <c r="AS29" t="n">
-        <v>-0.1429071044921875</v>
+        <v>-0.1870503597122302</v>
       </c>
       <c r="AT29" t="n">
-        <v>-0.06099207407957219</v>
+        <v>-0.1419111871923689</v>
       </c>
       <c r="AU29" t="n">
-        <v>0.4297310458397585</v>
+        <v>0.3390501295406771</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.658603176951479</v>
+        <v>1.482646275820055</v>
       </c>
       <c r="AW29" t="n">
-        <v>14.08670422421723</v>
+        <v>12.52902790657228</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.2877967126674525</v>
+        <v>0.2127459269928251</v>
       </c>
       <c r="AY29" t="n">
-        <v>7.427671111848438</v>
+        <v>6.936519572067394</v>
       </c>
       <c r="AZ29" t="inlineStr"/>
       <c r="BA29" t="n">
@@ -6312,13 +6312,13 @@
         <v>4.141628688529493</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.069281125234316</v>
+        <v>1.069280803852271</v>
       </c>
       <c r="AX30" t="n">
         <v>1.58125949133561</v>
       </c>
       <c r="AY30" t="n">
-        <v>559.0559240166102</v>
+        <v>559.055832055239</v>
       </c>
       <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="n">
@@ -6508,13 +6508,13 @@
         <v>0.1747636162719186</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.2561692140327632</v>
+        <v>0.2561693574724042</v>
       </c>
       <c r="AX31" t="n">
         <v>-0.01976120426501915</v>
       </c>
       <c r="AY31" t="n">
-        <v>496.5357044080974</v>
+        <v>496.5359241544062</v>
       </c>
       <c r="AZ31" t="inlineStr"/>
       <c r="BA31" t="n">
@@ -6529,12 +6529,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3189.TW</t>
+          <t>3037.TW</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kinsus</t>
+          <t>Unimicron</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6549,11 +6549,11 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IC substrates</t>
+          <t>IC substrates/PCBs</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -6602,7 +6602,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>Kinsus Interconnect Technology Corp.</t>
+          <t>Unimicron Technology Corp.</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Electronic Components</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
@@ -6621,7 +6621,7 @@
         </is>
       </c>
       <c r="X32" t="n">
-        <v>433651679232</v>
+        <v>1580127354880</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -6629,10 +6629,10 @@
         </is>
       </c>
       <c r="Z32" t="n">
-        <v>0.03102217987179756</v>
+        <v>0.0310616884380579</v>
       </c>
       <c r="AA32" t="n">
-        <v>13452820394.84216</v>
+        <v>49081423589.73511</v>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
@@ -6640,73 +6640,73 @@
         </is>
       </c>
       <c r="AC32" s="2" t="n">
-        <v>38292</v>
+        <v>36529</v>
       </c>
       <c r="AD32" t="n">
-        <v>21.8</v>
+        <v>26.6</v>
       </c>
       <c r="AE32" t="n">
-        <v>823</v>
+        <v>992</v>
       </c>
       <c r="AF32" t="n">
-        <v>741.342978515625</v>
+        <v>913.8883508300781</v>
       </c>
       <c r="AG32" t="n">
-        <v>391.8548277282715</v>
+        <v>545.3306629943847</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.1101474268332252</v>
+        <v>0.08547176369955212</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.10026760362055</v>
+        <v>0.8190798121509897</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.8918817022453611</v>
+        <v>0.6758425902771736</v>
       </c>
       <c r="AK32" t="n">
-        <v>889.477294921875</v>
+        <v>1082.782836914062</v>
       </c>
       <c r="AL32" t="n">
-        <v>99.8291015625</v>
+        <v>130.7322998046875</v>
       </c>
       <c r="AM32" t="n">
-        <v>-0.07473748380245482</v>
+        <v>-0.08384214619876518</v>
       </c>
       <c r="AN32" t="n">
-        <v>7.244089019320127</v>
+        <v>6.588025311893359</v>
       </c>
       <c r="AO32" t="n">
-        <v>61.18012422360248</v>
+        <v>62.67071320182094</v>
       </c>
       <c r="AP32" t="n">
-        <v>15741190</v>
+        <v>7435190</v>
       </c>
       <c r="AQ32" t="n">
-        <v>16060240.38</v>
+        <v>25433169.24</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.9801341466596404</v>
+        <v>0.292342253135575</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.03522012578616351</v>
+        <v>0.09856035437430788</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.6688439310364629</v>
+        <v>0.1143848849987141</v>
       </c>
       <c r="AU32" t="n">
-        <v>2.385662841609908</v>
+        <v>1.885431886427137</v>
       </c>
       <c r="AV32" t="n">
-        <v>7.244089019320127</v>
+        <v>6.47391979928438</v>
       </c>
       <c r="AW32" t="n">
-        <v>6.795457598677828</v>
+        <v>8.434149779618057</v>
       </c>
       <c r="AX32" t="n">
-        <v>4.284672448282133</v>
+        <v>3.538955690667947</v>
       </c>
       <c r="AY32" t="n">
-        <v>35.01456477732709</v>
+        <v>135.2735240076588</v>
       </c>
       <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="n">
@@ -6721,12 +6721,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>4062.T</t>
+          <t>3189.TW</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Ibiden</t>
+          <t>Kinsus</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6745,7 +6745,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -6794,7 +6794,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>Ibiden Co.,Ltd.</t>
+          <t>Kinsus Interconnect Technology Corp.</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -6804,27 +6804,27 @@
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>Electronic Components</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>TWD</t>
         </is>
       </c>
       <c r="X33" t="n">
-        <v>5340641886208</v>
+        <v>440501600256</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>TWD</t>
         </is>
       </c>
       <c r="Z33" t="n">
-        <v>0.006339345127344131</v>
+        <v>0.0310616884380579</v>
       </c>
       <c r="AA33" t="n">
-        <v>33856172118.22266</v>
+        <v>13682723463.6178</v>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
@@ -6832,77 +6832,77 @@
         </is>
       </c>
       <c r="AC33" s="2" t="n">
-        <v>36892</v>
+        <v>38292</v>
       </c>
       <c r="AD33" t="n">
-        <v>25.6</v>
+        <v>21.8</v>
       </c>
       <c r="AE33" t="n">
-        <v>19110</v>
+        <v>836</v>
       </c>
       <c r="AF33" t="n">
-        <v>20174.2</v>
+        <v>743.5078955078125</v>
       </c>
       <c r="AG33" t="n">
-        <v>11551.23948974609</v>
+        <v>395.3684684753418</v>
       </c>
       <c r="AH33" t="n">
-        <v>-0.05275054277245195</v>
+        <v>0.1243996264881839</v>
       </c>
       <c r="AI33" t="n">
-        <v>0.6543679158382727</v>
+        <v>1.11448323945474</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0.7464965571797217</v>
+        <v>0.8805442385807845</v>
       </c>
       <c r="AK33" t="n">
-        <v>26425</v>
+        <v>889.477294921875</v>
       </c>
       <c r="AL33" t="n">
-        <v>3099.432373046875</v>
+        <v>99.8291015625</v>
       </c>
       <c r="AM33" t="n">
-        <v>-0.2768211920529802</v>
+        <v>-0.06012215851622393</v>
       </c>
       <c r="AN33" t="n">
-        <v>5.165645092367043</v>
+        <v>7.374311567620445</v>
       </c>
       <c r="AO33" t="n">
-        <v>59.59115093811257</v>
+        <v>57.62711864406779</v>
       </c>
       <c r="AP33" t="n">
-        <v>9556700</v>
+        <v>3625232</v>
       </c>
       <c r="AQ33" t="n">
-        <v>8902530</v>
+        <v>15994283.82</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.073481358669951</v>
+        <v>0.2266579761118682</v>
       </c>
       <c r="AS33" t="n">
-        <v>-0.02100409836065575</v>
+        <v>0.02075702075702068</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.1546827794561934</v>
+        <v>0.683278707059386</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.281579009040321</v>
+        <v>2.648937502231131</v>
       </c>
       <c r="AV33" t="n">
-        <v>5.040586953107727</v>
+        <v>7.374311567620445</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.907304903168351</v>
+        <v>7.089253299356994</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.674591954577161</v>
+        <v>4.368148440782337</v>
       </c>
       <c r="AY33" t="n">
-        <v>26.61098226599517</v>
+        <v>35.58344611645862</v>
       </c>
       <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
@@ -6913,12 +6913,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>3037.TW</t>
+          <t>4062.T</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Unimicron</t>
+          <t>Ibiden</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IC substrates/PCBs</t>
+          <t>IC substrates</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -6986,7 +6986,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>Unimicron Technology Corp.</t>
+          <t>Ibiden Co.,Ltd.</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -7001,22 +7001,22 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="X34" t="n">
-        <v>1521191092224</v>
+        <v>5555832750080</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="Z34" t="n">
-        <v>0.03102217987179756</v>
+        <v>0.006313052028417587</v>
       </c>
       <c r="AA34" t="n">
-        <v>47190663682.34912</v>
+        <v>35074261212.44141</v>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
@@ -7024,77 +7024,77 @@
         </is>
       </c>
       <c r="AC34" s="2" t="n">
-        <v>36529</v>
+        <v>36892</v>
       </c>
       <c r="AD34" t="n">
-        <v>26.6</v>
+        <v>25.6</v>
       </c>
       <c r="AE34" t="n">
-        <v>955</v>
+        <v>19880</v>
       </c>
       <c r="AF34" t="n">
-        <v>915.1052331542969</v>
+        <v>20111.8</v>
       </c>
       <c r="AG34" t="n">
-        <v>541.136594619751</v>
+        <v>11626.23883300781</v>
       </c>
       <c r="AH34" t="n">
-        <v>0.0435958241744383</v>
+        <v>-0.01152557205222804</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.7648039506015387</v>
+        <v>0.709925306502315</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0.6910799274207806</v>
+        <v>0.7298629667662604</v>
       </c>
       <c r="AK34" t="n">
-        <v>1082.782836914062</v>
+        <v>26425</v>
       </c>
       <c r="AL34" t="n">
-        <v>130.7322998046875</v>
+        <v>3099.432373046875</v>
       </c>
       <c r="AM34" t="n">
-        <v>-0.1180133564715935</v>
+        <v>-0.247682119205298</v>
       </c>
       <c r="AN34" t="n">
-        <v>6.30500420651024</v>
+        <v>5.414077678506374</v>
       </c>
       <c r="AO34" t="n">
-        <v>64.70588235294117</v>
+        <v>57.29505770938147</v>
       </c>
       <c r="AP34" t="n">
-        <v>21029113</v>
+        <v>10053600</v>
       </c>
       <c r="AQ34" t="n">
-        <v>25691784.3</v>
+        <v>8900320</v>
       </c>
       <c r="AR34" t="n">
-        <v>0.818515084606249</v>
+        <v>1.129577363510526</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.09142857142857141</v>
+        <v>-0.02068965517241383</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.09366342564552776</v>
+        <v>0.1652989449003517</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.603960580586924</v>
+        <v>1.766128959386843</v>
       </c>
       <c r="AV34" t="n">
-        <v>6.30500420651024</v>
+        <v>5.414077678506374</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.783266755032317</v>
+        <v>6.086851187010986</v>
       </c>
       <c r="AX34" t="n">
-        <v>3.369659964302309</v>
+        <v>1.78235939597038</v>
       </c>
       <c r="AY34" t="n">
-        <v>130.1907241710627</v>
+        <v>27.72349495583367</v>
       </c>
       <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>2.810910996767463</v>
       </c>
       <c r="AW35" t="n">
-        <v>4.369887299668052</v>
+        <v>4.369886564181203</v>
       </c>
       <c r="AX35" t="n">
         <v>1.239983728429313</v>
@@ -7401,10 +7401,10 @@
         </is>
       </c>
       <c r="Z36" t="n">
-        <v>1.156203031539917</v>
+        <v>1.155668497085571</v>
       </c>
       <c r="AA36" t="n">
-        <v>6450294881.535278</v>
+        <v>6447312788.632202</v>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
@@ -7478,7 +7478,7 @@
         <v>3.378049068405549</v>
       </c>
       <c r="AY36" t="n">
-        <v>11.51427262096043</v>
+        <v>11.51427678118704</v>
       </c>
       <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="n">
@@ -7493,12 +7493,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AMKR</t>
+          <t>7911.T</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Amkor Technology</t>
+          <t>Toppan Holdings</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -7508,16 +7508,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>OSAT / advanced packaging</t>
+          <t>IC substrates / PCBs</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>OSAT, advanced packaging</t>
+          <t>Substrates/materials/photomasks</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -7526,13 +7526,9 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>SOXX</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" s="1" t="n">
         <v>46195</v>
       </c>
@@ -7570,111 +7566,111 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>Amkor Technology, Inc.</t>
+          <t>TOPPAN Holdings Inc.</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Conglomerates</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="X37" t="n">
-        <v>13731969024</v>
+        <v>1352526069760</v>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="Z37" t="n">
-        <v>1</v>
+        <v>0.006313052028417587</v>
       </c>
       <c r="AA37" t="n">
-        <v>13731969024</v>
+        <v>8538567448.186035</v>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Mid cap</t>
         </is>
       </c>
       <c r="AC37" s="2" t="n">
-        <v>35916</v>
+        <v>36529</v>
       </c>
       <c r="AD37" t="n">
-        <v>28.3</v>
+        <v>26.6</v>
       </c>
       <c r="AE37" t="n">
-        <v>55.27000045776367</v>
+        <v>4816</v>
       </c>
       <c r="AF37" t="n">
-        <v>69.63793495178223</v>
+        <v>4746.68</v>
       </c>
       <c r="AG37" t="n">
-        <v>54.21645660400391</v>
+        <v>4617.665220947266</v>
       </c>
       <c r="AH37" t="n">
-        <v>-0.2063233854359267</v>
+        <v>0.01460389156210229</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.0194321783412521</v>
+        <v>0.04295131187792078</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.2844427561988518</v>
+        <v>0.02793939640047549</v>
       </c>
       <c r="AK37" t="n">
-        <v>93.55000305175781</v>
+        <v>5784.6318359375</v>
       </c>
       <c r="AL37" t="n">
-        <v>22.67447090148926</v>
+        <v>3671.95654296875</v>
       </c>
       <c r="AM37" t="n">
-        <v>-0.4091929593290896</v>
+        <v>-0.1674491762673288</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.43754311612773</v>
+        <v>0.3115623629102917</v>
       </c>
       <c r="AO37" t="n">
-        <v>41.93762324358121</v>
+        <v>52.86284953395472</v>
       </c>
       <c r="AP37" t="n">
-        <v>2902800</v>
+        <v>1234600</v>
       </c>
       <c r="AQ37" t="n">
-        <v>6090066</v>
+        <v>1727784</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.4766450806937068</v>
+        <v>0.7145569122066184</v>
       </c>
       <c r="AS37" t="n">
-        <v>-0.2156946289150042</v>
+        <v>-0.07402422611036341</v>
       </c>
       <c r="AT37" t="n">
-        <v>-0.2777419358054822</v>
+        <v>-0.1316263974035341</v>
       </c>
       <c r="AU37" t="n">
-        <v>0.1231405954885074</v>
+        <v>0.0367714920131168</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.43754311612773</v>
+        <v>0.2026962226799915</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.340621170048958</v>
+        <v>1.726785602220096</v>
       </c>
       <c r="AX37" t="n">
-        <v>0.2916640516070137</v>
+        <v>0.04033121269564277</v>
       </c>
       <c r="AY37" t="n">
-        <v>3.468656415129503</v>
+        <v>3.12871163828531</v>
       </c>
       <c r="AZ37" t="inlineStr"/>
       <c r="BA37" t="n">
@@ -7689,12 +7685,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>7911.T</t>
+          <t>AMKR</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Toppan Holdings</t>
+          <t>Amkor Technology</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -7704,16 +7700,16 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>IC substrates / PCBs</t>
+          <t>OSAT / advanced packaging</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Substrates/materials/photomasks</t>
+          <t>OSAT, advanced packaging</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -7722,9 +7718,13 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>SOXX</t>
+        </is>
+      </c>
       <c r="K38" s="1" t="n">
         <v>46195</v>
       </c>
@@ -7762,119 +7762,119 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>TOPPAN Holdings Inc.</t>
+          <t>Amkor Technology, Inc.</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>Conglomerates</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X38" t="n">
-        <v>1319386873856</v>
+        <v>13731969024</v>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z38" t="n">
-        <v>0.006339345127344131</v>
+        <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>8364048749.86084</v>
+        <v>13731969024</v>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Mid cap</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC38" s="2" t="n">
-        <v>36529</v>
+        <v>35916</v>
       </c>
       <c r="AD38" t="n">
-        <v>26.6</v>
+        <v>28.3</v>
       </c>
       <c r="AE38" t="n">
-        <v>4698</v>
+        <v>55.27000045776367</v>
       </c>
       <c r="AF38" t="n">
-        <v>4741.6</v>
+        <v>69.63793495178223</v>
       </c>
       <c r="AG38" t="n">
-        <v>4612.594139404297</v>
+        <v>54.2164563369751</v>
       </c>
       <c r="AH38" t="n">
-        <v>-0.00919520836848331</v>
+        <v>-0.2063233854359267</v>
       </c>
       <c r="AI38" t="n">
-        <v>0.01851579783837942</v>
+        <v>0.01943218336219554</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.02796817944454233</v>
+        <v>0.2844427625250348</v>
       </c>
       <c r="AK38" t="n">
-        <v>5784.6318359375</v>
+        <v>93.55000305175781</v>
       </c>
       <c r="AL38" t="n">
-        <v>3671.95654296875</v>
+        <v>22.67447090148926</v>
       </c>
       <c r="AM38" t="n">
-        <v>-0.1878480544235694</v>
+        <v>-0.4091929593290896</v>
       </c>
       <c r="AN38" t="n">
-        <v>0.2794269063439681</v>
+        <v>1.43754311612773</v>
       </c>
       <c r="AO38" t="n">
-        <v>55.72232645403378</v>
+        <v>41.93762324358121</v>
       </c>
       <c r="AP38" t="n">
-        <v>1049100</v>
+        <v>2902800</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1750664</v>
+        <v>6090066</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.5992583385504014</v>
+        <v>0.4766450806937068</v>
       </c>
       <c r="AS38" t="n">
-        <v>-0.1046312178387651</v>
+        <v>-0.2156946289150042</v>
       </c>
       <c r="AT38" t="n">
-        <v>-0.1367144432194046</v>
+        <v>-0.2777419358054822</v>
       </c>
       <c r="AU38" t="n">
-        <v>-0.0291191481155999</v>
+        <v>0.1231405954885074</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.1726504845476564</v>
+        <v>1.43754311612773</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.665548345647908</v>
+        <v>1.340621359110374</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.01484136985966167</v>
+        <v>0.2916640516070137</v>
       </c>
       <c r="AY38" t="n">
-        <v>3.027553030751756</v>
+        <v>3.468656070569777</v>
       </c>
       <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>Weak momentum</t>
+          <t>Positive momentum</t>
         </is>
       </c>
     </row>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="X39" t="n">
-        <v>11020903907328</v>
+        <v>10462649384960</v>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
@@ -7981,10 +7981,10 @@
         </is>
       </c>
       <c r="Z39" t="n">
-        <v>0.006339345127344131</v>
+        <v>0.006312931887805462</v>
       </c>
       <c r="AA39" t="n">
-        <v>69865313483.84766</v>
+        <v>66049992933.24219</v>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
@@ -7998,22 +7998,22 @@
         <v>26.6</v>
       </c>
       <c r="AE39" t="n">
-        <v>2981</v>
+        <v>2830</v>
       </c>
       <c r="AF39" t="n">
-        <v>2789.96</v>
+        <v>2791.79</v>
       </c>
       <c r="AG39" t="n">
-        <v>2655.263491210937</v>
+        <v>2657.740026855469</v>
       </c>
       <c r="AH39" t="n">
-        <v>0.06847409998709653</v>
+        <v>0.01368655951916153</v>
       </c>
       <c r="AI39" t="n">
-        <v>0.1226757758193369</v>
+        <v>0.06481445566681043</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0.05072811388960652</v>
+        <v>0.05043757921768366</v>
       </c>
       <c r="AK39" t="n">
         <v>3108</v>
@@ -8022,43 +8022,43 @@
         <v>2280.993408203125</v>
       </c>
       <c r="AM39" t="n">
-        <v>-0.04086229086229087</v>
+        <v>-0.08944658944658945</v>
       </c>
       <c r="AN39" t="n">
-        <v>0.3068867228109668</v>
+        <v>0.2406874959929675</v>
       </c>
       <c r="AO39" t="n">
-        <v>58.85579937304075</v>
+        <v>46.6795615731786</v>
       </c>
       <c r="AP39" t="n">
-        <v>9910400</v>
+        <v>14660100</v>
       </c>
       <c r="AQ39" t="n">
-        <v>9084234</v>
+        <v>8977506</v>
       </c>
       <c r="AR39" t="n">
-        <v>1.09094503730309</v>
+        <v>1.632981364757651</v>
       </c>
       <c r="AS39" t="n">
-        <v>0.06274509803921569</v>
+        <v>0.0141551693244939</v>
       </c>
       <c r="AT39" t="n">
-        <v>0.1784937734730183</v>
+        <v>0.1139539460736076</v>
       </c>
       <c r="AU39" t="n">
-        <v>0.1145488702553283</v>
+        <v>0.04443334187800452</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.2503268876719853</v>
+        <v>0.1853061338013609</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.9341500313285018</v>
+        <v>0.8351585686001273</v>
       </c>
       <c r="AX39" t="n">
-        <v>0.1068018474350487</v>
+        <v>0.05073774848748336</v>
       </c>
       <c r="AY39" t="n">
-        <v>3.555730688933335</v>
+        <v>3.324964055579113</v>
       </c>
       <c r="AZ39" t="inlineStr"/>
       <c r="BA39" t="n">
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="X40" t="n">
-        <v>12870676905984</v>
+        <v>12984361418752</v>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
@@ -8173,10 +8173,10 @@
         </is>
       </c>
       <c r="Z40" t="n">
-        <v>0.006339345127344131</v>
+        <v>0.006312931887805462</v>
       </c>
       <c r="AA40" t="n">
-        <v>81591662929.57031</v>
+        <v>81969389243.23047</v>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
@@ -8190,22 +8190,22 @@
         <v>26.6</v>
       </c>
       <c r="AE40" t="n">
-        <v>158.5</v>
+        <v>159.8999938964844</v>
       </c>
       <c r="AF40" t="n">
-        <v>149.0659997558594</v>
+        <v>149.2739996337891</v>
       </c>
       <c r="AG40" t="n">
-        <v>151.8953266143799</v>
+        <v>151.9465099334717</v>
       </c>
       <c r="AH40" t="n">
-        <v>0.06328740463681637</v>
+        <v>0.07118449488031309</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.04348174188655296</v>
+        <v>0.05234397266837565</v>
       </c>
       <c r="AJ40" t="n">
-        <v>-0.01862681967631163</v>
+        <v>-0.01758849414081798</v>
       </c>
       <c r="AK40" t="n">
         <v>160.3000030517578</v>
@@ -8214,47 +8214,47 @@
         <v>142.8000030517578</v>
       </c>
       <c r="AM40" t="n">
-        <v>-0.01122896455077815</v>
+        <v>-0.002495378338478793</v>
       </c>
       <c r="AN40" t="n">
-        <v>0.1099439538705873</v>
+        <v>0.1197478324879915</v>
       </c>
       <c r="AO40" t="n">
-        <v>61.56247943641716</v>
+        <v>62.49998255475597</v>
       </c>
       <c r="AP40" t="n">
-        <v>350564400</v>
+        <v>227940200</v>
       </c>
       <c r="AQ40" t="n">
-        <v>251444748</v>
+        <v>249569902</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.394200526312047</v>
+        <v>0.9133320892196367</v>
       </c>
       <c r="AS40" t="n">
-        <v>0.06375838926174504</v>
+        <v>0.08333324718389545</v>
       </c>
       <c r="AT40" t="n">
-        <v>0.06091035124018007</v>
+        <v>0.06599995930989588</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.03126316696576326</v>
+        <v>0.06004025221158549</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.08267288704612241</v>
+        <v>0.09440432949079192</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.6081227767269783</v>
+        <v>0.6237297574276932</v>
       </c>
       <c r="AX40" t="n">
-        <v>0.01057324335115384</v>
+        <v>0.01949940343091439</v>
       </c>
       <c r="AY40" t="n">
-        <v>0.723237939232608</v>
+        <v>0.7384587577887154</v>
       </c>
       <c r="AZ40" t="inlineStr"/>
       <c r="BA40" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
@@ -8392,16 +8392,16 @@
         <v>184.9805242919922</v>
       </c>
       <c r="AG41" t="n">
-        <v>174.9056748199463</v>
+        <v>174.905675201416</v>
       </c>
       <c r="AH41" t="n">
         <v>0.04767787740640217</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.1080258159219933</v>
+        <v>0.108025813505386</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.05760161574184086</v>
+        <v>0.05760161343520886</v>
       </c>
       <c r="AK41" t="n">
         <v>202.5594635009766</v>
@@ -8437,16 +8437,16 @@
         <v>0.1445081459923894</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.164485622621221</v>
+        <v>0.1644855158548426</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.4855276902540089</v>
+        <v>0.4855275165028372</v>
       </c>
       <c r="AX41" t="n">
         <v>0.2669837165927196</v>
       </c>
       <c r="AY41" t="n">
-        <v>37.01776702760784</v>
+        <v>37.01777058383556</v>
       </c>
       <c r="AZ41" t="inlineStr"/>
       <c r="BA41" t="n">
@@ -8588,16 +8588,16 @@
         <v>1051.546401367187</v>
       </c>
       <c r="AG42" t="n">
-        <v>931.3983978271484</v>
+        <v>931.3983993530273</v>
       </c>
       <c r="AH42" t="n">
         <v>-0.008488837238560309</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.1194135587408214</v>
+        <v>0.1194135569069235</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.1289974342025189</v>
+        <v>0.1289974323529199</v>
       </c>
       <c r="AK42" t="n">
         <v>1115.93994140625</v>
@@ -8630,10 +8630,10 @@
         <v>-0.02266920921749049</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.2421443610520602</v>
+        <v>0.2421442707291079</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.3682512708696477</v>
+        <v>0.3682511612759205</v>
       </c>
       <c r="AW42" t="n">
         <v>0.4045756397610765</v>
@@ -8642,7 +8642,7 @@
         <v>0.3787117936883788</v>
       </c>
       <c r="AY42" t="n">
-        <v>2.375290803247275</v>
+        <v>2.375291136709352</v>
       </c>
       <c r="AZ42" t="inlineStr"/>
       <c r="BA42" t="n">
@@ -8784,28 +8784,28 @@
         <v>124.7998197937012</v>
       </c>
       <c r="AG43" t="n">
-        <v>106.4021577453613</v>
+        <v>106.4021579360962</v>
       </c>
       <c r="AH43" t="n">
         <v>-0.02924538091365481</v>
       </c>
       <c r="AI43" t="n">
-        <v>0.13860474348473</v>
+        <v>0.1386047414436846</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0.1729068511220291</v>
+        <v>0.1729068490194945</v>
       </c>
       <c r="AK43" t="n">
         <v>133.0599975585938</v>
       </c>
       <c r="AL43" t="n">
-        <v>77.69110870361328</v>
+        <v>77.69111633300781</v>
       </c>
       <c r="AM43" t="n">
         <v>-0.08950846423599401</v>
       </c>
       <c r="AN43" t="n">
-        <v>0.5593805204667446</v>
+        <v>0.5593803673330302</v>
       </c>
       <c r="AO43" t="n">
         <v>44.99023367211446</v>
@@ -8829,13 +8829,13 @@
         <v>0.2839083227387849</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.3642373062500344</v>
+        <v>0.364237189044949</v>
       </c>
       <c r="AW43" t="n">
-        <v>2.364124978364305</v>
+        <v>2.364124622010951</v>
       </c>
       <c r="AX43" t="n">
-        <v>0.4773274314811182</v>
+        <v>0.4773275689233549</v>
       </c>
       <c r="AY43" t="n">
         <v>104.1496160819709</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="X44" t="n">
-        <v>10866349056</v>
+        <v>10949994496</v>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
@@ -8953,10 +8953,10 @@
         </is>
       </c>
       <c r="Z44" t="n">
-        <v>0.7070635557174683</v>
+        <v>0.706813633441925</v>
       </c>
       <c r="AA44" t="n">
-        <v>7683199401.202515</v>
+        <v>7739605395.886841</v>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
@@ -8970,22 +8970,22 @@
         <v>15.7</v>
       </c>
       <c r="AE44" t="n">
-        <v>14.28999996185303</v>
+        <v>14.39999961853027</v>
       </c>
       <c r="AF44" t="n">
-        <v>14.28519998550415</v>
+        <v>14.26839998245239</v>
       </c>
       <c r="AG44" t="n">
-        <v>13.82971166133881</v>
+        <v>13.82076165676117</v>
       </c>
       <c r="AH44" t="n">
-        <v>0.0003360104411382903</v>
+        <v>0.009223152998214745</v>
       </c>
       <c r="AI44" t="n">
-        <v>0.03328256667859275</v>
+        <v>0.04191071202546492</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0.03293548956907544</v>
+        <v>0.03238883187542974</v>
       </c>
       <c r="AK44" t="n">
         <v>17.98999977111816</v>
@@ -8994,43 +8994,43 @@
         <v>11.26000022888184</v>
       </c>
       <c r="AM44" t="n">
-        <v>-0.2056698085791673</v>
+        <v>-0.1995553195254296</v>
       </c>
       <c r="AN44" t="n">
-        <v>0.269094109358831</v>
+        <v>0.2788631728083235</v>
       </c>
       <c r="AO44" t="n">
-        <v>64.09090771162793</v>
+        <v>54.8571327365147</v>
       </c>
       <c r="AP44" t="n">
-        <v>1326970</v>
+        <v>1622866</v>
       </c>
       <c r="AQ44" t="n">
-        <v>2579135.02</v>
+        <v>2542555.32</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.5145019511231328</v>
+        <v>0.6382814907641813</v>
       </c>
       <c r="AS44" t="n">
-        <v>0.02510763213811384</v>
+        <v>0.06666663840964993</v>
       </c>
       <c r="AT44" t="n">
-        <v>-0.01448276125151537</v>
+        <v>-0.01773535004011162</v>
       </c>
       <c r="AU44" t="n">
-        <v>0.03701017697856446</v>
+        <v>0.03597122400877217</v>
       </c>
       <c r="AV44" t="n">
-        <v>-0.01921755242525214</v>
+        <v>-0.008947014234688799</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.09433401565413546</v>
+        <v>0.1137432557266762</v>
       </c>
       <c r="AX44" t="n">
-        <v>0.1395534294516381</v>
+        <v>0.1483253319246738</v>
       </c>
       <c r="AY44" t="n">
-        <v>8.27303056838822</v>
+        <v>8.3444112668909</v>
       </c>
       <c r="AZ44" t="inlineStr"/>
       <c r="BA44" t="n">
@@ -9145,10 +9145,10 @@
         </is>
       </c>
       <c r="Z45" t="n">
-        <v>0.7825338840484619</v>
+        <v>0.7817691564559937</v>
       </c>
       <c r="AA45" t="n">
-        <v>4211270928.374023</v>
+        <v>4207155483.479004</v>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
@@ -9216,13 +9216,13 @@
         <v>-0.0001311130227846791</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.05830885633444849</v>
+        <v>0.05830861357722483</v>
       </c>
       <c r="AX45" t="n">
         <v>0.03111468145740592</v>
       </c>
       <c r="AY45" t="n">
-        <v>3.04118541253076</v>
+        <v>3.041186739914107</v>
       </c>
       <c r="AZ45" t="inlineStr"/>
       <c r="BA45" t="n">
@@ -9910,16 +9910,16 @@
         <v>125.4766003417969</v>
       </c>
       <c r="AG49" t="n">
-        <v>123.3250712203979</v>
+        <v>123.3250713348389</v>
       </c>
       <c r="AH49" t="n">
         <v>-0.004993774663713646</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.01236510336975938</v>
+        <v>0.01236510243032352</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.01744599942337666</v>
+        <v>0.0174459984792259</v>
       </c>
       <c r="AK49" t="n">
         <v>132.3166198730469</v>
@@ -9955,10 +9955,10 @@
         <v>0.04219098346425421</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.02606807247537235</v>
+        <v>0.02606813681135045</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.42619531150183</v>
+        <v>0.4261951872051573</v>
       </c>
       <c r="AX49" t="n">
         <v>0.08141511245651523</v>
@@ -10150,13 +10150,13 @@
         <v>0.003874344580677036</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.7397628370199933</v>
+        <v>0.7397627124517752</v>
       </c>
       <c r="AX50" t="n">
         <v>0.08042608884881464</v>
       </c>
       <c r="AY50" t="n">
-        <v>340.7882608929775</v>
+        <v>340.7883735745495</v>
       </c>
       <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
@@ -10298,16 +10298,16 @@
         <v>68.76764038085938</v>
       </c>
       <c r="AG51" t="n">
-        <v>62.58517864227295</v>
+        <v>62.58517873764038</v>
       </c>
       <c r="AH51" t="n">
         <v>-0.0200332741327327</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.07677250191837093</v>
+        <v>0.07677250027758253</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.09878475819210175</v>
+        <v>0.09878475651777108</v>
       </c>
       <c r="AK51" t="n">
         <v>71.69000244140625</v>
@@ -10343,7 +10343,7 @@
         <v>0.1036443555492417</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.1397193043756966</v>
+        <v>0.139719230846401</v>
       </c>
       <c r="AW51" t="n">
         <v>0.1177827135343774</v>
@@ -10352,7 +10352,7 @@
         <v>0.1612111644751451</v>
       </c>
       <c r="AY51" t="n">
-        <v>181.3585711142839</v>
+        <v>181.3585564078633</v>
       </c>
       <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="n">
@@ -10490,28 +10490,28 @@
         <v>46.19388656616211</v>
       </c>
       <c r="AG52" t="n">
-        <v>45.61528144836426</v>
+        <v>45.61528146743775</v>
       </c>
       <c r="AH52" t="n">
         <v>-0.01263989673123223</v>
       </c>
       <c r="AI52" t="n">
-        <v>-0.0001157690546900181</v>
+        <v>-0.0001157694727796921</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.01268445791467543</v>
+        <v>0.01268445749123348</v>
       </c>
       <c r="AK52" t="n">
         <v>49.82146072387695</v>
       </c>
       <c r="AL52" t="n">
-        <v>41.60917663574219</v>
+        <v>41.60918045043945</v>
       </c>
       <c r="AM52" t="n">
         <v>-0.08453104450040838</v>
       </c>
       <c r="AN52" t="n">
-        <v>0.09615244275640578</v>
+        <v>0.0961523422620032</v>
       </c>
       <c r="AO52" t="n">
         <v>46.77717360759849</v>
@@ -10532,19 +10532,19 @@
         <v>0.04848406191081689</v>
       </c>
       <c r="AU52" t="n">
-        <v>0.04744291091373642</v>
+        <v>0.04744300267529078</v>
       </c>
       <c r="AV52" t="n">
         <v>0.03767399850915143</v>
       </c>
       <c r="AW52" t="n">
-        <v>0.6218868948303693</v>
+        <v>0.621886564816418</v>
       </c>
       <c r="AX52" t="n">
         <v>0.05722107370420337</v>
       </c>
       <c r="AY52" t="n">
-        <v>185.0138459845253</v>
+        <v>185.0137555487315</v>
       </c>
       <c r="AZ52" t="inlineStr"/>
       <c r="BA52" t="n">
@@ -10686,28 +10686,28 @@
         <v>111.7686004638672</v>
       </c>
       <c r="AG53" t="n">
-        <v>103.780962638855</v>
+        <v>103.7809627151489</v>
       </c>
       <c r="AH53" t="n">
         <v>-0.04105446556230985</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.03275203447619801</v>
+        <v>0.03275203371697666</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.0769663107944778</v>
+        <v>0.07696631000275245</v>
       </c>
       <c r="AK53" t="n">
         <v>117.3600006103516</v>
       </c>
       <c r="AL53" t="n">
-        <v>85.22573089599609</v>
+        <v>85.22573852539062</v>
       </c>
       <c r="AM53" t="n">
         <v>-0.08674165177430881</v>
       </c>
       <c r="AN53" t="n">
-        <v>0.2576014212887332</v>
+        <v>0.2576013087084543</v>
       </c>
       <c r="AO53" t="n">
         <v>36.2098917069972</v>
@@ -10734,7 +10734,7 @@
         <v>0.2142183099005448</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.47201393786592</v>
+        <v>1.472013720371502</v>
       </c>
       <c r="AX53" t="n">
         <v>0.1556959724994926</v>
@@ -10882,16 +10882,16 @@
         <v>14.55814701080322</v>
       </c>
       <c r="AG54" t="n">
-        <v>14.18356305599213</v>
+        <v>14.18356304645538</v>
       </c>
       <c r="AH54" t="n">
         <v>0.01180456079373138</v>
       </c>
       <c r="AI54" t="n">
-        <v>0.03852603778663011</v>
+        <v>0.03852603848491398</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.0264097218260575</v>
+        <v>0.02640972251619478</v>
       </c>
       <c r="AK54" t="n">
         <v>16.86722755432129</v>
@@ -10924,19 +10924,19 @@
         <v>0.04024223587717857</v>
       </c>
       <c r="AU54" t="n">
-        <v>-0.05978361938702403</v>
+        <v>-0.05978367662087303</v>
       </c>
       <c r="AV54" t="n">
         <v>0.2033674134329424</v>
       </c>
       <c r="AW54" t="n">
-        <v>-0.2352606882865915</v>
+        <v>-0.2352608397417572</v>
       </c>
       <c r="AX54" t="n">
-        <v>0.03030728330828092</v>
+        <v>0.0303072145807306</v>
       </c>
       <c r="AY54" t="n">
-        <v>6.46989982174048</v>
+        <v>6.469898918575967</v>
       </c>
       <c r="AZ54" t="inlineStr"/>
       <c r="BA54" t="n">
@@ -11051,10 +11051,10 @@
         </is>
       </c>
       <c r="Z55" t="n">
-        <v>1.156203031539917</v>
+        <v>1.155668497085571</v>
       </c>
       <c r="AA55" t="n">
-        <v>151045534090.0898</v>
+        <v>150975702892.6758</v>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
@@ -11128,7 +11128,7 @@
         <v>0.2556575516954047</v>
       </c>
       <c r="AY55" t="n">
-        <v>6.045008437906104</v>
+        <v>6.045007821351476</v>
       </c>
       <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="n">
@@ -11270,16 +11270,16 @@
         <v>1021.180285644531</v>
       </c>
       <c r="AG56" t="n">
-        <v>845.7302255249024</v>
+        <v>845.7302249145508</v>
       </c>
       <c r="AH56" t="n">
         <v>-0.03022020573069983</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.1709644251032612</v>
+        <v>0.1709644259483296</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.2074539313180346</v>
+        <v>0.2074539321894369</v>
       </c>
       <c r="AK56" t="n">
         <v>1174.859985351562</v>
@@ -11654,16 +11654,16 @@
         <v>260.9173010253906</v>
       </c>
       <c r="AG58" t="n">
-        <v>304.360221862793</v>
+        <v>304.3602211761474</v>
       </c>
       <c r="AH58" t="n">
         <v>0.03438910945262985</v>
       </c>
       <c r="AI58" t="n">
-        <v>-0.1132546395300461</v>
+        <v>-0.1132546375295227</v>
       </c>
       <c r="AJ58" t="n">
-        <v>-0.1427352121493283</v>
+        <v>-0.1427352102153139</v>
       </c>
       <c r="AK58" t="n">
         <v>402.3219604492188</v>
@@ -11699,14 +11699,14 @@
         <v>0.0353896680152237</v>
       </c>
       <c r="AV58" t="n">
-        <v>-0.1935172463854551</v>
+        <v>-0.1935173199304933</v>
       </c>
       <c r="AW58" t="inlineStr"/>
       <c r="AX58" t="n">
         <v>-0.2609650154550651</v>
       </c>
       <c r="AY58" t="n">
-        <v>5.66524487433596</v>
+        <v>5.665245502257704</v>
       </c>
       <c r="AZ58" t="inlineStr"/>
       <c r="BA58" t="n">
@@ -12036,25 +12036,25 @@
         <v>133.7121131896973</v>
       </c>
       <c r="AG60" t="n">
-        <v>150.9246788406372</v>
+        <v>150.9246782302857</v>
       </c>
       <c r="AH60" t="n">
         <v>-0.1165348117277376</v>
       </c>
       <c r="AI60" t="n">
-        <v>-0.2172917102699118</v>
+        <v>-0.2172917071045765</v>
       </c>
       <c r="AJ60" t="n">
-        <v>-0.1140473896195257</v>
+        <v>-0.1140473860366619</v>
       </c>
       <c r="AK60" t="n">
-        <v>182.8191986083984</v>
+        <v>182.8191833496094</v>
       </c>
       <c r="AL60" t="n">
         <v>117.0400009155273</v>
       </c>
       <c r="AM60" t="n">
-        <v>-0.3538424949206005</v>
+        <v>-0.3538424409898209</v>
       </c>
       <c r="AN60" t="n">
         <v>0.00931302400345424</v>
@@ -12078,10 +12078,10 @@
         <v>-0.1416311737165825</v>
       </c>
       <c r="AU60" t="n">
-        <v>-0.2244171959345097</v>
+        <v>-0.2244171182353607</v>
       </c>
       <c r="AV60" t="n">
-        <v>-0.2194897999819536</v>
+        <v>-0.2194898786714919</v>
       </c>
       <c r="AW60" t="n">
         <v>2.27773499254422</v>
@@ -12090,7 +12090,7 @@
         <v>-0.2821161148537437</v>
       </c>
       <c r="AY60" t="n">
-        <v>15.54763589752667</v>
+        <v>15.54764252935437</v>
       </c>
       <c r="AZ60" t="inlineStr"/>
       <c r="BA60" t="n">
@@ -12422,16 +12422,16 @@
         <v>155.0342684936523</v>
       </c>
       <c r="AG62" t="n">
-        <v>161.9298695373535</v>
+        <v>161.9298696899414</v>
       </c>
       <c r="AH62" t="n">
         <v>-0.09316825432277331</v>
       </c>
       <c r="AI62" t="n">
-        <v>-0.1317846624617965</v>
+        <v>-0.1317846632799232</v>
       </c>
       <c r="AJ62" t="n">
-        <v>-0.04258387327429114</v>
+        <v>-0.04258387417647247</v>
       </c>
       <c r="AK62" t="n">
         <v>217.0162200927734</v>
@@ -12467,13 +12467,13 @@
         <v>-0.05794228357619136</v>
       </c>
       <c r="AV62" t="n">
-        <v>-0.3125760590520036</v>
+        <v>-0.3125761103399044</v>
       </c>
       <c r="AW62" t="n">
-        <v>7.125945592394846</v>
+        <v>7.125944696569317</v>
       </c>
       <c r="AX62" t="n">
-        <v>-0.1467716305016187</v>
+        <v>-0.1467715514890349</v>
       </c>
       <c r="AY62" t="n">
         <v>11.40029507829921</v>
@@ -12614,16 +12614,16 @@
         <v>185.0085992431641</v>
       </c>
       <c r="AG63" t="n">
-        <v>196.23141746521</v>
+        <v>196.2314173126221</v>
       </c>
       <c r="AH63" t="n">
         <v>-0.08166434105488174</v>
       </c>
       <c r="AI63" t="n">
-        <v>-0.1341855647217852</v>
+        <v>-0.1341855640485352</v>
       </c>
       <c r="AJ63" t="n">
-        <v>-0.05719175026616519</v>
+        <v>-0.0571917495330454</v>
       </c>
       <c r="AK63" t="n">
         <v>238.1012115478516</v>
@@ -12668,7 +12668,7 @@
         <v>-0.06317153909373063</v>
       </c>
       <c r="AY63" t="n">
-        <v>10.99030185294266</v>
+        <v>10.99029862499243</v>
       </c>
       <c r="AZ63" t="inlineStr"/>
       <c r="BA63" t="n">
@@ -12856,7 +12856,7 @@
         <v>-0.0118709232744223</v>
       </c>
       <c r="AY64" t="n">
-        <v>15.27645526437194</v>
+        <v>15.27645137305561</v>
       </c>
       <c r="AZ64" t="inlineStr"/>
       <c r="BA64" t="n">
@@ -13048,7 +13048,7 @@
         <v>-0.2977247885607798</v>
       </c>
       <c r="AY65" t="n">
-        <v>-0.9120200367430831</v>
+        <v>-0.9120200169932308</v>
       </c>
       <c r="AZ65" t="inlineStr"/>
       <c r="BA65" t="n">
@@ -13531,7 +13531,7 @@
         </is>
       </c>
       <c r="X68" t="n">
-        <v>1416072921088</v>
+        <v>1555511115776</v>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
@@ -13539,10 +13539,10 @@
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>0.03102217987179756</v>
+        <v>0.0310616884380579</v>
       </c>
       <c r="AA68" t="n">
-        <v>43929668869.57373</v>
+        <v>48316801640.16992</v>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
@@ -13556,22 +13556,22 @@
         <v>26</v>
       </c>
       <c r="AE68" t="n">
-        <v>457</v>
+        <v>502</v>
       </c>
       <c r="AF68" t="n">
-        <v>412.1667486572265</v>
+        <v>415.2889825439453</v>
       </c>
       <c r="AG68" t="n">
-        <v>263.5951696395874</v>
+        <v>265.6287010192871</v>
       </c>
       <c r="AH68" t="n">
-        <v>0.1087745469250807</v>
+        <v>0.2087968164358394</v>
       </c>
       <c r="AI68" t="n">
-        <v>0.7337191748424456</v>
+        <v>0.8898560211065074</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0.5636354384671785</v>
+        <v>0.5634190919519328</v>
       </c>
       <c r="AK68" t="n">
         <v>503.3821411132812</v>
@@ -13580,47 +13580,47 @@
         <v>42.06480407714844</v>
       </c>
       <c r="AM68" t="n">
-        <v>-0.0921410144005157</v>
+        <v>-0.002745709472776525</v>
       </c>
       <c r="AN68" t="n">
-        <v>9.864189434041931</v>
+        <v>10.93396738706575</v>
       </c>
       <c r="AO68" t="n">
-        <v>59.87012987012987</v>
+        <v>61.94581280788177</v>
       </c>
       <c r="AP68" t="n">
-        <v>69468368</v>
+        <v>102580525</v>
       </c>
       <c r="AQ68" t="n">
-        <v>98770405.86</v>
+        <v>98050504.56</v>
       </c>
       <c r="AR68" t="n">
-        <v>0.7033318066796896</v>
+        <v>1.046200888616824</v>
       </c>
       <c r="AS68" t="n">
-        <v>0.04936854190585538</v>
+        <v>0.1867612293144207</v>
       </c>
       <c r="AT68" t="n">
-        <v>0.4282516740853213</v>
+        <v>0.5688891474635258</v>
       </c>
       <c r="AU68" t="n">
-        <v>0.5436660266240809</v>
+        <v>0.6956681517840015</v>
       </c>
       <c r="AV68" t="n">
-        <v>9.600434901678154</v>
+        <v>10.63079560951596</v>
       </c>
       <c r="AW68" t="n">
-        <v>5.151951599366194</v>
+        <v>5.872819176249541</v>
       </c>
       <c r="AX68" t="n">
-        <v>1.214825064405663</v>
+        <v>1.432915059806658</v>
       </c>
       <c r="AY68" t="n">
-        <v>-0.4667316204618699</v>
+        <v>-0.4142216466911207</v>
       </c>
       <c r="AZ68" t="inlineStr"/>
       <c r="BA68" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
@@ -13806,13 +13806,13 @@
         <v>0.8568778533479506</v>
       </c>
       <c r="AW69" t="n">
-        <v>1.650180647343206</v>
+        <v>1.650180364604071</v>
       </c>
       <c r="AX69" t="n">
         <v>0.7945835878110208</v>
       </c>
       <c r="AY69" t="n">
-        <v>201.1085279004612</v>
+        <v>201.1085022069022</v>
       </c>
       <c r="AZ69" t="inlineStr"/>
       <c r="BA69" t="n">
@@ -13827,12 +13827,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>285A.T</t>
+          <t>STX</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Kioxia</t>
+          <t>Seagate</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -13842,27 +13842,31 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NAND / SSD storage</t>
+          <t>HDD / enterprise storage</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>NAND/storage</t>
+          <t>HDD/enterprise storage</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
-      <c r="J70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>S&amp;P 500, Nasdaq-100</t>
+        </is>
+      </c>
       <c r="K70" s="1" t="n">
         <v>46195</v>
       </c>
@@ -13906,27 +13910,27 @@
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X70" t="n">
-        <v>26119883456512</v>
+        <v>184207589376</v>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z70" t="n">
-        <v>0.006339345127344131</v>
+        <v>1</v>
       </c>
       <c r="AA70" t="n">
-        <v>165582955916.8359</v>
+        <v>184207589376</v>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
@@ -13934,71 +13938,73 @@
         </is>
       </c>
       <c r="AC70" s="2" t="n">
-        <v>45644</v>
+        <v>37601</v>
       </c>
       <c r="AD70" t="n">
-        <v>1.6</v>
+        <v>23.7</v>
       </c>
       <c r="AE70" t="n">
-        <v>47730</v>
+        <v>812.760009765625</v>
       </c>
       <c r="AF70" t="n">
-        <v>72998.60000000001</v>
+        <v>891.9062316894531</v>
       </c>
       <c r="AG70" t="n">
-        <v>33976.215</v>
+        <v>532.9958473205567</v>
       </c>
       <c r="AH70" t="n">
-        <v>-0.3461518440079673</v>
+        <v>-0.08873827663913603</v>
       </c>
       <c r="AI70" t="n">
-        <v>0.4048062740361162</v>
+        <v>0.5248899477387698</v>
       </c>
       <c r="AJ70" t="n">
-        <v>1.148520663646613</v>
+        <v>0.6733830782607186</v>
       </c>
       <c r="AK70" t="n">
-        <v>108700</v>
+        <v>1093.260498046875</v>
       </c>
       <c r="AL70" t="n">
-        <v>2300</v>
+        <v>146.8871765136719</v>
       </c>
       <c r="AM70" t="n">
-        <v>-0.5609015639374425</v>
+        <v>-0.2565724168964012</v>
       </c>
       <c r="AN70" t="n">
-        <v>19.75217391304348</v>
+        <v>4.533226446693768</v>
       </c>
       <c r="AO70" t="n">
-        <v>46.38255698711596</v>
+        <v>51.05563831812297</v>
       </c>
       <c r="AP70" t="n">
-        <v>52912400</v>
+        <v>5966700</v>
       </c>
       <c r="AQ70" t="n">
-        <v>43334514</v>
+        <v>4965466</v>
       </c>
       <c r="AR70" t="n">
-        <v>1.22102211645895</v>
+        <v>1.201639483585226</v>
       </c>
       <c r="AS70" t="n">
-        <v>-0.3869766247110198</v>
+        <v>-0.1071907355616433</v>
       </c>
       <c r="AT70" t="n">
-        <v>0.035357917570499</v>
+        <v>0.03922555015211127</v>
       </c>
       <c r="AU70" t="n">
-        <v>1.296367572768824</v>
+        <v>0.8977879572626952</v>
       </c>
       <c r="AV70" t="n">
-        <v>18.44987775061125</v>
-      </c>
-      <c r="AW70" t="inlineStr"/>
+        <v>4.533226446693768</v>
+      </c>
+      <c r="AW70" t="n">
+        <v>9.660505533541739</v>
+      </c>
       <c r="AX70" t="n">
-        <v>3.205286343612335</v>
+        <v>1.833547646867189</v>
       </c>
       <c r="AY70" t="n">
-        <v>28.81261711430356</v>
+        <v>153.18295209005</v>
       </c>
       <c r="AZ70" t="inlineStr"/>
       <c r="BA70" t="n">
@@ -14013,12 +14019,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STX</t>
+          <t>2344.TW</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Seagate</t>
+          <t>Winbond</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -14028,31 +14034,27 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>HDD / enterprise storage</t>
+          <t>Enterprise storage / data storage</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>HDD/enterprise storage</t>
+          <t>Specialty memory</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>S&amp;P 500, Nasdaq-100</t>
-        </is>
-      </c>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" s="1" t="n">
         <v>46195</v>
       </c>
@@ -14088,7 +14090,11 @@
       <c r="S71" t="n">
         <v>0</v>
       </c>
-      <c r="T71" t="inlineStr"/>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Winbond Electronics Corporation</t>
+        </is>
+      </c>
       <c r="U71" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -14096,27 +14102,27 @@
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TWD</t>
         </is>
       </c>
       <c r="X71" t="n">
-        <v>184207589376</v>
+        <v>807750074368</v>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>TWD</t>
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>1</v>
+        <v>0.0310616884380579</v>
       </c>
       <c r="AA71" t="n">
-        <v>184207589376</v>
+        <v>25090081145.83691</v>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
@@ -14124,77 +14130,77 @@
         </is>
       </c>
       <c r="AC71" s="2" t="n">
-        <v>37601</v>
+        <v>36529</v>
       </c>
       <c r="AD71" t="n">
-        <v>23.7</v>
+        <v>26.6</v>
       </c>
       <c r="AE71" t="n">
-        <v>812.760009765625</v>
+        <v>179.5</v>
       </c>
       <c r="AF71" t="n">
-        <v>891.9062316894531</v>
+        <v>173.44</v>
       </c>
       <c r="AG71" t="n">
-        <v>532.9958470916748</v>
+        <v>111.1770309638977</v>
       </c>
       <c r="AH71" t="n">
-        <v>-0.08873827663913603</v>
+        <v>0.03494003690036895</v>
       </c>
       <c r="AI71" t="n">
-        <v>0.524889948393596</v>
+        <v>0.6145421265862792</v>
       </c>
       <c r="AJ71" t="n">
-        <v>0.6733830789793114</v>
+        <v>0.5600344648196336</v>
       </c>
       <c r="AK71" t="n">
-        <v>1093.260498046875</v>
+        <v>222</v>
       </c>
       <c r="AL71" t="n">
-        <v>146.8871765136719</v>
+        <v>16.4140625</v>
       </c>
       <c r="AM71" t="n">
-        <v>-0.2565724168964012</v>
+        <v>-0.1914414414414415</v>
       </c>
       <c r="AN71" t="n">
-        <v>4.533226446693768</v>
+        <v>9.935744883388862</v>
       </c>
       <c r="AO71" t="n">
-        <v>51.05563831812297</v>
+        <v>57.74193548387096</v>
       </c>
       <c r="AP71" t="n">
-        <v>5966700</v>
+        <v>154697808</v>
       </c>
       <c r="AQ71" t="n">
-        <v>4965466</v>
+        <v>179994927.94</v>
       </c>
       <c r="AR71" t="n">
-        <v>1.201639483585226</v>
+        <v>0.8594564845269829</v>
       </c>
       <c r="AS71" t="n">
-        <v>-0.1071907355616433</v>
+        <v>0.0748502994011977</v>
       </c>
       <c r="AT71" t="n">
-        <v>0.03922555015211127</v>
+        <v>0.471311475409836</v>
       </c>
       <c r="AU71" t="n">
-        <v>0.8977878220295714</v>
+        <v>0.3879983344556133</v>
       </c>
       <c r="AV71" t="n">
-        <v>4.533226446693768</v>
+        <v>9.310844422648914</v>
       </c>
       <c r="AW71" t="n">
-        <v>9.660504466741012</v>
+        <v>4.804445019004053</v>
       </c>
       <c r="AX71" t="n">
-        <v>1.833547646867189</v>
+        <v>0.9872222736514633</v>
       </c>
       <c r="AY71" t="n">
-        <v>153.1830078780286</v>
+        <v>3.715527458829068</v>
       </c>
       <c r="AZ71" t="inlineStr"/>
       <c r="BA71" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
@@ -14205,12 +14211,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2344.TW</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Winbond</t>
+          <t>Lam Research</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -14225,22 +14231,26 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Specialty memory</t>
+          <t>Etch/deposition, memory equipment</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
-      </c>
-      <c r="J72" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
+        </is>
+      </c>
       <c r="K72" s="1" t="n">
         <v>46195</v>
       </c>
@@ -14274,11 +14284,11 @@
         </is>
       </c>
       <c r="S72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>Winbond Electronics Corporation</t>
+          <t>Lam Research Corporation</t>
         </is>
       </c>
       <c r="U72" t="inlineStr">
@@ -14288,101 +14298,101 @@
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X72" t="n">
-        <v>735750062080</v>
+        <v>389585403904</v>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>TWD</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>0.03102217987179756</v>
+        <v>1</v>
       </c>
       <c r="AA72" t="n">
-        <v>22824570766.53198</v>
+        <v>389585403904</v>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Mega cap</t>
         </is>
       </c>
       <c r="AC72" s="2" t="n">
-        <v>36529</v>
+        <v>30806</v>
       </c>
       <c r="AD72" t="n">
-        <v>26.6</v>
+        <v>42.3</v>
       </c>
       <c r="AE72" t="n">
-        <v>163.5</v>
+        <v>311.3500061035156</v>
       </c>
       <c r="AF72" t="n">
-        <v>173.01</v>
+        <v>337.7683770751953</v>
       </c>
       <c r="AG72" t="n">
-        <v>110.4934111785889</v>
+        <v>244.9322232818604</v>
       </c>
       <c r="AH72" t="n">
-        <v>-0.05496792092942604</v>
+        <v>-0.07821445927070403</v>
       </c>
       <c r="AI72" t="n">
-        <v>0.4797262411940324</v>
+        <v>0.2711680069356319</v>
       </c>
       <c r="AJ72" t="n">
-        <v>0.5657947216451349</v>
+        <v>0.3790279308676425</v>
       </c>
       <c r="AK72" t="n">
-        <v>222</v>
+        <v>433.3299865722656</v>
       </c>
       <c r="AL72" t="n">
-        <v>16.4140625</v>
+        <v>96.49594116210938</v>
       </c>
       <c r="AM72" t="n">
-        <v>-0.2635135135135135</v>
+        <v>-0.2814944366847034</v>
       </c>
       <c r="AN72" t="n">
-        <v>8.960970966206569</v>
+        <v>2.226560644457158</v>
       </c>
       <c r="AO72" t="n">
-        <v>54.35540069686411</v>
+        <v>51.28780555467554</v>
       </c>
       <c r="AP72" t="n">
-        <v>174570426</v>
+        <v>6709800</v>
       </c>
       <c r="AQ72" t="n">
-        <v>181837344.54</v>
+        <v>12433720</v>
       </c>
       <c r="AR72" t="n">
-        <v>0.9600361600177161</v>
+        <v>0.5396454158530191</v>
       </c>
       <c r="AS72" t="n">
-        <v>-0.07365439093484416</v>
+        <v>-0.1112664686518613</v>
       </c>
       <c r="AT72" t="n">
-        <v>0.345679012345679</v>
+        <v>0.0595795027068704</v>
       </c>
       <c r="AU72" t="n">
-        <v>0.2941418450834647</v>
+        <v>0.3503425054150335</v>
       </c>
       <c r="AV72" t="n">
-        <v>8.418682596622679</v>
+        <v>2.157571200020055</v>
       </c>
       <c r="AW72" t="n">
-        <v>4.165339876496194</v>
+        <v>4.110390740271722</v>
       </c>
       <c r="AX72" t="n">
-        <v>0.8100882548301631</v>
+        <v>0.68562960324334</v>
       </c>
       <c r="AY72" t="n">
-        <v>3.29520189146826</v>
+        <v>1650.444256062105</v>
       </c>
       <c r="AZ72" t="inlineStr"/>
       <c r="BA72" t="n">
@@ -14397,12 +14407,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>LRCX</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lam Research</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -14412,16 +14422,16 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Enterprise storage / data storage</t>
+          <t>HBM + DRAM + NAND</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Etch/deposition, memory equipment</t>
+          <t>HBM, DRAM, NAND</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G73" t="n">
         <v>1</v>
@@ -14434,7 +14444,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>S&amp;P 500, Nasdaq-100, SOXX</t>
+          <t>S&amp;P 500, Nasdaq-100, SOXX, STOXX Global AI Infrastructure</t>
         </is>
       </c>
       <c r="K73" s="1" t="n">
@@ -14456,10 +14466,10 @@
         </is>
       </c>
       <c r="O73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Q73" s="1" t="n">
         <v>46192</v>
@@ -14470,13 +14480,9 @@
         </is>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Lam Research Corporation</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="T73" t="inlineStr"/>
       <c r="U73" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -14484,7 +14490,7 @@
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
@@ -14492,9 +14498,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="X73" t="n">
-        <v>389585403904</v>
-      </c>
+      <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14503,82 +14507,80 @@
       <c r="Z73" t="n">
         <v>1</v>
       </c>
-      <c r="AA73" t="n">
-        <v>389585403904</v>
-      </c>
+      <c r="AA73" t="inlineStr"/>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>Mega cap</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AC73" s="2" t="n">
-        <v>30806</v>
+        <v>30834</v>
       </c>
       <c r="AD73" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="AE73" t="n">
-        <v>311.3500061035156</v>
+        <v>877.5700073242188</v>
       </c>
       <c r="AF73" t="n">
-        <v>337.7683770751953</v>
+        <v>970.8658251953125</v>
       </c>
       <c r="AG73" t="n">
-        <v>244.9322232818604</v>
+        <v>534.8599863433838</v>
       </c>
       <c r="AH73" t="n">
-        <v>-0.07821445927070403</v>
+        <v>-0.09609548039485794</v>
       </c>
       <c r="AI73" t="n">
-        <v>0.2711680069356319</v>
+        <v>0.640747166980655</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.3790279308676425</v>
+        <v>0.8151775230611662</v>
       </c>
       <c r="AK73" t="n">
-        <v>433.3299865722656</v>
+        <v>1213.373413085938</v>
       </c>
       <c r="AL73" t="n">
-        <v>96.49594116210938</v>
+        <v>111.6907348632812</v>
       </c>
       <c r="AM73" t="n">
-        <v>-0.2814944366847034</v>
+        <v>-0.2767519068245279</v>
       </c>
       <c r="AN73" t="n">
-        <v>2.226560644457158</v>
+        <v>6.85714238874368</v>
       </c>
       <c r="AO73" t="n">
-        <v>51.28780555467554</v>
+        <v>50.90142963896655</v>
       </c>
       <c r="AP73" t="n">
-        <v>6709800</v>
+        <v>34442200</v>
       </c>
       <c r="AQ73" t="n">
-        <v>12433720</v>
+        <v>50904862</v>
       </c>
       <c r="AR73" t="n">
-        <v>0.5396454158530191</v>
+        <v>0.6765994179495075</v>
       </c>
       <c r="AS73" t="n">
-        <v>-0.1112664686518613</v>
+        <v>-0.1038803040302462</v>
       </c>
       <c r="AT73" t="n">
-        <v>0.0595795027068704</v>
+        <v>0.1752721730431124</v>
       </c>
       <c r="AU73" t="n">
-        <v>0.3503425054150335</v>
+        <v>1.224717373021039</v>
       </c>
       <c r="AV73" t="n">
-        <v>2.157571200020055</v>
+        <v>6.85714238874368</v>
       </c>
       <c r="AW73" t="n">
-        <v>4.110391060249222</v>
+        <v>10.59125607552883</v>
       </c>
       <c r="AX73" t="n">
-        <v>0.68562960324334</v>
+        <v>1.783823430468583</v>
       </c>
       <c r="AY73" t="n">
-        <v>1650.444517115374</v>
+        <v>648.6924806844302</v>
       </c>
       <c r="AZ73" t="inlineStr"/>
       <c r="BA73" t="n">
@@ -14593,12 +14595,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>SanDisk</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -14608,29 +14610,29 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>HBM + DRAM + NAND</t>
+          <t>NAND / SSD storage</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>HBM, DRAM, NAND</t>
+          <t>NAND/storage, si cotiza separada en tu fuente</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G74" t="n">
         <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>S&amp;P 500, Nasdaq-100, SOXX, STOXX Global AI Infrastructure</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="K74" s="1" t="n">
@@ -14652,10 +14654,10 @@
         </is>
       </c>
       <c r="O74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="Q74" s="1" t="n">
         <v>46192</v>
@@ -14668,7 +14670,11 @@
       <c r="S74" t="n">
         <v>0</v>
       </c>
-      <c r="T74" t="inlineStr"/>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Sandisk Corporation</t>
+        </is>
+      </c>
       <c r="U74" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -14676,7 +14682,7 @@
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Computer Hardware</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -14684,7 +14690,9 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr"/>
+      <c r="X74" t="n">
+        <v>176982654976</v>
+      </c>
       <c r="Y74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14693,100 +14701,100 @@
       <c r="Z74" t="n">
         <v>1</v>
       </c>
-      <c r="AA74" t="inlineStr"/>
+      <c r="AA74" t="n">
+        <v>176982654976</v>
+      </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC74" s="2" t="n">
-        <v>30834</v>
+        <v>45701</v>
       </c>
       <c r="AD74" t="n">
-        <v>42.2</v>
+        <v>1.5</v>
       </c>
       <c r="AE74" t="n">
-        <v>877.5700073242188</v>
+        <v>1212.2099609375</v>
       </c>
       <c r="AF74" t="n">
-        <v>970.8658251953125</v>
+        <v>1688.094794921875</v>
       </c>
       <c r="AG74" t="n">
-        <v>534.8599863433838</v>
+        <v>872.2508486175537</v>
       </c>
       <c r="AH74" t="n">
-        <v>-0.09609548039485794</v>
+        <v>-0.2819064636748667</v>
       </c>
       <c r="AI74" t="n">
-        <v>0.640747166980655</v>
+        <v>0.3897492480044631</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.8151775230611662</v>
+        <v>0.9353317885529917</v>
       </c>
       <c r="AK74" t="n">
-        <v>1213.373413085938</v>
+        <v>2335</v>
       </c>
       <c r="AL74" t="n">
-        <v>111.6907348632812</v>
+        <v>40.68999862670898</v>
       </c>
       <c r="AM74" t="n">
-        <v>-0.2767519068245279</v>
+        <v>-0.4808522651231263</v>
       </c>
       <c r="AN74" t="n">
-        <v>6.85714238874368</v>
+        <v>28.79134927131217</v>
       </c>
       <c r="AO74" t="n">
-        <v>50.90142963896655</v>
+        <v>44.312063442193</v>
       </c>
       <c r="AP74" t="n">
-        <v>34442200</v>
+        <v>13883000</v>
       </c>
       <c r="AQ74" t="n">
-        <v>50904862</v>
+        <v>13780920</v>
       </c>
       <c r="AR74" t="n">
-        <v>0.6765994179495075</v>
+        <v>1.007407342905989</v>
       </c>
       <c r="AS74" t="n">
-        <v>-0.1038803040302462</v>
+        <v>-0.3672961641753663</v>
       </c>
       <c r="AT74" t="n">
-        <v>0.1752721730431124</v>
+        <v>-0.2241061564977476</v>
       </c>
       <c r="AU74" t="n">
-        <v>1.224717373021039</v>
+        <v>1.027276421423988</v>
       </c>
       <c r="AV74" t="n">
-        <v>6.85714238874368</v>
-      </c>
-      <c r="AW74" t="n">
-        <v>10.5912525713164</v>
-      </c>
+        <v>28.79134927131217</v>
+      </c>
+      <c r="AW74" t="inlineStr"/>
       <c r="AX74" t="n">
-        <v>1.783823430468583</v>
+        <v>3.404192718889677</v>
       </c>
       <c r="AY74" t="n">
-        <v>648.6923086698941</v>
+        <v>32.67249891493056</v>
       </c>
       <c r="AZ74" t="inlineStr"/>
       <c r="BA74" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>Strong momentum</t>
+          <t>Positive momentum</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>WDC</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SanDisk</t>
+          <t>Western Digital</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -14801,24 +14809,24 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>NAND/storage, si cotiza separada en tu fuente</t>
+          <t>HDD/NAND/storage</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G75" t="n">
         <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>S&amp;P 500, Nasdaq-100</t>
         </is>
       </c>
       <c r="K75" s="1" t="n">
@@ -14853,14 +14861,8 @@
           <t>https://www.blackrock.com/es/profesionales/productos/338777/ishares-ai-infrastructure-ucits-etf</t>
         </is>
       </c>
-      <c r="S75" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Sandisk Corporation</t>
-        </is>
-      </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
       <c r="U75" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -14876,9 +14878,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="X75" t="n">
-        <v>176982654976</v>
-      </c>
+      <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14887,80 +14887,80 @@
       <c r="Z75" t="n">
         <v>1</v>
       </c>
-      <c r="AA75" t="n">
-        <v>176982654976</v>
-      </c>
+      <c r="AA75" t="inlineStr"/>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="AC75" s="2" t="n">
-        <v>45701</v>
+        <v>28794</v>
       </c>
       <c r="AD75" t="n">
-        <v>1.5</v>
+        <v>47.8</v>
       </c>
       <c r="AE75" t="n">
-        <v>1212.2099609375</v>
+        <v>434.2999877929688</v>
       </c>
       <c r="AF75" t="n">
-        <v>1688.094794921875</v>
+        <v>561.1805792236328</v>
       </c>
       <c r="AG75" t="n">
-        <v>872.2508486175537</v>
+        <v>341.0865716171265</v>
       </c>
       <c r="AH75" t="n">
-        <v>-0.2819064636748667</v>
+        <v>-0.2260958346174371</v>
       </c>
       <c r="AI75" t="n">
-        <v>0.3897492480044631</v>
+        <v>0.2732837465101834</v>
       </c>
       <c r="AJ75" t="n">
-        <v>0.9353317885529917</v>
+        <v>0.6452731532731353</v>
       </c>
       <c r="AK75" t="n">
-        <v>2335</v>
+        <v>746.22998046875</v>
       </c>
       <c r="AL75" t="n">
-        <v>40.68999862670898</v>
+        <v>74.23881530761719</v>
       </c>
       <c r="AM75" t="n">
-        <v>-0.4808522651231263</v>
+        <v>-0.4180078539324299</v>
       </c>
       <c r="AN75" t="n">
-        <v>28.79134927131217</v>
+        <v>4.850039308862838</v>
       </c>
       <c r="AO75" t="n">
-        <v>44.312063442193</v>
+        <v>43.41204272369416</v>
       </c>
       <c r="AP75" t="n">
-        <v>13883000</v>
+        <v>11798000</v>
       </c>
       <c r="AQ75" t="n">
-        <v>13780920</v>
+        <v>8962192</v>
       </c>
       <c r="AR75" t="n">
-        <v>1.007407342905989</v>
+        <v>1.316419018918586</v>
       </c>
       <c r="AS75" t="n">
-        <v>-0.3672961641753663</v>
+        <v>-0.2545358351959711</v>
       </c>
       <c r="AT75" t="n">
-        <v>-0.2241061564977476</v>
+        <v>-0.09497244434495378</v>
       </c>
       <c r="AU75" t="n">
-        <v>1.027276421423988</v>
+        <v>0.5380465760513267</v>
       </c>
       <c r="AV75" t="n">
-        <v>28.79134927131217</v>
-      </c>
-      <c r="AW75" t="inlineStr"/>
+        <v>4.850039308862838</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>7.922699912708136</v>
+      </c>
       <c r="AX75" t="n">
-        <v>3.404192718889677</v>
+        <v>1.315509463132905</v>
       </c>
       <c r="AY75" t="n">
-        <v>32.67249891493056</v>
+        <v>638.1088111533334</v>
       </c>
       <c r="AZ75" t="inlineStr"/>
       <c r="BA75" t="n">
@@ -14975,12 +14975,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>WDC</t>
+          <t>000660.KS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Western Digital</t>
+          <t>SK Hynix</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -14990,31 +14990,27 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NAND / SSD storage</t>
+          <t>HBM + DRAM</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>HDD/NAND/storage</t>
+          <t>HBM/DRAM, memoria crítica para IA</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>S&amp;P 500, Nasdaq-100</t>
-        </is>
-      </c>
+      <c r="J76" t="inlineStr"/>
       <c r="K76" s="1" t="n">
         <v>46195</v>
       </c>
@@ -15047,8 +15043,14 @@
           <t>https://www.blackrock.com/es/profesionales/productos/338777/ishares-ai-infrastructure-ucits-etf</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
+      <c r="S76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>SK hynix Inc.</t>
+        </is>
+      </c>
       <c r="U76" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -15056,101 +15058,105 @@
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>Computer Hardware</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="X76" t="inlineStr"/>
+          <t>KRW</t>
+        </is>
+      </c>
+      <c r="X76" t="n">
+        <v>1007993994870784</v>
+      </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>KRW</t>
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA76" t="inlineStr"/>
+        <v>0.0007050296990200877</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>710665702817.8047</v>
+      </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Mega cap</t>
         </is>
       </c>
       <c r="AC76" s="2" t="n">
-        <v>28794</v>
+        <v>36529</v>
       </c>
       <c r="AD76" t="n">
-        <v>47.8</v>
+        <v>26.6</v>
       </c>
       <c r="AE76" t="n">
-        <v>434.2999877929688</v>
+        <v>1420000</v>
       </c>
       <c r="AF76" t="n">
-        <v>561.1805792236328</v>
+        <v>2107120</v>
       </c>
       <c r="AG76" t="n">
-        <v>341.0865718078613</v>
+        <v>1207841.44671875</v>
       </c>
       <c r="AH76" t="n">
-        <v>-0.2260958346174371</v>
+        <v>-0.3260943847526482</v>
       </c>
       <c r="AI76" t="n">
-        <v>0.2732837457981658</v>
+        <v>0.1756509961283452</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0.6452731523531021</v>
+        <v>0.7445336105365905</v>
       </c>
       <c r="AK76" t="n">
-        <v>746.22998046875</v>
+        <v>2919000</v>
       </c>
       <c r="AL76" t="n">
-        <v>74.23881530761719</v>
+        <v>243980.46875</v>
       </c>
       <c r="AM76" t="n">
-        <v>-0.4180078539324299</v>
+        <v>-0.513532031517643</v>
       </c>
       <c r="AN76" t="n">
-        <v>4.850039308862838</v>
+        <v>4.820138010534911</v>
       </c>
       <c r="AO76" t="n">
-        <v>43.41204272369416</v>
+        <v>37.77908343125735</v>
       </c>
       <c r="AP76" t="n">
-        <v>11798000</v>
+        <v>3284414</v>
       </c>
       <c r="AQ76" t="n">
-        <v>8962192</v>
+        <v>6009206.3</v>
       </c>
       <c r="AR76" t="n">
-        <v>1.316419018918586</v>
+        <v>0.5465636951089531</v>
       </c>
       <c r="AS76" t="n">
-        <v>-0.2545358351959711</v>
+        <v>-0.3486238532110092</v>
       </c>
       <c r="AT76" t="n">
-        <v>-0.09497244434495378</v>
+        <v>-0.2445545249089193</v>
       </c>
       <c r="AU76" t="n">
-        <v>0.5380465760513267</v>
+        <v>0.5687521150016823</v>
       </c>
       <c r="AV76" t="n">
-        <v>4.850039308862838</v>
+        <v>4.442495288271093</v>
       </c>
       <c r="AW76" t="n">
-        <v>7.922699912708136</v>
+        <v>10.79205193900623</v>
       </c>
       <c r="AX76" t="n">
-        <v>1.315509463132905</v>
+        <v>1.101710775920722</v>
       </c>
       <c r="AY76" t="n">
-        <v>638.1088672116349</v>
+        <v>-7.204292581275857</v>
       </c>
       <c r="AZ76" t="inlineStr"/>
       <c r="BA76" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
@@ -15161,12 +15167,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>000660.KS</t>
+          <t>005930.KS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SK Hynix</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -15176,16 +15182,16 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>HBM + DRAM</t>
+          <t>HBM/DRAM/NAND + foundry + packaging</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>HBM/DRAM, memoria crítica para IA</t>
+          <t>HBM/DRAM/NAND, foundry, packaging</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -15196,7 +15202,11 @@
       <c r="I77" t="n">
         <v>0</v>
       </c>
-      <c r="J77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>STOXX Global AI Infrastructure</t>
+        </is>
+      </c>
       <c r="K77" s="1" t="n">
         <v>46195</v>
       </c>
@@ -15216,10 +15226,10 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="Q77" s="1" t="n">
         <v>46192</v>
@@ -15234,7 +15244,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>SK hynix Inc.</t>
+          <t>Samsung Electronics Co., Ltd.</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -15244,7 +15254,7 @@
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Consumer Electronics</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -15253,7 +15263,7 @@
         </is>
       </c>
       <c r="X77" t="n">
-        <v>1009413682888704</v>
+        <v>1510309546164224</v>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
@@ -15261,10 +15271,10 @@
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>0.0007063643424771726</v>
+        <v>0.0007050296990200877</v>
       </c>
       <c r="AA77" t="n">
-        <v>713013832401.1406</v>
+        <v>1064813084759.328</v>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
@@ -15278,67 +15288,67 @@
         <v>26.6</v>
       </c>
       <c r="AE77" t="n">
-        <v>1422000</v>
+        <v>230000</v>
       </c>
       <c r="AF77" t="n">
-        <v>2124500</v>
+        <v>292232.52625</v>
       </c>
       <c r="AG77" t="n">
-        <v>1202997.7871875</v>
+        <v>196984.8521484375</v>
       </c>
       <c r="AH77" t="n">
-        <v>-0.3306660390680159</v>
+        <v>-0.2129555085759384</v>
       </c>
       <c r="AI77" t="n">
-        <v>0.1820470620519656</v>
+        <v>0.1676024704005363</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.7660049109208165</v>
+        <v>0.4835279112212589</v>
       </c>
       <c r="AK77" t="n">
-        <v>2919000</v>
+        <v>362100.65625</v>
       </c>
       <c r="AL77" t="n">
-        <v>243980.453125</v>
+        <v>66762.203125</v>
       </c>
       <c r="AM77" t="n">
-        <v>-0.512846865364851</v>
+        <v>-0.3648175002444504</v>
       </c>
       <c r="AN77" t="n">
-        <v>4.828335761272884</v>
+        <v>2.445063063143185</v>
       </c>
       <c r="AO77" t="n">
-        <v>40.34988713318284</v>
+        <v>42.16216216216215</v>
       </c>
       <c r="AP77" t="n">
-        <v>5002539</v>
+        <v>17786974</v>
       </c>
       <c r="AQ77" t="n">
-        <v>6068108</v>
+        <v>31293078.76</v>
       </c>
       <c r="AR77" t="n">
-        <v>0.8243984780758681</v>
+        <v>0.5683996175772894</v>
       </c>
       <c r="AS77" t="n">
-        <v>-0.3494967978042086</v>
+        <v>-0.1929824561403509</v>
       </c>
       <c r="AT77" t="n">
-        <v>-0.156442599203826</v>
+        <v>-0.1935073837905503</v>
       </c>
       <c r="AU77" t="n">
-        <v>0.7167014101518985</v>
+        <v>0.3774939940513222</v>
       </c>
       <c r="AV77" t="n">
-        <v>4.368203375441909</v>
+        <v>2.308043951588844</v>
       </c>
       <c r="AW77" t="n">
-        <v>10.7164062709706</v>
+        <v>2.172107178864284</v>
       </c>
       <c r="AX77" t="n">
-        <v>1.104670931943145</v>
+        <v>0.7955660253535874</v>
       </c>
       <c r="AY77" t="n">
-        <v>-7.21303144568902</v>
+        <v>52.87093254673965</v>
       </c>
       <c r="AZ77" t="inlineStr"/>
       <c r="BA77" t="n">
@@ -15353,12 +15363,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>005930.KS</t>
+          <t>285A.T</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Kioxia</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -15368,16 +15378,16 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>HBM/DRAM/NAND + foundry + packaging</t>
+          <t>NAND / SSD storage</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>HBM/DRAM/NAND, foundry, packaging</t>
+          <t>NAND/storage</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -15388,11 +15398,7 @@
       <c r="I78" t="n">
         <v>0</v>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>STOXX Global AI Infrastructure</t>
-        </is>
-      </c>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" s="1" t="n">
         <v>46195</v>
       </c>
@@ -15412,10 +15418,10 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>4.31</v>
+        <v>0</v>
       </c>
       <c r="Q78" s="1" t="n">
         <v>46192</v>
@@ -15428,11 +15434,7 @@
       <c r="S78" t="n">
         <v>0</v>
       </c>
-      <c r="T78" t="inlineStr">
-        <is>
-          <t>Samsung Electronics Co., Ltd.</t>
-        </is>
-      </c>
+      <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr">
         <is>
           <t>Technology</t>
@@ -15440,101 +15442,99 @@
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>Consumer Electronics</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="X78" t="n">
-        <v>1516876148506624</v>
+        <v>26273111867392</v>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>KRW</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>0.0007063643424771726</v>
+        <v>0.006313052028417587</v>
       </c>
       <c r="AA78" t="n">
-        <v>1071467223259.188</v>
+        <v>165863522167.2812</v>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>Mega cap</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC78" s="2" t="n">
-        <v>36529</v>
+        <v>45644</v>
       </c>
       <c r="AD78" t="n">
-        <v>26.6</v>
+        <v>1.6</v>
       </c>
       <c r="AE78" t="n">
-        <v>231000</v>
+        <v>48010</v>
       </c>
       <c r="AF78" t="n">
-        <v>293615.9275</v>
+        <v>72641.8</v>
       </c>
       <c r="AG78" t="n">
-        <v>196319.4504296875</v>
+        <v>34186.265</v>
       </c>
       <c r="AH78" t="n">
-        <v>-0.2132579388085137</v>
+        <v>-0.3390857605400748</v>
       </c>
       <c r="AI78" t="n">
-        <v>0.1766536606251017</v>
+        <v>0.4043651741423053</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.4956028394403007</v>
+        <v>1.124882610018966</v>
       </c>
       <c r="AK78" t="n">
-        <v>362100.65625</v>
+        <v>108700</v>
       </c>
       <c r="AL78" t="n">
-        <v>65083.26953125</v>
+        <v>2300</v>
       </c>
       <c r="AM78" t="n">
-        <v>-0.3620558372020349</v>
+        <v>-0.5583256669733211</v>
       </c>
       <c r="AN78" t="n">
-        <v>2.549299254074573</v>
+        <v>19.87391304347826</v>
       </c>
       <c r="AO78" t="n">
-        <v>46.73366834170854</v>
+        <v>37.42047426257953</v>
       </c>
       <c r="AP78" t="n">
-        <v>20546010</v>
+        <v>32549100</v>
       </c>
       <c r="AQ78" t="n">
-        <v>31541245.96</v>
+        <v>43134966</v>
       </c>
       <c r="AR78" t="n">
-        <v>0.6514013436899752</v>
+        <v>0.7545873572729835</v>
       </c>
       <c r="AS78" t="n">
-        <v>-0.1690647482014388</v>
+        <v>-0.3764935064935065</v>
       </c>
       <c r="AT78" t="n">
-        <v>-0.1387160087316859</v>
+        <v>-0.04930693069306935</v>
       </c>
       <c r="AU78" t="n">
-        <v>0.5407806622021825</v>
+        <v>1.297129186602871</v>
       </c>
       <c r="AV78" t="n">
-        <v>2.549299254074573</v>
-      </c>
-      <c r="AW78" t="n">
-        <v>2.166233015817673</v>
-      </c>
+        <v>18.77347611202636</v>
+      </c>
+      <c r="AW78" t="inlineStr"/>
       <c r="AX78" t="n">
-        <v>0.8033728341594726</v>
+        <v>3.229955947136564</v>
       </c>
       <c r="AY78" t="n">
-        <v>53.10514780480893</v>
+        <v>28.98750780762024</v>
       </c>
       <c r="AZ78" t="inlineStr"/>
       <c r="BA78" t="n">
@@ -16178,28 +16178,28 @@
         <v>157.5846905517578</v>
       </c>
       <c r="AG82" t="n">
-        <v>142.8491962814331</v>
+        <v>142.849194984436</v>
       </c>
       <c r="AH82" t="n">
         <v>0.07358139983918699</v>
       </c>
       <c r="AI82" t="n">
-        <v>0.1843258280744733</v>
+        <v>0.1843258388275417</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.1031541979507795</v>
+        <v>0.103154207966851</v>
       </c>
       <c r="AK82" t="n">
         <v>176.3200073242188</v>
       </c>
       <c r="AL82" t="n">
-        <v>107.8150939941406</v>
+        <v>107.8151016235352</v>
       </c>
       <c r="AM82" t="n">
         <v>-0.04049463675048726</v>
       </c>
       <c r="AN82" t="n">
-        <v>0.5691679746156471</v>
+        <v>0.5691678635755293</v>
       </c>
       <c r="AO82" t="n">
         <v>67.71010794050375</v>
@@ -16223,16 +16223,16 @@
         <v>0.2462020632721198</v>
       </c>
       <c r="AV82" t="n">
-        <v>0.5691679746156471</v>
+        <v>0.5691678635755293</v>
       </c>
       <c r="AW82" t="n">
-        <v>3.870523394195218</v>
+        <v>3.870522859307906</v>
       </c>
       <c r="AX82" t="n">
-        <v>0.2151608117657993</v>
+        <v>0.2151606785859466</v>
       </c>
       <c r="AY82" t="n">
-        <v>1350.990058116577</v>
+        <v>1350.98957512539</v>
       </c>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="n">
@@ -16973,13 +16973,13 @@
         <v>316.3519592285156</v>
       </c>
       <c r="AL86" t="n">
-        <v>62.17752838134766</v>
+        <v>62.17753219604492</v>
       </c>
       <c r="AM86" t="n">
         <v>-0.3086181550634508</v>
       </c>
       <c r="AN86" t="n">
-        <v>2.517669597273923</v>
+        <v>2.517669381458915</v>
       </c>
       <c r="AO86" t="n">
         <v>58.8034924611023</v>
@@ -17006,13 +17006,13 @@
         <v>1.889729579892497</v>
       </c>
       <c r="AW86" t="n">
-        <v>2.678710067763018</v>
+        <v>2.678710539818181</v>
       </c>
       <c r="AX86" t="n">
         <v>1.450396679886195</v>
       </c>
       <c r="AY86" t="n">
-        <v>17.03236357506422</v>
+        <v>17.03236215725805</v>
       </c>
       <c r="AZ86" t="inlineStr"/>
       <c r="BA86" t="n">
@@ -17507,7 +17507,7 @@
         </is>
       </c>
       <c r="X89" t="n">
-        <v>159807930368</v>
+        <v>146082217984</v>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
@@ -17515,10 +17515,10 @@
         </is>
       </c>
       <c r="Z89" t="n">
-        <v>0.148187667131424</v>
+        <v>0.1482843458652496</v>
       </c>
       <c r="AA89" t="n">
-        <v>23681564390.33496</v>
+        <v>21661706136.30225</v>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
@@ -17532,67 +17532,67 @@
         <v>17</v>
       </c>
       <c r="AE89" t="n">
-        <v>193.0399932861328</v>
+        <v>176.4600067138672</v>
       </c>
       <c r="AF89" t="n">
-        <v>212.0007992553711</v>
+        <v>211.4509994506836</v>
       </c>
       <c r="AG89" t="n">
-        <v>121.2983996772766</v>
+        <v>121.8810497093201</v>
       </c>
       <c r="AH89" t="n">
-        <v>-0.08943742682025724</v>
+        <v>-0.1654803847119072</v>
       </c>
       <c r="AI89" t="n">
-        <v>0.59144715676159</v>
+        <v>0.4478051110875323</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.7477625411333948</v>
+        <v>0.7348964416944486</v>
       </c>
       <c r="AK89" t="n">
         <v>276.0799865722656</v>
       </c>
       <c r="AL89" t="n">
-        <v>47.79999923706055</v>
+        <v>49.90999984741211</v>
       </c>
       <c r="AM89" t="n">
-        <v>-0.3007823722289141</v>
+        <v>-0.3608373830180635</v>
       </c>
       <c r="AN89" t="n">
-        <v>3.038493647850606</v>
+        <v>2.53556416055603</v>
       </c>
       <c r="AO89" t="n">
-        <v>58.9897052183574</v>
+        <v>45.79745012693149</v>
       </c>
       <c r="AP89" t="n">
-        <v>69983044</v>
+        <v>73744362</v>
       </c>
       <c r="AQ89" t="n">
-        <v>50321434.96</v>
+        <v>50640293.86</v>
       </c>
       <c r="AR89" t="n">
-        <v>1.39072035715255</v>
+        <v>1.456238824440345</v>
       </c>
       <c r="AS89" t="n">
-        <v>-0.1730991826530999</v>
+        <v>-0.1830555244728371</v>
       </c>
       <c r="AT89" t="n">
-        <v>-0.04198514498197115</v>
+        <v>-0.1086527977683646</v>
       </c>
       <c r="AU89" t="n">
-        <v>1.758108289442603</v>
+        <v>1.436956190988359</v>
       </c>
       <c r="AV89" t="n">
-        <v>3.038493647850606</v>
+        <v>2.356028919147864</v>
       </c>
       <c r="AW89" t="n">
-        <v>7.072548531498585</v>
+        <v>6.436317973874465</v>
       </c>
       <c r="AX89" t="n">
-        <v>1.725398677054621</v>
+        <v>1.491317268842708</v>
       </c>
       <c r="AY89" t="n">
-        <v>21.17077149079706</v>
+        <v>19.26654901670422</v>
       </c>
       <c r="AZ89" t="inlineStr"/>
       <c r="BA89" t="n">
@@ -17699,7 +17699,7 @@
         </is>
       </c>
       <c r="X90" t="n">
-        <v>1025870921728</v>
+        <v>957852745728</v>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
@@ -17707,10 +17707,10 @@
         </is>
       </c>
       <c r="Z90" t="n">
-        <v>0.148187667131424</v>
+        <v>0.1482843458652496</v>
       </c>
       <c r="AA90" t="n">
-        <v>152021418668.8359</v>
+        <v>142034567835.5098</v>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
@@ -17724,67 +17724,67 @@
         <v>14.3</v>
       </c>
       <c r="AE90" t="n">
-        <v>919.8699951171875</v>
+        <v>858.8800048828125</v>
       </c>
       <c r="AF90" t="n">
-        <v>1132.506207275391</v>
+        <v>1126.460606689453</v>
       </c>
       <c r="AG90" t="n">
-        <v>758.5551724243164</v>
+        <v>761.0810653686524</v>
       </c>
       <c r="AH90" t="n">
-        <v>-0.1877572156268955</v>
+        <v>-0.2375410202697023</v>
       </c>
       <c r="AI90" t="n">
-        <v>0.2126606324195437</v>
+        <v>0.1285000297133765</v>
       </c>
       <c r="AJ90" t="n">
-        <v>0.4929780303994757</v>
+        <v>0.4800796629250237</v>
       </c>
       <c r="AK90" t="n">
         <v>1382.329956054688</v>
       </c>
       <c r="AL90" t="n">
-        <v>184.8113250732422</v>
+        <v>191.4466552734375</v>
       </c>
       <c r="AM90" t="n">
-        <v>-0.3345510664164498</v>
+        <v>-0.3786722185098667</v>
       </c>
       <c r="AN90" t="n">
-        <v>3.977346462683689</v>
+        <v>3.486262785088097</v>
       </c>
       <c r="AO90" t="n">
-        <v>45.05135030146716</v>
+        <v>32.16565198812964</v>
       </c>
       <c r="AP90" t="n">
-        <v>57189157</v>
+        <v>49678017</v>
       </c>
       <c r="AQ90" t="n">
-        <v>36252216.38</v>
+        <v>36671240.82</v>
       </c>
       <c r="AR90" t="n">
-        <v>1.577535464329588</v>
+        <v>1.354686012503462</v>
       </c>
       <c r="AS90" t="n">
-        <v>-0.1591528076016159</v>
+        <v>-0.2248375407194833</v>
       </c>
       <c r="AT90" t="n">
-        <v>-0.09638601170783323</v>
+        <v>-0.1813953060867853</v>
       </c>
       <c r="AU90" t="n">
-        <v>0.500299141002426</v>
+        <v>0.3249560031512204</v>
       </c>
       <c r="AV90" t="n">
-        <v>3.977346462683689</v>
+        <v>3.486262785088097</v>
       </c>
       <c r="AW90" t="n">
-        <v>21.72846719346339</v>
+        <v>20.44538400388464</v>
       </c>
       <c r="AX90" t="n">
-        <v>0.4770550103675077</v>
+        <v>0.3791220729566376</v>
       </c>
       <c r="AY90" t="n">
-        <v>197.7557489404146</v>
+        <v>184.577717180149</v>
       </c>
       <c r="AZ90" t="inlineStr"/>
       <c r="BA90" t="n">
@@ -17891,7 +17891,7 @@
         </is>
       </c>
       <c r="X91" t="n">
-        <v>586912366592</v>
+        <v>554328522752</v>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
@@ -17899,10 +17899,10 @@
         </is>
       </c>
       <c r="Z91" t="n">
-        <v>0.148187667131424</v>
+        <v>0.1482843458652496</v>
       </c>
       <c r="AA91" t="n">
-        <v>86973174415.85156</v>
+        <v>82198242390.73047</v>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
@@ -17916,67 +17916,67 @@
         <v>10.4</v>
       </c>
       <c r="AE91" t="n">
-        <v>420.9500122070312</v>
+        <v>397.5799865722656</v>
       </c>
       <c r="AF91" t="n">
-        <v>513.8257781982422</v>
+        <v>511.7035247802734</v>
       </c>
       <c r="AG91" t="n">
-        <v>360.1154580688477</v>
+        <v>360.9533387756348</v>
       </c>
       <c r="AH91" t="n">
-        <v>-0.1807534186332279</v>
+        <v>-0.2230266798670435</v>
       </c>
       <c r="AI91" t="n">
-        <v>0.1689306936847823</v>
+        <v>0.1014719739700138</v>
       </c>
       <c r="AJ91" t="n">
-        <v>0.4268362178998935</v>
+        <v>0.4176445257882586</v>
       </c>
       <c r="AK91" t="n">
         <v>610.489990234375</v>
       </c>
       <c r="AL91" t="n">
-        <v>123.3260955810547</v>
+        <v>126.7698440551758</v>
       </c>
       <c r="AM91" t="n">
-        <v>-0.3104718849764874</v>
+        <v>-0.3487526528983227</v>
       </c>
       <c r="AN91" t="n">
-        <v>2.413308515312289</v>
+        <v>2.13623472155745</v>
       </c>
       <c r="AO91" t="n">
-        <v>38.5483963382999</v>
+        <v>29.18657965220305</v>
       </c>
       <c r="AP91" t="n">
-        <v>59827808</v>
+        <v>62872457</v>
       </c>
       <c r="AQ91" t="n">
-        <v>54751921.36</v>
+        <v>55078216.4</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.092707004867016</v>
+        <v>1.141512218612802</v>
       </c>
       <c r="AS91" t="n">
-        <v>-0.1952011814716842</v>
+        <v>-0.2242341725419207</v>
       </c>
       <c r="AT91" t="n">
-        <v>-0.003577996768237668</v>
+        <v>-0.1134635746988149</v>
       </c>
       <c r="AU91" t="n">
-        <v>0.502289970916302</v>
+        <v>0.3292869088834649</v>
       </c>
       <c r="AV91" t="n">
-        <v>2.413308515312289</v>
+        <v>2.13623472155745</v>
       </c>
       <c r="AW91" t="n">
-        <v>32.67601896149694</v>
+        <v>32.30223250214782</v>
       </c>
       <c r="AX91" t="n">
-        <v>0.3838689265885882</v>
+        <v>0.3070402026268819</v>
       </c>
       <c r="AY91" t="n">
-        <v>227.2832221510163</v>
+        <v>214.609572396949</v>
       </c>
       <c r="AZ91" t="inlineStr"/>
       <c r="BA91" t="n">
@@ -18359,7 +18359,7 @@
         <v>0.1263811006836935</v>
       </c>
       <c r="AV93" t="n">
-        <v>0.3136096999302989</v>
+        <v>0.3136098553802797</v>
       </c>
       <c r="AW93" t="n">
         <v>0.2990619195803677</v>
@@ -18368,7 +18368,7 @@
         <v>0.3165652204853286</v>
       </c>
       <c r="AY93" t="n">
-        <v>481.0811445530966</v>
+        <v>481.0813490084313</v>
       </c>
       <c r="AZ93" t="inlineStr"/>
       <c r="BA93" t="n">
@@ -18479,10 +18479,10 @@
         </is>
       </c>
       <c r="Z94" t="n">
-        <v>1.156203031539917</v>
+        <v>1.155668497085571</v>
       </c>
       <c r="AA94" t="n">
-        <v>7059649471.710938</v>
+        <v>7056385662.695312</v>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
@@ -18550,13 +18550,13 @@
         <v>0.06085226472901195</v>
       </c>
       <c r="AW94" t="n">
-        <v>0.6994787410652139</v>
+        <v>0.6994785832183097</v>
       </c>
       <c r="AX94" t="n">
         <v>0.1079828479200735</v>
       </c>
       <c r="AY94" t="n">
-        <v>7.643982826973444</v>
+        <v>7.643985889598593</v>
       </c>
       <c r="AZ94" t="inlineStr"/>
       <c r="BA94" t="n">
@@ -18667,10 +18667,10 @@
         </is>
       </c>
       <c r="Z95" t="n">
-        <v>1.156203031539917</v>
+        <v>1.155668497085571</v>
       </c>
       <c r="AA95" t="n">
-        <v>42575336701.20117</v>
+        <v>42555653320.55664</v>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
@@ -18744,7 +18744,7 @@
         <v>0.412317889606908</v>
       </c>
       <c r="AY95" t="n">
-        <v>11.03429047364181</v>
+        <v>11.03428828133952</v>
       </c>
       <c r="AZ95" t="inlineStr"/>
       <c r="BA95" t="n">
@@ -18934,7 +18934,7 @@
         <v>0.4185350617050061</v>
       </c>
       <c r="AW96" t="n">
-        <v>8.694404395003593</v>
+        <v>8.694403556891469</v>
       </c>
       <c r="AX96" t="n">
         <v>0.2350721494968062</v>
@@ -19289,13 +19289,13 @@
         <v>255.6900024414062</v>
       </c>
       <c r="AL98" t="n">
-        <v>63.82233047485352</v>
+        <v>63.82233428955078</v>
       </c>
       <c r="AM98" t="n">
         <v>-0.3520278810519846</v>
       </c>
       <c r="AN98" t="n">
-        <v>1.595956484871082</v>
+        <v>1.595956329709284</v>
       </c>
       <c r="AO98" t="n">
         <v>56.3101863446074</v>
@@ -19319,7 +19319,7 @@
         <v>0.360867856872048</v>
       </c>
       <c r="AV98" t="n">
-        <v>1.586335469119707</v>
+        <v>1.586335161092082</v>
       </c>
       <c r="AW98" t="n">
         <v>3.586805946455038</v>
@@ -19328,7 +19328,7 @@
         <v>0.8335019418261018</v>
       </c>
       <c r="AY98" t="n">
-        <v>215.1223550047973</v>
+        <v>215.1222541815995</v>
       </c>
       <c r="AZ98" t="inlineStr"/>
       <c r="BA98" t="n">
@@ -19437,7 +19437,7 @@
         </is>
       </c>
       <c r="Z99" t="n">
-        <v>0.154600128531456</v>
+        <v>0.1545542478561401</v>
       </c>
       <c r="AA99" t="inlineStr"/>
       <c r="AB99" t="inlineStr">
@@ -19512,7 +19512,7 @@
         <v>0.1201456310679612</v>
       </c>
       <c r="AY99" t="n">
-        <v>26.32768796510136</v>
+        <v>26.32769413807257</v>
       </c>
       <c r="AZ99" t="inlineStr"/>
       <c r="BA99" t="n">
@@ -19690,13 +19690,13 @@
         <v>1.277372105259189</v>
       </c>
       <c r="AW100" t="n">
-        <v>0.6998402373725046</v>
+        <v>0.699840090171616</v>
       </c>
       <c r="AX100" t="n">
         <v>0.4377879151449628</v>
       </c>
       <c r="AY100" t="n">
-        <v>14.66407844271657</v>
+        <v>14.66407375528334</v>
       </c>
       <c r="AZ100" t="inlineStr"/>
       <c r="BA100" t="n">
@@ -19834,25 +19834,25 @@
         <v>206.7642004394531</v>
       </c>
       <c r="AG101" t="n">
-        <v>218.5392498779297</v>
+        <v>218.5392499542236</v>
       </c>
       <c r="AH101" t="n">
         <v>0.04626430190173436</v>
       </c>
       <c r="AI101" t="n">
-        <v>-0.01010915910120957</v>
+        <v>-0.01010915944678914</v>
       </c>
       <c r="AJ101" t="n">
-        <v>-0.05388070767632713</v>
+        <v>-0.0538807080066257</v>
       </c>
       <c r="AK101" t="n">
-        <v>247.2834167480469</v>
+        <v>247.2834320068359</v>
       </c>
       <c r="AL101" t="n">
         <v>195.0859069824219</v>
       </c>
       <c r="AM101" t="n">
-        <v>-0.1251738403005411</v>
+        <v>-0.1251738942822727</v>
       </c>
       <c r="AN101" t="n">
         <v>0.1088961021184733</v>
@@ -19882,13 +19882,13 @@
         <v>0.09347035427524952</v>
       </c>
       <c r="AW101" t="n">
-        <v>0.5735534003470222</v>
+        <v>0.5735525271021373</v>
       </c>
       <c r="AX101" t="n">
         <v>-0.06598188885151257</v>
       </c>
       <c r="AY101" t="n">
-        <v>7.095231175318268</v>
+        <v>7.095229441941385</v>
       </c>
       <c r="AZ101" t="inlineStr"/>
       <c r="BA101" t="n">
@@ -20022,16 +20022,16 @@
         <v>67.17686309814454</v>
       </c>
       <c r="AG102" t="n">
-        <v>42.51158754348755</v>
+        <v>42.51158757209778</v>
       </c>
       <c r="AH102" t="n">
         <v>-0.1648910668519946</v>
       </c>
       <c r="AI102" t="n">
-        <v>0.3196401667364968</v>
+        <v>0.3196401658483812</v>
       </c>
       <c r="AJ102" t="n">
-        <v>0.5802012340617828</v>
+        <v>0.5802012329983097</v>
       </c>
       <c r="AK102" t="n">
         <v>79.81999969482422</v>
@@ -20070,13 +20070,13 @@
         <v>1.283306636260416</v>
       </c>
       <c r="AW102" t="n">
-        <v>0.4177838758235302</v>
+        <v>0.4177837391396646</v>
       </c>
       <c r="AX102" t="n">
         <v>1.057850303525782</v>
       </c>
       <c r="AY102" t="n">
-        <v>24.6202665613258</v>
+        <v>24.62027771979745</v>
       </c>
       <c r="AZ102" t="inlineStr"/>
       <c r="BA102" t="n">
@@ -20373,7 +20373,7 @@
         </is>
       </c>
       <c r="X104" t="n">
-        <v>560468590592</v>
+        <v>616061599744</v>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
@@ -20381,10 +20381,10 @@
         </is>
       </c>
       <c r="Z104" t="n">
-        <v>0.03102217987179756</v>
+        <v>0.0310616884380579</v>
       </c>
       <c r="AA104" t="n">
-        <v>17386957429.83789</v>
+        <v>19135913469.89966</v>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
@@ -20398,71 +20398,71 @@
         <v>26.6</v>
       </c>
       <c r="AE104" t="n">
-        <v>247</v>
+        <v>271.5</v>
       </c>
       <c r="AF104" t="n">
-        <v>218.75</v>
+        <v>219.49</v>
       </c>
       <c r="AG104" t="n">
-        <v>180.6177765655518</v>
+        <v>181.1501000976563</v>
       </c>
       <c r="AH104" t="n">
-        <v>0.1291428571428572</v>
+        <v>0.2369584035719166</v>
       </c>
       <c r="AI104" t="n">
-        <v>0.3675287377394776</v>
+        <v>0.4987571072477299</v>
       </c>
       <c r="AJ104" t="n">
-        <v>0.2111210987065211</v>
+        <v>0.211647136168708</v>
       </c>
       <c r="AK104" t="n">
-        <v>252.5</v>
+        <v>271.5</v>
       </c>
       <c r="AL104" t="n">
-        <v>113.7036819458008</v>
+        <v>115.1552200317383</v>
       </c>
       <c r="AM104" t="n">
-        <v>-0.0217821782178218</v>
+        <v>0</v>
       </c>
       <c r="AN104" t="n">
-        <v>1.172313119268536</v>
+        <v>1.357687301758193</v>
       </c>
       <c r="AO104" t="n">
-        <v>69.59706959706961</v>
+        <v>71.86440677966101</v>
       </c>
       <c r="AP104" t="n">
-        <v>32550357</v>
+        <v>26082727</v>
       </c>
       <c r="AQ104" t="n">
-        <v>28512071.88</v>
+        <v>27874616.14</v>
       </c>
       <c r="AR104" t="n">
-        <v>1.141634222058506</v>
+        <v>0.9357160962863038</v>
       </c>
       <c r="AS104" t="n">
-        <v>0.1569086651053864</v>
+        <v>0.222972972972973</v>
       </c>
       <c r="AT104" t="n">
-        <v>0.05330490405117261</v>
+        <v>0.2836879432624113</v>
       </c>
       <c r="AU104" t="n">
-        <v>0.4576066187262842</v>
+        <v>0.6549536510360119</v>
       </c>
       <c r="AV104" t="n">
-        <v>1.172313119268536</v>
+        <v>1.253532372082478</v>
       </c>
       <c r="AW104" t="n">
-        <v>4.072576956793891</v>
+        <v>4.59277865216668</v>
       </c>
       <c r="AX104" t="n">
-        <v>0.5056116088614915</v>
+        <v>0.6549536510360119</v>
       </c>
       <c r="AY104" t="n">
-        <v>63.72222690427212</v>
+        <v>70.14203848873851</v>
       </c>
       <c r="AZ104" t="inlineStr"/>
       <c r="BA104" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
@@ -20596,28 +20596,28 @@
         <v>407.7526507568359</v>
       </c>
       <c r="AG105" t="n">
-        <v>373.839365234375</v>
+        <v>373.8393661499023</v>
       </c>
       <c r="AH105" t="n">
         <v>0.1003729634693471</v>
       </c>
       <c r="AI105" t="n">
-        <v>0.200194614054316</v>
+        <v>0.2001946111150565</v>
       </c>
       <c r="AJ105" t="n">
-        <v>0.09071619705217326</v>
+        <v>0.09071619438102463</v>
       </c>
       <c r="AK105" t="n">
         <v>448.6799926757812</v>
       </c>
       <c r="AL105" t="n">
-        <v>313.2000122070312</v>
+        <v>313.2000427246094</v>
       </c>
       <c r="AM105" t="n">
         <v>0</v>
       </c>
       <c r="AN105" t="n">
-        <v>0.4325669705887341</v>
+        <v>0.4325668310023083</v>
       </c>
       <c r="AO105" t="n">
         <v>65.61718881791322</v>
@@ -20641,10 +20641,10 @@
         <v>0.2102971455704101</v>
       </c>
       <c r="AV105" t="n">
-        <v>0.2596692893308814</v>
+        <v>0.2596691814048004</v>
       </c>
       <c r="AW105" t="n">
-        <v>2.112531167978308</v>
+        <v>2.112532156377032</v>
       </c>
       <c r="AX105" t="n">
         <v>0.3822776469942279</v>
@@ -20765,10 +20765,10 @@
         </is>
       </c>
       <c r="Z106" t="n">
-        <v>1.156203031539917</v>
+        <v>1.155668497085571</v>
       </c>
       <c r="AA106" t="n">
-        <v>197400566208.6445</v>
+        <v>197309304206.1523</v>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>0.3012124187358578</v>
       </c>
       <c r="AY106" t="n">
-        <v>15.31990927955594</v>
+        <v>15.31990760684573</v>
       </c>
       <c r="AZ106" t="inlineStr"/>
       <c r="BA106" t="n">
@@ -21029,10 +21029,10 @@
         <v>0.06555211713328313</v>
       </c>
       <c r="AV107" t="n">
-        <v>0.1344644287524521</v>
+        <v>0.1344643473184957</v>
       </c>
       <c r="AW107" t="n">
-        <v>1.548835150990374</v>
+        <v>1.548834945459407</v>
       </c>
       <c r="AX107" t="n">
         <v>0.2175137391102846</v>
@@ -21145,7 +21145,7 @@
         </is>
       </c>
       <c r="X108" t="n">
-        <v>4285946658816</v>
+        <v>4714541350912</v>
       </c>
       <c r="Y108" t="inlineStr">
         <is>
@@ -21153,10 +21153,10 @@
         </is>
       </c>
       <c r="Z108" t="n">
-        <v>0.03102217987179756</v>
+        <v>0.0310616884380579</v>
       </c>
       <c r="AA108" t="n">
-        <v>132959408170.7197</v>
+        <v>146441614570.3691</v>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
@@ -21170,67 +21170,67 @@
         <v>26.6</v>
       </c>
       <c r="AE108" t="n">
-        <v>1650</v>
+        <v>1815</v>
       </c>
       <c r="AF108" t="n">
-        <v>1964.469541015625</v>
+        <v>1952.123911132813</v>
       </c>
       <c r="AG108" t="n">
-        <v>1495.316409301758</v>
+        <v>1499.268198852539</v>
       </c>
       <c r="AH108" t="n">
-        <v>-0.1600786036382347</v>
+        <v>-0.07024344630522961</v>
       </c>
       <c r="AI108" t="n">
-        <v>0.1034453910463486</v>
+        <v>0.2105906077305617</v>
       </c>
       <c r="AJ108" t="n">
-        <v>0.3137484005361377</v>
+        <v>0.302051169114949</v>
       </c>
       <c r="AK108" t="n">
         <v>2506.891357421875</v>
       </c>
       <c r="AL108" t="n">
-        <v>514.3106689453125</v>
+        <v>519.28466796875</v>
       </c>
       <c r="AM108" t="n">
-        <v>-0.3418143171162851</v>
+        <v>-0.2759957488279136</v>
       </c>
       <c r="AN108" t="n">
-        <v>2.208177663091502</v>
+        <v>2.495192737154382</v>
       </c>
       <c r="AO108" t="n">
-        <v>46.92737430167598</v>
+        <v>48.9247311827957</v>
       </c>
       <c r="AP108" t="n">
-        <v>9625558</v>
+        <v>10310352</v>
       </c>
       <c r="AQ108" t="n">
-        <v>11904469.32</v>
+        <v>11779941.2</v>
       </c>
       <c r="AR108" t="n">
-        <v>0.8085667442419012</v>
+        <v>0.8752464740655922</v>
       </c>
       <c r="AS108" t="n">
-        <v>-0.1223404255319149</v>
+        <v>-0.03968253968253965</v>
       </c>
       <c r="AT108" t="n">
-        <v>-0.2443608820798681</v>
+        <v>-0.1572791264642426</v>
       </c>
       <c r="AU108" t="n">
-        <v>0.2958030296566603</v>
+        <v>0.4537774701099391</v>
       </c>
       <c r="AV108" t="n">
-        <v>2.208177663091502</v>
+        <v>2.495192737154382</v>
       </c>
       <c r="AW108" t="n">
-        <v>5.210492496769102</v>
+        <v>5.831541746446012</v>
       </c>
       <c r="AX108" t="n">
-        <v>0.6669626472503403</v>
+        <v>0.8336589119753743</v>
       </c>
       <c r="AY108" t="n">
-        <v>65.79636646999613</v>
+        <v>72.47599177016886</v>
       </c>
       <c r="AZ108" t="inlineStr"/>
       <c r="BA108" t="n">
@@ -21337,7 +21337,7 @@
         </is>
       </c>
       <c r="X109" t="n">
-        <v>6181845204992</v>
+        <v>6186020634624</v>
       </c>
       <c r="Y109" t="inlineStr">
         <is>
@@ -21345,10 +21345,10 @@
         </is>
       </c>
       <c r="Z109" t="n">
-        <v>0.006339345127344131</v>
+        <v>0.006313052028417587</v>
       </c>
       <c r="AA109" t="n">
-        <v>39188850278.26172</v>
+        <v>39052670115.24609</v>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
@@ -21362,67 +21362,67 @@
         <v>26.6</v>
       </c>
       <c r="AE109" t="n">
-        <v>22210</v>
+        <v>22225</v>
       </c>
       <c r="AF109" t="n">
-        <v>24001.6</v>
+        <v>23980.4</v>
       </c>
       <c r="AG109" t="n">
-        <v>20995.11024414063</v>
+        <v>21020.61322265625</v>
       </c>
       <c r="AH109" t="n">
-        <v>-0.07464502366508896</v>
+        <v>-0.07320144784907678</v>
       </c>
       <c r="AI109" t="n">
-        <v>0.05786536682742249</v>
+        <v>0.05729551105795738</v>
       </c>
       <c r="AJ109" t="n">
-        <v>0.1431995222172473</v>
+        <v>0.1408040167997411</v>
       </c>
       <c r="AK109" t="n">
         <v>26150</v>
       </c>
       <c r="AL109" t="n">
-        <v>16864.458984375</v>
+        <v>16864.4609375</v>
       </c>
       <c r="AM109" t="n">
-        <v>-0.1506692160611854</v>
+        <v>-0.1500956022944551</v>
       </c>
       <c r="AN109" t="n">
-        <v>0.3169707976151306</v>
+        <v>0.3178600894725456</v>
       </c>
       <c r="AO109" t="n">
-        <v>22.80285035629454</v>
+        <v>22.71105826397147</v>
       </c>
       <c r="AP109" t="n">
-        <v>1168200</v>
+        <v>1004700</v>
       </c>
       <c r="AQ109" t="n">
-        <v>1335934</v>
+        <v>1321106</v>
       </c>
       <c r="AR109" t="n">
-        <v>0.8744443962052018</v>
+        <v>0.7604991575240745</v>
       </c>
       <c r="AS109" t="n">
-        <v>-0.1177755710029792</v>
+        <v>-0.1148944643568299</v>
       </c>
       <c r="AT109" t="n">
-        <v>-0.07880547490667777</v>
+        <v>-0.1378975950349108</v>
       </c>
       <c r="AU109" t="n">
-        <v>0.1446273321810077</v>
+        <v>0.1575194668688638</v>
       </c>
       <c r="AV109" t="n">
-        <v>0.1756590668106905</v>
+        <v>0.179210283934006</v>
       </c>
       <c r="AW109" t="n">
-        <v>0.1608497018995476</v>
+        <v>0.1363566005889099</v>
       </c>
       <c r="AX109" t="n">
-        <v>0.1067557286418612</v>
+        <v>0.1075031998678688</v>
       </c>
       <c r="AY109" t="n">
-        <v>19.71195571931356</v>
+        <v>19.72595813922726</v>
       </c>
       <c r="AZ109" t="inlineStr"/>
       <c r="BA109" t="n">
@@ -21556,28 +21556,28 @@
         <v>394.9421014404297</v>
       </c>
       <c r="AG110" t="n">
-        <v>333.4506100463867</v>
+        <v>333.4506093597412</v>
       </c>
       <c r="AH110" t="n">
         <v>-0.01269074314024332</v>
       </c>
       <c r="AI110" t="n">
-        <v>0.1693785554074638</v>
+        <v>0.1693785578154621</v>
       </c>
       <c r="AJ110" t="n">
-        <v>0.1844095933292453</v>
+        <v>0.1844095957681957</v>
       </c>
       <c r="AK110" t="n">
         <v>445.4800109863281</v>
       </c>
       <c r="AL110" t="n">
-        <v>220.1645812988281</v>
+        <v>220.1645660400391</v>
       </c>
       <c r="AM110" t="n">
         <v>-0.1246969941200161</v>
       </c>
       <c r="AN110" t="n">
-        <v>0.7710841152352816</v>
+        <v>0.7710842379825493</v>
       </c>
       <c r="AO110" t="n">
         <v>58.62544784127622</v>
@@ -21598,19 +21598,19 @@
         <v>-0.06127419360052611</v>
       </c>
       <c r="AU110" t="n">
-        <v>0.2239733993336805</v>
+        <v>0.2239735165822152</v>
       </c>
       <c r="AV110" t="n">
-        <v>0.7710841152352816</v>
+        <v>0.7710842379825493</v>
       </c>
       <c r="AW110" t="n">
-        <v>1.531893024705584</v>
+        <v>1.5318932755614</v>
       </c>
       <c r="AX110" t="n">
         <v>0.4328279443717782</v>
       </c>
       <c r="AY110" t="n">
-        <v>877.9847366696275</v>
+        <v>877.9849138222055</v>
       </c>
       <c r="AZ110" t="inlineStr"/>
       <c r="BA110" t="n">
@@ -21806,7 +21806,7 @@
         <v>0.209744724816826</v>
       </c>
       <c r="AY111" t="n">
-        <v>4.809474572440788</v>
+        <v>4.809474069605304</v>
       </c>
       <c r="AZ111" t="inlineStr"/>
       <c r="BA111" t="n">
@@ -21921,10 +21921,10 @@
         </is>
       </c>
       <c r="Z112" t="n">
-        <v>1.156203031539917</v>
+        <v>1.155668497085571</v>
       </c>
       <c r="AA112" t="n">
-        <v>93274297828.23633</v>
+        <v>93231175362.25586</v>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
@@ -21992,13 +21992,13 @@
         <v>0.772926138118484</v>
       </c>
       <c r="AW112" t="n">
-        <v>0.7826948061195205</v>
+        <v>0.7826946108374784</v>
       </c>
       <c r="AX112" t="n">
         <v>0.6348542540677973</v>
       </c>
       <c r="AY112" t="n">
-        <v>0.228757573792163</v>
+        <v>0.2287574810150743</v>
       </c>
       <c r="AZ112" t="inlineStr"/>
       <c r="BA112" t="n">
@@ -22113,10 +22113,10 @@
         </is>
       </c>
       <c r="Z113" t="n">
-        <v>1.156203031539917</v>
+        <v>1.155668497085571</v>
       </c>
       <c r="AA113" t="n">
-        <v>42490447349.66309</v>
+        <v>42470803214.96582</v>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
@@ -22184,13 +22184,13 @@
         <v>0.09178629326303289</v>
       </c>
       <c r="AW113" t="n">
-        <v>0.5737837649193829</v>
+        <v>0.5737836301373032</v>
       </c>
       <c r="AX113" t="n">
         <v>0.1148522073975351</v>
       </c>
       <c r="AY113" t="n">
-        <v>9.354092931230282</v>
+        <v>9.354093660479933</v>
       </c>
       <c r="AZ113" t="inlineStr"/>
       <c r="BA113" t="n">
@@ -22332,16 +22332,16 @@
         <v>1420.697885742188</v>
       </c>
       <c r="AG114" t="n">
-        <v>1216.465449829102</v>
+        <v>1216.465447998047</v>
       </c>
       <c r="AH114" t="n">
         <v>-0.01348481395795087</v>
       </c>
       <c r="AI114" t="n">
-        <v>0.1521412624250029</v>
+        <v>0.1521412641592352</v>
       </c>
       <c r="AJ114" t="n">
-        <v>0.1678900423697016</v>
+        <v>0.1678900441276394</v>
       </c>
       <c r="AK114" t="n">
         <v>1687.3154296875</v>
@@ -22374,10 +22374,10 @@
         <v>-0.1231612522951173</v>
       </c>
       <c r="AU114" t="n">
-        <v>0.1436510541359353</v>
+        <v>0.1436511680537538</v>
       </c>
       <c r="AV114" t="n">
-        <v>0.7687382641050649</v>
+        <v>0.7687384003441529</v>
       </c>
       <c r="AW114" t="n">
         <v>2.198240404755933</v>
@@ -22716,16 +22716,16 @@
         <v>161.4322882080078</v>
       </c>
       <c r="AG116" t="n">
-        <v>129.9591220855713</v>
+        <v>129.9591220474243</v>
       </c>
       <c r="AH116" t="n">
         <v>0.02018006601752953</v>
       </c>
       <c r="AI116" t="n">
-        <v>0.2672446519988529</v>
+        <v>0.2672446523708281</v>
       </c>
       <c r="AJ116" t="n">
-        <v>0.2421774294667294</v>
+        <v>0.2421774298313464</v>
       </c>
       <c r="AK116" t="n">
         <v>184.09619140625</v>
@@ -22758,19 +22758,19 @@
         <v>-0.02966687739905882</v>
       </c>
       <c r="AU116" t="n">
-        <v>0.4661847453061367</v>
+        <v>0.4661846457196981</v>
       </c>
       <c r="AV116" t="n">
-        <v>0.8607438924839257</v>
+        <v>0.8607440528808661</v>
       </c>
       <c r="AW116" t="n">
-        <v>4.574265760125077</v>
+        <v>4.574266479852812</v>
       </c>
       <c r="AX116" t="n">
         <v>0.5489840299902136</v>
       </c>
       <c r="AY116" t="n">
-        <v>7.623469782148632</v>
+        <v>7.623471504639866</v>
       </c>
       <c r="AZ116" t="inlineStr"/>
       <c r="BA116" t="n">
@@ -23153,7 +23153,7 @@
         <v>0.3738580515127394</v>
       </c>
       <c r="AV118" t="n">
-        <v>0.5243179592071905</v>
+        <v>0.5243178219781863</v>
       </c>
       <c r="AW118" t="n">
         <v>-0.290045598918205</v>
@@ -23162,7 +23162,7 @@
         <v>0.7436580066362866</v>
       </c>
       <c r="AY118" t="n">
-        <v>36.02131488832148</v>
+        <v>36.0212997108442</v>
       </c>
       <c r="AZ118" t="inlineStr"/>
       <c r="BA118" t="n">
@@ -23304,28 +23304,28 @@
         <v>676.4345825195312</v>
       </c>
       <c r="AG119" t="n">
-        <v>567.266852722168</v>
+        <v>567.2668518066406</v>
       </c>
       <c r="AH119" t="n">
         <v>-0.006762807943570204</v>
       </c>
       <c r="AI119" t="n">
-        <v>0.1843808291062292</v>
+        <v>0.1843808310177335</v>
       </c>
       <c r="AJ119" t="n">
-        <v>0.1924451063436816</v>
+        <v>0.1924451082682013</v>
       </c>
       <c r="AK119" t="n">
         <v>785.1200561523438</v>
       </c>
       <c r="AL119" t="n">
-        <v>372.1830749511719</v>
+        <v>372.18310546875</v>
       </c>
       <c r="AM119" t="n">
         <v>-0.1442582824285976</v>
       </c>
       <c r="AN119" t="n">
-        <v>0.8051868302708456</v>
+        <v>0.8051866822524929</v>
       </c>
       <c r="AO119" t="n">
         <v>57.14701478372736</v>
@@ -23349,16 +23349,16 @@
         <v>0.3227345576631968</v>
       </c>
       <c r="AV119" t="n">
-        <v>0.7359805946844185</v>
+        <v>0.7359807315710558</v>
       </c>
       <c r="AW119" t="n">
-        <v>6.600392559934566</v>
+        <v>6.600391903965576</v>
       </c>
       <c r="AX119" t="n">
         <v>0.5285996371577715</v>
       </c>
       <c r="AY119" t="n">
-        <v>90.35825496895262</v>
+        <v>90.35826089256912</v>
       </c>
       <c r="AZ119" t="inlineStr"/>
       <c r="BA119" t="n">
@@ -23500,16 +23500,16 @@
         <v>293.6175274658203</v>
       </c>
       <c r="AG120" t="n">
-        <v>226.87918800354</v>
+        <v>226.8791889190674</v>
       </c>
       <c r="AH120" t="n">
         <v>-0.02567129067058893</v>
       </c>
       <c r="AI120" t="n">
-        <v>0.2609353422395089</v>
+        <v>0.2609353371512466</v>
       </c>
       <c r="AJ120" t="n">
-        <v>0.2941580497072256</v>
+        <v>0.2941580444848995</v>
       </c>
       <c r="AK120" t="n">
         <v>330.5873718261719</v>
@@ -23542,13 +23542,13 @@
         <v>-0.0008868553352538999</v>
       </c>
       <c r="AU120" t="n">
-        <v>0.305119984685398</v>
+        <v>0.3051198938336177</v>
       </c>
       <c r="AV120" t="n">
         <v>0.5786596732062796</v>
       </c>
       <c r="AW120" t="n">
-        <v>0.7282526915371328</v>
+        <v>0.728252850848629</v>
       </c>
       <c r="AX120" t="n">
         <v>0.6386445054543586</v>
@@ -23746,7 +23746,7 @@
         <v>0.8928632191761952</v>
       </c>
       <c r="AY121" t="n">
-        <v>103.8772867510503</v>
+        <v>103.877310461946</v>
       </c>
       <c r="AZ121" t="inlineStr"/>
       <c r="BA121" t="n">
@@ -23886,16 +23886,16 @@
         <v>300.6927432250977</v>
       </c>
       <c r="AG122" t="n">
-        <v>248.6159850311279</v>
+        <v>248.6159851837158</v>
       </c>
       <c r="AH122" t="n">
         <v>-0.09409189269138241</v>
       </c>
       <c r="AI122" t="n">
-        <v>0.09566564620685414</v>
+        <v>0.09566564553439005</v>
       </c>
       <c r="AJ122" t="n">
-        <v>0.209466652707184</v>
+        <v>0.2094666519648747</v>
       </c>
       <c r="AK122" t="n">
         <v>376.1517333984375</v>
@@ -23928,16 +23928,16 @@
         <v>-0.1985861685679963</v>
       </c>
       <c r="AU122" t="n">
-        <v>0.3934016848197008</v>
+        <v>0.3934017935788177</v>
       </c>
       <c r="AV122" t="n">
-        <v>0.9563818607999486</v>
+        <v>0.9563816464022183</v>
       </c>
       <c r="AW122" t="n">
         <v>8.870262650796588</v>
       </c>
       <c r="AX122" t="n">
-        <v>0.5518564767949636</v>
+        <v>0.5518563418936917</v>
       </c>
       <c r="AY122" t="n">
         <v>26.41228296969114</v>
@@ -24243,10 +24243,10 @@
         </is>
       </c>
       <c r="Z124" t="n">
-        <v>0.1055351048707962</v>
+        <v>0.1054468601942062</v>
       </c>
       <c r="AA124" t="n">
-        <v>3465688929.195801</v>
+        <v>3462791044.183105</v>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>-0.06558656566590015</v>
       </c>
       <c r="AY124" t="n">
-        <v>1.883590682372755</v>
+        <v>1.8835903297372</v>
       </c>
       <c r="AZ124" t="inlineStr"/>
       <c r="BA124" t="n">
@@ -24512,7 +24512,7 @@
         <v>0.3891059547964462</v>
       </c>
       <c r="AY125" t="n">
-        <v>220.5936784671521</v>
+        <v>220.593543797971</v>
       </c>
       <c r="AZ125" t="inlineStr"/>
       <c r="BA125" t="n">
@@ -24735,7 +24735,7 @@
         </is>
       </c>
       <c r="Z127" t="n">
-        <v>1.156203031539917</v>
+        <v>1.155668497085571</v>
       </c>
       <c r="AA127" t="inlineStr"/>
       <c r="AB127" t="inlineStr">
@@ -24747,7 +24747,7 @@
         <v>35377</v>
       </c>
       <c r="AD127" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="AE127" t="n">
         <v>279.7999877929688</v>
@@ -24804,13 +24804,13 @@
         <v>0.2530078692184963</v>
       </c>
       <c r="AW127" t="n">
-        <v>1.251216889124606</v>
+        <v>1.251216750934474</v>
       </c>
       <c r="AX127" t="n">
         <v>0.1851863438041004</v>
       </c>
       <c r="AY127" t="n">
-        <v>28.43327988574663</v>
+        <v>28.43328283851758</v>
       </c>
       <c r="AZ127" t="inlineStr"/>
       <c r="BA127" t="n">
@@ -24925,10 +24925,10 @@
         </is>
       </c>
       <c r="Z128" t="n">
-        <v>1.156203031539917</v>
+        <v>1.155668497085571</v>
       </c>
       <c r="AA128" t="n">
-        <v>20265759207.63721</v>
+        <v>20256389965.17334</v>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>0.4942708189047786</v>
       </c>
       <c r="AY128" t="n">
-        <v>104.1347749237715</v>
+        <v>104.1347630208047</v>
       </c>
       <c r="AZ128" t="inlineStr"/>
       <c r="BA128" t="n">
@@ -25409,12 +25409,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ONTO</t>
+          <t>6857.T</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Onto Innovation</t>
+          <t>Advantest</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -25424,16 +25424,16 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Inspection / metrology</t>
+          <t>Semiconductor test equipment</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Metrology/inspection, packaging</t>
+          <t>AI chip testing equipment</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -25442,13 +25442,9 @@
         <v>0</v>
       </c>
       <c r="I131" t="n">
-        <v>1</v>
-      </c>
-      <c r="J131" t="inlineStr">
-        <is>
-          <t>SOXX</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J131" t="inlineStr"/>
       <c r="K131" s="1" t="n">
         <v>46195</v>
       </c>
@@ -25486,7 +25482,7 @@
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>Onto Innovation Inc.</t>
+          <t>Advantest Corporation</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
@@ -25501,22 +25497,22 @@
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="X131" t="n">
-        <v>15335941120</v>
+        <v>24807464763392</v>
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="Z131" t="n">
-        <v>1</v>
+        <v>0.006313052028417587</v>
       </c>
       <c r="AA131" t="n">
-        <v>15335941120</v>
+        <v>156610815744.4297</v>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
@@ -25524,77 +25520,77 @@
         </is>
       </c>
       <c r="AC131" s="2" t="n">
-        <v>43766</v>
+        <v>36529</v>
       </c>
       <c r="AD131" t="n">
-        <v>6.8</v>
+        <v>26.6</v>
       </c>
       <c r="AE131" t="n">
-        <v>308.2999877929688</v>
+        <v>34260</v>
       </c>
       <c r="AF131" t="n">
-        <v>294.5433984375</v>
+        <v>29592.1</v>
       </c>
       <c r="AG131" t="n">
-        <v>224.8297999572754</v>
+        <v>24832.48904296875</v>
       </c>
       <c r="AH131" t="n">
-        <v>0.04670479606212519</v>
+        <v>0.1577414242314672</v>
       </c>
       <c r="AI131" t="n">
-        <v>0.3712594498218442</v>
+        <v>0.3796442209525759</v>
       </c>
       <c r="AJ131" t="n">
-        <v>0.3100727683495352</v>
+        <v>0.1916687025934243</v>
       </c>
       <c r="AK131" t="n">
-        <v>378.4500122070312</v>
+        <v>35900</v>
       </c>
       <c r="AL131" t="n">
-        <v>92.68000030517578</v>
+        <v>10011.2412109375</v>
       </c>
       <c r="AM131" t="n">
-        <v>-0.1853614008491217</v>
+        <v>-0.04568245125348191</v>
       </c>
       <c r="AN131" t="n">
-        <v>2.326499641538645</v>
+        <v>2.422153085530514</v>
       </c>
       <c r="AO131" t="n">
-        <v>56.49667876097858</v>
+        <v>60.53230209281165</v>
       </c>
       <c r="AP131" t="n">
-        <v>2094000</v>
+        <v>7132900</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1325470</v>
+        <v>9171558</v>
       </c>
       <c r="AR131" t="n">
-        <v>1.579816970584019</v>
+        <v>0.7777195543003708</v>
       </c>
       <c r="AS131" t="n">
-        <v>-0.04087859180138209</v>
+        <v>0.1485082132081796</v>
       </c>
       <c r="AT131" t="n">
-        <v>0.08300830171995988</v>
+        <v>0.2110286320254506</v>
       </c>
       <c r="AU131" t="n">
-        <v>0.4786570157936152</v>
+        <v>0.3466783657957551</v>
       </c>
       <c r="AV131" t="n">
-        <v>2.326499641538645</v>
+        <v>2.31970304370269</v>
       </c>
       <c r="AW131" t="n">
-        <v>3.371809450777691</v>
+        <v>12.91241173191923</v>
       </c>
       <c r="AX131" t="n">
-        <v>0.8586844930884223</v>
+        <v>0.6201479597552864</v>
       </c>
       <c r="AY131" t="n">
-        <v>7.726294135710358</v>
+        <v>13.44641301543646</v>
       </c>
       <c r="AZ131" t="inlineStr"/>
       <c r="BA131" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
@@ -25605,12 +25601,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>6857.T</t>
+          <t>ONTO</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Advantest</t>
+          <t>Onto Innovation</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -25620,16 +25616,16 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Semiconductor test equipment</t>
+          <t>Inspection / metrology</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AI chip testing equipment</t>
+          <t>Metrology/inspection, packaging</t>
         </is>
       </c>
       <c r="F132" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -25638,9 +25634,13 @@
         <v>0</v>
       </c>
       <c r="I132" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>SOXX</t>
+        </is>
+      </c>
       <c r="K132" s="1" t="n">
         <v>46195</v>
       </c>
@@ -25678,7 +25678,7 @@
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>Advantest Corporation</t>
+          <t>Onto Innovation Inc.</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -25693,22 +25693,22 @@
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X132" t="n">
-        <v>23308590383104</v>
+        <v>15335941120</v>
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z132" t="n">
-        <v>0.006339345127344131</v>
+        <v>1</v>
       </c>
       <c r="AA132" t="n">
-        <v>147761198870.3906</v>
+        <v>15335941120</v>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
@@ -25716,77 +25716,77 @@
         </is>
       </c>
       <c r="AC132" s="2" t="n">
-        <v>36529</v>
+        <v>43766</v>
       </c>
       <c r="AD132" t="n">
-        <v>26.6</v>
+        <v>6.8</v>
       </c>
       <c r="AE132" t="n">
-        <v>32190</v>
+        <v>308.2999877929688</v>
       </c>
       <c r="AF132" t="n">
-        <v>29430.3</v>
+        <v>294.5433984375</v>
       </c>
       <c r="AG132" t="n">
-        <v>24746.07350585937</v>
+        <v>224.8297999572754</v>
       </c>
       <c r="AH132" t="n">
-        <v>0.09377070570126711</v>
+        <v>0.04670479606212519</v>
       </c>
       <c r="AI132" t="n">
-        <v>0.300812429591226</v>
+        <v>0.3712594498218442</v>
       </c>
       <c r="AJ132" t="n">
-        <v>0.1892917069462148</v>
+        <v>0.3100727683495352</v>
       </c>
       <c r="AK132" t="n">
-        <v>35900</v>
+        <v>378.4500122070312</v>
       </c>
       <c r="AL132" t="n">
-        <v>10011.2412109375</v>
+        <v>92.68000030517578</v>
       </c>
       <c r="AM132" t="n">
-        <v>-0.1033426183844011</v>
+        <v>-0.1853614008491217</v>
       </c>
       <c r="AN132" t="n">
-        <v>2.215385517315447</v>
+        <v>2.326499641538645</v>
       </c>
       <c r="AO132" t="n">
-        <v>60.6308146131155</v>
+        <v>56.49667876097858</v>
       </c>
       <c r="AP132" t="n">
-        <v>7228200</v>
+        <v>2094000</v>
       </c>
       <c r="AQ132" t="n">
-        <v>9217074</v>
+        <v>1325470</v>
       </c>
       <c r="AR132" t="n">
-        <v>0.7842185057861095</v>
+        <v>1.579816970584019</v>
       </c>
       <c r="AS132" t="n">
-        <v>0.1039094650205761</v>
+        <v>-0.04087859180138209</v>
       </c>
       <c r="AT132" t="n">
-        <v>0.1214074203100506</v>
+        <v>0.08300830171995988</v>
       </c>
       <c r="AU132" t="n">
-        <v>0.2383332967672693</v>
+        <v>0.4786570157936152</v>
       </c>
       <c r="AV132" t="n">
-        <v>2.086339830934895</v>
+        <v>2.326499641538645</v>
       </c>
       <c r="AW132" t="n">
-        <v>12.04643950104411</v>
+        <v>3.371809450777691</v>
       </c>
       <c r="AX132" t="n">
-        <v>0.5222581092972174</v>
+        <v>0.8586844930884223</v>
       </c>
       <c r="AY132" t="n">
-        <v>12.57355758436205</v>
+        <v>7.726294135710358</v>
       </c>
       <c r="AZ132" t="inlineStr"/>
       <c r="BA132" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         </is>
       </c>
       <c r="X133" t="n">
-        <v>24778490511360</v>
+        <v>25801456091136</v>
       </c>
       <c r="Y133" t="inlineStr">
         <is>
@@ -25901,10 +25901,10 @@
         </is>
       </c>
       <c r="Z133" t="n">
-        <v>0.006339345127344131</v>
+        <v>0.006312931887805462</v>
       </c>
       <c r="AA133" t="n">
-        <v>157079403086.1328</v>
+        <v>162882834909.5449</v>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
@@ -25918,22 +25918,22 @@
         <v>26.6</v>
       </c>
       <c r="AE133" t="n">
-        <v>54500</v>
+        <v>56750</v>
       </c>
       <c r="AF133" t="n">
-        <v>65765</v>
+        <v>65851.60000000001</v>
       </c>
       <c r="AG133" t="n">
-        <v>45631.25088867187</v>
+        <v>45774.11830078125</v>
       </c>
       <c r="AH133" t="n">
-        <v>-0.1712917205200335</v>
+        <v>-0.1382138019425497</v>
       </c>
       <c r="AI133" t="n">
-        <v>0.194356914145648</v>
+        <v>0.2397835743573768</v>
       </c>
       <c r="AJ133" t="n">
-        <v>0.4412272010786891</v>
+        <v>0.4386208286370441</v>
       </c>
       <c r="AK133" t="n">
         <v>78800</v>
@@ -25942,43 +25942,43 @@
         <v>19563.697265625</v>
       </c>
       <c r="AM133" t="n">
-        <v>-0.3083756345177665</v>
+        <v>-0.2798223350253807</v>
       </c>
       <c r="AN133" t="n">
-        <v>1.785771996981415</v>
+        <v>1.900780932636611</v>
       </c>
       <c r="AO133" t="n">
-        <v>33.40638697557921</v>
+        <v>34.99388753056235</v>
       </c>
       <c r="AP133" t="n">
-        <v>2877200</v>
+        <v>2551600</v>
       </c>
       <c r="AQ133" t="n">
-        <v>4745130</v>
+        <v>4725046</v>
       </c>
       <c r="AR133" t="n">
-        <v>0.6063479820363193</v>
+        <v>0.5400159067234478</v>
       </c>
       <c r="AS133" t="n">
-        <v>-0.2330424992963692</v>
+        <v>-0.2219632574718947</v>
       </c>
       <c r="AT133" t="n">
-        <v>0.0448619631901841</v>
+        <v>0.105375925204519</v>
       </c>
       <c r="AU133" t="n">
-        <v>0.3236197052365704</v>
+        <v>0.4073875446202302</v>
       </c>
       <c r="AV133" t="n">
-        <v>1.033012112465263</v>
+        <v>1.142817582402347</v>
       </c>
       <c r="AW133" t="n">
-        <v>2.734833762822262</v>
+        <v>2.930312167370482</v>
       </c>
       <c r="AX133" t="n">
-        <v>0.4895649844610999</v>
+        <v>0.5510607865718791</v>
       </c>
       <c r="AY133" t="n">
-        <v>19.1130349102143</v>
+        <v>19.94338956247085</v>
       </c>
       <c r="AZ133" t="inlineStr"/>
       <c r="BA133" t="n">
@@ -26120,16 +26120,16 @@
         <v>553.1085980224609</v>
       </c>
       <c r="AG134" t="n">
-        <v>380.6816049194336</v>
+        <v>380.6816050720215</v>
       </c>
       <c r="AH134" t="n">
         <v>-0.02525468492799698</v>
       </c>
       <c r="AI134" t="n">
-        <v>0.4162491900877101</v>
+        <v>0.4162491895200375</v>
       </c>
       <c r="AJ134" t="n">
-        <v>0.4529428027905873</v>
+        <v>0.4529428022082069</v>
       </c>
       <c r="AK134" t="n">
         <v>723</v>
@@ -26165,16 +26165,16 @@
         <v>0.6758656540571102</v>
       </c>
       <c r="AV134" t="n">
-        <v>1.965301776029878</v>
+        <v>1.965302024890588</v>
       </c>
       <c r="AW134" t="n">
-        <v>2.959830444821776</v>
+        <v>2.959831332390065</v>
       </c>
       <c r="AX134" t="n">
         <v>1.010203867993745</v>
       </c>
       <c r="AY134" t="n">
-        <v>7812.989784019137</v>
+        <v>7812.991471598939</v>
       </c>
       <c r="AZ134" t="inlineStr"/>
       <c r="BA134" t="n">
@@ -26316,28 +26316,28 @@
         <v>1758.692668457031</v>
       </c>
       <c r="AG135" t="n">
-        <v>1404.951268920898</v>
+        <v>1404.951266174317</v>
       </c>
       <c r="AH135" t="n">
         <v>-0.0100658168082246</v>
       </c>
       <c r="AI135" t="n">
-        <v>0.2391817629173558</v>
+        <v>0.23918176533987</v>
       </c>
       <c r="AJ135" t="n">
-        <v>0.2517819709204798</v>
+        <v>0.2517819733676263</v>
       </c>
       <c r="AK135" t="n">
         <v>1986.870361328125</v>
       </c>
       <c r="AL135" t="n">
-        <v>708.45361328125</v>
+        <v>708.4537353515625</v>
       </c>
       <c r="AM135" t="n">
         <v>-0.1237525990016737</v>
       </c>
       <c r="AN135" t="n">
-        <v>1.457450929173562</v>
+        <v>1.457450505741815</v>
       </c>
       <c r="AO135" t="n">
         <v>50.34200165282481</v>
@@ -26358,19 +26358,19 @@
         <v>0.09498722570309681</v>
       </c>
       <c r="AU135" t="n">
-        <v>0.2380334575343341</v>
+        <v>0.2380333500664973</v>
       </c>
       <c r="AV135" t="n">
-        <v>1.457450929173562</v>
+        <v>1.457450505741815</v>
       </c>
       <c r="AW135" t="n">
-        <v>1.370924757223249</v>
+        <v>1.370924363084391</v>
       </c>
       <c r="AX135" t="n">
         <v>0.5031651206257604</v>
       </c>
       <c r="AY135" t="n">
-        <v>988.335363241878</v>
+        <v>988.335162183554</v>
       </c>
       <c r="AZ135" t="inlineStr"/>
       <c r="BA135" t="n">
@@ -26566,7 +26566,7 @@
         <v>0.558456537890379</v>
       </c>
       <c r="AY136" t="n">
-        <v>3264.199449616654</v>
+        <v>3264.19985057864</v>
       </c>
       <c r="AZ136" t="inlineStr"/>
       <c r="BA136" t="n">
@@ -26704,28 +26704,28 @@
         <v>382.4803985595703</v>
       </c>
       <c r="AG137" t="n">
-        <v>295.4205001831054</v>
+        <v>295.4205004882813</v>
       </c>
       <c r="AH137" t="n">
         <v>-0.008289054845467492</v>
       </c>
       <c r="AI137" t="n">
-        <v>0.283966404916018</v>
+        <v>0.2839664035896527</v>
       </c>
       <c r="AJ137" t="n">
-        <v>0.2946982295490801</v>
+        <v>0.2946982282116284</v>
       </c>
       <c r="AK137" t="n">
         <v>483.8399963378906</v>
       </c>
       <c r="AL137" t="n">
-        <v>104.412712097168</v>
+        <v>104.4126968383789</v>
       </c>
       <c r="AM137" t="n">
         <v>-0.2160424924984873</v>
       </c>
       <c r="AN137" t="n">
-        <v>2.632795183076965</v>
+        <v>2.632795713970784</v>
       </c>
       <c r="AO137" t="n">
         <v>60.56011000872214</v>
@@ -26749,16 +26749,16 @@
         <v>0.2649092735195344</v>
       </c>
       <c r="AV137" t="n">
-        <v>2.572055341548659</v>
+        <v>2.572055598193284</v>
       </c>
       <c r="AW137" t="n">
-        <v>2.045019159024096</v>
+        <v>2.045019718520342</v>
       </c>
       <c r="AX137" t="n">
         <v>0.8289261037178648</v>
       </c>
       <c r="AY137" t="n">
-        <v>339.5666501264917</v>
+        <v>339.5667959341121</v>
       </c>
       <c r="AZ137" t="inlineStr"/>
       <c r="BA137" t="n">
@@ -26900,28 +26900,28 @@
         <v>425.6777319335937</v>
       </c>
       <c r="AG138" t="n">
-        <v>358.9664196777344</v>
+        <v>358.9664184570312</v>
       </c>
       <c r="AH138" t="n">
         <v>-0.01324411160307382</v>
       </c>
       <c r="AI138" t="n">
-        <v>0.1701373318485246</v>
+        <v>0.1701373358277001</v>
       </c>
       <c r="AJ138" t="n">
-        <v>0.1858427657822426</v>
+        <v>0.1858427698148259</v>
       </c>
       <c r="AK138" t="n">
         <v>477.5700073242188</v>
       </c>
       <c r="AL138" t="n">
-        <v>224.8433685302734</v>
+        <v>224.8433532714844</v>
       </c>
       <c r="AM138" t="n">
         <v>-0.1204640113428233</v>
       </c>
       <c r="AN138" t="n">
-        <v>0.8681449726117527</v>
+        <v>0.868145099391707</v>
       </c>
       <c r="AO138" t="n">
         <v>57.15554290691522</v>
@@ -26945,16 +26945,16 @@
         <v>0.2102909992776349</v>
       </c>
       <c r="AV138" t="n">
-        <v>0.7504139849265103</v>
+        <v>0.7504138736224693</v>
       </c>
       <c r="AW138" t="n">
-        <v>2.899316295903767</v>
+        <v>2.899316572073688</v>
       </c>
       <c r="AX138" t="n">
         <v>0.3210164320474449</v>
       </c>
       <c r="AY138" t="n">
-        <v>133.5030036470075</v>
+        <v>133.5030139156595</v>
       </c>
       <c r="AZ138" t="inlineStr"/>
       <c r="BA138" t="n">
@@ -27140,13 +27140,13 @@
         <v>1.855973990705625</v>
       </c>
       <c r="AW139" t="n">
-        <v>1.387359293259582</v>
+        <v>1.387359002904271</v>
       </c>
       <c r="AX139" t="n">
         <v>1.42976358400038</v>
       </c>
       <c r="AY139" t="n">
-        <v>2.096494368505751</v>
+        <v>2.096494856972399</v>
       </c>
       <c r="AZ139" t="inlineStr"/>
       <c r="BA139" t="n">
@@ -27161,12 +27161,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>6920.T</t>
+          <t>GFS</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Lasertec</t>
+          <t>GlobalFoundries</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -27176,16 +27176,16 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Inspection / metrology</t>
+          <t>Foundry</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>EUV mask inspection</t>
+          <t>Foundry, mature/specialty nodes</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -27194,9 +27194,13 @@
         <v>0</v>
       </c>
       <c r="I140" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>SOXX, STOXX Global AI Infrastructure</t>
+        </is>
+      </c>
       <c r="K140" s="1" t="n">
         <v>46195</v>
       </c>
@@ -27216,10 +27220,10 @@
         </is>
       </c>
       <c r="O140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P140" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="Q140" s="1" t="n">
         <v>46192</v>
@@ -27234,7 +27238,7 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>Lasertec Corporation</t>
+          <t>GLOBALFOUNDRIES Inc.</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
@@ -27244,27 +27248,27 @@
       </c>
       <c r="V140" t="inlineStr">
         <is>
-          <t>Semiconductor Equipment &amp; Materials</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W140" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X140" t="n">
-        <v>3357564731392</v>
+        <v>29591437312</v>
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>JPY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z140" t="n">
-        <v>0.006339345127344131</v>
+        <v>1</v>
       </c>
       <c r="AA140" t="n">
-        <v>21284761619.69238</v>
+        <v>29591437312</v>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
@@ -27272,73 +27276,71 @@
         </is>
       </c>
       <c r="AC140" s="2" t="n">
-        <v>40231</v>
+        <v>44497</v>
       </c>
       <c r="AD140" t="n">
-        <v>16.5</v>
+        <v>4.8</v>
       </c>
       <c r="AE140" t="n">
-        <v>37460</v>
+        <v>53.93000030517578</v>
       </c>
       <c r="AF140" t="n">
-        <v>44683.062578125</v>
+        <v>69.16365669250489</v>
       </c>
       <c r="AG140" t="n">
-        <v>36011.09791992188</v>
+        <v>51.89629417419434</v>
       </c>
       <c r="AH140" t="n">
-        <v>-0.1616510185597957</v>
+        <v>-0.2202552195158869</v>
       </c>
       <c r="AI140" t="n">
-        <v>0.04023487657332891</v>
+        <v>0.03918788736928169</v>
       </c>
       <c r="AJ140" t="n">
-        <v>0.2408136702048638</v>
+        <v>0.3327282379807539</v>
       </c>
       <c r="AK140" t="n">
-        <v>57263.48828125</v>
+        <v>89.83054351806641</v>
       </c>
       <c r="AL140" t="n">
-        <v>14136.361328125</v>
+        <v>31.57449913024902</v>
       </c>
       <c r="AM140" t="n">
-        <v>-0.3458309801873235</v>
+        <v>-0.3996474006156985</v>
       </c>
       <c r="AN140" t="n">
-        <v>1.649903969663781</v>
+        <v>0.7080239367442482</v>
       </c>
       <c r="AO140" t="n">
-        <v>44.1417614387728</v>
+        <v>44.64285536890945</v>
       </c>
       <c r="AP140" t="n">
-        <v>5470200</v>
+        <v>5712200</v>
       </c>
       <c r="AQ140" t="n">
-        <v>3608024</v>
+        <v>4062474</v>
       </c>
       <c r="AR140" t="n">
-        <v>1.516120735338789</v>
+        <v>1.406088998969593</v>
       </c>
       <c r="AS140" t="n">
-        <v>-0.1292422129242213</v>
+        <v>-0.2180658351360548</v>
       </c>
       <c r="AT140" t="n">
-        <v>-0.1352454115911035</v>
+        <v>-0.2713476039825269</v>
       </c>
       <c r="AU140" t="n">
-        <v>0.1715942253497553</v>
+        <v>0.2586277996213102</v>
       </c>
       <c r="AV140" t="n">
-        <v>1.33247191052229</v>
-      </c>
-      <c r="AW140" t="n">
-        <v>0.8428221673418566</v>
-      </c>
+        <v>0.6731016277130277</v>
+      </c>
+      <c r="AW140" t="inlineStr"/>
       <c r="AX140" t="n">
-        <v>0.1860036686645783</v>
+        <v>0.464814834002325</v>
       </c>
       <c r="AY140" t="n">
-        <v>287.6955094226686</v>
+        <v>0.1639594604897192</v>
       </c>
       <c r="AZ140" t="inlineStr"/>
       <c r="BA140" t="n">
@@ -27353,12 +27355,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>GFS</t>
+          <t>6920.T</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>GlobalFoundries</t>
+          <t>Lasertec</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -27368,16 +27370,16 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Foundry</t>
+          <t>Inspection / metrology</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Foundry, mature/specialty nodes</t>
+          <t>EUV mask inspection</t>
         </is>
       </c>
       <c r="F141" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -27386,13 +27388,9 @@
         <v>0</v>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>SOXX, STOXX Global AI Infrastructure</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J141" t="inlineStr"/>
       <c r="K141" s="1" t="n">
         <v>46195</v>
       </c>
@@ -27412,10 +27410,10 @@
         </is>
       </c>
       <c r="O141" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P141" t="n">
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="Q141" s="1" t="n">
         <v>46192</v>
@@ -27430,7 +27428,7 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>GLOBALFOUNDRIES Inc.</t>
+          <t>Lasertec Corporation</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
@@ -27440,27 +27438,27 @@
       </c>
       <c r="V141" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Semiconductor Equipment &amp; Materials</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="X141" t="n">
-        <v>29591437312</v>
+        <v>3548477915136</v>
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>JPY</t>
         </is>
       </c>
       <c r="Z141" t="n">
-        <v>1</v>
+        <v>0.006313052028417587</v>
       </c>
       <c r="AA141" t="n">
-        <v>29591437312</v>
+        <v>22401725699.94434</v>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
@@ -27468,75 +27466,77 @@
         </is>
       </c>
       <c r="AC141" s="2" t="n">
-        <v>44497</v>
+        <v>40231</v>
       </c>
       <c r="AD141" t="n">
-        <v>4.8</v>
+        <v>16.5</v>
       </c>
       <c r="AE141" t="n">
-        <v>53.93000030517578</v>
+        <v>39590</v>
       </c>
       <c r="AF141" t="n">
-        <v>69.16365669250489</v>
+        <v>44675.42484375</v>
       </c>
       <c r="AG141" t="n">
-        <v>51.89629417419434</v>
+        <v>36110.871875</v>
       </c>
       <c r="AH141" t="n">
-        <v>-0.2202552195158869</v>
+        <v>-0.1138304752900731</v>
       </c>
       <c r="AI141" t="n">
-        <v>0.03918788736928169</v>
+        <v>0.09634572482888859</v>
       </c>
       <c r="AJ141" t="n">
-        <v>0.3327282379807539</v>
+        <v>0.237173807334166</v>
       </c>
       <c r="AK141" t="n">
-        <v>89.83054351806641</v>
+        <v>57263.48828125</v>
       </c>
       <c r="AL141" t="n">
-        <v>31.57449913024902</v>
+        <v>14136.3603515625</v>
       </c>
       <c r="AM141" t="n">
-        <v>-0.3996474006156985</v>
+        <v>-0.308634503620292</v>
       </c>
       <c r="AN141" t="n">
-        <v>0.7080239367442482</v>
+        <v>1.800579428892678</v>
       </c>
       <c r="AO141" t="n">
-        <v>44.64285536890945</v>
+        <v>46.06741573033707</v>
       </c>
       <c r="AP141" t="n">
-        <v>5712200</v>
+        <v>3268000</v>
       </c>
       <c r="AQ141" t="n">
-        <v>4062474</v>
+        <v>3628498</v>
       </c>
       <c r="AR141" t="n">
-        <v>1.406088998969593</v>
+        <v>0.9006481469743128</v>
       </c>
       <c r="AS141" t="n">
-        <v>-0.2180658351360548</v>
+        <v>-0.1079315006759801</v>
       </c>
       <c r="AT141" t="n">
-        <v>-0.2713476039825269</v>
+        <v>-0.06456575209216631</v>
       </c>
       <c r="AU141" t="n">
-        <v>0.2586277996213102</v>
+        <v>0.3335548240513919</v>
       </c>
       <c r="AV141" t="n">
-        <v>0.6731016277130277</v>
-      </c>
-      <c r="AW141" t="inlineStr"/>
+        <v>1.688367511518522</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.9586253383857357</v>
+      </c>
       <c r="AX141" t="n">
-        <v>0.464814834002325</v>
+        <v>0.2534406097819182</v>
       </c>
       <c r="AY141" t="n">
-        <v>0.1639594604897192</v>
+        <v>304.1108523739733</v>
       </c>
       <c r="AZ141" t="inlineStr"/>
       <c r="BA141" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
@@ -27647,10 +27647,10 @@
         </is>
       </c>
       <c r="Z142" t="n">
-        <v>1.156203031539917</v>
+        <v>1.155668497085571</v>
       </c>
       <c r="AA142" t="n">
-        <v>48364250594.03027</v>
+        <v>48341890889.37988</v>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         </is>
       </c>
       <c r="X144" t="n">
-        <v>572717924352</v>
+        <v>564585103360</v>
       </c>
       <c r="Y144" t="inlineStr">
         <is>
@@ -28031,10 +28031,10 @@
         </is>
       </c>
       <c r="Z144" t="n">
-        <v>0.1274827271699905</v>
+        <v>0.1274684220552444</v>
       </c>
       <c r="AA144" t="n">
-        <v>73011642895.5293</v>
+        <v>71966772241.19629</v>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
@@ -28048,22 +28048,22 @@
         <v>22.4</v>
       </c>
       <c r="AE144" t="n">
-        <v>66.90000152587891</v>
+        <v>65.94999694824219</v>
       </c>
       <c r="AF144" t="n">
-        <v>75.26300010681152</v>
+        <v>74.81700004577637</v>
       </c>
       <c r="AG144" t="n">
-        <v>70.62699983596802</v>
+        <v>70.58999982833862</v>
       </c>
       <c r="AH144" t="n">
-        <v>-0.1111169973169291</v>
+        <v>-0.1185158866582321</v>
       </c>
       <c r="AI144" t="n">
-        <v>-0.05277016323424621</v>
+        <v>-0.06573173100127538</v>
       </c>
       <c r="AJ144" t="n">
-        <v>0.06564062301401252</v>
+        <v>0.05988100620083592</v>
       </c>
       <c r="AK144" t="n">
         <v>91.05000305175781</v>
@@ -28072,43 +28072,43 @@
         <v>48.65999984741211</v>
       </c>
       <c r="AM144" t="n">
-        <v>-0.2652388876049869</v>
+        <v>-0.2756727650986174</v>
       </c>
       <c r="AN144" t="n">
-        <v>0.3748459049663737</v>
+        <v>0.3553225884720099</v>
       </c>
       <c r="AO144" t="n">
-        <v>45.64885729141817</v>
+        <v>32.91591862672013</v>
       </c>
       <c r="AP144" t="n">
-        <v>79420452</v>
+        <v>40880886</v>
       </c>
       <c r="AQ144" t="n">
-        <v>136274002.44</v>
+        <v>131804222.38</v>
       </c>
       <c r="AR144" t="n">
-        <v>0.5827997312617862</v>
+        <v>0.310163705394337</v>
       </c>
       <c r="AS144" t="n">
-        <v>-0.160075326500244</v>
+        <v>-0.1582642216639559</v>
       </c>
       <c r="AT144" t="n">
-        <v>-0.08793452055105133</v>
+        <v>-0.1390339652484061</v>
       </c>
       <c r="AU144" t="n">
-        <v>-0.1127320932093432</v>
+        <v>-0.08656510061185207</v>
       </c>
       <c r="AV144" t="n">
-        <v>0.3326693328512529</v>
+        <v>0.2906066324374095</v>
       </c>
       <c r="AW144" t="n">
-        <v>1.883620660597023</v>
+        <v>1.759414142296031</v>
       </c>
       <c r="AX144" t="n">
-        <v>-0.1091877112496593</v>
+        <v>-0.1218375727268747</v>
       </c>
       <c r="AY144" t="n">
-        <v>1.703030364681976</v>
+        <v>1.664646341343119</v>
       </c>
       <c r="AZ144" t="inlineStr"/>
       <c r="BA144" t="n">
@@ -28215,7 +28215,7 @@
         </is>
       </c>
       <c r="X145" t="n">
-        <v>6338854256640</v>
+        <v>6831297527808</v>
       </c>
       <c r="Y145" t="inlineStr">
         <is>
@@ -28223,10 +28223,10 @@
         </is>
       </c>
       <c r="Z145" t="n">
-        <v>0.006339345127344131</v>
+        <v>0.006313052028417587</v>
       </c>
       <c r="AA145" t="n">
-        <v>40184184844.77539</v>
+        <v>43126336714.65234</v>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
@@ -28240,22 +28240,22 @@
         <v>25.6</v>
       </c>
       <c r="AE145" t="n">
-        <v>58440</v>
+        <v>62980</v>
       </c>
       <c r="AF145" t="n">
-        <v>71281</v>
+        <v>71238.8</v>
       </c>
       <c r="AG145" t="n">
-        <v>63420.0448828125</v>
+        <v>63478.90017578125</v>
       </c>
       <c r="AH145" t="n">
-        <v>-0.1801461820120369</v>
+        <v>-0.1159312060281757</v>
       </c>
       <c r="AI145" t="n">
-        <v>-0.07852477701670857</v>
+        <v>-0.007859307177656372</v>
       </c>
       <c r="AJ145" t="n">
-        <v>0.1239506394502394</v>
+        <v>0.1222437660818096</v>
       </c>
       <c r="AK145" t="n">
         <v>88480</v>
@@ -28264,43 +28264,43 @@
         <v>37284.22265625</v>
       </c>
       <c r="AM145" t="n">
-        <v>-0.3395117540687161</v>
+        <v>-0.2882007233273056</v>
       </c>
       <c r="AN145" t="n">
-        <v>0.5674190270453079</v>
+        <v>0.6891863505015998</v>
       </c>
       <c r="AO145" t="n">
-        <v>42.78889899909008</v>
+        <v>45.84409991386736</v>
       </c>
       <c r="AP145" t="n">
-        <v>1752700</v>
+        <v>1676600</v>
       </c>
       <c r="AQ145" t="n">
-        <v>1944202</v>
+        <v>1935272</v>
       </c>
       <c r="AR145" t="n">
-        <v>0.9015009757216585</v>
+        <v>0.8663381684848435</v>
       </c>
       <c r="AS145" t="n">
-        <v>-0.1827716403300238</v>
+        <v>-0.1320286659316428</v>
       </c>
       <c r="AT145" t="n">
-        <v>-0.1972527472527472</v>
+        <v>-0.1353651839648545</v>
       </c>
       <c r="AU145" t="n">
-        <v>-0.121755005958426</v>
+        <v>-0.07047311039665372</v>
       </c>
       <c r="AV145" t="n">
-        <v>0.3626578853073692</v>
+        <v>0.5086320068913079</v>
       </c>
       <c r="AW145" t="n">
-        <v>4.377998528303203</v>
+        <v>4.845759168919241</v>
       </c>
       <c r="AX145" t="n">
-        <v>0.150140055850134</v>
+        <v>0.2394904297987925</v>
       </c>
       <c r="AY145" t="n">
-        <v>38.98858997386135</v>
+        <v>42.09516781176229</v>
       </c>
       <c r="AZ145" t="inlineStr"/>
       <c r="BA145" t="n">
@@ -28407,7 +28407,7 @@
         </is>
       </c>
       <c r="X146" t="n">
-        <v>583539556352</v>
+        <v>613750079488</v>
       </c>
       <c r="Y146" t="inlineStr">
         <is>
@@ -28415,10 +28415,10 @@
         </is>
       </c>
       <c r="Z146" t="n">
-        <v>0.03102217987179756</v>
+        <v>0.0310616884380579</v>
       </c>
       <c r="AA146" t="n">
-        <v>18102669079.46069</v>
+        <v>19064113747.88953</v>
       </c>
       <c r="AB146" t="inlineStr">
         <is>
@@ -28432,22 +28432,22 @@
         <v>23</v>
       </c>
       <c r="AE146" t="n">
-        <v>183.5</v>
+        <v>193</v>
       </c>
       <c r="AF146" t="n">
-        <v>160.0881658935547</v>
+        <v>160.8903009033203</v>
       </c>
       <c r="AG146" t="n">
-        <v>140.52162109375</v>
+        <v>140.7848555755615</v>
       </c>
       <c r="AH146" t="n">
-        <v>0.1462433776773497</v>
+        <v>0.1995751074887637</v>
       </c>
       <c r="AI146" t="n">
-        <v>0.3058488691756314</v>
+        <v>0.3708860886419261</v>
       </c>
       <c r="AJ146" t="n">
-        <v>0.1392422365149824</v>
+        <v>0.1428097166102349</v>
       </c>
       <c r="AK146" t="n">
         <v>195</v>
@@ -28456,43 +28456,43 @@
         <v>105.6265716552734</v>
       </c>
       <c r="AM146" t="n">
-        <v>-0.05897435897435899</v>
+        <v>-0.01025641025641022</v>
       </c>
       <c r="AN146" t="n">
-        <v>0.7372522569309263</v>
+        <v>0.8271917470717647</v>
       </c>
       <c r="AO146" t="n">
-        <v>69.80198019801981</v>
+        <v>70.8133971291866</v>
       </c>
       <c r="AP146" t="n">
-        <v>64544291</v>
+        <v>69520322</v>
       </c>
       <c r="AQ146" t="n">
-        <v>74362119.95999999</v>
+        <v>73539389.23999999</v>
       </c>
       <c r="AR146" t="n">
-        <v>0.867972712917799</v>
+        <v>0.9453481014523586</v>
       </c>
       <c r="AS146" t="n">
-        <v>0.2698961937716262</v>
+        <v>0.3449477351916377</v>
       </c>
       <c r="AT146" t="n">
-        <v>0.3443753939913325</v>
+        <v>0.4240391313173595</v>
       </c>
       <c r="AU146" t="n">
-        <v>0.4143430165124702</v>
+        <v>0.5100188614350092</v>
       </c>
       <c r="AV146" t="n">
-        <v>0.6328680477189881</v>
+        <v>0.6673125384501106</v>
       </c>
       <c r="AW146" t="n">
-        <v>6.763519060826312</v>
+        <v>7.244593323422855</v>
       </c>
       <c r="AX146" t="n">
-        <v>0.2272847046817197</v>
+        <v>0.2908226049240974</v>
       </c>
       <c r="AY146" t="n">
-        <v>37.23406104356654</v>
+        <v>39.21348509295542</v>
       </c>
       <c r="AZ146" t="inlineStr"/>
       <c r="BA146" t="n">
@@ -28599,7 +28599,7 @@
         </is>
       </c>
       <c r="X147" t="n">
-        <v>233606037504</v>
+        <v>240042950656</v>
       </c>
       <c r="Y147" t="inlineStr">
         <is>
@@ -28607,10 +28607,10 @@
         </is>
       </c>
       <c r="Z147" t="n">
-        <v>0.03102217987179756</v>
+        <v>0.0310616884380579</v>
       </c>
       <c r="AA147" t="n">
-        <v>7246968514.586975</v>
+        <v>7456139345.028778</v>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
@@ -28624,22 +28624,22 @@
         <v>17.6</v>
       </c>
       <c r="AE147" t="n">
-        <v>87.09999847412109</v>
+        <v>89.5</v>
       </c>
       <c r="AF147" t="n">
-        <v>85.30988433837891</v>
+        <v>85.40611099243164</v>
       </c>
       <c r="AG147" t="n">
-        <v>74.67606834411622</v>
+        <v>74.78002899169923</v>
       </c>
       <c r="AH147" t="n">
-        <v>0.02098366619091596</v>
+        <v>0.04793438033879283</v>
       </c>
       <c r="AI147" t="n">
-        <v>0.1663709727292273</v>
+        <v>0.1968436119479806</v>
       </c>
       <c r="AJ147" t="n">
-        <v>0.1423992482472538</v>
+        <v>0.142097858800134</v>
       </c>
       <c r="AK147" t="n">
         <v>94.25801086425781</v>
@@ -28648,43 +28648,43 @@
         <v>65.35860443115234</v>
       </c>
       <c r="AM147" t="n">
-        <v>-0.07594062642001931</v>
+        <v>-0.05047858341833555</v>
       </c>
       <c r="AN147" t="n">
-        <v>0.332647770438103</v>
+        <v>0.3693682840838164</v>
       </c>
       <c r="AO147" t="n">
-        <v>62.81587960431818</v>
+        <v>62.27105531003006</v>
       </c>
       <c r="AP147" t="n">
-        <v>5217250</v>
+        <v>6532183</v>
       </c>
       <c r="AQ147" t="n">
-        <v>21180495.66</v>
+        <v>20558335.86</v>
       </c>
       <c r="AR147" t="n">
-        <v>0.2463233195176321</v>
+        <v>0.3177388989305091</v>
       </c>
       <c r="AS147" t="n">
-        <v>0.05320437349753049</v>
+        <v>0.08353512897510162</v>
       </c>
       <c r="AT147" t="n">
-        <v>0.1223163124495497</v>
+        <v>0.143372322148517</v>
       </c>
       <c r="AU147" t="n">
-        <v>0.2892330069513103</v>
+        <v>0.3342063549742842</v>
       </c>
       <c r="AV147" t="n">
-        <v>0.1237018078156353</v>
+        <v>0.158957437181263</v>
       </c>
       <c r="AW147" t="n">
-        <v>0.648574857970996</v>
+        <v>0.696308562762415</v>
       </c>
       <c r="AX147" t="n">
-        <v>0.3210427659811068</v>
+        <v>0.3574435089162282</v>
       </c>
       <c r="AY147" t="n">
-        <v>-0.08979245295354188</v>
+        <v>-0.06471201627158518</v>
       </c>
       <c r="AZ147" t="inlineStr"/>
       <c r="BA147" t="n">
@@ -28791,7 +28791,7 @@
         </is>
       </c>
       <c r="X148" t="n">
-        <v>3400886386688</v>
+        <v>3350709403648</v>
       </c>
       <c r="Y148" t="inlineStr">
         <is>
@@ -28799,10 +28799,10 @@
         </is>
       </c>
       <c r="Z148" t="n">
-        <v>0.03102217987179756</v>
+        <v>0.03104915097355843</v>
       </c>
       <c r="AA148" t="n">
-        <v>105502909211.3828</v>
+        <v>104036682142.3887</v>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
@@ -28816,67 +28816,67 @@
         <v>8.699999999999999</v>
       </c>
       <c r="AE148" t="n">
-        <v>6100</v>
+        <v>6010</v>
       </c>
       <c r="AF148" t="n">
-        <v>5150.428359375</v>
+        <v>5164.793515625</v>
       </c>
       <c r="AG148" t="n">
-        <v>4353.804869384766</v>
+        <v>4367.18758178711</v>
       </c>
       <c r="AH148" t="n">
-        <v>0.184367507781475</v>
+        <v>0.163647681522602</v>
       </c>
       <c r="AI148" t="n">
-        <v>0.4010733560647581</v>
+        <v>0.3761717094690562</v>
       </c>
       <c r="AJ148" t="n">
-        <v>0.1829717945312519</v>
+        <v>0.1826360601418222</v>
       </c>
       <c r="AK148" t="n">
         <v>6265</v>
       </c>
       <c r="AL148" t="n">
-        <v>2444.21142578125</v>
+        <v>2526.819091796875</v>
       </c>
       <c r="AM148" t="n">
-        <v>-0.0263367916999202</v>
+        <v>-0.04070231444533123</v>
       </c>
       <c r="AN148" t="n">
-        <v>1.495692449375667</v>
+        <v>1.378484482530232</v>
       </c>
       <c r="AO148" t="n">
-        <v>69.90154711673699</v>
+        <v>65.16516516516516</v>
       </c>
       <c r="AP148" t="n">
-        <v>1337905</v>
+        <v>1646047</v>
       </c>
       <c r="AQ148" t="n">
-        <v>1699942.1</v>
+        <v>1674827.16</v>
       </c>
       <c r="AR148" t="n">
-        <v>0.7870297464837185</v>
+        <v>0.982816041746063</v>
       </c>
       <c r="AS148" t="n">
-        <v>0.2103174603174602</v>
+        <v>0.2116935483870968</v>
       </c>
       <c r="AT148" t="n">
-        <v>0.08405288680017575</v>
+        <v>0.1082544448652309</v>
       </c>
       <c r="AU148" t="n">
-        <v>0.6941069006297438</v>
+        <v>0.6623816672978464</v>
       </c>
       <c r="AV148" t="n">
-        <v>1.495692449375667</v>
+        <v>1.378484482530232</v>
       </c>
       <c r="AW148" t="n">
-        <v>7.08186341267208</v>
+        <v>7.087597327215088</v>
       </c>
       <c r="AX148" t="n">
-        <v>0.4010415177202122</v>
+        <v>0.3803704133604058</v>
       </c>
       <c r="AY148" t="n">
-        <v>71.73171191867401</v>
+        <v>70.65861456851518</v>
       </c>
       <c r="AZ148" t="inlineStr"/>
       <c r="BA148" t="n">
@@ -29072,7 +29072,7 @@
         <v>0.6115822169461609</v>
       </c>
       <c r="AY149" t="n">
-        <v>2450.421847673214</v>
+        <v>2450.420925866068</v>
       </c>
       <c r="AZ149" t="inlineStr"/>
       <c r="BA149" t="n">
@@ -29214,16 +29214,16 @@
         <v>415.4798052978516</v>
       </c>
       <c r="AG150" t="n">
-        <v>221.0837464904785</v>
+        <v>221.0837463378906</v>
       </c>
       <c r="AH150" t="n">
         <v>0.09215895267971108</v>
       </c>
       <c r="AI150" t="n">
-        <v>1.052480095063047</v>
+        <v>1.05248009647963</v>
       </c>
       <c r="AJ150" t="n">
-        <v>0.8792869756065274</v>
+        <v>0.879286976903576</v>
       </c>
       <c r="AK150" t="n">
         <v>467.2699890136719</v>
@@ -29262,10 +29262,10 @@
         <v>2.43128803669638</v>
       </c>
       <c r="AW150" t="n">
-        <v>9.235264741023961</v>
+        <v>9.235262979646681</v>
       </c>
       <c r="AX150" t="n">
-        <v>2.583104546710907</v>
+        <v>2.583104762571462</v>
       </c>
       <c r="AY150" t="n">
         <v>40.39325497062877</v>
@@ -29410,16 +29410,16 @@
         <v>47.53984031677246</v>
       </c>
       <c r="AG151" t="n">
-        <v>30.00191758155823</v>
+        <v>30.001917552948</v>
       </c>
       <c r="AH151" t="n">
         <v>0.1194821199667904</v>
       </c>
       <c r="AI151" t="n">
-        <v>0.7738866549455738</v>
+        <v>0.7738866566371758</v>
       </c>
       <c r="AJ151" t="n">
-        <v>0.5845600597874636</v>
+        <v>0.5845600612985213</v>
       </c>
       <c r="AK151" t="n">
         <v>55.98620223999023</v>
@@ -29458,13 +29458,13 @@
         <v>1.663164725585572</v>
       </c>
       <c r="AW151" t="n">
-        <v>3.230374677615693</v>
+        <v>3.230374998303839</v>
       </c>
       <c r="AX151" t="n">
         <v>1.222585024650067</v>
       </c>
       <c r="AY151" t="n">
-        <v>6.386501199797168</v>
+        <v>6.386499733257128</v>
       </c>
       <c r="AZ151" t="inlineStr"/>
       <c r="BA151" t="n">
@@ -29650,13 +29650,13 @@
         <v>0.4677566115175937</v>
       </c>
       <c r="AW152" t="n">
-        <v>1.36270603169836</v>
+        <v>1.362706311510336</v>
       </c>
       <c r="AX152" t="n">
         <v>0.2517511554739953</v>
       </c>
       <c r="AY152" t="n">
-        <v>48.28881025992209</v>
+        <v>48.28883689732228</v>
       </c>
       <c r="AZ152" t="inlineStr"/>
       <c r="BA152" t="n">
@@ -29771,10 +29771,10 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>1.349236369132996</v>
+        <v>1.349309206008911</v>
       </c>
       <c r="AA153" t="n">
-        <v>170525189962.0068</v>
+        <v>170534395555.916</v>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
@@ -29794,16 +29794,16 @@
         <v>1396.456987304688</v>
       </c>
       <c r="AG153" t="n">
-        <v>1248.650485839844</v>
+        <v>1248.650487060547</v>
       </c>
       <c r="AH153" t="n">
         <v>0.09562987897899022</v>
       </c>
       <c r="AI153" t="n">
-        <v>0.2253228724537117</v>
+        <v>0.2253228712558142</v>
       </c>
       <c r="AJ153" t="n">
-        <v>0.1183729980014616</v>
+        <v>0.1183729969081202</v>
       </c>
       <c r="AK153" t="n">
         <v>1570.339965820312</v>
@@ -29842,13 +29842,13 @@
         <v>0.4280221036624443</v>
       </c>
       <c r="AW153" t="n">
-        <v>12.90943338906396</v>
+        <v>12.90943242430796</v>
       </c>
       <c r="AX153" t="n">
         <v>0.2783005599785742</v>
       </c>
       <c r="AY153" t="n">
-        <v>11.28808809474921</v>
+        <v>11.28808658884545</v>
       </c>
       <c r="AZ153" t="inlineStr"/>
       <c r="BA153" t="n">
@@ -29959,7 +29959,7 @@
         </is>
       </c>
       <c r="X154" t="n">
-        <v>3640499109888</v>
+        <v>3703507779584</v>
       </c>
       <c r="Y154" t="inlineStr">
         <is>
@@ -29967,10 +29967,10 @@
         </is>
       </c>
       <c r="Z154" t="n">
-        <v>0.03102217987179756</v>
+        <v>0.0310616884380579</v>
       </c>
       <c r="AA154" t="n">
-        <v>112936218210.0645</v>
+        <v>115037204777.3618</v>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
@@ -29984,22 +29984,22 @@
         <v>33.6</v>
       </c>
       <c r="AE154" t="n">
-        <v>260</v>
+        <v>264.5</v>
       </c>
       <c r="AF154" t="n">
-        <v>252.5371649169922</v>
+        <v>252.2143139648437</v>
       </c>
       <c r="AG154" t="n">
-        <v>228.6138608551025</v>
+        <v>228.9021590423584</v>
       </c>
       <c r="AH154" t="n">
-        <v>0.02955143289686024</v>
+        <v>0.04871129573109312</v>
       </c>
       <c r="AI154" t="n">
-        <v>0.1372888722822903</v>
+        <v>0.1555155316427321</v>
       </c>
       <c r="AJ154" t="n">
-        <v>0.1046450288377416</v>
+        <v>0.10184331602644</v>
       </c>
       <c r="AK154" t="n">
         <v>300.0641784667969</v>
@@ -30008,43 +30008,43 @@
         <v>166.5404815673828</v>
       </c>
       <c r="AM154" t="n">
-        <v>-0.1335186981382055</v>
+        <v>-0.1185219063752129</v>
       </c>
       <c r="AN154" t="n">
-        <v>0.5611819874244999</v>
+        <v>0.5882024448991547</v>
       </c>
       <c r="AO154" t="n">
-        <v>63.07692307692307</v>
+        <v>60.22099447513812</v>
       </c>
       <c r="AP154" t="n">
-        <v>37720298</v>
+        <v>34724617</v>
       </c>
       <c r="AQ154" t="n">
-        <v>68607163.04000001</v>
+        <v>63644613.5</v>
       </c>
       <c r="AR154" t="n">
-        <v>0.549801162569686</v>
+        <v>0.5456018206473986</v>
       </c>
       <c r="AS154" t="n">
-        <v>0.09473684210526323</v>
+        <v>0.1183932346723044</v>
       </c>
       <c r="AT154" t="n">
-        <v>0.0709708910617648</v>
+        <v>0.08516624681354013</v>
       </c>
       <c r="AU154" t="n">
-        <v>0.1873291059856457</v>
+        <v>0.2159675769514977</v>
       </c>
       <c r="AV154" t="n">
-        <v>0.5343422372648639</v>
+        <v>0.547595078199911</v>
       </c>
       <c r="AW154" t="n">
-        <v>1.930504533509446</v>
+        <v>1.954606575950384</v>
       </c>
       <c r="AX154" t="n">
-        <v>0.1540634345581156</v>
+        <v>0.174037609387006</v>
       </c>
       <c r="AY154" t="n">
-        <v>708.8071455763491</v>
+        <v>721.0923280000546</v>
       </c>
       <c r="AZ154" t="inlineStr"/>
       <c r="BA154" t="n">
@@ -30151,7 +30151,7 @@
         </is>
       </c>
       <c r="X155" t="n">
-        <v>229598396416</v>
+        <v>236773343232</v>
       </c>
       <c r="Y155" t="inlineStr">
         <is>
@@ -30159,10 +30159,10 @@
         </is>
       </c>
       <c r="Z155" t="n">
-        <v>0.03102217987179756</v>
+        <v>0.0310616884380579</v>
       </c>
       <c r="AA155" t="n">
-        <v>7122642751.893433</v>
+        <v>7354579817.909729</v>
       </c>
       <c r="AB155" t="inlineStr">
         <is>
@@ -30176,22 +30176,22 @@
         <v>26.6</v>
       </c>
       <c r="AE155" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="AF155" t="n">
-        <v>64.98188713073731</v>
+        <v>64.94196876525879</v>
       </c>
       <c r="AG155" t="n">
-        <v>49.11936758041382</v>
+        <v>49.23022119522095</v>
       </c>
       <c r="AH155" t="n">
-        <v>-0.01511016644933449</v>
+        <v>0.01629194887154717</v>
       </c>
       <c r="AI155" t="n">
-        <v>0.3029483715405119</v>
+        <v>0.3406399239661955</v>
       </c>
       <c r="AJ155" t="n">
-        <v>0.3229381877597426</v>
+        <v>0.3191484252677514</v>
       </c>
       <c r="AK155" t="n">
         <v>82.71868133544922</v>
@@ -30200,43 +30200,43 @@
         <v>38.79254150390625</v>
       </c>
       <c r="AM155" t="n">
-        <v>-0.2262932753913147</v>
+        <v>-0.2021149402472934</v>
       </c>
       <c r="AN155" t="n">
-        <v>0.6498016762721117</v>
+        <v>0.7013579786556152</v>
       </c>
       <c r="AO155" t="n">
-        <v>62.23021479078924</v>
+        <v>60.96654496506787</v>
       </c>
       <c r="AP155" t="n">
-        <v>13785063</v>
+        <v>18544579</v>
       </c>
       <c r="AQ155" t="n">
-        <v>56573201.22</v>
+        <v>52567096.6</v>
       </c>
       <c r="AR155" t="n">
-        <v>0.2436677208064133</v>
+        <v>0.3527792136041236</v>
       </c>
       <c r="AS155" t="n">
-        <v>-0.05337321937772033</v>
+        <v>0.05315896484812277</v>
       </c>
       <c r="AT155" t="n">
-        <v>0.3567669751788511</v>
+        <v>0.2905186897107908</v>
       </c>
       <c r="AU155" t="n">
-        <v>0.4332875880960323</v>
+        <v>0.5125280197685089</v>
       </c>
       <c r="AV155" t="n">
-        <v>0.5259712376725314</v>
+        <v>0.5574716492785121</v>
       </c>
       <c r="AW155" t="n">
-        <v>2.177017452067459</v>
+        <v>2.320744837818268</v>
       </c>
       <c r="AX155" t="n">
-        <v>0.4831549553861383</v>
+        <v>0.529503547741955</v>
       </c>
       <c r="AY155" t="n">
-        <v>7.421320619948188</v>
+        <v>7.684487979115874</v>
       </c>
       <c r="AZ155" t="inlineStr"/>
       <c r="BA155" t="n">
@@ -30343,7 +30343,7 @@
         </is>
       </c>
       <c r="X156" t="n">
-        <v>1221656444928</v>
+        <v>1285199101952</v>
       </c>
       <c r="Y156" t="inlineStr">
         <is>
@@ -30351,10 +30351,10 @@
         </is>
       </c>
       <c r="Z156" t="n">
-        <v>0.03102217987179756</v>
+        <v>0.0310616884380579</v>
       </c>
       <c r="AA156" t="n">
-        <v>37898445976.09717</v>
+        <v>39920454085.70483</v>
       </c>
       <c r="AB156" t="inlineStr">
         <is>
@@ -30368,22 +30368,22 @@
         <v>26.6</v>
       </c>
       <c r="AE156" t="n">
-        <v>298</v>
+        <v>313.5</v>
       </c>
       <c r="AF156" t="n">
-        <v>344.3856707763672</v>
+        <v>344.1532769775391</v>
       </c>
       <c r="AG156" t="n">
-        <v>296.8032266998291</v>
+        <v>296.9585179901123</v>
       </c>
       <c r="AH156" t="n">
-        <v>-0.1346910592179908</v>
+        <v>-0.08906867674411145</v>
       </c>
       <c r="AI156" t="n">
-        <v>0.004032211217775084</v>
+        <v>0.05570300566504871</v>
       </c>
       <c r="AJ156" t="n">
-        <v>0.1603164649037336</v>
+        <v>0.1589271097756428</v>
       </c>
       <c r="AK156" t="n">
         <v>399.9259948730469</v>
@@ -30392,43 +30392,43 @@
         <v>243.1204681396484</v>
       </c>
       <c r="AM156" t="n">
-        <v>-0.2548621399451727</v>
+        <v>-0.2161049693718511</v>
       </c>
       <c r="AN156" t="n">
-        <v>0.2257297885294822</v>
+        <v>0.2894841902818546</v>
       </c>
       <c r="AO156" t="n">
-        <v>41.66666666666667</v>
+        <v>45.45454545454546</v>
       </c>
       <c r="AP156" t="n">
-        <v>16833356</v>
+        <v>22725484</v>
       </c>
       <c r="AQ156" t="n">
-        <v>31717039.14</v>
+        <v>30455518.3</v>
       </c>
       <c r="AR156" t="n">
-        <v>0.530735417190017</v>
+        <v>0.7461860860860805</v>
       </c>
       <c r="AS156" t="n">
-        <v>-0.168079006758547</v>
+        <v>-0.1352268698058143</v>
       </c>
       <c r="AT156" t="n">
-        <v>-0.08611029272206094</v>
+        <v>-0.03998752974232156</v>
       </c>
       <c r="AU156" t="n">
-        <v>0.08265681584920781</v>
+        <v>0.1550679766053256</v>
       </c>
       <c r="AV156" t="n">
-        <v>0.1572533001436602</v>
+        <v>0.2017802144348142</v>
       </c>
       <c r="AW156" t="n">
-        <v>3.727005117362909</v>
+        <v>4.012839133234531</v>
       </c>
       <c r="AX156" t="n">
-        <v>0.1217418774533061</v>
+        <v>0.1800875120188303</v>
       </c>
       <c r="AY156" t="n">
-        <v>14.66554674762918</v>
+        <v>15.48036380185938</v>
       </c>
       <c r="AZ156" t="inlineStr"/>
       <c r="BA156" t="n">
@@ -30995,16 +30995,16 @@
         <v>0.3219917647284165</v>
       </c>
       <c r="AV159" t="n">
-        <v>0.5495733755640733</v>
+        <v>0.5495734829407382</v>
       </c>
       <c r="AW159" t="n">
-        <v>4.86413149155783</v>
+        <v>4.864131876001776</v>
       </c>
       <c r="AX159" t="n">
         <v>0.4202102124053861</v>
       </c>
       <c r="AY159" t="n">
-        <v>460.749971809701</v>
+        <v>460.7501580310887</v>
       </c>
       <c r="AZ159" t="inlineStr"/>
       <c r="BA159" t="n">
@@ -32476,7 +32476,7 @@
         <v>0.4185350617050061</v>
       </c>
       <c r="AW5" t="n">
-        <v>8.694404395003593</v>
+        <v>8.694403556891469</v>
       </c>
       <c r="AX5" t="n">
         <v>0.2350721494968062</v>
@@ -32878,13 +32878,13 @@
         <v>2.157571200020055</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.110391060249222</v>
+        <v>4.110390740271722</v>
       </c>
       <c r="AX7" t="n">
         <v>0.68562960324334</v>
       </c>
       <c r="AY7" t="n">
-        <v>1650.444517115374</v>
+        <v>1650.444256062105</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
@@ -33047,13 +33047,13 @@
         <v>316.3519592285156</v>
       </c>
       <c r="AL8" t="n">
-        <v>62.17752838134766</v>
+        <v>62.17753219604492</v>
       </c>
       <c r="AM8" t="n">
         <v>-0.3086181550634508</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.517669597273923</v>
+        <v>2.517669381458915</v>
       </c>
       <c r="AO8" t="n">
         <v>58.8034924611023</v>
@@ -33080,13 +33080,13 @@
         <v>1.889729579892497</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.678710067763018</v>
+        <v>2.678710539818181</v>
       </c>
       <c r="AX8" t="n">
         <v>1.450396679886195</v>
       </c>
       <c r="AY8" t="n">
-        <v>17.03236357506422</v>
+        <v>17.03236215725805</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
@@ -33507,10 +33507,10 @@
         <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>11995.80252626995</v>
+        <v>11989.36030614504</v>
       </c>
       <c r="D2" t="n">
-        <v>1499.475315783744</v>
+        <v>1498.67003826813</v>
       </c>
       <c r="E2" t="n">
         <v>407.253467136</v>
@@ -33522,7 +33522,7 @@
         <v>85</v>
       </c>
       <c r="H2" t="n">
-        <v>91.84558715425065</v>
+        <v>91.860012042436</v>
       </c>
       <c r="I2" t="n">
         <v>5</v>
@@ -33531,40 +33531,40 @@
         <v>0.625</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6690852410341646</v>
+        <v>0.6597038764904191</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4098150548057534</v>
+        <v>0.3722896619684397</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3330897518179773</v>
+        <v>0.3324550243556707</v>
       </c>
       <c r="N2" t="n">
-        <v>1.245017611931784</v>
+        <v>1.223022986183338</v>
       </c>
       <c r="O2" t="n">
         <v>0.7569965673307444</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6173477212351203</v>
+        <v>0.6152431147467662</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.568810270029648</v>
+        <v>4.34628480920354</v>
       </c>
       <c r="R2" t="n">
         <v>1.532000997437697</v>
       </c>
       <c r="S2" t="n">
-        <v>5.719360199586927</v>
+        <v>5.700716246071162</v>
       </c>
       <c r="T2" t="n">
-        <v>1298.271648648233</v>
+        <v>1298.210095991101</v>
       </c>
       <c r="U2" t="n">
-        <v>324.5932881027284</v>
+        <v>324.5933979758827</v>
       </c>
       <c r="V2" t="n">
-        <v>3953.340805346036</v>
+        <v>3955.456040790137</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -33582,10 +33582,10 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>1531.081906809492</v>
+        <v>1535.150432576199</v>
       </c>
       <c r="D3" t="n">
-        <v>102.0721271206328</v>
+        <v>102.3433621717466</v>
       </c>
       <c r="E3" t="n">
         <v>44.827049984</v>
@@ -33597,7 +33597,7 @@
         <v>90</v>
       </c>
       <c r="H3" t="n">
-        <v>89.06453093616649</v>
+        <v>89.01896477544285</v>
       </c>
       <c r="I3" t="n">
         <v>10</v>
@@ -33606,40 +33606,40 @@
         <v>0.625</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5131902043454265</v>
+        <v>0.5259362141222065</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2996716629798405</v>
+        <v>0.3241330569201628</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8743536465194296</v>
+        <v>0.8750863712899681</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7592982575128413</v>
+        <v>0.7619090342291015</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5645833578458648</v>
+        <v>0.5685324947030842</v>
       </c>
       <c r="P3" t="n">
-        <v>1.081038343886206</v>
+        <v>1.073136192036429</v>
       </c>
       <c r="Q3" t="n">
-        <v>6.902924605238539</v>
+        <v>6.964687329288858</v>
       </c>
       <c r="R3" t="n">
-        <v>4.944600709070524</v>
+        <v>4.944600901292497</v>
       </c>
       <c r="S3" t="n">
-        <v>5.999047774274203</v>
+        <v>6.005188327398943</v>
       </c>
       <c r="T3" t="n">
-        <v>253.9935131374394</v>
+        <v>254.8868795157027</v>
       </c>
       <c r="U3" t="n">
-        <v>38.81365800709766</v>
+        <v>39.8033700317921</v>
       </c>
       <c r="V3" t="n">
-        <v>850.8185798039475</v>
+        <v>850.4038101605739</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -33657,22 +33657,22 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>205.2596766268101</v>
+        <v>208.7699653026125</v>
       </c>
       <c r="D4" t="n">
-        <v>29.32281094668715</v>
+        <v>29.82428075751607</v>
       </c>
       <c r="E4" t="n">
         <v>13.731969024</v>
       </c>
       <c r="F4" t="n">
-        <v>76.42857142857143</v>
+        <v>81.42857142857143</v>
       </c>
       <c r="G4" t="n">
         <v>85</v>
       </c>
       <c r="H4" t="n">
-        <v>82.770177727671</v>
+        <v>86.17952486333053</v>
       </c>
       <c r="I4" t="n">
         <v>5</v>
@@ -33681,40 +33681,40 @@
         <v>0.7142857142857143</v>
       </c>
       <c r="K4" t="n">
-        <v>2.036208940780448</v>
+        <v>2.091355941222598</v>
       </c>
       <c r="L4" t="n">
-        <v>1.674591954577161</v>
+        <v>1.78235939597038</v>
       </c>
       <c r="M4" t="n">
-        <v>1.954670431167297</v>
+        <v>2.031195341023675</v>
       </c>
       <c r="N4" t="n">
-        <v>4.133038142605304</v>
+        <v>4.23342022897751</v>
       </c>
       <c r="O4" t="n">
-        <v>5.040586953107727</v>
+        <v>5.414077678506374</v>
       </c>
       <c r="P4" t="n">
-        <v>4.17088432132443</v>
+        <v>4.307527130219288</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.427269506216955</v>
+        <v>4.596621180396141</v>
       </c>
       <c r="R4" t="n">
-        <v>4.369887299668052</v>
+        <v>4.369886564181203</v>
       </c>
       <c r="S4" t="n">
-        <v>5.215348492133582</v>
+        <v>5.446390508617491</v>
       </c>
       <c r="T4" t="n">
-        <v>35.03326402098823</v>
+        <v>36.01402920509774</v>
       </c>
       <c r="U4" t="n">
-        <v>26.61098226599517</v>
+        <v>27.72349495583367</v>
       </c>
       <c r="V4" t="n">
-        <v>51.514590560554</v>
+        <v>53.44698576160119</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -33732,22 +33732,22 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>4180.246733686551</v>
+        <v>4197.891667975147</v>
       </c>
       <c r="D5" t="n">
-        <v>278.6831155791033</v>
+        <v>279.8594445316764</v>
       </c>
       <c r="E5" t="n">
         <v>59.301609472</v>
       </c>
       <c r="F5" t="n">
-        <v>70</v>
+        <v>70.33333333333333</v>
       </c>
       <c r="G5" t="n">
         <v>85</v>
       </c>
       <c r="H5" t="n">
-        <v>82.54682883604285</v>
+        <v>82.8667026453406</v>
       </c>
       <c r="I5" t="n">
         <v>9</v>
@@ -33756,40 +33756,40 @@
         <v>0.6</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5404605825711591</v>
+        <v>0.5606954563150012</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5031651206257604</v>
+        <v>0.5480769603117588</v>
       </c>
       <c r="M5" t="n">
-        <v>0.464349035296327</v>
+        <v>0.4714530222916855</v>
       </c>
       <c r="N5" t="n">
-        <v>1.322777454851159</v>
+        <v>1.376309166560543</v>
       </c>
       <c r="O5" t="n">
         <v>1.186115370620537</v>
       </c>
       <c r="P5" t="n">
-        <v>1.111375084761617</v>
+        <v>1.128694866673285</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.265107143214924</v>
+        <v>3.373736355180821</v>
       </c>
       <c r="R5" t="n">
-        <v>2.817075029363015</v>
+        <v>2.914814369722085</v>
       </c>
       <c r="S5" t="n">
-        <v>3.054147241227746</v>
+        <v>3.116929979072133</v>
       </c>
       <c r="T5" t="n">
-        <v>881.6762514615748</v>
+        <v>883.0888375214014</v>
       </c>
       <c r="U5" t="n">
-        <v>38.98858997386135</v>
+        <v>42.09516781176229</v>
       </c>
       <c r="V5" t="n">
-        <v>1241.142850314779</v>
+        <v>1236.264622318067</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -33807,22 +33807,22 @@
         <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>1504.922780162559</v>
+        <v>1519.860835951072</v>
       </c>
       <c r="D6" t="n">
-        <v>71.66298953155044</v>
+        <v>72.37432552147962</v>
       </c>
       <c r="E6" t="n">
-        <v>42.49044734966309</v>
+        <v>42.47080321496582</v>
       </c>
       <c r="F6" t="n">
-        <v>62.72727272727273</v>
+        <v>62.5</v>
       </c>
       <c r="G6" t="n">
         <v>60</v>
       </c>
       <c r="H6" t="n">
-        <v>70.98773551894804</v>
+        <v>70.86076438427855</v>
       </c>
       <c r="I6" t="n">
         <v>4</v>
@@ -33831,40 +33831,40 @@
         <v>0.1739130434782609</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4281622687125622</v>
+        <v>0.4425616161318481</v>
       </c>
       <c r="L6" t="n">
         <v>0.4605477310316053</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4581183650810024</v>
+        <v>0.4780279485316579</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7739903584707721</v>
+        <v>0.7908897020745584</v>
       </c>
       <c r="O6" t="n">
         <v>0.642135025809799</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6796364313312933</v>
+        <v>0.722597500927007</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.654275529237097</v>
+        <v>2.705037291531131</v>
       </c>
       <c r="R6" t="n">
-        <v>1.540364087847979</v>
+        <v>1.540364110510404</v>
       </c>
       <c r="S6" t="n">
-        <v>2.595441454008023</v>
+        <v>2.686482741287607</v>
       </c>
       <c r="T6" t="n">
-        <v>182.2233497004258</v>
+        <v>182.8194177038697</v>
       </c>
       <c r="U6" t="n">
-        <v>31.21679892900631</v>
+        <v>31.21679134026767</v>
       </c>
       <c r="V6" t="n">
-        <v>289.0557255167541</v>
+        <v>287.5936741814119</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -33875,150 +33875,150 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Memory / Storage</t>
+          <t>Networking / Interconnect / Custom Silicon</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>2815.795240397269</v>
+        <v>3602.436921809795</v>
       </c>
       <c r="D7" t="n">
-        <v>281.579524039727</v>
+        <v>189.6019432531471</v>
       </c>
       <c r="E7" t="n">
-        <v>171.282805446418</v>
+        <v>62.630395904</v>
       </c>
       <c r="F7" t="n">
-        <v>74.16666666666667</v>
+        <v>71.19047619047619</v>
       </c>
       <c r="G7" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="H7" t="n">
-        <v>68.53491842537272</v>
+        <v>67.69240069331937</v>
       </c>
       <c r="I7" t="n">
         <v>7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K7" t="n">
-        <v>1.414841025646756</v>
+        <v>0.604470051593196</v>
       </c>
       <c r="L7" t="n">
-        <v>1.159747998174404</v>
+        <v>0.4377879151449628</v>
       </c>
       <c r="M7" t="n">
-        <v>1.238789606623576</v>
+        <v>0.4161560510481742</v>
       </c>
       <c r="N7" t="n">
-        <v>7.653640350642939</v>
+        <v>1.591512516211977</v>
       </c>
       <c r="O7" t="n">
-        <v>4.691632877778304</v>
+        <v>1.114542643229167</v>
       </c>
       <c r="P7" t="n">
-        <v>5.796777085402929</v>
+        <v>0.9636046388772789</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.945128572488658</v>
+        <v>6.081456948572685</v>
       </c>
       <c r="R7" t="n">
-        <v>4.658645737931193</v>
+        <v>3.586805946455038</v>
       </c>
       <c r="S7" t="n">
-        <v>5.564450030622821</v>
+        <v>8.157516212902117</v>
       </c>
       <c r="T7" t="n">
-        <v>284.5139219351889</v>
+        <v>196.204376357745</v>
       </c>
       <c r="U7" t="n">
-        <v>42.88882335986975</v>
+        <v>26.32769413807257</v>
       </c>
       <c r="V7" t="n">
-        <v>263.2251574579711</v>
+        <v>343.3337570486651</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Moderate breadth</t>
+          <t>Narrow momentum</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Networking / Interconnect / Custom Silicon</t>
+          <t>Memory / Storage</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>3619.241510111935</v>
+        <v>2813.726181714421</v>
       </c>
       <c r="D8" t="n">
-        <v>190.4863952690492</v>
+        <v>281.3726181714421</v>
       </c>
       <c r="E8" t="n">
-        <v>62.630395904</v>
+        <v>171.4230885716406</v>
       </c>
       <c r="F8" t="n">
-        <v>71.19047619047619</v>
+        <v>72.08333333333333</v>
       </c>
       <c r="G8" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="H8" t="n">
-        <v>67.67989954216127</v>
+        <v>66.93630586491574</v>
       </c>
       <c r="I8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6239387755343552</v>
+        <v>1.448934913389941</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4770550103675077</v>
+        <v>1.208610119526813</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4240010931795615</v>
+        <v>1.24282150318605</v>
       </c>
       <c r="N8" t="n">
-        <v>1.660589776386783</v>
+        <v>7.82690347611149</v>
       </c>
       <c r="O8" t="n">
-        <v>1.114542643229167</v>
+        <v>4.691632877778304</v>
       </c>
       <c r="P8" t="n">
-        <v>1.004638778333778</v>
+        <v>5.787141110311561</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.202146542561576</v>
+        <v>6.089278224365655</v>
       </c>
       <c r="R8" t="n">
-        <v>3.586805946455038</v>
+        <v>5.338632097626797</v>
       </c>
       <c r="S8" t="n">
-        <v>8.293245497254979</v>
+        <v>5.611564542898722</v>
       </c>
       <c r="T8" t="n">
-        <v>197.5261041740687</v>
+        <v>284.5490905403739</v>
       </c>
       <c r="U8" t="n">
-        <v>26.32768796510136</v>
+        <v>42.7717157308351</v>
       </c>
       <c r="V8" t="n">
-        <v>343.4134653095337</v>
+        <v>263.2324399996129</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Narrow momentum</t>
+          <t>Moderate breadth</t>
         </is>
       </c>
     </row>
@@ -34074,13 +34074,13 @@
         <v>0.5097264054326101</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.708089235290239</v>
+        <v>1.708089166124536</v>
       </c>
       <c r="R9" t="n">
         <v>0.6637111084063636</v>
       </c>
       <c r="S9" t="n">
-        <v>6.515366071367915</v>
+        <v>6.515365523495047</v>
       </c>
       <c r="T9" t="n">
         <v>61.50048797635068</v>
@@ -34107,10 +34107,10 @@
         <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>13975.57245414483</v>
+        <v>13975.33146985199</v>
       </c>
       <c r="D10" t="n">
-        <v>1164.631037845403</v>
+        <v>1164.610955820999</v>
       </c>
       <c r="E10" t="n">
         <v>365.634699264</v>
@@ -34122,7 +34122,7 @@
         <v>42.5</v>
       </c>
       <c r="H10" t="n">
-        <v>62.42398186909679</v>
+        <v>62.42602779228921</v>
       </c>
       <c r="I10" t="n">
         <v>4</v>
@@ -34131,40 +34131,40 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5546118825779528</v>
+        <v>0.5561227081877103</v>
       </c>
       <c r="L10" t="n">
         <v>0.09379666984393364</v>
       </c>
       <c r="M10" t="n">
-        <v>0.08119481087028246</v>
+        <v>0.08126703246814462</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5756916265609037</v>
+        <v>0.5774481460421143</v>
       </c>
       <c r="O10" t="n">
         <v>0.1507375961902657</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2638989951017127</v>
+        <v>0.2639143680450011</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6104968860458077</v>
+        <v>0.6114379392560669</v>
       </c>
       <c r="R10" t="n">
         <v>0.672455481112939</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9744815619874879</v>
+        <v>0.9740178774467929</v>
       </c>
       <c r="T10" t="n">
-        <v>1253.332106421999</v>
+        <v>1253.263215026043</v>
       </c>
       <c r="U10" t="n">
-        <v>11.51117295827163</v>
+        <v>11.5111721719307</v>
       </c>
       <c r="V10" t="n">
-        <v>3000.719761484623</v>
+        <v>3000.711845822318</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -34224,22 +34224,22 @@
         <v>1.129456205977184</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4177838758235302</v>
+        <v>0.4177837391396646</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4177838758235302</v>
+        <v>0.4177837391396646</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4177838758235302</v>
+        <v>0.4177837391396647</v>
       </c>
       <c r="T11" t="n">
-        <v>12.29820481571351</v>
+        <v>12.29821039494933</v>
       </c>
       <c r="U11" t="n">
-        <v>12.29820481571351</v>
+        <v>12.29821039494933</v>
       </c>
       <c r="V11" t="n">
-        <v>22.78286918389555</v>
+        <v>22.78287951042256</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -34257,10 +34257,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>1223.87618701809</v>
+        <v>1223.806355820676</v>
       </c>
       <c r="D12" t="n">
-        <v>67.99312150100498</v>
+        <v>67.98924199003754</v>
       </c>
       <c r="E12" t="n">
         <v>47.19718195199999</v>
@@ -34272,7 +34272,7 @@
         <v>25</v>
       </c>
       <c r="H12" t="n">
-        <v>52.91723650523819</v>
+        <v>52.91683235808412</v>
       </c>
       <c r="I12" t="n">
         <v>3</v>
@@ -34281,40 +34281,40 @@
         <v>0.1578947368421053</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.01813707203486782</v>
+        <v>-0.01813707149355027</v>
       </c>
       <c r="L12" t="n">
         <v>0.01756100538300309</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1314495280530239</v>
+        <v>0.1314424431317191</v>
       </c>
       <c r="N12" t="n">
-        <v>0.07385201062854692</v>
+        <v>0.07385199943297877</v>
       </c>
       <c r="O12" t="n">
         <v>0.03767399850915143</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2093651956390273</v>
+        <v>0.2093457861336127</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.607296860316745</v>
+        <v>2.607296745088373</v>
       </c>
       <c r="R12" t="n">
         <v>1.836839349277011</v>
       </c>
       <c r="S12" t="n">
-        <v>2.076070720572219</v>
+        <v>2.075807535119521</v>
       </c>
       <c r="T12" t="n">
-        <v>75.22924094800294</v>
+        <v>75.22924127325932</v>
       </c>
       <c r="U12" t="n">
         <v>11.40029507829921</v>
       </c>
       <c r="V12" t="n">
-        <v>106.3656612396362</v>
+        <v>106.3713911591445</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -34332,10 +34332,10 @@
         <v>4</v>
       </c>
       <c r="C13" t="n">
-        <v>193.3435581196372</v>
+        <v>193.3341888771733</v>
       </c>
       <c r="D13" t="n">
-        <v>64.44785270654573</v>
+        <v>64.44472962572445</v>
       </c>
       <c r="E13" t="n">
         <v>79.65348659199999</v>
@@ -34347,7 +34347,7 @@
         <v>60</v>
       </c>
       <c r="H13" t="n">
-        <v>35.2812597326738</v>
+        <v>35.28006182829738</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
@@ -34362,7 +34362,7 @@
         <v>0.13904935248353</v>
       </c>
       <c r="M13" t="n">
-        <v>0.04145247669697699</v>
+        <v>0.04143053249318732</v>
       </c>
       <c r="N13" t="n">
         <v>0.1712573840399493</v>
@@ -34371,25 +34371,25 @@
         <v>0.1052102297158676</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.07201181932479093</v>
+        <v>-0.07205427276956758</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.328024379521858</v>
+        <v>1.328024344974325</v>
       </c>
       <c r="R13" t="n">
-        <v>1.277214139782041</v>
+        <v>1.277214070686975</v>
       </c>
       <c r="S13" t="n">
-        <v>1.055875327381544</v>
+        <v>1.055814487722448</v>
       </c>
       <c r="T13" t="n">
-        <v>88.2530439176883</v>
+        <v>88.25304168013935</v>
       </c>
       <c r="U13" t="n">
-        <v>77.97945033390954</v>
+        <v>77.97944438242618</v>
       </c>
       <c r="V13" t="n">
-        <v>113.7433792982093</v>
+        <v>113.7438436973593</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -34407,22 +34407,22 @@
         <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>2144.746729686995</v>
+        <v>2141.361425999839</v>
       </c>
       <c r="D14" t="n">
-        <v>214.4746729686995</v>
+        <v>214.1361425999839</v>
       </c>
       <c r="E14" t="n">
-        <v>52.96600534992383</v>
+        <v>51.0583450746211</v>
       </c>
       <c r="F14" t="n">
-        <v>52.5</v>
+        <v>52</v>
       </c>
       <c r="G14" t="n">
         <v>65</v>
       </c>
       <c r="H14" t="n">
-        <v>13.79044242761822</v>
+        <v>13.45914411889167</v>
       </c>
       <c r="I14" t="n">
         <v>2</v>
@@ -34431,40 +34431,40 @@
         <v>0.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1111696660435561</v>
+        <v>0.1073330761483029</v>
       </c>
       <c r="L14" t="n">
-        <v>0.07314476361260724</v>
+        <v>0.04511271413882456</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.1021279914906521</v>
+        <v>-0.1038301542093102</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2356282609075933</v>
+        <v>0.230848360151973</v>
       </c>
       <c r="O14" t="n">
-        <v>0.164485622621221</v>
+        <v>0.1644855158548426</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2436573859388654</v>
+        <v>0.2349857724226421</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5607151469610445</v>
+        <v>0.552718145108936</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4450516650075427</v>
+        <v>0.4450515781319568</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7210136368504568</v>
+        <v>0.7051611796540457</v>
       </c>
       <c r="T14" t="n">
-        <v>16.60596739239092</v>
+        <v>16.59155140246869</v>
       </c>
       <c r="U14" t="n">
-        <v>3.298458050732048</v>
+        <v>3.18307539774661</v>
       </c>
       <c r="V14" t="n">
-        <v>3.188727070882999</v>
+        <v>3.181495288646583</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>

--- a/company_radar_output.xlsx
+++ b/company_radar_output.xlsx
@@ -828,16 +828,16 @@
         <v>24.05020751953125</v>
       </c>
       <c r="AG2" t="n">
-        <v>13.95483158588409</v>
+        <v>13.95483160018921</v>
       </c>
       <c r="AH2" t="n">
         <v>0.3970772787234551</v>
       </c>
       <c r="AI2" t="n">
-        <v>1.407768110086611</v>
+        <v>1.407768107618405</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.723432301673856</v>
+        <v>0.7234322999071634</v>
       </c>
       <c r="AK2" t="n">
         <v>34.90000152587891</v>
@@ -876,13 +876,13 @@
         <v>2.111786875314704</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.648432107581607</v>
+        <v>3.648432720882887</v>
       </c>
       <c r="AX2" t="n">
         <v>2.566089581824358</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.637906113874107</v>
+        <v>4.637904760594109</v>
       </c>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
@@ -1214,16 +1214,16 @@
         <v>412.7755975341797</v>
       </c>
       <c r="AG4" t="n">
-        <v>431.3164932250976</v>
+        <v>431.3164930725098</v>
       </c>
       <c r="AH4" t="n">
         <v>0.2001678317610891</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.1485765132518189</v>
+        <v>0.1485765136581534</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.04298675330563295</v>
+        <v>-0.04298675296706811</v>
       </c>
       <c r="AK4" t="n">
         <v>538.6585083007812</v>
@@ -1262,13 +1262,13 @@
         <v>-0.04425616410192645</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.7903259799896616</v>
+        <v>0.7903255850886959</v>
       </c>
       <c r="AX4" t="n">
         <v>0.05215492796166088</v>
       </c>
       <c r="AY4" t="n">
-        <v>8377.807216503354</v>
+        <v>8377.811439869425</v>
       </c>
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
@@ -1606,16 +1606,16 @@
         <v>353.8855554199219</v>
       </c>
       <c r="AG6" t="n">
-        <v>331.1040270996094</v>
+        <v>331.1040278625488</v>
       </c>
       <c r="AH6" t="n">
         <v>-0.02256537855567975</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.04468676182070053</v>
+        <v>0.0446867594135032</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.06880474550513083</v>
+        <v>0.06880474304235995</v>
       </c>
       <c r="AK6" t="n">
         <v>402.3796691894531</v>
@@ -1651,10 +1651,10 @@
         <v>0.1329001750158174</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.709306929558289</v>
+        <v>0.7093070584454491</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.548824324540082</v>
+        <v>1.548824611122386</v>
       </c>
       <c r="AX6" t="n">
         <v>0.09900119368848959</v>
@@ -2430,7 +2430,7 @@
         <v>-0.2855113909482543</v>
       </c>
       <c r="AY10" t="n">
-        <v>624.6300744156522</v>
+        <v>624.6301274384572</v>
       </c>
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="n">
@@ -2616,7 +2616,7 @@
         <v>0.02181111407470326</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0.3261692345803724</v>
+        <v>-0.3261691786218727</v>
       </c>
       <c r="AX11" t="n">
         <v>-0.1977201601828333</v>
@@ -2764,16 +2764,16 @@
         <v>597.0579211425782</v>
       </c>
       <c r="AG12" t="n">
-        <v>626.8258279418945</v>
+        <v>626.825827331543</v>
       </c>
       <c r="AH12" t="n">
         <v>-0.01207243937547453</v>
       </c>
       <c r="AI12" t="n">
-        <v>-0.05898903763643992</v>
+        <v>-0.05898903672016065</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0.04748991740984199</v>
+        <v>-0.04748991648236578</v>
       </c>
       <c r="AK12" t="n">
         <v>782.664794921875</v>
@@ -2818,7 +2818,7 @@
         <v>-0.09149286621668584</v>
       </c>
       <c r="AY12" t="n">
-        <v>14.56447157765469</v>
+        <v>14.56447471106564</v>
       </c>
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="n">
@@ -2960,16 +2960,16 @@
         <v>152.0817073059082</v>
       </c>
       <c r="AG13" t="n">
-        <v>175.0893964004516</v>
+        <v>175.0893976211548</v>
       </c>
       <c r="AH13" t="n">
         <v>-0.01026884206596879</v>
       </c>
       <c r="AI13" t="n">
-        <v>-0.1403248433834188</v>
+        <v>-0.1403248493769751</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.1314053824363067</v>
+        <v>-0.1314053884920484</v>
       </c>
       <c r="AK13" t="n">
         <v>324.6299743652344</v>
@@ -3149,19 +3149,19 @@
         <v>49.13999938964844</v>
       </c>
       <c r="AF14" t="n">
-        <v>44.11459999084472</v>
+        <v>44.20160003662109</v>
       </c>
       <c r="AG14" t="n">
-        <v>41.27699998855591</v>
+        <v>41.38814998626709</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.113916920925196</v>
+        <v>0.1117244477334729</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.1904934807101426</v>
+        <v>0.1872963494612219</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.06874530617718211</v>
+        <v>0.06797718794600716</v>
       </c>
       <c r="AK14" t="n">
         <v>50.95000076293945</v>
@@ -3176,31 +3176,31 @@
         <v>0.5185413616441392</v>
       </c>
       <c r="AO14" t="n">
-        <v>68.46048384288645</v>
+        <v>72.40762602878027</v>
       </c>
       <c r="AP14" t="n">
         <v>5857000</v>
       </c>
       <c r="AQ14" t="n">
-        <v>5496132</v>
+        <v>5596552</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.065658539496504</v>
+        <v>1.04653722506286</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.1065075334043704</v>
+        <v>0.09103015965320815</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.281021861516547</v>
+        <v>0.2532517351959875</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.3209676984362921</v>
+        <v>0.3353260980549293</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.03627164249511772</v>
+        <v>0.06733271964544185</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0.2458564053423556</v>
+        <v>-0.2493125561117733</v>
       </c>
       <c r="AX14" t="n">
         <v>0.1603306059072593</v>
@@ -4710,16 +4710,16 @@
         <v>390.3288507080078</v>
       </c>
       <c r="AG22" t="n">
-        <v>368.2457229614258</v>
+        <v>368.2457228088379</v>
       </c>
       <c r="AH22" t="n">
         <v>0.006817685962849707</v>
       </c>
       <c r="AI22" t="n">
-        <v>0.06719498891652087</v>
+        <v>0.06719498935872825</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.05996845684721031</v>
+        <v>0.05996845728642342</v>
       </c>
       <c r="AK22" t="n">
         <v>480.8090515136719</v>
@@ -4755,16 +4755,16 @@
         <v>0.2130197017444788</v>
       </c>
       <c r="AV22" t="n">
-        <v>0.2719514541587664</v>
+        <v>0.2719513285240669</v>
       </c>
       <c r="AW22" t="n">
-        <v>7.90640422707655</v>
+        <v>7.906403457089615</v>
       </c>
       <c r="AX22" t="n">
         <v>0.1346806173757082</v>
       </c>
       <c r="AY22" t="n">
-        <v>345.0662981117114</v>
+        <v>345.0664070971853</v>
       </c>
       <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="n">
@@ -4906,16 +4906,16 @@
         <v>250.7141088867187</v>
       </c>
       <c r="AG23" t="n">
-        <v>264.0149974822998</v>
+        <v>264.0149976348877</v>
       </c>
       <c r="AH23" t="n">
         <v>-0.06538962500075107</v>
       </c>
       <c r="AI23" t="n">
-        <v>-0.1124746337945134</v>
+        <v>-0.1124746343074602</v>
       </c>
       <c r="AJ23" t="n">
-        <v>-0.05037929179183387</v>
+        <v>-0.05037929234066874</v>
       </c>
       <c r="AK23" t="n">
         <v>326.8851013183594</v>
@@ -4954,13 +4954,13 @@
         <v>0.01392432936372878</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.101073160159804</v>
+        <v>1.101073591365407</v>
       </c>
       <c r="AX23" t="n">
         <v>-0.179782753790763</v>
       </c>
       <c r="AY23" t="n">
-        <v>162.3519175675688</v>
+        <v>162.3520940465642</v>
       </c>
       <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="n">
@@ -5102,28 +5102,28 @@
         <v>308.9506811523437</v>
       </c>
       <c r="AG24" t="n">
-        <v>279.9858080291748</v>
+        <v>279.9858097076416</v>
       </c>
       <c r="AH24" t="n">
         <v>-0.009777251389431307</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.09266249896460121</v>
+        <v>0.09266249241427738</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.103451218928035</v>
+        <v>0.1034512123130347</v>
       </c>
       <c r="AK24" t="n">
         <v>339.7869262695312</v>
       </c>
       <c r="AL24" t="n">
-        <v>224.072265625</v>
+        <v>224.0722808837891</v>
       </c>
       <c r="AM24" t="n">
         <v>-0.09964166062967783</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.3653184244933536</v>
+        <v>0.3653183315184183</v>
       </c>
       <c r="AO24" t="n">
         <v>26.09353010535925</v>
@@ -5150,7 +5150,7 @@
         <v>0.319099981025472</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.146997838484401</v>
+        <v>1.146998298308064</v>
       </c>
       <c r="AX24" t="n">
         <v>0.1319238738306412</v>
@@ -5291,19 +5291,19 @@
         <v>315.7799987792969</v>
       </c>
       <c r="AF25" t="n">
-        <v>263.0145993041992</v>
+        <v>262.8749990844727</v>
       </c>
       <c r="AG25" t="n">
-        <v>217.7109499359131</v>
+        <v>217.4749499511719</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.200617758917899</v>
+        <v>0.201255349040719</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.450455288869265</v>
+        <v>0.452029297398145</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.2080908166613671</v>
+        <v>0.2087599015127681</v>
       </c>
       <c r="AK25" t="n">
         <v>330.8299865722656</v>
@@ -5324,25 +5324,25 @@
         <v>3023000</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3676410</v>
+        <v>3680204</v>
       </c>
       <c r="AR25" t="n">
-        <v>0.8222695510022006</v>
+        <v>0.8214218559623325</v>
       </c>
       <c r="AS25" t="n">
-        <v>0.1372901916531579</v>
+        <v>0.1589958477678406</v>
       </c>
       <c r="AT25" t="n">
-        <v>0.5984004995021353</v>
+        <v>0.5804013945132811</v>
       </c>
       <c r="AU25" t="n">
-        <v>0.6123563387197077</v>
+        <v>0.7053518491218307</v>
       </c>
       <c r="AV25" t="n">
-        <v>0.6162349825341615</v>
+        <v>0.5841276441283514</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.558373150761916</v>
+        <v>1.657633391603621</v>
       </c>
       <c r="AX25" t="n">
         <v>0.610958024163563</v>
@@ -5490,16 +5490,16 @@
         <v>206.5195993041992</v>
       </c>
       <c r="AG26" t="n">
-        <v>194.7469945526123</v>
+        <v>194.7469943237305</v>
       </c>
       <c r="AH26" t="n">
         <v>0.09025973525376263</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.1561667700154457</v>
+        <v>0.1561667713742629</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0.06045076474033317</v>
+        <v>0.06045076598665755</v>
       </c>
       <c r="AK26" t="n">
         <v>235.465576171875</v>
@@ -5532,19 +5532,19 @@
         <v>0.0004545275185088293</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.2331634804557765</v>
+        <v>0.2331635835110377</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.2386545952550136</v>
+        <v>0.2386544912799433</v>
       </c>
       <c r="AW26" t="n">
-        <v>10.13273336302724</v>
+        <v>10.1327323131406</v>
       </c>
       <c r="AX26" t="n">
         <v>0.1937231689913366</v>
       </c>
       <c r="AY26" t="n">
-        <v>5993.824361584319</v>
+        <v>5993.823766988628</v>
       </c>
       <c r="AZ26" t="inlineStr"/>
       <c r="BA26" t="n">
@@ -6312,13 +6312,13 @@
         <v>3.295892597568954</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.058920754213852</v>
+        <v>1.05892138528104</v>
       </c>
       <c r="AX30" t="n">
         <v>1.602844012693313</v>
       </c>
       <c r="AY30" t="n">
-        <v>563.7390716867531</v>
+        <v>563.7393035127313</v>
       </c>
       <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="n">
@@ -6460,16 +6460,16 @@
         <v>183.8708001708984</v>
       </c>
       <c r="AG31" t="n">
-        <v>167.6666438293457</v>
+        <v>167.6666441345215</v>
       </c>
       <c r="AH31" t="n">
         <v>-0.09833430249914854</v>
       </c>
       <c r="AI31" t="n">
-        <v>-0.01119274830313288</v>
+        <v>-0.01119275010289467</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.09664508080716172</v>
+        <v>0.09664507881112061</v>
       </c>
       <c r="AK31" t="n">
         <v>250.0962829589844</v>
@@ -6508,13 +6508,13 @@
         <v>0.0708100536498335</v>
       </c>
       <c r="AW31" t="n">
-        <v>0.2570614170929002</v>
+        <v>0.2570608353453818</v>
       </c>
       <c r="AX31" t="n">
         <v>-0.03184926264269583</v>
       </c>
       <c r="AY31" t="n">
-        <v>490.4002191916057</v>
+        <v>490.4003060061638</v>
       </c>
       <c r="AZ31" t="inlineStr"/>
       <c r="BA31" t="n">
@@ -6697,16 +6697,16 @@
         <v>0.08005432882520447</v>
       </c>
       <c r="AV32" t="n">
-        <v>0.2939610458131272</v>
+        <v>0.2939609684086177</v>
       </c>
       <c r="AW32" t="n">
-        <v>2.222532815874228</v>
+        <v>2.2225325758315</v>
       </c>
       <c r="AX32" t="n">
         <v>0.1407784747187895</v>
       </c>
       <c r="AY32" t="n">
-        <v>3.527352251565429</v>
+        <v>3.527353199138147</v>
       </c>
       <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="n">
@@ -6892,13 +6892,13 @@
         <v>6.571026451644251</v>
       </c>
       <c r="AW33" t="n">
-        <v>7.835668721110011</v>
+        <v>7.835669305050756</v>
       </c>
       <c r="AX33" t="n">
         <v>3.667071375485188</v>
       </c>
       <c r="AY33" t="n">
-        <v>139.1199724777036</v>
+        <v>139.1199541207782</v>
       </c>
       <c r="AZ33" t="inlineStr"/>
       <c r="BA33" t="n">
@@ -7084,13 +7084,13 @@
         <v>7.507149422877912</v>
       </c>
       <c r="AW34" t="n">
-        <v>6.963264017321485</v>
+        <v>6.963264578582747</v>
       </c>
       <c r="AX34" t="n">
         <v>4.535100425782744</v>
       </c>
       <c r="AY34" t="n">
-        <v>36.72120249786307</v>
+        <v>36.72121194315179</v>
       </c>
       <c r="AZ34" t="inlineStr"/>
       <c r="BA34" t="n">
@@ -7282,7 +7282,7 @@
         <v>1.909021129036435</v>
       </c>
       <c r="AY35" t="n">
-        <v>29.03108919779569</v>
+        <v>29.03108125280598</v>
       </c>
       <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="n">
@@ -7472,7 +7472,7 @@
         <v>3.017883058889199</v>
       </c>
       <c r="AW36" t="n">
-        <v>4.472610381430976</v>
+        <v>4.472610020252013</v>
       </c>
       <c r="AX36" t="n">
         <v>1.368787379477253</v>
@@ -7610,22 +7610,22 @@
         <v>18.8</v>
       </c>
       <c r="AE37" t="n">
-        <v>167.8000030517578</v>
+        <v>173.1999969482422</v>
       </c>
       <c r="AF37" t="n">
-        <v>172.6900006103516</v>
+        <v>173.1740005493164</v>
       </c>
       <c r="AG37" t="n">
-        <v>86.25950019836426</v>
+        <v>85.82650019645691</v>
       </c>
       <c r="AH37" t="n">
-        <v>-0.02831662251034028</v>
+        <v>0.0001501172164604103</v>
       </c>
       <c r="AI37" t="n">
-        <v>0.9452930131276114</v>
+        <v>1.018024695773302</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.001982392817369</v>
+        <v>1.017721800992946</v>
       </c>
       <c r="AK37" t="n">
         <v>239</v>
@@ -7634,43 +7634,43 @@
         <v>18.39999961853027</v>
       </c>
       <c r="AM37" t="n">
-        <v>-0.2979079370219339</v>
+        <v>-0.2753138203002419</v>
       </c>
       <c r="AN37" t="n">
-        <v>8.119565572315</v>
+        <v>8.413043507556159</v>
       </c>
       <c r="AO37" t="n">
-        <v>54.15162420072088</v>
+        <v>56.69724444429512</v>
       </c>
       <c r="AP37" t="n">
         <v>122218</v>
       </c>
       <c r="AQ37" t="n">
-        <v>167476.12</v>
+        <v>168663.76</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.7297637418397321</v>
+        <v>0.7246251358323803</v>
       </c>
       <c r="AS37" t="n">
-        <v>-0.03894617877462314</v>
+        <v>-0.03777779473198783</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.6196911730039614</v>
+        <v>0.6526716784798519</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.29666007900695</v>
+        <v>2.589637242450615</v>
       </c>
       <c r="AV37" t="n">
-        <v>7.028708426529523</v>
+        <v>7.287081344952767</v>
       </c>
       <c r="AW37" t="n">
-        <v>3.797834353193094</v>
+        <v>3.938534990209585</v>
       </c>
       <c r="AX37" t="n">
-        <v>4.115853870574529</v>
+        <v>4.280487834662643</v>
       </c>
       <c r="AY37" t="n">
-        <v>13.62322350093743</v>
+        <v>14.09381788238177</v>
       </c>
       <c r="AZ37" t="inlineStr"/>
       <c r="BA37" t="n">
@@ -7860,13 +7860,13 @@
         <v>1.426537185445178</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.298852155287945</v>
+        <v>1.298852497034242</v>
       </c>
       <c r="AX38" t="n">
         <v>0.3786007588427647</v>
       </c>
       <c r="AY38" t="n">
-        <v>3.769424423681537</v>
+        <v>3.76942405593077</v>
       </c>
       <c r="AZ38" t="inlineStr"/>
       <c r="BA38" t="n">
@@ -8058,7 +8058,7 @@
         <v>0.06837380610343935</v>
       </c>
       <c r="AY39" t="n">
-        <v>3.397555798263157</v>
+        <v>3.39755538807095</v>
       </c>
       <c r="AZ39" t="inlineStr"/>
       <c r="BA39" t="n">
@@ -8200,16 +8200,16 @@
         <v>185.8988687133789</v>
       </c>
       <c r="AG40" t="n">
-        <v>175.4987673187256</v>
+        <v>175.4987676239014</v>
       </c>
       <c r="AH40" t="n">
         <v>0.07666063425634939</v>
       </c>
       <c r="AI40" t="n">
-        <v>0.1404638160961518</v>
+        <v>0.1404638141129928</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0.05926025324021533</v>
+        <v>0.05926025139826185</v>
       </c>
       <c r="AK40" t="n">
         <v>202.5594635009766</v>
@@ -8242,13 +8242,13 @@
         <v>0.06882641303018389</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.1209389237096712</v>
+        <v>0.1209390195014914</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.2388891486233835</v>
+        <v>0.2388892656351207</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.5056914708977607</v>
+        <v>0.5056916437346808</v>
       </c>
       <c r="AX40" t="n">
         <v>0.3084973124342674</v>
@@ -8396,16 +8396,16 @@
         <v>1051.222001953125</v>
       </c>
       <c r="AG41" t="n">
-        <v>937.5152493286133</v>
+        <v>937.5152502441406</v>
       </c>
       <c r="AH41" t="n">
         <v>0.04839888580935647</v>
       </c>
       <c r="AI41" t="n">
-        <v>0.1755541857854461</v>
+        <v>0.1755541846374626</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0.1212852299799294</v>
+        <v>0.1212852288849422</v>
       </c>
       <c r="AK41" t="n">
         <v>1115.93994140625</v>
@@ -8441,16 +8441,16 @@
         <v>0.1646089237077826</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.4537132237477639</v>
+        <v>0.4537133407829865</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.4919914800975602</v>
+        <v>0.4919916033773228</v>
       </c>
       <c r="AX41" t="n">
         <v>0.4573653308780266</v>
       </c>
       <c r="AY41" t="n">
-        <v>2.56784596666754</v>
+        <v>2.567846319153081</v>
       </c>
       <c r="AZ41" t="inlineStr"/>
       <c r="BA41" t="n">
@@ -8592,28 +8592,28 @@
         <v>124.6162466430664</v>
       </c>
       <c r="AG42" t="n">
-        <v>106.9696457290649</v>
+        <v>106.9696458816528</v>
       </c>
       <c r="AH42" t="n">
         <v>0.03862855897516049</v>
       </c>
       <c r="AI42" t="n">
-        <v>0.2099693496564845</v>
+        <v>0.2099693479305118</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0.1649683028650686</v>
+        <v>0.1649683012032881</v>
       </c>
       <c r="AK42" t="n">
         <v>133.0599975585938</v>
       </c>
       <c r="AL42" t="n">
-        <v>77.69110870361328</v>
+        <v>77.69111633300781</v>
       </c>
       <c r="AM42" t="n">
         <v>-0.02728096309496775</v>
       </c>
       <c r="AN42" t="n">
-        <v>0.6659563087141487</v>
+        <v>0.6659561451145177</v>
       </c>
       <c r="AO42" t="n">
         <v>53.87055243190725</v>
@@ -8634,16 +8634,16 @@
         <v>0.04193550368324006</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.1961878292889969</v>
+        <v>0.1961877449450589</v>
       </c>
       <c r="AV42" t="n">
         <v>0.46433289254258</v>
       </c>
       <c r="AW42" t="n">
-        <v>2.471098033494694</v>
+        <v>2.471098388601466</v>
       </c>
       <c r="AX42" t="n">
-        <v>0.5782953052252939</v>
+        <v>0.5782954520610137</v>
       </c>
       <c r="AY42" t="n">
         <v>111.3360035277482</v>
@@ -8838,7 +8838,7 @@
         <v>0.03735182087828348</v>
       </c>
       <c r="AY43" t="n">
-        <v>0.7689005532217212</v>
+        <v>0.7689008466753149</v>
       </c>
       <c r="AZ43" t="inlineStr"/>
       <c r="BA43" t="n">
@@ -9216,13 +9216,13 @@
         <v>-0.0001311130227846791</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.07889821176478296</v>
+        <v>0.07889833791221168</v>
       </c>
       <c r="AX45" t="n">
-        <v>0.03111479667834094</v>
+        <v>0.03111468145740592</v>
       </c>
       <c r="AY45" t="n">
-        <v>3.041187182375416</v>
+        <v>3.041187624836822</v>
       </c>
       <c r="AZ45" t="inlineStr"/>
       <c r="BA45" t="n">
@@ -9547,19 +9547,19 @@
         <v>34.40999984741211</v>
       </c>
       <c r="AF47" t="n">
-        <v>32.29559989929199</v>
+        <v>32.42679985046387</v>
       </c>
       <c r="AG47" t="n">
-        <v>37.83809998512268</v>
+        <v>37.86459998130798</v>
       </c>
       <c r="AH47" t="n">
-        <v>0.06547021745109216</v>
+        <v>0.06115928818427241</v>
       </c>
       <c r="AI47" t="n">
-        <v>-0.09059916166663884</v>
+        <v>-0.09123561679249881</v>
       </c>
       <c r="AJ47" t="n">
-        <v>-0.1464793445762316</v>
+        <v>-0.1436117147290216</v>
       </c>
       <c r="AK47" t="n">
         <v>47.52000045776367</v>
@@ -9574,31 +9574,31 @@
         <v>0.185733952606002</v>
       </c>
       <c r="AO47" t="n">
-        <v>63.08088979612874</v>
+        <v>61.77966659215075</v>
       </c>
       <c r="AP47" t="n">
         <v>1664000</v>
       </c>
       <c r="AQ47" t="n">
-        <v>2165008</v>
+        <v>2193188</v>
       </c>
       <c r="AR47" t="n">
-        <v>0.76858838396902</v>
+        <v>0.7587128873584936</v>
       </c>
       <c r="AS47" t="n">
-        <v>0.1043003856198645</v>
+        <v>0.03054808255192398</v>
       </c>
       <c r="AT47" t="n">
-        <v>-0.1892082714216516</v>
+        <v>-0.2470459677690641</v>
       </c>
       <c r="AU47" t="n">
-        <v>-0.2539028481281473</v>
+        <v>-0.2596815794685243</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.0807160704305252</v>
+        <v>-0.05232722263889844</v>
       </c>
       <c r="AW47" t="n">
-        <v>-0.4252547108517403</v>
+        <v>-0.4058021077865738</v>
       </c>
       <c r="AX47" t="n">
         <v>-0.1025039199148389</v>
@@ -9783,12 +9783,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>DUK</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dominion Energy</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -9803,11 +9803,11 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Utility, Virginia data center exposure</t>
+          <t>Utility/data center load</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>Dominion Energy, Inc.</t>
+          <t>Duke Energy Corporation</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -9879,7 +9879,7 @@
         </is>
       </c>
       <c r="X49" t="n">
-        <v>60484997120</v>
+        <v>96620699648</v>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>1</v>
       </c>
       <c r="AA49" t="n">
-        <v>60484997120</v>
+        <v>96620699648</v>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
@@ -9904,71 +9904,71 @@
         <v>46.4</v>
       </c>
       <c r="AE49" t="n">
-        <v>68.76999664306641</v>
+        <v>123.9199981689453</v>
       </c>
       <c r="AF49" t="n">
-        <v>68.97580032348633</v>
+        <v>124.3260908508301</v>
       </c>
       <c r="AG49" t="n">
-        <v>62.81423795700073</v>
+        <v>122.1940333175659</v>
       </c>
       <c r="AH49" t="n">
-        <v>-0.002983708481159031</v>
+        <v>-0.003266351246996146</v>
       </c>
       <c r="AI49" t="n">
-        <v>0.09481542528849385</v>
+        <v>0.01412478829382646</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0.09809181113847898</v>
+        <v>0.01744813126614142</v>
       </c>
       <c r="AK49" t="n">
-        <v>71.69000244140625</v>
+        <v>131.1634063720703</v>
       </c>
       <c r="AL49" t="n">
-        <v>55.91819381713867</v>
+        <v>111.0921020507812</v>
       </c>
       <c r="AM49" t="n">
-        <v>-0.0407310043088146</v>
+        <v>-0.05522430686633495</v>
       </c>
       <c r="AN49" t="n">
-        <v>0.2298322236221571</v>
+        <v>0.1154708199895282</v>
       </c>
       <c r="AO49" t="n">
-        <v>40.23436568676536</v>
+        <v>37.5143936120282</v>
       </c>
       <c r="AP49" t="n">
-        <v>1951400</v>
+        <v>4124800</v>
       </c>
       <c r="AQ49" t="n">
-        <v>5188740</v>
+        <v>4124452</v>
       </c>
       <c r="AR49" t="n">
-        <v>0.3760835964029803</v>
+        <v>1.000084374845434</v>
       </c>
       <c r="AS49" t="n">
-        <v>-0.03195388855864689</v>
+        <v>0.00538468442537976</v>
       </c>
       <c r="AT49" t="n">
-        <v>0.1252001657749604</v>
+        <v>0.01767372082953256</v>
       </c>
       <c r="AU49" t="n">
-        <v>0.05546265462676869</v>
+        <v>0.01568433574976491</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.1737041048036754</v>
+        <v>0.03943007351198258</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.1309168236439833</v>
+        <v>0.4049954958672182</v>
       </c>
       <c r="AX49" t="n">
-        <v>0.1849901855780911</v>
+        <v>0.08279691057288874</v>
       </c>
       <c r="AY49" t="n">
-        <v>185.0928239036169</v>
+        <v>167.8542308083402</v>
       </c>
       <c r="AZ49" t="inlineStr"/>
       <c r="BA49" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
@@ -9979,12 +9979,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GEV</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Dominion Energy</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -9994,16 +9994,16 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Grid + power generation equipment</t>
+          <t>Utility / power generation</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Grid, gas turbines, power equipment</t>
+          <t>Utility, Virginia data center exposure</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G50" t="n">
         <v>1</v>
@@ -10056,17 +10056,17 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>GE Vernova Inc.</t>
+          <t>Dominion Energy, Inc.</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>Specialty Industrial Machinery</t>
+          <t>Utilities - Regulated Electric</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
@@ -10075,7 +10075,7 @@
         </is>
       </c>
       <c r="X50" t="n">
-        <v>283179188224</v>
+        <v>60484997120</v>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
@@ -10086,79 +10086,81 @@
         <v>1</v>
       </c>
       <c r="AA50" t="n">
-        <v>283179188224</v>
+        <v>60484997120</v>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>Mega cap</t>
+          <t>Large cap</t>
         </is>
       </c>
       <c r="AC50" s="2" t="n">
-        <v>45378</v>
+        <v>29297</v>
       </c>
       <c r="AD50" t="n">
-        <v>2.4</v>
+        <v>46.4</v>
       </c>
       <c r="AE50" t="n">
-        <v>1063.25</v>
+        <v>68.76999664306641</v>
       </c>
       <c r="AF50" t="n">
-        <v>1027.457961425781</v>
+        <v>68.97580032348633</v>
       </c>
       <c r="AG50" t="n">
-        <v>856.9074789428711</v>
+        <v>62.81423784255981</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.03483552604385975</v>
+        <v>-0.002983708481159031</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.2407990665593029</v>
+        <v>0.09481542728313208</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.1990302181669725</v>
+        <v>0.09809181313908644</v>
       </c>
       <c r="AK50" t="n">
-        <v>1174.859985351562</v>
+        <v>71.69000244140625</v>
       </c>
       <c r="AL50" t="n">
-        <v>546.9464721679688</v>
+        <v>55.91819763183594</v>
       </c>
       <c r="AM50" t="n">
-        <v>-0.09499854173530697</v>
+        <v>-0.0407310043088146</v>
       </c>
       <c r="AN50" t="n">
-        <v>0.943974509581393</v>
+        <v>0.2298321397239305</v>
       </c>
       <c r="AO50" t="n">
-        <v>60.56132701198218</v>
+        <v>40.23436568676536</v>
       </c>
       <c r="AP50" t="n">
-        <v>1489000</v>
+        <v>1951400</v>
       </c>
       <c r="AQ50" t="n">
-        <v>2891196</v>
+        <v>5188740</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.5150117805918382</v>
+        <v>0.3760835964029803</v>
       </c>
       <c r="AS50" t="n">
-        <v>0.005114227439395602</v>
+        <v>-0.03195388855864689</v>
       </c>
       <c r="AT50" t="n">
-        <v>0.01388003262055593</v>
+        <v>0.1252001657749604</v>
       </c>
       <c r="AU50" t="n">
-        <v>0.3270125313008285</v>
+        <v>0.05546265462676869</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.704326707179793</v>
-      </c>
-      <c r="AW50" t="inlineStr"/>
+        <v>0.1737040283887323</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>0.1309168236439833</v>
+      </c>
       <c r="AX50" t="n">
-        <v>0.5675378535686497</v>
+        <v>0.1849901855780911</v>
       </c>
       <c r="AY50" t="n">
-        <v>7.135185684177886</v>
+        <v>185.0928989414937</v>
       </c>
       <c r="AZ50" t="inlineStr"/>
       <c r="BA50" t="n">
@@ -10173,12 +10175,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DUK</t>
+          <t>GEV</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -10188,16 +10190,16 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Utility / power generation</t>
+          <t>Grid + power generation equipment</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Utility/data center load</t>
+          <t>Grid, gas turbines, power equipment</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G51" t="n">
         <v>1</v>
@@ -10250,17 +10252,17 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>Duke Energy Corporation</t>
+          <t>GE Vernova Inc.</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>Utilities - Regulated Electric</t>
+          <t>Specialty Industrial Machinery</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
@@ -10269,7 +10271,7 @@
         </is>
       </c>
       <c r="X51" t="n">
-        <v>96620699648</v>
+        <v>283179188224</v>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
@@ -10280,89 +10282,87 @@
         <v>1</v>
       </c>
       <c r="AA51" t="n">
-        <v>96620699648</v>
+        <v>283179188224</v>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>Large cap</t>
+          <t>Mega cap</t>
         </is>
       </c>
       <c r="AC51" s="2" t="n">
-        <v>29297</v>
+        <v>45378</v>
       </c>
       <c r="AD51" t="n">
-        <v>46.4</v>
+        <v>2.4</v>
       </c>
       <c r="AE51" t="n">
-        <v>123.9199981689453</v>
+        <v>1063.25</v>
       </c>
       <c r="AF51" t="n">
-        <v>124.5586462402344</v>
+        <v>1027.457961425781</v>
       </c>
       <c r="AG51" t="n">
-        <v>122.2211759185791</v>
+        <v>856.9074801635742</v>
       </c>
       <c r="AH51" t="n">
-        <v>-0.005127288153544352</v>
+        <v>0.03483552604385975</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.01389957376533446</v>
+        <v>0.2407990647917291</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.01912492089924278</v>
+        <v>0.1990302164589002</v>
       </c>
       <c r="AK51" t="n">
-        <v>131.1634063720703</v>
+        <v>1174.859985351562</v>
       </c>
       <c r="AL51" t="n">
-        <v>111.0921020507812</v>
+        <v>546.9464721679688</v>
       </c>
       <c r="AM51" t="n">
-        <v>-0.05522430686633495</v>
+        <v>-0.09499854173530697</v>
       </c>
       <c r="AN51" t="n">
-        <v>0.1154708199895282</v>
+        <v>0.943974509581393</v>
       </c>
       <c r="AO51" t="n">
-        <v>37.5143936120282</v>
+        <v>60.56132701198218</v>
       </c>
       <c r="AP51" t="n">
-        <v>4124800</v>
+        <v>1489000</v>
       </c>
       <c r="AQ51" t="n">
-        <v>4136014</v>
+        <v>2891196</v>
       </c>
       <c r="AR51" t="n">
-        <v>0.997288693897071</v>
+        <v>0.5150117805918382</v>
       </c>
       <c r="AS51" t="n">
-        <v>-3.817145435180969e-06</v>
+        <v>0.005114227439395602</v>
       </c>
       <c r="AT51" t="n">
-        <v>0.03356368878145566</v>
+        <v>0.01388003262055593</v>
       </c>
       <c r="AU51" t="n">
-        <v>-0.01646036734405443</v>
+        <v>0.3270125313008285</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.04118665125036114</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>0.4285558987541858</v>
-      </c>
+        <v>0.704326707179793</v>
+      </c>
+      <c r="AW51" t="inlineStr"/>
       <c r="AX51" t="n">
-        <v>0.08279691057288874</v>
+        <v>0.5675377125161767</v>
       </c>
       <c r="AY51" t="n">
-        <v>167.8543953759148</v>
+        <v>7.135185684177886</v>
       </c>
       <c r="AZ51" t="inlineStr"/>
       <c r="BA51" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>Positive momentum</t>
+          <t>Strong momentum</t>
         </is>
       </c>
     </row>
@@ -10544,13 +10544,13 @@
         <v>0.224120364007435</v>
       </c>
       <c r="AW52" t="n">
-        <v>1.425964825682528</v>
+        <v>1.425964617497652</v>
       </c>
       <c r="AX52" t="n">
         <v>0.1697540685206498</v>
       </c>
       <c r="AY52" t="n">
-        <v>200.8429617491752</v>
+        <v>200.8431193744437</v>
       </c>
       <c r="AZ52" t="inlineStr"/>
       <c r="BA52" t="n">
@@ -10685,19 +10685,19 @@
         <v>45.86000061035156</v>
       </c>
       <c r="AF53" t="n">
-        <v>46.23680000305175</v>
+        <v>46.19600006103516</v>
       </c>
       <c r="AG53" t="n">
-        <v>45.57788415908814</v>
+        <v>45.57842969894409</v>
       </c>
       <c r="AH53" t="n">
-        <v>-0.008149339761301055</v>
+        <v>-0.007273345100001438</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.006189766297152177</v>
+        <v>0.006177722955075682</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.0144569204148155</v>
+        <v>0.01354961911084374</v>
       </c>
       <c r="AK53" t="n">
         <v>49.82146072387695</v>
@@ -10718,31 +10718,31 @@
         <v>3934900</v>
       </c>
       <c r="AQ53" t="n">
-        <v>8580114</v>
+        <v>8577484</v>
       </c>
       <c r="AR53" t="n">
-        <v>0.4586069602338617</v>
+        <v>0.4587475767952467</v>
       </c>
       <c r="AS53" t="n">
-        <v>-0.008646729911260032</v>
+        <v>-0.01987604802262699</v>
       </c>
       <c r="AT53" t="n">
-        <v>0.06711117190442373</v>
+        <v>0.04259643015570092</v>
       </c>
       <c r="AU53" t="n">
-        <v>-0.03697064392080873</v>
+        <v>-0.01813537158241041</v>
       </c>
       <c r="AV53" t="n">
-        <v>0.05476652285708949</v>
+        <v>0.04124091896544591</v>
       </c>
       <c r="AW53" t="n">
-        <v>0.6170235374449509</v>
+        <v>0.6112485211085679</v>
       </c>
       <c r="AX53" t="n">
         <v>0.06301597098307044</v>
       </c>
       <c r="AY53" t="n">
-        <v>186.0334351288758</v>
+        <v>186.0334578617634</v>
       </c>
       <c r="AZ53" t="inlineStr"/>
       <c r="BA53" t="n">
@@ -10880,28 +10880,28 @@
         <v>94.54999984741211</v>
       </c>
       <c r="AG54" t="n">
-        <v>91.76001804351807</v>
+        <v>91.76001808166504</v>
       </c>
       <c r="AH54" t="n">
         <v>-0.01850869168142255</v>
       </c>
       <c r="AI54" t="n">
-        <v>0.01133374895094841</v>
+        <v>0.01133374853051139</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.03040520112551492</v>
+        <v>0.03040520069714936</v>
       </c>
       <c r="AK54" t="n">
         <v>98.29612731933594</v>
       </c>
       <c r="AL54" t="n">
-        <v>82.73964691162109</v>
+        <v>82.73965454101562</v>
       </c>
       <c r="AM54" t="n">
         <v>-0.05591394511121273</v>
       </c>
       <c r="AN54" t="n">
-        <v>0.1215905133228663</v>
+        <v>0.1215904099013985</v>
       </c>
       <c r="AO54" t="n">
         <v>27.61559402012043</v>
@@ -10922,7 +10922,7 @@
         <v>0.01100340043748282</v>
       </c>
       <c r="AU54" t="n">
-        <v>-0.006810545371110588</v>
+        <v>-0.006810626468382819</v>
       </c>
       <c r="AV54" t="n">
         <v>0.01744357669566865</v>
@@ -10934,7 +10934,7 @@
         <v>0.08170829325147677</v>
       </c>
       <c r="AY54" t="n">
-        <v>341.1938808769988</v>
+        <v>341.1941441128095</v>
       </c>
       <c r="AZ54" t="inlineStr"/>
       <c r="BA54" t="n">
@@ -11076,16 +11076,16 @@
         <v>14.5785573387146</v>
       </c>
       <c r="AG55" t="n">
-        <v>14.20934876441956</v>
+        <v>14.20934875011444</v>
       </c>
       <c r="AH55" t="n">
         <v>0.01038801028134384</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.03664142435017781</v>
+        <v>0.03664142539380588</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.0259834972324382</v>
+        <v>0.02598349826533641</v>
       </c>
       <c r="AK55" t="n">
         <v>16.86722755432129</v>
@@ -11118,19 +11118,19 @@
         <v>0.03017767944492755</v>
       </c>
       <c r="AU55" t="n">
-        <v>-0.07306691497668405</v>
+        <v>-0.07306685934859425</v>
       </c>
       <c r="AV55" t="n">
         <v>0.1949978445121092</v>
       </c>
       <c r="AW55" t="n">
-        <v>-0.2542447940858428</v>
+        <v>-0.2542448661003337</v>
       </c>
       <c r="AX55" t="n">
         <v>0.03030728330828092</v>
       </c>
       <c r="AY55" t="n">
-        <v>6.469904337566317</v>
+        <v>6.46989982174048</v>
       </c>
       <c r="AZ55" t="inlineStr"/>
       <c r="BA55" t="n">
@@ -11145,12 +11145,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TLN</t>
+          <t>ENR.DE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Talen Energy</t>
+          <t>Siemens Energy</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -11160,16 +11160,16 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Grid / power equipment</t>
+          <t>Grid + gas/power equipment</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Power generation/data center deals</t>
+          <t>Grid/gas/power equipment</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -11218,37 +11218,37 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>Talen Energy Corporation</t>
+          <t>Siemens Energy AG</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>Utilities - Independent Power Producers</t>
+          <t>Specialty Industrial Machinery</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="X56" t="n">
-        <v>17380417536</v>
+        <v>136748384256</v>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="Z56" t="n">
-        <v>1</v>
+        <v>1.157273530960083</v>
       </c>
       <c r="AA56" t="n">
-        <v>17380417536</v>
+        <v>158255285501.0273</v>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
@@ -11256,91 +11256,93 @@
         </is>
       </c>
       <c r="AC56" s="2" t="n">
-        <v>45079</v>
+        <v>44103</v>
       </c>
       <c r="AD56" t="n">
-        <v>3.2</v>
+        <v>5.9</v>
       </c>
       <c r="AE56" t="n">
-        <v>362.739990234375</v>
+        <v>160.7200012207031</v>
       </c>
       <c r="AF56" t="n">
-        <v>370.7248004150391</v>
+        <v>155.1731994628906</v>
       </c>
       <c r="AG56" t="n">
-        <v>363.6843495178223</v>
+        <v>147.211452293396</v>
       </c>
       <c r="AH56" t="n">
-        <v>-0.02153837609926501</v>
+        <v>0.03574587478386682</v>
       </c>
       <c r="AI56" t="n">
-        <v>-0.002596645373108109</v>
+        <v>0.09176289423722439</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.01935868537249696</v>
+        <v>0.05408374854985243</v>
       </c>
       <c r="AK56" t="n">
-        <v>445.8399963378906</v>
+        <v>187.6199951171875</v>
       </c>
       <c r="AL56" t="n">
-        <v>302.9700012207031</v>
+        <v>84.04161071777344</v>
       </c>
       <c r="AM56" t="n">
-        <v>-0.186389751449164</v>
+        <v>-0.1433748779264312</v>
       </c>
       <c r="AN56" t="n">
-        <v>0.1972802217145304</v>
+        <v>0.9123860174506799</v>
       </c>
       <c r="AO56" t="n">
-        <v>56.06846281776245</v>
+        <v>65.05611643443376</v>
       </c>
       <c r="AP56" t="n">
-        <v>492600</v>
+        <v>1583904</v>
       </c>
       <c r="AQ56" t="n">
-        <v>835244</v>
+        <v>2426827.38</v>
       </c>
       <c r="AR56" t="n">
-        <v>0.5897677804330231</v>
+        <v>0.6526644676309858</v>
       </c>
       <c r="AS56" t="n">
-        <v>-0.02586138789131454</v>
+        <v>0.08844641226258498</v>
       </c>
       <c r="AT56" t="n">
-        <v>0.08526807333860709</v>
+        <v>-0.07801747092759637</v>
       </c>
       <c r="AU56" t="n">
-        <v>-0.03705872450299774</v>
+        <v>0.00220661661475452</v>
       </c>
       <c r="AV56" t="n">
-        <v>-0.04692594740600986</v>
-      </c>
-      <c r="AW56" t="inlineStr"/>
+        <v>0.6670664607869392</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>5.486925119064987</v>
+      </c>
       <c r="AX56" t="n">
-        <v>-0.08567544630024082</v>
+        <v>0.3143760066811025</v>
       </c>
       <c r="AY56" t="n">
-        <v>6.800860005040323</v>
+        <v>6.374454312612864</v>
       </c>
       <c r="AZ56" t="inlineStr"/>
       <c r="BA56" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive momentum</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ENR.DE</t>
+          <t>TLN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Siemens Energy</t>
+          <t>Talen Energy</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -11350,16 +11352,16 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Grid + gas/power equipment</t>
+          <t>Grid / power equipment</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Grid/gas/power equipment</t>
+          <t>Power generation/data center deals</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -11408,37 +11410,37 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>Siemens Energy AG</t>
+          <t>Talen Energy Corporation</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>Specialty Industrial Machinery</t>
+          <t>Utilities - Independent Power Producers</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X57" t="n">
-        <v>136748384256</v>
+        <v>17380417536</v>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z57" t="n">
-        <v>1.157273530960083</v>
+        <v>1</v>
       </c>
       <c r="AA57" t="n">
-        <v>158255285501.0273</v>
+        <v>17380417536</v>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
@@ -11446,81 +11448,79 @@
         </is>
       </c>
       <c r="AC57" s="2" t="n">
-        <v>44103</v>
+        <v>45079</v>
       </c>
       <c r="AD57" t="n">
-        <v>5.9</v>
+        <v>3.2</v>
       </c>
       <c r="AE57" t="n">
-        <v>160.7200012207031</v>
+        <v>362.739990234375</v>
       </c>
       <c r="AF57" t="n">
-        <v>155.1191995239258</v>
+        <v>370.7248004150391</v>
       </c>
       <c r="AG57" t="n">
-        <v>146.9253952789307</v>
+        <v>363.6843495178223</v>
       </c>
       <c r="AH57" t="n">
-        <v>0.0361064375910054</v>
+        <v>-0.02153837609926501</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.09388850658243308</v>
+        <v>-0.002596645373108109</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.05576846827221105</v>
+        <v>0.01935868537249696</v>
       </c>
       <c r="AK57" t="n">
-        <v>187.6199951171875</v>
+        <v>445.8399963378906</v>
       </c>
       <c r="AL57" t="n">
-        <v>84.04161071777344</v>
+        <v>302.9700012207031</v>
       </c>
       <c r="AM57" t="n">
-        <v>-0.1433748779264312</v>
+        <v>-0.186389751449164</v>
       </c>
       <c r="AN57" t="n">
-        <v>0.9123860174506799</v>
+        <v>0.1972802217145304</v>
       </c>
       <c r="AO57" t="n">
-        <v>60.67365084392141</v>
+        <v>56.06846281776245</v>
       </c>
       <c r="AP57" t="n">
-        <v>1583795</v>
+        <v>492600</v>
       </c>
       <c r="AQ57" t="n">
-        <v>2426825.2</v>
+        <v>835244</v>
       </c>
       <c r="AR57" t="n">
-        <v>0.6526201392667259</v>
+        <v>0.5897677804330231</v>
       </c>
       <c r="AS57" t="n">
-        <v>0.08054319809803734</v>
+        <v>-0.02586138789131454</v>
       </c>
       <c r="AT57" t="n">
-        <v>-0.04162191922813996</v>
+        <v>0.08526807333860709</v>
       </c>
       <c r="AU57" t="n">
-        <v>-0.0122069452533079</v>
+        <v>-0.03705872450299774</v>
       </c>
       <c r="AV57" t="n">
-        <v>0.7018703138442359</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>5.417642422826281</v>
-      </c>
+        <v>-0.04692594740600986</v>
+      </c>
+      <c r="AW57" t="inlineStr"/>
       <c r="AX57" t="n">
-        <v>0.3143760066811025</v>
+        <v>-0.08567544630024082</v>
       </c>
       <c r="AY57" t="n">
-        <v>6.374454957999506</v>
+        <v>6.800860005040323</v>
       </c>
       <c r="AZ57" t="inlineStr"/>
       <c r="BA57" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>Weak momentum</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -11654,16 +11654,16 @@
         <v>261.0965008544922</v>
       </c>
       <c r="AG58" t="n">
-        <v>302.0657026672363</v>
+        <v>302.0657022857666</v>
       </c>
       <c r="AH58" t="n">
         <v>0.08197543465906443</v>
       </c>
       <c r="AI58" t="n">
-        <v>-0.06477300300719824</v>
+        <v>-0.06477300182612789</v>
       </c>
       <c r="AJ58" t="n">
-        <v>-0.1356301011699991</v>
+        <v>-0.1356301000784121</v>
       </c>
       <c r="AK58" t="n">
         <v>402.3219604492188</v>
@@ -11696,7 +11696,7 @@
         <v>0.05726043074097631</v>
       </c>
       <c r="AU58" t="n">
-        <v>-0.01772318562119646</v>
+        <v>-0.01772328985278415</v>
       </c>
       <c r="AV58" t="n">
         <v>-0.1294407810747112</v>
@@ -11898,7 +11898,7 @@
         <v>-0.3022018572606078</v>
       </c>
       <c r="AY59" t="n">
-        <v>-0.9125809268670633</v>
+        <v>-0.912580917055094</v>
       </c>
       <c r="AZ59" t="inlineStr"/>
       <c r="BA59" t="n">
@@ -12038,16 +12038,16 @@
         <v>153.895481262207</v>
       </c>
       <c r="AG60" t="n">
-        <v>160.7724200439453</v>
+        <v>160.7724196624756</v>
       </c>
       <c r="AH60" t="n">
         <v>-0.03746358458421084</v>
       </c>
       <c r="AI60" t="n">
-        <v>-0.07863547216417566</v>
+        <v>-0.07863546997802529</v>
       </c>
       <c r="AJ60" t="n">
-        <v>-0.04277436876212071</v>
+        <v>-0.04277436649088162</v>
       </c>
       <c r="AK60" t="n">
         <v>217.0162200927734</v>
@@ -12083,10 +12083,10 @@
         <v>-0.1338282997393593</v>
       </c>
       <c r="AV60" t="n">
-        <v>-0.264111478395747</v>
+        <v>-0.264111534178643</v>
       </c>
       <c r="AW60" t="n">
-        <v>7.60254181265873</v>
+        <v>7.602539906888541</v>
       </c>
       <c r="AX60" t="n">
         <v>-0.1010119792862805</v>
@@ -12245,13 +12245,13 @@
         <v>97.16828918457031</v>
       </c>
       <c r="AL61" t="n">
-        <v>68.33090209960938</v>
+        <v>68.33090972900391</v>
       </c>
       <c r="AM61" t="n">
         <v>-0.1129821965097163</v>
       </c>
       <c r="AN61" t="n">
-        <v>0.2613619869347366</v>
+        <v>0.2613618460990843</v>
       </c>
       <c r="AO61" t="n">
         <v>33.5411283908995</v>
@@ -12272,19 +12272,19 @@
         <v>-0.07003750852513257</v>
       </c>
       <c r="AU61" t="n">
-        <v>-0.06808844183764762</v>
+        <v>-0.06808851871218957</v>
       </c>
       <c r="AV61" t="n">
-        <v>0.2276545835127293</v>
+        <v>0.2276544501036113</v>
       </c>
       <c r="AW61" t="n">
-        <v>0.2201833921026064</v>
+        <v>0.2201831285220919</v>
       </c>
       <c r="AX61" t="n">
-        <v>0.08011008099274819</v>
+        <v>0.08010997772393691</v>
       </c>
       <c r="AY61" t="n">
-        <v>247.0260638390476</v>
+        <v>247.026148923067</v>
       </c>
       <c r="AZ61" t="inlineStr"/>
       <c r="BA61" t="n">
@@ -12419,19 +12419,19 @@
         <v>173.2200012207031</v>
       </c>
       <c r="AF62" t="n">
-        <v>182.9925994873047</v>
+        <v>183.2251995849609</v>
       </c>
       <c r="AG62" t="n">
-        <v>195.507546005249</v>
+        <v>195.6580326843262</v>
       </c>
       <c r="AH62" t="n">
-        <v>-0.05340433598944283</v>
+        <v>-0.054606017004874</v>
       </c>
       <c r="AI62" t="n">
-        <v>-0.1139983864558738</v>
+        <v>-0.1146798378568207</v>
       </c>
       <c r="AJ62" t="n">
-        <v>-0.06401260091315519</v>
+        <v>-0.06354368859173964</v>
       </c>
       <c r="AK62" t="n">
         <v>238.1012115478516</v>
@@ -12452,31 +12452,31 @@
         <v>537600</v>
       </c>
       <c r="AQ62" t="n">
-        <v>940674</v>
+        <v>946600</v>
       </c>
       <c r="AR62" t="n">
-        <v>0.5715051122918248</v>
+        <v>0.5679273188252694</v>
       </c>
       <c r="AS62" t="n">
-        <v>0.01191733048374233</v>
+        <v>-0.002993002509611431</v>
       </c>
       <c r="AT62" t="n">
-        <v>-0.1527358361785952</v>
+        <v>-0.177719170660192</v>
       </c>
       <c r="AU62" t="n">
-        <v>-0.1332769573587215</v>
+        <v>-0.1178704772016899</v>
       </c>
       <c r="AV62" t="n">
-        <v>-0.002922246940977202</v>
+        <v>-0.01454234492327866</v>
       </c>
       <c r="AW62" t="n">
-        <v>2.384511082029363</v>
+        <v>2.400197533600555</v>
       </c>
       <c r="AX62" t="n">
         <v>-0.04486502076836563</v>
       </c>
       <c r="AY62" t="n">
-        <v>11.22460539016646</v>
+        <v>11.22460456740921</v>
       </c>
       <c r="AZ62" t="inlineStr"/>
       <c r="BA62" t="n">
@@ -12658,13 +12658,13 @@
         <v>0.2962315927144186</v>
       </c>
       <c r="AW63" t="n">
-        <v>4.81728532857209</v>
+        <v>4.817286649346309</v>
       </c>
       <c r="AX63" t="n">
         <v>-0.008319802304547874</v>
       </c>
       <c r="AY63" t="n">
-        <v>15.33495190777066</v>
+        <v>15.33494800246854</v>
       </c>
       <c r="AZ63" t="inlineStr"/>
       <c r="BA63" t="n">
@@ -12802,25 +12802,25 @@
         <v>132.4999922180176</v>
       </c>
       <c r="AG64" t="n">
-        <v>149.8482818222046</v>
+        <v>149.848282585144</v>
       </c>
       <c r="AH64" t="n">
         <v>-0.04724524318422418</v>
       </c>
       <c r="AI64" t="n">
-        <v>-0.1575479122706683</v>
+        <v>-0.1575479165599395</v>
       </c>
       <c r="AJ64" t="n">
-        <v>-0.1157723625071044</v>
+        <v>-0.1157723670090721</v>
       </c>
       <c r="AK64" t="n">
-        <v>182.8191833496094</v>
+        <v>182.8191986083984</v>
       </c>
       <c r="AL64" t="n">
         <v>117.0400009155273</v>
       </c>
       <c r="AM64" t="n">
-        <v>-0.3094816662518515</v>
+        <v>-0.3094817238851508</v>
       </c>
       <c r="AN64" t="n">
         <v>0.07860557823202874</v>
@@ -12847,16 +12847,16 @@
         <v>-0.2626859546298553</v>
       </c>
       <c r="AV64" t="n">
-        <v>-0.1689427678735379</v>
+        <v>-0.1689428513540133</v>
       </c>
       <c r="AW64" t="n">
-        <v>2.280098490996768</v>
+        <v>2.280098816111697</v>
       </c>
       <c r="AX64" t="n">
-        <v>-0.2328310993448719</v>
+        <v>-0.2328311704834252</v>
       </c>
       <c r="AY64" t="n">
-        <v>16.683688538546</v>
+        <v>16.68369208210909</v>
       </c>
       <c r="AZ64" t="inlineStr"/>
       <c r="BA64" t="n">
@@ -13616,7 +13616,7 @@
         <v>1.481379503229102</v>
       </c>
       <c r="AY68" t="n">
-        <v>-0.4025528828437561</v>
+        <v>-0.4025528402928248</v>
       </c>
       <c r="AZ68" t="inlineStr"/>
       <c r="BA68" t="n">
@@ -13758,16 +13758,16 @@
         <v>169.932004699707</v>
       </c>
       <c r="AG69" t="n">
-        <v>124.1102587890625</v>
+        <v>124.1102591705322</v>
       </c>
       <c r="AH69" t="n">
         <v>0.2186050661674546</v>
       </c>
       <c r="AI69" t="n">
-        <v>0.668516397045045</v>
+        <v>0.6685163919166333</v>
       </c>
       <c r="AJ69" t="n">
-        <v>0.3692019205964516</v>
+        <v>0.3692019163880238</v>
       </c>
       <c r="AK69" t="n">
         <v>207.0800018310547</v>
@@ -13800,7 +13800,7 @@
         <v>0.731918202975957</v>
       </c>
       <c r="AU69" t="n">
-        <v>1.038399341040668</v>
+        <v>1.03839949412491</v>
       </c>
       <c r="AV69" t="n">
         <v>0.9231844052406342</v>
@@ -13812,7 +13812,7 @@
         <v>0.9608609343192547</v>
       </c>
       <c r="AY69" t="n">
-        <v>219.8349165480726</v>
+        <v>219.8349305851745</v>
       </c>
       <c r="AZ69" t="inlineStr"/>
       <c r="BA69" t="n">
@@ -13998,13 +13998,13 @@
         <v>9.631742221809654</v>
       </c>
       <c r="AW70" t="n">
-        <v>5.013499282431831</v>
+        <v>5.013499658311268</v>
       </c>
       <c r="AX70" t="n">
         <v>1.031505778356788</v>
       </c>
       <c r="AY70" t="n">
-        <v>3.82060885066927</v>
+        <v>3.82060933375904</v>
       </c>
       <c r="AZ70" t="inlineStr"/>
       <c r="BA70" t="n">
@@ -14522,28 +14522,28 @@
         <v>888.8800585937501</v>
       </c>
       <c r="AG73" t="n">
-        <v>549.3945110321044</v>
+        <v>549.394511795044</v>
       </c>
       <c r="AH73" t="n">
         <v>0.09513088186659746</v>
       </c>
       <c r="AI73" t="n">
-        <v>0.7718415144204493</v>
+        <v>0.771841511959908</v>
       </c>
       <c r="AJ73" t="n">
-        <v>0.6179267188597874</v>
+        <v>0.6179267166129863</v>
       </c>
       <c r="AK73" t="n">
         <v>1093.260498046875</v>
       </c>
       <c r="AL73" t="n">
-        <v>153.1653289794922</v>
+        <v>153.1653442382812</v>
       </c>
       <c r="AM73" t="n">
         <v>-0.1095992179535707</v>
       </c>
       <c r="AN73" t="n">
-        <v>5.355485336839797</v>
+        <v>5.355484703687366</v>
       </c>
       <c r="AO73" t="n">
         <v>66.81281676403665</v>
@@ -14567,16 +14567,16 @@
         <v>1.290742487183119</v>
       </c>
       <c r="AV73" t="n">
-        <v>5.302430573633002</v>
+        <v>5.302431196258731</v>
       </c>
       <c r="AW73" t="n">
-        <v>11.21327965225998</v>
+        <v>11.21328199042719</v>
       </c>
       <c r="AX73" t="n">
         <v>2.393730738646507</v>
       </c>
       <c r="AY73" t="n">
-        <v>183.6644669832194</v>
+        <v>183.6644335746797</v>
       </c>
       <c r="AZ73" t="inlineStr"/>
       <c r="BA73" t="n">
@@ -14708,28 +14708,28 @@
         <v>552.4081982421875</v>
       </c>
       <c r="AG74" t="n">
-        <v>349.6051797485351</v>
+        <v>349.605179977417</v>
       </c>
       <c r="AH74" t="n">
         <v>-0.07894200445971655</v>
       </c>
       <c r="AI74" t="n">
-        <v>0.455355976587474</v>
+        <v>0.4553559756346719</v>
       </c>
       <c r="AJ74" t="n">
-        <v>0.5800915725548603</v>
+        <v>0.5800915715203954</v>
       </c>
       <c r="AK74" t="n">
         <v>746.22998046875</v>
       </c>
       <c r="AL74" t="n">
-        <v>74.45821380615234</v>
+        <v>74.45822906494141</v>
       </c>
       <c r="AM74" t="n">
         <v>-0.3181726798575391</v>
       </c>
       <c r="AN74" t="n">
-        <v>5.833362792150777</v>
+        <v>5.833361391783851</v>
       </c>
       <c r="AO74" t="n">
         <v>51.56672577932869</v>
@@ -14753,16 +14753,16 @@
         <v>0.8082827593724291</v>
       </c>
       <c r="AV74" t="n">
-        <v>5.691748008036588</v>
+        <v>5.691747336573576</v>
       </c>
       <c r="AW74" t="n">
-        <v>9.001838260244229</v>
+        <v>9.001837510224638</v>
       </c>
       <c r="AX74" t="n">
-        <v>1.712712916626058</v>
+        <v>1.712713137315056</v>
       </c>
       <c r="AY74" t="n">
-        <v>747.7416702928771</v>
+        <v>747.7416046183458</v>
       </c>
       <c r="AZ74" t="inlineStr"/>
       <c r="BA74" t="n">
@@ -14949,10 +14949,10 @@
         <v>0.6548769557347731</v>
       </c>
       <c r="AV75" t="n">
-        <v>3.034030241449385</v>
+        <v>3.034030704604037</v>
       </c>
       <c r="AW75" t="n">
-        <v>2.785841774958126</v>
+        <v>2.785841367040424</v>
       </c>
       <c r="AX75" t="n">
         <v>1.142969017215477</v>
@@ -15148,13 +15148,13 @@
         <v>2.112306284098271</v>
       </c>
       <c r="AW76" t="n">
-        <v>4.466314125273241</v>
+        <v>4.466313439357992</v>
       </c>
       <c r="AX76" t="n">
         <v>0.7993763265122695</v>
       </c>
       <c r="AY76" t="n">
-        <v>1761.884421896872</v>
+        <v>1761.884561231511</v>
       </c>
       <c r="AZ76" t="inlineStr"/>
       <c r="BA76" t="n">
@@ -15288,28 +15288,28 @@
         <v>960.6536303710938</v>
       </c>
       <c r="AG77" t="n">
-        <v>552.443649597168</v>
+        <v>552.4436499786377</v>
       </c>
       <c r="AH77" t="n">
         <v>0.01145713962397221</v>
       </c>
       <c r="AI77" t="n">
-        <v>0.7588399719193952</v>
+        <v>0.758839970704893</v>
       </c>
       <c r="AJ77" t="n">
-        <v>0.7389169575423395</v>
+        <v>0.7389169563415943</v>
       </c>
       <c r="AK77" t="n">
         <v>1213.373413085938</v>
       </c>
       <c r="AL77" t="n">
-        <v>115.6044540405273</v>
+        <v>115.6044616699219</v>
       </c>
       <c r="AM77" t="n">
         <v>-0.1992077931942348</v>
       </c>
       <c r="AN77" t="n">
-        <v>7.405039245320923</v>
+        <v>7.40503869062468</v>
       </c>
       <c r="AO77" t="n">
         <v>56.36331046063454</v>
@@ -15336,13 +15336,13 @@
         <v>6.767735128032084</v>
       </c>
       <c r="AW77" t="n">
-        <v>11.42281947343774</v>
+        <v>11.42281462640524</v>
       </c>
       <c r="AX77" t="n">
         <v>2.082295175442205</v>
       </c>
       <c r="AY77" t="n">
-        <v>718.3504110271381</v>
+        <v>718.3501570839209</v>
       </c>
       <c r="AZ77" t="inlineStr"/>
       <c r="BA77" t="n">
@@ -15480,16 +15480,16 @@
         <v>2043380</v>
       </c>
       <c r="AG78" t="n">
-        <v>1229144.9725</v>
+        <v>1229144.9715625</v>
       </c>
       <c r="AH78" t="n">
         <v>-0.1949612896279693</v>
       </c>
       <c r="AI78" t="n">
-        <v>0.33832870556691</v>
+        <v>0.338328706587687</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0.6624401886816489</v>
+        <v>0.6624401899496339</v>
       </c>
       <c r="AK78" t="n">
         <v>2919000</v>
@@ -15525,16 +15525,16 @@
         <v>0.8582987867681218</v>
       </c>
       <c r="AV78" t="n">
-        <v>5.402612810930077</v>
+        <v>5.402612421554618</v>
       </c>
       <c r="AW78" t="n">
-        <v>12.93481674451947</v>
+        <v>12.93481951112979</v>
       </c>
       <c r="AX78" t="n">
         <v>1.434728328443371</v>
       </c>
       <c r="AY78" t="n">
-        <v>-8.187366619324349</v>
+        <v>-8.187366128649622</v>
       </c>
       <c r="AZ78" t="inlineStr"/>
       <c r="BA78" t="n">
@@ -16178,16 +16178,16 @@
         <v>159.5859490966797</v>
       </c>
       <c r="AG82" t="n">
-        <v>143.7636518478394</v>
+        <v>143.7636530303955</v>
       </c>
       <c r="AH82" t="n">
         <v>0.04714733067830235</v>
       </c>
       <c r="AI82" t="n">
-        <v>0.1623939602426223</v>
+        <v>0.1623939506811225</v>
       </c>
       <c r="AJ82" t="n">
-        <v>0.1100577026631653</v>
+        <v>0.1100576935321678</v>
       </c>
       <c r="AK82" t="n">
         <v>176.3200073242188</v>
@@ -16229,10 +16229,10 @@
         <v>3.761792252607514</v>
       </c>
       <c r="AX82" t="n">
-        <v>0.2002926500258817</v>
+        <v>0.2002927815762201</v>
       </c>
       <c r="AY82" t="n">
-        <v>1334.447702529471</v>
+        <v>1334.447384475125</v>
       </c>
       <c r="AZ82" t="inlineStr"/>
       <c r="BA82" t="n">
@@ -16247,12 +16247,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>KEYS</t>
+          <t>300502.SZ</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Keysight Technologies</t>
+          <t>Eoptolink</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -16262,19 +16262,19 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Switching / networking silicon</t>
+          <t>Optical networking / transceivers / fiber</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Testing/simulation/electronics measurement</t>
+          <t>Optical modules</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -16282,11 +16282,7 @@
       <c r="I83" t="n">
         <v>0</v>
       </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
-        </is>
-      </c>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" s="1" t="n">
         <v>46195</v>
       </c>
@@ -16324,7 +16320,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>Keysight Technologies, Inc.</t>
+          <t>Eoptolink Technology Inc., Ltd.</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -16334,27 +16330,27 @@
       </c>
       <c r="V83" t="inlineStr">
         <is>
-          <t>Scientific &amp; Technical Instruments</t>
+          <t>Communication Equipment</t>
         </is>
       </c>
       <c r="W83" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="X83" t="n">
-        <v>61149777920</v>
+        <v>624738500608</v>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CNY</t>
         </is>
       </c>
       <c r="Z83" t="n">
-        <v>1</v>
+        <v>0.1483261436223984</v>
       </c>
       <c r="AA83" t="n">
-        <v>61149777920</v>
+        <v>92665052567.62402</v>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
@@ -16362,77 +16358,77 @@
         </is>
       </c>
       <c r="AC83" s="2" t="n">
-        <v>41932</v>
+        <v>42432</v>
       </c>
       <c r="AD83" t="n">
-        <v>11.8</v>
+        <v>10.5</v>
       </c>
       <c r="AE83" t="n">
-        <v>357.8200073242188</v>
+        <v>448.0799865722656</v>
       </c>
       <c r="AF83" t="n">
-        <v>332.9876000976562</v>
+        <v>503.6078063964844</v>
       </c>
       <c r="AG83" t="n">
-        <v>277.6773490905762</v>
+        <v>364.8090197753907</v>
       </c>
       <c r="AH83" t="n">
-        <v>0.07457457040226068</v>
+        <v>-0.1102600458510414</v>
       </c>
       <c r="AI83" t="n">
-        <v>0.2886179175079226</v>
+        <v>0.2282590678491012</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0.1991889190394074</v>
+        <v>0.3804697227786493</v>
       </c>
       <c r="AK83" t="n">
-        <v>373.3399963378906</v>
+        <v>610.489990234375</v>
       </c>
       <c r="AL83" t="n">
-        <v>158.5099945068359</v>
+        <v>129.9640350341797</v>
       </c>
       <c r="AM83" t="n">
-        <v>-0.04157065721837516</v>
+        <v>-0.2660322138938889</v>
       </c>
       <c r="AN83" t="n">
-        <v>1.257397134089152</v>
+        <v>2.44772295238774</v>
       </c>
       <c r="AO83" t="n">
-        <v>71.86881793654932</v>
+        <v>43.42000253205848</v>
       </c>
       <c r="AP83" t="n">
-        <v>926800</v>
+        <v>38818795</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1352958</v>
+        <v>54835609.98</v>
       </c>
       <c r="AR83" t="n">
-        <v>0.6850175689119692</v>
+        <v>0.7079121580695145</v>
       </c>
       <c r="AS83" t="n">
-        <v>0.1327002666592989</v>
+        <v>-0.07206763162411811</v>
       </c>
       <c r="AT83" t="n">
-        <v>0.02524282201679551</v>
+        <v>0.09773087140677572</v>
       </c>
       <c r="AU83" t="n">
-        <v>0.5323541421853089</v>
+        <v>0.6408639200334638</v>
       </c>
       <c r="AV83" t="n">
-        <v>1.175462163295208</v>
+        <v>2.431907443329538</v>
       </c>
       <c r="AW83" t="n">
-        <v>1.143276513117577</v>
+        <v>35.31349971194724</v>
       </c>
       <c r="AX83" t="n">
-        <v>0.7320296900484096</v>
+        <v>0.4730584441428192</v>
       </c>
       <c r="AY83" t="n">
-        <v>11.66619494952987</v>
+        <v>241.9959224066451</v>
       </c>
       <c r="AZ83" t="inlineStr"/>
       <c r="BA83" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
@@ -16443,12 +16439,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>300502.SZ</t>
+          <t>ALAB</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Eoptolink</t>
+          <t>Astera Labs</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -16458,27 +16454,31 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Optical networking / transceivers / fiber</t>
+          <t>PCIe/CXL connectivity chips</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Optical modules</t>
+          <t>PCIe/CXL/connectivity chips para AI servers</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>Nasdaq-100, SOXX</t>
+        </is>
+      </c>
       <c r="K84" s="1" t="n">
         <v>46195</v>
       </c>
@@ -16512,11 +16512,11 @@
         </is>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>Eoptolink Technology Inc., Ltd.</t>
+          <t>Astera Labs, Inc.</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -16526,27 +16526,27 @@
       </c>
       <c r="V84" t="inlineStr">
         <is>
-          <t>Communication Equipment</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="X84" t="n">
-        <v>624738500608</v>
+        <v>55794540544</v>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="Z84" t="n">
-        <v>0.1483261436223984</v>
+        <v>1</v>
       </c>
       <c r="AA84" t="n">
-        <v>92665052567.62402</v>
+        <v>55794540544</v>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
@@ -16554,73 +16554,71 @@
         </is>
       </c>
       <c r="AC84" s="2" t="n">
-        <v>42432</v>
+        <v>45371</v>
       </c>
       <c r="AD84" t="n">
-        <v>10.5</v>
+        <v>2.4</v>
       </c>
       <c r="AE84" t="n">
-        <v>448.0799865722656</v>
+        <v>321.6099853515625</v>
       </c>
       <c r="AF84" t="n">
-        <v>503.6078063964844</v>
+        <v>355.0372982788086</v>
       </c>
       <c r="AG84" t="n">
-        <v>364.8090197753907</v>
+        <v>215.8044997787476</v>
       </c>
       <c r="AH84" t="n">
-        <v>-0.1102600458510414</v>
+        <v>-0.09415155277853604</v>
       </c>
       <c r="AI84" t="n">
-        <v>0.2282590678491012</v>
+        <v>0.4902839638714274</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0.3804697227786493</v>
+        <v>0.645180237867184</v>
       </c>
       <c r="AK84" t="n">
-        <v>610.489990234375</v>
+        <v>483.0199890136719</v>
       </c>
       <c r="AL84" t="n">
-        <v>129.9640350341797</v>
+        <v>100.2699966430664</v>
       </c>
       <c r="AM84" t="n">
-        <v>-0.2660322138938889</v>
+        <v>-0.3341683726002914</v>
       </c>
       <c r="AN84" t="n">
-        <v>2.44772295238774</v>
+        <v>2.207439873528724</v>
       </c>
       <c r="AO84" t="n">
-        <v>43.42000253205848</v>
+        <v>58.2180514437172</v>
       </c>
       <c r="AP84" t="n">
-        <v>38818795</v>
+        <v>2518100</v>
       </c>
       <c r="AQ84" t="n">
-        <v>54835609.98</v>
+        <v>5391200</v>
       </c>
       <c r="AR84" t="n">
-        <v>0.7079121580695145</v>
+        <v>0.4670759756640451</v>
       </c>
       <c r="AS84" t="n">
-        <v>-0.07206763162411811</v>
+        <v>0.05925166498810941</v>
       </c>
       <c r="AT84" t="n">
-        <v>0.09773087140677572</v>
+        <v>0.3821987084196674</v>
       </c>
       <c r="AU84" t="n">
-        <v>0.6408639200334638</v>
+        <v>1.486931388313741</v>
       </c>
       <c r="AV84" t="n">
-        <v>2.431907443329538</v>
-      </c>
-      <c r="AW84" t="n">
-        <v>35.31349971194724</v>
-      </c>
+        <v>0.68655923873295</v>
+      </c>
+      <c r="AW84" t="inlineStr"/>
       <c r="AX84" t="n">
-        <v>0.4730584441428192</v>
+        <v>0.7911004105834609</v>
       </c>
       <c r="AY84" t="n">
-        <v>241.9959224066451</v>
+        <v>4.184749180728712</v>
       </c>
       <c r="AZ84" t="inlineStr"/>
       <c r="BA84" t="n">
@@ -16635,12 +16633,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ALAB</t>
+          <t>CRDO</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Astera Labs</t>
+          <t>Credo Technology</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -16650,29 +16648,29 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>PCIe/CXL connectivity chips</t>
+          <t>Connectors / cabling</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PCIe/CXL/connectivity chips para AI servers</t>
+          <t>High-speed connectivity, active electrical cables</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
         <v>1</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Nasdaq-100, SOXX</t>
+          <t>SOXX</t>
         </is>
       </c>
       <c r="K85" s="1" t="n">
@@ -16712,7 +16710,7 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>Astera Labs, Inc.</t>
+          <t>Credo Technology Group Holding Ltd</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
@@ -16731,7 +16729,7 @@
         </is>
       </c>
       <c r="X85" t="n">
-        <v>55794540544</v>
+        <v>48465604608</v>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
@@ -16742,7 +16740,7 @@
         <v>1</v>
       </c>
       <c r="AA85" t="n">
-        <v>55794540544</v>
+        <v>48465604608</v>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
@@ -16750,71 +16748,71 @@
         </is>
       </c>
       <c r="AC85" s="2" t="n">
-        <v>45371</v>
+        <v>44588</v>
       </c>
       <c r="AD85" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="AE85" t="n">
-        <v>321.6099853515625</v>
+        <v>259.8999938964844</v>
       </c>
       <c r="AF85" t="n">
-        <v>355.0372982788086</v>
+        <v>239.3875991821289</v>
       </c>
       <c r="AG85" t="n">
-        <v>215.8044997787476</v>
+        <v>171.0870751953125</v>
       </c>
       <c r="AH85" t="n">
-        <v>-0.09415155277853604</v>
+        <v>0.08568695615159827</v>
       </c>
       <c r="AI85" t="n">
-        <v>0.4902839638714274</v>
+        <v>0.5191094569813839</v>
       </c>
       <c r="AJ85" t="n">
-        <v>0.645180237867184</v>
+        <v>0.39921498400066</v>
       </c>
       <c r="AK85" t="n">
-        <v>483.0199890136719</v>
+        <v>302.5199890136719</v>
       </c>
       <c r="AL85" t="n">
-        <v>100.2699966430664</v>
+        <v>87.80999755859375</v>
       </c>
       <c r="AM85" t="n">
-        <v>-0.3341683726002914</v>
+        <v>-0.1408832363644618</v>
       </c>
       <c r="AN85" t="n">
-        <v>2.207439873528724</v>
+        <v>1.959799580031404</v>
       </c>
       <c r="AO85" t="n">
-        <v>58.2180514437172</v>
+        <v>64.6920215204787</v>
       </c>
       <c r="AP85" t="n">
-        <v>2518100</v>
+        <v>3367600</v>
       </c>
       <c r="AQ85" t="n">
-        <v>5391200</v>
+        <v>7790608</v>
       </c>
       <c r="AR85" t="n">
-        <v>0.4670759756640451</v>
+        <v>0.4322640800307242</v>
       </c>
       <c r="AS85" t="n">
-        <v>0.05925166498810941</v>
+        <v>0.2823169690569092</v>
       </c>
       <c r="AT85" t="n">
-        <v>0.3821987084196674</v>
+        <v>0.5095544906810781</v>
       </c>
       <c r="AU85" t="n">
-        <v>1.486931388313741</v>
+        <v>1.140151421866809</v>
       </c>
       <c r="AV85" t="n">
-        <v>0.68655923873295</v>
+        <v>1.21511966113082</v>
       </c>
       <c r="AW85" t="inlineStr"/>
       <c r="AX85" t="n">
-        <v>0.7911004105834609</v>
+        <v>0.8146906275749606</v>
       </c>
       <c r="AY85" t="n">
-        <v>4.184749180728712</v>
+        <v>21.30901308211996</v>
       </c>
       <c r="AZ85" t="inlineStr"/>
       <c r="BA85" t="n">
@@ -16829,12 +16827,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Credo Technology</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -16844,29 +16842,29 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Connectors / cabling</t>
+          <t>Networking silicon + custom AI silicon</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>High-speed connectivity, active electrical cables</t>
+          <t>Networking silicon, custom silicon, optical/DSP</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86" t="n">
         <v>1</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>SOXX</t>
+          <t>S&amp;P 500, Nasdaq-100, SOXX, STOXX Global AI Infrastructure</t>
         </is>
       </c>
       <c r="K86" s="1" t="n">
@@ -16888,10 +16886,10 @@
         </is>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="Q86" s="1" t="n">
         <v>46192</v>
@@ -16906,7 +16904,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>Credo Technology Group Holding Ltd</t>
+          <t>Marvell Technology, Inc.</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -16925,7 +16923,7 @@
         </is>
       </c>
       <c r="X86" t="n">
-        <v>48465604608</v>
+        <v>199272824832</v>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
@@ -16936,7 +16934,7 @@
         <v>1</v>
       </c>
       <c r="AA86" t="n">
-        <v>48465604608</v>
+        <v>199272824832</v>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
@@ -16944,71 +16942,73 @@
         </is>
       </c>
       <c r="AC86" s="2" t="n">
-        <v>44588</v>
+        <v>36707</v>
       </c>
       <c r="AD86" t="n">
-        <v>4.5</v>
+        <v>26.1</v>
       </c>
       <c r="AE86" t="n">
-        <v>259.8999938964844</v>
+        <v>222.0200042724609</v>
       </c>
       <c r="AF86" t="n">
-        <v>239.3875991821289</v>
+        <v>238.0678646850586</v>
       </c>
       <c r="AG86" t="n">
-        <v>171.0870751953125</v>
+        <v>141.380521774292</v>
       </c>
       <c r="AH86" t="n">
-        <v>0.08568695615159827</v>
+        <v>-0.06740876360540082</v>
       </c>
       <c r="AI86" t="n">
-        <v>0.5191094569813839</v>
+        <v>0.5703719401100136</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0.39921498400066</v>
+        <v>0.6838802240744581</v>
       </c>
       <c r="AK86" t="n">
-        <v>302.5199890136719</v>
+        <v>316.3519592285156</v>
       </c>
       <c r="AL86" t="n">
-        <v>87.80999755859375</v>
+        <v>62.17752838134766</v>
       </c>
       <c r="AM86" t="n">
-        <v>-0.1408832363644618</v>
+        <v>-0.2981867259052262</v>
       </c>
       <c r="AN86" t="n">
-        <v>1.959799580031404</v>
+        <v>2.570743483252764</v>
       </c>
       <c r="AO86" t="n">
-        <v>64.6920215204787</v>
+        <v>63.55981374527989</v>
       </c>
       <c r="AP86" t="n">
-        <v>3367600</v>
+        <v>14437700</v>
       </c>
       <c r="AQ86" t="n">
-        <v>7790608</v>
+        <v>39638516</v>
       </c>
       <c r="AR86" t="n">
-        <v>0.4322640800307242</v>
+        <v>0.3642341201673645</v>
       </c>
       <c r="AS86" t="n">
-        <v>0.2823169690569092</v>
+        <v>0.1767013615162132</v>
       </c>
       <c r="AT86" t="n">
-        <v>0.5095544906810781</v>
+        <v>0.2554399539457268</v>
       </c>
       <c r="AU86" t="n">
-        <v>1.140151421866809</v>
+        <v>1.826433498852696</v>
       </c>
       <c r="AV86" t="n">
-        <v>1.21511966113082</v>
-      </c>
-      <c r="AW86" t="inlineStr"/>
+        <v>1.814942292466414</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>2.739770110452003</v>
+      </c>
       <c r="AX86" t="n">
-        <v>0.8146906275749606</v>
+        <v>1.48736776838524</v>
       </c>
       <c r="AY86" t="n">
-        <v>21.30901308211996</v>
+        <v>17.30443078297695</v>
       </c>
       <c r="AZ86" t="inlineStr"/>
       <c r="BA86" t="n">
@@ -17023,12 +17023,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>SMTC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Semtech</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -17038,31 +17038,27 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Networking silicon + custom AI silicon</t>
+          <t>High-speed interconnect / PCIe / CXL</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Networking silicon, custom silicon, optical/DSP</t>
+          <t>Signal integrity/connectivity</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>S&amp;P 500, Nasdaq-100, SOXX, STOXX Global AI Infrastructure</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" s="1" t="n">
         <v>46195</v>
       </c>
@@ -17082,10 +17078,10 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="Q87" s="1" t="n">
         <v>46192</v>
@@ -17096,11 +17092,11 @@
         </is>
       </c>
       <c r="S87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>Marvell Technology, Inc.</t>
+          <t>Semtech Corporation</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -17119,7 +17115,7 @@
         </is>
       </c>
       <c r="X87" t="n">
-        <v>199272824832</v>
+        <v>13073767424</v>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
@@ -17130,7 +17126,7 @@
         <v>1</v>
       </c>
       <c r="AA87" t="n">
-        <v>199272824832</v>
+        <v>13073767424</v>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
@@ -17138,73 +17134,73 @@
         </is>
       </c>
       <c r="AC87" s="2" t="n">
-        <v>36707</v>
+        <v>29297</v>
       </c>
       <c r="AD87" t="n">
-        <v>26.1</v>
+        <v>46.4</v>
       </c>
       <c r="AE87" t="n">
-        <v>222.0200042724609</v>
+        <v>140.3500061035156</v>
       </c>
       <c r="AF87" t="n">
-        <v>238.0678646850586</v>
+        <v>141.1516000366211</v>
       </c>
       <c r="AG87" t="n">
-        <v>141.3805215835571</v>
+        <v>102.5627501678467</v>
       </c>
       <c r="AH87" t="n">
-        <v>-0.06740876360540082</v>
+        <v>-0.005678957467697865</v>
       </c>
       <c r="AI87" t="n">
-        <v>0.5703719422285844</v>
+        <v>0.3684306034484166</v>
       </c>
       <c r="AJ87" t="n">
-        <v>0.6838802263461616</v>
+        <v>0.3762462473522086</v>
       </c>
       <c r="AK87" t="n">
-        <v>316.3519592285156</v>
+        <v>174.7299957275391</v>
       </c>
       <c r="AL87" t="n">
-        <v>62.17752838134766</v>
+        <v>48.47000122070312</v>
       </c>
       <c r="AM87" t="n">
-        <v>-0.2981867259052262</v>
+        <v>-0.1967606619623172</v>
       </c>
       <c r="AN87" t="n">
-        <v>2.570743483252764</v>
+        <v>1.895605582191889</v>
       </c>
       <c r="AO87" t="n">
-        <v>63.55981374527989</v>
+        <v>59.4234848024937</v>
       </c>
       <c r="AP87" t="n">
-        <v>14437700</v>
+        <v>1917400</v>
       </c>
       <c r="AQ87" t="n">
-        <v>39638516</v>
+        <v>3205526</v>
       </c>
       <c r="AR87" t="n">
-        <v>0.3642341201673645</v>
+        <v>0.5981545618410208</v>
       </c>
       <c r="AS87" t="n">
-        <v>0.1767013615162132</v>
+        <v>0.1231594680841777</v>
       </c>
       <c r="AT87" t="n">
-        <v>0.2554399539457268</v>
+        <v>0.01968909274836128</v>
       </c>
       <c r="AU87" t="n">
-        <v>1.826433498852696</v>
+        <v>0.6109963461751837</v>
       </c>
       <c r="AV87" t="n">
-        <v>1.814942020173138</v>
+        <v>1.778107775767989</v>
       </c>
       <c r="AW87" t="n">
-        <v>2.739770110452003</v>
+        <v>1.196057055838012</v>
       </c>
       <c r="AX87" t="n">
-        <v>1.48736798099246</v>
+        <v>0.8648684841845169</v>
       </c>
       <c r="AY87" t="n">
-        <v>17.30443510057087</v>
+        <v>120.3837890625</v>
       </c>
       <c r="AZ87" t="inlineStr"/>
       <c r="BA87" t="n">
@@ -17219,12 +17215,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>KEYS</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Semtech</t>
+          <t>Keysight Technologies</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -17234,19 +17230,19 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>High-speed interconnect / PCIe / CXL</t>
+          <t>Switching / networking silicon</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Signal integrity/connectivity</t>
+          <t>Testing/simulation/electronics measurement</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -17254,7 +17250,11 @@
       <c r="I88" t="n">
         <v>0</v>
       </c>
-      <c r="J88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
+        </is>
+      </c>
       <c r="K88" s="1" t="n">
         <v>46195</v>
       </c>
@@ -17292,7 +17292,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>Semtech Corporation</t>
+          <t>Keysight Technologies, Inc.</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -17302,7 +17302,7 @@
       </c>
       <c r="V88" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>Scientific &amp; Technical Instruments</t>
         </is>
       </c>
       <c r="W88" t="inlineStr">
@@ -17311,7 +17311,7 @@
         </is>
       </c>
       <c r="X88" t="n">
-        <v>13073767424</v>
+        <v>61149777920</v>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
@@ -17322,7 +17322,7 @@
         <v>1</v>
       </c>
       <c r="AA88" t="n">
-        <v>13073767424</v>
+        <v>61149777920</v>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
@@ -17330,81 +17330,81 @@
         </is>
       </c>
       <c r="AC88" s="2" t="n">
-        <v>29297</v>
+        <v>41932</v>
       </c>
       <c r="AD88" t="n">
-        <v>46.4</v>
+        <v>11.8</v>
       </c>
       <c r="AE88" t="n">
-        <v>140.3500061035156</v>
+        <v>357.8200073242188</v>
       </c>
       <c r="AF88" t="n">
-        <v>141.1516000366211</v>
+        <v>334.0342010498047</v>
       </c>
       <c r="AG88" t="n">
-        <v>102.5627501678467</v>
+        <v>275.3318492889404</v>
       </c>
       <c r="AH88" t="n">
-        <v>-0.005678957467697865</v>
+        <v>0.07120769729464804</v>
       </c>
       <c r="AI88" t="n">
-        <v>0.3684306034484166</v>
+        <v>0.2995954091337727</v>
       </c>
       <c r="AJ88" t="n">
-        <v>0.3762462473522086</v>
+        <v>0.2132058165899307</v>
       </c>
       <c r="AK88" t="n">
-        <v>174.7299957275391</v>
+        <v>373.3399963378906</v>
       </c>
       <c r="AL88" t="n">
-        <v>48.47000122070312</v>
+        <v>158.5099945068359</v>
       </c>
       <c r="AM88" t="n">
-        <v>-0.1967606619623172</v>
+        <v>-0.04157065721837516</v>
       </c>
       <c r="AN88" t="n">
-        <v>1.895605582191889</v>
+        <v>1.257397134089152</v>
       </c>
       <c r="AO88" t="n">
-        <v>59.4234848024937</v>
+        <v>68.48267044791481</v>
       </c>
       <c r="AP88" t="n">
-        <v>1917400</v>
+        <v>926800</v>
       </c>
       <c r="AQ88" t="n">
-        <v>3205526</v>
+        <v>1402828</v>
       </c>
       <c r="AR88" t="n">
-        <v>0.5981545618410208</v>
+        <v>0.6606654557793258</v>
       </c>
       <c r="AS88" t="n">
-        <v>0.1231594680841777</v>
+        <v>0.09851716223727869</v>
       </c>
       <c r="AT88" t="n">
-        <v>0.01968909274836128</v>
+        <v>-0.01059031283534839</v>
       </c>
       <c r="AU88" t="n">
-        <v>0.6109963461751837</v>
+        <v>0.5226383290392287</v>
       </c>
       <c r="AV88" t="n">
-        <v>1.778107775767989</v>
+        <v>1.215740882734476</v>
       </c>
       <c r="AW88" t="n">
-        <v>1.196057055838012</v>
+        <v>1.141736946415687</v>
       </c>
       <c r="AX88" t="n">
-        <v>0.8648684841845169</v>
+        <v>0.7320296900484096</v>
       </c>
       <c r="AY88" t="n">
-        <v>120.3837890625</v>
+        <v>11.66619494952987</v>
       </c>
       <c r="AZ88" t="inlineStr"/>
       <c r="BA88" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>Strong momentum</t>
+          <t>Positive momentum</t>
         </is>
       </c>
     </row>
@@ -17538,16 +17538,16 @@
         <v>390.3288507080078</v>
       </c>
       <c r="AG89" t="n">
-        <v>368.2457229614258</v>
+        <v>368.2457228088379</v>
       </c>
       <c r="AH89" t="n">
         <v>0.006817685962849707</v>
       </c>
       <c r="AI89" t="n">
-        <v>0.06719498891652087</v>
+        <v>0.06719498935872825</v>
       </c>
       <c r="AJ89" t="n">
-        <v>0.05996845684721031</v>
+        <v>0.05996845728642342</v>
       </c>
       <c r="AK89" t="n">
         <v>480.8090515136719</v>
@@ -17583,16 +17583,16 @@
         <v>0.2130197017444788</v>
       </c>
       <c r="AV89" t="n">
-        <v>0.2719514541587664</v>
+        <v>0.2719513285240669</v>
       </c>
       <c r="AW89" t="n">
-        <v>7.90640422707655</v>
+        <v>7.906403457089615</v>
       </c>
       <c r="AX89" t="n">
         <v>0.1346806173757082</v>
       </c>
       <c r="AY89" t="n">
-        <v>345.0662981117114</v>
+        <v>345.0664070971853</v>
       </c>
       <c r="AZ89" t="inlineStr"/>
       <c r="BA89" t="n">
@@ -17912,22 +17912,22 @@
         <v>25.3</v>
       </c>
       <c r="AE91" t="n">
-        <v>960</v>
+        <v>966.5</v>
       </c>
       <c r="AF91" t="n">
-        <v>946.9299999999999</v>
+        <v>945.86</v>
       </c>
       <c r="AG91" t="n">
-        <v>863.7424999999999</v>
+        <v>864.885</v>
       </c>
       <c r="AH91" t="n">
-        <v>0.01380249860074145</v>
+        <v>0.02182141120250347</v>
       </c>
       <c r="AI91" t="n">
-        <v>0.1114423569524483</v>
+        <v>0.1174896084450534</v>
       </c>
       <c r="AJ91" t="n">
-        <v>0.09631053236352272</v>
+        <v>0.09362516403914967</v>
       </c>
       <c r="AK91" t="n">
         <v>1112</v>
@@ -17936,43 +17936,43 @@
         <v>540</v>
       </c>
       <c r="AM91" t="n">
-        <v>-0.1366906474820144</v>
+        <v>-0.1308453237410072</v>
       </c>
       <c r="AN91" t="n">
-        <v>0.7777777777777777</v>
+        <v>0.7898148148148147</v>
       </c>
       <c r="AO91" t="n">
-        <v>66.66666666666666</v>
+        <v>70.54631828978623</v>
       </c>
       <c r="AP91" t="n">
-        <v>254225</v>
+        <v>282702</v>
       </c>
       <c r="AQ91" t="n">
-        <v>139053.46</v>
+        <v>139623</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.828253680275198</v>
+        <v>2.024752368879053</v>
       </c>
       <c r="AS91" t="n">
-        <v>0.05263157894736836</v>
+        <v>0.06854615809839681</v>
       </c>
       <c r="AT91" t="n">
-        <v>-0.09090909090909094</v>
+        <v>-0.07600382409177819</v>
       </c>
       <c r="AU91" t="n">
-        <v>0.1573236889692586</v>
+        <v>0.1644578313253011</v>
       </c>
       <c r="AV91" t="n">
-        <v>0.7219730941704037</v>
+        <v>0.7604735883424407</v>
       </c>
       <c r="AW91" t="n">
-        <v>2.383701711122197</v>
+        <v>2.363077107358014</v>
       </c>
       <c r="AX91" t="n">
-        <v>0.1650485436893203</v>
+        <v>0.1729368932038835</v>
       </c>
       <c r="AY91" t="n">
-        <v>27.42316729092432</v>
+        <v>27.61561905140535</v>
       </c>
       <c r="AZ91" t="inlineStr"/>
       <c r="BA91" t="n">
@@ -18350,13 +18350,13 @@
         <v>3.486945008676512</v>
       </c>
       <c r="AW93" t="n">
-        <v>22.59788502624816</v>
+        <v>22.59788052094044</v>
       </c>
       <c r="AX93" t="n">
         <v>0.5141953560504113</v>
       </c>
       <c r="AY93" t="n">
-        <v>202.7534559842768</v>
+        <v>202.7534769769822</v>
       </c>
       <c r="AZ93" t="inlineStr"/>
       <c r="BA93" t="n">
@@ -18690,16 +18690,16 @@
         <v>176.4689997863769</v>
       </c>
       <c r="AG95" t="n">
-        <v>138.6813031387329</v>
+        <v>138.681303024292</v>
       </c>
       <c r="AH95" t="n">
         <v>-0.05938150216694227</v>
       </c>
       <c r="AI95" t="n">
-        <v>0.1969169724855577</v>
+        <v>0.1969169734732632</v>
       </c>
       <c r="AJ95" t="n">
-        <v>0.2724786672204995</v>
+        <v>0.2724786682705591</v>
       </c>
       <c r="AK95" t="n">
         <v>255.6900024414062</v>
@@ -18735,16 +18735,16 @@
         <v>0.2479745676758427</v>
       </c>
       <c r="AV95" t="n">
-        <v>1.551771602772806</v>
+        <v>1.551771303483166</v>
       </c>
       <c r="AW95" t="n">
-        <v>3.634858449899055</v>
+        <v>3.634856968840582</v>
       </c>
       <c r="AX95" t="n">
-        <v>0.8369328618149012</v>
+        <v>0.8369327067210199</v>
       </c>
       <c r="AY95" t="n">
-        <v>215.5267532612938</v>
+        <v>215.5268206025819</v>
       </c>
       <c r="AZ95" t="inlineStr"/>
       <c r="BA95" t="n">
@@ -19082,16 +19082,16 @@
         <v>85.73300018310547</v>
       </c>
       <c r="AG97" t="n">
-        <v>75.68503484725952</v>
+        <v>75.68503492355347</v>
       </c>
       <c r="AH97" t="n">
         <v>-0.07655164289297167</v>
       </c>
       <c r="AI97" t="n">
-        <v>0.04604560635690835</v>
+        <v>0.04604560530244672</v>
       </c>
       <c r="AJ97" t="n">
-        <v>0.1327602657001326</v>
+        <v>0.1327602645582586</v>
       </c>
       <c r="AK97" t="n">
         <v>102.7099990844727</v>
@@ -19130,13 +19130,13 @@
         <v>0.2322701088787473</v>
       </c>
       <c r="AW97" t="n">
-        <v>0.1777551742156562</v>
+        <v>0.1777554415591225</v>
       </c>
       <c r="AX97" t="n">
         <v>0.2307528998742794</v>
       </c>
       <c r="AY97" t="n">
-        <v>449.6599906102052</v>
+        <v>449.6598377067398</v>
       </c>
       <c r="AZ97" t="inlineStr"/>
       <c r="BA97" t="n">
@@ -19264,22 +19264,22 @@
         <v>25.2</v>
       </c>
       <c r="AE98" t="n">
-        <v>142.5</v>
+        <v>140</v>
       </c>
       <c r="AF98" t="n">
-        <v>140.412000579834</v>
+        <v>140.1160005187988</v>
       </c>
       <c r="AG98" t="n">
-        <v>132.4874848556518</v>
+        <v>132.5909002685547</v>
       </c>
       <c r="AH98" t="n">
-        <v>0.01487051969592046</v>
+        <v>-0.0008278891659005971</v>
       </c>
       <c r="AI98" t="n">
-        <v>0.07557329022629578</v>
+        <v>0.05587939833305788</v>
       </c>
       <c r="AJ98" t="n">
-        <v>0.05981331544497248</v>
+        <v>0.05675427374731234</v>
       </c>
       <c r="AK98" t="n">
         <v>164.8832092285156</v>
@@ -19288,13 +19288,13 @@
         <v>110.5768280029297</v>
       </c>
       <c r="AM98" t="n">
-        <v>-0.1357519018051996</v>
+        <v>-0.1509141491419504</v>
       </c>
       <c r="AN98" t="n">
-        <v>0.2886967601948622</v>
+        <v>0.2660880451037242</v>
       </c>
       <c r="AO98" t="n">
-        <v>62.46973182228285</v>
+        <v>61.57516861134175</v>
       </c>
       <c r="AP98" t="n">
         <v>140962</v>
@@ -19306,25 +19306,25 @@
         <v>0.8047257097995658</v>
       </c>
       <c r="AS98" t="n">
-        <v>0.06422708361110252</v>
+        <v>0.03473759676446009</v>
       </c>
       <c r="AT98" t="n">
-        <v>-0.05957709527737298</v>
+        <v>-0.09138615048778242</v>
       </c>
       <c r="AU98" t="n">
-        <v>0.0560935480890612</v>
+        <v>0.03305444550382886</v>
       </c>
       <c r="AV98" t="n">
-        <v>0.02912939757634092</v>
+        <v>0.05522949329998328</v>
       </c>
       <c r="AW98" t="n">
-        <v>0.8707441226249568</v>
+        <v>0.8080909500269489</v>
       </c>
       <c r="AX98" t="n">
-        <v>0.1309996341370812</v>
+        <v>0.1111575352925711</v>
       </c>
       <c r="AY98" t="n">
-        <v>7.823549419692291</v>
+        <v>7.668752354666166</v>
       </c>
       <c r="AZ98" t="inlineStr"/>
       <c r="BA98" t="n">
@@ -19502,13 +19502,13 @@
         <v>1.605326859739912</v>
       </c>
       <c r="AW99" t="n">
-        <v>0.9637003554533097</v>
+        <v>0.9637001845666304</v>
       </c>
       <c r="AX99" t="n">
         <v>0.6528417589211029</v>
       </c>
       <c r="AY99" t="n">
-        <v>17.00699540585473</v>
+        <v>17.00699181349152</v>
       </c>
       <c r="AZ99" t="inlineStr"/>
       <c r="BA99" t="n">
@@ -19636,22 +19636,22 @@
         <v>19.3</v>
       </c>
       <c r="AE100" t="n">
-        <v>130.6000061035156</v>
+        <v>127.9499969482422</v>
       </c>
       <c r="AF100" t="n">
-        <v>135.3640007019043</v>
+        <v>135.0160005187988</v>
       </c>
       <c r="AG100" t="n">
-        <v>112.1015115737915</v>
+        <v>112.2871462631226</v>
       </c>
       <c r="AH100" t="n">
-        <v>-0.03519395536247372</v>
+        <v>-0.0523345643731522</v>
       </c>
       <c r="AI100" t="n">
-        <v>0.1650155673195128</v>
+        <v>0.1394892577322862</v>
       </c>
       <c r="AJ100" t="n">
-        <v>0.2075127159440677</v>
+        <v>0.2024172401925302</v>
       </c>
       <c r="AK100" t="n">
         <v>156.8999938964844</v>
@@ -19660,13 +19660,13 @@
         <v>72.51947784423828</v>
       </c>
       <c r="AM100" t="n">
-        <v>-0.1676226183305036</v>
+        <v>-0.1845124160255998</v>
       </c>
       <c r="AN100" t="n">
-        <v>0.80089556607159</v>
+        <v>0.7643535330337172</v>
       </c>
       <c r="AO100" t="n">
-        <v>55.36232666067077</v>
+        <v>59.04172913454833</v>
       </c>
       <c r="AP100" t="n">
         <v>863053</v>
@@ -19678,25 +19678,25 @@
         <v>0.7015661979077834</v>
       </c>
       <c r="AS100" t="n">
-        <v>-0.005331278994458621</v>
+        <v>0.02074191069621656</v>
       </c>
       <c r="AT100" t="n">
-        <v>-0.07046259001056498</v>
+        <v>-0.1139196512711396</v>
       </c>
       <c r="AU100" t="n">
-        <v>0.3266123901135394</v>
+        <v>0.3060148448387894</v>
       </c>
       <c r="AV100" t="n">
-        <v>0.7632459209368048</v>
+        <v>0.7077855040904788</v>
       </c>
       <c r="AW100" t="n">
-        <v>3.399231021381805</v>
+        <v>3.320784872954745</v>
       </c>
       <c r="AX100" t="n">
-        <v>0.4638787698632261</v>
+        <v>0.4341751560726326</v>
       </c>
       <c r="AY100" t="n">
-        <v>11.47363703295033</v>
+        <v>11.22053404066811</v>
       </c>
       <c r="AZ100" t="inlineStr"/>
       <c r="BA100" t="n">
@@ -19879,10 +19879,10 @@
         <v>-0.07815316156307239</v>
       </c>
       <c r="AV101" t="n">
-        <v>0.05573531284137534</v>
+        <v>0.05573523418857418</v>
       </c>
       <c r="AW101" t="n">
-        <v>0.5611561999085617</v>
+        <v>0.5611563718960657</v>
       </c>
       <c r="AX101" t="n">
         <v>-0.06641367136488729</v>
@@ -20019,19 +20019,19 @@
         <v>54.29000091552734</v>
       </c>
       <c r="AF102" t="n">
-        <v>65.82533477783203</v>
+        <v>65.28073028564454</v>
       </c>
       <c r="AG102" t="n">
-        <v>43.06367395401001</v>
+        <v>43.19921054840088</v>
       </c>
       <c r="AH102" t="n">
-        <v>-0.1752415525304618</v>
+        <v>-0.168361005185233</v>
       </c>
       <c r="AI102" t="n">
-        <v>0.2606913421624577</v>
+        <v>0.2567359501790021</v>
       </c>
       <c r="AJ102" t="n">
-        <v>0.5285582657933554</v>
+        <v>0.5111556312470869</v>
       </c>
       <c r="AK102" t="n">
         <v>79.81999969482422</v>
@@ -20046,37 +20046,37 @@
         <v>1.57982030549697</v>
       </c>
       <c r="AO102" t="n">
-        <v>55.89875265523077</v>
+        <v>51.96261598945432</v>
       </c>
       <c r="AP102" t="n">
         <v>4590600</v>
       </c>
       <c r="AQ102" t="n">
-        <v>12064316</v>
+        <v>11973848</v>
       </c>
       <c r="AR102" t="n">
-        <v>0.3805105900740663</v>
+        <v>0.3833855248538314</v>
       </c>
       <c r="AS102" t="n">
-        <v>-0.1350963753448162</v>
+        <v>-0.1252014225882321</v>
       </c>
       <c r="AT102" t="n">
-        <v>-0.155774808869141</v>
+        <v>-0.1149452006986013</v>
       </c>
       <c r="AU102" t="n">
         <v>0.6217244421796095</v>
       </c>
       <c r="AV102" t="n">
-        <v>1.098100412306465</v>
+        <v>1.120808839570873</v>
       </c>
       <c r="AW102" t="n">
-        <v>0.3446652022407248</v>
+        <v>0.3260812159867732</v>
       </c>
       <c r="AX102" t="n">
         <v>0.991456290573157</v>
       </c>
       <c r="AY102" t="n">
-        <v>23.79367092149746</v>
+        <v>23.79366282265363</v>
       </c>
       <c r="AZ102" t="inlineStr"/>
       <c r="BA102" t="n">
@@ -20458,7 +20458,7 @@
         <v>0.6275234800243652</v>
       </c>
       <c r="AY104" t="n">
-        <v>68.9628886795329</v>
+        <v>68.96289742120172</v>
       </c>
       <c r="AZ104" t="inlineStr"/>
       <c r="BA104" t="n">
@@ -20596,16 +20596,16 @@
         <v>412.4048596191406</v>
       </c>
       <c r="AG105" t="n">
-        <v>375.9748469543457</v>
+        <v>375.974847869873</v>
       </c>
       <c r="AH105" t="n">
         <v>0.09482223410897328</v>
       </c>
       <c r="AI105" t="n">
-        <v>0.2009048302650189</v>
+        <v>0.2009048273407243</v>
       </c>
       <c r="AJ105" t="n">
-        <v>0.09689481346931328</v>
+        <v>0.09689481079829099</v>
       </c>
       <c r="AK105" t="n">
         <v>459.9599914550781</v>
@@ -20638,7 +20638,7 @@
         <v>0.1331385831333214</v>
       </c>
       <c r="AU105" t="n">
-        <v>0.1696518915014795</v>
+        <v>0.1696517990325344</v>
       </c>
       <c r="AV105" t="n">
         <v>0.285677241923957</v>
@@ -20650,7 +20650,7 @@
         <v>0.3909962647791967</v>
       </c>
       <c r="AY105" t="n">
-        <v>1309.460286687587</v>
+        <v>1309.460400039927</v>
       </c>
       <c r="AZ105" t="inlineStr"/>
       <c r="BA105" t="n">
@@ -20788,28 +20788,28 @@
         <v>161.232056274414</v>
       </c>
       <c r="AG106" t="n">
-        <v>131.6645709609985</v>
+        <v>131.6645710372925</v>
       </c>
       <c r="AH106" t="n">
         <v>0.06300200685864699</v>
       </c>
       <c r="AI106" t="n">
-        <v>0.301716917001289</v>
+        <v>0.3017169162469999</v>
       </c>
       <c r="AJ106" t="n">
-        <v>0.2245667539688709</v>
+        <v>0.2245667532592872</v>
       </c>
       <c r="AK106" t="n">
         <v>184.09619140625</v>
       </c>
       <c r="AL106" t="n">
-        <v>87.42485809326172</v>
+        <v>87.42486572265625</v>
       </c>
       <c r="AM106" t="n">
         <v>-0.06901930952260971</v>
       </c>
       <c r="AN106" t="n">
-        <v>0.9604263950513445</v>
+        <v>0.9604262239688237</v>
       </c>
       <c r="AO106" t="n">
         <v>68.15045437980628</v>
@@ -20833,16 +20833,16 @@
         <v>0.5176140245821204</v>
       </c>
       <c r="AV106" t="n">
-        <v>0.9213488527635538</v>
+        <v>0.9213486884334954</v>
       </c>
       <c r="AW106" t="n">
         <v>4.571960508642494</v>
       </c>
       <c r="AX106" t="n">
-        <v>0.6120005344529098</v>
+        <v>0.6120006501267066</v>
       </c>
       <c r="AY106" t="n">
-        <v>7.974293878129872</v>
+        <v>7.974295670696314</v>
       </c>
       <c r="AZ106" t="inlineStr"/>
       <c r="BA106" t="n">
@@ -20974,22 +20974,22 @@
         <v>26.6</v>
       </c>
       <c r="AE107" t="n">
-        <v>309.25</v>
+        <v>306.3999938964844</v>
       </c>
       <c r="AF107" t="n">
-        <v>278.4229992675781</v>
+        <v>278.9499993896484</v>
       </c>
       <c r="AG107" t="n">
-        <v>253.9222040557861</v>
+        <v>254.472190322876</v>
       </c>
       <c r="AH107" t="n">
-        <v>0.1107200224604852</v>
+        <v>0.09840471255385341</v>
       </c>
       <c r="AI107" t="n">
-        <v>0.2178927051690938</v>
+        <v>0.2040608190141409</v>
       </c>
       <c r="AJ107" t="n">
-        <v>0.09648937674788471</v>
+        <v>0.09619050724448464</v>
       </c>
       <c r="AK107" t="n">
         <v>311</v>
@@ -20998,43 +20998,43 @@
         <v>206.813720703125</v>
       </c>
       <c r="AM107" t="n">
-        <v>-0.00562700964630225</v>
+        <v>-0.01479101641001812</v>
       </c>
       <c r="AN107" t="n">
-        <v>0.4953069793851794</v>
+        <v>0.4815264328439433</v>
       </c>
       <c r="AO107" t="n">
-        <v>80.13744859730363</v>
+        <v>78.93613650392659</v>
       </c>
       <c r="AP107" t="n">
         <v>528878</v>
       </c>
       <c r="AQ107" t="n">
-        <v>911960.86</v>
+        <v>910201.3</v>
       </c>
       <c r="AR107" t="n">
-        <v>0.5799349765953772</v>
+        <v>0.5810560806713855</v>
       </c>
       <c r="AS107" t="n">
-        <v>0.1323690702620568</v>
+        <v>0.1674603911040538</v>
       </c>
       <c r="AT107" t="n">
-        <v>0.1725118483412322</v>
+        <v>0.1579742510535542</v>
       </c>
       <c r="AU107" t="n">
-        <v>0.1834561226239209</v>
+        <v>0.2234897842819679</v>
       </c>
       <c r="AV107" t="n">
-        <v>0.4237952646865755</v>
+        <v>0.4437236773291533</v>
       </c>
       <c r="AW107" t="n">
-        <v>1.233191021224727</v>
+        <v>1.170263195438176</v>
       </c>
       <c r="AX107" t="n">
-        <v>0.324991518998522</v>
+        <v>0.3127805766662595</v>
       </c>
       <c r="AY107" t="n">
-        <v>15.61814523303686</v>
+        <v>15.46499465795759</v>
       </c>
       <c r="AZ107" t="inlineStr"/>
       <c r="BA107" t="n">
@@ -21224,13 +21224,13 @@
         <v>0.1283942663505433</v>
       </c>
       <c r="AW108" t="n">
-        <v>1.632831311214979</v>
+        <v>1.632831531479225</v>
       </c>
       <c r="AX108" t="n">
         <v>0.2121874216633055</v>
       </c>
       <c r="AY108" t="n">
-        <v>537.6384674420491</v>
+        <v>537.6386114918878</v>
       </c>
       <c r="AZ108" t="inlineStr"/>
       <c r="BA108" t="n">
@@ -21422,7 +21422,7 @@
         <v>0.9043785394344797</v>
       </c>
       <c r="AY109" t="n">
-        <v>75.30977657673184</v>
+        <v>75.30976479228991</v>
       </c>
       <c r="AZ109" t="inlineStr"/>
       <c r="BA109" t="n">
@@ -21614,7 +21614,7 @@
         <v>0.05916672725271321</v>
       </c>
       <c r="AY110" t="n">
-        <v>18.82137636911543</v>
+        <v>18.82137411271324</v>
       </c>
       <c r="AZ110" t="inlineStr"/>
       <c r="BA110" t="n">
@@ -21793,16 +21793,16 @@
         <v>0.1619079811618305</v>
       </c>
       <c r="AV111" t="n">
-        <v>0.6706195201244369</v>
+        <v>0.6706196294924671</v>
       </c>
       <c r="AW111" t="n">
-        <v>1.47392626498661</v>
+        <v>1.473926025153732</v>
       </c>
       <c r="AX111" t="n">
         <v>0.4308437533081064</v>
       </c>
       <c r="AY111" t="n">
-        <v>876.7676888106755</v>
+        <v>876.7672170581523</v>
       </c>
       <c r="AZ111" t="inlineStr"/>
       <c r="BA111" t="n">
@@ -21934,22 +21934,22 @@
         <v>26.4</v>
       </c>
       <c r="AE112" t="n">
-        <v>62.5</v>
+        <v>61.72999954223633</v>
       </c>
       <c r="AF112" t="n">
-        <v>70.98400016784667</v>
+        <v>70.67260009765624</v>
       </c>
       <c r="AG112" t="n">
-        <v>51.48890946388244</v>
+        <v>51.62751790046692</v>
       </c>
       <c r="AH112" t="n">
-        <v>-0.1195198938885617</v>
+        <v>-0.1265356098836454</v>
       </c>
       <c r="AI112" t="n">
-        <v>0.2138536366524024</v>
+        <v>0.1956801731442146</v>
       </c>
       <c r="AJ112" t="n">
-        <v>0.3786269879660067</v>
+        <v>0.3688940117924413</v>
       </c>
       <c r="AK112" t="n">
         <v>88</v>
@@ -21958,43 +21958,43 @@
         <v>31.03618240356445</v>
       </c>
       <c r="AM112" t="n">
-        <v>-0.2897727272727273</v>
+        <v>-0.2985227324745872</v>
       </c>
       <c r="AN112" t="n">
-        <v>1.013778601611195</v>
+        <v>0.9889688344899901</v>
       </c>
       <c r="AO112" t="n">
-        <v>46.43788915322534</v>
+        <v>50.48661375178474</v>
       </c>
       <c r="AP112" t="n">
-        <v>2976643</v>
+        <v>2979014</v>
       </c>
       <c r="AQ112" t="n">
-        <v>4729072.48</v>
+        <v>4729119.9</v>
       </c>
       <c r="AR112" t="n">
-        <v>0.6294348442720421</v>
+        <v>0.6299298945666402</v>
       </c>
       <c r="AS112" t="n">
-        <v>-0.03415235845680842</v>
+        <v>-0.03031731557967066</v>
       </c>
       <c r="AT112" t="n">
-        <v>-0.03310642651384588</v>
+        <v>-0.09140421954688094</v>
       </c>
       <c r="AU112" t="n">
-        <v>0.4573858301784364</v>
+        <v>0.3953566318322221</v>
       </c>
       <c r="AV112" t="n">
-        <v>0.7182083734552747</v>
+        <v>0.6968085256975205</v>
       </c>
       <c r="AW112" t="n">
-        <v>0.7687690699463745</v>
+        <v>0.7331408567219155</v>
       </c>
       <c r="AX112" t="n">
-        <v>0.6459147529877161</v>
+        <v>0.6256370711758676</v>
       </c>
       <c r="AY112" t="n">
-        <v>0.2370705589287743</v>
+        <v>0.2218301173442934</v>
       </c>
       <c r="AZ112" t="inlineStr"/>
       <c r="BA112" t="n">
@@ -22133,64 +22133,64 @@
         <v>1402.010009765625</v>
       </c>
       <c r="AF113" t="n">
-        <v>1399.265974121094</v>
+        <v>1412.108571777344</v>
       </c>
       <c r="AG113" t="n">
-        <v>1225.062455444336</v>
+        <v>1220.193063659668</v>
       </c>
       <c r="AH113" t="n">
-        <v>0.001961053649042643</v>
+        <v>-0.007151406211640121</v>
       </c>
       <c r="AI113" t="n">
-        <v>0.1444396190046566</v>
+        <v>0.1490067035462748</v>
       </c>
       <c r="AJ113" t="n">
-        <v>0.1421997041069822</v>
+        <v>0.1572829036923653</v>
       </c>
       <c r="AK113" t="n">
         <v>1687.3154296875</v>
       </c>
       <c r="AL113" t="n">
-        <v>815.0369262695312</v>
+        <v>791.9683227539062</v>
       </c>
       <c r="AM113" t="n">
         <v>-0.1690883725129658</v>
       </c>
       <c r="AN113" t="n">
-        <v>0.7201797422635827</v>
+        <v>0.7702854640579875</v>
       </c>
       <c r="AO113" t="n">
-        <v>55.32070059611894</v>
+        <v>57.86947046501224</v>
       </c>
       <c r="AP113" t="n">
         <v>440300</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1003586</v>
+        <v>975396</v>
       </c>
       <c r="AR113" t="n">
-        <v>0.4387267259607049</v>
+        <v>0.4514064031429286</v>
       </c>
       <c r="AS113" t="n">
-        <v>0.06860519037014101</v>
+        <v>0.01859909107767765</v>
       </c>
       <c r="AT113" t="n">
-        <v>-0.09410897368197091</v>
+        <v>-0.1221433727945653</v>
       </c>
       <c r="AU113" t="n">
-        <v>0.2010179293131833</v>
+        <v>0.2319894500809652</v>
       </c>
       <c r="AV113" t="n">
-        <v>0.6632937173992568</v>
+        <v>0.7702854640579875</v>
       </c>
       <c r="AW113" t="n">
-        <v>2.162363650318415</v>
+        <v>2.117208533164119</v>
       </c>
       <c r="AX113" t="n">
         <v>0.5026610614847582</v>
       </c>
       <c r="AY113" t="n">
-        <v>166.0122584303974</v>
+        <v>166.0122963772504</v>
       </c>
       <c r="AZ113" t="inlineStr"/>
       <c r="BA113" t="n">
@@ -22720,28 +22720,28 @@
         <v>71.66839965820313</v>
       </c>
       <c r="AG116" t="n">
-        <v>54.97803950309753</v>
+        <v>54.97803956985474</v>
       </c>
       <c r="AH116" t="n">
         <v>-0.1244397768156713</v>
       </c>
       <c r="AI116" t="n">
-        <v>0.1413648170641768</v>
+        <v>0.1413648156782721</v>
       </c>
       <c r="AJ116" t="n">
-        <v>0.3035823086082441</v>
+        <v>0.3035823070253665</v>
       </c>
       <c r="AK116" t="n">
         <v>87.34999847412109</v>
       </c>
       <c r="AL116" t="n">
-        <v>30.51562690734863</v>
+        <v>30.51562881469727</v>
       </c>
       <c r="AM116" t="n">
         <v>-0.2816256314121088</v>
       </c>
       <c r="AN116" t="n">
-        <v>1.056323476182258</v>
+        <v>1.056323347653831</v>
       </c>
       <c r="AO116" t="n">
         <v>49.01315763206199</v>
@@ -22762,10 +22762,10 @@
         <v>-0.1411068161179481</v>
       </c>
       <c r="AU116" t="n">
-        <v>0.3383958941900262</v>
+        <v>0.3383957852931296</v>
       </c>
       <c r="AV116" t="n">
-        <v>0.3514805455665957</v>
+        <v>0.3514803234935395</v>
       </c>
       <c r="AW116" t="n">
         <v>-0.327361883053842</v>
@@ -22774,7 +22774,7 @@
         <v>0.6939858510603569</v>
       </c>
       <c r="AY116" t="n">
-        <v>34.96667167508497</v>
+        <v>34.96665201494434</v>
       </c>
       <c r="AZ116" t="inlineStr"/>
       <c r="BA116" t="n">
@@ -22916,28 +22916,28 @@
         <v>672.7850341796875</v>
       </c>
       <c r="AG117" t="n">
-        <v>573.3147856140137</v>
+        <v>573.3147862243652</v>
       </c>
       <c r="AH117" t="n">
         <v>0.01931522619707504</v>
       </c>
       <c r="AI117" t="n">
-        <v>0.1961666548725276</v>
+        <v>0.1961666535990871</v>
       </c>
       <c r="AJ117" t="n">
-        <v>0.173500232440617</v>
+        <v>0.1735002311913074</v>
       </c>
       <c r="AK117" t="n">
         <v>785.1200561523438</v>
       </c>
       <c r="AL117" t="n">
-        <v>372.1830444335938</v>
+        <v>372.1830749511719</v>
       </c>
       <c r="AM117" t="n">
         <v>-0.1265284539313729</v>
       </c>
       <c r="AN117" t="n">
-        <v>0.84258804787985</v>
+        <v>0.8425878967947296</v>
       </c>
       <c r="AO117" t="n">
         <v>62.2852447290829</v>
@@ -22964,13 +22964,13 @@
         <v>0.8181345973530314</v>
       </c>
       <c r="AW117" t="n">
-        <v>6.506793243944874</v>
+        <v>6.50679512471411</v>
       </c>
       <c r="AX117" t="n">
         <v>0.5602701854683556</v>
       </c>
       <c r="AY117" t="n">
-        <v>92.25107027178997</v>
+        <v>92.25108841082779</v>
       </c>
       <c r="AZ117" t="inlineStr"/>
       <c r="BA117" t="n">
@@ -23112,16 +23112,16 @@
         <v>290.968359375</v>
       </c>
       <c r="AG118" t="n">
-        <v>229.633023147583</v>
+        <v>229.6330230712891</v>
       </c>
       <c r="AH118" t="n">
         <v>-0.03913955739791286</v>
       </c>
       <c r="AI118" t="n">
-        <v>0.2175077553744618</v>
+        <v>0.2175077557789702</v>
       </c>
       <c r="AJ118" t="n">
-        <v>0.2671015491878854</v>
+        <v>0.2671015496088709</v>
       </c>
       <c r="AK118" t="n">
         <v>330.5873718261719</v>
@@ -23160,13 +23160,13 @@
         <v>0.4806684544808424</v>
       </c>
       <c r="AW118" t="n">
-        <v>0.6913798637355102</v>
+        <v>0.6913801760027161</v>
       </c>
       <c r="AX118" t="n">
         <v>0.6014129975356362</v>
       </c>
       <c r="AY118" t="n">
-        <v>407.6984280889421</v>
+        <v>407.6983212570057</v>
       </c>
       <c r="AZ118" t="inlineStr"/>
       <c r="BA118" t="n">
@@ -23358,7 +23358,7 @@
         <v>1.008728429463747</v>
       </c>
       <c r="AY119" t="n">
-        <v>110.2970071909981</v>
+        <v>110.2970197721385</v>
       </c>
       <c r="AZ119" t="inlineStr"/>
       <c r="BA119" t="n">
@@ -23498,28 +23498,28 @@
         <v>296.738879699707</v>
       </c>
       <c r="AG120" t="n">
-        <v>251.182854385376</v>
+        <v>251.1828553009033</v>
       </c>
       <c r="AH120" t="n">
         <v>-0.009769138997727578</v>
       </c>
       <c r="AI120" t="n">
-        <v>0.1698250545678892</v>
+        <v>0.1698250503040359</v>
       </c>
       <c r="AJ120" t="n">
-        <v>0.1813659830636247</v>
+        <v>0.1813659787577064</v>
       </c>
       <c r="AK120" t="n">
         <v>376.1517333984375</v>
       </c>
       <c r="AL120" t="n">
-        <v>121.6859588623047</v>
+        <v>121.6859512329102</v>
       </c>
       <c r="AM120" t="n">
         <v>-0.218825887938574</v>
       </c>
       <c r="AN120" t="n">
-        <v>1.414740361871899</v>
+        <v>1.414740513269876</v>
       </c>
       <c r="AO120" t="n">
         <v>52.03098283827845</v>
@@ -23540,7 +23540,7 @@
         <v>-0.2076855550089801</v>
       </c>
       <c r="AU120" t="n">
-        <v>0.2534476142991369</v>
+        <v>0.2534476958862495</v>
       </c>
       <c r="AV120" t="n">
         <v>1.219768018881246</v>
@@ -23549,10 +23549,10 @@
         <v>9.728373581939298</v>
       </c>
       <c r="AX120" t="n">
-        <v>0.6739996757549456</v>
+        <v>0.6739995302358921</v>
       </c>
       <c r="AY120" t="n">
-        <v>28.56984894992791</v>
+        <v>28.56984327425575</v>
       </c>
       <c r="AZ120" t="inlineStr"/>
       <c r="BA120" t="n">
@@ -23683,19 +23683,19 @@
         <v>297.5899963378906</v>
       </c>
       <c r="AF121" t="n">
-        <v>344.8259997558594</v>
+        <v>345.0721997070312</v>
       </c>
       <c r="AG121" t="n">
-        <v>300.4539989471435</v>
+        <v>299.7268489074707</v>
       </c>
       <c r="AH121" t="n">
-        <v>-0.1369850401402805</v>
+        <v>-0.1376007786470581</v>
       </c>
       <c r="AI121" t="n">
-        <v>-0.009532249926075154</v>
+        <v>-0.007129333182426145</v>
       </c>
       <c r="AJ121" t="n">
-        <v>0.1476831760076585</v>
+        <v>0.1512889184430695</v>
       </c>
       <c r="AK121" t="n">
         <v>437.510009765625</v>
@@ -23716,25 +23716,25 @@
         <v>1769500</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1358682</v>
+        <v>1362162</v>
       </c>
       <c r="AR121" t="n">
-        <v>1.302365086164386</v>
+        <v>1.299037853060062</v>
       </c>
       <c r="AS121" t="n">
-        <v>-0.0970903254211456</v>
+        <v>-0.1268155322036072</v>
       </c>
       <c r="AT121" t="n">
-        <v>-0.2827428278725452</v>
+        <v>-0.3155231412982082</v>
       </c>
       <c r="AU121" t="n">
-        <v>0.1041071408959213</v>
+        <v>0.1217535027803331</v>
       </c>
       <c r="AV121" t="n">
-        <v>0.6718539120106215</v>
+        <v>0.6388017090112987</v>
       </c>
       <c r="AW121" t="n">
-        <v>2.221019572506169</v>
+        <v>2.157453542046585</v>
       </c>
       <c r="AX121" t="n">
         <v>0.3072260237933893</v>
@@ -23879,31 +23879,31 @@
         <v>62.77999877929688</v>
       </c>
       <c r="AF122" t="n">
-        <v>67.89210189819336</v>
+        <v>67.90505889892579</v>
       </c>
       <c r="AG122" t="n">
-        <v>60.81401529312134</v>
+        <v>60.7676005935669</v>
       </c>
       <c r="AH122" t="n">
-        <v>-0.07529746429948903</v>
+        <v>-0.07547390728660408</v>
       </c>
       <c r="AI122" t="n">
-        <v>0.03232780267343927</v>
+        <v>0.03311630155005685</v>
       </c>
       <c r="AJ122" t="n">
-        <v>0.1163890687197007</v>
+        <v>0.1174549963408378</v>
       </c>
       <c r="AK122" t="n">
         <v>75.72768402099609</v>
       </c>
       <c r="AL122" t="n">
-        <v>49.78789138793945</v>
+        <v>49.78788757324219</v>
       </c>
       <c r="AM122" t="n">
         <v>-0.1709769077066898</v>
       </c>
       <c r="AN122" t="n">
-        <v>0.2609491390210714</v>
+        <v>0.2609492356337111</v>
       </c>
       <c r="AO122" t="n">
         <v>32.84442359140041</v>
@@ -23912,31 +23912,31 @@
         <v>3153700</v>
       </c>
       <c r="AQ122" t="n">
-        <v>6303188</v>
+        <v>6120322</v>
       </c>
       <c r="AR122" t="n">
-        <v>0.5003341166406586</v>
+        <v>0.5152833462030266</v>
       </c>
       <c r="AS122" t="n">
-        <v>-0.08275216930499751</v>
+        <v>-0.09135048747417029</v>
       </c>
       <c r="AT122" t="n">
-        <v>-0.0257343843645802</v>
+        <v>-0.05581063660235486</v>
       </c>
       <c r="AU122" t="n">
-        <v>-0.03317781446982226</v>
+        <v>-0.02557909639978073</v>
       </c>
       <c r="AV122" t="n">
-        <v>-0.03063283641588954</v>
+        <v>-0.04928299644944112</v>
       </c>
       <c r="AW122" t="n">
-        <v>0.1982229134085289</v>
+        <v>0.1952474218957441</v>
       </c>
       <c r="AX122" t="n">
         <v>0.1864985129296501</v>
       </c>
       <c r="AY122" t="n">
-        <v>4.697840874774061</v>
+        <v>4.697839888427948</v>
       </c>
       <c r="AZ122" t="inlineStr"/>
       <c r="BA122" t="n">
@@ -24068,22 +24068,22 @@
         <v>20.4</v>
       </c>
       <c r="AE123" t="n">
-        <v>141.75</v>
+        <v>140.6999969482422</v>
       </c>
       <c r="AF123" t="n">
-        <v>139.9449993896484</v>
+        <v>139.8789993286133</v>
       </c>
       <c r="AG123" t="n">
-        <v>137.627621421814</v>
+        <v>137.6002473831177</v>
       </c>
       <c r="AH123" t="n">
-        <v>0.01289792860212091</v>
+        <v>0.00586934152781704</v>
       </c>
       <c r="AI123" t="n">
-        <v>0.02995313393923582</v>
+        <v>0.02252720924617191</v>
       </c>
       <c r="AJ123" t="n">
-        <v>0.01683802963310677</v>
+        <v>0.01656066750484042</v>
       </c>
       <c r="AK123" t="n">
         <v>157.5401306152344</v>
@@ -24092,13 +24092,13 @@
         <v>121.6237258911133</v>
       </c>
       <c r="AM123" t="n">
-        <v>-0.1002292593866076</v>
+        <v>-0.1068942472069001</v>
       </c>
       <c r="AN123" t="n">
-        <v>0.1654798351343494</v>
+        <v>0.1568466260785943</v>
       </c>
       <c r="AO123" t="n">
-        <v>65.23518850091085</v>
+        <v>69.04765836635556</v>
       </c>
       <c r="AP123" t="n">
         <v>361800</v>
@@ -24110,25 +24110,25 @@
         <v>0.5618840067032234</v>
       </c>
       <c r="AS123" t="n">
-        <v>0.02941178752008322</v>
+        <v>0.0391433034761417</v>
       </c>
       <c r="AT123" t="n">
-        <v>-0.0106229615467196</v>
+        <v>-0.05432380862520836</v>
       </c>
       <c r="AU123" t="n">
-        <v>-0.04219872246807765</v>
+        <v>-0.04580429939441488</v>
       </c>
       <c r="AV123" t="n">
-        <v>0.07905098810395672</v>
+        <v>0.09652023747177507</v>
       </c>
       <c r="AW123" t="n">
-        <v>0.6081904125501385</v>
+        <v>0.5903934246344744</v>
       </c>
       <c r="AX123" t="n">
-        <v>0.1271776308022379</v>
+        <v>0.1188281426031867</v>
       </c>
       <c r="AY123" t="n">
-        <v>9.468564229311092</v>
+        <v>9.391019083714623</v>
       </c>
       <c r="AZ123" t="inlineStr"/>
       <c r="BA123" t="n">
@@ -24320,7 +24320,7 @@
         <v>0.4878204930926373</v>
       </c>
       <c r="AY124" t="n">
-        <v>236.3409181731074</v>
+        <v>236.3408220135651</v>
       </c>
       <c r="AZ124" t="inlineStr"/>
       <c r="BA124" t="n">
@@ -24435,10 +24435,10 @@
         </is>
       </c>
       <c r="Z125" t="n">
-        <v>0.1050850674510002</v>
+        <v>0.1050425693392754</v>
       </c>
       <c r="AA125" t="n">
-        <v>3562167846.022781</v>
+        <v>3560727247.365189</v>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
@@ -24452,22 +24452,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AE125" t="n">
-        <v>187.3999938964844</v>
+        <v>185.6999969482422</v>
       </c>
       <c r="AF125" t="n">
-        <v>178.503999633789</v>
+        <v>179.3289996337891</v>
       </c>
       <c r="AG125" t="n">
-        <v>177.6258544921875</v>
+        <v>177.4315588760376</v>
       </c>
       <c r="AH125" t="n">
-        <v>0.04983638619272379</v>
+        <v>0.03552686585807896</v>
       </c>
       <c r="AI125" t="n">
-        <v>0.05502655811137425</v>
+        <v>0.04660071818442013</v>
       </c>
       <c r="AJ125" t="n">
-        <v>0.004943791229672367</v>
+        <v>0.01069393049224754</v>
       </c>
       <c r="AK125" t="n">
         <v>210.6000061035156</v>
@@ -24476,43 +24476,43 @@
         <v>110.4240570068359</v>
       </c>
       <c r="AM125" t="n">
-        <v>-0.1101614982652366</v>
+        <v>-0.1182336582793564</v>
       </c>
       <c r="AN125" t="n">
-        <v>0.6970939030512449</v>
+        <v>0.6816987346946164</v>
       </c>
       <c r="AO125" t="n">
-        <v>57.99178777283674</v>
+        <v>56.03959307088023</v>
       </c>
       <c r="AP125" t="n">
-        <v>205422</v>
+        <v>206420</v>
       </c>
       <c r="AQ125" t="n">
-        <v>450376.3</v>
+        <v>448780.46</v>
       </c>
       <c r="AR125" t="n">
-        <v>0.4561119224079953</v>
+        <v>0.4599576371930275</v>
       </c>
       <c r="AS125" t="n">
-        <v>0.1313009405457128</v>
+        <v>0.1146457991895806</v>
       </c>
       <c r="AT125" t="n">
-        <v>-0.07181773372135047</v>
+        <v>-0.07565951921369463</v>
       </c>
       <c r="AU125" t="n">
-        <v>-0.02106019133309844</v>
+        <v>-0.03396166656612065</v>
       </c>
       <c r="AV125" t="n">
-        <v>0.3699729696446163</v>
+        <v>0.3856600875138039</v>
       </c>
       <c r="AW125" t="n">
-        <v>1.447771444925947</v>
+        <v>1.428606023065305</v>
       </c>
       <c r="AX125" t="n">
-        <v>-0.02663102928306815</v>
+        <v>-0.03546093501212844</v>
       </c>
       <c r="AY125" t="n">
-        <v>2.003806901436595</v>
+        <v>1.976557900732935</v>
       </c>
       <c r="AZ125" t="inlineStr"/>
       <c r="BA125" t="n">
@@ -24750,22 +24750,22 @@
         <v>29.8</v>
       </c>
       <c r="AE127" t="n">
-        <v>284.1000061035156</v>
+        <v>284</v>
       </c>
       <c r="AF127" t="n">
-        <v>273.461000366211</v>
+        <v>273.7650006103515</v>
       </c>
       <c r="AG127" t="n">
-        <v>248.2370627593994</v>
+        <v>248.4514437866211</v>
       </c>
       <c r="AH127" t="n">
-        <v>0.03890502017858943</v>
+        <v>0.03738607698876706</v>
       </c>
       <c r="AI127" t="n">
-        <v>0.1444705433808484</v>
+        <v>0.1430804976279763</v>
       </c>
       <c r="AJ127" t="n">
-        <v>0.1016122948218232</v>
+        <v>0.1018853279253655</v>
       </c>
       <c r="AK127" t="n">
         <v>287.4500122070312</v>
@@ -24774,43 +24774,43 @@
         <v>203.75</v>
       </c>
       <c r="AM127" t="n">
-        <v>-0.01165422146895867</v>
+        <v>-0.0120021292764686</v>
       </c>
       <c r="AN127" t="n">
-        <v>0.3943558581767639</v>
+        <v>0.3938650306748466</v>
       </c>
       <c r="AO127" t="n">
-        <v>62.03047050389046</v>
+        <v>61.5148471059201</v>
       </c>
       <c r="AP127" t="n">
-        <v>613430</v>
+        <v>613772</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1022501.2</v>
+        <v>1022508.04</v>
       </c>
       <c r="AR127" t="n">
-        <v>0.5999308362669893</v>
+        <v>0.600261294766934</v>
       </c>
       <c r="AS127" t="n">
-        <v>0.04950126816483502</v>
+        <v>0.07352112305615544</v>
       </c>
       <c r="AT127" t="n">
-        <v>0.1063084875710978</v>
+        <v>0.0753502212668804</v>
       </c>
       <c r="AU127" t="n">
-        <v>0.2091934870980263</v>
+        <v>0.2046659597030753</v>
       </c>
       <c r="AV127" t="n">
-        <v>0.2385907132329286</v>
+        <v>0.2418657173122751</v>
       </c>
       <c r="AW127" t="n">
-        <v>1.267216833643371</v>
+        <v>1.201266836762512</v>
       </c>
       <c r="AX127" t="n">
-        <v>0.2034005082147816</v>
+        <v>0.2029768989461798</v>
       </c>
       <c r="AY127" t="n">
-        <v>28.88561301329391</v>
+        <v>28.87510196358976</v>
       </c>
       <c r="AZ127" t="inlineStr"/>
       <c r="BA127" t="n">
@@ -24942,22 +24942,22 @@
         <v>28.1</v>
       </c>
       <c r="AE128" t="n">
-        <v>235.1999969482422</v>
+        <v>233.5</v>
       </c>
       <c r="AF128" t="n">
-        <v>255.3069989013672</v>
+        <v>257.2139990234375</v>
       </c>
       <c r="AG128" t="n">
-        <v>201.2635311508179</v>
+        <v>201.0559061050415</v>
       </c>
       <c r="AH128" t="n">
-        <v>-0.07875617213648323</v>
+        <v>-0.09219560021411066</v>
       </c>
       <c r="AI128" t="n">
-        <v>0.1686170644198519</v>
+        <v>0.1613685194505456</v>
       </c>
       <c r="AJ128" t="n">
-        <v>0.268520916042418</v>
+        <v>0.2793158082561187</v>
       </c>
       <c r="AK128" t="n">
         <v>320.2999877929688</v>
@@ -24966,43 +24966,43 @@
         <v>105.1371765136719</v>
       </c>
       <c r="AM128" t="n">
-        <v>-0.2656883986512431</v>
+        <v>-0.2709959135217744</v>
       </c>
       <c r="AN128" t="n">
-        <v>1.237077356910542</v>
+        <v>1.220908034082844</v>
       </c>
       <c r="AO128" t="n">
-        <v>54.5154181875746</v>
+        <v>53.51351467269144</v>
       </c>
       <c r="AP128" t="n">
         <v>312149</v>
       </c>
       <c r="AQ128" t="n">
-        <v>482220.78</v>
+        <v>471819.9</v>
       </c>
       <c r="AR128" t="n">
-        <v>0.6473155304505956</v>
+        <v>0.6615850666748053</v>
       </c>
       <c r="AS128" t="n">
-        <v>-0.004233700308722388</v>
+        <v>-0.04303278688524592</v>
       </c>
       <c r="AT128" t="n">
-        <v>-0.0772851997644316</v>
+        <v>-0.08717749329833158</v>
       </c>
       <c r="AU128" t="n">
-        <v>0.3259539080330143</v>
+        <v>0.3335531716499203</v>
       </c>
       <c r="AV128" t="n">
-        <v>0.9822678207854552</v>
+        <v>0.9946694217003613</v>
       </c>
       <c r="AW128" t="n">
-        <v>2.40279675386875</v>
+        <v>2.36131032326349</v>
       </c>
       <c r="AX128" t="n">
-        <v>0.5874096735999594</v>
+        <v>0.575936069706487</v>
       </c>
       <c r="AY128" t="n">
-        <v>110.6878926057542</v>
+        <v>109.8806135597085</v>
       </c>
       <c r="AZ128" t="inlineStr"/>
       <c r="BA128" t="n">
@@ -25577,7 +25577,7 @@
         <v>0.3496686357246537</v>
       </c>
       <c r="AV131" t="n">
-        <v>2.621568791272754</v>
+        <v>2.621569138665244</v>
       </c>
       <c r="AW131" t="n">
         <v>14.73774427866254</v>
@@ -25728,16 +25728,16 @@
         <v>1774.028134765625</v>
       </c>
       <c r="AG132" t="n">
-        <v>1424.464445495606</v>
+        <v>1424.464441223145</v>
       </c>
       <c r="AH132" t="n">
         <v>0.0394874353547483</v>
       </c>
       <c r="AI132" t="n">
-        <v>0.2945777354331141</v>
+        <v>0.2945777393159998</v>
       </c>
       <c r="AJ132" t="n">
-        <v>0.2454000802725531</v>
+        <v>0.2454000840079382</v>
       </c>
       <c r="AK132" t="n">
         <v>1986.870361328125</v>
@@ -25773,16 +25773,16 @@
         <v>0.315572938184012</v>
       </c>
       <c r="AV132" t="n">
-        <v>1.457893969572734</v>
+        <v>1.457894169525142</v>
       </c>
       <c r="AW132" t="n">
-        <v>1.45071988371546</v>
+        <v>1.450719287355041</v>
       </c>
       <c r="AX132" t="n">
         <v>0.5921726633323869</v>
       </c>
       <c r="AY132" t="n">
-        <v>1046.917290394544</v>
+        <v>1046.916864467282</v>
       </c>
       <c r="AZ132" t="inlineStr"/>
       <c r="BA132" t="n">
@@ -25920,28 +25920,28 @@
         <v>44662.633515625</v>
       </c>
       <c r="AG133" t="n">
-        <v>36391.802890625</v>
+        <v>36391.80291015625</v>
       </c>
       <c r="AH133" t="n">
         <v>-0.1308170400113325</v>
       </c>
       <c r="AI133" t="n">
-        <v>0.06672373766897222</v>
+        <v>0.06672373709646817</v>
       </c>
       <c r="AJ133" t="n">
-        <v>0.2272718021104327</v>
+        <v>0.2272718014517638</v>
       </c>
       <c r="AK133" t="n">
         <v>57263.48828125</v>
       </c>
       <c r="AL133" t="n">
-        <v>14136.361328125</v>
+        <v>14136.3603515625</v>
       </c>
       <c r="AM133" t="n">
         <v>-0.3220811172149466</v>
       </c>
       <c r="AN133" t="n">
-        <v>1.746109773153977</v>
+        <v>1.746109962859655</v>
       </c>
       <c r="AO133" t="n">
         <v>44.35504801453413</v>
@@ -25968,13 +25968,13 @@
         <v>1.677551187563324</v>
       </c>
       <c r="AW133" t="n">
-        <v>0.8999286995258073</v>
+        <v>0.8999285179119125</v>
       </c>
       <c r="AX133" t="n">
         <v>0.2290619972653212</v>
       </c>
       <c r="AY133" t="n">
-        <v>298.1767131817404</v>
+        <v>298.1767483637111</v>
       </c>
       <c r="AZ133" t="inlineStr"/>
       <c r="BA133" t="n">
@@ -26161,16 +26161,16 @@
         <v>0.4325993340277117</v>
       </c>
       <c r="AV134" t="n">
-        <v>1.71409130556271</v>
+        <v>1.714091083943792</v>
       </c>
       <c r="AW134" t="n">
-        <v>2.725357014966525</v>
+        <v>2.725356179895042</v>
       </c>
       <c r="AX134" t="n">
         <v>0.8910397213063719</v>
       </c>
       <c r="AY134" t="n">
-        <v>7349.779340709322</v>
+        <v>7349.781722020615</v>
       </c>
       <c r="AZ134" t="inlineStr"/>
       <c r="BA134" t="n">
@@ -26360,13 +26360,13 @@
         <v>1.690580759743954</v>
       </c>
       <c r="AW135" t="n">
-        <v>3.216525454534819</v>
+        <v>3.216525160904033</v>
       </c>
       <c r="AX135" t="n">
         <v>0.6161096794712813</v>
       </c>
       <c r="AY135" t="n">
-        <v>20.82172615966546</v>
+        <v>20.82172419354403</v>
       </c>
       <c r="AZ135" t="inlineStr"/>
       <c r="BA135" t="n">
@@ -26498,22 +26498,22 @@
         <v>27.6</v>
       </c>
       <c r="AE136" t="n">
-        <v>907.7999877929688</v>
+        <v>893.7999877929688</v>
       </c>
       <c r="AF136" t="n">
-        <v>912.337998046875</v>
+        <v>914.8139978027343</v>
       </c>
       <c r="AG136" t="n">
-        <v>733.9455525207519</v>
+        <v>732.8559184265137</v>
       </c>
       <c r="AH136" t="n">
-        <v>-0.004974044996066351</v>
+        <v>-0.02297080068761359</v>
       </c>
       <c r="AI136" t="n">
-        <v>0.2368764749307493</v>
+        <v>0.219612157478392</v>
       </c>
       <c r="AJ136" t="n">
-        <v>0.24305950886061</v>
+        <v>0.2482862931187015</v>
       </c>
       <c r="AK136" t="n">
         <v>1079</v>
@@ -26522,43 +26522,43 @@
         <v>400.14208984375</v>
       </c>
       <c r="AM136" t="n">
-        <v>-0.1586654422678696</v>
+        <v>-0.1716404190982681</v>
       </c>
       <c r="AN136" t="n">
-        <v>1.268694073516365</v>
+        <v>1.233706501962804</v>
       </c>
       <c r="AO136" t="n">
-        <v>57.1344283073559</v>
+        <v>55.04102610612353</v>
       </c>
       <c r="AP136" t="n">
         <v>108009</v>
       </c>
       <c r="AQ136" t="n">
-        <v>194778.2</v>
+        <v>188906.08</v>
       </c>
       <c r="AR136" t="n">
-        <v>0.5545230421063548</v>
+        <v>0.5717603160258262</v>
       </c>
       <c r="AS136" t="n">
-        <v>0.001986741493342992</v>
+        <v>-0.03205548607157149</v>
       </c>
       <c r="AT136" t="n">
-        <v>0.08744609615172161</v>
+        <v>0.05825244332134738</v>
       </c>
       <c r="AU136" t="n">
-        <v>0.3060109769445529</v>
+        <v>0.2906787362540557</v>
       </c>
       <c r="AV136" t="n">
-        <v>1.19916614885193</v>
+        <v>1.188487500650089</v>
       </c>
       <c r="AW136" t="n">
-        <v>1.562602299785321</v>
+        <v>1.516877961654613</v>
       </c>
       <c r="AX136" t="n">
-        <v>0.6456021612102938</v>
+        <v>0.6202238503855109</v>
       </c>
       <c r="AY136" t="n">
-        <v>307.8550478022608</v>
+        <v>303.0918916888835</v>
       </c>
       <c r="AZ136" t="inlineStr"/>
       <c r="BA136" t="n">
@@ -26748,13 +26748,13 @@
         <v>1.146021122991128</v>
       </c>
       <c r="AW137" t="n">
-        <v>5.096770230979607</v>
+        <v>5.096768838925998</v>
       </c>
       <c r="AX137" t="n">
         <v>0.6025882934899727</v>
       </c>
       <c r="AY137" t="n">
-        <v>3356.66351878448</v>
+        <v>3356.662281835218</v>
       </c>
       <c r="AZ137" t="inlineStr"/>
       <c r="BA137" t="n">
@@ -27088,16 +27088,16 @@
         <v>383.4401983642578</v>
       </c>
       <c r="AG139" t="n">
-        <v>301.7146716308594</v>
+        <v>301.7146713256836</v>
       </c>
       <c r="AH139" t="n">
         <v>0.09219119521496455</v>
       </c>
       <c r="AI139" t="n">
-        <v>0.3880332907950244</v>
+        <v>0.3880332921989804</v>
       </c>
       <c r="AJ139" t="n">
-        <v>0.2708702440343627</v>
+        <v>0.2708702453198115</v>
       </c>
       <c r="AK139" t="n">
         <v>483.8399963378906</v>
@@ -27133,16 +27133,16 @@
         <v>0.3314313362930374</v>
       </c>
       <c r="AV139" t="n">
-        <v>2.754803425613409</v>
+        <v>2.754803168770167</v>
       </c>
       <c r="AW139" t="n">
-        <v>2.390787243213779</v>
+        <v>2.390786405386056</v>
       </c>
       <c r="AX139" t="n">
         <v>1.019287610487297</v>
       </c>
       <c r="AY139" t="n">
-        <v>375.0141078131134</v>
+        <v>375.014148059057</v>
       </c>
       <c r="AZ139" t="inlineStr"/>
       <c r="BA139" t="n">
@@ -27275,7 +27275,7 @@
         <v>35712</v>
       </c>
       <c r="AD140" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="AE140" t="n">
         <v>426.3500061035156</v>
@@ -27284,28 +27284,28 @@
         <v>425.0627716064453</v>
       </c>
       <c r="AG140" t="n">
-        <v>362.3197262573242</v>
+        <v>362.3197290039063</v>
       </c>
       <c r="AH140" t="n">
         <v>0.003028339772512822</v>
       </c>
       <c r="AI140" t="n">
-        <v>0.1767231403810354</v>
+        <v>0.1767231314608293</v>
       </c>
       <c r="AJ140" t="n">
-        <v>0.1731703818537338</v>
+        <v>0.1731703729604595</v>
       </c>
       <c r="AK140" t="n">
         <v>477.5700073242188</v>
       </c>
       <c r="AL140" t="n">
-        <v>224.8433685302734</v>
+        <v>224.8433532714844</v>
       </c>
       <c r="AM140" t="n">
         <v>-0.1072512939153866</v>
       </c>
       <c r="AN140" t="n">
-        <v>0.8962089426538318</v>
+        <v>0.8962090713383219</v>
       </c>
       <c r="AO140" t="n">
         <v>64.52163542510675</v>
@@ -27329,16 +27329,16 @@
         <v>0.1697582629354335</v>
       </c>
       <c r="AV140" t="n">
-        <v>0.7886522677975589</v>
+        <v>0.7886521532975281</v>
       </c>
       <c r="AW140" t="n">
-        <v>2.912360675762981</v>
+        <v>2.912361771387349</v>
       </c>
       <c r="AX140" t="n">
         <v>0.3408612332366396</v>
       </c>
       <c r="AY140" t="n">
-        <v>135.5235266287603</v>
+        <v>135.5235578974853</v>
       </c>
       <c r="AZ140" t="inlineStr"/>
       <c r="BA140" t="n">
@@ -27530,7 +27530,7 @@
         <v>1.485575502854449</v>
       </c>
       <c r="AY141" t="n">
-        <v>2.167621661583097</v>
+        <v>2.167621411739689</v>
       </c>
       <c r="AZ141" t="inlineStr"/>
       <c r="BA141" t="n">
@@ -28102,7 +28102,7 @@
         <v>0.5036322881823128</v>
       </c>
       <c r="AW144" t="n">
-        <v>5.183491610110258</v>
+        <v>5.183491039781575</v>
       </c>
       <c r="AX144" t="n">
         <v>0.2884953705768014</v>
@@ -28237,25 +28237,25 @@
         <v>36735</v>
       </c>
       <c r="AD145" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="AE145" t="n">
         <v>165.3800048828125</v>
       </c>
       <c r="AF145" t="n">
-        <v>158.2855993652344</v>
+        <v>159.3053991699219</v>
       </c>
       <c r="AG145" t="n">
-        <v>149.7500498199463</v>
+        <v>149.6904998016358</v>
       </c>
       <c r="AH145" t="n">
-        <v>0.04482028400580029</v>
+        <v>0.03813182569167783</v>
       </c>
       <c r="AI145" t="n">
-        <v>0.1043736217895024</v>
+        <v>0.1048129647637486</v>
       </c>
       <c r="AJ145" t="n">
-        <v>0.05699864244152764</v>
+        <v>0.06423186094660283</v>
       </c>
       <c r="AK145" t="n">
         <v>207.4600067138672</v>
@@ -28270,31 +28270,31 @@
         <v>1.155349897659925</v>
       </c>
       <c r="AO145" t="n">
-        <v>57.0933578046367</v>
+        <v>59.53388320118695</v>
       </c>
       <c r="AP145" t="n">
         <v>468400</v>
       </c>
       <c r="AQ145" t="n">
-        <v>528550</v>
+        <v>524912</v>
       </c>
       <c r="AR145" t="n">
-        <v>0.8861980891117207</v>
+        <v>0.8923400493797056</v>
       </c>
       <c r="AS145" t="n">
-        <v>0.1315772274335394</v>
+        <v>0.1180368234856617</v>
       </c>
       <c r="AT145" t="n">
-        <v>-0.01764182425319849</v>
+        <v>-0.03489726719327413</v>
       </c>
       <c r="AU145" t="n">
-        <v>0.02086422767168217</v>
+        <v>0.06435834525518258</v>
       </c>
       <c r="AV145" t="n">
-        <v>0.8998276747271516</v>
+        <v>0.8765461254612545</v>
       </c>
       <c r="AW145" t="n">
-        <v>3.354892810677065</v>
+        <v>3.465963458387055</v>
       </c>
       <c r="AX145" t="n">
         <v>0.4318615141369047</v>
@@ -28486,13 +28486,13 @@
         <v>0.6786263058407418</v>
       </c>
       <c r="AW146" t="n">
-        <v>7.457230184248068</v>
+        <v>7.457230889274586</v>
       </c>
       <c r="AX146" t="n">
         <v>0.2941667049368542</v>
       </c>
       <c r="AY146" t="n">
-        <v>39.31766911186335</v>
+        <v>39.3176651061496</v>
       </c>
       <c r="AZ146" t="inlineStr"/>
       <c r="BA146" t="n">
@@ -28684,7 +28684,7 @@
         <v>0.4378284780765058</v>
       </c>
       <c r="AY147" t="n">
-        <v>-0.00932621551143975</v>
+        <v>-0.009326294496149967</v>
       </c>
       <c r="AZ147" t="inlineStr"/>
       <c r="BA147" t="n">
@@ -28876,7 +28876,7 @@
         <v>0.4779839617261583</v>
       </c>
       <c r="AY148" t="n">
-        <v>75.72598049939984</v>
+        <v>75.72598747893431</v>
       </c>
       <c r="AZ148" t="inlineStr"/>
       <c r="BA148" t="n">
@@ -29018,16 +29018,16 @@
         <v>421.7149853515625</v>
       </c>
       <c r="AG149" t="n">
-        <v>229.0891036605835</v>
+        <v>229.0891036224365</v>
       </c>
       <c r="AH149" t="n">
         <v>0.1638429143072311</v>
       </c>
       <c r="AI149" t="n">
-        <v>1.142441476770426</v>
+        <v>1.142441477127177</v>
       </c>
       <c r="AJ149" t="n">
-        <v>0.8408338878324475</v>
+        <v>0.8408338881389759</v>
       </c>
       <c r="AK149" t="n">
         <v>494.510009765625</v>
@@ -29066,13 +29066,13 @@
         <v>2.579608409781542</v>
       </c>
       <c r="AW149" t="n">
-        <v>9.8223511428191</v>
+        <v>9.822352963441945</v>
       </c>
       <c r="AX149" t="n">
         <v>2.875583847209645</v>
       </c>
       <c r="AY149" t="n">
-        <v>43.77206586627874</v>
+        <v>43.77206976122071</v>
       </c>
       <c r="AZ149" t="inlineStr"/>
       <c r="BA149" t="n">
@@ -29214,16 +29214,16 @@
         <v>48.49041641235352</v>
       </c>
       <c r="AG150" t="n">
-        <v>30.85659341812134</v>
+        <v>30.85659331321716</v>
       </c>
       <c r="AH150" t="n">
         <v>0.210754689858996</v>
       </c>
       <c r="AI150" t="n">
-        <v>0.9026727380085218</v>
+        <v>0.9026727444771008</v>
       </c>
       <c r="AJ150" t="n">
-        <v>0.5714766615771738</v>
+        <v>0.5714766669197748</v>
       </c>
       <c r="AK150" t="n">
         <v>59.81999969482422</v>
@@ -29256,7 +29256,7 @@
         <v>0.7789053977424432</v>
       </c>
       <c r="AU150" t="n">
-        <v>1.611786669250655</v>
+        <v>1.611786890862744</v>
       </c>
       <c r="AV150" t="n">
         <v>1.811111970593642</v>
@@ -29268,7 +29268,7 @@
         <v>1.451859484580525</v>
       </c>
       <c r="AY150" t="n">
-        <v>7.148465876173342</v>
+        <v>7.148469111820397</v>
       </c>
       <c r="AZ150" t="inlineStr"/>
       <c r="BA150" t="n">
@@ -29410,16 +29410,16 @@
         <v>344.096025390625</v>
       </c>
       <c r="AG151" t="n">
-        <v>285.1131730651855</v>
+        <v>285.1131728363037</v>
       </c>
       <c r="AH151" t="n">
         <v>0.05522871323874456</v>
       </c>
       <c r="AI151" t="n">
-        <v>0.2735293925563373</v>
+        <v>0.2735293935786953</v>
       </c>
       <c r="AJ151" t="n">
-        <v>0.2068752267435716</v>
+        <v>0.2068752277124215</v>
       </c>
       <c r="AK151" t="n">
         <v>385.5466918945312</v>
@@ -29452,19 +29452,19 @@
         <v>0.06873767888217341</v>
       </c>
       <c r="AU151" t="n">
-        <v>0.4273496204070841</v>
+        <v>0.4273495347911667</v>
       </c>
       <c r="AV151" t="n">
         <v>0.6727348568573412</v>
       </c>
       <c r="AW151" t="n">
-        <v>5.228863761710798</v>
+        <v>5.228864984559779</v>
       </c>
       <c r="AX151" t="n">
-        <v>0.511604759434316</v>
+        <v>0.5116046634124181</v>
       </c>
       <c r="AY151" t="n">
-        <v>490.4650212985672</v>
+        <v>490.465179897115</v>
       </c>
       <c r="AZ151" t="inlineStr"/>
       <c r="BA151" t="n">
@@ -29602,16 +29602,16 @@
         <v>144.891393737793</v>
       </c>
       <c r="AG152" t="n">
-        <v>132.3426166534424</v>
+        <v>132.3426162719726</v>
       </c>
       <c r="AH152" t="n">
         <v>0.06038043686492256</v>
       </c>
       <c r="AI152" t="n">
-        <v>0.1609261118961871</v>
+        <v>0.1609261152424877</v>
       </c>
       <c r="AJ152" t="n">
-        <v>0.09482037911651187</v>
+        <v>0.09482038227226663</v>
       </c>
       <c r="AK152" t="n">
         <v>154.7599945068359</v>
@@ -29650,13 +29650,13 @@
         <v>0.4715298365489073</v>
       </c>
       <c r="AW152" t="n">
-        <v>1.350658071902379</v>
+        <v>1.350658346290149</v>
       </c>
       <c r="AX152" t="n">
         <v>0.2635111903289538</v>
       </c>
       <c r="AY152" t="n">
-        <v>48.75187588776065</v>
+        <v>48.75191813980952</v>
       </c>
       <c r="AZ152" t="inlineStr"/>
       <c r="BA152" t="n">
@@ -29771,10 +29771,10 @@
         </is>
       </c>
       <c r="Z153" t="n">
-        <v>1.353582859039307</v>
+        <v>1.353289842605591</v>
       </c>
       <c r="AA153" t="n">
-        <v>172230364643.0859</v>
+        <v>172193081127.793</v>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
@@ -29788,22 +29788,22 @@
         <v>38.1</v>
       </c>
       <c r="AE153" t="n">
-        <v>1525</v>
+        <v>1541</v>
       </c>
       <c r="AF153" t="n">
-        <v>1417.844865722656</v>
+        <v>1423.465827636719</v>
       </c>
       <c r="AG153" t="n">
-        <v>1256.982324829102</v>
+        <v>1258.89030090332</v>
       </c>
       <c r="AH153" t="n">
-        <v>0.07557606397419803</v>
+        <v>0.08256901576514486</v>
       </c>
       <c r="AI153" t="n">
-        <v>0.2132231057483946</v>
+        <v>0.2240939491663816</v>
       </c>
       <c r="AJ153" t="n">
-        <v>0.1279751812862011</v>
+        <v>0.130730633650372</v>
       </c>
       <c r="AK153" t="n">
         <v>1570.339965820312</v>
@@ -29812,43 +29812,43 @@
         <v>1025.915771484375</v>
       </c>
       <c r="AM153" t="n">
-        <v>-0.02887270706163803</v>
+        <v>-0.01868383054556333</v>
       </c>
       <c r="AN153" t="n">
-        <v>0.4864768067592049</v>
+        <v>0.5020726289940556</v>
       </c>
       <c r="AO153" t="n">
-        <v>66.63785598021526</v>
+        <v>68.58303393988021</v>
       </c>
       <c r="AP153" t="n">
-        <v>17087733</v>
+        <v>17092577</v>
       </c>
       <c r="AQ153" t="n">
-        <v>24235687.62</v>
+        <v>24235784.5</v>
       </c>
       <c r="AR153" t="n">
-        <v>0.7050649136894593</v>
+        <v>0.7052619650088076</v>
       </c>
       <c r="AS153" t="n">
-        <v>0.1063974050389755</v>
+        <v>0.1284848042759852</v>
       </c>
       <c r="AT153" t="n">
-        <v>0.3174311063614075</v>
+        <v>0.3232517522466891</v>
       </c>
       <c r="AU153" t="n">
-        <v>0.199941178600652</v>
+        <v>0.1873085734724698</v>
       </c>
       <c r="AV153" t="n">
-        <v>0.3845894160614278</v>
+        <v>0.4349408456006636</v>
       </c>
       <c r="AW153" t="n">
-        <v>12.90441922166756</v>
+        <v>12.82844067455684</v>
       </c>
       <c r="AX153" t="n">
-        <v>0.2741231071681867</v>
+        <v>0.2874909561614267</v>
       </c>
       <c r="AY153" t="n">
-        <v>11.24793094411277</v>
+        <v>11.3764307926887</v>
       </c>
       <c r="AZ153" t="inlineStr"/>
       <c r="BA153" t="n">
@@ -30034,13 +30034,13 @@
         <v>0.6532829826006121</v>
       </c>
       <c r="AW154" t="n">
-        <v>2.579402307328823</v>
+        <v>2.57940265693087</v>
       </c>
       <c r="AX154" t="n">
         <v>0.6198833381969675</v>
       </c>
       <c r="AY154" t="n">
-        <v>8.197662469570856</v>
+        <v>8.197663046666598</v>
       </c>
       <c r="AZ154" t="inlineStr"/>
       <c r="BA154" t="n">
@@ -30232,7 +30232,7 @@
         <v>0.2327867948522071</v>
       </c>
       <c r="AY155" t="n">
-        <v>16.21633246398222</v>
+        <v>16.21633073774683</v>
       </c>
       <c r="AZ155" t="inlineStr"/>
       <c r="BA155" t="n">
@@ -30422,13 +30422,13 @@
         <v>0.4845991080319463</v>
       </c>
       <c r="AW156" t="n">
-        <v>1.938103724442899</v>
+        <v>1.938103470645643</v>
       </c>
       <c r="AX156" t="n">
         <v>0.1518440817993501</v>
       </c>
       <c r="AY156" t="n">
-        <v>707.4421894745338</v>
+        <v>707.4424200333385</v>
       </c>
       <c r="AZ156" t="inlineStr"/>
       <c r="BA156" t="n">
@@ -30766,16 +30766,16 @@
         <v>117.2427130126953</v>
       </c>
       <c r="AG158" t="n">
-        <v>91.37841758728027</v>
+        <v>91.37841808319092</v>
       </c>
       <c r="AH158" t="n">
         <v>-0.0474461274784489</v>
       </c>
       <c r="AI158" t="n">
-        <v>0.2221704342658859</v>
+        <v>0.2221704276331671</v>
       </c>
       <c r="AJ158" t="n">
-        <v>0.2830459982600455</v>
+        <v>0.2830459912969552</v>
       </c>
       <c r="AK158" t="n">
         <v>129.5154876708984</v>
@@ -30808,19 +30808,19 @@
         <v>-0.05170632498490246</v>
       </c>
       <c r="AU158" t="n">
-        <v>0.4665610219795986</v>
+        <v>0.4665608750481027</v>
       </c>
       <c r="AV158" t="n">
-        <v>0.6449134522872288</v>
+        <v>0.6449132674452016</v>
       </c>
       <c r="AW158" t="n">
-        <v>1.315427304559138</v>
+        <v>1.315427487683872</v>
       </c>
       <c r="AX158" t="n">
         <v>0.4821831674877435</v>
       </c>
       <c r="AY158" t="n">
-        <v>2253.589070486988</v>
+        <v>2253.588561811669</v>
       </c>
       <c r="AZ158" t="inlineStr"/>
       <c r="BA158" t="n">
@@ -32428,16 +32428,16 @@
         <v>390.3288507080078</v>
       </c>
       <c r="AG5" t="n">
-        <v>368.2457229614258</v>
+        <v>368.2457228088379</v>
       </c>
       <c r="AH5" t="n">
         <v>0.006817685962849707</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.06719498891652087</v>
+        <v>0.06719498935872825</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.05996845684721031</v>
+        <v>0.05996845728642342</v>
       </c>
       <c r="AK5" t="n">
         <v>480.8090515136719</v>
@@ -32473,16 +32473,16 @@
         <v>0.2130197017444788</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.2719514541587664</v>
+        <v>0.2719513285240669</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.90640422707655</v>
+        <v>7.906403457089615</v>
       </c>
       <c r="AX5" t="n">
         <v>0.1346806173757082</v>
       </c>
       <c r="AY5" t="n">
-        <v>345.0662981117114</v>
+        <v>345.0664070971853</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
@@ -32621,7 +32621,7 @@
         <v>44588</v>
       </c>
       <c r="AD6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AE6" t="n">
         <v>259.8999938964844</v>
@@ -32878,13 +32878,13 @@
         <v>2.112306284098271</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.466314125273241</v>
+        <v>4.466313439357992</v>
       </c>
       <c r="AX7" t="n">
         <v>0.7993763265122695</v>
       </c>
       <c r="AY7" t="n">
-        <v>1761.884421896872</v>
+        <v>1761.884561231511</v>
       </c>
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="n">
@@ -33032,16 +33032,16 @@
         <v>238.0678646850586</v>
       </c>
       <c r="AG8" t="n">
-        <v>141.3805215835571</v>
+        <v>141.380521774292</v>
       </c>
       <c r="AH8" t="n">
         <v>-0.06740876360540082</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.5703719422285844</v>
+        <v>0.5703719401100136</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.6838802263461616</v>
+        <v>0.6838802240744581</v>
       </c>
       <c r="AK8" t="n">
         <v>316.3519592285156</v>
@@ -33077,16 +33077,16 @@
         <v>1.826433498852696</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.814942020173138</v>
+        <v>1.814942292466414</v>
       </c>
       <c r="AW8" t="n">
         <v>2.739770110452003</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.48736798099246</v>
+        <v>1.48736776838524</v>
       </c>
       <c r="AY8" t="n">
-        <v>17.30443510057087</v>
+        <v>17.30443078297695</v>
       </c>
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="n">
@@ -33101,7 +33101,7 @@
         <v>0.125</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.1859209976240574</v>
+        <v>0.185920971048155</v>
       </c>
     </row>
     <row r="9">
@@ -33353,7 +33353,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.004758677337975</v>
+        <v>1.004758650762073</v>
       </c>
     </row>
     <row r="5">
@@ -33363,7 +33363,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.325241163296551</v>
+        <v>1.325241181628873</v>
       </c>
     </row>
   </sheetData>
@@ -33540,31 +33540,31 @@
         <v>0.3434100978214519</v>
       </c>
       <c r="N2" t="n">
-        <v>1.092220073795788</v>
+        <v>1.088206643498178</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8022121066136985</v>
+        <v>0.7861584374107934</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5485310008180568</v>
+        <v>0.548229768195763</v>
       </c>
       <c r="Q2" t="n">
-        <v>4.34219397447991</v>
+        <v>4.356373931636823</v>
       </c>
       <c r="R2" t="n">
-        <v>1.558373150761916</v>
+        <v>1.657633391603621</v>
       </c>
       <c r="S2" t="n">
-        <v>5.614082409775221</v>
+        <v>5.615037008854257</v>
       </c>
       <c r="T2" t="n">
-        <v>1294.241645704557</v>
+        <v>1294.241611210162</v>
       </c>
       <c r="U2" t="n">
-        <v>326.4574711791196</v>
+        <v>326.4575145863986</v>
       </c>
       <c r="V2" t="n">
-        <v>3932.235364678148</v>
+        <v>3932.235105895843</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -33606,40 +33606,40 @@
         <v>0.8571428571428571</v>
       </c>
       <c r="K3" t="n">
-        <v>2.302173344845386</v>
+        <v>2.32569248257226</v>
       </c>
       <c r="L3" t="n">
         <v>1.909021129036435</v>
       </c>
       <c r="M3" t="n">
-        <v>2.11736460204461</v>
+        <v>2.122794043326742</v>
       </c>
       <c r="N3" t="n">
-        <v>4.498950977677493</v>
+        <v>4.535861383537314</v>
       </c>
       <c r="O3" t="n">
         <v>5.64739125254327</v>
       </c>
       <c r="P3" t="n">
-        <v>4.383784327716199</v>
+        <v>4.392305170270118</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.70173863176758</v>
+        <v>4.721838849302309</v>
       </c>
       <c r="R3" t="n">
-        <v>4.472610381430976</v>
+        <v>4.472610020252013</v>
       </c>
       <c r="S3" t="n">
-        <v>5.32289586819948</v>
+        <v>5.327536029074072</v>
       </c>
       <c r="T3" t="n">
-        <v>37.61311266929203</v>
+        <v>37.68033811281199</v>
       </c>
       <c r="U3" t="n">
-        <v>29.03108919779569</v>
+        <v>29.03108125280598</v>
       </c>
       <c r="V3" t="n">
-        <v>53.77283720016319</v>
+        <v>53.78835227736469</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -33681,40 +33681,40 @@
         <v>0.7333333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6207508029334536</v>
+        <v>0.6190589155451349</v>
       </c>
       <c r="L4" t="n">
         <v>0.6025882934899727</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4995290411268904</v>
+        <v>0.4992293585793043</v>
       </c>
       <c r="N4" t="n">
-        <v>1.419608536633934</v>
+        <v>1.417344520428265</v>
       </c>
       <c r="O4" t="n">
-        <v>1.457893969572734</v>
+        <v>1.457894169525142</v>
       </c>
       <c r="P4" t="n">
-        <v>1.160348102898738</v>
+        <v>1.160180085872293</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.575230573390149</v>
+        <v>3.579897908984224</v>
       </c>
       <c r="R4" t="n">
-        <v>2.818858845364753</v>
+        <v>2.818858975641196</v>
       </c>
       <c r="S4" t="n">
-        <v>3.222350670480818</v>
+        <v>3.222008409808982</v>
       </c>
       <c r="T4" t="n">
-        <v>866.0289464520158</v>
+        <v>865.7114575721538</v>
       </c>
       <c r="U4" t="n">
         <v>43.79898642891938</v>
       </c>
       <c r="V4" t="n">
-        <v>1153.586174382792</v>
+        <v>1153.530021406329</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -33732,10 +33732,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>1555.602311504603</v>
+        <v>1555.56502798931</v>
       </c>
       <c r="D5" t="n">
-        <v>103.7068207669735</v>
+        <v>103.7043351992873</v>
       </c>
       <c r="E5" t="n">
         <v>46.603882496</v>
@@ -33747,7 +33747,7 @@
         <v>92.5</v>
       </c>
       <c r="H5" t="n">
-        <v>83.73824603406287</v>
+        <v>83.73797611427895</v>
       </c>
       <c r="I5" t="n">
         <v>11</v>
@@ -33756,40 +33756,40 @@
         <v>0.6875</v>
       </c>
       <c r="K5" t="n">
-        <v>0.602418842187054</v>
+        <v>0.6032543267477628</v>
       </c>
       <c r="L5" t="n">
         <v>0.36599759150668</v>
       </c>
       <c r="M5" t="n">
-        <v>0.9517311656490965</v>
+        <v>0.9532271565085444</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8268161020198205</v>
+        <v>0.8299630548133961</v>
       </c>
       <c r="O5" t="n">
         <v>0.6630089197289767</v>
       </c>
       <c r="P5" t="n">
-        <v>1.112033032412568</v>
+        <v>1.117624060705567</v>
       </c>
       <c r="Q5" t="n">
-        <v>7.420286858034455</v>
+        <v>7.415538467703513</v>
       </c>
       <c r="R5" t="n">
-        <v>5.166674404931157</v>
+        <v>5.166675016355647</v>
       </c>
       <c r="S5" t="n">
-        <v>6.505243973415662</v>
+        <v>6.496680624340819</v>
       </c>
       <c r="T5" t="n">
-        <v>245.2808306734617</v>
+        <v>245.2888576396456</v>
       </c>
       <c r="U5" t="n">
-        <v>44.12575938183674</v>
+        <v>44.12576132930774</v>
       </c>
       <c r="V5" t="n">
-        <v>725.5940573645024</v>
+        <v>725.6252836240927</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -33831,7 +33831,7 @@
         <v>0.7692307692307693</v>
       </c>
       <c r="K6" t="n">
-        <v>1.812720301167298</v>
+        <v>1.812720319558048</v>
       </c>
       <c r="L6" t="n">
         <v>1.458053915836237</v>
@@ -33840,31 +33840,31 @@
         <v>1.678371606189715</v>
       </c>
       <c r="N6" t="n">
-        <v>8.771649781792979</v>
+        <v>8.771649783871471</v>
       </c>
       <c r="O6" t="n">
-        <v>5.547180409483333</v>
+        <v>5.547179879064097</v>
       </c>
       <c r="P6" t="n">
-        <v>7.080488032673799</v>
+        <v>7.080488156216358</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.799691664130643</v>
+        <v>6.799691543107836</v>
       </c>
       <c r="R6" t="n">
-        <v>5.630646402204134</v>
+        <v>5.630646590143852</v>
       </c>
       <c r="S6" t="n">
-        <v>6.672975609518104</v>
+        <v>6.672976309726673</v>
       </c>
       <c r="T6" t="n">
-        <v>314.9574001688075</v>
+        <v>314.9573836156215</v>
       </c>
       <c r="U6" t="n">
         <v>53.94008400813689</v>
       </c>
       <c r="V6" t="n">
-        <v>265.2923276373285</v>
+        <v>265.2923433055394</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -33882,10 +33882,10 @@
         <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>1535.173458698284</v>
+        <v>1535.172018099627</v>
       </c>
       <c r="D7" t="n">
-        <v>73.10349803325164</v>
+        <v>73.10342943331557</v>
       </c>
       <c r="E7" t="n">
         <v>42.68146012600977</v>
@@ -33897,7 +33897,7 @@
         <v>60</v>
       </c>
       <c r="H7" t="n">
-        <v>70.624149531824</v>
+        <v>70.62418296136896</v>
       </c>
       <c r="I7" t="n">
         <v>5</v>
@@ -33906,40 +33906,40 @@
         <v>0.2173913043478261</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4665411006894358</v>
+        <v>0.4642834621477322</v>
       </c>
       <c r="L7" t="n">
         <v>0.4813617568851039</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4987443448927734</v>
+        <v>0.4956804988968573</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7864843475713166</v>
+        <v>0.7904377129673438</v>
       </c>
       <c r="O7" t="n">
-        <v>0.6323055701729033</v>
+        <v>0.6200595659789243</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7096033710588255</v>
+        <v>0.7150778130999229</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.887948008219086</v>
+        <v>2.876711057562442</v>
       </c>
       <c r="R7" t="n">
-        <v>1.553378788100794</v>
+        <v>1.553378778316478</v>
       </c>
       <c r="S7" t="n">
-        <v>2.858621150870005</v>
+        <v>2.844641851372497</v>
       </c>
       <c r="T7" t="n">
-        <v>183.8926323340121</v>
+        <v>183.8801976218975</v>
       </c>
       <c r="U7" t="n">
-        <v>31.76826031250644</v>
+        <v>31.76824764460005</v>
       </c>
       <c r="V7" t="n">
-        <v>284.5797275896105</v>
+        <v>284.5569724795565</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -33950,221 +33950,221 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Networking / Interconnect / Custom Silicon</t>
+          <t>AI Infrastructure Software / Data Layer</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>3489.46198668451</v>
+        <v>2920.254139392</v>
       </c>
       <c r="D8" t="n">
-        <v>183.6558940360268</v>
+        <v>292.0254139392</v>
       </c>
       <c r="E8" t="n">
-        <v>62.60144128</v>
+        <v>102.866489344</v>
       </c>
       <c r="F8" t="n">
-        <v>70</v>
+        <v>81.5</v>
       </c>
       <c r="G8" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="H8" t="n">
-        <v>70.26981789400723</v>
+        <v>69.98953404053856</v>
       </c>
       <c r="I8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.7</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6398241451285166</v>
+        <v>0.3777087444868225</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6528417589211029</v>
+        <v>0.1774641123642821</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3923284772227236</v>
+        <v>0.314622831458762</v>
       </c>
       <c r="N8" t="n">
-        <v>1.663812998624125</v>
+        <v>0.5413339198835578</v>
       </c>
       <c r="O8" t="n">
-        <v>1.21511966113082</v>
+        <v>0.4797930673616737</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9693543575211638</v>
+        <v>0.4574678980230928</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.417619094334725</v>
+        <v>1.663878692367686</v>
       </c>
       <c r="R8" t="n">
-        <v>3.634858449899055</v>
+        <v>0.5876307380881448</v>
       </c>
       <c r="S8" t="n">
-        <v>8.097539331231138</v>
+        <v>5.882616316019644</v>
       </c>
       <c r="T8" t="n">
-        <v>189.0373678195527</v>
+        <v>58.90911188244031</v>
       </c>
       <c r="U8" t="n">
-        <v>27.42316729092432</v>
+        <v>9.57855454427702</v>
       </c>
       <c r="V8" t="n">
-        <v>316.4381551000415</v>
+        <v>239.2190190807541</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Narrow momentum</t>
+          <t>Broad strong momentum</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Infrastructure Software / Data Layer</t>
+          <t>Networking / Interconnect / Custom Silicon</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>2920.254139392</v>
+        <v>3489.46198668451</v>
       </c>
       <c r="D9" t="n">
-        <v>292.0254139392</v>
+        <v>183.6558940360268</v>
       </c>
       <c r="E9" t="n">
-        <v>102.866489344</v>
+        <v>62.60144128</v>
       </c>
       <c r="F9" t="n">
-        <v>81.5</v>
+        <v>68.80952380952381</v>
       </c>
       <c r="G9" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="H9" t="n">
-        <v>69.98953404053856</v>
+        <v>69.83171469820411</v>
       </c>
       <c r="I9" t="n">
         <v>7</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3777087444868225</v>
+        <v>0.6378404499251211</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1774641123642821</v>
+        <v>0.6528417589211029</v>
       </c>
       <c r="M9" t="n">
-        <v>0.314622831458762</v>
+        <v>0.3919198041105227</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5382278247319954</v>
+        <v>1.666166268205304</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4797931301790235</v>
+        <v>1.215740882734476</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4573162833411457</v>
+        <v>0.9694253581468586</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.664224341322761</v>
+        <v>6.409025937524198</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5876307380881448</v>
+        <v>3.634856968840582</v>
       </c>
       <c r="S9" t="n">
-        <v>5.882633655444419</v>
+        <v>8.096376860639081</v>
       </c>
       <c r="T9" t="n">
-        <v>58.90908333599337</v>
+        <v>189.0270949697847</v>
       </c>
       <c r="U9" t="n">
-        <v>9.57855454427702</v>
+        <v>27.61561905140535</v>
       </c>
       <c r="V9" t="n">
-        <v>239.2189359620361</v>
+        <v>316.434743129565</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Broad strong momentum</t>
+          <t>Narrow momentum</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Other / Indirect AI Infrastructure</t>
+          <t>Energy / Grid / Nuclear</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>52.31110144</v>
+        <v>1264.344941821027</v>
       </c>
       <c r="D10" t="n">
-        <v>26.15555072</v>
+        <v>70.24138565672374</v>
       </c>
       <c r="E10" t="n">
-        <v>26.15555072</v>
+        <v>48.482545664</v>
       </c>
       <c r="F10" t="n">
-        <v>32.5</v>
+        <v>39.47368421052632</v>
       </c>
       <c r="G10" t="n">
-        <v>32.5</v>
+        <v>25</v>
       </c>
       <c r="H10" t="n">
-        <v>55.9483614191703</v>
+        <v>58.50521330611095</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="K10" t="n">
-        <v>0.283588373698309</v>
+        <v>0.0006538885477019921</v>
       </c>
       <c r="L10" t="n">
-        <v>0.283588373698309</v>
+        <v>0.01365857008026872</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8871644737680049</v>
+        <v>0.1768515669898564</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1797209584990114</v>
+        <v>0.1155500209017505</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1797209584990114</v>
+        <v>0.04124091896544591</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9627934440560079</v>
+        <v>0.2838186973064511</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3446652022407248</v>
+        <v>2.628157069160592</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3446652022407248</v>
+        <v>1.955239309055402</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3446652022407248</v>
+        <v>2.174347103980354</v>
       </c>
       <c r="T10" t="n">
-        <v>11.86353525953863</v>
+        <v>76.03631270495261</v>
       </c>
       <c r="U10" t="n">
-        <v>11.86353525953863</v>
+        <v>12.06533983470229</v>
       </c>
       <c r="V10" t="n">
-        <v>22.03597645158747</v>
+        <v>105.2213088464409</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -34175,150 +34175,150 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Cloud / Compute Services</t>
+          <t>Other / Indirect AI Infrastructure</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>13703.1779387205</v>
+        <v>52.31110144</v>
       </c>
       <c r="D11" t="n">
-        <v>1141.931494893375</v>
+        <v>26.15555072</v>
       </c>
       <c r="E11" t="n">
-        <v>365.162725376</v>
+        <v>26.15555072</v>
       </c>
       <c r="F11" t="n">
-        <v>43.75</v>
+        <v>32.5</v>
       </c>
       <c r="G11" t="n">
-        <v>55</v>
+        <v>32.5</v>
       </c>
       <c r="H11" t="n">
-        <v>55.63850968874749</v>
+        <v>55.9483614191703</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6254044512440996</v>
+        <v>0.283588373698309</v>
       </c>
       <c r="L11" t="n">
-        <v>0.07557806082507523</v>
+        <v>0.283588373698309</v>
       </c>
       <c r="M11" t="n">
-        <v>0.06793912207436754</v>
+        <v>0.8871644737680049</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6548739845366891</v>
+        <v>0.1910751721312152</v>
       </c>
       <c r="O11" t="n">
-        <v>0.09747388656486589</v>
+        <v>0.1910751721312152</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2151356215795066</v>
+        <v>0.9838290287746984</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.638205854858409</v>
+        <v>0.3260812159867732</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6086879284348038</v>
+        <v>0.3260812159867732</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9134742876500572</v>
+        <v>0.3260812159867732</v>
       </c>
       <c r="T11" t="n">
-        <v>1238.148603961386</v>
+        <v>11.86353121011671</v>
       </c>
       <c r="U11" t="n">
-        <v>13.72423560572188</v>
+        <v>11.86353121011671</v>
       </c>
       <c r="V11" t="n">
-        <v>2965.490517598078</v>
+        <v>22.03596894935434</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Narrow momentum</t>
+          <t>Weak breadth</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Energy / Grid / Nuclear</t>
+          <t>AI Cloud / Compute Services</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>1264.344941821027</v>
+        <v>13703.1779387205</v>
       </c>
       <c r="D12" t="n">
-        <v>70.24138565672374</v>
+        <v>1141.931494893375</v>
       </c>
       <c r="E12" t="n">
-        <v>48.482545664</v>
+        <v>365.162725376</v>
       </c>
       <c r="F12" t="n">
-        <v>36.57894736842105</v>
+        <v>43.75</v>
       </c>
       <c r="G12" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="H12" t="n">
-        <v>53.08343092677666</v>
+        <v>55.63850968874749</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.25</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0006539051508513387</v>
+        <v>0.6254044512440996</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01365857008026872</v>
+        <v>0.07557806082507523</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1768516147597899</v>
+        <v>0.06793912207436754</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1187977304679111</v>
+        <v>0.6548739952772858</v>
       </c>
       <c r="O12" t="n">
-        <v>0.05476652285708949</v>
+        <v>0.09747388656486589</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2889605845230797</v>
+        <v>0.2151356613685093</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.624680011352741</v>
+        <v>0.6382059109525209</v>
       </c>
       <c r="R12" t="n">
-        <v>1.955239146497938</v>
+        <v>0.6086879284348038</v>
       </c>
       <c r="S12" t="n">
-        <v>2.164315833743631</v>
+        <v>0.9134742735621338</v>
       </c>
       <c r="T12" t="n">
-        <v>76.03628992535306</v>
+        <v>1238.14896047547</v>
       </c>
       <c r="U12" t="n">
-        <v>12.06533983470229</v>
+        <v>13.72423717242735</v>
       </c>
       <c r="V12" t="n">
-        <v>105.2212765705061</v>
+        <v>2965.491653653544</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Weak breadth</t>
+          <t>Narrow momentum</t>
         </is>
       </c>
     </row>
@@ -34356,40 +34356,40 @@
         <v>0.25</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1786559248460641</v>
+        <v>0.1756816215555455</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1249283689773661</v>
+        <v>0.1247165643430652</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03562357087060993</v>
+        <v>0.03434218224727722</v>
       </c>
       <c r="N13" t="n">
-        <v>0.208910463376162</v>
+        <v>0.2128296146247252</v>
       </c>
       <c r="O13" t="n">
-        <v>0.08476021220505459</v>
+        <v>0.08639771424472786</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.05575687500047868</v>
+        <v>-0.05437184633197861</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.319441819756381</v>
+        <v>1.292582712884851</v>
       </c>
       <c r="R13" t="n">
-        <v>1.214252577560329</v>
+        <v>1.1812775791199</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9987626198624945</v>
+        <v>0.9941293554850736</v>
       </c>
       <c r="T13" t="n">
-        <v>88.37682970124175</v>
+        <v>88.17238217730429</v>
       </c>
       <c r="U13" t="n">
-        <v>81.60585106478186</v>
+        <v>81.20221154175901</v>
       </c>
       <c r="V13" t="n">
-        <v>109.8678386421434</v>
+        <v>109.7776805544961</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -34431,40 +34431,40 @@
         <v>0.6</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1544858001450093</v>
+        <v>0.1544858033064877</v>
       </c>
       <c r="L14" t="n">
         <v>0.08914955131736912</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.06026940487221748</v>
+        <v>-0.06026940256908837</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2956013797375714</v>
+        <v>0.2808188176239643</v>
       </c>
       <c r="O14" t="n">
         <v>0.1723642781731225</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2855933949824077</v>
+        <v>0.283302941271096</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.6119061097602642</v>
+        <v>0.6143377823147705</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4988414754976604</v>
+        <v>0.4988416235560018</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7861110101580716</v>
+        <v>0.7864536982320487</v>
       </c>
       <c r="T14" t="n">
-        <v>17.56391423017507</v>
+        <v>17.5639142979959</v>
       </c>
       <c r="U14" t="n">
-        <v>3.219371490319287</v>
+        <v>3.219371506453886</v>
       </c>
       <c r="V14" t="n">
-        <v>3.406808200448244</v>
+        <v>3.406808216984382</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
